--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -37,580 +37,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>03.09.20261</t>
-  </si>
-  <si>
-    <t>03.09.20262</t>
-  </si>
-  <si>
-    <t>03.09.20263</t>
-  </si>
-  <si>
-    <t>03.09.20264</t>
-  </si>
-  <si>
-    <t>03.09.20265</t>
-  </si>
-  <si>
-    <t>03.09.20266</t>
-  </si>
-  <si>
-    <t>03.09.20267</t>
-  </si>
-  <si>
-    <t>03.09.20268</t>
-  </si>
-  <si>
-    <t>03.09.20269</t>
-  </si>
-  <si>
-    <t>03.09.202610</t>
-  </si>
-  <si>
-    <t>03.09.202611</t>
-  </si>
-  <si>
-    <t>03.09.202612</t>
-  </si>
-  <si>
-    <t>03.09.202613</t>
-  </si>
-  <si>
-    <t>03.09.202614</t>
-  </si>
-  <si>
-    <t>03.09.202615</t>
-  </si>
-  <si>
-    <t>03.09.202616</t>
-  </si>
-  <si>
-    <t>03.09.202617</t>
-  </si>
-  <si>
-    <t>03.09.202618</t>
-  </si>
-  <si>
-    <t>03.09.202619</t>
-  </si>
-  <si>
-    <t>03.09.202620</t>
-  </si>
-  <si>
-    <t>03.09.202621</t>
-  </si>
-  <si>
-    <t>03.09.202622</t>
-  </si>
-  <si>
-    <t>03.09.202623</t>
-  </si>
-  <si>
-    <t>03.09.202624</t>
-  </si>
-  <si>
-    <t>03.09.202625</t>
-  </si>
-  <si>
-    <t>03.09.202626</t>
-  </si>
-  <si>
-    <t>03.09.202627</t>
-  </si>
-  <si>
-    <t>03.09.202628</t>
-  </si>
-  <si>
-    <t>03.09.202629</t>
-  </si>
-  <si>
-    <t>03.09.202630</t>
-  </si>
-  <si>
-    <t>03.09.202631</t>
-  </si>
-  <si>
-    <t>03.09.202632</t>
-  </si>
-  <si>
-    <t>03.09.202633</t>
-  </si>
-  <si>
-    <t>03.09.202634</t>
-  </si>
-  <si>
-    <t>03.09.202635</t>
-  </si>
-  <si>
-    <t>03.09.202636</t>
-  </si>
-  <si>
-    <t>03.09.202637</t>
-  </si>
-  <si>
-    <t>03.09.202638</t>
-  </si>
-  <si>
-    <t>03.09.202639</t>
-  </si>
-  <si>
-    <t>03.09.202640</t>
-  </si>
-  <si>
-    <t>03.09.202641</t>
-  </si>
-  <si>
-    <t>03.09.202642</t>
-  </si>
-  <si>
-    <t>03.09.202643</t>
-  </si>
-  <si>
-    <t>03.09.202644</t>
-  </si>
-  <si>
-    <t>03.09.202645</t>
-  </si>
-  <si>
-    <t>03.09.202646</t>
-  </si>
-  <si>
-    <t>03.09.202647</t>
-  </si>
-  <si>
-    <t>03.09.202648</t>
-  </si>
-  <si>
-    <t>03.09.202649</t>
-  </si>
-  <si>
-    <t>03.09.202650</t>
-  </si>
-  <si>
-    <t>03.09.202651</t>
-  </si>
-  <si>
-    <t>03.09.202652</t>
-  </si>
-  <si>
-    <t>03.09.202653</t>
-  </si>
-  <si>
-    <t>03.09.202654</t>
-  </si>
-  <si>
-    <t>03.09.202655</t>
-  </si>
-  <si>
-    <t>03.09.202656</t>
-  </si>
-  <si>
-    <t>03.09.202657</t>
-  </si>
-  <si>
-    <t>03.09.202658</t>
-  </si>
-  <si>
-    <t>03.09.202659</t>
-  </si>
-  <si>
-    <t>03.09.202660</t>
-  </si>
-  <si>
-    <t>03.09.202661</t>
-  </si>
-  <si>
-    <t>03.09.202662</t>
-  </si>
-  <si>
-    <t>03.09.202663</t>
-  </si>
-  <si>
-    <t>03.09.202664</t>
-  </si>
-  <si>
-    <t>03.09.202665</t>
-  </si>
-  <si>
-    <t>03.09.202666</t>
-  </si>
-  <si>
-    <t>03.09.202667</t>
-  </si>
-  <si>
-    <t>03.09.202668</t>
-  </si>
-  <si>
-    <t>03.09.202669</t>
-  </si>
-  <si>
-    <t>03.09.202670</t>
-  </si>
-  <si>
-    <t>03.09.202671</t>
-  </si>
-  <si>
-    <t>03.09.202672</t>
-  </si>
-  <si>
-    <t>03.09.202673</t>
-  </si>
-  <si>
-    <t>03.09.202674</t>
-  </si>
-  <si>
-    <t>03.09.202675</t>
-  </si>
-  <si>
-    <t>03.09.202676</t>
-  </si>
-  <si>
-    <t>03.09.202677</t>
-  </si>
-  <si>
-    <t>03.09.202678</t>
-  </si>
-  <si>
-    <t>03.09.202679</t>
-  </si>
-  <si>
-    <t>03.09.202680</t>
-  </si>
-  <si>
-    <t>03.09.202681</t>
-  </si>
-  <si>
-    <t>03.09.202682</t>
-  </si>
-  <si>
-    <t>03.09.202683</t>
-  </si>
-  <si>
-    <t>03.09.202684</t>
-  </si>
-  <si>
-    <t>03.09.202685</t>
-  </si>
-  <si>
-    <t>03.09.202686</t>
-  </si>
-  <si>
-    <t>03.09.202687</t>
-  </si>
-  <si>
-    <t>03.09.202688</t>
-  </si>
-  <si>
-    <t>03.09.202689</t>
-  </si>
-  <si>
-    <t>03.09.202690</t>
-  </si>
-  <si>
-    <t>03.09.202691</t>
-  </si>
-  <si>
-    <t>03.09.202692</t>
-  </si>
-  <si>
-    <t>03.09.202693</t>
-  </si>
-  <si>
-    <t>03.09.202694</t>
-  </si>
-  <si>
-    <t>03.09.202695</t>
-  </si>
-  <si>
-    <t>03.09.202696</t>
-  </si>
-  <si>
-    <t>04.09.20261</t>
-  </si>
-  <si>
-    <t>04.09.20262</t>
-  </si>
-  <si>
-    <t>04.09.20263</t>
-  </si>
-  <si>
-    <t>04.09.20264</t>
-  </si>
-  <si>
-    <t>04.09.20265</t>
-  </si>
-  <si>
-    <t>04.09.20266</t>
-  </si>
-  <si>
-    <t>04.09.20267</t>
-  </si>
-  <si>
-    <t>04.09.20268</t>
-  </si>
-  <si>
-    <t>04.09.20269</t>
-  </si>
-  <si>
-    <t>04.09.202610</t>
-  </si>
-  <si>
-    <t>04.09.202611</t>
-  </si>
-  <si>
-    <t>04.09.202612</t>
-  </si>
-  <si>
-    <t>04.09.202613</t>
-  </si>
-  <si>
-    <t>04.09.202614</t>
-  </si>
-  <si>
-    <t>04.09.202615</t>
-  </si>
-  <si>
-    <t>04.09.202616</t>
-  </si>
-  <si>
-    <t>04.09.202617</t>
-  </si>
-  <si>
-    <t>04.09.202618</t>
-  </si>
-  <si>
-    <t>04.09.202619</t>
-  </si>
-  <si>
-    <t>04.09.202620</t>
-  </si>
-  <si>
-    <t>04.09.202621</t>
-  </si>
-  <si>
-    <t>04.09.202622</t>
-  </si>
-  <si>
-    <t>04.09.202623</t>
-  </si>
-  <si>
-    <t>04.09.202624</t>
-  </si>
-  <si>
-    <t>04.09.202625</t>
-  </si>
-  <si>
-    <t>04.09.202626</t>
-  </si>
-  <si>
-    <t>04.09.202627</t>
-  </si>
-  <si>
-    <t>04.09.202628</t>
-  </si>
-  <si>
-    <t>04.09.202629</t>
-  </si>
-  <si>
-    <t>04.09.202630</t>
-  </si>
-  <si>
-    <t>04.09.202631</t>
-  </si>
-  <si>
-    <t>04.09.202632</t>
-  </si>
-  <si>
-    <t>04.09.202633</t>
-  </si>
-  <si>
-    <t>04.09.202634</t>
-  </si>
-  <si>
-    <t>04.09.202635</t>
-  </si>
-  <si>
-    <t>04.09.202636</t>
-  </si>
-  <si>
-    <t>04.09.202637</t>
-  </si>
-  <si>
-    <t>04.09.202638</t>
-  </si>
-  <si>
-    <t>04.09.202639</t>
-  </si>
-  <si>
-    <t>04.09.202640</t>
-  </si>
-  <si>
-    <t>04.09.202641</t>
-  </si>
-  <si>
-    <t>04.09.202642</t>
-  </si>
-  <si>
-    <t>04.09.202643</t>
-  </si>
-  <si>
-    <t>04.09.202644</t>
-  </si>
-  <si>
-    <t>04.09.202645</t>
-  </si>
-  <si>
-    <t>04.09.202646</t>
-  </si>
-  <si>
-    <t>04.09.202647</t>
-  </si>
-  <si>
-    <t>04.09.202648</t>
-  </si>
-  <si>
-    <t>04.09.202649</t>
-  </si>
-  <si>
-    <t>04.09.202650</t>
-  </si>
-  <si>
-    <t>04.09.202651</t>
-  </si>
-  <si>
-    <t>04.09.202652</t>
-  </si>
-  <si>
-    <t>04.09.202653</t>
-  </si>
-  <si>
-    <t>04.09.202654</t>
-  </si>
-  <si>
-    <t>04.09.202655</t>
-  </si>
-  <si>
-    <t>04.09.202656</t>
-  </si>
-  <si>
-    <t>04.09.202657</t>
-  </si>
-  <si>
-    <t>04.09.202658</t>
-  </si>
-  <si>
-    <t>04.09.202659</t>
-  </si>
-  <si>
-    <t>04.09.202660</t>
-  </si>
-  <si>
-    <t>04.09.202661</t>
-  </si>
-  <si>
-    <t>04.09.202662</t>
-  </si>
-  <si>
-    <t>04.09.202663</t>
-  </si>
-  <si>
-    <t>04.09.202664</t>
-  </si>
-  <si>
-    <t>04.09.202665</t>
-  </si>
-  <si>
-    <t>04.09.202666</t>
-  </si>
-  <si>
-    <t>04.09.202667</t>
-  </si>
-  <si>
-    <t>04.09.202668</t>
-  </si>
-  <si>
-    <t>04.09.202669</t>
-  </si>
-  <si>
-    <t>04.09.202670</t>
-  </si>
-  <si>
-    <t>04.09.202671</t>
-  </si>
-  <si>
-    <t>04.09.202672</t>
-  </si>
-  <si>
-    <t>04.09.202673</t>
-  </si>
-  <si>
-    <t>04.09.202674</t>
-  </si>
-  <si>
-    <t>04.09.202675</t>
-  </si>
-  <si>
-    <t>04.09.202676</t>
-  </si>
-  <si>
-    <t>04.09.202677</t>
-  </si>
-  <si>
-    <t>04.09.202678</t>
-  </si>
-  <si>
-    <t>04.09.202679</t>
-  </si>
-  <si>
-    <t>04.09.202680</t>
-  </si>
-  <si>
-    <t>04.09.202681</t>
-  </si>
-  <si>
-    <t>04.09.202682</t>
-  </si>
-  <si>
-    <t>04.09.202683</t>
-  </si>
-  <si>
-    <t>04.09.202684</t>
-  </si>
-  <si>
-    <t>04.09.202685</t>
-  </si>
-  <si>
-    <t>04.09.202686</t>
-  </si>
-  <si>
-    <t>04.09.202687</t>
-  </si>
-  <si>
-    <t>04.09.202688</t>
-  </si>
-  <si>
-    <t>04.09.202689</t>
-  </si>
-  <si>
-    <t>04.09.202690</t>
-  </si>
-  <si>
-    <t>04.09.202691</t>
-  </si>
-  <si>
-    <t>04.09.202692</t>
-  </si>
-  <si>
-    <t>04.09.202693</t>
-  </si>
-  <si>
-    <t>04.09.202694</t>
-  </si>
-  <si>
-    <t>04.09.202695</t>
-  </si>
-  <si>
-    <t>04.09.202696</t>
+    <t>12.09.20261</t>
+  </si>
+  <si>
+    <t>12.09.20262</t>
+  </si>
+  <si>
+    <t>12.09.20263</t>
+  </si>
+  <si>
+    <t>12.09.20264</t>
+  </si>
+  <si>
+    <t>12.09.20265</t>
+  </si>
+  <si>
+    <t>12.09.20266</t>
+  </si>
+  <si>
+    <t>12.09.20267</t>
+  </si>
+  <si>
+    <t>12.09.20268</t>
+  </si>
+  <si>
+    <t>12.09.20269</t>
+  </si>
+  <si>
+    <t>12.09.202610</t>
+  </si>
+  <si>
+    <t>12.09.202611</t>
+  </si>
+  <si>
+    <t>12.09.202612</t>
+  </si>
+  <si>
+    <t>12.09.202613</t>
+  </si>
+  <si>
+    <t>12.09.202614</t>
+  </si>
+  <si>
+    <t>12.09.202615</t>
+  </si>
+  <si>
+    <t>12.09.202616</t>
+  </si>
+  <si>
+    <t>12.09.202617</t>
+  </si>
+  <si>
+    <t>12.09.202618</t>
+  </si>
+  <si>
+    <t>12.09.202619</t>
+  </si>
+  <si>
+    <t>12.09.202620</t>
+  </si>
+  <si>
+    <t>12.09.202621</t>
+  </si>
+  <si>
+    <t>12.09.202622</t>
+  </si>
+  <si>
+    <t>12.09.202623</t>
+  </si>
+  <si>
+    <t>12.09.202624</t>
+  </si>
+  <si>
+    <t>12.09.202625</t>
+  </si>
+  <si>
+    <t>12.09.202626</t>
+  </si>
+  <si>
+    <t>12.09.202627</t>
+  </si>
+  <si>
+    <t>12.09.202628</t>
+  </si>
+  <si>
+    <t>12.09.202629</t>
+  </si>
+  <si>
+    <t>12.09.202630</t>
+  </si>
+  <si>
+    <t>12.09.202631</t>
+  </si>
+  <si>
+    <t>12.09.202632</t>
+  </si>
+  <si>
+    <t>12.09.202633</t>
+  </si>
+  <si>
+    <t>12.09.202634</t>
+  </si>
+  <si>
+    <t>12.09.202635</t>
+  </si>
+  <si>
+    <t>12.09.202636</t>
+  </si>
+  <si>
+    <t>12.09.202637</t>
+  </si>
+  <si>
+    <t>12.09.202638</t>
+  </si>
+  <si>
+    <t>12.09.202639</t>
+  </si>
+  <si>
+    <t>12.09.202640</t>
+  </si>
+  <si>
+    <t>12.09.202641</t>
+  </si>
+  <si>
+    <t>12.09.202642</t>
+  </si>
+  <si>
+    <t>12.09.202643</t>
+  </si>
+  <si>
+    <t>12.09.202644</t>
+  </si>
+  <si>
+    <t>12.09.202645</t>
+  </si>
+  <si>
+    <t>12.09.202646</t>
+  </si>
+  <si>
+    <t>12.09.202647</t>
+  </si>
+  <si>
+    <t>12.09.202648</t>
+  </si>
+  <si>
+    <t>12.09.202649</t>
+  </si>
+  <si>
+    <t>12.09.202650</t>
+  </si>
+  <si>
+    <t>12.09.202651</t>
+  </si>
+  <si>
+    <t>12.09.202652</t>
+  </si>
+  <si>
+    <t>12.09.202653</t>
+  </si>
+  <si>
+    <t>12.09.202654</t>
+  </si>
+  <si>
+    <t>12.09.202655</t>
+  </si>
+  <si>
+    <t>12.09.202656</t>
+  </si>
+  <si>
+    <t>12.09.202657</t>
+  </si>
+  <si>
+    <t>12.09.202658</t>
+  </si>
+  <si>
+    <t>12.09.202659</t>
+  </si>
+  <si>
+    <t>12.09.202660</t>
+  </si>
+  <si>
+    <t>12.09.202661</t>
+  </si>
+  <si>
+    <t>12.09.202662</t>
+  </si>
+  <si>
+    <t>12.09.202663</t>
+  </si>
+  <si>
+    <t>12.09.202664</t>
+  </si>
+  <si>
+    <t>12.09.202665</t>
+  </si>
+  <si>
+    <t>12.09.202666</t>
+  </si>
+  <si>
+    <t>12.09.202667</t>
+  </si>
+  <si>
+    <t>12.09.202668</t>
+  </si>
+  <si>
+    <t>12.09.202669</t>
+  </si>
+  <si>
+    <t>12.09.202670</t>
+  </si>
+  <si>
+    <t>12.09.202671</t>
+  </si>
+  <si>
+    <t>12.09.202672</t>
+  </si>
+  <si>
+    <t>12.09.202673</t>
+  </si>
+  <si>
+    <t>12.09.202674</t>
+  </si>
+  <si>
+    <t>12.09.202675</t>
+  </si>
+  <si>
+    <t>12.09.202676</t>
+  </si>
+  <si>
+    <t>12.09.202677</t>
+  </si>
+  <si>
+    <t>12.09.202678</t>
+  </si>
+  <si>
+    <t>12.09.202679</t>
+  </si>
+  <si>
+    <t>12.09.202680</t>
+  </si>
+  <si>
+    <t>12.09.202681</t>
+  </si>
+  <si>
+    <t>12.09.202682</t>
+  </si>
+  <si>
+    <t>12.09.202683</t>
+  </si>
+  <si>
+    <t>12.09.202684</t>
+  </si>
+  <si>
+    <t>12.09.202685</t>
+  </si>
+  <si>
+    <t>12.09.202686</t>
+  </si>
+  <si>
+    <t>12.09.202687</t>
+  </si>
+  <si>
+    <t>12.09.202688</t>
+  </si>
+  <si>
+    <t>12.09.202689</t>
+  </si>
+  <si>
+    <t>12.09.202690</t>
+  </si>
+  <si>
+    <t>12.09.202691</t>
+  </si>
+  <si>
+    <t>12.09.202692</t>
+  </si>
+  <si>
+    <t>12.09.202693</t>
+  </si>
+  <si>
+    <t>12.09.202694</t>
+  </si>
+  <si>
+    <t>12.09.202695</t>
+  </si>
+  <si>
+    <t>12.09.202696</t>
+  </si>
+  <si>
+    <t>13.09.20261</t>
+  </si>
+  <si>
+    <t>13.09.20262</t>
+  </si>
+  <si>
+    <t>13.09.20263</t>
+  </si>
+  <si>
+    <t>13.09.20264</t>
+  </si>
+  <si>
+    <t>13.09.20265</t>
+  </si>
+  <si>
+    <t>13.09.20266</t>
+  </si>
+  <si>
+    <t>13.09.20267</t>
+  </si>
+  <si>
+    <t>13.09.20268</t>
+  </si>
+  <si>
+    <t>13.09.20269</t>
+  </si>
+  <si>
+    <t>13.09.202610</t>
+  </si>
+  <si>
+    <t>13.09.202611</t>
+  </si>
+  <si>
+    <t>13.09.202612</t>
+  </si>
+  <si>
+    <t>13.09.202613</t>
+  </si>
+  <si>
+    <t>13.09.202614</t>
+  </si>
+  <si>
+    <t>13.09.202615</t>
+  </si>
+  <si>
+    <t>13.09.202616</t>
+  </si>
+  <si>
+    <t>13.09.202617</t>
+  </si>
+  <si>
+    <t>13.09.202618</t>
+  </si>
+  <si>
+    <t>13.09.202619</t>
+  </si>
+  <si>
+    <t>13.09.202620</t>
+  </si>
+  <si>
+    <t>13.09.202621</t>
+  </si>
+  <si>
+    <t>13.09.202622</t>
+  </si>
+  <si>
+    <t>13.09.202623</t>
+  </si>
+  <si>
+    <t>13.09.202624</t>
+  </si>
+  <si>
+    <t>13.09.202625</t>
+  </si>
+  <si>
+    <t>13.09.202626</t>
+  </si>
+  <si>
+    <t>13.09.202627</t>
+  </si>
+  <si>
+    <t>13.09.202628</t>
+  </si>
+  <si>
+    <t>13.09.202629</t>
+  </si>
+  <si>
+    <t>13.09.202630</t>
+  </si>
+  <si>
+    <t>13.09.202631</t>
+  </si>
+  <si>
+    <t>13.09.202632</t>
+  </si>
+  <si>
+    <t>13.09.202633</t>
+  </si>
+  <si>
+    <t>13.09.202634</t>
+  </si>
+  <si>
+    <t>13.09.202635</t>
+  </si>
+  <si>
+    <t>13.09.202636</t>
+  </si>
+  <si>
+    <t>13.09.202637</t>
+  </si>
+  <si>
+    <t>13.09.202638</t>
+  </si>
+  <si>
+    <t>13.09.202639</t>
+  </si>
+  <si>
+    <t>13.09.202640</t>
+  </si>
+  <si>
+    <t>13.09.202641</t>
+  </si>
+  <si>
+    <t>13.09.202642</t>
+  </si>
+  <si>
+    <t>13.09.202643</t>
+  </si>
+  <si>
+    <t>13.09.202644</t>
+  </si>
+  <si>
+    <t>13.09.202645</t>
+  </si>
+  <si>
+    <t>13.09.202646</t>
+  </si>
+  <si>
+    <t>13.09.202647</t>
+  </si>
+  <si>
+    <t>13.09.202648</t>
+  </si>
+  <si>
+    <t>13.09.202649</t>
+  </si>
+  <si>
+    <t>13.09.202650</t>
+  </si>
+  <si>
+    <t>13.09.202651</t>
+  </si>
+  <si>
+    <t>13.09.202652</t>
+  </si>
+  <si>
+    <t>13.09.202653</t>
+  </si>
+  <si>
+    <t>13.09.202654</t>
+  </si>
+  <si>
+    <t>13.09.202655</t>
+  </si>
+  <si>
+    <t>13.09.202656</t>
+  </si>
+  <si>
+    <t>13.09.202657</t>
+  </si>
+  <si>
+    <t>13.09.202658</t>
+  </si>
+  <si>
+    <t>13.09.202659</t>
+  </si>
+  <si>
+    <t>13.09.202660</t>
+  </si>
+  <si>
+    <t>13.09.202661</t>
+  </si>
+  <si>
+    <t>13.09.202662</t>
+  </si>
+  <si>
+    <t>13.09.202663</t>
+  </si>
+  <si>
+    <t>13.09.202664</t>
+  </si>
+  <si>
+    <t>13.09.202665</t>
+  </si>
+  <si>
+    <t>13.09.202666</t>
+  </si>
+  <si>
+    <t>13.09.202667</t>
+  </si>
+  <si>
+    <t>13.09.202668</t>
+  </si>
+  <si>
+    <t>13.09.202669</t>
+  </si>
+  <si>
+    <t>13.09.202670</t>
+  </si>
+  <si>
+    <t>13.09.202671</t>
+  </si>
+  <si>
+    <t>13.09.202672</t>
+  </si>
+  <si>
+    <t>13.09.202673</t>
+  </si>
+  <si>
+    <t>13.09.202674</t>
+  </si>
+  <si>
+    <t>13.09.202675</t>
+  </si>
+  <si>
+    <t>13.09.202676</t>
+  </si>
+  <si>
+    <t>13.09.202677</t>
+  </si>
+  <si>
+    <t>13.09.202678</t>
+  </si>
+  <si>
+    <t>13.09.202679</t>
+  </si>
+  <si>
+    <t>13.09.202680</t>
+  </si>
+  <si>
+    <t>13.09.202681</t>
+  </si>
+  <si>
+    <t>13.09.202682</t>
+  </si>
+  <si>
+    <t>13.09.202683</t>
+  </si>
+  <si>
+    <t>13.09.202684</t>
+  </si>
+  <si>
+    <t>13.09.202685</t>
+  </si>
+  <si>
+    <t>13.09.202686</t>
+  </si>
+  <si>
+    <t>13.09.202687</t>
+  </si>
+  <si>
+    <t>13.09.202688</t>
+  </si>
+  <si>
+    <t>13.09.202689</t>
+  </si>
+  <si>
+    <t>13.09.202690</t>
+  </si>
+  <si>
+    <t>13.09.202691</t>
+  </si>
+  <si>
+    <t>13.09.202692</t>
+  </si>
+  <si>
+    <t>13.09.202693</t>
+  </si>
+  <si>
+    <t>13.09.202694</t>
+  </si>
+  <si>
+    <t>13.09.202695</t>
+  </si>
+  <si>
+    <t>13.09.202696</t>
   </si>
 </sst>
 </file>
@@ -1000,13 +1000,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46268</v>
+        <v>46277</v>
       </c>
       <c r="B2">
-        <v>28.402</v>
+        <v>19.348</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>0.523</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46268.01041666666</v>
+        <v>46277.01041666666</v>
       </c>
       <c r="B3">
-        <v>22.741</v>
+        <v>47.439</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1046,16 +1046,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46268.02083333334</v>
+        <v>46277.02083333334</v>
       </c>
       <c r="B4">
-        <v>9.307</v>
+        <v>24.165</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>34.5</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1069,16 +1069,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46268.03125</v>
+        <v>46277.03125</v>
       </c>
       <c r="B5">
-        <v>10.224</v>
+        <v>7.296</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>34.5</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1092,16 +1092,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46268.04166666666</v>
+        <v>46277.04166666666</v>
       </c>
       <c r="B6">
-        <v>8.250999999999999</v>
+        <v>26.527</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>25.25</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1115,16 +1115,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46268.05208333334</v>
+        <v>46277.05208333334</v>
       </c>
       <c r="B7">
-        <v>0.386</v>
+        <v>26.08</v>
       </c>
       <c r="C7">
-        <v>0.107</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>25.25</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1138,16 +1138,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46268.0625</v>
+        <v>46277.0625</v>
       </c>
       <c r="B8">
-        <v>0.174</v>
+        <v>21.308</v>
       </c>
       <c r="C8">
-        <v>1.028</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>25</v>
+        <v>25.25</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1161,16 +1161,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46268.07291666666</v>
+        <v>46277.07291666666</v>
       </c>
       <c r="B9">
-        <v>0.043</v>
+        <v>19.603</v>
       </c>
       <c r="C9">
-        <v>0.414</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>25</v>
+        <v>25.25</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1184,16 +1184,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46268.08333333334</v>
+        <v>46277.08333333334</v>
       </c>
       <c r="B10">
-        <v>3.401</v>
+        <v>9.689</v>
       </c>
       <c r="C10">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>25.25</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1207,16 +1207,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46268.09375</v>
+        <v>46277.09375</v>
       </c>
       <c r="B11">
-        <v>2.385</v>
+        <v>1.686</v>
       </c>
       <c r="C11">
-        <v>0.003</v>
+        <v>0.039</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>25.25</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1230,16 +1230,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46268.10416666666</v>
+        <v>46277.10416666666</v>
       </c>
       <c r="B12">
-        <v>13.525</v>
+        <v>4.19</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>25.25</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1253,16 +1253,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46268.11458333334</v>
+        <v>46277.11458333334</v>
       </c>
       <c r="B13">
-        <v>3.821</v>
+        <v>14.403</v>
       </c>
       <c r="C13">
-        <v>0.054</v>
+        <v>0.746</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>25.25</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1276,16 +1276,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46268.125</v>
+        <v>46277.125</v>
       </c>
       <c r="B14">
-        <v>13.869</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>0.04</v>
+        <v>5.768</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>25.25</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1299,16 +1299,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46268.13541666666</v>
+        <v>46277.13541666666</v>
       </c>
       <c r="B15">
-        <v>6.883</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>4.644</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>25.25</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1322,16 +1322,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46268.14583333334</v>
+        <v>46277.14583333334</v>
       </c>
       <c r="B16">
-        <v>3.806</v>
+        <v>3.378</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>2.753</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1345,16 +1345,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46268.15625</v>
+        <v>46277.15625</v>
       </c>
       <c r="B17">
-        <v>9.861000000000001</v>
+        <v>8.702</v>
       </c>
       <c r="C17">
-        <v>0.091</v>
+        <v>0.19</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1368,16 +1368,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46268.16666666666</v>
+        <v>46277.16666666666</v>
       </c>
       <c r="B18">
-        <v>13.046</v>
+        <v>3.758</v>
       </c>
       <c r="C18">
-        <v>0.028</v>
+        <v>0.47</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1391,16 +1391,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46268.17708333334</v>
+        <v>46277.17708333334</v>
       </c>
       <c r="B19">
-        <v>3.083</v>
+        <v>2.04</v>
       </c>
       <c r="C19">
-        <v>0.016</v>
+        <v>0.039</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46268.1875</v>
+        <v>46277.1875</v>
       </c>
       <c r="B20">
-        <v>0.054</v>
+        <v>13.665</v>
       </c>
       <c r="C20">
-        <v>0.872</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1437,16 +1437,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46268.19791666666</v>
+        <v>46277.19791666666</v>
       </c>
       <c r="B21">
-        <v>0.173</v>
+        <v>7.871</v>
       </c>
       <c r="C21">
-        <v>1.925</v>
+        <v>0.196</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1460,13 +1460,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46268.20833333334</v>
+        <v>46277.20833333334</v>
       </c>
       <c r="B22">
-        <v>2.247</v>
+        <v>9.505000000000001</v>
       </c>
       <c r="C22">
-        <v>2.157</v>
+        <v>0.22</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1483,13 +1483,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46268.21875</v>
+        <v>46277.21875</v>
       </c>
       <c r="B23">
-        <v>0.516</v>
+        <v>9.945</v>
       </c>
       <c r="C23">
-        <v>0.551</v>
+        <v>0.024</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1506,16 +1506,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46268.22916666666</v>
+        <v>46277.22916666666</v>
       </c>
       <c r="B24">
-        <v>0.586</v>
+        <v>0.005</v>
       </c>
       <c r="C24">
-        <v>1.242</v>
+        <v>0.796</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1529,16 +1529,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46268.23958333334</v>
+        <v>46277.23958333334</v>
       </c>
       <c r="B25">
-        <v>0.17</v>
+        <v>0.017</v>
       </c>
       <c r="C25">
-        <v>3.967</v>
+        <v>1.207</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1552,16 +1552,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46268.25</v>
+        <v>46277.25</v>
       </c>
       <c r="B26">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>3.946</v>
+        <v>4.81</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1575,13 +1575,13 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46268.26041666666</v>
+        <v>46277.26041666666</v>
       </c>
       <c r="B27">
-        <v>0.054</v>
+        <v>0.333</v>
       </c>
       <c r="C27">
-        <v>1.137</v>
+        <v>0.055</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1598,13 +1598,13 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46268.27083333334</v>
+        <v>46277.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>5.382</v>
       </c>
       <c r="C28">
-        <v>9.464</v>
+        <v>0.011</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1621,13 +1621,13 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46268.28125</v>
+        <v>46277.28125</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>0.241</v>
       </c>
       <c r="C29">
-        <v>25.665</v>
+        <v>0.163</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1644,13 +1644,13 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46268.29166666666</v>
+        <v>46277.29166666666</v>
       </c>
       <c r="B30">
-        <v>0.023</v>
+        <v>0.475</v>
       </c>
       <c r="C30">
-        <v>11.412</v>
+        <v>0.273</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1667,13 +1667,13 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46268.30208333334</v>
+        <v>46277.30208333334</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>7.607</v>
       </c>
       <c r="C31">
-        <v>25.702</v>
+        <v>0</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1690,13 +1690,13 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46268.3125</v>
+        <v>46277.3125</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>33.513</v>
       </c>
       <c r="C32">
-        <v>25.357</v>
+        <v>0</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -1713,13 +1713,13 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46268.32291666666</v>
+        <v>46277.32291666666</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>18.786</v>
       </c>
       <c r="C33">
-        <v>17.083</v>
+        <v>0</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -1736,16 +1736,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46268.33333333334</v>
+        <v>46277.33333333334</v>
       </c>
       <c r="B34">
-        <v>0.006</v>
+        <v>41.775</v>
       </c>
       <c r="C34">
-        <v>3.793</v>
+        <v>0.029</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1759,16 +1759,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46268.34375</v>
+        <v>46277.34375</v>
       </c>
       <c r="B35">
-        <v>0.059</v>
+        <v>18.546</v>
       </c>
       <c r="C35">
-        <v>16.995</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -1782,19 +1782,19 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46268.35416666666</v>
+        <v>46277.35416666666</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>8.055999999999999</v>
       </c>
       <c r="C36">
-        <v>19.324</v>
+        <v>0.04</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E36">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F36">
         <v>35</v>
@@ -1805,19 +1805,19 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46268.36458333334</v>
+        <v>46277.36458333334</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>0.501</v>
       </c>
       <c r="C37">
-        <v>19.607</v>
+        <v>0.773</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E37">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F37">
         <v>36</v>
@@ -1828,19 +1828,19 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46268.375</v>
+        <v>46277.375</v>
       </c>
       <c r="B38">
-        <v>0.145</v>
+        <v>18.993</v>
       </c>
       <c r="C38">
-        <v>12.337</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="E38">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F38">
         <v>37</v>
@@ -1851,19 +1851,19 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46268.38541666666</v>
+        <v>46277.38541666666</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>7.505</v>
       </c>
       <c r="C39">
-        <v>23.465</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="E39">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F39">
         <v>38</v>
@@ -1874,19 +1874,19 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46268.39583333334</v>
+        <v>46277.39583333334</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>4.983</v>
       </c>
       <c r="C40">
-        <v>35.668</v>
+        <v>0.021</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>73.5</v>
       </c>
       <c r="E40">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F40">
         <v>39</v>
@@ -1897,19 +1897,19 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46268.40625</v>
+        <v>46277.40625</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="C41">
-        <v>27.151</v>
+        <v>0.224</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>65.5</v>
       </c>
       <c r="E41">
-        <v>74.75</v>
+        <v>0</v>
       </c>
       <c r="F41">
         <v>40</v>
@@ -1920,19 +1920,19 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46268.41666666666</v>
+        <v>46277.41666666666</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>6.336</v>
       </c>
       <c r="C42">
-        <v>17.893</v>
+        <v>0.907</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>70.25</v>
       </c>
       <c r="E42">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F42">
         <v>41</v>
@@ -1943,19 +1943,19 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46268.42708333334</v>
+        <v>46277.42708333334</v>
       </c>
       <c r="B43">
-        <v>0.04</v>
+        <v>0.269</v>
       </c>
       <c r="C43">
-        <v>5.367</v>
+        <v>0.231</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>70.25</v>
       </c>
       <c r="E43">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F43">
         <v>42</v>
@@ -1966,19 +1966,19 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46268.4375</v>
+        <v>46277.4375</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>5.19</v>
       </c>
       <c r="C44">
-        <v>17.664</v>
+        <v>0.002</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>74.5</v>
       </c>
       <c r="E44">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F44">
         <v>43</v>
@@ -1989,19 +1989,19 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46268.44791666666</v>
+        <v>46277.44791666666</v>
       </c>
       <c r="B45">
-        <v>0.16</v>
+        <v>0.109</v>
       </c>
       <c r="C45">
-        <v>6.186</v>
+        <v>0.368</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>74.5</v>
       </c>
       <c r="E45">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F45">
         <v>44</v>
@@ -2012,19 +2012,19 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46268.45833333334</v>
+        <v>46277.45833333334</v>
       </c>
       <c r="B46">
-        <v>0.517</v>
+        <v>2.587</v>
       </c>
       <c r="C46">
-        <v>0.205</v>
+        <v>0.099</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E46">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F46">
         <v>45</v>
@@ -2035,19 +2035,19 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46268.46875</v>
+        <v>46277.46875</v>
       </c>
       <c r="B47">
-        <v>0.998</v>
+        <v>2.383</v>
       </c>
       <c r="C47">
-        <v>0.099</v>
+        <v>0.073</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E47">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F47">
         <v>46</v>
@@ -2058,19 +2058,19 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46268.47916666666</v>
+        <v>46277.47916666666</v>
       </c>
       <c r="B48">
-        <v>6.773</v>
+        <v>22.355</v>
       </c>
       <c r="C48">
-        <v>0.024</v>
+        <v>0.002</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E48">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="F48">
         <v>47</v>
@@ -2081,19 +2081,19 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46268.48958333334</v>
+        <v>46277.48958333334</v>
       </c>
       <c r="B49">
-        <v>0.081</v>
+        <v>6.27</v>
       </c>
       <c r="C49">
-        <v>1.035</v>
+        <v>0.038</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>137.5</v>
       </c>
       <c r="E49">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F49">
         <v>48</v>
@@ -2104,19 +2104,19 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46268.5</v>
+        <v>46277.5</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>10.141</v>
       </c>
       <c r="C50">
-        <v>5.838</v>
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>137.5</v>
       </c>
       <c r="E50">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F50">
         <v>49</v>
@@ -2127,19 +2127,19 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46268.51041666666</v>
+        <v>46277.51041666666</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>28.3</v>
       </c>
       <c r="C51">
-        <v>4.484</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>137.5</v>
       </c>
       <c r="E51">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F51">
         <v>50</v>
@@ -2150,19 +2150,19 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46268.52083333334</v>
+        <v>46277.52083333334</v>
       </c>
       <c r="B52">
-        <v>0.21</v>
+        <v>6.23</v>
       </c>
       <c r="C52">
-        <v>0.514</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E52">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F52">
         <v>51</v>
@@ -2173,19 +2173,19 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46268.53125</v>
+        <v>46277.53125</v>
       </c>
       <c r="B53">
-        <v>0.269</v>
+        <v>5.748</v>
       </c>
       <c r="C53">
-        <v>1.524</v>
+        <v>2.584</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E53">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F53">
         <v>52</v>
@@ -2196,16 +2196,16 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46268.54166666666</v>
+        <v>46277.54166666666</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>0.113</v>
       </c>
       <c r="C54">
-        <v>5.592</v>
+        <v>4.264</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -2219,16 +2219,16 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46268.55208333334</v>
+        <v>46277.55208333334</v>
       </c>
       <c r="B55">
-        <v>0.116</v>
+        <v>0.443</v>
       </c>
       <c r="C55">
-        <v>1.67</v>
+        <v>0.077</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -2242,16 +2242,16 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46268.5625</v>
+        <v>46277.5625</v>
       </c>
       <c r="B56">
-        <v>0.035</v>
+        <v>0.053</v>
       </c>
       <c r="C56">
-        <v>4.753</v>
+        <v>6.946</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2265,19 +2265,19 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46268.57291666666</v>
+        <v>46277.57291666666</v>
       </c>
       <c r="B57">
-        <v>0.097</v>
+        <v>0</v>
       </c>
       <c r="C57">
-        <v>3.599</v>
+        <v>3.728</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>51.25</v>
       </c>
       <c r="E57">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F57">
         <v>56</v>
@@ -2288,19 +2288,19 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46268.58333333334</v>
+        <v>46277.58333333334</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="C58">
-        <v>7.045</v>
+        <v>7.614</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>38.75</v>
       </c>
       <c r="E58">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F58">
         <v>57</v>
@@ -2311,19 +2311,19 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46268.59375</v>
+        <v>46277.59375</v>
       </c>
       <c r="B59">
-        <v>1.458</v>
+        <v>0.762</v>
       </c>
       <c r="C59">
-        <v>0.862</v>
+        <v>3.286</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>38.75</v>
       </c>
       <c r="E59">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F59">
         <v>58</v>
@@ -2334,19 +2334,19 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46268.60416666666</v>
+        <v>46277.60416666666</v>
       </c>
       <c r="B60">
-        <v>4.947</v>
+        <v>1.35</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E60">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F60">
         <v>59</v>
@@ -2357,19 +2357,19 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46268.61458333334</v>
+        <v>46277.61458333334</v>
       </c>
       <c r="B61">
-        <v>5.787</v>
+        <v>1.35</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E61">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F61">
         <v>60</v>
@@ -2380,19 +2380,19 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46268.625</v>
+        <v>46277.625</v>
       </c>
       <c r="B62">
-        <v>0.255</v>
+        <v>0.489</v>
       </c>
       <c r="C62">
-        <v>0.062</v>
+        <v>3.115</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E62">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F62">
         <v>61</v>
@@ -2403,19 +2403,19 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46268.63541666666</v>
+        <v>46277.63541666666</v>
       </c>
       <c r="B63">
-        <v>0.08599999999999999</v>
+        <v>1.163</v>
       </c>
       <c r="C63">
-        <v>3.472</v>
+        <v>0.339</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>38.75</v>
       </c>
       <c r="E63">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F63">
         <v>62</v>
@@ -2426,19 +2426,19 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46268.64583333334</v>
+        <v>46277.64583333334</v>
       </c>
       <c r="B64">
-        <v>20.576</v>
+        <v>0.153</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>0.869</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="E64">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F64">
         <v>63</v>
@@ -2449,19 +2449,19 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46268.65625</v>
+        <v>46277.65625</v>
       </c>
       <c r="B65">
-        <v>43.908</v>
+        <v>9.942</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>40.25</v>
       </c>
       <c r="E65">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F65">
         <v>64</v>
@@ -2472,16 +2472,16 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46268.66666666666</v>
+        <v>46277.66666666666</v>
       </c>
       <c r="B66">
-        <v>1.776</v>
+        <v>6.857</v>
       </c>
       <c r="C66">
-        <v>4.118</v>
+        <v>0</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>41.5</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -2495,16 +2495,16 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46268.67708333334</v>
+        <v>46277.67708333334</v>
       </c>
       <c r="B67">
-        <v>6.253</v>
+        <v>2.265</v>
       </c>
       <c r="C67">
-        <v>0.105</v>
+        <v>0.024</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>45.25</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -2518,16 +2518,16 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46268.6875</v>
+        <v>46277.6875</v>
       </c>
       <c r="B68">
-        <v>18.209</v>
+        <v>6.057</v>
       </c>
       <c r="C68">
         <v>0</v>
       </c>
       <c r="D68">
-        <v>8.5</v>
+        <v>45.25</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -2541,16 +2541,16 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46268.69791666666</v>
+        <v>46277.69791666666</v>
       </c>
       <c r="B69">
-        <v>34.62</v>
+        <v>10.358</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>32.25</v>
+        <v>49</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -2564,16 +2564,16 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46268.70833333334</v>
+        <v>46277.70833333334</v>
       </c>
       <c r="B70">
-        <v>3.274</v>
+        <v>2.627</v>
       </c>
       <c r="C70">
-        <v>0.003</v>
+        <v>2.237</v>
       </c>
       <c r="D70">
-        <v>37.5</v>
+        <v>36.5</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -2587,16 +2587,16 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46268.71875</v>
+        <v>46277.71875</v>
       </c>
       <c r="B71">
-        <v>8.553000000000001</v>
+        <v>13.482</v>
       </c>
       <c r="C71">
-        <v>1.026</v>
+        <v>0</v>
       </c>
       <c r="D71">
-        <v>37.5</v>
+        <v>18.5</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -2610,16 +2610,16 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46268.72916666666</v>
+        <v>46277.72916666666</v>
       </c>
       <c r="B72">
-        <v>7.32</v>
+        <v>2.701</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="D72">
-        <v>37.5</v>
+        <v>19.5</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -2633,16 +2633,16 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46268.73958333334</v>
+        <v>46277.73958333334</v>
       </c>
       <c r="B73">
-        <v>20.384</v>
+        <v>0.445</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>0.747</v>
       </c>
       <c r="D73">
-        <v>29</v>
+        <v>19.5</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -2656,16 +2656,16 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46268.75</v>
+        <v>46277.75</v>
       </c>
       <c r="B74">
-        <v>1.034</v>
+        <v>13.195</v>
       </c>
       <c r="C74">
-        <v>6.862</v>
+        <v>0</v>
       </c>
       <c r="D74">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -2679,16 +2679,16 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46268.76041666666</v>
+        <v>46277.76041666666</v>
       </c>
       <c r="B75">
-        <v>5.499</v>
+        <v>21.005</v>
       </c>
       <c r="C75">
-        <v>1.763</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -2702,16 +2702,16 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46268.77083333334</v>
+        <v>46277.77083333334</v>
       </c>
       <c r="B76">
-        <v>2.541</v>
+        <v>34.852</v>
       </c>
       <c r="C76">
-        <v>0.448</v>
+        <v>0</v>
       </c>
       <c r="D76">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -2725,16 +2725,16 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46268.78125</v>
+        <v>46277.78125</v>
       </c>
       <c r="B77">
-        <v>15.537</v>
+        <v>37.948</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
       <c r="D77">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -2748,16 +2748,16 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46268.79166666666</v>
+        <v>46277.79166666666</v>
       </c>
       <c r="B78">
-        <v>5.201</v>
+        <v>32.529</v>
       </c>
       <c r="C78">
         <v>0</v>
       </c>
       <c r="D78">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -2771,16 +2771,16 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46268.80208333334</v>
+        <v>46277.80208333334</v>
       </c>
       <c r="B79">
-        <v>1.783</v>
+        <v>26.528</v>
       </c>
       <c r="C79">
-        <v>0.097</v>
+        <v>0</v>
       </c>
       <c r="D79">
-        <v>50</v>
+        <v>36.5</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46268.8125</v>
+        <v>46277.8125</v>
       </c>
       <c r="B80">
-        <v>18.542</v>
+        <v>2.479</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>3.559</v>
       </c>
       <c r="D80">
-        <v>50</v>
+        <v>57.5</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -2817,16 +2817,16 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46268.82291666666</v>
+        <v>46277.82291666666</v>
       </c>
       <c r="B81">
-        <v>38.873</v>
+        <v>0.008</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>1.437</v>
       </c>
       <c r="D81">
-        <v>16.75</v>
+        <v>57.5</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -2840,16 +2840,16 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46268.83333333334</v>
+        <v>46277.83333333334</v>
       </c>
       <c r="B82">
-        <v>3.92</v>
+        <v>10.605</v>
       </c>
       <c r="C82">
-        <v>3.867</v>
+        <v>0</v>
       </c>
       <c r="D82">
-        <v>25</v>
+        <v>42.5</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -2863,16 +2863,16 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46268.84375</v>
+        <v>46277.84375</v>
       </c>
       <c r="B83">
-        <v>0</v>
+        <v>18.956</v>
       </c>
       <c r="C83">
-        <v>8.231999999999999</v>
+        <v>0</v>
       </c>
       <c r="D83">
-        <v>25</v>
+        <v>42.5</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -2886,16 +2886,16 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46268.85416666666</v>
+        <v>46277.85416666666</v>
       </c>
       <c r="B84">
-        <v>2.33</v>
+        <v>15.172</v>
       </c>
       <c r="C84">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -2909,16 +2909,16 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46268.86458333334</v>
+        <v>46277.86458333334</v>
       </c>
       <c r="B85">
-        <v>1.227</v>
+        <v>3.137</v>
       </c>
       <c r="C85">
-        <v>1.949</v>
+        <v>1.017</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -2932,16 +2932,16 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46268.875</v>
+        <v>46277.875</v>
       </c>
       <c r="B86">
-        <v>8.053000000000001</v>
+        <v>1.305</v>
       </c>
       <c r="C86">
-        <v>0.137</v>
+        <v>0.099</v>
       </c>
       <c r="D86">
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -2955,16 +2955,16 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46268.88541666666</v>
+        <v>46277.88541666666</v>
       </c>
       <c r="B87">
-        <v>11.291</v>
+        <v>0.152</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>2.142</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -2978,13 +2978,13 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46268.89583333334</v>
+        <v>46277.89583333334</v>
       </c>
       <c r="B88">
-        <v>3.106</v>
+        <v>0.78</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>3.797</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3001,13 +3001,13 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46268.90625</v>
+        <v>46277.90625</v>
       </c>
       <c r="B89">
-        <v>1.187</v>
+        <v>0</v>
       </c>
       <c r="C89">
-        <v>0.759</v>
+        <v>0</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3024,10 +3024,10 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46268.91666666666</v>
+        <v>46277.91666666666</v>
       </c>
       <c r="B90">
-        <v>14.518</v>
+        <v>10.086</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -3047,13 +3047,13 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46268.92708333334</v>
+        <v>46277.92708333334</v>
       </c>
       <c r="B91">
-        <v>1.064</v>
+        <v>1.457</v>
       </c>
       <c r="C91">
-        <v>6.115</v>
+        <v>0</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3070,13 +3070,13 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46268.9375</v>
+        <v>46277.9375</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>11.107</v>
       </c>
       <c r="C92">
-        <v>9.733000000000001</v>
+        <v>0</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3093,13 +3093,13 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46268.94791666666</v>
+        <v>46277.94791666666</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>18.653</v>
       </c>
       <c r="C93">
-        <v>8.134</v>
+        <v>0</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3116,13 +3116,13 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46268.95833333334</v>
+        <v>46277.95833333334</v>
       </c>
       <c r="B94">
-        <v>0.173</v>
+        <v>18.513</v>
       </c>
       <c r="C94">
-        <v>3.587</v>
+        <v>0</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3139,13 +3139,13 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46268.96875</v>
+        <v>46277.96875</v>
       </c>
       <c r="B95">
-        <v>0.015</v>
+        <v>12.046</v>
       </c>
       <c r="C95">
-        <v>3.961</v>
+        <v>0</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3162,13 +3162,13 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46268.97916666666</v>
+        <v>46277.97916666666</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>10.817</v>
       </c>
       <c r="C96">
-        <v>5.762</v>
+        <v>0</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3185,13 +3185,13 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46268.98958333334</v>
+        <v>46277.98958333334</v>
       </c>
       <c r="B97">
-        <v>1.745</v>
+        <v>5.081</v>
       </c>
       <c r="C97">
-        <v>0.279</v>
+        <v>0</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3208,10 +3208,10 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46269</v>
+        <v>46278</v>
       </c>
       <c r="B98">
-        <v>23.633</v>
+        <v>5.581</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -3231,10 +3231,10 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46269.01041666666</v>
+        <v>46278.01041666666</v>
       </c>
       <c r="B99">
-        <v>33.306</v>
+        <v>6.817</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46269.02083333334</v>
+        <v>46278.02083333334</v>
       </c>
       <c r="B100">
-        <v>11.073</v>
+        <v>11.327</v>
       </c>
       <c r="C100">
         <v>0</v>
       </c>
       <c r="D100">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -3277,16 +3277,16 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46269.03125</v>
+        <v>46278.03125</v>
       </c>
       <c r="B101">
-        <v>12.176</v>
+        <v>0.061</v>
       </c>
       <c r="C101">
-        <v>0.008999999999999999</v>
+        <v>1.071</v>
       </c>
       <c r="D101">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -3300,16 +3300,16 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46269.04166666666</v>
+        <v>46278.04166666666</v>
       </c>
       <c r="B102">
-        <v>16.059</v>
+        <v>0.016</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>4.045</v>
       </c>
       <c r="D102">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -3323,16 +3323,16 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46269.05208333334</v>
+        <v>46278.05208333334</v>
       </c>
       <c r="B103">
-        <v>14.329</v>
+        <v>0</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>24.065</v>
       </c>
       <c r="D103">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -3346,16 +3346,16 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46269.0625</v>
+        <v>46278.0625</v>
       </c>
       <c r="B104">
-        <v>6.305</v>
+        <v>0.029</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>4.193</v>
       </c>
       <c r="D104">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -3369,16 +3369,16 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46269.07291666666</v>
+        <v>46278.07291666666</v>
       </c>
       <c r="B105">
-        <v>3.002</v>
+        <v>0</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>6.779</v>
       </c>
       <c r="D105">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -3392,16 +3392,16 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46269.08333333334</v>
+        <v>46278.08333333334</v>
       </c>
       <c r="B106">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="D106">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -3415,16 +3415,16 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46269.09375</v>
+        <v>46278.09375</v>
       </c>
       <c r="B107">
-        <v>0.235</v>
+        <v>0.143</v>
       </c>
       <c r="C107">
-        <v>1.266</v>
+        <v>0.121</v>
       </c>
       <c r="D107">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -3438,16 +3438,16 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46269.10416666666</v>
+        <v>46278.10416666666</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="C108">
-        <v>4.294</v>
+        <v>0.026</v>
       </c>
       <c r="D108">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -3461,16 +3461,16 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46269.11458333334</v>
+        <v>46278.11458333334</v>
       </c>
       <c r="B109">
-        <v>0.04</v>
+        <v>1.166</v>
       </c>
       <c r="C109">
-        <v>2.806</v>
+        <v>1.138</v>
       </c>
       <c r="D109">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -3484,16 +3484,16 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46269.125</v>
+        <v>46278.125</v>
       </c>
       <c r="B110">
-        <v>4.643</v>
+        <v>10.73</v>
       </c>
       <c r="C110">
-        <v>0.28</v>
+        <v>0.189</v>
       </c>
       <c r="D110">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -3507,16 +3507,16 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46269.13541666666</v>
+        <v>46278.13541666666</v>
       </c>
       <c r="B111">
-        <v>2.814</v>
+        <v>17.415</v>
       </c>
       <c r="C111">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="D111">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -3530,16 +3530,16 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46269.14583333334</v>
+        <v>46278.14583333334</v>
       </c>
       <c r="B112">
-        <v>0.092</v>
+        <v>30.389</v>
       </c>
       <c r="C112">
-        <v>1.082</v>
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -3553,16 +3553,16 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46269.15625</v>
+        <v>46278.15625</v>
       </c>
       <c r="B113">
-        <v>0.6820000000000001</v>
+        <v>37.011</v>
       </c>
       <c r="C113">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="D113">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -3576,16 +3576,16 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46269.16666666666</v>
+        <v>46278.16666666666</v>
       </c>
       <c r="B114">
-        <v>11.632</v>
+        <v>22.819</v>
       </c>
       <c r="C114">
-        <v>0.099</v>
+        <v>0</v>
       </c>
       <c r="D114">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46269.17708333334</v>
+        <v>46278.17708333334</v>
       </c>
       <c r="B115">
-        <v>30.174</v>
+        <v>27.926</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -3622,16 +3622,16 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46269.1875</v>
+        <v>46278.1875</v>
       </c>
       <c r="B116">
-        <v>7.134</v>
+        <v>21.278</v>
       </c>
       <c r="C116">
         <v>0</v>
       </c>
       <c r="D116">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -3645,16 +3645,16 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46269.19791666666</v>
+        <v>46278.19791666666</v>
       </c>
       <c r="B117">
-        <v>3.09</v>
+        <v>46.51</v>
       </c>
       <c r="C117">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="D117">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -3668,16 +3668,16 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46269.20833333334</v>
+        <v>46278.20833333334</v>
       </c>
       <c r="B118">
-        <v>25.155</v>
+        <v>35.166</v>
       </c>
       <c r="C118">
         <v>0</v>
       </c>
       <c r="D118">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -3691,16 +3691,16 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46269.21875</v>
+        <v>46278.21875</v>
       </c>
       <c r="B119">
-        <v>14.811</v>
+        <v>28.82</v>
       </c>
       <c r="C119">
         <v>0</v>
       </c>
       <c r="D119">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46269.22916666666</v>
+        <v>46278.22916666666</v>
       </c>
       <c r="B120">
-        <v>10.552</v>
+        <v>40.096</v>
       </c>
       <c r="C120">
         <v>0</v>
       </c>
       <c r="D120">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -3737,16 +3737,16 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46269.23958333334</v>
+        <v>46278.23958333334</v>
       </c>
       <c r="B121">
-        <v>12.094</v>
+        <v>28.489</v>
       </c>
       <c r="C121">
         <v>0</v>
       </c>
       <c r="D121">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -3760,16 +3760,16 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46269.25</v>
+        <v>46278.25</v>
       </c>
       <c r="B122">
-        <v>1.24</v>
+        <v>1.859</v>
       </c>
       <c r="C122">
-        <v>6.089</v>
+        <v>0.464</v>
       </c>
       <c r="D122">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -3783,16 +3783,16 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46269.26041666666</v>
+        <v>46278.26041666666</v>
       </c>
       <c r="B123">
-        <v>3.925</v>
+        <v>0.027</v>
       </c>
       <c r="C123">
-        <v>0.003</v>
+        <v>0.181</v>
       </c>
       <c r="D123">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -3806,16 +3806,16 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46269.27083333334</v>
+        <v>46278.27083333334</v>
       </c>
       <c r="B124">
-        <v>0.743</v>
+        <v>0.121</v>
       </c>
       <c r="C124">
-        <v>1.064</v>
+        <v>0.174</v>
       </c>
       <c r="D124">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -3829,16 +3829,16 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46269.28125</v>
+        <v>46278.28125</v>
       </c>
       <c r="B125">
-        <v>0.208</v>
+        <v>0.034</v>
       </c>
       <c r="C125">
-        <v>5.273</v>
+        <v>0.894</v>
       </c>
       <c r="D125">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -3852,16 +3852,16 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46269.29166666666</v>
+        <v>46278.29166666666</v>
       </c>
       <c r="B126">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="C126">
-        <v>4.056</v>
+        <v>7.098</v>
       </c>
       <c r="D126">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -3875,13 +3875,13 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46269.30208333334</v>
+        <v>46278.30208333334</v>
       </c>
       <c r="B127">
-        <v>0.121</v>
+        <v>0</v>
       </c>
       <c r="C127">
-        <v>6.618</v>
+        <v>10.585</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -3898,13 +3898,13 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46269.3125</v>
+        <v>46278.3125</v>
       </c>
       <c r="B128">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="C128">
-        <v>6.834</v>
+        <v>7.019</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -3921,13 +3921,13 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46269.32291666666</v>
+        <v>46278.32291666666</v>
       </c>
       <c r="B129">
         <v>0</v>
       </c>
       <c r="C129">
-        <v>15.726</v>
+        <v>11.187</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -3944,16 +3944,16 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46269.33333333334</v>
+        <v>46278.33333333334</v>
       </c>
       <c r="B130">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="C130">
-        <v>7.141</v>
+        <v>19.617</v>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -3967,16 +3967,16 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46269.34375</v>
+        <v>46278.34375</v>
       </c>
       <c r="B131">
-        <v>0.052</v>
+        <v>0</v>
       </c>
       <c r="C131">
-        <v>15.775</v>
+        <v>10.046</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -3990,19 +3990,19 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46269.35416666666</v>
+        <v>46278.35416666666</v>
       </c>
       <c r="B132">
         <v>0</v>
       </c>
       <c r="C132">
-        <v>10.342</v>
+        <v>0</v>
       </c>
       <c r="D132">
         <v>0</v>
       </c>
       <c r="E132">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F132">
         <v>35</v>
@@ -4013,19 +4013,19 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46269.36458333334</v>
+        <v>46278.36458333334</v>
       </c>
       <c r="B133">
-        <v>0.127</v>
+        <v>0</v>
       </c>
       <c r="C133">
-        <v>6.47</v>
+        <v>0</v>
       </c>
       <c r="D133">
         <v>0</v>
       </c>
       <c r="E133">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F133">
         <v>36</v>
@@ -4036,19 +4036,19 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46269.375</v>
+        <v>46278.375</v>
       </c>
       <c r="B134">
-        <v>1.236</v>
+        <v>0</v>
       </c>
       <c r="C134">
-        <v>4.597</v>
+        <v>0</v>
       </c>
       <c r="D134">
         <v>0</v>
       </c>
       <c r="E134">
-        <v>38.25</v>
+        <v>0</v>
       </c>
       <c r="F134">
         <v>37</v>
@@ -4059,19 +4059,19 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46269.38541666666</v>
+        <v>46278.38541666666</v>
       </c>
       <c r="B135">
-        <v>11.395</v>
+        <v>0</v>
       </c>
       <c r="C135">
-        <v>0.032</v>
+        <v>0</v>
       </c>
       <c r="D135">
         <v>0</v>
       </c>
       <c r="E135">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F135">
         <v>38</v>
@@ -4082,19 +4082,19 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46269.39583333334</v>
+        <v>46278.39583333334</v>
       </c>
       <c r="B136">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="C136">
-        <v>0.284</v>
+        <v>0</v>
       </c>
       <c r="D136">
         <v>0</v>
       </c>
       <c r="E136">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F136">
         <v>39</v>
@@ -4105,13 +4105,13 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46269.40625</v>
+        <v>46278.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
       </c>
       <c r="C137">
-        <v>18.307</v>
+        <v>0</v>
       </c>
       <c r="D137">
         <v>0</v>
@@ -4128,13 +4128,13 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46269.41666666666</v>
+        <v>46278.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
       </c>
       <c r="C138">
-        <v>13.602</v>
+        <v>0</v>
       </c>
       <c r="D138">
         <v>0</v>
@@ -4151,13 +4151,13 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46269.42708333334</v>
+        <v>46278.42708333334</v>
       </c>
       <c r="B139">
-        <v>0.136</v>
+        <v>0</v>
       </c>
       <c r="C139">
-        <v>11.2</v>
+        <v>0</v>
       </c>
       <c r="D139">
         <v>0</v>
@@ -4174,19 +4174,19 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46269.4375</v>
+        <v>46278.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
       </c>
       <c r="C140">
-        <v>37.997</v>
+        <v>0</v>
       </c>
       <c r="D140">
         <v>0</v>
       </c>
       <c r="E140">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F140">
         <v>43</v>
@@ -4197,19 +4197,19 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46269.44791666666</v>
+        <v>46278.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
       </c>
       <c r="C141">
-        <v>22.446</v>
+        <v>0</v>
       </c>
       <c r="D141">
         <v>0</v>
       </c>
       <c r="E141">
-        <v>46.25</v>
+        <v>0</v>
       </c>
       <c r="F141">
         <v>44</v>
@@ -4220,19 +4220,19 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46269.45833333334</v>
+        <v>46278.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
       </c>
       <c r="C142">
-        <v>24.903</v>
+        <v>0</v>
       </c>
       <c r="D142">
         <v>0</v>
       </c>
       <c r="E142">
-        <v>46.25</v>
+        <v>0</v>
       </c>
       <c r="F142">
         <v>45</v>
@@ -4243,19 +4243,19 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46269.46875</v>
+        <v>46278.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
       </c>
       <c r="C143">
-        <v>16.439</v>
+        <v>0</v>
       </c>
       <c r="D143">
         <v>0</v>
       </c>
       <c r="E143">
-        <v>46.25</v>
+        <v>0</v>
       </c>
       <c r="F143">
         <v>46</v>
@@ -4266,19 +4266,19 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46269.47916666666</v>
+        <v>46278.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
       </c>
       <c r="C144">
-        <v>14.212</v>
+        <v>0</v>
       </c>
       <c r="D144">
         <v>0</v>
       </c>
       <c r="E144">
-        <v>46.25</v>
+        <v>0</v>
       </c>
       <c r="F144">
         <v>47</v>
@@ -4289,7 +4289,7 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46269.48958333334</v>
+        <v>46278.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -4301,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="E145">
-        <v>46.25</v>
+        <v>0</v>
       </c>
       <c r="F145">
         <v>48</v>
@@ -4312,7 +4312,7 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46269.5</v>
+        <v>46278.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -4324,7 +4324,7 @@
         <v>0</v>
       </c>
       <c r="E146">
-        <v>46.25</v>
+        <v>0</v>
       </c>
       <c r="F146">
         <v>49</v>
@@ -4335,7 +4335,7 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46269.51041666666</v>
+        <v>46278.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -4358,7 +4358,7 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46269.52083333334</v>
+        <v>46278.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -4381,7 +4381,7 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46269.53125</v>
+        <v>46278.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46269.54166666666</v>
+        <v>46278.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46269.55208333334</v>
+        <v>46278.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -4450,7 +4450,7 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46269.5625</v>
+        <v>46278.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4473,7 +4473,7 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46269.57291666666</v>
+        <v>46278.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4496,7 +4496,7 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46269.58333333334</v>
+        <v>46278.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46269.59375</v>
+        <v>46278.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4542,7 +4542,7 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46269.60416666666</v>
+        <v>46278.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46269.61458333334</v>
+        <v>46278.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46269.625</v>
+        <v>46278.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4611,7 +4611,7 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46269.63541666666</v>
+        <v>46278.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46269.64583333334</v>
+        <v>46278.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46269.65625</v>
+        <v>46278.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46269.66666666666</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46269.67708333334</v>
+        <v>46278.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46269.6875</v>
+        <v>46278.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46269.69791666666</v>
+        <v>46278.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4772,7 +4772,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46269.70833333334</v>
+        <v>46278.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46269.71875</v>
+        <v>46278.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46269.72916666666</v>
+        <v>46278.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46269.73958333334</v>
+        <v>46278.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46269.75</v>
+        <v>46278.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46269.76041666666</v>
+        <v>46278.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46269.77083333334</v>
+        <v>46278.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46269.78125</v>
+        <v>46278.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46269.79166666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46269.80208333334</v>
+        <v>46278.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46269.8125</v>
+        <v>46278.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -5025,7 +5025,7 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46269.82291666666</v>
+        <v>46278.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46269.83333333334</v>
+        <v>46278.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -5071,7 +5071,7 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46269.84375</v>
+        <v>46278.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -5094,7 +5094,7 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46269.85416666666</v>
+        <v>46278.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46269.86458333334</v>
+        <v>46278.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46269.875</v>
+        <v>46278.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46269.88541666666</v>
+        <v>46278.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46269.89583333334</v>
+        <v>46278.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46269.90625</v>
+        <v>46278.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46269.91666666666</v>
+        <v>46278.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46269.92708333334</v>
+        <v>46278.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46269.9375</v>
+        <v>46278.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46269.94791666666</v>
+        <v>46278.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46269.95833333334</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -5347,7 +5347,7 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46269.96875</v>
+        <v>46278.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46269.97916666666</v>
+        <v>46278.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46269.98958333334</v>
+        <v>46278.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -37,868 +37,868 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>18.09.20261</t>
-  </si>
-  <si>
-    <t>18.09.20262</t>
-  </si>
-  <si>
-    <t>18.09.20263</t>
-  </si>
-  <si>
-    <t>18.09.20264</t>
-  </si>
-  <si>
-    <t>18.09.20265</t>
-  </si>
-  <si>
-    <t>18.09.20266</t>
-  </si>
-  <si>
-    <t>18.09.20267</t>
-  </si>
-  <si>
-    <t>18.09.20268</t>
-  </si>
-  <si>
-    <t>18.09.20269</t>
-  </si>
-  <si>
-    <t>18.09.202610</t>
-  </si>
-  <si>
-    <t>18.09.202611</t>
-  </si>
-  <si>
-    <t>18.09.202612</t>
-  </si>
-  <si>
-    <t>18.09.202613</t>
-  </si>
-  <si>
-    <t>18.09.202614</t>
-  </si>
-  <si>
-    <t>18.09.202615</t>
-  </si>
-  <si>
-    <t>18.09.202616</t>
-  </si>
-  <si>
-    <t>18.09.202617</t>
-  </si>
-  <si>
-    <t>18.09.202618</t>
-  </si>
-  <si>
-    <t>18.09.202619</t>
-  </si>
-  <si>
-    <t>18.09.202620</t>
-  </si>
-  <si>
-    <t>18.09.202621</t>
-  </si>
-  <si>
-    <t>18.09.202622</t>
-  </si>
-  <si>
-    <t>18.09.202623</t>
-  </si>
-  <si>
-    <t>18.09.202624</t>
-  </si>
-  <si>
-    <t>18.09.202625</t>
-  </si>
-  <si>
-    <t>18.09.202626</t>
-  </si>
-  <si>
-    <t>18.09.202627</t>
-  </si>
-  <si>
-    <t>18.09.202628</t>
-  </si>
-  <si>
-    <t>18.09.202629</t>
-  </si>
-  <si>
-    <t>18.09.202630</t>
-  </si>
-  <si>
-    <t>18.09.202631</t>
-  </si>
-  <si>
-    <t>18.09.202632</t>
-  </si>
-  <si>
-    <t>18.09.202633</t>
-  </si>
-  <si>
-    <t>18.09.202634</t>
-  </si>
-  <si>
-    <t>18.09.202635</t>
-  </si>
-  <si>
-    <t>18.09.202636</t>
-  </si>
-  <si>
-    <t>18.09.202637</t>
-  </si>
-  <si>
-    <t>18.09.202638</t>
-  </si>
-  <si>
-    <t>18.09.202639</t>
-  </si>
-  <si>
-    <t>18.09.202640</t>
-  </si>
-  <si>
-    <t>18.09.202641</t>
-  </si>
-  <si>
-    <t>18.09.202642</t>
-  </si>
-  <si>
-    <t>18.09.202643</t>
-  </si>
-  <si>
-    <t>18.09.202644</t>
-  </si>
-  <si>
-    <t>18.09.202645</t>
-  </si>
-  <si>
-    <t>18.09.202646</t>
-  </si>
-  <si>
-    <t>18.09.202647</t>
-  </si>
-  <si>
-    <t>18.09.202648</t>
-  </si>
-  <si>
-    <t>18.09.202649</t>
-  </si>
-  <si>
-    <t>18.09.202650</t>
-  </si>
-  <si>
-    <t>18.09.202651</t>
-  </si>
-  <si>
-    <t>18.09.202652</t>
-  </si>
-  <si>
-    <t>18.09.202653</t>
-  </si>
-  <si>
-    <t>18.09.202654</t>
-  </si>
-  <si>
-    <t>18.09.202655</t>
-  </si>
-  <si>
-    <t>18.09.202656</t>
-  </si>
-  <si>
-    <t>18.09.202657</t>
-  </si>
-  <si>
-    <t>18.09.202658</t>
-  </si>
-  <si>
-    <t>18.09.202659</t>
-  </si>
-  <si>
-    <t>18.09.202660</t>
-  </si>
-  <si>
-    <t>18.09.202661</t>
-  </si>
-  <si>
-    <t>18.09.202662</t>
-  </si>
-  <si>
-    <t>18.09.202663</t>
-  </si>
-  <si>
-    <t>18.09.202664</t>
-  </si>
-  <si>
-    <t>18.09.202665</t>
-  </si>
-  <si>
-    <t>18.09.202666</t>
-  </si>
-  <si>
-    <t>18.09.202667</t>
-  </si>
-  <si>
-    <t>18.09.202668</t>
-  </si>
-  <si>
-    <t>18.09.202669</t>
-  </si>
-  <si>
-    <t>18.09.202670</t>
-  </si>
-  <si>
-    <t>18.09.202671</t>
-  </si>
-  <si>
-    <t>18.09.202672</t>
-  </si>
-  <si>
-    <t>18.09.202673</t>
-  </si>
-  <si>
-    <t>18.09.202674</t>
-  </si>
-  <si>
-    <t>18.09.202675</t>
-  </si>
-  <si>
-    <t>18.09.202676</t>
-  </si>
-  <si>
-    <t>18.09.202677</t>
-  </si>
-  <si>
-    <t>18.09.202678</t>
-  </si>
-  <si>
-    <t>18.09.202679</t>
-  </si>
-  <si>
-    <t>18.09.202680</t>
-  </si>
-  <si>
-    <t>18.09.202681</t>
-  </si>
-  <si>
-    <t>18.09.202682</t>
-  </si>
-  <si>
-    <t>18.09.202683</t>
-  </si>
-  <si>
-    <t>18.09.202684</t>
-  </si>
-  <si>
-    <t>18.09.202685</t>
-  </si>
-  <si>
-    <t>18.09.202686</t>
-  </si>
-  <si>
-    <t>18.09.202687</t>
-  </si>
-  <si>
-    <t>18.09.202688</t>
-  </si>
-  <si>
-    <t>18.09.202689</t>
-  </si>
-  <si>
-    <t>18.09.202690</t>
-  </si>
-  <si>
-    <t>18.09.202691</t>
-  </si>
-  <si>
-    <t>18.09.202692</t>
-  </si>
-  <si>
-    <t>18.09.202693</t>
-  </si>
-  <si>
-    <t>18.09.202694</t>
-  </si>
-  <si>
-    <t>18.09.202695</t>
-  </si>
-  <si>
-    <t>18.09.202696</t>
-  </si>
-  <si>
-    <t>19.09.20261</t>
-  </si>
-  <si>
-    <t>19.09.20262</t>
-  </si>
-  <si>
-    <t>19.09.20263</t>
-  </si>
-  <si>
-    <t>19.09.20264</t>
-  </si>
-  <si>
-    <t>19.09.20265</t>
-  </si>
-  <si>
-    <t>19.09.20266</t>
-  </si>
-  <si>
-    <t>19.09.20267</t>
-  </si>
-  <si>
-    <t>19.09.20268</t>
-  </si>
-  <si>
-    <t>19.09.20269</t>
-  </si>
-  <si>
-    <t>19.09.202610</t>
-  </si>
-  <si>
-    <t>19.09.202611</t>
-  </si>
-  <si>
-    <t>19.09.202612</t>
-  </si>
-  <si>
-    <t>19.09.202613</t>
-  </si>
-  <si>
-    <t>19.09.202614</t>
-  </si>
-  <si>
-    <t>19.09.202615</t>
-  </si>
-  <si>
-    <t>19.09.202616</t>
-  </si>
-  <si>
-    <t>19.09.202617</t>
-  </si>
-  <si>
-    <t>19.09.202618</t>
-  </si>
-  <si>
-    <t>19.09.202619</t>
-  </si>
-  <si>
-    <t>19.09.202620</t>
-  </si>
-  <si>
-    <t>19.09.202621</t>
-  </si>
-  <si>
-    <t>19.09.202622</t>
-  </si>
-  <si>
-    <t>19.09.202623</t>
-  </si>
-  <si>
-    <t>19.09.202624</t>
-  </si>
-  <si>
-    <t>19.09.202625</t>
-  </si>
-  <si>
-    <t>19.09.202626</t>
-  </si>
-  <si>
-    <t>19.09.202627</t>
-  </si>
-  <si>
-    <t>19.09.202628</t>
-  </si>
-  <si>
-    <t>19.09.202629</t>
-  </si>
-  <si>
-    <t>19.09.202630</t>
-  </si>
-  <si>
-    <t>19.09.202631</t>
-  </si>
-  <si>
-    <t>19.09.202632</t>
-  </si>
-  <si>
-    <t>19.09.202633</t>
-  </si>
-  <si>
-    <t>19.09.202634</t>
-  </si>
-  <si>
-    <t>19.09.202635</t>
-  </si>
-  <si>
-    <t>19.09.202636</t>
-  </si>
-  <si>
-    <t>19.09.202637</t>
-  </si>
-  <si>
-    <t>19.09.202638</t>
-  </si>
-  <si>
-    <t>19.09.202639</t>
-  </si>
-  <si>
-    <t>19.09.202640</t>
-  </si>
-  <si>
-    <t>19.09.202641</t>
-  </si>
-  <si>
-    <t>19.09.202642</t>
-  </si>
-  <si>
-    <t>19.09.202643</t>
-  </si>
-  <si>
-    <t>19.09.202644</t>
-  </si>
-  <si>
-    <t>19.09.202645</t>
-  </si>
-  <si>
-    <t>19.09.202646</t>
-  </si>
-  <si>
-    <t>19.09.202647</t>
-  </si>
-  <si>
-    <t>19.09.202648</t>
-  </si>
-  <si>
-    <t>19.09.202649</t>
-  </si>
-  <si>
-    <t>19.09.202650</t>
-  </si>
-  <si>
-    <t>19.09.202651</t>
-  </si>
-  <si>
-    <t>19.09.202652</t>
-  </si>
-  <si>
-    <t>19.09.202653</t>
-  </si>
-  <si>
-    <t>19.09.202654</t>
-  </si>
-  <si>
-    <t>19.09.202655</t>
-  </si>
-  <si>
-    <t>19.09.202656</t>
-  </si>
-  <si>
-    <t>19.09.202657</t>
-  </si>
-  <si>
-    <t>19.09.202658</t>
-  </si>
-  <si>
-    <t>19.09.202659</t>
-  </si>
-  <si>
-    <t>19.09.202660</t>
-  </si>
-  <si>
-    <t>19.09.202661</t>
-  </si>
-  <si>
-    <t>19.09.202662</t>
-  </si>
-  <si>
-    <t>19.09.202663</t>
-  </si>
-  <si>
-    <t>19.09.202664</t>
-  </si>
-  <si>
-    <t>19.09.202665</t>
-  </si>
-  <si>
-    <t>19.09.202666</t>
-  </si>
-  <si>
-    <t>19.09.202667</t>
-  </si>
-  <si>
-    <t>19.09.202668</t>
-  </si>
-  <si>
-    <t>19.09.202669</t>
-  </si>
-  <si>
-    <t>19.09.202670</t>
-  </si>
-  <si>
-    <t>19.09.202671</t>
-  </si>
-  <si>
-    <t>19.09.202672</t>
-  </si>
-  <si>
-    <t>19.09.202673</t>
-  </si>
-  <si>
-    <t>19.09.202674</t>
-  </si>
-  <si>
-    <t>19.09.202675</t>
-  </si>
-  <si>
-    <t>19.09.202676</t>
-  </si>
-  <si>
-    <t>19.09.202677</t>
-  </si>
-  <si>
-    <t>19.09.202678</t>
-  </si>
-  <si>
-    <t>19.09.202679</t>
-  </si>
-  <si>
-    <t>19.09.202680</t>
-  </si>
-  <si>
-    <t>19.09.202681</t>
-  </si>
-  <si>
-    <t>19.09.202682</t>
-  </si>
-  <si>
-    <t>19.09.202683</t>
-  </si>
-  <si>
-    <t>19.09.202684</t>
-  </si>
-  <si>
-    <t>19.09.202685</t>
-  </si>
-  <si>
-    <t>19.09.202686</t>
-  </si>
-  <si>
-    <t>19.09.202687</t>
-  </si>
-  <si>
-    <t>19.09.202688</t>
-  </si>
-  <si>
-    <t>19.09.202689</t>
-  </si>
-  <si>
-    <t>19.09.202690</t>
-  </si>
-  <si>
-    <t>19.09.202691</t>
-  </si>
-  <si>
-    <t>19.09.202692</t>
-  </si>
-  <si>
-    <t>19.09.202693</t>
-  </si>
-  <si>
-    <t>19.09.202694</t>
-  </si>
-  <si>
-    <t>19.09.202695</t>
-  </si>
-  <si>
-    <t>19.09.202696</t>
-  </si>
-  <si>
-    <t>20.09.20261</t>
-  </si>
-  <si>
-    <t>20.09.20262</t>
-  </si>
-  <si>
-    <t>20.09.20263</t>
-  </si>
-  <si>
-    <t>20.09.20264</t>
-  </si>
-  <si>
-    <t>20.09.20265</t>
-  </si>
-  <si>
-    <t>20.09.20266</t>
-  </si>
-  <si>
-    <t>20.09.20267</t>
-  </si>
-  <si>
-    <t>20.09.20268</t>
-  </si>
-  <si>
-    <t>20.09.20269</t>
-  </si>
-  <si>
-    <t>20.09.202610</t>
-  </si>
-  <si>
-    <t>20.09.202611</t>
-  </si>
-  <si>
-    <t>20.09.202612</t>
-  </si>
-  <si>
-    <t>20.09.202613</t>
-  </si>
-  <si>
-    <t>20.09.202614</t>
-  </si>
-  <si>
-    <t>20.09.202615</t>
-  </si>
-  <si>
-    <t>20.09.202616</t>
-  </si>
-  <si>
-    <t>20.09.202617</t>
-  </si>
-  <si>
-    <t>20.09.202618</t>
-  </si>
-  <si>
-    <t>20.09.202619</t>
-  </si>
-  <si>
-    <t>20.09.202620</t>
-  </si>
-  <si>
-    <t>20.09.202621</t>
-  </si>
-  <si>
-    <t>20.09.202622</t>
-  </si>
-  <si>
-    <t>20.09.202623</t>
-  </si>
-  <si>
-    <t>20.09.202624</t>
-  </si>
-  <si>
-    <t>20.09.202625</t>
-  </si>
-  <si>
-    <t>20.09.202626</t>
-  </si>
-  <si>
-    <t>20.09.202627</t>
-  </si>
-  <si>
-    <t>20.09.202628</t>
-  </si>
-  <si>
-    <t>20.09.202629</t>
-  </si>
-  <si>
-    <t>20.09.202630</t>
-  </si>
-  <si>
-    <t>20.09.202631</t>
-  </si>
-  <si>
-    <t>20.09.202632</t>
-  </si>
-  <si>
-    <t>20.09.202633</t>
-  </si>
-  <si>
-    <t>20.09.202634</t>
-  </si>
-  <si>
-    <t>20.09.202635</t>
-  </si>
-  <si>
-    <t>20.09.202636</t>
-  </si>
-  <si>
-    <t>20.09.202637</t>
-  </si>
-  <si>
-    <t>20.09.202638</t>
-  </si>
-  <si>
-    <t>20.09.202639</t>
-  </si>
-  <si>
-    <t>20.09.202640</t>
-  </si>
-  <si>
-    <t>20.09.202641</t>
-  </si>
-  <si>
-    <t>20.09.202642</t>
-  </si>
-  <si>
-    <t>20.09.202643</t>
-  </si>
-  <si>
-    <t>20.09.202644</t>
-  </si>
-  <si>
-    <t>20.09.202645</t>
-  </si>
-  <si>
-    <t>20.09.202646</t>
-  </si>
-  <si>
-    <t>20.09.202647</t>
-  </si>
-  <si>
-    <t>20.09.202648</t>
-  </si>
-  <si>
-    <t>20.09.202649</t>
-  </si>
-  <si>
-    <t>20.09.202650</t>
-  </si>
-  <si>
-    <t>20.09.202651</t>
-  </si>
-  <si>
-    <t>20.09.202652</t>
-  </si>
-  <si>
-    <t>20.09.202653</t>
-  </si>
-  <si>
-    <t>20.09.202654</t>
-  </si>
-  <si>
-    <t>20.09.202655</t>
-  </si>
-  <si>
-    <t>20.09.202656</t>
-  </si>
-  <si>
-    <t>20.09.202657</t>
-  </si>
-  <si>
-    <t>20.09.202658</t>
-  </si>
-  <si>
-    <t>20.09.202659</t>
-  </si>
-  <si>
-    <t>20.09.202660</t>
-  </si>
-  <si>
-    <t>20.09.202661</t>
-  </si>
-  <si>
-    <t>20.09.202662</t>
-  </si>
-  <si>
-    <t>20.09.202663</t>
-  </si>
-  <si>
-    <t>20.09.202664</t>
-  </si>
-  <si>
-    <t>20.09.202665</t>
-  </si>
-  <si>
-    <t>20.09.202666</t>
-  </si>
-  <si>
-    <t>20.09.202667</t>
-  </si>
-  <si>
-    <t>20.09.202668</t>
-  </si>
-  <si>
-    <t>20.09.202669</t>
-  </si>
-  <si>
-    <t>20.09.202670</t>
-  </si>
-  <si>
-    <t>20.09.202671</t>
-  </si>
-  <si>
-    <t>20.09.202672</t>
-  </si>
-  <si>
-    <t>20.09.202673</t>
-  </si>
-  <si>
-    <t>20.09.202674</t>
-  </si>
-  <si>
-    <t>20.09.202675</t>
-  </si>
-  <si>
-    <t>20.09.202676</t>
-  </si>
-  <si>
-    <t>20.09.202677</t>
-  </si>
-  <si>
-    <t>20.09.202678</t>
-  </si>
-  <si>
-    <t>20.09.202679</t>
-  </si>
-  <si>
-    <t>20.09.202680</t>
-  </si>
-  <si>
-    <t>20.09.202681</t>
-  </si>
-  <si>
-    <t>20.09.202682</t>
-  </si>
-  <si>
-    <t>20.09.202683</t>
-  </si>
-  <si>
-    <t>20.09.202684</t>
-  </si>
-  <si>
-    <t>20.09.202685</t>
-  </si>
-  <si>
-    <t>20.09.202686</t>
-  </si>
-  <si>
-    <t>20.09.202687</t>
-  </si>
-  <si>
-    <t>20.09.202688</t>
-  </si>
-  <si>
-    <t>20.09.202689</t>
-  </si>
-  <si>
-    <t>20.09.202690</t>
-  </si>
-  <si>
-    <t>20.09.202691</t>
-  </si>
-  <si>
-    <t>20.09.202692</t>
-  </si>
-  <si>
-    <t>20.09.202693</t>
-  </si>
-  <si>
-    <t>20.09.202694</t>
-  </si>
-  <si>
-    <t>20.09.202695</t>
-  </si>
-  <si>
-    <t>20.09.202696</t>
+    <t>28.09.20261</t>
+  </si>
+  <si>
+    <t>28.09.20262</t>
+  </si>
+  <si>
+    <t>28.09.20263</t>
+  </si>
+  <si>
+    <t>28.09.20264</t>
+  </si>
+  <si>
+    <t>28.09.20265</t>
+  </si>
+  <si>
+    <t>28.09.20266</t>
+  </si>
+  <si>
+    <t>28.09.20267</t>
+  </si>
+  <si>
+    <t>28.09.20268</t>
+  </si>
+  <si>
+    <t>28.09.20269</t>
+  </si>
+  <si>
+    <t>28.09.202610</t>
+  </si>
+  <si>
+    <t>28.09.202611</t>
+  </si>
+  <si>
+    <t>28.09.202612</t>
+  </si>
+  <si>
+    <t>28.09.202613</t>
+  </si>
+  <si>
+    <t>28.09.202614</t>
+  </si>
+  <si>
+    <t>28.09.202615</t>
+  </si>
+  <si>
+    <t>28.09.202616</t>
+  </si>
+  <si>
+    <t>28.09.202617</t>
+  </si>
+  <si>
+    <t>28.09.202618</t>
+  </si>
+  <si>
+    <t>28.09.202619</t>
+  </si>
+  <si>
+    <t>28.09.202620</t>
+  </si>
+  <si>
+    <t>28.09.202621</t>
+  </si>
+  <si>
+    <t>28.09.202622</t>
+  </si>
+  <si>
+    <t>28.09.202623</t>
+  </si>
+  <si>
+    <t>28.09.202624</t>
+  </si>
+  <si>
+    <t>28.09.202625</t>
+  </si>
+  <si>
+    <t>28.09.202626</t>
+  </si>
+  <si>
+    <t>28.09.202627</t>
+  </si>
+  <si>
+    <t>28.09.202628</t>
+  </si>
+  <si>
+    <t>28.09.202629</t>
+  </si>
+  <si>
+    <t>28.09.202630</t>
+  </si>
+  <si>
+    <t>28.09.202631</t>
+  </si>
+  <si>
+    <t>28.09.202632</t>
+  </si>
+  <si>
+    <t>28.09.202633</t>
+  </si>
+  <si>
+    <t>28.09.202634</t>
+  </si>
+  <si>
+    <t>28.09.202635</t>
+  </si>
+  <si>
+    <t>28.09.202636</t>
+  </si>
+  <si>
+    <t>28.09.202637</t>
+  </si>
+  <si>
+    <t>28.09.202638</t>
+  </si>
+  <si>
+    <t>28.09.202639</t>
+  </si>
+  <si>
+    <t>28.09.202640</t>
+  </si>
+  <si>
+    <t>28.09.202641</t>
+  </si>
+  <si>
+    <t>28.09.202642</t>
+  </si>
+  <si>
+    <t>28.09.202643</t>
+  </si>
+  <si>
+    <t>28.09.202644</t>
+  </si>
+  <si>
+    <t>28.09.202645</t>
+  </si>
+  <si>
+    <t>28.09.202646</t>
+  </si>
+  <si>
+    <t>28.09.202647</t>
+  </si>
+  <si>
+    <t>28.09.202648</t>
+  </si>
+  <si>
+    <t>28.09.202649</t>
+  </si>
+  <si>
+    <t>28.09.202650</t>
+  </si>
+  <si>
+    <t>28.09.202651</t>
+  </si>
+  <si>
+    <t>28.09.202652</t>
+  </si>
+  <si>
+    <t>28.09.202653</t>
+  </si>
+  <si>
+    <t>28.09.202654</t>
+  </si>
+  <si>
+    <t>28.09.202655</t>
+  </si>
+  <si>
+    <t>28.09.202656</t>
+  </si>
+  <si>
+    <t>28.09.202657</t>
+  </si>
+  <si>
+    <t>28.09.202658</t>
+  </si>
+  <si>
+    <t>28.09.202659</t>
+  </si>
+  <si>
+    <t>28.09.202660</t>
+  </si>
+  <si>
+    <t>28.09.202661</t>
+  </si>
+  <si>
+    <t>28.09.202662</t>
+  </si>
+  <si>
+    <t>28.09.202663</t>
+  </si>
+  <si>
+    <t>28.09.202664</t>
+  </si>
+  <si>
+    <t>28.09.202665</t>
+  </si>
+  <si>
+    <t>28.09.202666</t>
+  </si>
+  <si>
+    <t>28.09.202667</t>
+  </si>
+  <si>
+    <t>28.09.202668</t>
+  </si>
+  <si>
+    <t>28.09.202669</t>
+  </si>
+  <si>
+    <t>28.09.202670</t>
+  </si>
+  <si>
+    <t>28.09.202671</t>
+  </si>
+  <si>
+    <t>28.09.202672</t>
+  </si>
+  <si>
+    <t>28.09.202673</t>
+  </si>
+  <si>
+    <t>28.09.202674</t>
+  </si>
+  <si>
+    <t>28.09.202675</t>
+  </si>
+  <si>
+    <t>28.09.202676</t>
+  </si>
+  <si>
+    <t>28.09.202677</t>
+  </si>
+  <si>
+    <t>28.09.202678</t>
+  </si>
+  <si>
+    <t>28.09.202679</t>
+  </si>
+  <si>
+    <t>28.09.202680</t>
+  </si>
+  <si>
+    <t>28.09.202681</t>
+  </si>
+  <si>
+    <t>28.09.202682</t>
+  </si>
+  <si>
+    <t>28.09.202683</t>
+  </si>
+  <si>
+    <t>28.09.202684</t>
+  </si>
+  <si>
+    <t>28.09.202685</t>
+  </si>
+  <si>
+    <t>28.09.202686</t>
+  </si>
+  <si>
+    <t>28.09.202687</t>
+  </si>
+  <si>
+    <t>28.09.202688</t>
+  </si>
+  <si>
+    <t>28.09.202689</t>
+  </si>
+  <si>
+    <t>28.09.202690</t>
+  </si>
+  <si>
+    <t>28.09.202691</t>
+  </si>
+  <si>
+    <t>28.09.202692</t>
+  </si>
+  <si>
+    <t>28.09.202693</t>
+  </si>
+  <si>
+    <t>28.09.202694</t>
+  </si>
+  <si>
+    <t>28.09.202695</t>
+  </si>
+  <si>
+    <t>28.09.202696</t>
+  </si>
+  <si>
+    <t>29.09.20261</t>
+  </si>
+  <si>
+    <t>29.09.20262</t>
+  </si>
+  <si>
+    <t>29.09.20263</t>
+  </si>
+  <si>
+    <t>29.09.20264</t>
+  </si>
+  <si>
+    <t>29.09.20265</t>
+  </si>
+  <si>
+    <t>29.09.20266</t>
+  </si>
+  <si>
+    <t>29.09.20267</t>
+  </si>
+  <si>
+    <t>29.09.20268</t>
+  </si>
+  <si>
+    <t>29.09.20269</t>
+  </si>
+  <si>
+    <t>29.09.202610</t>
+  </si>
+  <si>
+    <t>29.09.202611</t>
+  </si>
+  <si>
+    <t>29.09.202612</t>
+  </si>
+  <si>
+    <t>29.09.202613</t>
+  </si>
+  <si>
+    <t>29.09.202614</t>
+  </si>
+  <si>
+    <t>29.09.202615</t>
+  </si>
+  <si>
+    <t>29.09.202616</t>
+  </si>
+  <si>
+    <t>29.09.202617</t>
+  </si>
+  <si>
+    <t>29.09.202618</t>
+  </si>
+  <si>
+    <t>29.09.202619</t>
+  </si>
+  <si>
+    <t>29.09.202620</t>
+  </si>
+  <si>
+    <t>29.09.202621</t>
+  </si>
+  <si>
+    <t>29.09.202622</t>
+  </si>
+  <si>
+    <t>29.09.202623</t>
+  </si>
+  <si>
+    <t>29.09.202624</t>
+  </si>
+  <si>
+    <t>29.09.202625</t>
+  </si>
+  <si>
+    <t>29.09.202626</t>
+  </si>
+  <si>
+    <t>29.09.202627</t>
+  </si>
+  <si>
+    <t>29.09.202628</t>
+  </si>
+  <si>
+    <t>29.09.202629</t>
+  </si>
+  <si>
+    <t>29.09.202630</t>
+  </si>
+  <si>
+    <t>29.09.202631</t>
+  </si>
+  <si>
+    <t>29.09.202632</t>
+  </si>
+  <si>
+    <t>29.09.202633</t>
+  </si>
+  <si>
+    <t>29.09.202634</t>
+  </si>
+  <si>
+    <t>29.09.202635</t>
+  </si>
+  <si>
+    <t>29.09.202636</t>
+  </si>
+  <si>
+    <t>29.09.202637</t>
+  </si>
+  <si>
+    <t>29.09.202638</t>
+  </si>
+  <si>
+    <t>29.09.202639</t>
+  </si>
+  <si>
+    <t>29.09.202640</t>
+  </si>
+  <si>
+    <t>29.09.202641</t>
+  </si>
+  <si>
+    <t>29.09.202642</t>
+  </si>
+  <si>
+    <t>29.09.202643</t>
+  </si>
+  <si>
+    <t>29.09.202644</t>
+  </si>
+  <si>
+    <t>29.09.202645</t>
+  </si>
+  <si>
+    <t>29.09.202646</t>
+  </si>
+  <si>
+    <t>29.09.202647</t>
+  </si>
+  <si>
+    <t>29.09.202648</t>
+  </si>
+  <si>
+    <t>29.09.202649</t>
+  </si>
+  <si>
+    <t>29.09.202650</t>
+  </si>
+  <si>
+    <t>29.09.202651</t>
+  </si>
+  <si>
+    <t>29.09.202652</t>
+  </si>
+  <si>
+    <t>29.09.202653</t>
+  </si>
+  <si>
+    <t>29.09.202654</t>
+  </si>
+  <si>
+    <t>29.09.202655</t>
+  </si>
+  <si>
+    <t>29.09.202656</t>
+  </si>
+  <si>
+    <t>29.09.202657</t>
+  </si>
+  <si>
+    <t>29.09.202658</t>
+  </si>
+  <si>
+    <t>29.09.202659</t>
+  </si>
+  <si>
+    <t>29.09.202660</t>
+  </si>
+  <si>
+    <t>29.09.202661</t>
+  </si>
+  <si>
+    <t>29.09.202662</t>
+  </si>
+  <si>
+    <t>29.09.202663</t>
+  </si>
+  <si>
+    <t>29.09.202664</t>
+  </si>
+  <si>
+    <t>29.09.202665</t>
+  </si>
+  <si>
+    <t>29.09.202666</t>
+  </si>
+  <si>
+    <t>29.09.202667</t>
+  </si>
+  <si>
+    <t>29.09.202668</t>
+  </si>
+  <si>
+    <t>29.09.202669</t>
+  </si>
+  <si>
+    <t>29.09.202670</t>
+  </si>
+  <si>
+    <t>29.09.202671</t>
+  </si>
+  <si>
+    <t>29.09.202672</t>
+  </si>
+  <si>
+    <t>29.09.202673</t>
+  </si>
+  <si>
+    <t>29.09.202674</t>
+  </si>
+  <si>
+    <t>29.09.202675</t>
+  </si>
+  <si>
+    <t>29.09.202676</t>
+  </si>
+  <si>
+    <t>29.09.202677</t>
+  </si>
+  <si>
+    <t>29.09.202678</t>
+  </si>
+  <si>
+    <t>29.09.202679</t>
+  </si>
+  <si>
+    <t>29.09.202680</t>
+  </si>
+  <si>
+    <t>29.09.202681</t>
+  </si>
+  <si>
+    <t>29.09.202682</t>
+  </si>
+  <si>
+    <t>29.09.202683</t>
+  </si>
+  <si>
+    <t>29.09.202684</t>
+  </si>
+  <si>
+    <t>29.09.202685</t>
+  </si>
+  <si>
+    <t>29.09.202686</t>
+  </si>
+  <si>
+    <t>29.09.202687</t>
+  </si>
+  <si>
+    <t>29.09.202688</t>
+  </si>
+  <si>
+    <t>29.09.202689</t>
+  </si>
+  <si>
+    <t>29.09.202690</t>
+  </si>
+  <si>
+    <t>29.09.202691</t>
+  </si>
+  <si>
+    <t>29.09.202692</t>
+  </si>
+  <si>
+    <t>29.09.202693</t>
+  </si>
+  <si>
+    <t>29.09.202694</t>
+  </si>
+  <si>
+    <t>29.09.202695</t>
+  </si>
+  <si>
+    <t>29.09.202696</t>
+  </si>
+  <si>
+    <t>30.09.20261</t>
+  </si>
+  <si>
+    <t>30.09.20262</t>
+  </si>
+  <si>
+    <t>30.09.20263</t>
+  </si>
+  <si>
+    <t>30.09.20264</t>
+  </si>
+  <si>
+    <t>30.09.20265</t>
+  </si>
+  <si>
+    <t>30.09.20266</t>
+  </si>
+  <si>
+    <t>30.09.20267</t>
+  </si>
+  <si>
+    <t>30.09.20268</t>
+  </si>
+  <si>
+    <t>30.09.20269</t>
+  </si>
+  <si>
+    <t>30.09.202610</t>
+  </si>
+  <si>
+    <t>30.09.202611</t>
+  </si>
+  <si>
+    <t>30.09.202612</t>
+  </si>
+  <si>
+    <t>30.09.202613</t>
+  </si>
+  <si>
+    <t>30.09.202614</t>
+  </si>
+  <si>
+    <t>30.09.202615</t>
+  </si>
+  <si>
+    <t>30.09.202616</t>
+  </si>
+  <si>
+    <t>30.09.202617</t>
+  </si>
+  <si>
+    <t>30.09.202618</t>
+  </si>
+  <si>
+    <t>30.09.202619</t>
+  </si>
+  <si>
+    <t>30.09.202620</t>
+  </si>
+  <si>
+    <t>30.09.202621</t>
+  </si>
+  <si>
+    <t>30.09.202622</t>
+  </si>
+  <si>
+    <t>30.09.202623</t>
+  </si>
+  <si>
+    <t>30.09.202624</t>
+  </si>
+  <si>
+    <t>30.09.202625</t>
+  </si>
+  <si>
+    <t>30.09.202626</t>
+  </si>
+  <si>
+    <t>30.09.202627</t>
+  </si>
+  <si>
+    <t>30.09.202628</t>
+  </si>
+  <si>
+    <t>30.09.202629</t>
+  </si>
+  <si>
+    <t>30.09.202630</t>
+  </si>
+  <si>
+    <t>30.09.202631</t>
+  </si>
+  <si>
+    <t>30.09.202632</t>
+  </si>
+  <si>
+    <t>30.09.202633</t>
+  </si>
+  <si>
+    <t>30.09.202634</t>
+  </si>
+  <si>
+    <t>30.09.202635</t>
+  </si>
+  <si>
+    <t>30.09.202636</t>
+  </si>
+  <si>
+    <t>30.09.202637</t>
+  </si>
+  <si>
+    <t>30.09.202638</t>
+  </si>
+  <si>
+    <t>30.09.202639</t>
+  </si>
+  <si>
+    <t>30.09.202640</t>
+  </si>
+  <si>
+    <t>30.09.202641</t>
+  </si>
+  <si>
+    <t>30.09.202642</t>
+  </si>
+  <si>
+    <t>30.09.202643</t>
+  </si>
+  <si>
+    <t>30.09.202644</t>
+  </si>
+  <si>
+    <t>30.09.202645</t>
+  </si>
+  <si>
+    <t>30.09.202646</t>
+  </si>
+  <si>
+    <t>30.09.202647</t>
+  </si>
+  <si>
+    <t>30.09.202648</t>
+  </si>
+  <si>
+    <t>30.09.202649</t>
+  </si>
+  <si>
+    <t>30.09.202650</t>
+  </si>
+  <si>
+    <t>30.09.202651</t>
+  </si>
+  <si>
+    <t>30.09.202652</t>
+  </si>
+  <si>
+    <t>30.09.202653</t>
+  </si>
+  <si>
+    <t>30.09.202654</t>
+  </si>
+  <si>
+    <t>30.09.202655</t>
+  </si>
+  <si>
+    <t>30.09.202656</t>
+  </si>
+  <si>
+    <t>30.09.202657</t>
+  </si>
+  <si>
+    <t>30.09.202658</t>
+  </si>
+  <si>
+    <t>30.09.202659</t>
+  </si>
+  <si>
+    <t>30.09.202660</t>
+  </si>
+  <si>
+    <t>30.09.202661</t>
+  </si>
+  <si>
+    <t>30.09.202662</t>
+  </si>
+  <si>
+    <t>30.09.202663</t>
+  </si>
+  <si>
+    <t>30.09.202664</t>
+  </si>
+  <si>
+    <t>30.09.202665</t>
+  </si>
+  <si>
+    <t>30.09.202666</t>
+  </si>
+  <si>
+    <t>30.09.202667</t>
+  </si>
+  <si>
+    <t>30.09.202668</t>
+  </si>
+  <si>
+    <t>30.09.202669</t>
+  </si>
+  <si>
+    <t>30.09.202670</t>
+  </si>
+  <si>
+    <t>30.09.202671</t>
+  </si>
+  <si>
+    <t>30.09.202672</t>
+  </si>
+  <si>
+    <t>30.09.202673</t>
+  </si>
+  <si>
+    <t>30.09.202674</t>
+  </si>
+  <si>
+    <t>30.09.202675</t>
+  </si>
+  <si>
+    <t>30.09.202676</t>
+  </si>
+  <si>
+    <t>30.09.202677</t>
+  </si>
+  <si>
+    <t>30.09.202678</t>
+  </si>
+  <si>
+    <t>30.09.202679</t>
+  </si>
+  <si>
+    <t>30.09.202680</t>
+  </si>
+  <si>
+    <t>30.09.202681</t>
+  </si>
+  <si>
+    <t>30.09.202682</t>
+  </si>
+  <si>
+    <t>30.09.202683</t>
+  </si>
+  <si>
+    <t>30.09.202684</t>
+  </si>
+  <si>
+    <t>30.09.202685</t>
+  </si>
+  <si>
+    <t>30.09.202686</t>
+  </si>
+  <si>
+    <t>30.09.202687</t>
+  </si>
+  <si>
+    <t>30.09.202688</t>
+  </si>
+  <si>
+    <t>30.09.202689</t>
+  </si>
+  <si>
+    <t>30.09.202690</t>
+  </si>
+  <si>
+    <t>30.09.202691</t>
+  </si>
+  <si>
+    <t>30.09.202692</t>
+  </si>
+  <si>
+    <t>30.09.202693</t>
+  </si>
+  <si>
+    <t>30.09.202694</t>
+  </si>
+  <si>
+    <t>30.09.202695</t>
+  </si>
+  <si>
+    <t>30.09.202696</t>
   </si>
 </sst>
 </file>
@@ -1288,19 +1288,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46283</v>
+        <v>46293</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>3.273</v>
       </c>
       <c r="C2">
-        <v>3.843</v>
+        <v>1.186</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1311,19 +1311,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46283.01041666666</v>
+        <v>46293.01041666666</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>4.035</v>
       </c>
       <c r="C3">
-        <v>2.223</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -1334,19 +1334,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46283.02083333334</v>
+        <v>46293.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.002</v>
+        <v>0.796</v>
       </c>
       <c r="C4">
-        <v>1.42</v>
+        <v>0.598</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -1357,19 +1357,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46283.03125</v>
+        <v>46293.03125</v>
       </c>
       <c r="B5">
-        <v>0.004</v>
+        <v>0.063</v>
       </c>
       <c r="C5">
-        <v>1.545</v>
+        <v>1.747</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -1380,19 +1380,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46283.04166666666</v>
+        <v>46293.04166666666</v>
       </c>
       <c r="B6">
-        <v>4.141</v>
+        <v>2.81</v>
       </c>
       <c r="C6">
-        <v>0.8070000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46283.05208333334</v>
+        <v>46293.05208333334</v>
       </c>
       <c r="B7">
-        <v>7.354</v>
+        <v>4.582</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1426,13 +1426,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46283.0625</v>
+        <v>46293.0625</v>
       </c>
       <c r="B8">
-        <v>13.946</v>
+        <v>0.132</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.261</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1449,13 +1449,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46283.07291666666</v>
+        <v>46293.07291666666</v>
       </c>
       <c r="B9">
-        <v>6.607</v>
+        <v>0.073</v>
       </c>
       <c r="C9">
-        <v>0.005</v>
+        <v>0.483</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1472,13 +1472,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46283.08333333334</v>
+        <v>46293.08333333334</v>
       </c>
       <c r="B10">
-        <v>0.268</v>
+        <v>0.026</v>
       </c>
       <c r="C10">
-        <v>0.008</v>
+        <v>0.304</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1495,13 +1495,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46283.09375</v>
+        <v>46293.09375</v>
       </c>
       <c r="B11">
-        <v>7.487</v>
+        <v>0.006</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>2.032</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1518,13 +1518,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46283.10416666666</v>
+        <v>46293.10416666666</v>
       </c>
       <c r="B12">
-        <v>4.715</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>5.665</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1541,13 +1541,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46283.11458333334</v>
+        <v>46293.11458333334</v>
       </c>
       <c r="B13">
-        <v>3.022</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>0.03</v>
+        <v>17.42</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1564,13 +1564,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46283.125</v>
+        <v>46293.125</v>
       </c>
       <c r="B14">
-        <v>2.616</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>3.345</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1587,13 +1587,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46283.13541666666</v>
+        <v>46293.13541666666</v>
       </c>
       <c r="B15">
-        <v>10.492</v>
+        <v>0.081</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>0.292</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1610,13 +1610,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46283.14583333334</v>
+        <v>46293.14583333334</v>
       </c>
       <c r="B16">
-        <v>37.064</v>
+        <v>0.11</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>0.078</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1633,13 +1633,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46283.15625</v>
+        <v>46293.15625</v>
       </c>
       <c r="B17">
-        <v>35.756</v>
+        <v>0.026</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>0.244</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1656,13 +1656,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46283.16666666666</v>
+        <v>46293.16666666666</v>
       </c>
       <c r="B18">
-        <v>14.294</v>
+        <v>0.11</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1679,10 +1679,10 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46283.17708333334</v>
+        <v>46293.17708333334</v>
       </c>
       <c r="B19">
-        <v>32.667</v>
+        <v>5.643</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1691,7 +1691,7 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F19">
         <v>18</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46283.1875</v>
+        <v>46293.1875</v>
       </c>
       <c r="B20">
-        <v>36.028</v>
+        <v>2.23</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1725,19 +1725,19 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46283.19791666666</v>
+        <v>46293.19791666666</v>
       </c>
       <c r="B21">
-        <v>40.948</v>
+        <v>16.31</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F21">
         <v>20</v>
@@ -1748,13 +1748,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46283.20833333334</v>
+        <v>46293.20833333334</v>
       </c>
       <c r="B22">
-        <v>22.108</v>
+        <v>4.5</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1771,10 +1771,10 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46283.21875</v>
+        <v>46293.21875</v>
       </c>
       <c r="B23">
-        <v>42.075</v>
+        <v>7.699</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46283.22916666666</v>
+        <v>46293.22916666666</v>
       </c>
       <c r="B24">
-        <v>31.368</v>
+        <v>8.821</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46283.23958333334</v>
+        <v>46293.23958333334</v>
       </c>
       <c r="B25">
-        <v>24.817</v>
+        <v>22.569</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1840,13 +1840,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46283.25</v>
+        <v>46293.25</v>
       </c>
       <c r="B26">
-        <v>24.649</v>
+        <v>16.688</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46283.26041666666</v>
+        <v>46293.26041666666</v>
       </c>
       <c r="B27">
-        <v>34.818</v>
+        <v>35.383</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46283.27083333334</v>
+        <v>46293.27083333334</v>
       </c>
       <c r="B28">
-        <v>33.298</v>
+        <v>27.735</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -1909,16 +1909,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46283.28125</v>
+        <v>46293.28125</v>
       </c>
       <c r="B29">
-        <v>5.698</v>
+        <v>8.028</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1932,16 +1932,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46283.29166666666</v>
+        <v>46293.29166666666</v>
       </c>
       <c r="B30">
-        <v>59.95</v>
+        <v>0.914</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>0.106</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1955,13 +1955,13 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46283.30208333334</v>
+        <v>46293.30208333334</v>
       </c>
       <c r="B31">
-        <v>89.01300000000001</v>
+        <v>0.165</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>0.298</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1978,16 +1978,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46283.3125</v>
+        <v>46293.3125</v>
       </c>
       <c r="B32">
-        <v>31.508</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="C32">
-        <v>0.003</v>
+        <v>0.482</v>
       </c>
       <c r="D32">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2001,16 +2001,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46283.32291666666</v>
+        <v>46293.32291666666</v>
       </c>
       <c r="B33">
-        <v>0.036</v>
+        <v>0.093</v>
       </c>
       <c r="C33">
-        <v>4.105</v>
+        <v>1.989</v>
       </c>
       <c r="D33">
-        <v>76.75</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2024,19 +2024,19 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46283.33333333334</v>
+        <v>46293.33333333334</v>
       </c>
       <c r="B34">
-        <v>0.274</v>
+        <v>0.04</v>
       </c>
       <c r="C34">
-        <v>3.09</v>
+        <v>3.914</v>
       </c>
       <c r="D34">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F34">
         <v>33</v>
@@ -2047,19 +2047,19 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46283.34375</v>
+        <v>46293.34375</v>
       </c>
       <c r="B35">
-        <v>0.101</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>0.301</v>
+        <v>28.294</v>
       </c>
       <c r="D35">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F35">
         <v>34</v>
@@ -2070,19 +2070,19 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46283.35416666666</v>
+        <v>46293.35416666666</v>
       </c>
       <c r="B36">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>0.956</v>
+        <v>26.44</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F36">
         <v>35</v>
@@ -2093,19 +2093,19 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46283.36458333334</v>
+        <v>46293.36458333334</v>
       </c>
       <c r="B37">
-        <v>4.688</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>0.096</v>
+        <v>5.693</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F37">
         <v>36</v>
@@ -2116,19 +2116,19 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46283.375</v>
+        <v>46293.375</v>
       </c>
       <c r="B38">
-        <v>8.44</v>
+        <v>0.129</v>
       </c>
       <c r="C38">
-        <v>0.339</v>
+        <v>5.64</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F38">
         <v>37</v>
@@ -2139,19 +2139,19 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46283.38541666666</v>
+        <v>46293.38541666666</v>
       </c>
       <c r="B39">
-        <v>3.429</v>
+        <v>0.026</v>
       </c>
       <c r="C39">
-        <v>0.9340000000000001</v>
+        <v>9.026999999999999</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="F39">
         <v>38</v>
@@ -2162,19 +2162,19 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46283.39583333334</v>
+        <v>46293.39583333334</v>
       </c>
       <c r="B40">
-        <v>14.454</v>
+        <v>2.615</v>
       </c>
       <c r="C40">
-        <v>0.03</v>
+        <v>5.05</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="F40">
         <v>39</v>
@@ -2185,19 +2185,19 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46283.40625</v>
+        <v>46293.40625</v>
       </c>
       <c r="B41">
-        <v>0.315</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>1.231</v>
+        <v>12.072</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="F41">
         <v>40</v>
@@ -2208,19 +2208,19 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46283.41666666666</v>
+        <v>46293.41666666666</v>
       </c>
       <c r="B42">
-        <v>0.657</v>
+        <v>0.053</v>
       </c>
       <c r="C42">
-        <v>0.165</v>
+        <v>8.462</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F42">
         <v>41</v>
@@ -2231,19 +2231,19 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46283.42708333334</v>
+        <v>46293.42708333334</v>
       </c>
       <c r="B43">
-        <v>0.079</v>
+        <v>0.705</v>
       </c>
       <c r="C43">
-        <v>0.306</v>
+        <v>2.683</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F43">
         <v>42</v>
@@ -2254,19 +2254,19 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46283.4375</v>
+        <v>46293.4375</v>
       </c>
       <c r="B44">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>1.467</v>
+        <v>7.9</v>
       </c>
       <c r="D44">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F44">
         <v>43</v>
@@ -2277,19 +2277,19 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46283.44791666666</v>
+        <v>46293.44791666666</v>
       </c>
       <c r="B45">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <v>0.854</v>
+        <v>23.66</v>
       </c>
       <c r="D45">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F45">
         <v>44</v>
@@ -2300,19 +2300,19 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46283.45833333334</v>
+        <v>46293.45833333334</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="C46">
-        <v>13.773</v>
+        <v>6.486</v>
       </c>
       <c r="D46">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F46">
         <v>45</v>
@@ -2323,19 +2323,19 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46283.46875</v>
+        <v>46293.46875</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>0.621</v>
       </c>
       <c r="C47">
-        <v>19.242</v>
+        <v>1.714</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F47">
         <v>46</v>
@@ -2346,19 +2346,19 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46283.47916666666</v>
+        <v>46293.47916666666</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>0.155</v>
       </c>
       <c r="C48">
-        <v>18.125</v>
+        <v>4.911</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F48">
         <v>47</v>
@@ -2369,19 +2369,19 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46283.48958333334</v>
+        <v>46293.48958333334</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="C49">
-        <v>22.506</v>
+        <v>7.781</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F49">
         <v>48</v>
@@ -2392,19 +2392,19 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46283.5</v>
+        <v>46293.5</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>7.731</v>
       </c>
       <c r="C50">
-        <v>24.549</v>
+        <v>2.262</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F50">
         <v>49</v>
@@ -2415,19 +2415,19 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46283.51041666666</v>
+        <v>46293.51041666666</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>12.028</v>
       </c>
       <c r="C51">
-        <v>32.629</v>
+        <v>0</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F51">
         <v>50</v>
@@ -2438,13 +2438,13 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46283.52083333334</v>
+        <v>46293.52083333334</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>2.932</v>
       </c>
       <c r="C52">
-        <v>55.216</v>
+        <v>15.745</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2461,19 +2461,19 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46283.53125</v>
+        <v>46293.53125</v>
       </c>
       <c r="B53">
-        <v>1.055</v>
+        <v>0.135</v>
       </c>
       <c r="C53">
-        <v>6.441</v>
+        <v>5.595</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F53">
         <v>52</v>
@@ -2484,13 +2484,13 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46283.54166666666</v>
+        <v>46293.54166666666</v>
       </c>
       <c r="B54">
-        <v>3.521</v>
+        <v>0.224</v>
       </c>
       <c r="C54">
-        <v>0.347</v>
+        <v>6.385</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2507,13 +2507,13 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46283.55208333334</v>
+        <v>46293.55208333334</v>
       </c>
       <c r="B55">
-        <v>0.038</v>
+        <v>3.064</v>
       </c>
       <c r="C55">
-        <v>0.533</v>
+        <v>0.22</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2530,19 +2530,19 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46283.5625</v>
+        <v>46293.5625</v>
       </c>
       <c r="B56">
-        <v>0.429</v>
+        <v>0.199</v>
       </c>
       <c r="C56">
-        <v>0.132</v>
+        <v>3.048</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F56">
         <v>55</v>
@@ -2553,19 +2553,19 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46283.57291666666</v>
+        <v>46293.57291666666</v>
       </c>
       <c r="B57">
-        <v>0.206</v>
+        <v>2.393</v>
       </c>
       <c r="C57">
-        <v>2.317</v>
+        <v>1.278</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F57">
         <v>56</v>
@@ -2576,19 +2576,19 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46283.58333333334</v>
+        <v>46293.58333333334</v>
       </c>
       <c r="B58">
-        <v>0.155</v>
+        <v>0.011</v>
       </c>
       <c r="C58">
-        <v>0.352</v>
+        <v>24.959</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F58">
         <v>57</v>
@@ -2599,19 +2599,19 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46283.59375</v>
+        <v>46293.59375</v>
       </c>
       <c r="B59">
-        <v>0.247</v>
+        <v>0</v>
       </c>
       <c r="C59">
-        <v>0.641</v>
+        <v>12.914</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F59">
         <v>58</v>
@@ -2622,19 +2622,19 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46283.60416666666</v>
+        <v>46293.60416666666</v>
       </c>
       <c r="B60">
-        <v>0.09</v>
+        <v>2.44</v>
       </c>
       <c r="C60">
-        <v>5.898</v>
+        <v>1.846</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F60">
         <v>59</v>
@@ -2645,19 +2645,19 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46283.61458333334</v>
+        <v>46293.61458333334</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="C61">
-        <v>26.407</v>
+        <v>21.417</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F61">
         <v>60</v>
@@ -2668,19 +2668,19 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46283.625</v>
+        <v>46293.625</v>
       </c>
       <c r="B62">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="C62">
-        <v>11.805</v>
+        <v>25.484</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F62">
         <v>61</v>
@@ -2691,19 +2691,19 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46283.63541666666</v>
+        <v>46293.63541666666</v>
       </c>
       <c r="B63">
-        <v>0.094</v>
+        <v>8.048999999999999</v>
       </c>
       <c r="C63">
-        <v>1.989</v>
+        <v>6.825</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F63">
         <v>62</v>
@@ -2714,19 +2714,19 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46283.64583333334</v>
+        <v>46293.64583333334</v>
       </c>
       <c r="B64">
-        <v>0.27</v>
+        <v>59.192</v>
       </c>
       <c r="C64">
-        <v>13.886</v>
+        <v>0</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F64">
         <v>63</v>
@@ -2737,13 +2737,13 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46283.65625</v>
+        <v>46293.65625</v>
       </c>
       <c r="B65">
-        <v>0.347</v>
+        <v>21.419</v>
       </c>
       <c r="C65">
-        <v>0.294</v>
+        <v>0</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -2760,13 +2760,13 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46283.66666666666</v>
+        <v>46293.66666666666</v>
       </c>
       <c r="B66">
-        <v>1.341</v>
+        <v>12.407</v>
       </c>
       <c r="C66">
-        <v>0.488</v>
+        <v>0</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -2783,13 +2783,13 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46283.67708333334</v>
+        <v>46293.67708333334</v>
       </c>
       <c r="B67">
-        <v>1.223</v>
+        <v>14.263</v>
       </c>
       <c r="C67">
-        <v>0.128</v>
+        <v>0</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -2806,13 +2806,13 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46283.6875</v>
+        <v>46293.6875</v>
       </c>
       <c r="B68">
-        <v>10.236</v>
+        <v>17.574</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46283.69791666666</v>
+        <v>46293.69791666666</v>
       </c>
       <c r="B69">
-        <v>21.355</v>
+        <v>30.534</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -2852,13 +2852,13 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46283.70833333334</v>
+        <v>46293.70833333334</v>
       </c>
       <c r="B70">
-        <v>22.032</v>
+        <v>5.272</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -2875,13 +2875,13 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46283.71875</v>
+        <v>46293.71875</v>
       </c>
       <c r="B71">
-        <v>38.271</v>
+        <v>0.131</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -2898,16 +2898,16 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46283.72916666666</v>
+        <v>46293.72916666666</v>
       </c>
       <c r="B72">
-        <v>14.938</v>
+        <v>3.928</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="D72">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -2921,16 +2921,16 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46283.73958333334</v>
+        <v>46293.73958333334</v>
       </c>
       <c r="B73">
-        <v>26.477</v>
+        <v>11.133</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -2944,10 +2944,10 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46283.75</v>
+        <v>46293.75</v>
       </c>
       <c r="B74">
-        <v>12.68</v>
+        <v>13.332</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2967,16 +2967,16 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46283.76041666666</v>
+        <v>46293.76041666666</v>
       </c>
       <c r="B75">
-        <v>0.377</v>
+        <v>22.156</v>
       </c>
       <c r="C75">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -2990,16 +2990,16 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46283.77083333334</v>
+        <v>46293.77083333334</v>
       </c>
       <c r="B76">
-        <v>8.69</v>
+        <v>25.948</v>
       </c>
       <c r="C76">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D76">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -3013,16 +3013,16 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46283.78125</v>
+        <v>46293.78125</v>
       </c>
       <c r="B77">
-        <v>4.609</v>
+        <v>13.519</v>
       </c>
       <c r="C77">
-        <v>0.109</v>
+        <v>0</v>
       </c>
       <c r="D77">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -3036,13 +3036,13 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46283.79166666666</v>
+        <v>46293.79166666666</v>
       </c>
       <c r="B78">
-        <v>2.169</v>
+        <v>4.517</v>
       </c>
       <c r="C78">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -3059,13 +3059,13 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46283.80208333334</v>
+        <v>46293.80208333334</v>
       </c>
       <c r="B79">
-        <v>0.757</v>
+        <v>3.677</v>
       </c>
       <c r="C79">
-        <v>0.03</v>
+        <v>0.007</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -3082,13 +3082,13 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46283.8125</v>
+        <v>46293.8125</v>
       </c>
       <c r="B80">
-        <v>0.094</v>
+        <v>1.117</v>
       </c>
       <c r="C80">
-        <v>0.176</v>
+        <v>0.483</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3105,13 +3105,13 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46283.82291666666</v>
+        <v>46293.82291666666</v>
       </c>
       <c r="B81">
-        <v>0.08599999999999999</v>
+        <v>0</v>
       </c>
       <c r="C81">
-        <v>0.172</v>
+        <v>5.12</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -3128,13 +3128,13 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46283.83333333334</v>
+        <v>46293.83333333334</v>
       </c>
       <c r="B82">
-        <v>0.178</v>
+        <v>0.968</v>
       </c>
       <c r="C82">
-        <v>0.224</v>
+        <v>1.494</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -3151,13 +3151,13 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46283.84375</v>
+        <v>46293.84375</v>
       </c>
       <c r="B83">
-        <v>0.447</v>
+        <v>12.334</v>
       </c>
       <c r="C83">
-        <v>0.637</v>
+        <v>0.382</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -3174,13 +3174,13 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46283.85416666666</v>
+        <v>46293.85416666666</v>
       </c>
       <c r="B84">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="C84">
-        <v>2.679</v>
+        <v>2.534</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -3197,13 +3197,13 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46283.86458333334</v>
+        <v>46293.86458333334</v>
       </c>
       <c r="B85">
-        <v>0.111</v>
+        <v>1.902</v>
       </c>
       <c r="C85">
-        <v>0.243</v>
+        <v>2.28</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -3220,13 +3220,13 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46283.875</v>
+        <v>46293.875</v>
       </c>
       <c r="B86">
-        <v>26.127</v>
+        <v>0.005</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>2.946</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -3243,13 +3243,13 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46283.88541666666</v>
+        <v>46293.88541666666</v>
       </c>
       <c r="B87">
-        <v>20.118</v>
+        <v>0.02</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>2.587</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -3266,13 +3266,13 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46283.89583333334</v>
+        <v>46293.89583333334</v>
       </c>
       <c r="B88">
-        <v>19.567</v>
+        <v>0</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>4.956</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3289,13 +3289,13 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46283.90625</v>
+        <v>46293.90625</v>
       </c>
       <c r="B89">
-        <v>15.616</v>
+        <v>0</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>17.074</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3312,13 +3312,13 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46283.91666666666</v>
+        <v>46293.91666666666</v>
       </c>
       <c r="B90">
-        <v>4.221</v>
+        <v>0.656</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>6.557</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3335,13 +3335,13 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46283.92708333334</v>
+        <v>46293.92708333334</v>
       </c>
       <c r="B91">
-        <v>21.103</v>
+        <v>0</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3358,13 +3358,13 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46283.9375</v>
+        <v>46293.9375</v>
       </c>
       <c r="B92">
-        <v>28.144</v>
+        <v>0</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>7.152</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3381,13 +3381,13 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46283.94791666666</v>
+        <v>46293.94791666666</v>
       </c>
       <c r="B93">
-        <v>15.356</v>
+        <v>0</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>11.314</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3404,13 +3404,13 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46283.95833333334</v>
+        <v>46293.95833333334</v>
       </c>
       <c r="B94">
-        <v>61.377</v>
+        <v>0</v>
       </c>
       <c r="C94">
-        <v>0</v>
+        <v>5.503</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3427,13 +3427,13 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46283.96875</v>
+        <v>46293.96875</v>
       </c>
       <c r="B95">
-        <v>76.708</v>
+        <v>0.162</v>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3450,16 +3450,16 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46283.97916666666</v>
+        <v>46293.97916666666</v>
       </c>
       <c r="B96">
-        <v>36.591</v>
+        <v>0</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>2.975</v>
       </c>
       <c r="D96">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -3473,16 +3473,16 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46283.98958333334</v>
+        <v>46293.98958333334</v>
       </c>
       <c r="B97">
-        <v>15.741</v>
+        <v>0.031</v>
       </c>
       <c r="C97">
-        <v>0.115</v>
+        <v>0.8</v>
       </c>
       <c r="D97">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -3496,16 +3496,16 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46284</v>
+        <v>46294</v>
       </c>
       <c r="B98">
-        <v>5.869</v>
+        <v>1.2</v>
       </c>
       <c r="C98">
-        <v>0.008</v>
+        <v>0.09</v>
       </c>
       <c r="D98">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -3519,16 +3519,16 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46284.01041666666</v>
+        <v>46294.01041666666</v>
       </c>
       <c r="B99">
-        <v>0.139</v>
+        <v>8.057</v>
       </c>
       <c r="C99">
-        <v>0.137</v>
+        <v>0</v>
       </c>
       <c r="D99">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -3542,13 +3542,13 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46284.02083333334</v>
+        <v>46294.02083333334</v>
       </c>
       <c r="B100">
-        <v>19.961</v>
+        <v>4.656</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>1.252</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -3565,13 +3565,13 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46284.03125</v>
+        <v>46294.03125</v>
       </c>
       <c r="B101">
-        <v>8.858000000000001</v>
+        <v>0.012</v>
       </c>
       <c r="C101">
-        <v>0.255</v>
+        <v>2.438</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -3588,13 +3588,13 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46284.04166666666</v>
+        <v>46294.04166666666</v>
       </c>
       <c r="B102">
-        <v>0.061</v>
+        <v>0.241</v>
       </c>
       <c r="C102">
-        <v>0.079</v>
+        <v>1.871</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3611,13 +3611,13 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46284.05208333334</v>
+        <v>46294.05208333334</v>
       </c>
       <c r="B103">
-        <v>1.293</v>
+        <v>4.048</v>
       </c>
       <c r="C103">
-        <v>0.04</v>
+        <v>0.101</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -3634,13 +3634,13 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46284.0625</v>
+        <v>46294.0625</v>
       </c>
       <c r="B104">
-        <v>1.721</v>
+        <v>3.114</v>
       </c>
       <c r="C104">
-        <v>0.018</v>
+        <v>0.222</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -3657,13 +3657,13 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46284.07291666666</v>
+        <v>46294.07291666666</v>
       </c>
       <c r="B105">
-        <v>3.134</v>
+        <v>0.239</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -3680,13 +3680,13 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46284.08333333334</v>
+        <v>46294.08333333334</v>
       </c>
       <c r="B106">
-        <v>0.987</v>
+        <v>10.389</v>
       </c>
       <c r="C106">
-        <v>0.065</v>
+        <v>0</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -3703,13 +3703,13 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46284.09375</v>
+        <v>46294.09375</v>
       </c>
       <c r="B107">
-        <v>0.207</v>
+        <v>6.251</v>
       </c>
       <c r="C107">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -3726,13 +3726,13 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46284.10416666666</v>
+        <v>46294.10416666666</v>
       </c>
       <c r="B108">
-        <v>0.702</v>
+        <v>0.928</v>
       </c>
       <c r="C108">
-        <v>0.08500000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -3749,13 +3749,13 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46284.11458333334</v>
+        <v>46294.11458333334</v>
       </c>
       <c r="B109">
-        <v>0.8120000000000001</v>
+        <v>0.194</v>
       </c>
       <c r="C109">
-        <v>0.004</v>
+        <v>0.593</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -3772,13 +3772,13 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46284.125</v>
+        <v>46294.125</v>
       </c>
       <c r="B110">
-        <v>0.857</v>
+        <v>8.236000000000001</v>
       </c>
       <c r="C110">
-        <v>0.524</v>
+        <v>0</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -3795,13 +3795,13 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46284.13541666666</v>
+        <v>46294.13541666666</v>
       </c>
       <c r="B111">
-        <v>0.554</v>
+        <v>9.734</v>
       </c>
       <c r="C111">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -3818,13 +3818,13 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46284.14583333334</v>
+        <v>46294.14583333334</v>
       </c>
       <c r="B112">
-        <v>0.144</v>
+        <v>22.985</v>
       </c>
       <c r="C112">
-        <v>0.08400000000000001</v>
+        <v>0</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -3841,13 +3841,13 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46284.15625</v>
+        <v>46294.15625</v>
       </c>
       <c r="B113">
-        <v>0.394</v>
+        <v>4.162</v>
       </c>
       <c r="C113">
-        <v>0.527</v>
+        <v>0.016</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -3864,13 +3864,13 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46284.16666666666</v>
+        <v>46294.16666666666</v>
       </c>
       <c r="B114">
-        <v>0.073</v>
+        <v>1.869</v>
       </c>
       <c r="C114">
-        <v>0.393</v>
+        <v>0.058</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -3887,13 +3887,13 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46284.17708333334</v>
+        <v>46294.17708333334</v>
       </c>
       <c r="B115">
-        <v>4.13</v>
+        <v>2.443</v>
       </c>
       <c r="C115">
-        <v>0.021</v>
+        <v>0.003</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -3910,13 +3910,13 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46284.1875</v>
+        <v>46294.1875</v>
       </c>
       <c r="B116">
-        <v>4.45</v>
+        <v>13.169</v>
       </c>
       <c r="C116">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -3933,13 +3933,13 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46284.19791666666</v>
+        <v>46294.19791666666</v>
       </c>
       <c r="B117">
-        <v>3.236</v>
+        <v>10.581</v>
       </c>
       <c r="C117">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -3956,13 +3956,13 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46284.20833333334</v>
+        <v>46294.20833333334</v>
       </c>
       <c r="B118">
-        <v>2.747</v>
+        <v>1.218</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>0.127</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -3979,10 +3979,10 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46284.21875</v>
+        <v>46294.21875</v>
       </c>
       <c r="B119">
-        <v>17.462</v>
+        <v>4.398</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -4002,10 +4002,10 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46284.22916666666</v>
+        <v>46294.22916666666</v>
       </c>
       <c r="B120">
-        <v>16.559</v>
+        <v>9.368</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -4025,10 +4025,10 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46284.23958333334</v>
+        <v>46294.23958333334</v>
       </c>
       <c r="B121">
-        <v>7.191</v>
+        <v>11.927</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -4048,13 +4048,13 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46284.25</v>
+        <v>46294.25</v>
       </c>
       <c r="B122">
-        <v>6.524</v>
+        <v>15.741</v>
       </c>
       <c r="C122">
-        <v>0</v>
+        <v>1.088</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -4071,10 +4071,10 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46284.26041666666</v>
+        <v>46294.26041666666</v>
       </c>
       <c r="B123">
-        <v>3.226</v>
+        <v>31.915</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -4094,10 +4094,10 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46284.27083333334</v>
+        <v>46294.27083333334</v>
       </c>
       <c r="B124">
-        <v>6.815</v>
+        <v>23.683</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -4117,13 +4117,13 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46284.28125</v>
+        <v>46294.28125</v>
       </c>
       <c r="B125">
-        <v>0.8090000000000001</v>
+        <v>33.605</v>
       </c>
       <c r="C125">
-        <v>2.501</v>
+        <v>0</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -4140,13 +4140,13 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46284.29166666666</v>
+        <v>46294.29166666666</v>
       </c>
       <c r="B126">
-        <v>14.63</v>
+        <v>48.953</v>
       </c>
       <c r="C126">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -4163,13 +4163,13 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46284.30208333334</v>
+        <v>46294.30208333334</v>
       </c>
       <c r="B127">
-        <v>0.498</v>
+        <v>32.477</v>
       </c>
       <c r="C127">
-        <v>0.122</v>
+        <v>0</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -4186,13 +4186,13 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46284.3125</v>
+        <v>46294.3125</v>
       </c>
       <c r="B128">
-        <v>1.493</v>
+        <v>0.283</v>
       </c>
       <c r="C128">
-        <v>0.067</v>
+        <v>2.461</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -4209,13 +4209,13 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46284.32291666666</v>
+        <v>46294.32291666666</v>
       </c>
       <c r="B129">
-        <v>0.308</v>
+        <v>0.005</v>
       </c>
       <c r="C129">
-        <v>0.581</v>
+        <v>2.661</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -4232,13 +4232,13 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46284.33333333334</v>
+        <v>46294.33333333334</v>
       </c>
       <c r="B130">
-        <v>10.204</v>
+        <v>0.119</v>
       </c>
       <c r="C130">
-        <v>0.02</v>
+        <v>0.603</v>
       </c>
       <c r="D130">
         <v>0</v>
@@ -4255,13 +4255,13 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46284.34375</v>
+        <v>46294.34375</v>
       </c>
       <c r="B131">
-        <v>0.746</v>
+        <v>0.191</v>
       </c>
       <c r="C131">
-        <v>0.037</v>
+        <v>4.95</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -4278,13 +4278,13 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46284.35416666666</v>
+        <v>46294.35416666666</v>
       </c>
       <c r="B132">
-        <v>5.163</v>
+        <v>0.023</v>
       </c>
       <c r="C132">
-        <v>0.287</v>
+        <v>8.944000000000001</v>
       </c>
       <c r="D132">
         <v>0</v>
@@ -4301,19 +4301,19 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46284.36458333334</v>
+        <v>46294.36458333334</v>
       </c>
       <c r="B133">
-        <v>0.198</v>
+        <v>0</v>
       </c>
       <c r="C133">
-        <v>3.218</v>
+        <v>5.207</v>
       </c>
       <c r="D133">
         <v>0</v>
       </c>
       <c r="E133">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F133">
         <v>36</v>
@@ -4324,19 +4324,19 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46284.375</v>
+        <v>46294.375</v>
       </c>
       <c r="B134">
-        <v>0.026</v>
+        <v>0.5</v>
       </c>
       <c r="C134">
-        <v>5.669</v>
+        <v>0.061</v>
       </c>
       <c r="D134">
         <v>0</v>
       </c>
       <c r="E134">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F134">
         <v>37</v>
@@ -4347,19 +4347,19 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46284.38541666666</v>
+        <v>46294.38541666666</v>
       </c>
       <c r="B135">
-        <v>2.731</v>
+        <v>3.339</v>
       </c>
       <c r="C135">
-        <v>0.963</v>
+        <v>0.014</v>
       </c>
       <c r="D135">
         <v>0</v>
       </c>
       <c r="E135">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F135">
         <v>38</v>
@@ -4370,19 +4370,19 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46284.39583333334</v>
+        <v>46294.39583333334</v>
       </c>
       <c r="B136">
-        <v>0.143</v>
+        <v>5.061</v>
       </c>
       <c r="C136">
-        <v>5.531</v>
+        <v>0.012</v>
       </c>
       <c r="D136">
         <v>0</v>
       </c>
       <c r="E136">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F136">
         <v>39</v>
@@ -4393,13 +4393,13 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46284.40625</v>
+        <v>46294.40625</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="C137">
-        <v>12.506</v>
+        <v>0.353</v>
       </c>
       <c r="D137">
         <v>0</v>
@@ -4416,13 +4416,13 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46284.41666666666</v>
+        <v>46294.41666666666</v>
       </c>
       <c r="B138">
-        <v>0.003</v>
+        <v>0.258</v>
       </c>
       <c r="C138">
-        <v>7.275</v>
+        <v>0.132</v>
       </c>
       <c r="D138">
         <v>0</v>
@@ -4439,13 +4439,13 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46284.42708333334</v>
+        <v>46294.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>0.103</v>
       </c>
       <c r="C139">
-        <v>7.365</v>
+        <v>0.189</v>
       </c>
       <c r="D139">
         <v>0</v>
@@ -4462,13 +4462,13 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46284.4375</v>
+        <v>46294.4375</v>
       </c>
       <c r="B140">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="C140">
-        <v>3.181</v>
+        <v>3.59</v>
       </c>
       <c r="D140">
         <v>0</v>
@@ -4485,19 +4485,19 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46284.44791666666</v>
+        <v>46294.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
       </c>
       <c r="C141">
-        <v>18.711</v>
+        <v>11.153</v>
       </c>
       <c r="D141">
         <v>0</v>
       </c>
       <c r="E141">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F141">
         <v>44</v>
@@ -4508,19 +4508,19 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46284.45833333334</v>
+        <v>46294.45833333334</v>
       </c>
       <c r="B142">
-        <v>0.103</v>
+        <v>0</v>
       </c>
       <c r="C142">
-        <v>7.578</v>
+        <v>17.793</v>
       </c>
       <c r="D142">
         <v>0</v>
       </c>
       <c r="E142">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F142">
         <v>45</v>
@@ -4531,19 +4531,19 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46284.46875</v>
+        <v>46294.46875</v>
       </c>
       <c r="B143">
-        <v>0.012</v>
+        <v>0.041</v>
       </c>
       <c r="C143">
-        <v>5.763</v>
+        <v>3.48</v>
       </c>
       <c r="D143">
         <v>0</v>
       </c>
       <c r="E143">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F143">
         <v>46</v>
@@ -4554,19 +4554,19 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46284.47916666666</v>
+        <v>46294.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="C144">
-        <v>6.24</v>
+        <v>1.765</v>
       </c>
       <c r="D144">
         <v>0</v>
       </c>
       <c r="E144">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F144">
         <v>47</v>
@@ -4577,19 +4577,19 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46284.48958333334</v>
+        <v>46294.48958333334</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="C145">
-        <v>3.879</v>
+        <v>2.184</v>
       </c>
       <c r="D145">
         <v>0</v>
       </c>
       <c r="E145">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F145">
         <v>48</v>
@@ -4600,19 +4600,19 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46284.5</v>
+        <v>46294.5</v>
       </c>
       <c r="B146">
         <v>0</v>
       </c>
       <c r="C146">
-        <v>13.979</v>
+        <v>12.413</v>
       </c>
       <c r="D146">
         <v>0</v>
       </c>
       <c r="E146">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F146">
         <v>49</v>
@@ -4623,19 +4623,19 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46284.51041666666</v>
+        <v>46294.51041666666</v>
       </c>
       <c r="B147">
-        <v>0.101</v>
+        <v>0</v>
       </c>
       <c r="C147">
-        <v>3.151</v>
+        <v>12.427</v>
       </c>
       <c r="D147">
         <v>0</v>
       </c>
       <c r="E147">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F147">
         <v>50</v>
@@ -4646,19 +4646,19 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46284.52083333334</v>
+        <v>46294.52083333334</v>
       </c>
       <c r="B148">
-        <v>0.099</v>
+        <v>0.012</v>
       </c>
       <c r="C148">
-        <v>1.047</v>
+        <v>5.268</v>
       </c>
       <c r="D148">
         <v>0</v>
       </c>
       <c r="E148">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F148">
         <v>51</v>
@@ -4669,19 +4669,19 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46284.53125</v>
+        <v>46294.53125</v>
       </c>
       <c r="B149">
-        <v>0.044</v>
+        <v>1.548</v>
       </c>
       <c r="C149">
-        <v>0.871</v>
+        <v>1.367</v>
       </c>
       <c r="D149">
         <v>0</v>
       </c>
       <c r="E149">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F149">
         <v>52</v>
@@ -4692,19 +4692,19 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46284.54166666666</v>
+        <v>46294.54166666666</v>
       </c>
       <c r="B150">
-        <v>4.862</v>
+        <v>7.241</v>
       </c>
       <c r="C150">
-        <v>0.062</v>
+        <v>0</v>
       </c>
       <c r="D150">
         <v>0</v>
       </c>
       <c r="E150">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F150">
         <v>53</v>
@@ -4715,19 +4715,19 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46284.55208333334</v>
+        <v>46294.55208333334</v>
       </c>
       <c r="B151">
-        <v>17.11</v>
+        <v>0.287</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="D151">
         <v>0</v>
       </c>
       <c r="E151">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F151">
         <v>54</v>
@@ -4738,19 +4738,19 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46284.5625</v>
+        <v>46294.5625</v>
       </c>
       <c r="B152">
-        <v>0.8179999999999999</v>
+        <v>0.139</v>
       </c>
       <c r="C152">
-        <v>2.904</v>
+        <v>1.117</v>
       </c>
       <c r="D152">
         <v>0</v>
       </c>
       <c r="E152">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F152">
         <v>55</v>
@@ -4761,19 +4761,19 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46284.57291666666</v>
+        <v>46294.57291666666</v>
       </c>
       <c r="B153">
-        <v>0.054</v>
+        <v>0</v>
       </c>
       <c r="C153">
-        <v>2.382</v>
+        <v>9.099</v>
       </c>
       <c r="D153">
         <v>0</v>
       </c>
       <c r="E153">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F153">
         <v>56</v>
@@ -4784,19 +4784,19 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46284.58333333334</v>
+        <v>46294.58333333334</v>
       </c>
       <c r="B154">
-        <v>1.636</v>
+        <v>0</v>
       </c>
       <c r="C154">
-        <v>3.999</v>
+        <v>36.027</v>
       </c>
       <c r="D154">
         <v>0</v>
       </c>
       <c r="E154">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F154">
         <v>57</v>
@@ -4807,19 +4807,19 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46284.59375</v>
+        <v>46294.59375</v>
       </c>
       <c r="B155">
-        <v>0.004</v>
+        <v>0.198</v>
       </c>
       <c r="C155">
-        <v>9.345000000000001</v>
+        <v>0.909</v>
       </c>
       <c r="D155">
         <v>0</v>
       </c>
       <c r="E155">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F155">
         <v>58</v>
@@ -4830,19 +4830,19 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46284.60416666666</v>
+        <v>46294.60416666666</v>
       </c>
       <c r="B156">
-        <v>0.023</v>
+        <v>0.079</v>
       </c>
       <c r="C156">
-        <v>10.915</v>
+        <v>1.991</v>
       </c>
       <c r="D156">
         <v>0</v>
       </c>
       <c r="E156">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F156">
         <v>59</v>
@@ -4853,19 +4853,19 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46284.61458333334</v>
+        <v>46294.61458333334</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>0.052</v>
       </c>
       <c r="C157">
-        <v>18.408</v>
+        <v>3.015</v>
       </c>
       <c r="D157">
         <v>0</v>
       </c>
       <c r="E157">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F157">
         <v>60</v>
@@ -4876,19 +4876,19 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46284.625</v>
+        <v>46294.625</v>
       </c>
       <c r="B158">
         <v>0</v>
       </c>
       <c r="C158">
-        <v>12.06</v>
+        <v>25.56</v>
       </c>
       <c r="D158">
         <v>0</v>
       </c>
       <c r="E158">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F158">
         <v>61</v>
@@ -4899,19 +4899,19 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46284.63541666666</v>
+        <v>46294.63541666666</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="C159">
-        <v>16.587</v>
+        <v>3.163</v>
       </c>
       <c r="D159">
         <v>0</v>
       </c>
       <c r="E159">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F159">
         <v>62</v>
@@ -4922,19 +4922,19 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46284.64583333334</v>
+        <v>46294.64583333334</v>
       </c>
       <c r="B160">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="C160">
-        <v>17.788</v>
+        <v>5.256</v>
       </c>
       <c r="D160">
         <v>0</v>
       </c>
       <c r="E160">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F160">
         <v>63</v>
@@ -4945,19 +4945,19 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46284.65625</v>
+        <v>46294.65625</v>
       </c>
       <c r="B161">
-        <v>0.011</v>
+        <v>7.34</v>
       </c>
       <c r="C161">
-        <v>10.671</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="D161">
         <v>0</v>
       </c>
       <c r="E161">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F161">
         <v>64</v>
@@ -4968,19 +4968,19 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46284.66666666666</v>
+        <v>46294.66666666666</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>6.648</v>
       </c>
       <c r="C162">
-        <v>29.459</v>
+        <v>0.001</v>
       </c>
       <c r="D162">
         <v>0</v>
       </c>
       <c r="E162">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F162">
         <v>65</v>
@@ -4991,13 +4991,13 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46284.67708333334</v>
+        <v>46294.67708333334</v>
       </c>
       <c r="B163">
-        <v>0</v>
+        <v>25.675</v>
       </c>
       <c r="C163">
-        <v>26.123</v>
+        <v>0</v>
       </c>
       <c r="D163">
         <v>0</v>
@@ -5014,13 +5014,13 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46284.6875</v>
+        <v>46294.6875</v>
       </c>
       <c r="B164">
-        <v>0.221</v>
+        <v>58.554</v>
       </c>
       <c r="C164">
-        <v>0.542</v>
+        <v>0</v>
       </c>
       <c r="D164">
         <v>0</v>
@@ -5037,16 +5037,16 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46284.69791666666</v>
+        <v>46294.69791666666</v>
       </c>
       <c r="B165">
-        <v>13.746</v>
+        <v>49.225</v>
       </c>
       <c r="C165">
         <v>0</v>
       </c>
       <c r="D165">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -5060,16 +5060,16 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46284.70833333334</v>
+        <v>46294.70833333334</v>
       </c>
       <c r="B166">
-        <v>11.485</v>
+        <v>24.331</v>
       </c>
       <c r="C166">
-        <v>1.617</v>
+        <v>0</v>
       </c>
       <c r="D166">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -5083,16 +5083,16 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46284.71875</v>
+        <v>46294.71875</v>
       </c>
       <c r="B167">
-        <v>27.745</v>
+        <v>52.827</v>
       </c>
       <c r="C167">
         <v>0</v>
       </c>
       <c r="D167">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -5106,16 +5106,16 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46284.72916666666</v>
+        <v>46294.72916666666</v>
       </c>
       <c r="B168">
-        <v>42.633</v>
+        <v>35.685</v>
       </c>
       <c r="C168">
         <v>0</v>
       </c>
       <c r="D168">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -5129,16 +5129,16 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46284.73958333334</v>
+        <v>46294.73958333334</v>
       </c>
       <c r="B169">
-        <v>39.174</v>
+        <v>12.204</v>
       </c>
       <c r="C169">
         <v>0</v>
       </c>
       <c r="D169">
-        <v>0</v>
+        <v>149.75</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -5152,16 +5152,16 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46284.75</v>
+        <v>46294.75</v>
       </c>
       <c r="B170">
-        <v>9.801</v>
+        <v>0.167</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>0.706</v>
       </c>
       <c r="D170">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -5175,16 +5175,16 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46284.76041666666</v>
+        <v>46294.76041666666</v>
       </c>
       <c r="B171">
-        <v>9.859999999999999</v>
+        <v>0.204</v>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>0.224</v>
       </c>
       <c r="D171">
-        <v>0</v>
+        <v>137.5</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -5198,16 +5198,16 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46284.77083333334</v>
+        <v>46294.77083333334</v>
       </c>
       <c r="B172">
-        <v>6.36</v>
+        <v>0.011</v>
       </c>
       <c r="C172">
-        <v>0</v>
+        <v>10.318</v>
       </c>
       <c r="D172">
-        <v>0</v>
+        <v>137.5</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -5221,16 +5221,16 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46284.78125</v>
+        <v>46294.78125</v>
       </c>
       <c r="B173">
-        <v>16.345</v>
+        <v>0.307</v>
       </c>
       <c r="C173">
-        <v>0</v>
+        <v>0.291</v>
       </c>
       <c r="D173">
-        <v>0</v>
+        <v>137.5</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -5244,16 +5244,16 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46284.79166666666</v>
+        <v>46294.79166666666</v>
       </c>
       <c r="B174">
-        <v>3.916</v>
+        <v>0.481</v>
       </c>
       <c r="C174">
-        <v>0.02</v>
+        <v>0.134</v>
       </c>
       <c r="D174">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -5267,16 +5267,16 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46284.80208333334</v>
+        <v>46294.80208333334</v>
       </c>
       <c r="B175">
-        <v>0.05</v>
+        <v>0.021</v>
       </c>
       <c r="C175">
-        <v>3.312</v>
+        <v>15.325</v>
       </c>
       <c r="D175">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -5290,16 +5290,16 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46284.8125</v>
+        <v>46294.8125</v>
       </c>
       <c r="B176">
-        <v>0.078</v>
+        <v>0</v>
       </c>
       <c r="C176">
-        <v>0.173</v>
+        <v>17.841</v>
       </c>
       <c r="D176">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -5313,16 +5313,16 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46284.82291666666</v>
+        <v>46294.82291666666</v>
       </c>
       <c r="B177">
-        <v>0.139</v>
+        <v>0</v>
       </c>
       <c r="C177">
-        <v>0.19</v>
+        <v>29.014</v>
       </c>
       <c r="D177">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="E177">
         <v>0</v>
@@ -5336,16 +5336,16 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46284.83333333334</v>
+        <v>46294.83333333334</v>
       </c>
       <c r="B178">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="C178">
-        <v>0.039</v>
+        <v>9.618</v>
       </c>
       <c r="D178">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -5359,16 +5359,16 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46284.84375</v>
+        <v>46294.84375</v>
       </c>
       <c r="B179">
-        <v>1.77</v>
+        <v>0.27</v>
       </c>
       <c r="C179">
-        <v>0.002</v>
+        <v>0.403</v>
       </c>
       <c r="D179">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -5382,13 +5382,13 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46284.85416666666</v>
+        <v>46294.85416666666</v>
       </c>
       <c r="B180">
-        <v>5.871</v>
+        <v>0.496</v>
       </c>
       <c r="C180">
-        <v>0</v>
+        <v>0.719</v>
       </c>
       <c r="D180">
         <v>0</v>
@@ -5405,13 +5405,13 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46284.86458333334</v>
+        <v>46294.86458333334</v>
       </c>
       <c r="B181">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="C181">
-        <v>1.745</v>
+        <v>28.929</v>
       </c>
       <c r="D181">
         <v>0</v>
@@ -5428,13 +5428,13 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46284.875</v>
+        <v>46294.875</v>
       </c>
       <c r="B182">
-        <v>3.247</v>
+        <v>0</v>
       </c>
       <c r="C182">
-        <v>1.446</v>
+        <v>29.413</v>
       </c>
       <c r="D182">
         <v>0</v>
@@ -5451,13 +5451,13 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46284.88541666666</v>
+        <v>46294.88541666666</v>
       </c>
       <c r="B183">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="C183">
-        <v>0.695</v>
+        <v>39.81</v>
       </c>
       <c r="D183">
         <v>0</v>
@@ -5474,13 +5474,13 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46284.89583333334</v>
+        <v>46294.89583333334</v>
       </c>
       <c r="B184">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="C184">
-        <v>0.257</v>
+        <v>49.156</v>
       </c>
       <c r="D184">
         <v>0</v>
@@ -5497,19 +5497,19 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46284.90625</v>
+        <v>46294.90625</v>
       </c>
       <c r="B185">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="C185">
-        <v>0.132</v>
+        <v>23.795</v>
       </c>
       <c r="D185">
         <v>0</v>
       </c>
       <c r="E185">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F185">
         <v>88</v>
@@ -5520,19 +5520,19 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46284.91666666666</v>
+        <v>46294.91666666666</v>
       </c>
       <c r="B186">
-        <v>6.74</v>
+        <v>0</v>
       </c>
       <c r="C186">
-        <v>0.051</v>
+        <v>8.31</v>
       </c>
       <c r="D186">
         <v>0</v>
       </c>
       <c r="E186">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F186">
         <v>89</v>
@@ -5543,19 +5543,19 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46284.92708333334</v>
+        <v>46294.92708333334</v>
       </c>
       <c r="B187">
-        <v>2.279</v>
+        <v>1.015</v>
       </c>
       <c r="C187">
-        <v>2.167</v>
+        <v>0.857</v>
       </c>
       <c r="D187">
         <v>0</v>
       </c>
       <c r="E187">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F187">
         <v>90</v>
@@ -5566,19 +5566,19 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46284.9375</v>
+        <v>46294.9375</v>
       </c>
       <c r="B188">
-        <v>2.612</v>
+        <v>0.218</v>
       </c>
       <c r="C188">
-        <v>0.356</v>
+        <v>3.275</v>
       </c>
       <c r="D188">
         <v>0</v>
       </c>
       <c r="E188">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F188">
         <v>91</v>
@@ -5589,19 +5589,19 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46284.94791666666</v>
+        <v>46294.94791666666</v>
       </c>
       <c r="B189">
-        <v>3.013</v>
+        <v>0.332</v>
       </c>
       <c r="C189">
-        <v>0.059</v>
+        <v>1.341</v>
       </c>
       <c r="D189">
         <v>0</v>
       </c>
       <c r="E189">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F189">
         <v>92</v>
@@ -5612,19 +5612,19 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46284.95833333334</v>
+        <v>46294.95833333334</v>
       </c>
       <c r="B190">
-        <v>11.27</v>
+        <v>0.02</v>
       </c>
       <c r="C190">
-        <v>0</v>
+        <v>0.382</v>
       </c>
       <c r="D190">
         <v>0</v>
       </c>
       <c r="E190">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F190">
         <v>93</v>
@@ -5635,19 +5635,19 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46284.96875</v>
+        <v>46294.96875</v>
       </c>
       <c r="B191">
-        <v>26.421</v>
+        <v>0.048</v>
       </c>
       <c r="C191">
-        <v>0</v>
+        <v>2.212</v>
       </c>
       <c r="D191">
         <v>0</v>
       </c>
       <c r="E191">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F191">
         <v>94</v>
@@ -5658,19 +5658,19 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46284.97916666666</v>
+        <v>46294.97916666666</v>
       </c>
       <c r="B192">
-        <v>19.326</v>
+        <v>0.02</v>
       </c>
       <c r="C192">
-        <v>0</v>
+        <v>2.072</v>
       </c>
       <c r="D192">
         <v>0</v>
       </c>
       <c r="E192">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F192">
         <v>95</v>
@@ -5681,19 +5681,19 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46284.98958333334</v>
+        <v>46294.98958333334</v>
       </c>
       <c r="B193">
-        <v>35.039</v>
+        <v>1.788</v>
       </c>
       <c r="C193">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="D193">
         <v>0</v>
       </c>
       <c r="E193">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F193">
         <v>96</v>
@@ -5704,13 +5704,13 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194" s="2">
-        <v>46285</v>
+        <v>46295</v>
       </c>
       <c r="B194">
-        <v>10.794</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="C194">
-        <v>0</v>
+        <v>0.966</v>
       </c>
       <c r="D194">
         <v>0</v>
@@ -5727,13 +5727,13 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195" s="2">
-        <v>46285.01041666666</v>
+        <v>46295.01041666666</v>
       </c>
       <c r="B195">
-        <v>6.459</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="C195">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="D195">
         <v>0</v>
@@ -5750,13 +5750,13 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196" s="2">
-        <v>46285.02083333334</v>
+        <v>46295.02083333334</v>
       </c>
       <c r="B196">
-        <v>4.025</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="C196">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="D196">
         <v>0</v>
@@ -5773,10 +5773,10 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197" s="2">
-        <v>46285.03125</v>
+        <v>46295.03125</v>
       </c>
       <c r="B197">
-        <v>2.629</v>
+        <v>0.628</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -5796,10 +5796,10 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198" s="2">
-        <v>46285.04166666666</v>
+        <v>46295.04166666666</v>
       </c>
       <c r="B198">
-        <v>14.552</v>
+        <v>13.702</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -5819,13 +5819,13 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199" s="2">
-        <v>46285.05208333334</v>
+        <v>46295.05208333334</v>
       </c>
       <c r="B199">
-        <v>9.379</v>
+        <v>1.148</v>
       </c>
       <c r="C199">
-        <v>0</v>
+        <v>0.149</v>
       </c>
       <c r="D199">
         <v>0</v>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200" s="2">
-        <v>46285.0625</v>
+        <v>46295.0625</v>
       </c>
       <c r="B200">
-        <v>0.71</v>
+        <v>8.086</v>
       </c>
       <c r="C200">
         <v>0</v>
@@ -5865,10 +5865,10 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201" s="2">
-        <v>46285.07291666666</v>
+        <v>46295.07291666666</v>
       </c>
       <c r="B201">
-        <v>2.825</v>
+        <v>8.629</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -5888,13 +5888,13 @@
     </row>
     <row r="202" spans="1:7">
       <c r="A202" s="2">
-        <v>46285.08333333334</v>
+        <v>46295.08333333334</v>
       </c>
       <c r="B202">
-        <v>3.193</v>
+        <v>20.576</v>
       </c>
       <c r="C202">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="D202">
         <v>0</v>
@@ -5911,13 +5911,13 @@
     </row>
     <row r="203" spans="1:7">
       <c r="A203" s="2">
-        <v>46285.09375</v>
+        <v>46295.09375</v>
       </c>
       <c r="B203">
-        <v>5.081</v>
+        <v>0.992</v>
       </c>
       <c r="C203">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="D203">
         <v>0</v>
@@ -5934,13 +5934,13 @@
     </row>
     <row r="204" spans="1:7">
       <c r="A204" s="2">
-        <v>46285.10416666666</v>
+        <v>46295.10416666666</v>
       </c>
       <c r="B204">
-        <v>10.303</v>
+        <v>4.989</v>
       </c>
       <c r="C204">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="D204">
         <v>0</v>
@@ -5957,10 +5957,10 @@
     </row>
     <row r="205" spans="1:7">
       <c r="A205" s="2">
-        <v>46285.11458333334</v>
+        <v>46295.11458333334</v>
       </c>
       <c r="B205">
-        <v>3.398</v>
+        <v>15.289</v>
       </c>
       <c r="C205">
         <v>0</v>
@@ -5980,13 +5980,13 @@
     </row>
     <row r="206" spans="1:7">
       <c r="A206" s="2">
-        <v>46285.125</v>
+        <v>46295.125</v>
       </c>
       <c r="B206">
-        <v>1.198</v>
+        <v>7.071</v>
       </c>
       <c r="C206">
-        <v>0.49</v>
+        <v>0.006</v>
       </c>
       <c r="D206">
         <v>0</v>
@@ -6003,13 +6003,13 @@
     </row>
     <row r="207" spans="1:7">
       <c r="A207" s="2">
-        <v>46285.13541666666</v>
+        <v>46295.13541666666</v>
       </c>
       <c r="B207">
-        <v>0</v>
+        <v>0.265</v>
       </c>
       <c r="C207">
-        <v>4.241</v>
+        <v>0.013</v>
       </c>
       <c r="D207">
         <v>0</v>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="208" spans="1:7">
       <c r="A208" s="2">
-        <v>46285.14583333334</v>
+        <v>46295.14583333334</v>
       </c>
       <c r="B208">
-        <v>0</v>
+        <v>15.285</v>
       </c>
       <c r="C208">
-        <v>3.784</v>
+        <v>0</v>
       </c>
       <c r="D208">
         <v>0</v>
@@ -6049,13 +6049,13 @@
     </row>
     <row r="209" spans="1:7">
       <c r="A209" s="2">
-        <v>46285.15625</v>
+        <v>46295.15625</v>
       </c>
       <c r="B209">
-        <v>0</v>
+        <v>23.208</v>
       </c>
       <c r="C209">
-        <v>11.221</v>
+        <v>0</v>
       </c>
       <c r="D209">
         <v>0</v>
@@ -6072,13 +6072,13 @@
     </row>
     <row r="210" spans="1:7">
       <c r="A210" s="2">
-        <v>46285.16666666666</v>
+        <v>46295.16666666666</v>
       </c>
       <c r="B210">
-        <v>0</v>
+        <v>27.129</v>
       </c>
       <c r="C210">
-        <v>5.05</v>
+        <v>0.025</v>
       </c>
       <c r="D210">
         <v>0</v>
@@ -6095,13 +6095,13 @@
     </row>
     <row r="211" spans="1:7">
       <c r="A211" s="2">
-        <v>46285.17708333334</v>
+        <v>46295.17708333334</v>
       </c>
       <c r="B211">
-        <v>0.042</v>
+        <v>14.813</v>
       </c>
       <c r="C211">
-        <v>0.153</v>
+        <v>0</v>
       </c>
       <c r="D211">
         <v>0</v>
@@ -6118,13 +6118,13 @@
     </row>
     <row r="212" spans="1:7">
       <c r="A212" s="2">
-        <v>46285.1875</v>
+        <v>46295.1875</v>
       </c>
       <c r="B212">
-        <v>0</v>
+        <v>34.028</v>
       </c>
       <c r="C212">
-        <v>6.46</v>
+        <v>0</v>
       </c>
       <c r="D212">
         <v>0</v>
@@ -6141,13 +6141,13 @@
     </row>
     <row r="213" spans="1:7">
       <c r="A213" s="2">
-        <v>46285.19791666666</v>
+        <v>46295.19791666666</v>
       </c>
       <c r="B213">
-        <v>0</v>
+        <v>18.562</v>
       </c>
       <c r="C213">
-        <v>0.787</v>
+        <v>0</v>
       </c>
       <c r="D213">
         <v>0</v>
@@ -6164,13 +6164,13 @@
     </row>
     <row r="214" spans="1:7">
       <c r="A214" s="2">
-        <v>46285.20833333334</v>
+        <v>46295.20833333334</v>
       </c>
       <c r="B214">
-        <v>10.547</v>
+        <v>1.749</v>
       </c>
       <c r="C214">
-        <v>0.005</v>
+        <v>0.076</v>
       </c>
       <c r="D214">
         <v>0</v>
@@ -6187,13 +6187,13 @@
     </row>
     <row r="215" spans="1:7">
       <c r="A215" s="2">
-        <v>46285.21875</v>
+        <v>46295.21875</v>
       </c>
       <c r="B215">
-        <v>5.072</v>
+        <v>2.847</v>
       </c>
       <c r="C215">
-        <v>0</v>
+        <v>0.228</v>
       </c>
       <c r="D215">
         <v>0</v>
@@ -6210,10 +6210,10 @@
     </row>
     <row r="216" spans="1:7">
       <c r="A216" s="2">
-        <v>46285.22916666666</v>
+        <v>46295.22916666666</v>
       </c>
       <c r="B216">
-        <v>1.419</v>
+        <v>14.873</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -6233,10 +6233,10 @@
     </row>
     <row r="217" spans="1:7">
       <c r="A217" s="2">
-        <v>46285.23958333334</v>
+        <v>46295.23958333334</v>
       </c>
       <c r="B217">
-        <v>2.32</v>
+        <v>39.745</v>
       </c>
       <c r="C217">
         <v>0</v>
@@ -6256,13 +6256,13 @@
     </row>
     <row r="218" spans="1:7">
       <c r="A218" s="2">
-        <v>46285.25</v>
+        <v>46295.25</v>
       </c>
       <c r="B218">
-        <v>2.947</v>
+        <v>32.877</v>
       </c>
       <c r="C218">
-        <v>0.211</v>
+        <v>0</v>
       </c>
       <c r="D218">
         <v>0</v>
@@ -6279,10 +6279,10 @@
     </row>
     <row r="219" spans="1:7">
       <c r="A219" s="2">
-        <v>46285.26041666666</v>
+        <v>46295.26041666666</v>
       </c>
       <c r="B219">
-        <v>3.848</v>
+        <v>37.296</v>
       </c>
       <c r="C219">
         <v>0</v>
@@ -6302,10 +6302,10 @@
     </row>
     <row r="220" spans="1:7">
       <c r="A220" s="2">
-        <v>46285.27083333334</v>
+        <v>46295.27083333334</v>
       </c>
       <c r="B220">
-        <v>2.826</v>
+        <v>30.171</v>
       </c>
       <c r="C220">
         <v>0</v>
@@ -6325,13 +6325,13 @@
     </row>
     <row r="221" spans="1:7">
       <c r="A221" s="2">
-        <v>46285.28125</v>
+        <v>46295.28125</v>
       </c>
       <c r="B221">
-        <v>0.008999999999999999</v>
+        <v>20.06</v>
       </c>
       <c r="C221">
-        <v>1.843</v>
+        <v>0</v>
       </c>
       <c r="D221">
         <v>0</v>
@@ -6348,13 +6348,13 @@
     </row>
     <row r="222" spans="1:7">
       <c r="A222" s="2">
-        <v>46285.29166666666</v>
+        <v>46295.29166666666</v>
       </c>
       <c r="B222">
-        <v>16.806</v>
+        <v>70.15300000000001</v>
       </c>
       <c r="C222">
-        <v>0.062</v>
+        <v>0</v>
       </c>
       <c r="D222">
         <v>0</v>
@@ -6371,16 +6371,16 @@
     </row>
     <row r="223" spans="1:7">
       <c r="A223" s="2">
-        <v>46285.30208333334</v>
+        <v>46295.30208333334</v>
       </c>
       <c r="B223">
-        <v>8.252000000000001</v>
+        <v>74.622</v>
       </c>
       <c r="C223">
-        <v>1.948</v>
+        <v>0</v>
       </c>
       <c r="D223">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -6394,16 +6394,16 @@
     </row>
     <row r="224" spans="1:7">
       <c r="A224" s="2">
-        <v>46285.3125</v>
+        <v>46295.3125</v>
       </c>
       <c r="B224">
-        <v>0</v>
+        <v>50.288</v>
       </c>
       <c r="C224">
-        <v>11.409</v>
+        <v>0</v>
       </c>
       <c r="D224">
-        <v>0</v>
+        <v>49.5</v>
       </c>
       <c r="E224">
         <v>0</v>
@@ -6417,16 +6417,16 @@
     </row>
     <row r="225" spans="1:7">
       <c r="A225" s="2">
-        <v>46285.32291666666</v>
+        <v>46295.32291666666</v>
       </c>
       <c r="B225">
-        <v>0</v>
+        <v>72.751</v>
       </c>
       <c r="C225">
-        <v>19.414</v>
+        <v>0</v>
       </c>
       <c r="D225">
-        <v>0</v>
+        <v>49.5</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -6440,16 +6440,16 @@
     </row>
     <row r="226" spans="1:7">
       <c r="A226" s="2">
-        <v>46285.33333333334</v>
+        <v>46295.33333333334</v>
       </c>
       <c r="B226">
-        <v>0.272</v>
+        <v>25.758</v>
       </c>
       <c r="C226">
-        <v>8.387</v>
+        <v>0</v>
       </c>
       <c r="D226">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -6463,16 +6463,16 @@
     </row>
     <row r="227" spans="1:7">
       <c r="A227" s="2">
-        <v>46285.34375</v>
+        <v>46295.34375</v>
       </c>
       <c r="B227">
-        <v>5.62</v>
+        <v>6.036</v>
       </c>
       <c r="C227">
-        <v>0.003</v>
+        <v>0.078</v>
       </c>
       <c r="D227">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="E227">
         <v>0</v>
@@ -6486,16 +6486,16 @@
     </row>
     <row r="228" spans="1:7">
       <c r="A228" s="2">
-        <v>46285.35416666666</v>
+        <v>46295.35416666666</v>
       </c>
       <c r="B228">
-        <v>0.173</v>
+        <v>20.556</v>
       </c>
       <c r="C228">
-        <v>0.304</v>
+        <v>0</v>
       </c>
       <c r="D228">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="E228">
         <v>0</v>
@@ -6509,16 +6509,16 @@
     </row>
     <row r="229" spans="1:7">
       <c r="A229" s="2">
-        <v>46285.36458333334</v>
+        <v>46295.36458333334</v>
       </c>
       <c r="B229">
-        <v>0.101</v>
+        <v>6.576</v>
       </c>
       <c r="C229">
-        <v>1.164</v>
+        <v>0.11</v>
       </c>
       <c r="D229">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="E229">
         <v>0</v>
@@ -6532,16 +6532,16 @@
     </row>
     <row r="230" spans="1:7">
       <c r="A230" s="2">
-        <v>46285.375</v>
+        <v>46295.375</v>
       </c>
       <c r="B230">
-        <v>1.621</v>
+        <v>29.441</v>
       </c>
       <c r="C230">
-        <v>0.676</v>
+        <v>0</v>
       </c>
       <c r="D230">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -6555,16 +6555,16 @@
     </row>
     <row r="231" spans="1:7">
       <c r="A231" s="2">
-        <v>46285.38541666666</v>
+        <v>46295.38541666666</v>
       </c>
       <c r="B231">
-        <v>0.521</v>
+        <v>0.758</v>
       </c>
       <c r="C231">
-        <v>0.031</v>
+        <v>21.517</v>
       </c>
       <c r="D231">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="E231">
         <v>0</v>
@@ -6578,16 +6578,16 @@
     </row>
     <row r="232" spans="1:7">
       <c r="A232" s="2">
-        <v>46285.39583333334</v>
+        <v>46295.39583333334</v>
       </c>
       <c r="B232">
         <v>0</v>
       </c>
       <c r="C232">
-        <v>0</v>
+        <v>50.827</v>
       </c>
       <c r="D232">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -6601,7 +6601,7 @@
     </row>
     <row r="233" spans="1:7">
       <c r="A233" s="2">
-        <v>46285.40625</v>
+        <v>46295.40625</v>
       </c>
       <c r="B233">
         <v>0</v>
@@ -6610,7 +6610,7 @@
         <v>0</v>
       </c>
       <c r="D233">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -6624,7 +6624,7 @@
     </row>
     <row r="234" spans="1:7">
       <c r="A234" s="2">
-        <v>46285.41666666666</v>
+        <v>46295.41666666666</v>
       </c>
       <c r="B234">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="D234">
-        <v>0</v>
+        <v>16.25</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -6647,7 +6647,7 @@
     </row>
     <row r="235" spans="1:7">
       <c r="A235" s="2">
-        <v>46285.42708333334</v>
+        <v>46295.42708333334</v>
       </c>
       <c r="B235">
         <v>0</v>
@@ -6670,7 +6670,7 @@
     </row>
     <row r="236" spans="1:7">
       <c r="A236" s="2">
-        <v>46285.4375</v>
+        <v>46295.4375</v>
       </c>
       <c r="B236">
         <v>0</v>
@@ -6693,7 +6693,7 @@
     </row>
     <row r="237" spans="1:7">
       <c r="A237" s="2">
-        <v>46285.44791666666</v>
+        <v>46295.44791666666</v>
       </c>
       <c r="B237">
         <v>0</v>
@@ -6716,7 +6716,7 @@
     </row>
     <row r="238" spans="1:7">
       <c r="A238" s="2">
-        <v>46285.45833333334</v>
+        <v>46295.45833333334</v>
       </c>
       <c r="B238">
         <v>0</v>
@@ -6739,7 +6739,7 @@
     </row>
     <row r="239" spans="1:7">
       <c r="A239" s="2">
-        <v>46285.46875</v>
+        <v>46295.46875</v>
       </c>
       <c r="B239">
         <v>0</v>
@@ -6762,7 +6762,7 @@
     </row>
     <row r="240" spans="1:7">
       <c r="A240" s="2">
-        <v>46285.47916666666</v>
+        <v>46295.47916666666</v>
       </c>
       <c r="B240">
         <v>0</v>
@@ -6785,7 +6785,7 @@
     </row>
     <row r="241" spans="1:7">
       <c r="A241" s="2">
-        <v>46285.48958333334</v>
+        <v>46295.48958333334</v>
       </c>
       <c r="B241">
         <v>0</v>
@@ -6808,7 +6808,7 @@
     </row>
     <row r="242" spans="1:7">
       <c r="A242" s="2">
-        <v>46285.5</v>
+        <v>46295.5</v>
       </c>
       <c r="B242">
         <v>0</v>
@@ -6831,7 +6831,7 @@
     </row>
     <row r="243" spans="1:7">
       <c r="A243" s="2">
-        <v>46285.51041666666</v>
+        <v>46295.51041666666</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -6854,7 +6854,7 @@
     </row>
     <row r="244" spans="1:7">
       <c r="A244" s="2">
-        <v>46285.52083333334</v>
+        <v>46295.52083333334</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -6877,7 +6877,7 @@
     </row>
     <row r="245" spans="1:7">
       <c r="A245" s="2">
-        <v>46285.53125</v>
+        <v>46295.53125</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -6900,7 +6900,7 @@
     </row>
     <row r="246" spans="1:7">
       <c r="A246" s="2">
-        <v>46285.54166666666</v>
+        <v>46295.54166666666</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -6923,7 +6923,7 @@
     </row>
     <row r="247" spans="1:7">
       <c r="A247" s="2">
-        <v>46285.55208333334</v>
+        <v>46295.55208333334</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -6946,7 +6946,7 @@
     </row>
     <row r="248" spans="1:7">
       <c r="A248" s="2">
-        <v>46285.5625</v>
+        <v>46295.5625</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -6969,7 +6969,7 @@
     </row>
     <row r="249" spans="1:7">
       <c r="A249" s="2">
-        <v>46285.57291666666</v>
+        <v>46295.57291666666</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -6992,7 +6992,7 @@
     </row>
     <row r="250" spans="1:7">
       <c r="A250" s="2">
-        <v>46285.58333333334</v>
+        <v>46295.58333333334</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -7015,7 +7015,7 @@
     </row>
     <row r="251" spans="1:7">
       <c r="A251" s="2">
-        <v>46285.59375</v>
+        <v>46295.59375</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -7038,7 +7038,7 @@
     </row>
     <row r="252" spans="1:7">
       <c r="A252" s="2">
-        <v>46285.60416666666</v>
+        <v>46295.60416666666</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -7061,7 +7061,7 @@
     </row>
     <row r="253" spans="1:7">
       <c r="A253" s="2">
-        <v>46285.61458333334</v>
+        <v>46295.61458333334</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -7084,7 +7084,7 @@
     </row>
     <row r="254" spans="1:7">
       <c r="A254" s="2">
-        <v>46285.625</v>
+        <v>46295.625</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -7107,7 +7107,7 @@
     </row>
     <row r="255" spans="1:7">
       <c r="A255" s="2">
-        <v>46285.63541666666</v>
+        <v>46295.63541666666</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -7130,7 +7130,7 @@
     </row>
     <row r="256" spans="1:7">
       <c r="A256" s="2">
-        <v>46285.64583333334</v>
+        <v>46295.64583333334</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -7153,7 +7153,7 @@
     </row>
     <row r="257" spans="1:7">
       <c r="A257" s="2">
-        <v>46285.65625</v>
+        <v>46295.65625</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -7176,7 +7176,7 @@
     </row>
     <row r="258" spans="1:7">
       <c r="A258" s="2">
-        <v>46285.66666666666</v>
+        <v>46295.66666666666</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -7199,7 +7199,7 @@
     </row>
     <row r="259" spans="1:7">
       <c r="A259" s="2">
-        <v>46285.67708333334</v>
+        <v>46295.67708333334</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -7222,7 +7222,7 @@
     </row>
     <row r="260" spans="1:7">
       <c r="A260" s="2">
-        <v>46285.6875</v>
+        <v>46295.6875</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -7245,7 +7245,7 @@
     </row>
     <row r="261" spans="1:7">
       <c r="A261" s="2">
-        <v>46285.69791666666</v>
+        <v>46295.69791666666</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -7268,7 +7268,7 @@
     </row>
     <row r="262" spans="1:7">
       <c r="A262" s="2">
-        <v>46285.70833333334</v>
+        <v>46295.70833333334</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -7291,7 +7291,7 @@
     </row>
     <row r="263" spans="1:7">
       <c r="A263" s="2">
-        <v>46285.71875</v>
+        <v>46295.71875</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -7314,7 +7314,7 @@
     </row>
     <row r="264" spans="1:7">
       <c r="A264" s="2">
-        <v>46285.72916666666</v>
+        <v>46295.72916666666</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -7337,7 +7337,7 @@
     </row>
     <row r="265" spans="1:7">
       <c r="A265" s="2">
-        <v>46285.73958333334</v>
+        <v>46295.73958333334</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -7360,7 +7360,7 @@
     </row>
     <row r="266" spans="1:7">
       <c r="A266" s="2">
-        <v>46285.75</v>
+        <v>46295.75</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -7383,7 +7383,7 @@
     </row>
     <row r="267" spans="1:7">
       <c r="A267" s="2">
-        <v>46285.76041666666</v>
+        <v>46295.76041666666</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -7406,7 +7406,7 @@
     </row>
     <row r="268" spans="1:7">
       <c r="A268" s="2">
-        <v>46285.77083333334</v>
+        <v>46295.77083333334</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -7429,7 +7429,7 @@
     </row>
     <row r="269" spans="1:7">
       <c r="A269" s="2">
-        <v>46285.78125</v>
+        <v>46295.78125</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -7452,7 +7452,7 @@
     </row>
     <row r="270" spans="1:7">
       <c r="A270" s="2">
-        <v>46285.79166666666</v>
+        <v>46295.79166666666</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -7475,7 +7475,7 @@
     </row>
     <row r="271" spans="1:7">
       <c r="A271" s="2">
-        <v>46285.80208333334</v>
+        <v>46295.80208333334</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -7498,7 +7498,7 @@
     </row>
     <row r="272" spans="1:7">
       <c r="A272" s="2">
-        <v>46285.8125</v>
+        <v>46295.8125</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -7521,7 +7521,7 @@
     </row>
     <row r="273" spans="1:7">
       <c r="A273" s="2">
-        <v>46285.82291666666</v>
+        <v>46295.82291666666</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -7544,7 +7544,7 @@
     </row>
     <row r="274" spans="1:7">
       <c r="A274" s="2">
-        <v>46285.83333333334</v>
+        <v>46295.83333333334</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -7567,7 +7567,7 @@
     </row>
     <row r="275" spans="1:7">
       <c r="A275" s="2">
-        <v>46285.84375</v>
+        <v>46295.84375</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -7590,7 +7590,7 @@
     </row>
     <row r="276" spans="1:7">
       <c r="A276" s="2">
-        <v>46285.85416666666</v>
+        <v>46295.85416666666</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -7613,7 +7613,7 @@
     </row>
     <row r="277" spans="1:7">
       <c r="A277" s="2">
-        <v>46285.86458333334</v>
+        <v>46295.86458333334</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -7636,7 +7636,7 @@
     </row>
     <row r="278" spans="1:7">
       <c r="A278" s="2">
-        <v>46285.875</v>
+        <v>46295.875</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -7659,7 +7659,7 @@
     </row>
     <row r="279" spans="1:7">
       <c r="A279" s="2">
-        <v>46285.88541666666</v>
+        <v>46295.88541666666</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -7682,7 +7682,7 @@
     </row>
     <row r="280" spans="1:7">
       <c r="A280" s="2">
-        <v>46285.89583333334</v>
+        <v>46295.89583333334</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -7705,7 +7705,7 @@
     </row>
     <row r="281" spans="1:7">
       <c r="A281" s="2">
-        <v>46285.90625</v>
+        <v>46295.90625</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -7728,7 +7728,7 @@
     </row>
     <row r="282" spans="1:7">
       <c r="A282" s="2">
-        <v>46285.91666666666</v>
+        <v>46295.91666666666</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -7751,7 +7751,7 @@
     </row>
     <row r="283" spans="1:7">
       <c r="A283" s="2">
-        <v>46285.92708333334</v>
+        <v>46295.92708333334</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -7774,7 +7774,7 @@
     </row>
     <row r="284" spans="1:7">
       <c r="A284" s="2">
-        <v>46285.9375</v>
+        <v>46295.9375</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -7797,7 +7797,7 @@
     </row>
     <row r="285" spans="1:7">
       <c r="A285" s="2">
-        <v>46285.94791666666</v>
+        <v>46295.94791666666</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -7820,7 +7820,7 @@
     </row>
     <row r="286" spans="1:7">
       <c r="A286" s="2">
-        <v>46285.95833333334</v>
+        <v>46295.95833333334</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -7843,7 +7843,7 @@
     </row>
     <row r="287" spans="1:7">
       <c r="A287" s="2">
-        <v>46285.96875</v>
+        <v>46295.96875</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -7866,7 +7866,7 @@
     </row>
     <row r="288" spans="1:7">
       <c r="A288" s="2">
-        <v>46285.97916666666</v>
+        <v>46295.97916666666</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -7889,7 +7889,7 @@
     </row>
     <row r="289" spans="1:7">
       <c r="A289" s="2">
-        <v>46285.98958333334</v>
+        <v>46295.98958333334</v>
       </c>
       <c r="B289">
         <v>0</v>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -37,868 +37,868 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>28.09.20261</t>
-  </si>
-  <si>
-    <t>28.09.20262</t>
-  </si>
-  <si>
-    <t>28.09.20263</t>
-  </si>
-  <si>
-    <t>28.09.20264</t>
-  </si>
-  <si>
-    <t>28.09.20265</t>
-  </si>
-  <si>
-    <t>28.09.20266</t>
-  </si>
-  <si>
-    <t>28.09.20267</t>
-  </si>
-  <si>
-    <t>28.09.20268</t>
-  </si>
-  <si>
-    <t>28.09.20269</t>
-  </si>
-  <si>
-    <t>28.09.202610</t>
-  </si>
-  <si>
-    <t>28.09.202611</t>
-  </si>
-  <si>
-    <t>28.09.202612</t>
-  </si>
-  <si>
-    <t>28.09.202613</t>
-  </si>
-  <si>
-    <t>28.09.202614</t>
-  </si>
-  <si>
-    <t>28.09.202615</t>
-  </si>
-  <si>
-    <t>28.09.202616</t>
-  </si>
-  <si>
-    <t>28.09.202617</t>
-  </si>
-  <si>
-    <t>28.09.202618</t>
-  </si>
-  <si>
-    <t>28.09.202619</t>
-  </si>
-  <si>
-    <t>28.09.202620</t>
-  </si>
-  <si>
-    <t>28.09.202621</t>
-  </si>
-  <si>
-    <t>28.09.202622</t>
-  </si>
-  <si>
-    <t>28.09.202623</t>
-  </si>
-  <si>
-    <t>28.09.202624</t>
-  </si>
-  <si>
-    <t>28.09.202625</t>
-  </si>
-  <si>
-    <t>28.09.202626</t>
-  </si>
-  <si>
-    <t>28.09.202627</t>
-  </si>
-  <si>
-    <t>28.09.202628</t>
-  </si>
-  <si>
-    <t>28.09.202629</t>
-  </si>
-  <si>
-    <t>28.09.202630</t>
-  </si>
-  <si>
-    <t>28.09.202631</t>
-  </si>
-  <si>
-    <t>28.09.202632</t>
-  </si>
-  <si>
-    <t>28.09.202633</t>
-  </si>
-  <si>
-    <t>28.09.202634</t>
-  </si>
-  <si>
-    <t>28.09.202635</t>
-  </si>
-  <si>
-    <t>28.09.202636</t>
-  </si>
-  <si>
-    <t>28.09.202637</t>
-  </si>
-  <si>
-    <t>28.09.202638</t>
-  </si>
-  <si>
-    <t>28.09.202639</t>
-  </si>
-  <si>
-    <t>28.09.202640</t>
-  </si>
-  <si>
-    <t>28.09.202641</t>
-  </si>
-  <si>
-    <t>28.09.202642</t>
-  </si>
-  <si>
-    <t>28.09.202643</t>
-  </si>
-  <si>
-    <t>28.09.202644</t>
-  </si>
-  <si>
-    <t>28.09.202645</t>
-  </si>
-  <si>
-    <t>28.09.202646</t>
-  </si>
-  <si>
-    <t>28.09.202647</t>
-  </si>
-  <si>
-    <t>28.09.202648</t>
-  </si>
-  <si>
-    <t>28.09.202649</t>
-  </si>
-  <si>
-    <t>28.09.202650</t>
-  </si>
-  <si>
-    <t>28.09.202651</t>
-  </si>
-  <si>
-    <t>28.09.202652</t>
-  </si>
-  <si>
-    <t>28.09.202653</t>
-  </si>
-  <si>
-    <t>28.09.202654</t>
-  </si>
-  <si>
-    <t>28.09.202655</t>
-  </si>
-  <si>
-    <t>28.09.202656</t>
-  </si>
-  <si>
-    <t>28.09.202657</t>
-  </si>
-  <si>
-    <t>28.09.202658</t>
-  </si>
-  <si>
-    <t>28.09.202659</t>
-  </si>
-  <si>
-    <t>28.09.202660</t>
-  </si>
-  <si>
-    <t>28.09.202661</t>
-  </si>
-  <si>
-    <t>28.09.202662</t>
-  </si>
-  <si>
-    <t>28.09.202663</t>
-  </si>
-  <si>
-    <t>28.09.202664</t>
-  </si>
-  <si>
-    <t>28.09.202665</t>
-  </si>
-  <si>
-    <t>28.09.202666</t>
-  </si>
-  <si>
-    <t>28.09.202667</t>
-  </si>
-  <si>
-    <t>28.09.202668</t>
-  </si>
-  <si>
-    <t>28.09.202669</t>
-  </si>
-  <si>
-    <t>28.09.202670</t>
-  </si>
-  <si>
-    <t>28.09.202671</t>
-  </si>
-  <si>
-    <t>28.09.202672</t>
-  </si>
-  <si>
-    <t>28.09.202673</t>
-  </si>
-  <si>
-    <t>28.09.202674</t>
-  </si>
-  <si>
-    <t>28.09.202675</t>
-  </si>
-  <si>
-    <t>28.09.202676</t>
-  </si>
-  <si>
-    <t>28.09.202677</t>
-  </si>
-  <si>
-    <t>28.09.202678</t>
-  </si>
-  <si>
-    <t>28.09.202679</t>
-  </si>
-  <si>
-    <t>28.09.202680</t>
-  </si>
-  <si>
-    <t>28.09.202681</t>
-  </si>
-  <si>
-    <t>28.09.202682</t>
-  </si>
-  <si>
-    <t>28.09.202683</t>
-  </si>
-  <si>
-    <t>28.09.202684</t>
-  </si>
-  <si>
-    <t>28.09.202685</t>
-  </si>
-  <si>
-    <t>28.09.202686</t>
-  </si>
-  <si>
-    <t>28.09.202687</t>
-  </si>
-  <si>
-    <t>28.09.202688</t>
-  </si>
-  <si>
-    <t>28.09.202689</t>
-  </si>
-  <si>
-    <t>28.09.202690</t>
-  </si>
-  <si>
-    <t>28.09.202691</t>
-  </si>
-  <si>
-    <t>28.09.202692</t>
-  </si>
-  <si>
-    <t>28.09.202693</t>
-  </si>
-  <si>
-    <t>28.09.202694</t>
-  </si>
-  <si>
-    <t>28.09.202695</t>
-  </si>
-  <si>
-    <t>28.09.202696</t>
-  </si>
-  <si>
-    <t>29.09.20261</t>
-  </si>
-  <si>
-    <t>29.09.20262</t>
-  </si>
-  <si>
-    <t>29.09.20263</t>
-  </si>
-  <si>
-    <t>29.09.20264</t>
-  </si>
-  <si>
-    <t>29.09.20265</t>
-  </si>
-  <si>
-    <t>29.09.20266</t>
-  </si>
-  <si>
-    <t>29.09.20267</t>
-  </si>
-  <si>
-    <t>29.09.20268</t>
-  </si>
-  <si>
-    <t>29.09.20269</t>
-  </si>
-  <si>
-    <t>29.09.202610</t>
-  </si>
-  <si>
-    <t>29.09.202611</t>
-  </si>
-  <si>
-    <t>29.09.202612</t>
-  </si>
-  <si>
-    <t>29.09.202613</t>
-  </si>
-  <si>
-    <t>29.09.202614</t>
-  </si>
-  <si>
-    <t>29.09.202615</t>
-  </si>
-  <si>
-    <t>29.09.202616</t>
-  </si>
-  <si>
-    <t>29.09.202617</t>
-  </si>
-  <si>
-    <t>29.09.202618</t>
-  </si>
-  <si>
-    <t>29.09.202619</t>
-  </si>
-  <si>
-    <t>29.09.202620</t>
-  </si>
-  <si>
-    <t>29.09.202621</t>
-  </si>
-  <si>
-    <t>29.09.202622</t>
-  </si>
-  <si>
-    <t>29.09.202623</t>
-  </si>
-  <si>
-    <t>29.09.202624</t>
-  </si>
-  <si>
-    <t>29.09.202625</t>
-  </si>
-  <si>
-    <t>29.09.202626</t>
-  </si>
-  <si>
-    <t>29.09.202627</t>
-  </si>
-  <si>
-    <t>29.09.202628</t>
-  </si>
-  <si>
-    <t>29.09.202629</t>
-  </si>
-  <si>
-    <t>29.09.202630</t>
-  </si>
-  <si>
-    <t>29.09.202631</t>
-  </si>
-  <si>
-    <t>29.09.202632</t>
-  </si>
-  <si>
-    <t>29.09.202633</t>
-  </si>
-  <si>
-    <t>29.09.202634</t>
-  </si>
-  <si>
-    <t>29.09.202635</t>
-  </si>
-  <si>
-    <t>29.09.202636</t>
-  </si>
-  <si>
-    <t>29.09.202637</t>
-  </si>
-  <si>
-    <t>29.09.202638</t>
-  </si>
-  <si>
-    <t>29.09.202639</t>
-  </si>
-  <si>
-    <t>29.09.202640</t>
-  </si>
-  <si>
-    <t>29.09.202641</t>
-  </si>
-  <si>
-    <t>29.09.202642</t>
-  </si>
-  <si>
-    <t>29.09.202643</t>
-  </si>
-  <si>
-    <t>29.09.202644</t>
-  </si>
-  <si>
-    <t>29.09.202645</t>
-  </si>
-  <si>
-    <t>29.09.202646</t>
-  </si>
-  <si>
-    <t>29.09.202647</t>
-  </si>
-  <si>
-    <t>29.09.202648</t>
-  </si>
-  <si>
-    <t>29.09.202649</t>
-  </si>
-  <si>
-    <t>29.09.202650</t>
-  </si>
-  <si>
-    <t>29.09.202651</t>
-  </si>
-  <si>
-    <t>29.09.202652</t>
-  </si>
-  <si>
-    <t>29.09.202653</t>
-  </si>
-  <si>
-    <t>29.09.202654</t>
-  </si>
-  <si>
-    <t>29.09.202655</t>
-  </si>
-  <si>
-    <t>29.09.202656</t>
-  </si>
-  <si>
-    <t>29.09.202657</t>
-  </si>
-  <si>
-    <t>29.09.202658</t>
-  </si>
-  <si>
-    <t>29.09.202659</t>
-  </si>
-  <si>
-    <t>29.09.202660</t>
-  </si>
-  <si>
-    <t>29.09.202661</t>
-  </si>
-  <si>
-    <t>29.09.202662</t>
-  </si>
-  <si>
-    <t>29.09.202663</t>
-  </si>
-  <si>
-    <t>29.09.202664</t>
-  </si>
-  <si>
-    <t>29.09.202665</t>
-  </si>
-  <si>
-    <t>29.09.202666</t>
-  </si>
-  <si>
-    <t>29.09.202667</t>
-  </si>
-  <si>
-    <t>29.09.202668</t>
-  </si>
-  <si>
-    <t>29.09.202669</t>
-  </si>
-  <si>
-    <t>29.09.202670</t>
-  </si>
-  <si>
-    <t>29.09.202671</t>
-  </si>
-  <si>
-    <t>29.09.202672</t>
-  </si>
-  <si>
-    <t>29.09.202673</t>
-  </si>
-  <si>
-    <t>29.09.202674</t>
-  </si>
-  <si>
-    <t>29.09.202675</t>
-  </si>
-  <si>
-    <t>29.09.202676</t>
-  </si>
-  <si>
-    <t>29.09.202677</t>
-  </si>
-  <si>
-    <t>29.09.202678</t>
-  </si>
-  <si>
-    <t>29.09.202679</t>
-  </si>
-  <si>
-    <t>29.09.202680</t>
-  </si>
-  <si>
-    <t>29.09.202681</t>
-  </si>
-  <si>
-    <t>29.09.202682</t>
-  </si>
-  <si>
-    <t>29.09.202683</t>
-  </si>
-  <si>
-    <t>29.09.202684</t>
-  </si>
-  <si>
-    <t>29.09.202685</t>
-  </si>
-  <si>
-    <t>29.09.202686</t>
-  </si>
-  <si>
-    <t>29.09.202687</t>
-  </si>
-  <si>
-    <t>29.09.202688</t>
-  </si>
-  <si>
-    <t>29.09.202689</t>
-  </si>
-  <si>
-    <t>29.09.202690</t>
-  </si>
-  <si>
-    <t>29.09.202691</t>
-  </si>
-  <si>
-    <t>29.09.202692</t>
-  </si>
-  <si>
-    <t>29.09.202693</t>
-  </si>
-  <si>
-    <t>29.09.202694</t>
-  </si>
-  <si>
-    <t>29.09.202695</t>
-  </si>
-  <si>
-    <t>29.09.202696</t>
-  </si>
-  <si>
-    <t>30.09.20261</t>
-  </si>
-  <si>
-    <t>30.09.20262</t>
-  </si>
-  <si>
-    <t>30.09.20263</t>
-  </si>
-  <si>
-    <t>30.09.20264</t>
-  </si>
-  <si>
-    <t>30.09.20265</t>
-  </si>
-  <si>
-    <t>30.09.20266</t>
-  </si>
-  <si>
-    <t>30.09.20267</t>
-  </si>
-  <si>
-    <t>30.09.20268</t>
-  </si>
-  <si>
-    <t>30.09.20269</t>
-  </si>
-  <si>
-    <t>30.09.202610</t>
-  </si>
-  <si>
-    <t>30.09.202611</t>
-  </si>
-  <si>
-    <t>30.09.202612</t>
-  </si>
-  <si>
-    <t>30.09.202613</t>
-  </si>
-  <si>
-    <t>30.09.202614</t>
-  </si>
-  <si>
-    <t>30.09.202615</t>
-  </si>
-  <si>
-    <t>30.09.202616</t>
-  </si>
-  <si>
-    <t>30.09.202617</t>
-  </si>
-  <si>
-    <t>30.09.202618</t>
-  </si>
-  <si>
-    <t>30.09.202619</t>
-  </si>
-  <si>
-    <t>30.09.202620</t>
-  </si>
-  <si>
-    <t>30.09.202621</t>
-  </si>
-  <si>
-    <t>30.09.202622</t>
-  </si>
-  <si>
-    <t>30.09.202623</t>
-  </si>
-  <si>
-    <t>30.09.202624</t>
-  </si>
-  <si>
-    <t>30.09.202625</t>
-  </si>
-  <si>
-    <t>30.09.202626</t>
-  </si>
-  <si>
-    <t>30.09.202627</t>
-  </si>
-  <si>
-    <t>30.09.202628</t>
-  </si>
-  <si>
-    <t>30.09.202629</t>
-  </si>
-  <si>
-    <t>30.09.202630</t>
-  </si>
-  <si>
-    <t>30.09.202631</t>
-  </si>
-  <si>
-    <t>30.09.202632</t>
-  </si>
-  <si>
-    <t>30.09.202633</t>
-  </si>
-  <si>
-    <t>30.09.202634</t>
-  </si>
-  <si>
-    <t>30.09.202635</t>
-  </si>
-  <si>
-    <t>30.09.202636</t>
-  </si>
-  <si>
-    <t>30.09.202637</t>
-  </si>
-  <si>
-    <t>30.09.202638</t>
-  </si>
-  <si>
-    <t>30.09.202639</t>
-  </si>
-  <si>
-    <t>30.09.202640</t>
-  </si>
-  <si>
-    <t>30.09.202641</t>
-  </si>
-  <si>
-    <t>30.09.202642</t>
-  </si>
-  <si>
-    <t>30.09.202643</t>
-  </si>
-  <si>
-    <t>30.09.202644</t>
-  </si>
-  <si>
-    <t>30.09.202645</t>
-  </si>
-  <si>
-    <t>30.09.202646</t>
-  </si>
-  <si>
-    <t>30.09.202647</t>
-  </si>
-  <si>
-    <t>30.09.202648</t>
-  </si>
-  <si>
-    <t>30.09.202649</t>
-  </si>
-  <si>
-    <t>30.09.202650</t>
-  </si>
-  <si>
-    <t>30.09.202651</t>
-  </si>
-  <si>
-    <t>30.09.202652</t>
-  </si>
-  <si>
-    <t>30.09.202653</t>
-  </si>
-  <si>
-    <t>30.09.202654</t>
-  </si>
-  <si>
-    <t>30.09.202655</t>
-  </si>
-  <si>
-    <t>30.09.202656</t>
-  </si>
-  <si>
-    <t>30.09.202657</t>
-  </si>
-  <si>
-    <t>30.09.202658</t>
-  </si>
-  <si>
-    <t>30.09.202659</t>
-  </si>
-  <si>
-    <t>30.09.202660</t>
-  </si>
-  <si>
-    <t>30.09.202661</t>
-  </si>
-  <si>
-    <t>30.09.202662</t>
-  </si>
-  <si>
-    <t>30.09.202663</t>
-  </si>
-  <si>
-    <t>30.09.202664</t>
-  </si>
-  <si>
-    <t>30.09.202665</t>
-  </si>
-  <si>
-    <t>30.09.202666</t>
-  </si>
-  <si>
-    <t>30.09.202667</t>
-  </si>
-  <si>
-    <t>30.09.202668</t>
-  </si>
-  <si>
-    <t>30.09.202669</t>
-  </si>
-  <si>
-    <t>30.09.202670</t>
-  </si>
-  <si>
-    <t>30.09.202671</t>
-  </si>
-  <si>
-    <t>30.09.202672</t>
-  </si>
-  <si>
-    <t>30.09.202673</t>
-  </si>
-  <si>
-    <t>30.09.202674</t>
-  </si>
-  <si>
-    <t>30.09.202675</t>
-  </si>
-  <si>
-    <t>30.09.202676</t>
-  </si>
-  <si>
-    <t>30.09.202677</t>
-  </si>
-  <si>
-    <t>30.09.202678</t>
-  </si>
-  <si>
-    <t>30.09.202679</t>
-  </si>
-  <si>
-    <t>30.09.202680</t>
-  </si>
-  <si>
-    <t>30.09.202681</t>
-  </si>
-  <si>
-    <t>30.09.202682</t>
-  </si>
-  <si>
-    <t>30.09.202683</t>
-  </si>
-  <si>
-    <t>30.09.202684</t>
-  </si>
-  <si>
-    <t>30.09.202685</t>
-  </si>
-  <si>
-    <t>30.09.202686</t>
-  </si>
-  <si>
-    <t>30.09.202687</t>
-  </si>
-  <si>
-    <t>30.09.202688</t>
-  </si>
-  <si>
-    <t>30.09.202689</t>
-  </si>
-  <si>
-    <t>30.09.202690</t>
-  </si>
-  <si>
-    <t>30.09.202691</t>
-  </si>
-  <si>
-    <t>30.09.202692</t>
-  </si>
-  <si>
-    <t>30.09.202693</t>
-  </si>
-  <si>
-    <t>30.09.202694</t>
-  </si>
-  <si>
-    <t>30.09.202695</t>
-  </si>
-  <si>
-    <t>30.09.202696</t>
+    <t>01.10.20261</t>
+  </si>
+  <si>
+    <t>01.10.20262</t>
+  </si>
+  <si>
+    <t>01.10.20263</t>
+  </si>
+  <si>
+    <t>01.10.20264</t>
+  </si>
+  <si>
+    <t>01.10.20265</t>
+  </si>
+  <si>
+    <t>01.10.20266</t>
+  </si>
+  <si>
+    <t>01.10.20267</t>
+  </si>
+  <si>
+    <t>01.10.20268</t>
+  </si>
+  <si>
+    <t>01.10.20269</t>
+  </si>
+  <si>
+    <t>01.10.202610</t>
+  </si>
+  <si>
+    <t>01.10.202611</t>
+  </si>
+  <si>
+    <t>01.10.202612</t>
+  </si>
+  <si>
+    <t>01.10.202613</t>
+  </si>
+  <si>
+    <t>01.10.202614</t>
+  </si>
+  <si>
+    <t>01.10.202615</t>
+  </si>
+  <si>
+    <t>01.10.202616</t>
+  </si>
+  <si>
+    <t>01.10.202617</t>
+  </si>
+  <si>
+    <t>01.10.202618</t>
+  </si>
+  <si>
+    <t>01.10.202619</t>
+  </si>
+  <si>
+    <t>01.10.202620</t>
+  </si>
+  <si>
+    <t>01.10.202621</t>
+  </si>
+  <si>
+    <t>01.10.202622</t>
+  </si>
+  <si>
+    <t>01.10.202623</t>
+  </si>
+  <si>
+    <t>01.10.202624</t>
+  </si>
+  <si>
+    <t>01.10.202625</t>
+  </si>
+  <si>
+    <t>01.10.202626</t>
+  </si>
+  <si>
+    <t>01.10.202627</t>
+  </si>
+  <si>
+    <t>01.10.202628</t>
+  </si>
+  <si>
+    <t>01.10.202629</t>
+  </si>
+  <si>
+    <t>01.10.202630</t>
+  </si>
+  <si>
+    <t>01.10.202631</t>
+  </si>
+  <si>
+    <t>01.10.202632</t>
+  </si>
+  <si>
+    <t>01.10.202633</t>
+  </si>
+  <si>
+    <t>01.10.202634</t>
+  </si>
+  <si>
+    <t>01.10.202635</t>
+  </si>
+  <si>
+    <t>01.10.202636</t>
+  </si>
+  <si>
+    <t>01.10.202637</t>
+  </si>
+  <si>
+    <t>01.10.202638</t>
+  </si>
+  <si>
+    <t>01.10.202639</t>
+  </si>
+  <si>
+    <t>01.10.202640</t>
+  </si>
+  <si>
+    <t>01.10.202641</t>
+  </si>
+  <si>
+    <t>01.10.202642</t>
+  </si>
+  <si>
+    <t>01.10.202643</t>
+  </si>
+  <si>
+    <t>01.10.202644</t>
+  </si>
+  <si>
+    <t>01.10.202645</t>
+  </si>
+  <si>
+    <t>01.10.202646</t>
+  </si>
+  <si>
+    <t>01.10.202647</t>
+  </si>
+  <si>
+    <t>01.10.202648</t>
+  </si>
+  <si>
+    <t>01.10.202649</t>
+  </si>
+  <si>
+    <t>01.10.202650</t>
+  </si>
+  <si>
+    <t>01.10.202651</t>
+  </si>
+  <si>
+    <t>01.10.202652</t>
+  </si>
+  <si>
+    <t>01.10.202653</t>
+  </si>
+  <si>
+    <t>01.10.202654</t>
+  </si>
+  <si>
+    <t>01.10.202655</t>
+  </si>
+  <si>
+    <t>01.10.202656</t>
+  </si>
+  <si>
+    <t>01.10.202657</t>
+  </si>
+  <si>
+    <t>01.10.202658</t>
+  </si>
+  <si>
+    <t>01.10.202659</t>
+  </si>
+  <si>
+    <t>01.10.202660</t>
+  </si>
+  <si>
+    <t>01.10.202661</t>
+  </si>
+  <si>
+    <t>01.10.202662</t>
+  </si>
+  <si>
+    <t>01.10.202663</t>
+  </si>
+  <si>
+    <t>01.10.202664</t>
+  </si>
+  <si>
+    <t>01.10.202665</t>
+  </si>
+  <si>
+    <t>01.10.202666</t>
+  </si>
+  <si>
+    <t>01.10.202667</t>
+  </si>
+  <si>
+    <t>01.10.202668</t>
+  </si>
+  <si>
+    <t>01.10.202669</t>
+  </si>
+  <si>
+    <t>01.10.202670</t>
+  </si>
+  <si>
+    <t>01.10.202671</t>
+  </si>
+  <si>
+    <t>01.10.202672</t>
+  </si>
+  <si>
+    <t>01.10.202673</t>
+  </si>
+  <si>
+    <t>01.10.202674</t>
+  </si>
+  <si>
+    <t>01.10.202675</t>
+  </si>
+  <si>
+    <t>01.10.202676</t>
+  </si>
+  <si>
+    <t>01.10.202677</t>
+  </si>
+  <si>
+    <t>01.10.202678</t>
+  </si>
+  <si>
+    <t>01.10.202679</t>
+  </si>
+  <si>
+    <t>01.10.202680</t>
+  </si>
+  <si>
+    <t>01.10.202681</t>
+  </si>
+  <si>
+    <t>01.10.202682</t>
+  </si>
+  <si>
+    <t>01.10.202683</t>
+  </si>
+  <si>
+    <t>01.10.202684</t>
+  </si>
+  <si>
+    <t>01.10.202685</t>
+  </si>
+  <si>
+    <t>01.10.202686</t>
+  </si>
+  <si>
+    <t>01.10.202687</t>
+  </si>
+  <si>
+    <t>01.10.202688</t>
+  </si>
+  <si>
+    <t>01.10.202689</t>
+  </si>
+  <si>
+    <t>01.10.202690</t>
+  </si>
+  <si>
+    <t>01.10.202691</t>
+  </si>
+  <si>
+    <t>01.10.202692</t>
+  </si>
+  <si>
+    <t>01.10.202693</t>
+  </si>
+  <si>
+    <t>01.10.202694</t>
+  </si>
+  <si>
+    <t>01.10.202695</t>
+  </si>
+  <si>
+    <t>01.10.202696</t>
+  </si>
+  <si>
+    <t>02.10.20261</t>
+  </si>
+  <si>
+    <t>02.10.20262</t>
+  </si>
+  <si>
+    <t>02.10.20263</t>
+  </si>
+  <si>
+    <t>02.10.20264</t>
+  </si>
+  <si>
+    <t>02.10.20265</t>
+  </si>
+  <si>
+    <t>02.10.20266</t>
+  </si>
+  <si>
+    <t>02.10.20267</t>
+  </si>
+  <si>
+    <t>02.10.20268</t>
+  </si>
+  <si>
+    <t>02.10.20269</t>
+  </si>
+  <si>
+    <t>02.10.202610</t>
+  </si>
+  <si>
+    <t>02.10.202611</t>
+  </si>
+  <si>
+    <t>02.10.202612</t>
+  </si>
+  <si>
+    <t>02.10.202613</t>
+  </si>
+  <si>
+    <t>02.10.202614</t>
+  </si>
+  <si>
+    <t>02.10.202615</t>
+  </si>
+  <si>
+    <t>02.10.202616</t>
+  </si>
+  <si>
+    <t>02.10.202617</t>
+  </si>
+  <si>
+    <t>02.10.202618</t>
+  </si>
+  <si>
+    <t>02.10.202619</t>
+  </si>
+  <si>
+    <t>02.10.202620</t>
+  </si>
+  <si>
+    <t>02.10.202621</t>
+  </si>
+  <si>
+    <t>02.10.202622</t>
+  </si>
+  <si>
+    <t>02.10.202623</t>
+  </si>
+  <si>
+    <t>02.10.202624</t>
+  </si>
+  <si>
+    <t>02.10.202625</t>
+  </si>
+  <si>
+    <t>02.10.202626</t>
+  </si>
+  <si>
+    <t>02.10.202627</t>
+  </si>
+  <si>
+    <t>02.10.202628</t>
+  </si>
+  <si>
+    <t>02.10.202629</t>
+  </si>
+  <si>
+    <t>02.10.202630</t>
+  </si>
+  <si>
+    <t>02.10.202631</t>
+  </si>
+  <si>
+    <t>02.10.202632</t>
+  </si>
+  <si>
+    <t>02.10.202633</t>
+  </si>
+  <si>
+    <t>02.10.202634</t>
+  </si>
+  <si>
+    <t>02.10.202635</t>
+  </si>
+  <si>
+    <t>02.10.202636</t>
+  </si>
+  <si>
+    <t>02.10.202637</t>
+  </si>
+  <si>
+    <t>02.10.202638</t>
+  </si>
+  <si>
+    <t>02.10.202639</t>
+  </si>
+  <si>
+    <t>02.10.202640</t>
+  </si>
+  <si>
+    <t>02.10.202641</t>
+  </si>
+  <si>
+    <t>02.10.202642</t>
+  </si>
+  <si>
+    <t>02.10.202643</t>
+  </si>
+  <si>
+    <t>02.10.202644</t>
+  </si>
+  <si>
+    <t>02.10.202645</t>
+  </si>
+  <si>
+    <t>02.10.202646</t>
+  </si>
+  <si>
+    <t>02.10.202647</t>
+  </si>
+  <si>
+    <t>02.10.202648</t>
+  </si>
+  <si>
+    <t>02.10.202649</t>
+  </si>
+  <si>
+    <t>02.10.202650</t>
+  </si>
+  <si>
+    <t>02.10.202651</t>
+  </si>
+  <si>
+    <t>02.10.202652</t>
+  </si>
+  <si>
+    <t>02.10.202653</t>
+  </si>
+  <si>
+    <t>02.10.202654</t>
+  </si>
+  <si>
+    <t>02.10.202655</t>
+  </si>
+  <si>
+    <t>02.10.202656</t>
+  </si>
+  <si>
+    <t>02.10.202657</t>
+  </si>
+  <si>
+    <t>02.10.202658</t>
+  </si>
+  <si>
+    <t>02.10.202659</t>
+  </si>
+  <si>
+    <t>02.10.202660</t>
+  </si>
+  <si>
+    <t>02.10.202661</t>
+  </si>
+  <si>
+    <t>02.10.202662</t>
+  </si>
+  <si>
+    <t>02.10.202663</t>
+  </si>
+  <si>
+    <t>02.10.202664</t>
+  </si>
+  <si>
+    <t>02.10.202665</t>
+  </si>
+  <si>
+    <t>02.10.202666</t>
+  </si>
+  <si>
+    <t>02.10.202667</t>
+  </si>
+  <si>
+    <t>02.10.202668</t>
+  </si>
+  <si>
+    <t>02.10.202669</t>
+  </si>
+  <si>
+    <t>02.10.202670</t>
+  </si>
+  <si>
+    <t>02.10.202671</t>
+  </si>
+  <si>
+    <t>02.10.202672</t>
+  </si>
+  <si>
+    <t>02.10.202673</t>
+  </si>
+  <si>
+    <t>02.10.202674</t>
+  </si>
+  <si>
+    <t>02.10.202675</t>
+  </si>
+  <si>
+    <t>02.10.202676</t>
+  </si>
+  <si>
+    <t>02.10.202677</t>
+  </si>
+  <si>
+    <t>02.10.202678</t>
+  </si>
+  <si>
+    <t>02.10.202679</t>
+  </si>
+  <si>
+    <t>02.10.202680</t>
+  </si>
+  <si>
+    <t>02.10.202681</t>
+  </si>
+  <si>
+    <t>02.10.202682</t>
+  </si>
+  <si>
+    <t>02.10.202683</t>
+  </si>
+  <si>
+    <t>02.10.202684</t>
+  </si>
+  <si>
+    <t>02.10.202685</t>
+  </si>
+  <si>
+    <t>02.10.202686</t>
+  </si>
+  <si>
+    <t>02.10.202687</t>
+  </si>
+  <si>
+    <t>02.10.202688</t>
+  </si>
+  <si>
+    <t>02.10.202689</t>
+  </si>
+  <si>
+    <t>02.10.202690</t>
+  </si>
+  <si>
+    <t>02.10.202691</t>
+  </si>
+  <si>
+    <t>02.10.202692</t>
+  </si>
+  <si>
+    <t>02.10.202693</t>
+  </si>
+  <si>
+    <t>02.10.202694</t>
+  </si>
+  <si>
+    <t>02.10.202695</t>
+  </si>
+  <si>
+    <t>02.10.202696</t>
+  </si>
+  <si>
+    <t>03.10.20261</t>
+  </si>
+  <si>
+    <t>03.10.20262</t>
+  </si>
+  <si>
+    <t>03.10.20263</t>
+  </si>
+  <si>
+    <t>03.10.20264</t>
+  </si>
+  <si>
+    <t>03.10.20265</t>
+  </si>
+  <si>
+    <t>03.10.20266</t>
+  </si>
+  <si>
+    <t>03.10.20267</t>
+  </si>
+  <si>
+    <t>03.10.20268</t>
+  </si>
+  <si>
+    <t>03.10.20269</t>
+  </si>
+  <si>
+    <t>03.10.202610</t>
+  </si>
+  <si>
+    <t>03.10.202611</t>
+  </si>
+  <si>
+    <t>03.10.202612</t>
+  </si>
+  <si>
+    <t>03.10.202613</t>
+  </si>
+  <si>
+    <t>03.10.202614</t>
+  </si>
+  <si>
+    <t>03.10.202615</t>
+  </si>
+  <si>
+    <t>03.10.202616</t>
+  </si>
+  <si>
+    <t>03.10.202617</t>
+  </si>
+  <si>
+    <t>03.10.202618</t>
+  </si>
+  <si>
+    <t>03.10.202619</t>
+  </si>
+  <si>
+    <t>03.10.202620</t>
+  </si>
+  <si>
+    <t>03.10.202621</t>
+  </si>
+  <si>
+    <t>03.10.202622</t>
+  </si>
+  <si>
+    <t>03.10.202623</t>
+  </si>
+  <si>
+    <t>03.10.202624</t>
+  </si>
+  <si>
+    <t>03.10.202625</t>
+  </si>
+  <si>
+    <t>03.10.202626</t>
+  </si>
+  <si>
+    <t>03.10.202627</t>
+  </si>
+  <si>
+    <t>03.10.202628</t>
+  </si>
+  <si>
+    <t>03.10.202629</t>
+  </si>
+  <si>
+    <t>03.10.202630</t>
+  </si>
+  <si>
+    <t>03.10.202631</t>
+  </si>
+  <si>
+    <t>03.10.202632</t>
+  </si>
+  <si>
+    <t>03.10.202633</t>
+  </si>
+  <si>
+    <t>03.10.202634</t>
+  </si>
+  <si>
+    <t>03.10.202635</t>
+  </si>
+  <si>
+    <t>03.10.202636</t>
+  </si>
+  <si>
+    <t>03.10.202637</t>
+  </si>
+  <si>
+    <t>03.10.202638</t>
+  </si>
+  <si>
+    <t>03.10.202639</t>
+  </si>
+  <si>
+    <t>03.10.202640</t>
+  </si>
+  <si>
+    <t>03.10.202641</t>
+  </si>
+  <si>
+    <t>03.10.202642</t>
+  </si>
+  <si>
+    <t>03.10.202643</t>
+  </si>
+  <si>
+    <t>03.10.202644</t>
+  </si>
+  <si>
+    <t>03.10.202645</t>
+  </si>
+  <si>
+    <t>03.10.202646</t>
+  </si>
+  <si>
+    <t>03.10.202647</t>
+  </si>
+  <si>
+    <t>03.10.202648</t>
+  </si>
+  <si>
+    <t>03.10.202649</t>
+  </si>
+  <si>
+    <t>03.10.202650</t>
+  </si>
+  <si>
+    <t>03.10.202651</t>
+  </si>
+  <si>
+    <t>03.10.202652</t>
+  </si>
+  <si>
+    <t>03.10.202653</t>
+  </si>
+  <si>
+    <t>03.10.202654</t>
+  </si>
+  <si>
+    <t>03.10.202655</t>
+  </si>
+  <si>
+    <t>03.10.202656</t>
+  </si>
+  <si>
+    <t>03.10.202657</t>
+  </si>
+  <si>
+    <t>03.10.202658</t>
+  </si>
+  <si>
+    <t>03.10.202659</t>
+  </si>
+  <si>
+    <t>03.10.202660</t>
+  </si>
+  <si>
+    <t>03.10.202661</t>
+  </si>
+  <si>
+    <t>03.10.202662</t>
+  </si>
+  <si>
+    <t>03.10.202663</t>
+  </si>
+  <si>
+    <t>03.10.202664</t>
+  </si>
+  <si>
+    <t>03.10.202665</t>
+  </si>
+  <si>
+    <t>03.10.202666</t>
+  </si>
+  <si>
+    <t>03.10.202667</t>
+  </si>
+  <si>
+    <t>03.10.202668</t>
+  </si>
+  <si>
+    <t>03.10.202669</t>
+  </si>
+  <si>
+    <t>03.10.202670</t>
+  </si>
+  <si>
+    <t>03.10.202671</t>
+  </si>
+  <si>
+    <t>03.10.202672</t>
+  </si>
+  <si>
+    <t>03.10.202673</t>
+  </si>
+  <si>
+    <t>03.10.202674</t>
+  </si>
+  <si>
+    <t>03.10.202675</t>
+  </si>
+  <si>
+    <t>03.10.202676</t>
+  </si>
+  <si>
+    <t>03.10.202677</t>
+  </si>
+  <si>
+    <t>03.10.202678</t>
+  </si>
+  <si>
+    <t>03.10.202679</t>
+  </si>
+  <si>
+    <t>03.10.202680</t>
+  </si>
+  <si>
+    <t>03.10.202681</t>
+  </si>
+  <si>
+    <t>03.10.202682</t>
+  </si>
+  <si>
+    <t>03.10.202683</t>
+  </si>
+  <si>
+    <t>03.10.202684</t>
+  </si>
+  <si>
+    <t>03.10.202685</t>
+  </si>
+  <si>
+    <t>03.10.202686</t>
+  </si>
+  <si>
+    <t>03.10.202687</t>
+  </si>
+  <si>
+    <t>03.10.202688</t>
+  </si>
+  <si>
+    <t>03.10.202689</t>
+  </si>
+  <si>
+    <t>03.10.202690</t>
+  </si>
+  <si>
+    <t>03.10.202691</t>
+  </si>
+  <si>
+    <t>03.10.202692</t>
+  </si>
+  <si>
+    <t>03.10.202693</t>
+  </si>
+  <si>
+    <t>03.10.202694</t>
+  </si>
+  <si>
+    <t>03.10.202695</t>
+  </si>
+  <si>
+    <t>03.10.202696</t>
   </si>
 </sst>
 </file>
@@ -1288,19 +1288,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46293</v>
+        <v>46296</v>
       </c>
       <c r="B2">
-        <v>3.273</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>1.186</v>
+        <v>41.624</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1311,19 +1311,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46293.01041666666</v>
+        <v>46296.01041666666</v>
       </c>
       <c r="B3">
-        <v>4.035</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>17.956</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -1334,19 +1334,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46293.02083333334</v>
+        <v>46296.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.796</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0.598</v>
+        <v>5.03</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -1357,19 +1357,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46293.03125</v>
+        <v>46296.03125</v>
       </c>
       <c r="B5">
-        <v>0.063</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>1.747</v>
+        <v>8.010999999999999</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>12.5</v>
+        <v>37.5</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -1380,19 +1380,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46293.04166666666</v>
+        <v>46296.04166666666</v>
       </c>
       <c r="B6">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>0.03</v>
+        <v>9.654999999999999</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>12.5</v>
+        <v>37.5</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -1403,19 +1403,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46293.05208333334</v>
+        <v>46296.05208333334</v>
       </c>
       <c r="B7">
-        <v>4.582</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>14.463</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -1426,19 +1426,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46293.0625</v>
+        <v>46296.0625</v>
       </c>
       <c r="B8">
-        <v>0.132</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>0.261</v>
+        <v>12.806</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -1449,19 +1449,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46293.07291666666</v>
+        <v>46296.07291666666</v>
       </c>
       <c r="B9">
-        <v>0.073</v>
+        <v>0.296</v>
       </c>
       <c r="C9">
-        <v>0.483</v>
+        <v>2.194</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -1472,19 +1472,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46293.08333333334</v>
+        <v>46296.08333333334</v>
       </c>
       <c r="B10">
-        <v>0.026</v>
+        <v>2.134</v>
       </c>
       <c r="C10">
-        <v>0.304</v>
+        <v>1.109</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F10">
         <v>9</v>
@@ -1495,19 +1495,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46293.09375</v>
+        <v>46296.09375</v>
       </c>
       <c r="B11">
-        <v>0.006</v>
+        <v>10.033</v>
       </c>
       <c r="C11">
-        <v>2.032</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -1518,19 +1518,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46293.10416666666</v>
+        <v>46296.10416666666</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>5.545</v>
       </c>
       <c r="C12">
-        <v>5.665</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F12">
         <v>11</v>
@@ -1541,19 +1541,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46293.11458333334</v>
+        <v>46296.11458333334</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>18.987</v>
       </c>
       <c r="C13">
-        <v>17.42</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F13">
         <v>12</v>
@@ -1564,19 +1564,19 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46293.125</v>
+        <v>46296.125</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>8.423</v>
       </c>
       <c r="C14">
-        <v>3.345</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F14">
         <v>13</v>
@@ -1587,19 +1587,19 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46293.13541666666</v>
+        <v>46296.13541666666</v>
       </c>
       <c r="B15">
-        <v>0.081</v>
+        <v>3.601</v>
       </c>
       <c r="C15">
-        <v>0.292</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F15">
         <v>14</v>
@@ -1610,13 +1610,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46293.14583333334</v>
+        <v>46296.14583333334</v>
       </c>
       <c r="B16">
-        <v>0.11</v>
+        <v>10.105</v>
       </c>
       <c r="C16">
-        <v>0.078</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1633,13 +1633,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46293.15625</v>
+        <v>46296.15625</v>
       </c>
       <c r="B17">
-        <v>0.026</v>
+        <v>13.722</v>
       </c>
       <c r="C17">
-        <v>0.244</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1656,13 +1656,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46293.16666666666</v>
+        <v>46296.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.11</v>
+        <v>0.042</v>
       </c>
       <c r="C18">
-        <v>0.08599999999999999</v>
+        <v>2.629</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1679,19 +1679,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46293.17708333334</v>
+        <v>46296.17708333334</v>
       </c>
       <c r="B19">
-        <v>5.643</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>7.847</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F19">
         <v>18</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46293.1875</v>
+        <v>46296.1875</v>
       </c>
       <c r="B20">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>0.001</v>
+        <v>17.308</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1725,19 +1725,19 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46293.19791666666</v>
+        <v>46296.19791666666</v>
       </c>
       <c r="B21">
-        <v>16.31</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>0.003</v>
+        <v>17.735</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F21">
         <v>20</v>
@@ -1748,13 +1748,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46293.20833333334</v>
+        <v>46296.20833333334</v>
       </c>
       <c r="B22">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>0.006</v>
+        <v>7.813</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1771,13 +1771,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46293.21875</v>
+        <v>46296.21875</v>
       </c>
       <c r="B23">
-        <v>7.699</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>9.499000000000001</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1794,13 +1794,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46293.22916666666</v>
+        <v>46296.22916666666</v>
       </c>
       <c r="B24">
-        <v>8.821</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>17.441</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1817,13 +1817,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46293.23958333334</v>
+        <v>46296.23958333334</v>
       </c>
       <c r="B25">
-        <v>22.569</v>
+        <v>2.209</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1.215</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1840,13 +1840,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46293.25</v>
+        <v>46296.25</v>
       </c>
       <c r="B26">
-        <v>16.688</v>
+        <v>0.223</v>
       </c>
       <c r="C26">
-        <v>1.02</v>
+        <v>2.387</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1863,13 +1863,13 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46293.26041666666</v>
+        <v>46296.26041666666</v>
       </c>
       <c r="B27">
-        <v>35.383</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>5.025</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1886,13 +1886,13 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46293.27083333334</v>
+        <v>46296.27083333334</v>
       </c>
       <c r="B28">
-        <v>27.735</v>
+        <v>0.031</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>2.218</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1909,16 +1909,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46293.28125</v>
+        <v>46296.28125</v>
       </c>
       <c r="B29">
-        <v>8.028</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>0.002</v>
+        <v>4.447</v>
       </c>
       <c r="D29">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1932,16 +1932,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46293.29166666666</v>
+        <v>46296.29166666666</v>
       </c>
       <c r="B30">
-        <v>0.914</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>0.106</v>
+        <v>10.563</v>
       </c>
       <c r="D30">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1955,13 +1955,13 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46293.30208333334</v>
+        <v>46296.30208333334</v>
       </c>
       <c r="B31">
-        <v>0.165</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>0.298</v>
+        <v>5.176</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1978,13 +1978,13 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46293.3125</v>
+        <v>46296.3125</v>
       </c>
       <c r="B32">
-        <v>0.08799999999999999</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>0.482</v>
+        <v>12.53</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -2001,13 +2001,13 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46293.32291666666</v>
+        <v>46296.32291666666</v>
       </c>
       <c r="B33">
-        <v>0.093</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>1.989</v>
+        <v>10.197</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -2024,13 +2024,13 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46293.33333333334</v>
+        <v>46296.33333333334</v>
       </c>
       <c r="B34">
-        <v>0.04</v>
+        <v>11.41</v>
       </c>
       <c r="C34">
-        <v>3.914</v>
+        <v>1.258</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -2047,19 +2047,19 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46293.34375</v>
+        <v>46296.34375</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>20.409</v>
       </c>
       <c r="C35">
-        <v>28.294</v>
+        <v>0</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35">
-        <v>62.5</v>
+        <v>25</v>
       </c>
       <c r="F35">
         <v>34</v>
@@ -2070,19 +2070,19 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46293.35416666666</v>
+        <v>46296.35416666666</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>0.729</v>
       </c>
       <c r="C36">
-        <v>26.44</v>
+        <v>4.164</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F36">
         <v>35</v>
@@ -2093,19 +2093,19 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46293.36458333334</v>
+        <v>46296.36458333334</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
       <c r="C37">
-        <v>5.693</v>
+        <v>15.055</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F37">
         <v>36</v>
@@ -2116,19 +2116,19 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46293.375</v>
+        <v>46296.375</v>
       </c>
       <c r="B38">
-        <v>0.129</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>5.64</v>
+        <v>14.646</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F38">
         <v>37</v>
@@ -2139,19 +2139,19 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46293.38541666666</v>
+        <v>46296.38541666666</v>
       </c>
       <c r="B39">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>9.026999999999999</v>
+        <v>28.552</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="F39">
         <v>38</v>
@@ -2162,19 +2162,19 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46293.39583333334</v>
+        <v>46296.39583333334</v>
       </c>
       <c r="B40">
-        <v>2.615</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>5.05</v>
+        <v>52.826</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40">
-        <v>87.5</v>
+        <v>37.5</v>
       </c>
       <c r="F40">
         <v>39</v>
@@ -2185,19 +2185,19 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46293.40625</v>
+        <v>46296.40625</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C41">
-        <v>12.072</v>
+        <v>11.473</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>87.5</v>
+        <v>62.5</v>
       </c>
       <c r="F41">
         <v>40</v>
@@ -2208,19 +2208,19 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46293.41666666666</v>
+        <v>46296.41666666666</v>
       </c>
       <c r="B42">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>8.462</v>
+        <v>23.721</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="F42">
         <v>41</v>
@@ -2231,19 +2231,19 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46293.42708333334</v>
+        <v>46296.42708333334</v>
       </c>
       <c r="B43">
-        <v>0.705</v>
+        <v>0.045</v>
       </c>
       <c r="C43">
-        <v>2.683</v>
+        <v>1.432</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="F43">
         <v>42</v>
@@ -2254,13 +2254,13 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46293.4375</v>
+        <v>46296.4375</v>
       </c>
       <c r="B44">
         <v>0</v>
       </c>
       <c r="C44">
-        <v>7.9</v>
+        <v>18.428</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -2277,19 +2277,19 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46293.44791666666</v>
+        <v>46296.44791666666</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>0.078</v>
       </c>
       <c r="C45">
-        <v>23.66</v>
+        <v>3.002</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="F45">
         <v>44</v>
@@ -2300,19 +2300,19 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46293.45833333334</v>
+        <v>46296.45833333334</v>
       </c>
       <c r="B46">
-        <v>0.062</v>
+        <v>0.099</v>
       </c>
       <c r="C46">
-        <v>6.486</v>
+        <v>5.528</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="F46">
         <v>45</v>
@@ -2323,19 +2323,19 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46293.46875</v>
+        <v>46296.46875</v>
       </c>
       <c r="B47">
-        <v>0.621</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <v>1.714</v>
+        <v>14.802</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="F47">
         <v>46</v>
@@ -2346,19 +2346,19 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46293.47916666666</v>
+        <v>46296.47916666666</v>
       </c>
       <c r="B48">
-        <v>0.155</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <v>4.911</v>
+        <v>27.631</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="F48">
         <v>47</v>
@@ -2369,19 +2369,19 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46293.48958333334</v>
+        <v>46296.48958333334</v>
       </c>
       <c r="B49">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="C49">
-        <v>7.781</v>
+        <v>9.324</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>100</v>
+        <v>137.5</v>
       </c>
       <c r="F49">
         <v>48</v>
@@ -2392,19 +2392,19 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46293.5</v>
+        <v>46296.5</v>
       </c>
       <c r="B50">
-        <v>7.731</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>2.262</v>
+        <v>32.398</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="F50">
         <v>49</v>
@@ -2415,19 +2415,19 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46293.51041666666</v>
+        <v>46296.51041666666</v>
       </c>
       <c r="B51">
-        <v>12.028</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>11.393</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>100</v>
+        <v>137.5</v>
       </c>
       <c r="F51">
         <v>50</v>
@@ -2438,19 +2438,19 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46293.52083333334</v>
+        <v>46296.52083333334</v>
       </c>
       <c r="B52">
-        <v>2.932</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <v>15.745</v>
+        <v>18.725</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>137.5</v>
       </c>
       <c r="F52">
         <v>51</v>
@@ -2461,19 +2461,19 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46293.53125</v>
+        <v>46296.53125</v>
       </c>
       <c r="B53">
-        <v>0.135</v>
+        <v>0.001</v>
       </c>
       <c r="C53">
-        <v>5.595</v>
+        <v>5.517</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>25</v>
+        <v>137.5</v>
       </c>
       <c r="F53">
         <v>52</v>
@@ -2484,19 +2484,19 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46293.54166666666</v>
+        <v>46296.54166666666</v>
       </c>
       <c r="B54">
-        <v>0.224</v>
+        <v>0.53</v>
       </c>
       <c r="C54">
-        <v>6.385</v>
+        <v>2.736</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="F54">
         <v>53</v>
@@ -2507,19 +2507,19 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46293.55208333334</v>
+        <v>46296.55208333334</v>
       </c>
       <c r="B55">
-        <v>3.064</v>
+        <v>0.048</v>
       </c>
       <c r="C55">
-        <v>0.22</v>
+        <v>5.505</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>50</v>
+        <v>112.5</v>
       </c>
       <c r="F55">
         <v>54</v>
@@ -2530,19 +2530,19 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46293.5625</v>
+        <v>46296.5625</v>
       </c>
       <c r="B56">
-        <v>0.199</v>
+        <v>1.458</v>
       </c>
       <c r="C56">
-        <v>3.048</v>
+        <v>0.592</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>50</v>
+        <v>112.5</v>
       </c>
       <c r="F56">
         <v>55</v>
@@ -2553,19 +2553,19 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46293.57291666666</v>
+        <v>46296.57291666666</v>
       </c>
       <c r="B57">
-        <v>2.393</v>
+        <v>1.138</v>
       </c>
       <c r="C57">
-        <v>1.278</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F57">
         <v>56</v>
@@ -2576,19 +2576,19 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46293.58333333334</v>
+        <v>46296.58333333334</v>
       </c>
       <c r="B58">
-        <v>0.011</v>
+        <v>0.146</v>
       </c>
       <c r="C58">
-        <v>24.959</v>
+        <v>14.817</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F58">
         <v>57</v>
@@ -2599,19 +2599,19 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46293.59375</v>
+        <v>46296.59375</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>6.483</v>
       </c>
       <c r="C59">
-        <v>12.914</v>
+        <v>0.016</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="F59">
         <v>58</v>
@@ -2622,19 +2622,19 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46293.60416666666</v>
+        <v>46296.60416666666</v>
       </c>
       <c r="B60">
-        <v>2.44</v>
+        <v>7.873</v>
       </c>
       <c r="C60">
-        <v>1.846</v>
+        <v>0</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60">
-        <v>50</v>
+        <v>112.5</v>
       </c>
       <c r="F60">
         <v>59</v>
@@ -2645,19 +2645,19 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46293.61458333334</v>
+        <v>46296.61458333334</v>
       </c>
       <c r="B61">
-        <v>0.07099999999999999</v>
+        <v>2.091</v>
       </c>
       <c r="C61">
-        <v>21.417</v>
+        <v>1.705</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F61">
         <v>60</v>
@@ -2668,19 +2668,19 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46293.625</v>
+        <v>46296.625</v>
       </c>
       <c r="B62">
         <v>0</v>
       </c>
       <c r="C62">
-        <v>25.484</v>
+        <v>48.454</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>37.5</v>
+        <v>87.5</v>
       </c>
       <c r="F62">
         <v>61</v>
@@ -2691,19 +2691,19 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46293.63541666666</v>
+        <v>46296.63541666666</v>
       </c>
       <c r="B63">
-        <v>8.048999999999999</v>
+        <v>0.053</v>
       </c>
       <c r="C63">
-        <v>6.825</v>
+        <v>17.28</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>37.5</v>
+        <v>87.5</v>
       </c>
       <c r="F63">
         <v>62</v>
@@ -2714,19 +2714,19 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46293.64583333334</v>
+        <v>46296.64583333334</v>
       </c>
       <c r="B64">
-        <v>59.192</v>
+        <v>0.123</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>2.447</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>25</v>
+        <v>87.5</v>
       </c>
       <c r="F64">
         <v>63</v>
@@ -2737,19 +2737,19 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46293.65625</v>
+        <v>46296.65625</v>
       </c>
       <c r="B65">
-        <v>21.419</v>
+        <v>4.038</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="F65">
         <v>64</v>
@@ -2760,19 +2760,19 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46293.66666666666</v>
+        <v>46296.66666666666</v>
       </c>
       <c r="B66">
-        <v>12.407</v>
+        <v>0.371</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="F66">
         <v>65</v>
@@ -2783,19 +2783,19 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46293.67708333334</v>
+        <v>46296.67708333334</v>
       </c>
       <c r="B67">
-        <v>14.263</v>
+        <v>3.373</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>0.162</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F67">
         <v>66</v>
@@ -2806,19 +2806,19 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46293.6875</v>
+        <v>46296.6875</v>
       </c>
       <c r="B68">
-        <v>17.574</v>
+        <v>0.614</v>
       </c>
       <c r="C68">
-        <v>0.021</v>
+        <v>0.102</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F68">
         <v>67</v>
@@ -2829,19 +2829,19 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46293.69791666666</v>
+        <v>46296.69791666666</v>
       </c>
       <c r="B69">
-        <v>30.534</v>
+        <v>3.087</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F69">
         <v>68</v>
@@ -2852,19 +2852,19 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46293.70833333334</v>
+        <v>46296.70833333334</v>
       </c>
       <c r="B70">
-        <v>5.272</v>
+        <v>13.598</v>
       </c>
       <c r="C70">
-        <v>0.065</v>
+        <v>0.156</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F70">
         <v>69</v>
@@ -2875,19 +2875,19 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46293.71875</v>
+        <v>46296.71875</v>
       </c>
       <c r="B71">
-        <v>0.131</v>
+        <v>25.233</v>
       </c>
       <c r="C71">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>77.75</v>
       </c>
       <c r="F71">
         <v>70</v>
@@ -2898,13 +2898,13 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46293.72916666666</v>
+        <v>46296.72916666666</v>
       </c>
       <c r="B72">
-        <v>3.928</v>
+        <v>16.053</v>
       </c>
       <c r="C72">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -2921,10 +2921,10 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46293.73958333334</v>
+        <v>46296.73958333334</v>
       </c>
       <c r="B73">
-        <v>11.133</v>
+        <v>2.737</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -2944,13 +2944,13 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46293.75</v>
+        <v>46296.75</v>
       </c>
       <c r="B74">
-        <v>13.332</v>
+        <v>8.866</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>0.081</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -2967,10 +2967,10 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46293.76041666666</v>
+        <v>46296.76041666666</v>
       </c>
       <c r="B75">
-        <v>22.156</v>
+        <v>20.042</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -2990,10 +2990,10 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46293.77083333334</v>
+        <v>46296.77083333334</v>
       </c>
       <c r="B76">
-        <v>25.948</v>
+        <v>24.686</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46293.78125</v>
+        <v>46296.78125</v>
       </c>
       <c r="B77">
-        <v>13.519</v>
+        <v>29.13</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -3036,16 +3036,16 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46293.79166666666</v>
+        <v>46296.79166666666</v>
       </c>
       <c r="B78">
-        <v>4.517</v>
+        <v>1.78</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>24.75</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -3059,13 +3059,13 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46293.80208333334</v>
+        <v>46296.80208333334</v>
       </c>
       <c r="B79">
-        <v>3.677</v>
+        <v>11.792</v>
       </c>
       <c r="C79">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -3082,13 +3082,13 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46293.8125</v>
+        <v>46296.8125</v>
       </c>
       <c r="B80">
-        <v>1.117</v>
+        <v>11.921</v>
       </c>
       <c r="C80">
-        <v>0.483</v>
+        <v>0</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3105,13 +3105,13 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46293.82291666666</v>
+        <v>46296.82291666666</v>
       </c>
       <c r="B81">
-        <v>0</v>
+        <v>22.813</v>
       </c>
       <c r="C81">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -3128,13 +3128,13 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46293.83333333334</v>
+        <v>46296.83333333334</v>
       </c>
       <c r="B82">
-        <v>0.968</v>
+        <v>18.264</v>
       </c>
       <c r="C82">
-        <v>1.494</v>
+        <v>0.754</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -3151,16 +3151,16 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46293.84375</v>
+        <v>46296.84375</v>
       </c>
       <c r="B83">
-        <v>12.334</v>
+        <v>2.652</v>
       </c>
       <c r="C83">
-        <v>0.382</v>
+        <v>0.28</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46293.85416666666</v>
+        <v>46296.85416666666</v>
       </c>
       <c r="B84">
-        <v>0</v>
+        <v>1.782</v>
       </c>
       <c r="C84">
-        <v>2.534</v>
+        <v>1.572</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -3197,13 +3197,13 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46293.86458333334</v>
+        <v>46296.86458333334</v>
       </c>
       <c r="B85">
-        <v>1.902</v>
+        <v>7.143</v>
       </c>
       <c r="C85">
-        <v>2.28</v>
+        <v>1.106</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -3220,13 +3220,13 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46293.875</v>
+        <v>46296.875</v>
       </c>
       <c r="B86">
-        <v>0.005</v>
+        <v>0.999</v>
       </c>
       <c r="C86">
-        <v>2.946</v>
+        <v>0.959</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -3243,13 +3243,13 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46293.88541666666</v>
+        <v>46296.88541666666</v>
       </c>
       <c r="B87">
-        <v>0.02</v>
+        <v>3.278</v>
       </c>
       <c r="C87">
-        <v>2.587</v>
+        <v>0.024</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -3266,13 +3266,13 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46293.89583333334</v>
+        <v>46296.89583333334</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>9.377000000000001</v>
       </c>
       <c r="C88">
-        <v>4.956</v>
+        <v>0.436</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3289,13 +3289,13 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46293.90625</v>
+        <v>46296.90625</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>2.447</v>
       </c>
       <c r="C89">
-        <v>17.074</v>
+        <v>1.304</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3312,13 +3312,13 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46293.91666666666</v>
+        <v>46296.91666666666</v>
       </c>
       <c r="B90">
-        <v>0.656</v>
+        <v>14.294</v>
       </c>
       <c r="C90">
-        <v>6.557</v>
+        <v>0.22</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3335,13 +3335,13 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46293.92708333334</v>
+        <v>46296.92708333334</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>0.271</v>
       </c>
       <c r="C91">
-        <v>3.37</v>
+        <v>3.425</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3358,13 +3358,13 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46293.9375</v>
+        <v>46296.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
       </c>
       <c r="C92">
-        <v>7.152</v>
+        <v>7.896</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3381,13 +3381,13 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46293.94791666666</v>
+        <v>46296.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
       </c>
       <c r="C93">
-        <v>11.314</v>
+        <v>18.279</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3404,13 +3404,13 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46293.95833333334</v>
+        <v>46296.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
       </c>
       <c r="C94">
-        <v>5.503</v>
+        <v>21.122</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3427,13 +3427,13 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46293.96875</v>
+        <v>46296.96875</v>
       </c>
       <c r="B95">
-        <v>0.162</v>
+        <v>0</v>
       </c>
       <c r="C95">
-        <v>2.17</v>
+        <v>49.355</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3450,19 +3450,19 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46293.97916666666</v>
+        <v>46296.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
       </c>
       <c r="C96">
-        <v>2.975</v>
+        <v>21.973</v>
       </c>
       <c r="D96">
         <v>0</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F96">
         <v>95</v>
@@ -3473,19 +3473,19 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46293.98958333334</v>
+        <v>46296.98958333334</v>
       </c>
       <c r="B97">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="C97">
-        <v>0.8</v>
+        <v>19.411</v>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
       <c r="E97">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F97">
         <v>96</v>
@@ -3496,19 +3496,19 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="B98">
-        <v>1.2</v>
+        <v>3.355</v>
       </c>
       <c r="C98">
-        <v>0.09</v>
+        <v>2.4</v>
       </c>
       <c r="D98">
         <v>0</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F98">
         <v>1</v>
@@ -3519,19 +3519,19 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46294.01041666666</v>
+        <v>46297.01041666666</v>
       </c>
       <c r="B99">
-        <v>8.057</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="C99">
-        <v>0</v>
+        <v>2.104</v>
       </c>
       <c r="D99">
         <v>0</v>
       </c>
       <c r="E99">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F99">
         <v>2</v>
@@ -3542,19 +3542,19 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46294.02083333334</v>
+        <v>46297.02083333334</v>
       </c>
       <c r="B100">
-        <v>4.656</v>
+        <v>7.041</v>
       </c>
       <c r="C100">
-        <v>1.252</v>
+        <v>0.008</v>
       </c>
       <c r="D100">
         <v>0</v>
       </c>
       <c r="E100">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F100">
         <v>3</v>
@@ -3565,19 +3565,19 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46294.03125</v>
+        <v>46297.03125</v>
       </c>
       <c r="B101">
-        <v>0.012</v>
+        <v>2.132</v>
       </c>
       <c r="C101">
-        <v>2.438</v>
+        <v>0.04</v>
       </c>
       <c r="D101">
         <v>0</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F101">
         <v>4</v>
@@ -3588,19 +3588,19 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46294.04166666666</v>
+        <v>46297.04166666666</v>
       </c>
       <c r="B102">
-        <v>0.241</v>
+        <v>0.634</v>
       </c>
       <c r="C102">
-        <v>1.871</v>
+        <v>1.289</v>
       </c>
       <c r="D102">
         <v>0</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F102">
         <v>5</v>
@@ -3611,19 +3611,19 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46294.05208333334</v>
+        <v>46297.05208333334</v>
       </c>
       <c r="B103">
-        <v>4.048</v>
+        <v>0</v>
       </c>
       <c r="C103">
-        <v>0.101</v>
+        <v>5.007</v>
       </c>
       <c r="D103">
         <v>0</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F103">
         <v>6</v>
@@ -3634,19 +3634,19 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46294.0625</v>
+        <v>46297.0625</v>
       </c>
       <c r="B104">
-        <v>3.114</v>
+        <v>0</v>
       </c>
       <c r="C104">
-        <v>0.222</v>
+        <v>3.377</v>
       </c>
       <c r="D104">
         <v>0</v>
       </c>
       <c r="E104">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F104">
         <v>7</v>
@@ -3657,19 +3657,19 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46294.07291666666</v>
+        <v>46297.07291666666</v>
       </c>
       <c r="B105">
-        <v>0.239</v>
+        <v>2.961</v>
       </c>
       <c r="C105">
-        <v>0.556</v>
+        <v>0.018</v>
       </c>
       <c r="D105">
         <v>0</v>
       </c>
       <c r="E105">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F105">
         <v>8</v>
@@ -3680,19 +3680,19 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46294.08333333334</v>
+        <v>46297.08333333334</v>
       </c>
       <c r="B106">
-        <v>10.389</v>
+        <v>0.322</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="D106">
         <v>0</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F106">
         <v>9</v>
@@ -3703,19 +3703,19 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46294.09375</v>
+        <v>46297.09375</v>
       </c>
       <c r="B107">
-        <v>6.251</v>
+        <v>5.897</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="D107">
         <v>0</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F107">
         <v>10</v>
@@ -3726,19 +3726,19 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46294.10416666666</v>
+        <v>46297.10416666666</v>
       </c>
       <c r="B108">
-        <v>0.928</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C108">
-        <v>0.14</v>
+        <v>0.322</v>
       </c>
       <c r="D108">
         <v>0</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F108">
         <v>11</v>
@@ -3749,19 +3749,19 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46294.11458333334</v>
+        <v>46297.11458333334</v>
       </c>
       <c r="B109">
-        <v>0.194</v>
+        <v>4.786</v>
       </c>
       <c r="C109">
-        <v>0.593</v>
+        <v>0.017</v>
       </c>
       <c r="D109">
         <v>0</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F109">
         <v>12</v>
@@ -3772,10 +3772,10 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46294.125</v>
+        <v>46297.125</v>
       </c>
       <c r="B110">
-        <v>8.236000000000001</v>
+        <v>9.382999999999999</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -3784,7 +3784,7 @@
         <v>0</v>
       </c>
       <c r="E110">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F110">
         <v>13</v>
@@ -3795,10 +3795,10 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46294.13541666666</v>
+        <v>46297.13541666666</v>
       </c>
       <c r="B111">
-        <v>9.734</v>
+        <v>9.141</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F111">
         <v>14</v>
@@ -3818,19 +3818,19 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46294.14583333334</v>
+        <v>46297.14583333334</v>
       </c>
       <c r="B112">
-        <v>22.985</v>
+        <v>0.031</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>3.694</v>
       </c>
       <c r="D112">
         <v>0</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F112">
         <v>15</v>
@@ -3841,19 +3841,19 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46294.15625</v>
+        <v>46297.15625</v>
       </c>
       <c r="B113">
-        <v>4.162</v>
+        <v>0</v>
       </c>
       <c r="C113">
-        <v>0.016</v>
+        <v>4.327</v>
       </c>
       <c r="D113">
         <v>0</v>
       </c>
       <c r="E113">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F113">
         <v>16</v>
@@ -3864,19 +3864,19 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46294.16666666666</v>
+        <v>46297.16666666666</v>
       </c>
       <c r="B114">
-        <v>1.869</v>
+        <v>0.028</v>
       </c>
       <c r="C114">
-        <v>0.058</v>
+        <v>1.236</v>
       </c>
       <c r="D114">
         <v>0</v>
       </c>
       <c r="E114">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F114">
         <v>17</v>
@@ -3887,19 +3887,19 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46294.17708333334</v>
+        <v>46297.17708333334</v>
       </c>
       <c r="B115">
-        <v>2.443</v>
+        <v>0</v>
       </c>
       <c r="C115">
-        <v>0.003</v>
+        <v>4.299</v>
       </c>
       <c r="D115">
         <v>0</v>
       </c>
       <c r="E115">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F115">
         <v>18</v>
@@ -3910,19 +3910,19 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46294.1875</v>
+        <v>46297.1875</v>
       </c>
       <c r="B116">
-        <v>13.169</v>
+        <v>0</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>3.722</v>
       </c>
       <c r="D116">
         <v>0</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F116">
         <v>19</v>
@@ -3933,19 +3933,19 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46294.19791666666</v>
+        <v>46297.19791666666</v>
       </c>
       <c r="B117">
-        <v>10.581</v>
+        <v>3.955</v>
       </c>
       <c r="C117">
-        <v>0.004</v>
+        <v>0.231</v>
       </c>
       <c r="D117">
         <v>0</v>
       </c>
       <c r="E117">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F117">
         <v>20</v>
@@ -3956,19 +3956,19 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46294.20833333334</v>
+        <v>46297.20833333334</v>
       </c>
       <c r="B118">
-        <v>1.218</v>
+        <v>12.004</v>
       </c>
       <c r="C118">
-        <v>0.127</v>
+        <v>0</v>
       </c>
       <c r="D118">
         <v>0</v>
       </c>
       <c r="E118">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F118">
         <v>21</v>
@@ -3979,10 +3979,10 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46294.21875</v>
+        <v>46297.21875</v>
       </c>
       <c r="B119">
-        <v>4.398</v>
+        <v>10.401</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -4002,16 +4002,16 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46294.22916666666</v>
+        <v>46297.22916666666</v>
       </c>
       <c r="B120">
-        <v>9.368</v>
+        <v>0.599</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -4025,16 +4025,16 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46294.23958333334</v>
+        <v>46297.23958333334</v>
       </c>
       <c r="B121">
-        <v>11.927</v>
+        <v>5.884</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -4048,13 +4048,13 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46294.25</v>
+        <v>46297.25</v>
       </c>
       <c r="B122">
-        <v>15.741</v>
+        <v>15.995</v>
       </c>
       <c r="C122">
-        <v>1.088</v>
+        <v>1.198</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -4071,10 +4071,10 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46294.26041666666</v>
+        <v>46297.26041666666</v>
       </c>
       <c r="B123">
-        <v>31.915</v>
+        <v>10.112</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -4094,16 +4094,16 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46294.27083333334</v>
+        <v>46297.27083333334</v>
       </c>
       <c r="B124">
-        <v>23.683</v>
+        <v>0.118</v>
       </c>
       <c r="C124">
-        <v>0</v>
+        <v>4.875</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -4117,16 +4117,16 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46294.28125</v>
+        <v>46297.28125</v>
       </c>
       <c r="B125">
-        <v>33.605</v>
+        <v>0.229</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="D125">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -4140,13 +4140,13 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46294.29166666666</v>
+        <v>46297.29166666666</v>
       </c>
       <c r="B126">
-        <v>48.953</v>
+        <v>1.604</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>0.078</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -4163,13 +4163,13 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46294.30208333334</v>
+        <v>46297.30208333334</v>
       </c>
       <c r="B127">
-        <v>32.477</v>
+        <v>0.321</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>0.092</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -4186,13 +4186,13 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46294.3125</v>
+        <v>46297.3125</v>
       </c>
       <c r="B128">
-        <v>0.283</v>
+        <v>0.776</v>
       </c>
       <c r="C128">
-        <v>2.461</v>
+        <v>0.731</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -4209,13 +4209,13 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46294.32291666666</v>
+        <v>46297.32291666666</v>
       </c>
       <c r="B129">
-        <v>0.005</v>
+        <v>0.171</v>
       </c>
       <c r="C129">
-        <v>2.661</v>
+        <v>5.251</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -4232,13 +4232,13 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46294.33333333334</v>
+        <v>46297.33333333334</v>
       </c>
       <c r="B130">
-        <v>0.119</v>
+        <v>32.95</v>
       </c>
       <c r="C130">
-        <v>0.603</v>
+        <v>0.057</v>
       </c>
       <c r="D130">
         <v>0</v>
@@ -4255,16 +4255,16 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46294.34375</v>
+        <v>46297.34375</v>
       </c>
       <c r="B131">
-        <v>0.191</v>
+        <v>11.077</v>
       </c>
       <c r="C131">
-        <v>4.95</v>
+        <v>2.155</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -4278,16 +4278,16 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46294.35416666666</v>
+        <v>46297.35416666666</v>
       </c>
       <c r="B132">
-        <v>0.023</v>
+        <v>0.01</v>
       </c>
       <c r="C132">
-        <v>8.944000000000001</v>
+        <v>4.045</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -4301,19 +4301,19 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46294.36458333334</v>
+        <v>46297.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
       </c>
       <c r="C133">
-        <v>5.207</v>
+        <v>23.338</v>
       </c>
       <c r="D133">
         <v>0</v>
       </c>
       <c r="E133">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F133">
         <v>36</v>
@@ -4324,19 +4324,19 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46294.375</v>
+        <v>46297.375</v>
       </c>
       <c r="B134">
-        <v>0.5</v>
+        <v>13.718</v>
       </c>
       <c r="C134">
-        <v>0.061</v>
+        <v>4.844</v>
       </c>
       <c r="D134">
         <v>0</v>
       </c>
       <c r="E134">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F134">
         <v>37</v>
@@ -4347,19 +4347,19 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46294.38541666666</v>
+        <v>46297.38541666666</v>
       </c>
       <c r="B135">
-        <v>3.339</v>
+        <v>5.22</v>
       </c>
       <c r="C135">
-        <v>0.014</v>
+        <v>3.639</v>
       </c>
       <c r="D135">
         <v>0</v>
       </c>
       <c r="E135">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F135">
         <v>38</v>
@@ -4370,19 +4370,19 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46294.39583333334</v>
+        <v>46297.39583333334</v>
       </c>
       <c r="B136">
-        <v>5.061</v>
+        <v>0</v>
       </c>
       <c r="C136">
-        <v>0.012</v>
+        <v>16.636</v>
       </c>
       <c r="D136">
         <v>0</v>
       </c>
       <c r="E136">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F136">
         <v>39</v>
@@ -4393,19 +4393,19 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46294.40625</v>
+        <v>46297.40625</v>
       </c>
       <c r="B137">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="C137">
-        <v>0.353</v>
+        <v>21.796</v>
       </c>
       <c r="D137">
         <v>0</v>
       </c>
       <c r="E137">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F137">
         <v>40</v>
@@ -4416,19 +4416,19 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46294.41666666666</v>
+        <v>46297.41666666666</v>
       </c>
       <c r="B138">
-        <v>0.258</v>
+        <v>0.124</v>
       </c>
       <c r="C138">
-        <v>0.132</v>
+        <v>7.12</v>
       </c>
       <c r="D138">
         <v>0</v>
       </c>
       <c r="E138">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F138">
         <v>41</v>
@@ -4439,19 +4439,19 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46294.42708333334</v>
+        <v>46297.42708333334</v>
       </c>
       <c r="B139">
-        <v>0.103</v>
+        <v>1.827</v>
       </c>
       <c r="C139">
-        <v>0.189</v>
+        <v>1.75</v>
       </c>
       <c r="D139">
         <v>0</v>
       </c>
       <c r="E139">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F139">
         <v>42</v>
@@ -4462,19 +4462,19 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46294.4375</v>
+        <v>46297.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
       </c>
       <c r="C140">
-        <v>3.59</v>
+        <v>52.854</v>
       </c>
       <c r="D140">
         <v>0</v>
       </c>
       <c r="E140">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F140">
         <v>43</v>
@@ -4485,19 +4485,19 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46294.44791666666</v>
+        <v>46297.44791666666</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="C141">
-        <v>11.153</v>
+        <v>17.418</v>
       </c>
       <c r="D141">
         <v>0</v>
       </c>
       <c r="E141">
-        <v>37.5</v>
+        <v>100</v>
       </c>
       <c r="F141">
         <v>44</v>
@@ -4508,13 +4508,13 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46294.45833333334</v>
+        <v>46297.45833333334</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>3.117</v>
       </c>
       <c r="C142">
-        <v>17.793</v>
+        <v>0.114</v>
       </c>
       <c r="D142">
         <v>0</v>
@@ -4531,19 +4531,19 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46294.46875</v>
+        <v>46297.46875</v>
       </c>
       <c r="B143">
-        <v>0.041</v>
+        <v>0.106</v>
       </c>
       <c r="C143">
-        <v>3.48</v>
+        <v>8.119</v>
       </c>
       <c r="D143">
         <v>0</v>
       </c>
       <c r="E143">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="F143">
         <v>46</v>
@@ -4554,13 +4554,13 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46294.47916666666</v>
+        <v>46297.47916666666</v>
       </c>
       <c r="B144">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="C144">
-        <v>1.765</v>
+        <v>19.833</v>
       </c>
       <c r="D144">
         <v>0</v>
@@ -4577,13 +4577,13 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46294.48958333334</v>
+        <v>46297.48958333334</v>
       </c>
       <c r="B145">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="C145">
-        <v>2.184</v>
+        <v>30.401</v>
       </c>
       <c r="D145">
         <v>0</v>
@@ -4600,13 +4600,13 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46294.5</v>
+        <v>46297.5</v>
       </c>
       <c r="B146">
         <v>0</v>
       </c>
       <c r="C146">
-        <v>12.413</v>
+        <v>16.194</v>
       </c>
       <c r="D146">
         <v>0</v>
@@ -4623,13 +4623,13 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46294.51041666666</v>
+        <v>46297.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>0.117</v>
       </c>
       <c r="C147">
-        <v>12.427</v>
+        <v>1.641</v>
       </c>
       <c r="D147">
         <v>0</v>
@@ -4646,19 +4646,19 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46294.52083333334</v>
+        <v>46297.52083333334</v>
       </c>
       <c r="B148">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="C148">
-        <v>5.268</v>
+        <v>18.739</v>
       </c>
       <c r="D148">
         <v>0</v>
       </c>
       <c r="E148">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="F148">
         <v>51</v>
@@ -4669,19 +4669,19 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46294.53125</v>
+        <v>46297.53125</v>
       </c>
       <c r="B149">
-        <v>1.548</v>
+        <v>0</v>
       </c>
       <c r="C149">
-        <v>1.367</v>
+        <v>39.556</v>
       </c>
       <c r="D149">
         <v>0</v>
       </c>
       <c r="E149">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="F149">
         <v>52</v>
@@ -4692,13 +4692,13 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46294.54166666666</v>
+        <v>46297.54166666666</v>
       </c>
       <c r="B150">
-        <v>7.241</v>
+        <v>0.146</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>6.495</v>
       </c>
       <c r="D150">
         <v>0</v>
@@ -4715,13 +4715,13 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46294.55208333334</v>
+        <v>46297.55208333334</v>
       </c>
       <c r="B151">
-        <v>0.287</v>
+        <v>0</v>
       </c>
       <c r="C151">
-        <v>0.21</v>
+        <v>3.115</v>
       </c>
       <c r="D151">
         <v>0</v>
@@ -4738,19 +4738,19 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46294.5625</v>
+        <v>46297.5625</v>
       </c>
       <c r="B152">
-        <v>0.139</v>
+        <v>0</v>
       </c>
       <c r="C152">
-        <v>1.117</v>
+        <v>20.608</v>
       </c>
       <c r="D152">
         <v>0</v>
       </c>
       <c r="E152">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="F152">
         <v>55</v>
@@ -4761,19 +4761,19 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46294.57291666666</v>
+        <v>46297.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
       </c>
       <c r="C153">
-        <v>9.099</v>
+        <v>26.646</v>
       </c>
       <c r="D153">
         <v>0</v>
       </c>
       <c r="E153">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="F153">
         <v>56</v>
@@ -4784,19 +4784,19 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46294.58333333334</v>
+        <v>46297.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
       </c>
       <c r="C154">
-        <v>36.027</v>
+        <v>26.479</v>
       </c>
       <c r="D154">
         <v>0</v>
       </c>
       <c r="E154">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="F154">
         <v>57</v>
@@ -4807,13 +4807,13 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46294.59375</v>
+        <v>46297.59375</v>
       </c>
       <c r="B155">
-        <v>0.198</v>
+        <v>0.289</v>
       </c>
       <c r="C155">
-        <v>0.909</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="D155">
         <v>0</v>
@@ -4830,19 +4830,19 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46294.60416666666</v>
+        <v>46297.60416666666</v>
       </c>
       <c r="B156">
-        <v>0.079</v>
+        <v>0.286</v>
       </c>
       <c r="C156">
-        <v>1.991</v>
+        <v>0.41</v>
       </c>
       <c r="D156">
         <v>0</v>
       </c>
       <c r="E156">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="F156">
         <v>59</v>
@@ -4853,19 +4853,19 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46294.61458333334</v>
+        <v>46297.61458333334</v>
       </c>
       <c r="B157">
-        <v>0.052</v>
+        <v>0.603</v>
       </c>
       <c r="C157">
-        <v>3.015</v>
+        <v>0.143</v>
       </c>
       <c r="D157">
         <v>0</v>
       </c>
       <c r="E157">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="F157">
         <v>60</v>
@@ -4876,19 +4876,19 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46294.625</v>
+        <v>46297.625</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="C158">
-        <v>25.56</v>
+        <v>4.538</v>
       </c>
       <c r="D158">
         <v>0</v>
       </c>
       <c r="E158">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="F158">
         <v>61</v>
@@ -4899,19 +4899,19 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46294.63541666666</v>
+        <v>46297.63541666666</v>
       </c>
       <c r="B159">
-        <v>0.039</v>
+        <v>9.832000000000001</v>
       </c>
       <c r="C159">
-        <v>3.163</v>
+        <v>0.488</v>
       </c>
       <c r="D159">
         <v>0</v>
       </c>
       <c r="E159">
-        <v>37.5</v>
+        <v>62.5</v>
       </c>
       <c r="F159">
         <v>62</v>
@@ -4922,19 +4922,19 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46294.64583333334</v>
+        <v>46297.64583333334</v>
       </c>
       <c r="B160">
-        <v>0.06</v>
+        <v>29.014</v>
       </c>
       <c r="C160">
-        <v>5.256</v>
+        <v>0</v>
       </c>
       <c r="D160">
         <v>0</v>
       </c>
       <c r="E160">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="F160">
         <v>63</v>
@@ -4945,19 +4945,19 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46294.65625</v>
+        <v>46297.65625</v>
       </c>
       <c r="B161">
-        <v>7.34</v>
+        <v>17.966</v>
       </c>
       <c r="C161">
-        <v>0.08599999999999999</v>
+        <v>0</v>
       </c>
       <c r="D161">
         <v>0</v>
       </c>
       <c r="E161">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="F161">
         <v>64</v>
@@ -4968,19 +4968,19 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46294.66666666666</v>
+        <v>46297.66666666666</v>
       </c>
       <c r="B162">
-        <v>6.648</v>
+        <v>0.208</v>
       </c>
       <c r="C162">
-        <v>0.001</v>
+        <v>5.174</v>
       </c>
       <c r="D162">
         <v>0</v>
       </c>
       <c r="E162">
-        <v>25</v>
+        <v>67.5</v>
       </c>
       <c r="F162">
         <v>65</v>
@@ -4991,19 +4991,19 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46294.67708333334</v>
+        <v>46297.67708333334</v>
       </c>
       <c r="B163">
-        <v>25.675</v>
+        <v>15.355</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="D163">
         <v>0</v>
       </c>
       <c r="E163">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="F163">
         <v>66</v>
@@ -5014,10 +5014,10 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46294.6875</v>
+        <v>46297.6875</v>
       </c>
       <c r="B164">
-        <v>58.554</v>
+        <v>29.101</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -5026,7 +5026,7 @@
         <v>0</v>
       </c>
       <c r="E164">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F164">
         <v>67</v>
@@ -5037,19 +5037,19 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46294.69791666666</v>
+        <v>46297.69791666666</v>
       </c>
       <c r="B165">
-        <v>49.225</v>
+        <v>31.287</v>
       </c>
       <c r="C165">
         <v>0</v>
       </c>
       <c r="D165">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E165">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F165">
         <v>68</v>
@@ -5060,19 +5060,19 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46294.70833333334</v>
+        <v>46297.70833333334</v>
       </c>
       <c r="B166">
-        <v>24.331</v>
+        <v>5.239</v>
       </c>
       <c r="C166">
         <v>0</v>
       </c>
       <c r="D166">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="E166">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F166">
         <v>69</v>
@@ -5083,16 +5083,16 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46294.71875</v>
+        <v>46297.71875</v>
       </c>
       <c r="B167">
-        <v>52.827</v>
+        <v>11.691</v>
       </c>
       <c r="C167">
         <v>0</v>
       </c>
       <c r="D167">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -5106,16 +5106,16 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46294.72916666666</v>
+        <v>46297.72916666666</v>
       </c>
       <c r="B168">
-        <v>35.685</v>
+        <v>3.369</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>0.433</v>
       </c>
       <c r="D168">
-        <v>112.5</v>
+        <v>0</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -5129,16 +5129,16 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46294.73958333334</v>
+        <v>46297.73958333334</v>
       </c>
       <c r="B169">
-        <v>12.204</v>
+        <v>4.853</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="D169">
-        <v>149.75</v>
+        <v>0</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -5152,16 +5152,16 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46294.75</v>
+        <v>46297.75</v>
       </c>
       <c r="B170">
-        <v>0.167</v>
+        <v>0.137</v>
       </c>
       <c r="C170">
-        <v>0.706</v>
+        <v>0.755</v>
       </c>
       <c r="D170">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -5175,16 +5175,16 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46294.76041666666</v>
+        <v>46297.76041666666</v>
       </c>
       <c r="B171">
-        <v>0.204</v>
+        <v>0.033</v>
       </c>
       <c r="C171">
-        <v>0.224</v>
+        <v>3.057</v>
       </c>
       <c r="D171">
-        <v>137.5</v>
+        <v>0</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -5198,19 +5198,19 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46294.77083333334</v>
+        <v>46297.77083333334</v>
       </c>
       <c r="B172">
-        <v>0.011</v>
+        <v>0.121</v>
       </c>
       <c r="C172">
-        <v>10.318</v>
+        <v>1.504</v>
       </c>
       <c r="D172">
-        <v>137.5</v>
+        <v>0</v>
       </c>
       <c r="E172">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F172">
         <v>75</v>
@@ -5221,19 +5221,19 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46294.78125</v>
+        <v>46297.78125</v>
       </c>
       <c r="B173">
-        <v>0.307</v>
+        <v>0.108</v>
       </c>
       <c r="C173">
-        <v>0.291</v>
+        <v>0.615</v>
       </c>
       <c r="D173">
-        <v>137.5</v>
+        <v>0</v>
       </c>
       <c r="E173">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F173">
         <v>76</v>
@@ -5244,19 +5244,19 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46294.79166666666</v>
+        <v>46297.79166666666</v>
       </c>
       <c r="B174">
-        <v>0.481</v>
+        <v>0.258</v>
       </c>
       <c r="C174">
-        <v>0.134</v>
+        <v>0.034</v>
       </c>
       <c r="D174">
-        <v>112.5</v>
+        <v>0</v>
       </c>
       <c r="E174">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F174">
         <v>77</v>
@@ -5267,19 +5267,19 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46294.80208333334</v>
+        <v>46297.80208333334</v>
       </c>
       <c r="B175">
-        <v>0.021</v>
+        <v>5.931</v>
       </c>
       <c r="C175">
-        <v>15.325</v>
+        <v>0</v>
       </c>
       <c r="D175">
-        <v>112.5</v>
+        <v>0</v>
       </c>
       <c r="E175">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F175">
         <v>78</v>
@@ -5290,19 +5290,19 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46294.8125</v>
+        <v>46297.8125</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>0.544</v>
       </c>
       <c r="C176">
-        <v>17.841</v>
+        <v>0.008</v>
       </c>
       <c r="D176">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="E176">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F176">
         <v>79</v>
@@ -5313,19 +5313,19 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46294.82291666666</v>
+        <v>46297.82291666666</v>
       </c>
       <c r="B177">
-        <v>0</v>
+        <v>5.485</v>
       </c>
       <c r="C177">
-        <v>29.014</v>
+        <v>0</v>
       </c>
       <c r="D177">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="E177">
-        <v>0</v>
+        <v>40.25</v>
       </c>
       <c r="F177">
         <v>80</v>
@@ -5336,19 +5336,19 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46294.83333333334</v>
+        <v>46297.83333333334</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>15.646</v>
       </c>
       <c r="C178">
-        <v>9.618</v>
+        <v>0</v>
       </c>
       <c r="D178">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E178">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F178">
         <v>81</v>
@@ -5359,19 +5359,19 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46294.84375</v>
+        <v>46297.84375</v>
       </c>
       <c r="B179">
-        <v>0.27</v>
+        <v>18.312</v>
       </c>
       <c r="C179">
-        <v>0.403</v>
+        <v>0</v>
       </c>
       <c r="D179">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E179">
-        <v>0</v>
+        <v>46.25</v>
       </c>
       <c r="F179">
         <v>82</v>
@@ -5382,19 +5382,19 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46294.85416666666</v>
+        <v>46297.85416666666</v>
       </c>
       <c r="B180">
-        <v>0.496</v>
+        <v>14.229</v>
       </c>
       <c r="C180">
-        <v>0.719</v>
+        <v>0</v>
       </c>
       <c r="D180">
         <v>0</v>
       </c>
       <c r="E180">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F180">
         <v>83</v>
@@ -5405,13 +5405,13 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46294.86458333334</v>
+        <v>46297.86458333334</v>
       </c>
       <c r="B181">
-        <v>0</v>
+        <v>4.566</v>
       </c>
       <c r="C181">
-        <v>28.929</v>
+        <v>0.012</v>
       </c>
       <c r="D181">
         <v>0</v>
@@ -5428,13 +5428,13 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46294.875</v>
+        <v>46297.875</v>
       </c>
       <c r="B182">
-        <v>0</v>
+        <v>1.866</v>
       </c>
       <c r="C182">
-        <v>29.413</v>
+        <v>0.028</v>
       </c>
       <c r="D182">
         <v>0</v>
@@ -5451,13 +5451,13 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46294.88541666666</v>
+        <v>46297.88541666666</v>
       </c>
       <c r="B183">
-        <v>0</v>
+        <v>1.398</v>
       </c>
       <c r="C183">
-        <v>39.81</v>
+        <v>0.029</v>
       </c>
       <c r="D183">
         <v>0</v>
@@ -5474,13 +5474,13 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46294.89583333334</v>
+        <v>46297.89583333334</v>
       </c>
       <c r="B184">
-        <v>0</v>
+        <v>3.032</v>
       </c>
       <c r="C184">
-        <v>49.156</v>
+        <v>0.01</v>
       </c>
       <c r="D184">
         <v>0</v>
@@ -5497,19 +5497,19 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46294.90625</v>
+        <v>46297.90625</v>
       </c>
       <c r="B185">
-        <v>0</v>
+        <v>0.164</v>
       </c>
       <c r="C185">
-        <v>23.795</v>
+        <v>5.741</v>
       </c>
       <c r="D185">
         <v>0</v>
       </c>
       <c r="E185">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F185">
         <v>88</v>
@@ -5520,19 +5520,19 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46294.91666666666</v>
+        <v>46297.91666666666</v>
       </c>
       <c r="B186">
-        <v>0</v>
+        <v>4.634</v>
       </c>
       <c r="C186">
-        <v>8.31</v>
+        <v>5.511</v>
       </c>
       <c r="D186">
         <v>0</v>
       </c>
       <c r="E186">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F186">
         <v>89</v>
@@ -5543,19 +5543,19 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46294.92708333334</v>
+        <v>46297.92708333334</v>
       </c>
       <c r="B187">
-        <v>1.015</v>
+        <v>11.874</v>
       </c>
       <c r="C187">
-        <v>0.857</v>
+        <v>0.017</v>
       </c>
       <c r="D187">
         <v>0</v>
       </c>
       <c r="E187">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F187">
         <v>90</v>
@@ -5566,19 +5566,19 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46294.9375</v>
+        <v>46297.9375</v>
       </c>
       <c r="B188">
-        <v>0.218</v>
+        <v>0.586</v>
       </c>
       <c r="C188">
-        <v>3.275</v>
+        <v>0.178</v>
       </c>
       <c r="D188">
         <v>0</v>
       </c>
       <c r="E188">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F188">
         <v>91</v>
@@ -5589,19 +5589,19 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46294.94791666666</v>
+        <v>46297.94791666666</v>
       </c>
       <c r="B189">
-        <v>0.332</v>
+        <v>1.365</v>
       </c>
       <c r="C189">
-        <v>1.341</v>
+        <v>0.224</v>
       </c>
       <c r="D189">
         <v>0</v>
       </c>
       <c r="E189">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F189">
         <v>92</v>
@@ -5612,19 +5612,19 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46294.95833333334</v>
+        <v>46297.95833333334</v>
       </c>
       <c r="B190">
-        <v>0.02</v>
+        <v>5.319</v>
       </c>
       <c r="C190">
-        <v>0.382</v>
+        <v>0</v>
       </c>
       <c r="D190">
         <v>0</v>
       </c>
       <c r="E190">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F190">
         <v>93</v>
@@ -5635,19 +5635,19 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46294.96875</v>
+        <v>46297.96875</v>
       </c>
       <c r="B191">
-        <v>0.048</v>
+        <v>3.109</v>
       </c>
       <c r="C191">
-        <v>2.212</v>
+        <v>0</v>
       </c>
       <c r="D191">
         <v>0</v>
       </c>
       <c r="E191">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F191">
         <v>94</v>
@@ -5658,19 +5658,19 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46294.97916666666</v>
+        <v>46297.97916666666</v>
       </c>
       <c r="B192">
-        <v>0.02</v>
+        <v>1.459</v>
       </c>
       <c r="C192">
-        <v>2.072</v>
+        <v>0.305</v>
       </c>
       <c r="D192">
         <v>0</v>
       </c>
       <c r="E192">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F192">
         <v>95</v>
@@ -5681,19 +5681,19 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46294.98958333334</v>
+        <v>46297.98958333334</v>
       </c>
       <c r="B193">
-        <v>1.788</v>
+        <v>2.143</v>
       </c>
       <c r="C193">
-        <v>0.014</v>
+        <v>2.379</v>
       </c>
       <c r="D193">
         <v>0</v>
       </c>
       <c r="E193">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F193">
         <v>96</v>
@@ -5704,13 +5704,13 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194" s="2">
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="B194">
-        <v>0.07099999999999999</v>
+        <v>0.314</v>
       </c>
       <c r="C194">
-        <v>0.966</v>
+        <v>2.846</v>
       </c>
       <c r="D194">
         <v>0</v>
@@ -5727,13 +5727,13 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195" s="2">
-        <v>46295.01041666666</v>
+        <v>46298.01041666666</v>
       </c>
       <c r="B195">
-        <v>0.8080000000000001</v>
+        <v>5.059</v>
       </c>
       <c r="C195">
-        <v>0.138</v>
+        <v>0</v>
       </c>
       <c r="D195">
         <v>0</v>
@@ -5750,13 +5750,13 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196" s="2">
-        <v>46295.02083333334</v>
+        <v>46298.02083333334</v>
       </c>
       <c r="B196">
-        <v>9.300000000000001</v>
+        <v>1.179</v>
       </c>
       <c r="C196">
-        <v>0</v>
+        <v>0.113</v>
       </c>
       <c r="D196">
         <v>0</v>
@@ -5773,13 +5773,13 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197" s="2">
-        <v>46295.03125</v>
+        <v>46298.03125</v>
       </c>
       <c r="B197">
-        <v>0.628</v>
+        <v>0.572</v>
       </c>
       <c r="C197">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="D197">
         <v>0</v>
@@ -5796,10 +5796,10 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198" s="2">
-        <v>46295.04166666666</v>
+        <v>46298.04166666666</v>
       </c>
       <c r="B198">
-        <v>13.702</v>
+        <v>5.326</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -5819,13 +5819,13 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199" s="2">
-        <v>46295.05208333334</v>
+        <v>46298.05208333334</v>
       </c>
       <c r="B199">
-        <v>1.148</v>
+        <v>10.019</v>
       </c>
       <c r="C199">
-        <v>0.149</v>
+        <v>0</v>
       </c>
       <c r="D199">
         <v>0</v>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200" s="2">
-        <v>46295.0625</v>
+        <v>46298.0625</v>
       </c>
       <c r="B200">
-        <v>8.086</v>
+        <v>8.893000000000001</v>
       </c>
       <c r="C200">
         <v>0</v>
@@ -5865,16 +5865,16 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201" s="2">
-        <v>46295.07291666666</v>
+        <v>46298.07291666666</v>
       </c>
       <c r="B201">
-        <v>8.629</v>
+        <v>0.145</v>
       </c>
       <c r="C201">
-        <v>0</v>
+        <v>3.152</v>
       </c>
       <c r="D201">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E201">
         <v>0</v>
@@ -5888,16 +5888,16 @@
     </row>
     <row r="202" spans="1:7">
       <c r="A202" s="2">
-        <v>46295.08333333334</v>
+        <v>46298.08333333334</v>
       </c>
       <c r="B202">
-        <v>20.576</v>
+        <v>9.189</v>
       </c>
       <c r="C202">
-        <v>0.019</v>
+        <v>0.291</v>
       </c>
       <c r="D202">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -5911,16 +5911,16 @@
     </row>
     <row r="203" spans="1:7">
       <c r="A203" s="2">
-        <v>46295.09375</v>
+        <v>46298.09375</v>
       </c>
       <c r="B203">
-        <v>0.992</v>
+        <v>17.425</v>
       </c>
       <c r="C203">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="D203">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E203">
         <v>0</v>
@@ -5934,16 +5934,16 @@
     </row>
     <row r="204" spans="1:7">
       <c r="A204" s="2">
-        <v>46295.10416666666</v>
+        <v>46298.10416666666</v>
       </c>
       <c r="B204">
-        <v>4.989</v>
+        <v>10.113</v>
       </c>
       <c r="C204">
-        <v>0.007</v>
+        <v>1.327</v>
       </c>
       <c r="D204">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -5957,16 +5957,16 @@
     </row>
     <row r="205" spans="1:7">
       <c r="A205" s="2">
-        <v>46295.11458333334</v>
+        <v>46298.11458333334</v>
       </c>
       <c r="B205">
-        <v>15.289</v>
+        <v>0</v>
       </c>
       <c r="C205">
-        <v>0</v>
+        <v>5.623</v>
       </c>
       <c r="D205">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E205">
         <v>0</v>
@@ -5980,16 +5980,16 @@
     </row>
     <row r="206" spans="1:7">
       <c r="A206" s="2">
-        <v>46295.125</v>
+        <v>46298.125</v>
       </c>
       <c r="B206">
-        <v>7.071</v>
+        <v>13.578</v>
       </c>
       <c r="C206">
-        <v>0.006</v>
+        <v>0.645</v>
       </c>
       <c r="D206">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -6003,16 +6003,16 @@
     </row>
     <row r="207" spans="1:7">
       <c r="A207" s="2">
-        <v>46295.13541666666</v>
+        <v>46298.13541666666</v>
       </c>
       <c r="B207">
-        <v>0.265</v>
+        <v>36.352</v>
       </c>
       <c r="C207">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="D207">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E207">
         <v>0</v>
@@ -6026,16 +6026,16 @@
     </row>
     <row r="208" spans="1:7">
       <c r="A208" s="2">
-        <v>46295.14583333334</v>
+        <v>46298.14583333334</v>
       </c>
       <c r="B208">
-        <v>15.285</v>
+        <v>38.244</v>
       </c>
       <c r="C208">
         <v>0</v>
       </c>
       <c r="D208">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -6049,10 +6049,10 @@
     </row>
     <row r="209" spans="1:7">
       <c r="A209" s="2">
-        <v>46295.15625</v>
+        <v>46298.15625</v>
       </c>
       <c r="B209">
-        <v>23.208</v>
+        <v>23.005</v>
       </c>
       <c r="C209">
         <v>0</v>
@@ -6072,13 +6072,13 @@
     </row>
     <row r="210" spans="1:7">
       <c r="A210" s="2">
-        <v>46295.16666666666</v>
+        <v>46298.16666666666</v>
       </c>
       <c r="B210">
-        <v>27.129</v>
+        <v>23.229</v>
       </c>
       <c r="C210">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="D210">
         <v>0</v>
@@ -6095,16 +6095,16 @@
     </row>
     <row r="211" spans="1:7">
       <c r="A211" s="2">
-        <v>46295.17708333334</v>
+        <v>46298.17708333334</v>
       </c>
       <c r="B211">
-        <v>14.813</v>
+        <v>7.019</v>
       </c>
       <c r="C211">
-        <v>0</v>
+        <v>0.326</v>
       </c>
       <c r="D211">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -6118,16 +6118,16 @@
     </row>
     <row r="212" spans="1:7">
       <c r="A212" s="2">
-        <v>46295.1875</v>
+        <v>46298.1875</v>
       </c>
       <c r="B212">
-        <v>34.028</v>
+        <v>2.4</v>
       </c>
       <c r="C212">
-        <v>0</v>
+        <v>0.434</v>
       </c>
       <c r="D212">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E212">
         <v>0</v>
@@ -6141,16 +6141,16 @@
     </row>
     <row r="213" spans="1:7">
       <c r="A213" s="2">
-        <v>46295.19791666666</v>
+        <v>46298.19791666666</v>
       </c>
       <c r="B213">
-        <v>18.562</v>
+        <v>13.151</v>
       </c>
       <c r="C213">
         <v>0</v>
       </c>
       <c r="D213">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -6164,16 +6164,16 @@
     </row>
     <row r="214" spans="1:7">
       <c r="A214" s="2">
-        <v>46295.20833333334</v>
+        <v>46298.20833333334</v>
       </c>
       <c r="B214">
-        <v>1.749</v>
+        <v>8.101000000000001</v>
       </c>
       <c r="C214">
-        <v>0.076</v>
+        <v>0</v>
       </c>
       <c r="D214">
-        <v>0</v>
+        <v>21.75</v>
       </c>
       <c r="E214">
         <v>0</v>
@@ -6187,16 +6187,16 @@
     </row>
     <row r="215" spans="1:7">
       <c r="A215" s="2">
-        <v>46295.21875</v>
+        <v>46298.21875</v>
       </c>
       <c r="B215">
-        <v>2.847</v>
+        <v>2.207</v>
       </c>
       <c r="C215">
-        <v>0.228</v>
+        <v>0.008</v>
       </c>
       <c r="D215">
-        <v>0</v>
+        <v>21.75</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -6210,16 +6210,16 @@
     </row>
     <row r="216" spans="1:7">
       <c r="A216" s="2">
-        <v>46295.22916666666</v>
+        <v>46298.22916666666</v>
       </c>
       <c r="B216">
-        <v>14.873</v>
+        <v>0.089</v>
       </c>
       <c r="C216">
-        <v>0</v>
+        <v>1.051</v>
       </c>
       <c r="D216">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -6233,16 +6233,16 @@
     </row>
     <row r="217" spans="1:7">
       <c r="A217" s="2">
-        <v>46295.23958333334</v>
+        <v>46298.23958333334</v>
       </c>
       <c r="B217">
-        <v>39.745</v>
+        <v>0.062</v>
       </c>
       <c r="C217">
-        <v>0</v>
+        <v>2.089</v>
       </c>
       <c r="D217">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -6256,13 +6256,13 @@
     </row>
     <row r="218" spans="1:7">
       <c r="A218" s="2">
-        <v>46295.25</v>
+        <v>46298.25</v>
       </c>
       <c r="B218">
-        <v>32.877</v>
+        <v>13.046</v>
       </c>
       <c r="C218">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="D218">
         <v>0</v>
@@ -6279,10 +6279,10 @@
     </row>
     <row r="219" spans="1:7">
       <c r="A219" s="2">
-        <v>46295.26041666666</v>
+        <v>46298.26041666666</v>
       </c>
       <c r="B219">
-        <v>37.296</v>
+        <v>8.926</v>
       </c>
       <c r="C219">
         <v>0</v>
@@ -6302,10 +6302,10 @@
     </row>
     <row r="220" spans="1:7">
       <c r="A220" s="2">
-        <v>46295.27083333334</v>
+        <v>46298.27083333334</v>
       </c>
       <c r="B220">
-        <v>30.171</v>
+        <v>13.632</v>
       </c>
       <c r="C220">
         <v>0</v>
@@ -6325,10 +6325,10 @@
     </row>
     <row r="221" spans="1:7">
       <c r="A221" s="2">
-        <v>46295.28125</v>
+        <v>46298.28125</v>
       </c>
       <c r="B221">
-        <v>20.06</v>
+        <v>9.483000000000001</v>
       </c>
       <c r="C221">
         <v>0</v>
@@ -6348,13 +6348,13 @@
     </row>
     <row r="222" spans="1:7">
       <c r="A222" s="2">
-        <v>46295.29166666666</v>
+        <v>46298.29166666666</v>
       </c>
       <c r="B222">
-        <v>70.15300000000001</v>
+        <v>0.85</v>
       </c>
       <c r="C222">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="D222">
         <v>0</v>
@@ -6371,16 +6371,16 @@
     </row>
     <row r="223" spans="1:7">
       <c r="A223" s="2">
-        <v>46295.30208333334</v>
+        <v>46298.30208333334</v>
       </c>
       <c r="B223">
-        <v>74.622</v>
+        <v>0.274</v>
       </c>
       <c r="C223">
-        <v>0</v>
+        <v>2.538</v>
       </c>
       <c r="D223">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -6394,16 +6394,16 @@
     </row>
     <row r="224" spans="1:7">
       <c r="A224" s="2">
-        <v>46295.3125</v>
+        <v>46298.3125</v>
       </c>
       <c r="B224">
-        <v>50.288</v>
+        <v>0</v>
       </c>
       <c r="C224">
-        <v>0</v>
+        <v>20.359</v>
       </c>
       <c r="D224">
-        <v>49.5</v>
+        <v>0</v>
       </c>
       <c r="E224">
         <v>0</v>
@@ -6417,16 +6417,16 @@
     </row>
     <row r="225" spans="1:7">
       <c r="A225" s="2">
-        <v>46295.32291666666</v>
+        <v>46298.32291666666</v>
       </c>
       <c r="B225">
-        <v>72.751</v>
+        <v>0</v>
       </c>
       <c r="C225">
-        <v>0</v>
+        <v>27.733</v>
       </c>
       <c r="D225">
-        <v>49.5</v>
+        <v>0</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -6440,16 +6440,16 @@
     </row>
     <row r="226" spans="1:7">
       <c r="A226" s="2">
-        <v>46295.33333333334</v>
+        <v>46298.33333333334</v>
       </c>
       <c r="B226">
-        <v>25.758</v>
+        <v>0.054</v>
       </c>
       <c r="C226">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="D226">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -6463,16 +6463,16 @@
     </row>
     <row r="227" spans="1:7">
       <c r="A227" s="2">
-        <v>46295.34375</v>
+        <v>46298.34375</v>
       </c>
       <c r="B227">
-        <v>6.036</v>
+        <v>0</v>
       </c>
       <c r="C227">
-        <v>0.078</v>
+        <v>0</v>
       </c>
       <c r="D227">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="E227">
         <v>0</v>
@@ -6486,16 +6486,16 @@
     </row>
     <row r="228" spans="1:7">
       <c r="A228" s="2">
-        <v>46295.35416666666</v>
+        <v>46298.35416666666</v>
       </c>
       <c r="B228">
-        <v>20.556</v>
+        <v>0</v>
       </c>
       <c r="C228">
         <v>0</v>
       </c>
       <c r="D228">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="E228">
         <v>0</v>
@@ -6509,16 +6509,16 @@
     </row>
     <row r="229" spans="1:7">
       <c r="A229" s="2">
-        <v>46295.36458333334</v>
+        <v>46298.36458333334</v>
       </c>
       <c r="B229">
-        <v>6.576</v>
+        <v>0</v>
       </c>
       <c r="C229">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="D229">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="E229">
         <v>0</v>
@@ -6532,16 +6532,16 @@
     </row>
     <row r="230" spans="1:7">
       <c r="A230" s="2">
-        <v>46295.375</v>
+        <v>46298.375</v>
       </c>
       <c r="B230">
-        <v>29.441</v>
+        <v>0</v>
       </c>
       <c r="C230">
         <v>0</v>
       </c>
       <c r="D230">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -6555,16 +6555,16 @@
     </row>
     <row r="231" spans="1:7">
       <c r="A231" s="2">
-        <v>46295.38541666666</v>
+        <v>46298.38541666666</v>
       </c>
       <c r="B231">
-        <v>0.758</v>
+        <v>0</v>
       </c>
       <c r="C231">
-        <v>21.517</v>
+        <v>0</v>
       </c>
       <c r="D231">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="E231">
         <v>0</v>
@@ -6578,16 +6578,16 @@
     </row>
     <row r="232" spans="1:7">
       <c r="A232" s="2">
-        <v>46295.39583333334</v>
+        <v>46298.39583333334</v>
       </c>
       <c r="B232">
         <v>0</v>
       </c>
       <c r="C232">
-        <v>50.827</v>
+        <v>0</v>
       </c>
       <c r="D232">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -6601,7 +6601,7 @@
     </row>
     <row r="233" spans="1:7">
       <c r="A233" s="2">
-        <v>46295.40625</v>
+        <v>46298.40625</v>
       </c>
       <c r="B233">
         <v>0</v>
@@ -6610,7 +6610,7 @@
         <v>0</v>
       </c>
       <c r="D233">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -6624,7 +6624,7 @@
     </row>
     <row r="234" spans="1:7">
       <c r="A234" s="2">
-        <v>46295.41666666666</v>
+        <v>46298.41666666666</v>
       </c>
       <c r="B234">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="D234">
-        <v>16.25</v>
+        <v>0</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -6647,7 +6647,7 @@
     </row>
     <row r="235" spans="1:7">
       <c r="A235" s="2">
-        <v>46295.42708333334</v>
+        <v>46298.42708333334</v>
       </c>
       <c r="B235">
         <v>0</v>
@@ -6670,7 +6670,7 @@
     </row>
     <row r="236" spans="1:7">
       <c r="A236" s="2">
-        <v>46295.4375</v>
+        <v>46298.4375</v>
       </c>
       <c r="B236">
         <v>0</v>
@@ -6693,7 +6693,7 @@
     </row>
     <row r="237" spans="1:7">
       <c r="A237" s="2">
-        <v>46295.44791666666</v>
+        <v>46298.44791666666</v>
       </c>
       <c r="B237">
         <v>0</v>
@@ -6716,7 +6716,7 @@
     </row>
     <row r="238" spans="1:7">
       <c r="A238" s="2">
-        <v>46295.45833333334</v>
+        <v>46298.45833333334</v>
       </c>
       <c r="B238">
         <v>0</v>
@@ -6739,7 +6739,7 @@
     </row>
     <row r="239" spans="1:7">
       <c r="A239" s="2">
-        <v>46295.46875</v>
+        <v>46298.46875</v>
       </c>
       <c r="B239">
         <v>0</v>
@@ -6762,7 +6762,7 @@
     </row>
     <row r="240" spans="1:7">
       <c r="A240" s="2">
-        <v>46295.47916666666</v>
+        <v>46298.47916666666</v>
       </c>
       <c r="B240">
         <v>0</v>
@@ -6785,7 +6785,7 @@
     </row>
     <row r="241" spans="1:7">
       <c r="A241" s="2">
-        <v>46295.48958333334</v>
+        <v>46298.48958333334</v>
       </c>
       <c r="B241">
         <v>0</v>
@@ -6808,7 +6808,7 @@
     </row>
     <row r="242" spans="1:7">
       <c r="A242" s="2">
-        <v>46295.5</v>
+        <v>46298.5</v>
       </c>
       <c r="B242">
         <v>0</v>
@@ -6831,7 +6831,7 @@
     </row>
     <row r="243" spans="1:7">
       <c r="A243" s="2">
-        <v>46295.51041666666</v>
+        <v>46298.51041666666</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -6854,7 +6854,7 @@
     </row>
     <row r="244" spans="1:7">
       <c r="A244" s="2">
-        <v>46295.52083333334</v>
+        <v>46298.52083333334</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -6877,7 +6877,7 @@
     </row>
     <row r="245" spans="1:7">
       <c r="A245" s="2">
-        <v>46295.53125</v>
+        <v>46298.53125</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -6900,7 +6900,7 @@
     </row>
     <row r="246" spans="1:7">
       <c r="A246" s="2">
-        <v>46295.54166666666</v>
+        <v>46298.54166666666</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -6923,7 +6923,7 @@
     </row>
     <row r="247" spans="1:7">
       <c r="A247" s="2">
-        <v>46295.55208333334</v>
+        <v>46298.55208333334</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -6946,7 +6946,7 @@
     </row>
     <row r="248" spans="1:7">
       <c r="A248" s="2">
-        <v>46295.5625</v>
+        <v>46298.5625</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -6969,7 +6969,7 @@
     </row>
     <row r="249" spans="1:7">
       <c r="A249" s="2">
-        <v>46295.57291666666</v>
+        <v>46298.57291666666</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -6992,7 +6992,7 @@
     </row>
     <row r="250" spans="1:7">
       <c r="A250" s="2">
-        <v>46295.58333333334</v>
+        <v>46298.58333333334</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -7015,7 +7015,7 @@
     </row>
     <row r="251" spans="1:7">
       <c r="A251" s="2">
-        <v>46295.59375</v>
+        <v>46298.59375</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -7038,7 +7038,7 @@
     </row>
     <row r="252" spans="1:7">
       <c r="A252" s="2">
-        <v>46295.60416666666</v>
+        <v>46298.60416666666</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -7061,7 +7061,7 @@
     </row>
     <row r="253" spans="1:7">
       <c r="A253" s="2">
-        <v>46295.61458333334</v>
+        <v>46298.61458333334</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -7084,7 +7084,7 @@
     </row>
     <row r="254" spans="1:7">
       <c r="A254" s="2">
-        <v>46295.625</v>
+        <v>46298.625</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -7107,7 +7107,7 @@
     </row>
     <row r="255" spans="1:7">
       <c r="A255" s="2">
-        <v>46295.63541666666</v>
+        <v>46298.63541666666</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -7130,7 +7130,7 @@
     </row>
     <row r="256" spans="1:7">
       <c r="A256" s="2">
-        <v>46295.64583333334</v>
+        <v>46298.64583333334</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -7153,7 +7153,7 @@
     </row>
     <row r="257" spans="1:7">
       <c r="A257" s="2">
-        <v>46295.65625</v>
+        <v>46298.65625</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -7176,7 +7176,7 @@
     </row>
     <row r="258" spans="1:7">
       <c r="A258" s="2">
-        <v>46295.66666666666</v>
+        <v>46298.66666666666</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -7199,7 +7199,7 @@
     </row>
     <row r="259" spans="1:7">
       <c r="A259" s="2">
-        <v>46295.67708333334</v>
+        <v>46298.67708333334</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -7222,7 +7222,7 @@
     </row>
     <row r="260" spans="1:7">
       <c r="A260" s="2">
-        <v>46295.6875</v>
+        <v>46298.6875</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -7245,7 +7245,7 @@
     </row>
     <row r="261" spans="1:7">
       <c r="A261" s="2">
-        <v>46295.69791666666</v>
+        <v>46298.69791666666</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -7268,7 +7268,7 @@
     </row>
     <row r="262" spans="1:7">
       <c r="A262" s="2">
-        <v>46295.70833333334</v>
+        <v>46298.70833333334</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -7291,7 +7291,7 @@
     </row>
     <row r="263" spans="1:7">
       <c r="A263" s="2">
-        <v>46295.71875</v>
+        <v>46298.71875</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -7314,7 +7314,7 @@
     </row>
     <row r="264" spans="1:7">
       <c r="A264" s="2">
-        <v>46295.72916666666</v>
+        <v>46298.72916666666</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -7337,7 +7337,7 @@
     </row>
     <row r="265" spans="1:7">
       <c r="A265" s="2">
-        <v>46295.73958333334</v>
+        <v>46298.73958333334</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -7360,7 +7360,7 @@
     </row>
     <row r="266" spans="1:7">
       <c r="A266" s="2">
-        <v>46295.75</v>
+        <v>46298.75</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -7383,7 +7383,7 @@
     </row>
     <row r="267" spans="1:7">
       <c r="A267" s="2">
-        <v>46295.76041666666</v>
+        <v>46298.76041666666</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -7406,7 +7406,7 @@
     </row>
     <row r="268" spans="1:7">
       <c r="A268" s="2">
-        <v>46295.77083333334</v>
+        <v>46298.77083333334</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -7429,7 +7429,7 @@
     </row>
     <row r="269" spans="1:7">
       <c r="A269" s="2">
-        <v>46295.78125</v>
+        <v>46298.78125</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -7452,7 +7452,7 @@
     </row>
     <row r="270" spans="1:7">
       <c r="A270" s="2">
-        <v>46295.79166666666</v>
+        <v>46298.79166666666</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -7475,7 +7475,7 @@
     </row>
     <row r="271" spans="1:7">
       <c r="A271" s="2">
-        <v>46295.80208333334</v>
+        <v>46298.80208333334</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -7498,7 +7498,7 @@
     </row>
     <row r="272" spans="1:7">
       <c r="A272" s="2">
-        <v>46295.8125</v>
+        <v>46298.8125</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -7521,7 +7521,7 @@
     </row>
     <row r="273" spans="1:7">
       <c r="A273" s="2">
-        <v>46295.82291666666</v>
+        <v>46298.82291666666</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -7544,7 +7544,7 @@
     </row>
     <row r="274" spans="1:7">
       <c r="A274" s="2">
-        <v>46295.83333333334</v>
+        <v>46298.83333333334</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -7567,7 +7567,7 @@
     </row>
     <row r="275" spans="1:7">
       <c r="A275" s="2">
-        <v>46295.84375</v>
+        <v>46298.84375</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -7590,7 +7590,7 @@
     </row>
     <row r="276" spans="1:7">
       <c r="A276" s="2">
-        <v>46295.85416666666</v>
+        <v>46298.85416666666</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -7613,7 +7613,7 @@
     </row>
     <row r="277" spans="1:7">
       <c r="A277" s="2">
-        <v>46295.86458333334</v>
+        <v>46298.86458333334</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -7636,7 +7636,7 @@
     </row>
     <row r="278" spans="1:7">
       <c r="A278" s="2">
-        <v>46295.875</v>
+        <v>46298.875</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -7659,7 +7659,7 @@
     </row>
     <row r="279" spans="1:7">
       <c r="A279" s="2">
-        <v>46295.88541666666</v>
+        <v>46298.88541666666</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -7682,7 +7682,7 @@
     </row>
     <row r="280" spans="1:7">
       <c r="A280" s="2">
-        <v>46295.89583333334</v>
+        <v>46298.89583333334</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -7705,7 +7705,7 @@
     </row>
     <row r="281" spans="1:7">
       <c r="A281" s="2">
-        <v>46295.90625</v>
+        <v>46298.90625</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -7728,7 +7728,7 @@
     </row>
     <row r="282" spans="1:7">
       <c r="A282" s="2">
-        <v>46295.91666666666</v>
+        <v>46298.91666666666</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -7751,7 +7751,7 @@
     </row>
     <row r="283" spans="1:7">
       <c r="A283" s="2">
-        <v>46295.92708333334</v>
+        <v>46298.92708333334</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -7774,7 +7774,7 @@
     </row>
     <row r="284" spans="1:7">
       <c r="A284" s="2">
-        <v>46295.9375</v>
+        <v>46298.9375</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -7797,7 +7797,7 @@
     </row>
     <row r="285" spans="1:7">
       <c r="A285" s="2">
-        <v>46295.94791666666</v>
+        <v>46298.94791666666</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -7820,7 +7820,7 @@
     </row>
     <row r="286" spans="1:7">
       <c r="A286" s="2">
-        <v>46295.95833333334</v>
+        <v>46298.95833333334</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -7843,7 +7843,7 @@
     </row>
     <row r="287" spans="1:7">
       <c r="A287" s="2">
-        <v>46295.96875</v>
+        <v>46298.96875</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -7866,7 +7866,7 @@
     </row>
     <row r="288" spans="1:7">
       <c r="A288" s="2">
-        <v>46295.97916666666</v>
+        <v>46298.97916666666</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -7889,7 +7889,7 @@
     </row>
     <row r="289" spans="1:7">
       <c r="A289" s="2">
-        <v>46295.98958333334</v>
+        <v>46298.98958333334</v>
       </c>
       <c r="B289">
         <v>0</v>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
   <si>
     <t>Timestamp (CET)</t>
   </si>
@@ -37,582 +37,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>01.10.20261</t>
-  </si>
-  <si>
-    <t>01.10.20262</t>
-  </si>
-  <si>
-    <t>01.10.20263</t>
-  </si>
-  <si>
-    <t>01.10.20264</t>
-  </si>
-  <si>
-    <t>01.10.20265</t>
-  </si>
-  <si>
-    <t>01.10.20266</t>
-  </si>
-  <si>
-    <t>01.10.20267</t>
-  </si>
-  <si>
-    <t>01.10.20268</t>
-  </si>
-  <si>
-    <t>01.10.20269</t>
-  </si>
-  <si>
-    <t>01.10.202610</t>
-  </si>
-  <si>
-    <t>01.10.202611</t>
-  </si>
-  <si>
-    <t>01.10.202612</t>
-  </si>
-  <si>
-    <t>01.10.202613</t>
-  </si>
-  <si>
-    <t>01.10.202614</t>
-  </si>
-  <si>
-    <t>01.10.202615</t>
-  </si>
-  <si>
-    <t>01.10.202616</t>
-  </si>
-  <si>
-    <t>01.10.202617</t>
-  </si>
-  <si>
-    <t>01.10.202618</t>
-  </si>
-  <si>
-    <t>01.10.202619</t>
-  </si>
-  <si>
-    <t>01.10.202620</t>
-  </si>
-  <si>
-    <t>01.10.202621</t>
-  </si>
-  <si>
-    <t>01.10.202622</t>
-  </si>
-  <si>
-    <t>01.10.202623</t>
-  </si>
-  <si>
-    <t>01.10.202624</t>
-  </si>
-  <si>
-    <t>01.10.202625</t>
-  </si>
-  <si>
-    <t>01.10.202626</t>
-  </si>
-  <si>
-    <t>01.10.202627</t>
-  </si>
-  <si>
-    <t>01.10.202628</t>
-  </si>
-  <si>
-    <t>01.10.202629</t>
-  </si>
-  <si>
-    <t>01.10.202630</t>
-  </si>
-  <si>
-    <t>01.10.202631</t>
-  </si>
-  <si>
-    <t>01.10.202632</t>
-  </si>
-  <si>
-    <t>01.10.202633</t>
-  </si>
-  <si>
-    <t>01.10.202634</t>
-  </si>
-  <si>
-    <t>01.10.202635</t>
-  </si>
-  <si>
-    <t>01.10.202636</t>
-  </si>
-  <si>
-    <t>01.10.202637</t>
-  </si>
-  <si>
-    <t>01.10.202638</t>
-  </si>
-  <si>
-    <t>01.10.202639</t>
-  </si>
-  <si>
-    <t>01.10.202640</t>
-  </si>
-  <si>
-    <t>01.10.202641</t>
-  </si>
-  <si>
-    <t>01.10.202642</t>
-  </si>
-  <si>
-    <t>01.10.202643</t>
-  </si>
-  <si>
-    <t>01.10.202644</t>
-  </si>
-  <si>
-    <t>01.10.202645</t>
-  </si>
-  <si>
-    <t>01.10.202646</t>
-  </si>
-  <si>
-    <t>01.10.202647</t>
-  </si>
-  <si>
-    <t>01.10.202648</t>
-  </si>
-  <si>
-    <t>01.10.202649</t>
-  </si>
-  <si>
-    <t>01.10.202650</t>
-  </si>
-  <si>
-    <t>01.10.202651</t>
-  </si>
-  <si>
-    <t>01.10.202652</t>
-  </si>
-  <si>
-    <t>01.10.202653</t>
-  </si>
-  <si>
-    <t>01.10.202654</t>
-  </si>
-  <si>
-    <t>01.10.202655</t>
-  </si>
-  <si>
-    <t>01.10.202656</t>
-  </si>
-  <si>
-    <t>01.10.202657</t>
-  </si>
-  <si>
-    <t>01.10.202658</t>
-  </si>
-  <si>
-    <t>01.10.202659</t>
-  </si>
-  <si>
-    <t>01.10.202660</t>
-  </si>
-  <si>
-    <t>01.10.202661</t>
-  </si>
-  <si>
-    <t>01.10.202662</t>
-  </si>
-  <si>
-    <t>01.10.202663</t>
-  </si>
-  <si>
-    <t>01.10.202664</t>
-  </si>
-  <si>
-    <t>01.10.202665</t>
-  </si>
-  <si>
-    <t>01.10.202666</t>
-  </si>
-  <si>
-    <t>01.10.202667</t>
-  </si>
-  <si>
-    <t>01.10.202668</t>
-  </si>
-  <si>
-    <t>01.10.202669</t>
-  </si>
-  <si>
-    <t>01.10.202670</t>
-  </si>
-  <si>
-    <t>01.10.202671</t>
-  </si>
-  <si>
-    <t>01.10.202672</t>
-  </si>
-  <si>
-    <t>01.10.202673</t>
-  </si>
-  <si>
-    <t>01.10.202674</t>
-  </si>
-  <si>
-    <t>01.10.202675</t>
-  </si>
-  <si>
-    <t>01.10.202676</t>
-  </si>
-  <si>
-    <t>01.10.202677</t>
-  </si>
-  <si>
-    <t>01.10.202678</t>
-  </si>
-  <si>
-    <t>01.10.202679</t>
-  </si>
-  <si>
-    <t>01.10.202680</t>
-  </si>
-  <si>
-    <t>01.10.202681</t>
-  </si>
-  <si>
-    <t>01.10.202682</t>
-  </si>
-  <si>
-    <t>01.10.202683</t>
-  </si>
-  <si>
-    <t>01.10.202684</t>
-  </si>
-  <si>
-    <t>01.10.202685</t>
-  </si>
-  <si>
-    <t>01.10.202686</t>
-  </si>
-  <si>
-    <t>01.10.202687</t>
-  </si>
-  <si>
-    <t>01.10.202688</t>
-  </si>
-  <si>
-    <t>01.10.202689</t>
-  </si>
-  <si>
-    <t>01.10.202690</t>
-  </si>
-  <si>
-    <t>01.10.202691</t>
-  </si>
-  <si>
-    <t>01.10.202692</t>
-  </si>
-  <si>
-    <t>01.10.202693</t>
-  </si>
-  <si>
-    <t>01.10.202694</t>
-  </si>
-  <si>
-    <t>01.10.202695</t>
-  </si>
-  <si>
-    <t>01.10.202696</t>
-  </si>
-  <si>
-    <t>02.10.20261</t>
-  </si>
-  <si>
-    <t>02.10.20262</t>
-  </si>
-  <si>
-    <t>02.10.20263</t>
-  </si>
-  <si>
-    <t>02.10.20264</t>
-  </si>
-  <si>
-    <t>02.10.20265</t>
-  </si>
-  <si>
-    <t>02.10.20266</t>
-  </si>
-  <si>
-    <t>02.10.20267</t>
-  </si>
-  <si>
-    <t>02.10.20268</t>
-  </si>
-  <si>
-    <t>02.10.20269</t>
-  </si>
-  <si>
-    <t>02.10.202610</t>
-  </si>
-  <si>
-    <t>02.10.202611</t>
-  </si>
-  <si>
-    <t>02.10.202612</t>
-  </si>
-  <si>
-    <t>02.10.202613</t>
-  </si>
-  <si>
-    <t>02.10.202614</t>
-  </si>
-  <si>
-    <t>02.10.202615</t>
-  </si>
-  <si>
-    <t>02.10.202616</t>
-  </si>
-  <si>
-    <t>02.10.202617</t>
-  </si>
-  <si>
-    <t>02.10.202618</t>
-  </si>
-  <si>
-    <t>02.10.202619</t>
-  </si>
-  <si>
-    <t>02.10.202620</t>
-  </si>
-  <si>
-    <t>02.10.202621</t>
-  </si>
-  <si>
-    <t>02.10.202622</t>
-  </si>
-  <si>
-    <t>02.10.202623</t>
-  </si>
-  <si>
-    <t>02.10.202624</t>
-  </si>
-  <si>
-    <t>02.10.202625</t>
-  </si>
-  <si>
-    <t>02.10.202626</t>
-  </si>
-  <si>
-    <t>02.10.202627</t>
-  </si>
-  <si>
-    <t>02.10.202628</t>
-  </si>
-  <si>
-    <t>02.10.202629</t>
-  </si>
-  <si>
-    <t>02.10.202630</t>
-  </si>
-  <si>
-    <t>02.10.202631</t>
-  </si>
-  <si>
-    <t>02.10.202632</t>
-  </si>
-  <si>
-    <t>02.10.202633</t>
-  </si>
-  <si>
-    <t>02.10.202634</t>
-  </si>
-  <si>
-    <t>02.10.202635</t>
-  </si>
-  <si>
-    <t>02.10.202636</t>
-  </si>
-  <si>
-    <t>02.10.202637</t>
-  </si>
-  <si>
-    <t>02.10.202638</t>
-  </si>
-  <si>
-    <t>02.10.202639</t>
-  </si>
-  <si>
-    <t>02.10.202640</t>
-  </si>
-  <si>
-    <t>02.10.202641</t>
-  </si>
-  <si>
-    <t>02.10.202642</t>
-  </si>
-  <si>
-    <t>02.10.202643</t>
-  </si>
-  <si>
-    <t>02.10.202644</t>
-  </si>
-  <si>
-    <t>02.10.202645</t>
-  </si>
-  <si>
-    <t>02.10.202646</t>
-  </si>
-  <si>
-    <t>02.10.202647</t>
-  </si>
-  <si>
-    <t>02.10.202648</t>
-  </si>
-  <si>
-    <t>02.10.202649</t>
-  </si>
-  <si>
-    <t>02.10.202650</t>
-  </si>
-  <si>
-    <t>02.10.202651</t>
-  </si>
-  <si>
-    <t>02.10.202652</t>
-  </si>
-  <si>
-    <t>02.10.202653</t>
-  </si>
-  <si>
-    <t>02.10.202654</t>
-  </si>
-  <si>
-    <t>02.10.202655</t>
-  </si>
-  <si>
-    <t>02.10.202656</t>
-  </si>
-  <si>
-    <t>02.10.202657</t>
-  </si>
-  <si>
-    <t>02.10.202658</t>
-  </si>
-  <si>
-    <t>02.10.202659</t>
-  </si>
-  <si>
-    <t>02.10.202660</t>
-  </si>
-  <si>
-    <t>02.10.202661</t>
-  </si>
-  <si>
-    <t>02.10.202662</t>
-  </si>
-  <si>
-    <t>02.10.202663</t>
-  </si>
-  <si>
-    <t>02.10.202664</t>
-  </si>
-  <si>
-    <t>02.10.202665</t>
-  </si>
-  <si>
-    <t>02.10.202666</t>
-  </si>
-  <si>
-    <t>02.10.202667</t>
-  </si>
-  <si>
-    <t>02.10.202668</t>
-  </si>
-  <si>
-    <t>02.10.202669</t>
-  </si>
-  <si>
-    <t>02.10.202670</t>
-  </si>
-  <si>
-    <t>02.10.202671</t>
-  </si>
-  <si>
-    <t>02.10.202672</t>
-  </si>
-  <si>
-    <t>02.10.202673</t>
-  </si>
-  <si>
-    <t>02.10.202674</t>
-  </si>
-  <si>
-    <t>02.10.202675</t>
-  </si>
-  <si>
-    <t>02.10.202676</t>
-  </si>
-  <si>
-    <t>02.10.202677</t>
-  </si>
-  <si>
-    <t>02.10.202678</t>
-  </si>
-  <si>
-    <t>02.10.202679</t>
-  </si>
-  <si>
-    <t>02.10.202680</t>
-  </si>
-  <si>
-    <t>02.10.202681</t>
-  </si>
-  <si>
-    <t>02.10.202682</t>
-  </si>
-  <si>
-    <t>02.10.202683</t>
-  </si>
-  <si>
-    <t>02.10.202684</t>
-  </si>
-  <si>
-    <t>02.10.202685</t>
-  </si>
-  <si>
-    <t>02.10.202686</t>
-  </si>
-  <si>
-    <t>02.10.202687</t>
-  </si>
-  <si>
-    <t>02.10.202688</t>
-  </si>
-  <si>
-    <t>02.10.202689</t>
-  </si>
-  <si>
-    <t>02.10.202690</t>
-  </si>
-  <si>
-    <t>02.10.202691</t>
-  </si>
-  <si>
-    <t>02.10.202692</t>
-  </si>
-  <si>
-    <t>02.10.202693</t>
-  </si>
-  <si>
-    <t>02.10.202694</t>
-  </si>
-  <si>
-    <t>02.10.202695</t>
-  </si>
-  <si>
-    <t>02.10.202696</t>
-  </si>
-  <si>
     <t>03.10.20261</t>
   </si>
   <si>
@@ -899,6 +323,294 @@
   </si>
   <si>
     <t>03.10.202696</t>
+  </si>
+  <si>
+    <t>04.10.20261</t>
+  </si>
+  <si>
+    <t>04.10.20262</t>
+  </si>
+  <si>
+    <t>04.10.20263</t>
+  </si>
+  <si>
+    <t>04.10.20264</t>
+  </si>
+  <si>
+    <t>04.10.20265</t>
+  </si>
+  <si>
+    <t>04.10.20266</t>
+  </si>
+  <si>
+    <t>04.10.20267</t>
+  </si>
+  <si>
+    <t>04.10.20268</t>
+  </si>
+  <si>
+    <t>04.10.20269</t>
+  </si>
+  <si>
+    <t>04.10.202610</t>
+  </si>
+  <si>
+    <t>04.10.202611</t>
+  </si>
+  <si>
+    <t>04.10.202612</t>
+  </si>
+  <si>
+    <t>04.10.202613</t>
+  </si>
+  <si>
+    <t>04.10.202614</t>
+  </si>
+  <si>
+    <t>04.10.202615</t>
+  </si>
+  <si>
+    <t>04.10.202616</t>
+  </si>
+  <si>
+    <t>04.10.202617</t>
+  </si>
+  <si>
+    <t>04.10.202618</t>
+  </si>
+  <si>
+    <t>04.10.202619</t>
+  </si>
+  <si>
+    <t>04.10.202620</t>
+  </si>
+  <si>
+    <t>04.10.202621</t>
+  </si>
+  <si>
+    <t>04.10.202622</t>
+  </si>
+  <si>
+    <t>04.10.202623</t>
+  </si>
+  <si>
+    <t>04.10.202624</t>
+  </si>
+  <si>
+    <t>04.10.202625</t>
+  </si>
+  <si>
+    <t>04.10.202626</t>
+  </si>
+  <si>
+    <t>04.10.202627</t>
+  </si>
+  <si>
+    <t>04.10.202628</t>
+  </si>
+  <si>
+    <t>04.10.202629</t>
+  </si>
+  <si>
+    <t>04.10.202630</t>
+  </si>
+  <si>
+    <t>04.10.202631</t>
+  </si>
+  <si>
+    <t>04.10.202632</t>
+  </si>
+  <si>
+    <t>04.10.202633</t>
+  </si>
+  <si>
+    <t>04.10.202634</t>
+  </si>
+  <si>
+    <t>04.10.202635</t>
+  </si>
+  <si>
+    <t>04.10.202636</t>
+  </si>
+  <si>
+    <t>04.10.202637</t>
+  </si>
+  <si>
+    <t>04.10.202638</t>
+  </si>
+  <si>
+    <t>04.10.202639</t>
+  </si>
+  <si>
+    <t>04.10.202640</t>
+  </si>
+  <si>
+    <t>04.10.202641</t>
+  </si>
+  <si>
+    <t>04.10.202642</t>
+  </si>
+  <si>
+    <t>04.10.202643</t>
+  </si>
+  <si>
+    <t>04.10.202644</t>
+  </si>
+  <si>
+    <t>04.10.202645</t>
+  </si>
+  <si>
+    <t>04.10.202646</t>
+  </si>
+  <si>
+    <t>04.10.202647</t>
+  </si>
+  <si>
+    <t>04.10.202648</t>
+  </si>
+  <si>
+    <t>04.10.202649</t>
+  </si>
+  <si>
+    <t>04.10.202650</t>
+  </si>
+  <si>
+    <t>04.10.202651</t>
+  </si>
+  <si>
+    <t>04.10.202652</t>
+  </si>
+  <si>
+    <t>04.10.202653</t>
+  </si>
+  <si>
+    <t>04.10.202654</t>
+  </si>
+  <si>
+    <t>04.10.202655</t>
+  </si>
+  <si>
+    <t>04.10.202656</t>
+  </si>
+  <si>
+    <t>04.10.202657</t>
+  </si>
+  <si>
+    <t>04.10.202658</t>
+  </si>
+  <si>
+    <t>04.10.202659</t>
+  </si>
+  <si>
+    <t>04.10.202660</t>
+  </si>
+  <si>
+    <t>04.10.202661</t>
+  </si>
+  <si>
+    <t>04.10.202662</t>
+  </si>
+  <si>
+    <t>04.10.202663</t>
+  </si>
+  <si>
+    <t>04.10.202664</t>
+  </si>
+  <si>
+    <t>04.10.202665</t>
+  </si>
+  <si>
+    <t>04.10.202666</t>
+  </si>
+  <si>
+    <t>04.10.202667</t>
+  </si>
+  <si>
+    <t>04.10.202668</t>
+  </si>
+  <si>
+    <t>04.10.202669</t>
+  </si>
+  <si>
+    <t>04.10.202670</t>
+  </si>
+  <si>
+    <t>04.10.202671</t>
+  </si>
+  <si>
+    <t>04.10.202672</t>
+  </si>
+  <si>
+    <t>04.10.202673</t>
+  </si>
+  <si>
+    <t>04.10.202674</t>
+  </si>
+  <si>
+    <t>04.10.202675</t>
+  </si>
+  <si>
+    <t>04.10.202676</t>
+  </si>
+  <si>
+    <t>04.10.202677</t>
+  </si>
+  <si>
+    <t>04.10.202678</t>
+  </si>
+  <si>
+    <t>04.10.202679</t>
+  </si>
+  <si>
+    <t>04.10.202680</t>
+  </si>
+  <si>
+    <t>04.10.202681</t>
+  </si>
+  <si>
+    <t>04.10.202682</t>
+  </si>
+  <si>
+    <t>04.10.202683</t>
+  </si>
+  <si>
+    <t>04.10.202684</t>
+  </si>
+  <si>
+    <t>04.10.202685</t>
+  </si>
+  <si>
+    <t>04.10.202686</t>
+  </si>
+  <si>
+    <t>04.10.202687</t>
+  </si>
+  <si>
+    <t>04.10.202688</t>
+  </si>
+  <si>
+    <t>04.10.202689</t>
+  </si>
+  <si>
+    <t>04.10.202690</t>
+  </si>
+  <si>
+    <t>04.10.202691</t>
+  </si>
+  <si>
+    <t>04.10.202692</t>
+  </si>
+  <si>
+    <t>04.10.202693</t>
+  </si>
+  <si>
+    <t>04.10.202694</t>
+  </si>
+  <si>
+    <t>04.10.202695</t>
+  </si>
+  <si>
+    <t>04.10.202696</t>
   </si>
 </sst>
 </file>
@@ -1260,7 +972,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G289"/>
+  <dimension ref="A1:G193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1288,13 +1000,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.314</v>
       </c>
       <c r="C2">
-        <v>41.624</v>
+        <v>2.846</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1311,19 +1023,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46296.01041666666</v>
+        <v>46298.01041666666</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>5.059</v>
       </c>
       <c r="C3">
-        <v>17.956</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -1334,19 +1046,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46296.02083333334</v>
+        <v>46298.02083333334</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>1.179</v>
       </c>
       <c r="C4">
-        <v>5.03</v>
+        <v>0.113</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -1357,19 +1069,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46296.03125</v>
+        <v>46298.03125</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>0.572</v>
       </c>
       <c r="C5">
-        <v>8.010999999999999</v>
+        <v>0.047</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -1380,19 +1092,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46296.04166666666</v>
+        <v>46298.04166666666</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>5.326</v>
       </c>
       <c r="C6">
-        <v>9.654999999999999</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -1403,19 +1115,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46296.05208333334</v>
+        <v>46298.05208333334</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>10.019</v>
       </c>
       <c r="C7">
-        <v>14.463</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -1426,19 +1138,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46296.0625</v>
+        <v>46298.0625</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>8.893000000000001</v>
       </c>
       <c r="C8">
-        <v>12.806</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -1449,19 +1161,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46296.07291666666</v>
+        <v>46298.07291666666</v>
       </c>
       <c r="B9">
-        <v>0.296</v>
+        <v>0.145</v>
       </c>
       <c r="C9">
-        <v>2.194</v>
+        <v>3.152</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E9">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -1472,19 +1184,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46296.08333333334</v>
+        <v>46298.08333333334</v>
       </c>
       <c r="B10">
-        <v>2.134</v>
+        <v>9.189</v>
       </c>
       <c r="C10">
-        <v>1.109</v>
+        <v>0.291</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E10">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F10">
         <v>9</v>
@@ -1495,19 +1207,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46296.09375</v>
+        <v>46298.09375</v>
       </c>
       <c r="B11">
-        <v>10.033</v>
+        <v>17.425</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E11">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -1518,19 +1230,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46296.10416666666</v>
+        <v>46298.10416666666</v>
       </c>
       <c r="B12">
-        <v>5.545</v>
+        <v>10.113</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>1.327</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E12">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <v>11</v>
@@ -1541,19 +1253,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46296.11458333334</v>
+        <v>46298.11458333334</v>
       </c>
       <c r="B13">
-        <v>18.987</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>5.623</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E13">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>12</v>
@@ -1564,19 +1276,19 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46296.125</v>
+        <v>46298.125</v>
       </c>
       <c r="B14">
-        <v>8.423</v>
+        <v>13.578</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>0.645</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E14">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F14">
         <v>13</v>
@@ -1587,19 +1299,19 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46296.13541666666</v>
+        <v>46298.13541666666</v>
       </c>
       <c r="B15">
-        <v>3.601</v>
+        <v>36.352</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E15">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <v>14</v>
@@ -1610,16 +1322,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46296.14583333334</v>
+        <v>46298.14583333334</v>
       </c>
       <c r="B16">
-        <v>10.105</v>
+        <v>38.244</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1633,10 +1345,10 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46296.15625</v>
+        <v>46298.15625</v>
       </c>
       <c r="B17">
-        <v>13.722</v>
+        <v>23.005</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1656,13 +1368,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46296.16666666666</v>
+        <v>46298.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.042</v>
+        <v>23.229</v>
       </c>
       <c r="C18">
-        <v>2.629</v>
+        <v>0</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1679,16 +1391,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46296.17708333334</v>
+        <v>46298.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>7.019</v>
       </c>
       <c r="C19">
-        <v>7.847</v>
+        <v>0.326</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1702,16 +1414,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46296.1875</v>
+        <v>46298.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="C20">
-        <v>17.308</v>
+        <v>0.434</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1725,16 +1437,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46296.19791666666</v>
+        <v>46298.19791666666</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>13.151</v>
       </c>
       <c r="C21">
-        <v>17.735</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1748,16 +1460,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46296.20833333334</v>
+        <v>46298.20833333334</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>8.101000000000001</v>
       </c>
       <c r="C22">
-        <v>7.813</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>21.75</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1771,16 +1483,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46296.21875</v>
+        <v>46298.21875</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>2.207</v>
       </c>
       <c r="C23">
-        <v>9.499000000000001</v>
+        <v>0.008</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>21.75</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1794,16 +1506,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46296.22916666666</v>
+        <v>46298.22916666666</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>0.089</v>
       </c>
       <c r="C24">
-        <v>17.441</v>
+        <v>1.051</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1817,16 +1529,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46296.23958333334</v>
+        <v>46298.23958333334</v>
       </c>
       <c r="B25">
-        <v>2.209</v>
+        <v>0.062</v>
       </c>
       <c r="C25">
-        <v>1.215</v>
+        <v>2.089</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1840,13 +1552,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46296.25</v>
+        <v>46298.25</v>
       </c>
       <c r="B26">
-        <v>0.223</v>
+        <v>13.046</v>
       </c>
       <c r="C26">
-        <v>2.387</v>
+        <v>0.105</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1863,13 +1575,13 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46296.26041666666</v>
+        <v>46298.26041666666</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>8.926</v>
       </c>
       <c r="C27">
-        <v>5.025</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1886,13 +1598,13 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46296.27083333334</v>
+        <v>46298.27083333334</v>
       </c>
       <c r="B28">
-        <v>0.031</v>
+        <v>13.632</v>
       </c>
       <c r="C28">
-        <v>2.218</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1909,13 +1621,13 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46296.28125</v>
+        <v>46298.28125</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>9.483000000000001</v>
       </c>
       <c r="C29">
-        <v>4.447</v>
+        <v>0</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1932,13 +1644,13 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46296.29166666666</v>
+        <v>46298.29166666666</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="C30">
-        <v>10.563</v>
+        <v>0.059</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1955,13 +1667,13 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46296.30208333334</v>
+        <v>46298.30208333334</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>0.274</v>
       </c>
       <c r="C31">
-        <v>5.176</v>
+        <v>2.538</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1978,13 +1690,13 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46296.3125</v>
+        <v>46298.3125</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32">
-        <v>12.53</v>
+        <v>20.359</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -2001,13 +1713,13 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46296.32291666666</v>
+        <v>46298.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>10.197</v>
+        <v>27.733</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -2024,19 +1736,19 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46296.33333333334</v>
+        <v>46298.33333333334</v>
       </c>
       <c r="B34">
-        <v>11.41</v>
+        <v>0.054</v>
       </c>
       <c r="C34">
-        <v>1.258</v>
+        <v>3.19</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F34">
         <v>33</v>
@@ -2047,19 +1759,19 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46296.34375</v>
+        <v>46298.34375</v>
       </c>
       <c r="B35">
-        <v>20.409</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>10.822</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F35">
         <v>34</v>
@@ -2070,13 +1782,13 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46296.35416666666</v>
+        <v>46298.35416666666</v>
       </c>
       <c r="B36">
-        <v>0.729</v>
+        <v>0.03</v>
       </c>
       <c r="C36">
-        <v>4.164</v>
+        <v>8.191000000000001</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -2093,13 +1805,13 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46296.36458333334</v>
+        <v>46298.36458333334</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>0.527</v>
       </c>
       <c r="C37">
-        <v>15.055</v>
+        <v>1.951</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -2116,13 +1828,13 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46296.375</v>
+        <v>46298.375</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>2.692</v>
       </c>
       <c r="C38">
-        <v>14.646</v>
+        <v>0.307</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2139,13 +1851,13 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46296.38541666666</v>
+        <v>46298.38541666666</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>11.919</v>
       </c>
       <c r="C39">
-        <v>28.552</v>
+        <v>0</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -2162,19 +1874,19 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46296.39583333334</v>
+        <v>46298.39583333334</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
-        <v>52.826</v>
+        <v>0</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F40">
         <v>39</v>
@@ -2185,19 +1897,19 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46296.40625</v>
+        <v>46298.40625</v>
       </c>
       <c r="B41">
-        <v>0.01</v>
+        <v>14.294</v>
       </c>
       <c r="C41">
-        <v>11.473</v>
+        <v>0.077</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F41">
         <v>40</v>
@@ -2208,19 +1920,19 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46296.41666666666</v>
+        <v>46298.41666666666</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>2.273</v>
       </c>
       <c r="C42">
-        <v>23.721</v>
+        <v>0.612</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="F42">
         <v>41</v>
@@ -2231,19 +1943,19 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46296.42708333334</v>
+        <v>46298.42708333334</v>
       </c>
       <c r="B43">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>1.432</v>
+        <v>7.272</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F43">
         <v>42</v>
@@ -2254,19 +1966,19 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46296.4375</v>
+        <v>46298.4375</v>
       </c>
       <c r="B44">
         <v>0</v>
       </c>
       <c r="C44">
-        <v>18.428</v>
+        <v>6.056</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F44">
         <v>43</v>
@@ -2277,19 +1989,19 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46296.44791666666</v>
+        <v>46298.44791666666</v>
       </c>
       <c r="B45">
-        <v>0.078</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <v>3.002</v>
+        <v>12.128</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F45">
         <v>44</v>
@@ -2300,19 +2012,19 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46296.45833333334</v>
+        <v>46298.45833333334</v>
       </c>
       <c r="B46">
-        <v>0.099</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>5.528</v>
+        <v>12.215</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F46">
         <v>45</v>
@@ -2323,19 +2035,19 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46296.46875</v>
+        <v>46298.46875</v>
       </c>
       <c r="B47">
         <v>0</v>
       </c>
       <c r="C47">
-        <v>14.802</v>
+        <v>26.858</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F47">
         <v>46</v>
@@ -2346,19 +2058,19 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46296.47916666666</v>
+        <v>46298.47916666666</v>
       </c>
       <c r="B48">
         <v>0</v>
       </c>
       <c r="C48">
-        <v>27.631</v>
+        <v>19.573</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F48">
         <v>47</v>
@@ -2369,19 +2081,19 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46296.48958333334</v>
+        <v>46298.48958333334</v>
       </c>
       <c r="B49">
         <v>0</v>
       </c>
       <c r="C49">
-        <v>9.324</v>
+        <v>5.782</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>137.5</v>
+        <v>0</v>
       </c>
       <c r="F49">
         <v>48</v>
@@ -2392,19 +2104,19 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46296.5</v>
+        <v>46298.5</v>
       </c>
       <c r="B50">
         <v>0</v>
       </c>
       <c r="C50">
-        <v>32.398</v>
+        <v>23.274</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F50">
         <v>49</v>
@@ -2415,19 +2127,19 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46296.51041666666</v>
+        <v>46298.51041666666</v>
       </c>
       <c r="B51">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="C51">
-        <v>11.393</v>
+        <v>19.847</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>137.5</v>
+        <v>0</v>
       </c>
       <c r="F51">
         <v>50</v>
@@ -2438,19 +2150,19 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46296.52083333334</v>
+        <v>46298.52083333334</v>
       </c>
       <c r="B52">
         <v>0</v>
       </c>
       <c r="C52">
-        <v>18.725</v>
+        <v>15.095</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>137.5</v>
+        <v>0</v>
       </c>
       <c r="F52">
         <v>51</v>
@@ -2461,19 +2173,19 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46296.53125</v>
+        <v>46298.53125</v>
       </c>
       <c r="B53">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>5.517</v>
+        <v>7.901</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>137.5</v>
+        <v>0</v>
       </c>
       <c r="F53">
         <v>52</v>
@@ -2484,19 +2196,19 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46296.54166666666</v>
+        <v>46298.54166666666</v>
       </c>
       <c r="B54">
-        <v>0.53</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="C54">
-        <v>2.736</v>
+        <v>3.342</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F54">
         <v>53</v>
@@ -2507,19 +2219,19 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46296.55208333334</v>
+        <v>46298.55208333334</v>
       </c>
       <c r="B55">
-        <v>0.048</v>
+        <v>0.675</v>
       </c>
       <c r="C55">
-        <v>5.505</v>
+        <v>2.148</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>112.5</v>
+        <v>0</v>
       </c>
       <c r="F55">
         <v>54</v>
@@ -2530,19 +2242,19 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46296.5625</v>
+        <v>46298.5625</v>
       </c>
       <c r="B56">
-        <v>1.458</v>
+        <v>0</v>
       </c>
       <c r="C56">
-        <v>0.592</v>
+        <v>17.874</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>112.5</v>
+        <v>0</v>
       </c>
       <c r="F56">
         <v>55</v>
@@ -2553,19 +2265,19 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46296.57291666666</v>
+        <v>46298.57291666666</v>
       </c>
       <c r="B57">
-        <v>1.138</v>
+        <v>0.175</v>
       </c>
       <c r="C57">
-        <v>0.06900000000000001</v>
+        <v>2.026</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F57">
         <v>56</v>
@@ -2576,19 +2288,19 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46296.58333333334</v>
+        <v>46298.58333333334</v>
       </c>
       <c r="B58">
-        <v>0.146</v>
+        <v>0</v>
       </c>
       <c r="C58">
-        <v>14.817</v>
+        <v>9.449</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F58">
         <v>57</v>
@@ -2599,19 +2311,19 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46296.59375</v>
+        <v>46298.59375</v>
       </c>
       <c r="B59">
-        <v>6.483</v>
+        <v>0.047</v>
       </c>
       <c r="C59">
-        <v>0.016</v>
+        <v>3.697</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F59">
         <v>58</v>
@@ -2622,19 +2334,19 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46296.60416666666</v>
+        <v>46298.60416666666</v>
       </c>
       <c r="B60">
-        <v>7.873</v>
+        <v>0</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>22.531</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60">
-        <v>112.5</v>
+        <v>0</v>
       </c>
       <c r="F60">
         <v>59</v>
@@ -2645,19 +2357,19 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46296.61458333334</v>
+        <v>46298.61458333334</v>
       </c>
       <c r="B61">
-        <v>2.091</v>
+        <v>0</v>
       </c>
       <c r="C61">
-        <v>1.705</v>
+        <v>9.302</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F61">
         <v>60</v>
@@ -2668,19 +2380,19 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46296.625</v>
+        <v>46298.625</v>
       </c>
       <c r="B62">
         <v>0</v>
       </c>
       <c r="C62">
-        <v>48.454</v>
+        <v>15.062</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="F62">
         <v>61</v>
@@ -2691,19 +2403,19 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46296.63541666666</v>
+        <v>46298.63541666666</v>
       </c>
       <c r="B63">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="C63">
-        <v>17.28</v>
+        <v>18.122</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="F63">
         <v>62</v>
@@ -2714,19 +2426,19 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46296.64583333334</v>
+        <v>46298.64583333334</v>
       </c>
       <c r="B64">
-        <v>0.123</v>
+        <v>0.05</v>
       </c>
       <c r="C64">
-        <v>2.447</v>
+        <v>2.129</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="F64">
         <v>63</v>
@@ -2737,19 +2449,19 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46296.65625</v>
+        <v>46298.65625</v>
       </c>
       <c r="B65">
-        <v>4.038</v>
+        <v>9.082000000000001</v>
       </c>
       <c r="C65">
-        <v>0.08</v>
+        <v>0.757</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="F65">
         <v>64</v>
@@ -2760,19 +2472,19 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46296.66666666666</v>
+        <v>46298.66666666666</v>
       </c>
       <c r="B66">
-        <v>0.371</v>
+        <v>23.941</v>
       </c>
       <c r="C66">
-        <v>0.6850000000000001</v>
+        <v>0</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>87.5</v>
+        <v>37.5</v>
       </c>
       <c r="F66">
         <v>65</v>
@@ -2783,19 +2495,19 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46296.67708333334</v>
+        <v>46298.67708333334</v>
       </c>
       <c r="B67">
-        <v>3.373</v>
+        <v>38.347</v>
       </c>
       <c r="C67">
-        <v>0.162</v>
+        <v>0</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>100</v>
+        <v>37.5</v>
       </c>
       <c r="F67">
         <v>66</v>
@@ -2806,19 +2518,19 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46296.6875</v>
+        <v>46298.6875</v>
       </c>
       <c r="B68">
-        <v>0.614</v>
+        <v>15.994</v>
       </c>
       <c r="C68">
-        <v>0.102</v>
+        <v>0</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F68">
         <v>67</v>
@@ -2829,19 +2541,19 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46296.69791666666</v>
+        <v>46298.69791666666</v>
       </c>
       <c r="B69">
-        <v>3.087</v>
+        <v>13.096</v>
       </c>
       <c r="C69">
-        <v>0.057</v>
+        <v>0</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F69">
         <v>68</v>
@@ -2852,19 +2564,19 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46296.70833333334</v>
+        <v>46298.70833333334</v>
       </c>
       <c r="B70">
-        <v>13.598</v>
+        <v>1.035</v>
       </c>
       <c r="C70">
-        <v>0.156</v>
+        <v>2.162</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F70">
         <v>69</v>
@@ -2875,19 +2587,19 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46296.71875</v>
+        <v>46298.71875</v>
       </c>
       <c r="B71">
-        <v>25.233</v>
+        <v>1.41</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
       <c r="E71">
-        <v>77.75</v>
+        <v>0</v>
       </c>
       <c r="F71">
         <v>70</v>
@@ -2898,13 +2610,13 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46296.72916666666</v>
+        <v>46298.72916666666</v>
       </c>
       <c r="B72">
-        <v>16.053</v>
+        <v>0.296</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>3.615</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -2921,13 +2633,13 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46296.73958333334</v>
+        <v>46298.73958333334</v>
       </c>
       <c r="B73">
-        <v>2.737</v>
+        <v>0.889</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>0.236</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -2944,13 +2656,13 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46296.75</v>
+        <v>46298.75</v>
       </c>
       <c r="B74">
-        <v>8.866</v>
+        <v>0</v>
       </c>
       <c r="C74">
-        <v>0.081</v>
+        <v>8.298</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -2967,13 +2679,13 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46296.76041666666</v>
+        <v>46298.76041666666</v>
       </c>
       <c r="B75">
-        <v>20.042</v>
+        <v>0</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>7.399</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -2990,13 +2702,13 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46296.77083333334</v>
+        <v>46298.77083333334</v>
       </c>
       <c r="B76">
-        <v>24.686</v>
+        <v>3.832</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -3013,13 +2725,13 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46296.78125</v>
+        <v>46298.78125</v>
       </c>
       <c r="B77">
-        <v>29.13</v>
+        <v>0.735</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>2.646</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -3036,16 +2748,16 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46296.79166666666</v>
+        <v>46298.79166666666</v>
       </c>
       <c r="B78">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="C78">
-        <v>0.016</v>
+        <v>5.075</v>
       </c>
       <c r="D78">
-        <v>24.75</v>
+        <v>0</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -3059,13 +2771,13 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46296.80208333334</v>
+        <v>46298.80208333334</v>
       </c>
       <c r="B79">
-        <v>11.792</v>
+        <v>0</v>
       </c>
       <c r="C79">
-        <v>0.004</v>
+        <v>10.732</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -3082,13 +2794,13 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46296.8125</v>
+        <v>46298.8125</v>
       </c>
       <c r="B80">
-        <v>11.921</v>
+        <v>0</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>18.373</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3105,13 +2817,13 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46296.82291666666</v>
+        <v>46298.82291666666</v>
       </c>
       <c r="B81">
-        <v>22.813</v>
+        <v>0</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>19.385</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -3128,13 +2840,13 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46296.83333333334</v>
+        <v>46298.83333333334</v>
       </c>
       <c r="B82">
-        <v>18.264</v>
+        <v>0.026</v>
       </c>
       <c r="C82">
-        <v>0.754</v>
+        <v>4.444</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -3151,16 +2863,16 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46296.84375</v>
+        <v>46298.84375</v>
       </c>
       <c r="B83">
-        <v>2.652</v>
+        <v>0</v>
       </c>
       <c r="C83">
-        <v>0.28</v>
+        <v>6.645</v>
       </c>
       <c r="D83">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -3174,16 +2886,16 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46296.85416666666</v>
+        <v>46298.85416666666</v>
       </c>
       <c r="B84">
-        <v>1.782</v>
+        <v>0</v>
       </c>
       <c r="C84">
-        <v>1.572</v>
+        <v>11.002</v>
       </c>
       <c r="D84">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -3197,13 +2909,13 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46296.86458333334</v>
+        <v>46298.86458333334</v>
       </c>
       <c r="B85">
-        <v>7.143</v>
+        <v>0.032</v>
       </c>
       <c r="C85">
-        <v>1.106</v>
+        <v>6.661</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -3220,13 +2932,13 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46296.875</v>
+        <v>46298.875</v>
       </c>
       <c r="B86">
-        <v>0.999</v>
+        <v>0</v>
       </c>
       <c r="C86">
-        <v>0.959</v>
+        <v>4.366</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -3243,13 +2955,13 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46296.88541666666</v>
+        <v>46298.88541666666</v>
       </c>
       <c r="B87">
-        <v>3.278</v>
+        <v>0</v>
       </c>
       <c r="C87">
-        <v>0.024</v>
+        <v>7.571</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -3266,13 +2978,13 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46296.89583333334</v>
+        <v>46298.89583333334</v>
       </c>
       <c r="B88">
-        <v>9.377000000000001</v>
+        <v>0</v>
       </c>
       <c r="C88">
-        <v>0.436</v>
+        <v>18.862</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3289,13 +3001,13 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46296.90625</v>
+        <v>46298.90625</v>
       </c>
       <c r="B89">
-        <v>2.447</v>
+        <v>0.008</v>
       </c>
       <c r="C89">
-        <v>1.304</v>
+        <v>5.244</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3312,13 +3024,13 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46296.91666666666</v>
+        <v>46298.91666666666</v>
       </c>
       <c r="B90">
-        <v>14.294</v>
+        <v>0.017</v>
       </c>
       <c r="C90">
-        <v>0.22</v>
+        <v>3.805</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3335,13 +3047,13 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46296.92708333334</v>
+        <v>46298.92708333334</v>
       </c>
       <c r="B91">
-        <v>0.271</v>
+        <v>0.046</v>
       </c>
       <c r="C91">
-        <v>3.425</v>
+        <v>0.279</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3358,13 +3070,13 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46296.9375</v>
+        <v>46298.9375</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="C92">
-        <v>7.896</v>
+        <v>0.519</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3381,13 +3093,13 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46296.94791666666</v>
+        <v>46298.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
       </c>
       <c r="C93">
-        <v>18.279</v>
+        <v>2.492</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3404,13 +3116,13 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46296.95833333334</v>
+        <v>46298.95833333334</v>
       </c>
       <c r="B94">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="C94">
-        <v>21.122</v>
+        <v>1.734</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3427,13 +3139,13 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46296.96875</v>
+        <v>46298.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
       </c>
       <c r="C95">
-        <v>49.355</v>
+        <v>1.116</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3450,19 +3162,19 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46296.97916666666</v>
+        <v>46298.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
       </c>
       <c r="C96">
-        <v>21.973</v>
+        <v>1.491</v>
       </c>
       <c r="D96">
         <v>0</v>
       </c>
       <c r="E96">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F96">
         <v>95</v>
@@ -3473,19 +3185,19 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46296.98958333334</v>
+        <v>46298.98958333334</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>1.449</v>
       </c>
       <c r="C97">
-        <v>19.411</v>
+        <v>1.086</v>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
       <c r="E97">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F97">
         <v>96</v>
@@ -3496,19 +3208,19 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46297</v>
+        <v>46299</v>
       </c>
       <c r="B98">
-        <v>3.355</v>
+        <v>0.927</v>
       </c>
       <c r="C98">
-        <v>2.4</v>
+        <v>1.828</v>
       </c>
       <c r="D98">
         <v>0</v>
       </c>
       <c r="E98">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F98">
         <v>1</v>
@@ -3519,19 +3231,19 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46297.01041666666</v>
+        <v>46299.01041666666</v>
       </c>
       <c r="B99">
-        <v>0.008999999999999999</v>
+        <v>1.248</v>
       </c>
       <c r="C99">
-        <v>2.104</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="D99">
         <v>0</v>
       </c>
       <c r="E99">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F99">
         <v>2</v>
@@ -3542,19 +3254,19 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46297.02083333334</v>
+        <v>46299.02083333334</v>
       </c>
       <c r="B100">
-        <v>7.041</v>
+        <v>0</v>
       </c>
       <c r="C100">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="D100">
         <v>0</v>
       </c>
       <c r="E100">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F100">
         <v>3</v>
@@ -3565,19 +3277,19 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46297.03125</v>
+        <v>46299.03125</v>
       </c>
       <c r="B101">
-        <v>2.132</v>
+        <v>0</v>
       </c>
       <c r="C101">
-        <v>0.04</v>
+        <v>11.549</v>
       </c>
       <c r="D101">
         <v>0</v>
       </c>
       <c r="E101">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F101">
         <v>4</v>
@@ -3588,19 +3300,19 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46297.04166666666</v>
+        <v>46299.04166666666</v>
       </c>
       <c r="B102">
-        <v>0.634</v>
+        <v>0</v>
       </c>
       <c r="C102">
-        <v>1.289</v>
+        <v>8.581</v>
       </c>
       <c r="D102">
         <v>0</v>
       </c>
       <c r="E102">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F102">
         <v>5</v>
@@ -3611,19 +3323,19 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46297.05208333334</v>
+        <v>46299.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
       </c>
       <c r="C103">
-        <v>5.007</v>
+        <v>8.853</v>
       </c>
       <c r="D103">
         <v>0</v>
       </c>
       <c r="E103">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F103">
         <v>6</v>
@@ -3634,19 +3346,19 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46297.0625</v>
+        <v>46299.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
       </c>
       <c r="C104">
-        <v>3.377</v>
+        <v>4.096</v>
       </c>
       <c r="D104">
         <v>0</v>
       </c>
       <c r="E104">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F104">
         <v>7</v>
@@ -3657,19 +3369,19 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46297.07291666666</v>
+        <v>46299.07291666666</v>
       </c>
       <c r="B105">
-        <v>2.961</v>
+        <v>0.31</v>
       </c>
       <c r="C105">
-        <v>0.018</v>
+        <v>2.337</v>
       </c>
       <c r="D105">
         <v>0</v>
       </c>
       <c r="E105">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F105">
         <v>8</v>
@@ -3680,19 +3392,19 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46297.08333333334</v>
+        <v>46299.08333333334</v>
       </c>
       <c r="B106">
-        <v>0.322</v>
+        <v>0</v>
       </c>
       <c r="C106">
-        <v>0.074</v>
+        <v>8.084</v>
       </c>
       <c r="D106">
         <v>0</v>
       </c>
       <c r="E106">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F106">
         <v>9</v>
@@ -3703,19 +3415,19 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46297.09375</v>
+        <v>46299.09375</v>
       </c>
       <c r="B107">
-        <v>5.897</v>
+        <v>0</v>
       </c>
       <c r="C107">
-        <v>0.004</v>
+        <v>3.155</v>
       </c>
       <c r="D107">
         <v>0</v>
       </c>
       <c r="E107">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F107">
         <v>10</v>
@@ -3726,19 +3438,19 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46297.10416666666</v>
+        <v>46299.10416666666</v>
       </c>
       <c r="B108">
-        <v>0.07000000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="C108">
-        <v>0.322</v>
+        <v>0.746</v>
       </c>
       <c r="D108">
         <v>0</v>
       </c>
       <c r="E108">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F108">
         <v>11</v>
@@ -3749,19 +3461,19 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46297.11458333334</v>
+        <v>46299.11458333334</v>
       </c>
       <c r="B109">
-        <v>4.786</v>
+        <v>0.51</v>
       </c>
       <c r="C109">
-        <v>0.017</v>
+        <v>0.028</v>
       </c>
       <c r="D109">
         <v>0</v>
       </c>
       <c r="E109">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F109">
         <v>12</v>
@@ -3772,19 +3484,19 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46297.125</v>
+        <v>46299.125</v>
       </c>
       <c r="B110">
-        <v>9.382999999999999</v>
+        <v>2.495</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>0.359</v>
       </c>
       <c r="D110">
         <v>0</v>
       </c>
       <c r="E110">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F110">
         <v>13</v>
@@ -3795,19 +3507,19 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46297.13541666666</v>
+        <v>46299.13541666666</v>
       </c>
       <c r="B111">
-        <v>9.141</v>
+        <v>0</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>5.354</v>
       </c>
       <c r="D111">
         <v>0</v>
       </c>
       <c r="E111">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F111">
         <v>14</v>
@@ -3818,19 +3530,19 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46297.14583333334</v>
+        <v>46299.14583333334</v>
       </c>
       <c r="B112">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="C112">
-        <v>3.694</v>
+        <v>1.713</v>
       </c>
       <c r="D112">
         <v>0</v>
       </c>
       <c r="E112">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F112">
         <v>15</v>
@@ -3841,19 +3553,19 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46297.15625</v>
+        <v>46299.15625</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>0.326</v>
       </c>
       <c r="C113">
-        <v>4.327</v>
+        <v>0.204</v>
       </c>
       <c r="D113">
         <v>0</v>
       </c>
       <c r="E113">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F113">
         <v>16</v>
@@ -3864,19 +3576,19 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46297.16666666666</v>
+        <v>46299.16666666666</v>
       </c>
       <c r="B114">
-        <v>0.028</v>
+        <v>0.023</v>
       </c>
       <c r="C114">
-        <v>1.236</v>
+        <v>0.595</v>
       </c>
       <c r="D114">
         <v>0</v>
       </c>
       <c r="E114">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F114">
         <v>17</v>
@@ -3887,19 +3599,19 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46297.17708333334</v>
+        <v>46299.17708333334</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="C115">
-        <v>4.299</v>
+        <v>0.129</v>
       </c>
       <c r="D115">
         <v>0</v>
       </c>
       <c r="E115">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F115">
         <v>18</v>
@@ -3910,19 +3622,19 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46297.1875</v>
+        <v>46299.1875</v>
       </c>
       <c r="B116">
-        <v>0</v>
+        <v>0.162</v>
       </c>
       <c r="C116">
-        <v>3.722</v>
+        <v>0.385</v>
       </c>
       <c r="D116">
         <v>0</v>
       </c>
       <c r="E116">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F116">
         <v>19</v>
@@ -3933,19 +3645,19 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46297.19791666666</v>
+        <v>46299.19791666666</v>
       </c>
       <c r="B117">
-        <v>3.955</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C117">
-        <v>0.231</v>
+        <v>0.369</v>
       </c>
       <c r="D117">
         <v>0</v>
       </c>
       <c r="E117">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F117">
         <v>20</v>
@@ -3956,19 +3668,19 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46297.20833333334</v>
+        <v>46299.20833333334</v>
       </c>
       <c r="B118">
-        <v>12.004</v>
+        <v>0.427</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>0.768</v>
       </c>
       <c r="D118">
         <v>0</v>
       </c>
       <c r="E118">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F118">
         <v>21</v>
@@ -3979,10 +3691,10 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46297.21875</v>
+        <v>46299.21875</v>
       </c>
       <c r="B119">
-        <v>10.401</v>
+        <v>1.773</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -4002,16 +3714,16 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46297.22916666666</v>
+        <v>46299.22916666666</v>
       </c>
       <c r="B120">
-        <v>0.599</v>
+        <v>0.237</v>
       </c>
       <c r="C120">
-        <v>0.01</v>
+        <v>0.12</v>
       </c>
       <c r="D120">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -4025,16 +3737,16 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46297.23958333334</v>
+        <v>46299.23958333334</v>
       </c>
       <c r="B121">
-        <v>5.884</v>
+        <v>3.702</v>
       </c>
       <c r="C121">
-        <v>0.038</v>
+        <v>0.031</v>
       </c>
       <c r="D121">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -4048,13 +3760,13 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46297.25</v>
+        <v>46299.25</v>
       </c>
       <c r="B122">
-        <v>15.995</v>
+        <v>2.243</v>
       </c>
       <c r="C122">
-        <v>1.198</v>
+        <v>0.353</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -4071,13 +3783,13 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46297.26041666666</v>
+        <v>46299.26041666666</v>
       </c>
       <c r="B123">
-        <v>10.112</v>
+        <v>0.614</v>
       </c>
       <c r="C123">
-        <v>0</v>
+        <v>0.636</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -4094,16 +3806,16 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46297.27083333334</v>
+        <v>46299.27083333334</v>
       </c>
       <c r="B124">
-        <v>0.118</v>
+        <v>0</v>
       </c>
       <c r="C124">
-        <v>4.875</v>
+        <v>4.233</v>
       </c>
       <c r="D124">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -4117,16 +3829,16 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46297.28125</v>
+        <v>46299.28125</v>
       </c>
       <c r="B125">
-        <v>0.229</v>
+        <v>0.055</v>
       </c>
       <c r="C125">
-        <v>0.146</v>
+        <v>0.92</v>
       </c>
       <c r="D125">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -4140,13 +3852,13 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46297.29166666666</v>
+        <v>46299.29166666666</v>
       </c>
       <c r="B126">
-        <v>1.604</v>
+        <v>1.697</v>
       </c>
       <c r="C126">
-        <v>0.078</v>
+        <v>0.003</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -4163,13 +3875,13 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46297.30208333334</v>
+        <v>46299.30208333334</v>
       </c>
       <c r="B127">
-        <v>0.321</v>
+        <v>0.824</v>
       </c>
       <c r="C127">
-        <v>0.092</v>
+        <v>8.577999999999999</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -4186,13 +3898,13 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46297.3125</v>
+        <v>46299.3125</v>
       </c>
       <c r="B128">
-        <v>0.776</v>
+        <v>0</v>
       </c>
       <c r="C128">
-        <v>0.731</v>
+        <v>22.205</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -4209,13 +3921,13 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46297.32291666666</v>
+        <v>46299.32291666666</v>
       </c>
       <c r="B129">
-        <v>0.171</v>
+        <v>0</v>
       </c>
       <c r="C129">
-        <v>5.251</v>
+        <v>26.611</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -4232,13 +3944,13 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46297.33333333334</v>
+        <v>46299.33333333334</v>
       </c>
       <c r="B130">
-        <v>32.95</v>
+        <v>4.501</v>
       </c>
       <c r="C130">
-        <v>0.057</v>
+        <v>3.483</v>
       </c>
       <c r="D130">
         <v>0</v>
@@ -4255,19 +3967,19 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46297.34375</v>
+        <v>46299.34375</v>
       </c>
       <c r="B131">
-        <v>11.077</v>
+        <v>0.198</v>
       </c>
       <c r="C131">
-        <v>2.155</v>
+        <v>0.146</v>
       </c>
       <c r="D131">
+        <v>0</v>
+      </c>
+      <c r="E131">
         <v>25</v>
-      </c>
-      <c r="E131">
-        <v>0</v>
       </c>
       <c r="F131">
         <v>34</v>
@@ -4278,19 +3990,19 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46297.35416666666</v>
+        <v>46299.35416666666</v>
       </c>
       <c r="B132">
-        <v>0.01</v>
+        <v>0.222</v>
       </c>
       <c r="C132">
-        <v>4.045</v>
+        <v>0.278</v>
       </c>
       <c r="D132">
+        <v>0</v>
+      </c>
+      <c r="E132">
         <v>25</v>
-      </c>
-      <c r="E132">
-        <v>0</v>
       </c>
       <c r="F132">
         <v>35</v>
@@ -4301,13 +4013,13 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46297.36458333334</v>
+        <v>46299.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
       </c>
       <c r="C133">
-        <v>23.338</v>
+        <v>0</v>
       </c>
       <c r="D133">
         <v>0</v>
@@ -4324,13 +4036,13 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46297.375</v>
+        <v>46299.375</v>
       </c>
       <c r="B134">
-        <v>13.718</v>
+        <v>0</v>
       </c>
       <c r="C134">
-        <v>4.844</v>
+        <v>0</v>
       </c>
       <c r="D134">
         <v>0</v>
@@ -4347,13 +4059,13 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46297.38541666666</v>
+        <v>46299.38541666666</v>
       </c>
       <c r="B135">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="C135">
-        <v>3.639</v>
+        <v>0</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -4370,13 +4082,13 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46297.39583333334</v>
+        <v>46299.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
       </c>
       <c r="C136">
-        <v>16.636</v>
+        <v>0</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -4393,19 +4105,19 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46297.40625</v>
+        <v>46299.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
       </c>
       <c r="C137">
-        <v>21.796</v>
+        <v>0</v>
       </c>
       <c r="D137">
         <v>0</v>
       </c>
       <c r="E137">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F137">
         <v>40</v>
@@ -4416,19 +4128,19 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46297.41666666666</v>
+        <v>46299.41666666666</v>
       </c>
       <c r="B138">
-        <v>0.124</v>
+        <v>0</v>
       </c>
       <c r="C138">
-        <v>7.12</v>
+        <v>0</v>
       </c>
       <c r="D138">
         <v>0</v>
       </c>
       <c r="E138">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F138">
         <v>41</v>
@@ -4439,19 +4151,19 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46297.42708333334</v>
+        <v>46299.42708333334</v>
       </c>
       <c r="B139">
-        <v>1.827</v>
+        <v>0</v>
       </c>
       <c r="C139">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="D139">
         <v>0</v>
       </c>
       <c r="E139">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F139">
         <v>42</v>
@@ -4462,19 +4174,19 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46297.4375</v>
+        <v>46299.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
       </c>
       <c r="C140">
-        <v>52.854</v>
+        <v>0</v>
       </c>
       <c r="D140">
         <v>0</v>
       </c>
       <c r="E140">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F140">
         <v>43</v>
@@ -4485,19 +4197,19 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46297.44791666666</v>
+        <v>46299.44791666666</v>
       </c>
       <c r="B141">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="C141">
-        <v>17.418</v>
+        <v>0</v>
       </c>
       <c r="D141">
         <v>0</v>
       </c>
       <c r="E141">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F141">
         <v>44</v>
@@ -4508,19 +4220,19 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46297.45833333334</v>
+        <v>46299.45833333334</v>
       </c>
       <c r="B142">
-        <v>3.117</v>
+        <v>0</v>
       </c>
       <c r="C142">
-        <v>0.114</v>
+        <v>0</v>
       </c>
       <c r="D142">
         <v>0</v>
       </c>
       <c r="E142">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F142">
         <v>45</v>
@@ -4531,19 +4243,19 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46297.46875</v>
+        <v>46299.46875</v>
       </c>
       <c r="B143">
-        <v>0.106</v>
+        <v>0</v>
       </c>
       <c r="C143">
-        <v>8.119</v>
+        <v>0</v>
       </c>
       <c r="D143">
         <v>0</v>
       </c>
       <c r="E143">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F143">
         <v>46</v>
@@ -4554,19 +4266,19 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46297.47916666666</v>
+        <v>46299.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
       </c>
       <c r="C144">
-        <v>19.833</v>
+        <v>0</v>
       </c>
       <c r="D144">
         <v>0</v>
       </c>
       <c r="E144">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F144">
         <v>47</v>
@@ -4577,19 +4289,19 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46297.48958333334</v>
+        <v>46299.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
       </c>
       <c r="C145">
-        <v>30.401</v>
+        <v>0</v>
       </c>
       <c r="D145">
         <v>0</v>
       </c>
       <c r="E145">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F145">
         <v>48</v>
@@ -4600,19 +4312,19 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46297.5</v>
+        <v>46299.5</v>
       </c>
       <c r="B146">
         <v>0</v>
       </c>
       <c r="C146">
-        <v>16.194</v>
+        <v>0</v>
       </c>
       <c r="D146">
         <v>0</v>
       </c>
       <c r="E146">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F146">
         <v>49</v>
@@ -4623,19 +4335,19 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46297.51041666666</v>
+        <v>46299.51041666666</v>
       </c>
       <c r="B147">
-        <v>0.117</v>
+        <v>0</v>
       </c>
       <c r="C147">
-        <v>1.641</v>
+        <v>0</v>
       </c>
       <c r="D147">
         <v>0</v>
       </c>
       <c r="E147">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F147">
         <v>50</v>
@@ -4646,19 +4358,19 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46297.52083333334</v>
+        <v>46299.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
       </c>
       <c r="C148">
-        <v>18.739</v>
+        <v>0</v>
       </c>
       <c r="D148">
         <v>0</v>
       </c>
       <c r="E148">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F148">
         <v>51</v>
@@ -4669,19 +4381,19 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46297.53125</v>
+        <v>46299.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
       </c>
       <c r="C149">
-        <v>39.556</v>
+        <v>0</v>
       </c>
       <c r="D149">
         <v>0</v>
       </c>
       <c r="E149">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F149">
         <v>52</v>
@@ -4692,19 +4404,19 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46297.54166666666</v>
+        <v>46299.54166666666</v>
       </c>
       <c r="B150">
-        <v>0.146</v>
+        <v>0</v>
       </c>
       <c r="C150">
-        <v>6.495</v>
+        <v>0</v>
       </c>
       <c r="D150">
         <v>0</v>
       </c>
       <c r="E150">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F150">
         <v>53</v>
@@ -4715,19 +4427,19 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46297.55208333334</v>
+        <v>46299.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
       </c>
       <c r="C151">
-        <v>3.115</v>
+        <v>0</v>
       </c>
       <c r="D151">
         <v>0</v>
       </c>
       <c r="E151">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F151">
         <v>54</v>
@@ -4738,19 +4450,19 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46297.5625</v>
+        <v>46299.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
       </c>
       <c r="C152">
-        <v>20.608</v>
+        <v>0</v>
       </c>
       <c r="D152">
         <v>0</v>
       </c>
       <c r="E152">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F152">
         <v>55</v>
@@ -4761,19 +4473,19 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46297.57291666666</v>
+        <v>46299.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
       </c>
       <c r="C153">
-        <v>26.646</v>
+        <v>0</v>
       </c>
       <c r="D153">
         <v>0</v>
       </c>
       <c r="E153">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F153">
         <v>56</v>
@@ -4784,19 +4496,19 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46297.58333333334</v>
+        <v>46299.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
       </c>
       <c r="C154">
-        <v>26.479</v>
+        <v>0</v>
       </c>
       <c r="D154">
         <v>0</v>
       </c>
       <c r="E154">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F154">
         <v>57</v>
@@ -4807,19 +4519,19 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46297.59375</v>
+        <v>46299.59375</v>
       </c>
       <c r="B155">
-        <v>0.289</v>
+        <v>0</v>
       </c>
       <c r="C155">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="D155">
         <v>0</v>
       </c>
       <c r="E155">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F155">
         <v>58</v>
@@ -4830,19 +4542,19 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46297.60416666666</v>
+        <v>46299.60416666666</v>
       </c>
       <c r="B156">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="C156">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="D156">
         <v>0</v>
       </c>
       <c r="E156">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F156">
         <v>59</v>
@@ -4853,19 +4565,19 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46297.61458333334</v>
+        <v>46299.61458333334</v>
       </c>
       <c r="B157">
-        <v>0.603</v>
+        <v>0</v>
       </c>
       <c r="C157">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="D157">
         <v>0</v>
       </c>
       <c r="E157">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F157">
         <v>60</v>
@@ -4876,19 +4588,19 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46297.625</v>
+        <v>46299.625</v>
       </c>
       <c r="B158">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="C158">
-        <v>4.538</v>
+        <v>0</v>
       </c>
       <c r="D158">
         <v>0</v>
       </c>
       <c r="E158">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F158">
         <v>61</v>
@@ -4899,19 +4611,19 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46297.63541666666</v>
+        <v>46299.63541666666</v>
       </c>
       <c r="B159">
-        <v>9.832000000000001</v>
+        <v>0</v>
       </c>
       <c r="C159">
-        <v>0.488</v>
+        <v>0</v>
       </c>
       <c r="D159">
         <v>0</v>
       </c>
       <c r="E159">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F159">
         <v>62</v>
@@ -4922,10 +4634,10 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46297.64583333334</v>
+        <v>46299.64583333334</v>
       </c>
       <c r="B160">
-        <v>29.014</v>
+        <v>0</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -4934,7 +4646,7 @@
         <v>0</v>
       </c>
       <c r="E160">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F160">
         <v>63</v>
@@ -4945,10 +4657,10 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46297.65625</v>
+        <v>46299.65625</v>
       </c>
       <c r="B161">
-        <v>17.966</v>
+        <v>0</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -4957,7 +4669,7 @@
         <v>0</v>
       </c>
       <c r="E161">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F161">
         <v>64</v>
@@ -4968,19 +4680,19 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46297.66666666666</v>
+        <v>46299.66666666666</v>
       </c>
       <c r="B162">
-        <v>0.208</v>
+        <v>0</v>
       </c>
       <c r="C162">
-        <v>5.174</v>
+        <v>0</v>
       </c>
       <c r="D162">
         <v>0</v>
       </c>
       <c r="E162">
-        <v>67.5</v>
+        <v>0</v>
       </c>
       <c r="F162">
         <v>65</v>
@@ -4991,19 +4703,19 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46297.67708333334</v>
+        <v>46299.67708333334</v>
       </c>
       <c r="B163">
-        <v>15.355</v>
+        <v>0</v>
       </c>
       <c r="C163">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="D163">
         <v>0</v>
       </c>
       <c r="E163">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="F163">
         <v>66</v>
@@ -5014,10 +4726,10 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46297.6875</v>
+        <v>46299.6875</v>
       </c>
       <c r="B164">
-        <v>29.101</v>
+        <v>0</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -5026,7 +4738,7 @@
         <v>0</v>
       </c>
       <c r="E164">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F164">
         <v>67</v>
@@ -5037,10 +4749,10 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46297.69791666666</v>
+        <v>46299.69791666666</v>
       </c>
       <c r="B165">
-        <v>31.287</v>
+        <v>0</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -5049,7 +4761,7 @@
         <v>0</v>
       </c>
       <c r="E165">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F165">
         <v>68</v>
@@ -5060,10 +4772,10 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46297.70833333334</v>
+        <v>46299.70833333334</v>
       </c>
       <c r="B166">
-        <v>5.239</v>
+        <v>0</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -5072,7 +4784,7 @@
         <v>0</v>
       </c>
       <c r="E166">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F166">
         <v>69</v>
@@ -5083,10 +4795,10 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46297.71875</v>
+        <v>46299.71875</v>
       </c>
       <c r="B167">
-        <v>11.691</v>
+        <v>0</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -5106,13 +4818,13 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46297.72916666666</v>
+        <v>46299.72916666666</v>
       </c>
       <c r="B168">
-        <v>3.369</v>
+        <v>0</v>
       </c>
       <c r="C168">
-        <v>0.433</v>
+        <v>0</v>
       </c>
       <c r="D168">
         <v>0</v>
@@ -5129,13 +4841,13 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46297.73958333334</v>
+        <v>46299.73958333334</v>
       </c>
       <c r="B169">
-        <v>4.853</v>
+        <v>0</v>
       </c>
       <c r="C169">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="D169">
         <v>0</v>
@@ -5152,13 +4864,13 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46297.75</v>
+        <v>46299.75</v>
       </c>
       <c r="B170">
-        <v>0.137</v>
+        <v>0</v>
       </c>
       <c r="C170">
-        <v>0.755</v>
+        <v>0</v>
       </c>
       <c r="D170">
         <v>0</v>
@@ -5175,13 +4887,13 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46297.76041666666</v>
+        <v>46299.76041666666</v>
       </c>
       <c r="B171">
-        <v>0.033</v>
+        <v>0</v>
       </c>
       <c r="C171">
-        <v>3.057</v>
+        <v>0</v>
       </c>
       <c r="D171">
         <v>0</v>
@@ -5198,19 +4910,19 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46297.77083333334</v>
+        <v>46299.77083333334</v>
       </c>
       <c r="B172">
-        <v>0.121</v>
+        <v>0</v>
       </c>
       <c r="C172">
-        <v>1.504</v>
+        <v>0</v>
       </c>
       <c r="D172">
         <v>0</v>
       </c>
       <c r="E172">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F172">
         <v>75</v>
@@ -5221,19 +4933,19 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46297.78125</v>
+        <v>46299.78125</v>
       </c>
       <c r="B173">
-        <v>0.108</v>
+        <v>0</v>
       </c>
       <c r="C173">
-        <v>0.615</v>
+        <v>0</v>
       </c>
       <c r="D173">
         <v>0</v>
       </c>
       <c r="E173">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F173">
         <v>76</v>
@@ -5244,19 +4956,19 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46297.79166666666</v>
+        <v>46299.79166666666</v>
       </c>
       <c r="B174">
-        <v>0.258</v>
+        <v>0</v>
       </c>
       <c r="C174">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="D174">
         <v>0</v>
       </c>
       <c r="E174">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F174">
         <v>77</v>
@@ -5267,10 +4979,10 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46297.80208333334</v>
+        <v>46299.80208333334</v>
       </c>
       <c r="B175">
-        <v>5.931</v>
+        <v>0</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -5279,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="E175">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F175">
         <v>78</v>
@@ -5290,19 +5002,19 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46297.8125</v>
+        <v>46299.8125</v>
       </c>
       <c r="B176">
-        <v>0.544</v>
+        <v>0</v>
       </c>
       <c r="C176">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="D176">
         <v>0</v>
       </c>
       <c r="E176">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F176">
         <v>79</v>
@@ -5313,10 +5025,10 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46297.82291666666</v>
+        <v>46299.82291666666</v>
       </c>
       <c r="B177">
-        <v>5.485</v>
+        <v>0</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -5325,7 +5037,7 @@
         <v>0</v>
       </c>
       <c r="E177">
-        <v>40.25</v>
+        <v>0</v>
       </c>
       <c r="F177">
         <v>80</v>
@@ -5336,10 +5048,10 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46297.83333333334</v>
+        <v>46299.83333333334</v>
       </c>
       <c r="B178">
-        <v>15.646</v>
+        <v>0</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -5348,7 +5060,7 @@
         <v>0</v>
       </c>
       <c r="E178">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F178">
         <v>81</v>
@@ -5359,10 +5071,10 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46297.84375</v>
+        <v>46299.84375</v>
       </c>
       <c r="B179">
-        <v>18.312</v>
+        <v>0</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -5371,7 +5083,7 @@
         <v>0</v>
       </c>
       <c r="E179">
-        <v>46.25</v>
+        <v>0</v>
       </c>
       <c r="F179">
         <v>82</v>
@@ -5382,10 +5094,10 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46297.85416666666</v>
+        <v>46299.85416666666</v>
       </c>
       <c r="B180">
-        <v>14.229</v>
+        <v>0</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -5394,7 +5106,7 @@
         <v>0</v>
       </c>
       <c r="E180">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F180">
         <v>83</v>
@@ -5405,13 +5117,13 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46297.86458333334</v>
+        <v>46299.86458333334</v>
       </c>
       <c r="B181">
-        <v>4.566</v>
+        <v>0</v>
       </c>
       <c r="C181">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="D181">
         <v>0</v>
@@ -5428,13 +5140,13 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46297.875</v>
+        <v>46299.875</v>
       </c>
       <c r="B182">
-        <v>1.866</v>
+        <v>0</v>
       </c>
       <c r="C182">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="D182">
         <v>0</v>
@@ -5451,13 +5163,13 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46297.88541666666</v>
+        <v>46299.88541666666</v>
       </c>
       <c r="B183">
-        <v>1.398</v>
+        <v>0</v>
       </c>
       <c r="C183">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="D183">
         <v>0</v>
@@ -5474,13 +5186,13 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46297.89583333334</v>
+        <v>46299.89583333334</v>
       </c>
       <c r="B184">
-        <v>3.032</v>
+        <v>0</v>
       </c>
       <c r="C184">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D184">
         <v>0</v>
@@ -5497,13 +5209,13 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46297.90625</v>
+        <v>46299.90625</v>
       </c>
       <c r="B185">
-        <v>0.164</v>
+        <v>0</v>
       </c>
       <c r="C185">
-        <v>5.741</v>
+        <v>0</v>
       </c>
       <c r="D185">
         <v>0</v>
@@ -5520,13 +5232,13 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46297.91666666666</v>
+        <v>46299.91666666666</v>
       </c>
       <c r="B186">
-        <v>4.634</v>
+        <v>0</v>
       </c>
       <c r="C186">
-        <v>5.511</v>
+        <v>0</v>
       </c>
       <c r="D186">
         <v>0</v>
@@ -5543,13 +5255,13 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46297.92708333334</v>
+        <v>46299.92708333334</v>
       </c>
       <c r="B187">
-        <v>11.874</v>
+        <v>0</v>
       </c>
       <c r="C187">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="D187">
         <v>0</v>
@@ -5566,13 +5278,13 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46297.9375</v>
+        <v>46299.9375</v>
       </c>
       <c r="B188">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="C188">
-        <v>0.178</v>
+        <v>0</v>
       </c>
       <c r="D188">
         <v>0</v>
@@ -5589,13 +5301,13 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46297.94791666666</v>
+        <v>46299.94791666666</v>
       </c>
       <c r="B189">
-        <v>1.365</v>
+        <v>0</v>
       </c>
       <c r="C189">
-        <v>0.224</v>
+        <v>0</v>
       </c>
       <c r="D189">
         <v>0</v>
@@ -5612,10 +5324,10 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46297.95833333334</v>
+        <v>46299.95833333334</v>
       </c>
       <c r="B190">
-        <v>5.319</v>
+        <v>0</v>
       </c>
       <c r="C190">
         <v>0</v>
@@ -5635,10 +5347,10 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46297.96875</v>
+        <v>46299.96875</v>
       </c>
       <c r="B191">
-        <v>3.109</v>
+        <v>0</v>
       </c>
       <c r="C191">
         <v>0</v>
@@ -5658,13 +5370,13 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46297.97916666666</v>
+        <v>46299.97916666666</v>
       </c>
       <c r="B192">
-        <v>1.459</v>
+        <v>0</v>
       </c>
       <c r="C192">
-        <v>0.305</v>
+        <v>0</v>
       </c>
       <c r="D192">
         <v>0</v>
@@ -5681,13 +5393,13 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46297.98958333334</v>
+        <v>46299.98958333334</v>
       </c>
       <c r="B193">
-        <v>2.143</v>
+        <v>0</v>
       </c>
       <c r="C193">
-        <v>2.379</v>
+        <v>0</v>
       </c>
       <c r="D193">
         <v>0</v>
@@ -5700,2214 +5412,6 @@
       </c>
       <c r="G193" t="s">
         <v>198</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7">
-      <c r="A194" s="2">
-        <v>46298</v>
-      </c>
-      <c r="B194">
-        <v>0.314</v>
-      </c>
-      <c r="C194">
-        <v>2.846</v>
-      </c>
-      <c r="D194">
-        <v>0</v>
-      </c>
-      <c r="E194">
-        <v>0</v>
-      </c>
-      <c r="F194">
-        <v>1</v>
-      </c>
-      <c r="G194" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7">
-      <c r="A195" s="2">
-        <v>46298.01041666666</v>
-      </c>
-      <c r="B195">
-        <v>5.059</v>
-      </c>
-      <c r="C195">
-        <v>0</v>
-      </c>
-      <c r="D195">
-        <v>0</v>
-      </c>
-      <c r="E195">
-        <v>0</v>
-      </c>
-      <c r="F195">
-        <v>2</v>
-      </c>
-      <c r="G195" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7">
-      <c r="A196" s="2">
-        <v>46298.02083333334</v>
-      </c>
-      <c r="B196">
-        <v>1.179</v>
-      </c>
-      <c r="C196">
-        <v>0.113</v>
-      </c>
-      <c r="D196">
-        <v>0</v>
-      </c>
-      <c r="E196">
-        <v>0</v>
-      </c>
-      <c r="F196">
-        <v>3</v>
-      </c>
-      <c r="G196" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7">
-      <c r="A197" s="2">
-        <v>46298.03125</v>
-      </c>
-      <c r="B197">
-        <v>0.572</v>
-      </c>
-      <c r="C197">
-        <v>0.047</v>
-      </c>
-      <c r="D197">
-        <v>0</v>
-      </c>
-      <c r="E197">
-        <v>0</v>
-      </c>
-      <c r="F197">
-        <v>4</v>
-      </c>
-      <c r="G197" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7">
-      <c r="A198" s="2">
-        <v>46298.04166666666</v>
-      </c>
-      <c r="B198">
-        <v>5.326</v>
-      </c>
-      <c r="C198">
-        <v>0</v>
-      </c>
-      <c r="D198">
-        <v>0</v>
-      </c>
-      <c r="E198">
-        <v>0</v>
-      </c>
-      <c r="F198">
-        <v>5</v>
-      </c>
-      <c r="G198" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7">
-      <c r="A199" s="2">
-        <v>46298.05208333334</v>
-      </c>
-      <c r="B199">
-        <v>10.019</v>
-      </c>
-      <c r="C199">
-        <v>0</v>
-      </c>
-      <c r="D199">
-        <v>0</v>
-      </c>
-      <c r="E199">
-        <v>0</v>
-      </c>
-      <c r="F199">
-        <v>6</v>
-      </c>
-      <c r="G199" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7">
-      <c r="A200" s="2">
-        <v>46298.0625</v>
-      </c>
-      <c r="B200">
-        <v>8.893000000000001</v>
-      </c>
-      <c r="C200">
-        <v>0</v>
-      </c>
-      <c r="D200">
-        <v>0</v>
-      </c>
-      <c r="E200">
-        <v>0</v>
-      </c>
-      <c r="F200">
-        <v>7</v>
-      </c>
-      <c r="G200" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7">
-      <c r="A201" s="2">
-        <v>46298.07291666666</v>
-      </c>
-      <c r="B201">
-        <v>0.145</v>
-      </c>
-      <c r="C201">
-        <v>3.152</v>
-      </c>
-      <c r="D201">
-        <v>25</v>
-      </c>
-      <c r="E201">
-        <v>0</v>
-      </c>
-      <c r="F201">
-        <v>8</v>
-      </c>
-      <c r="G201" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7">
-      <c r="A202" s="2">
-        <v>46298.08333333334</v>
-      </c>
-      <c r="B202">
-        <v>9.189</v>
-      </c>
-      <c r="C202">
-        <v>0.291</v>
-      </c>
-      <c r="D202">
-        <v>10</v>
-      </c>
-      <c r="E202">
-        <v>0</v>
-      </c>
-      <c r="F202">
-        <v>9</v>
-      </c>
-      <c r="G202" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7">
-      <c r="A203" s="2">
-        <v>46298.09375</v>
-      </c>
-      <c r="B203">
-        <v>17.425</v>
-      </c>
-      <c r="C203">
-        <v>0</v>
-      </c>
-      <c r="D203">
-        <v>10</v>
-      </c>
-      <c r="E203">
-        <v>0</v>
-      </c>
-      <c r="F203">
-        <v>10</v>
-      </c>
-      <c r="G203" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7">
-      <c r="A204" s="2">
-        <v>46298.10416666666</v>
-      </c>
-      <c r="B204">
-        <v>10.113</v>
-      </c>
-      <c r="C204">
-        <v>1.327</v>
-      </c>
-      <c r="D204">
-        <v>25</v>
-      </c>
-      <c r="E204">
-        <v>0</v>
-      </c>
-      <c r="F204">
-        <v>11</v>
-      </c>
-      <c r="G204" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7">
-      <c r="A205" s="2">
-        <v>46298.11458333334</v>
-      </c>
-      <c r="B205">
-        <v>0</v>
-      </c>
-      <c r="C205">
-        <v>5.623</v>
-      </c>
-      <c r="D205">
-        <v>35</v>
-      </c>
-      <c r="E205">
-        <v>0</v>
-      </c>
-      <c r="F205">
-        <v>12</v>
-      </c>
-      <c r="G205" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7">
-      <c r="A206" s="2">
-        <v>46298.125</v>
-      </c>
-      <c r="B206">
-        <v>13.578</v>
-      </c>
-      <c r="C206">
-        <v>0.645</v>
-      </c>
-      <c r="D206">
-        <v>15</v>
-      </c>
-      <c r="E206">
-        <v>0</v>
-      </c>
-      <c r="F206">
-        <v>13</v>
-      </c>
-      <c r="G206" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7">
-      <c r="A207" s="2">
-        <v>46298.13541666666</v>
-      </c>
-      <c r="B207">
-        <v>36.352</v>
-      </c>
-      <c r="C207">
-        <v>0</v>
-      </c>
-      <c r="D207">
-        <v>15</v>
-      </c>
-      <c r="E207">
-        <v>0</v>
-      </c>
-      <c r="F207">
-        <v>14</v>
-      </c>
-      <c r="G207" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7">
-      <c r="A208" s="2">
-        <v>46298.14583333334</v>
-      </c>
-      <c r="B208">
-        <v>38.244</v>
-      </c>
-      <c r="C208">
-        <v>0</v>
-      </c>
-      <c r="D208">
-        <v>15</v>
-      </c>
-      <c r="E208">
-        <v>0</v>
-      </c>
-      <c r="F208">
-        <v>15</v>
-      </c>
-      <c r="G208" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7">
-      <c r="A209" s="2">
-        <v>46298.15625</v>
-      </c>
-      <c r="B209">
-        <v>23.005</v>
-      </c>
-      <c r="C209">
-        <v>0</v>
-      </c>
-      <c r="D209">
-        <v>0</v>
-      </c>
-      <c r="E209">
-        <v>0</v>
-      </c>
-      <c r="F209">
-        <v>16</v>
-      </c>
-      <c r="G209" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="210" spans="1:7">
-      <c r="A210" s="2">
-        <v>46298.16666666666</v>
-      </c>
-      <c r="B210">
-        <v>23.229</v>
-      </c>
-      <c r="C210">
-        <v>0</v>
-      </c>
-      <c r="D210">
-        <v>0</v>
-      </c>
-      <c r="E210">
-        <v>0</v>
-      </c>
-      <c r="F210">
-        <v>17</v>
-      </c>
-      <c r="G210" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="211" spans="1:7">
-      <c r="A211" s="2">
-        <v>46298.17708333334</v>
-      </c>
-      <c r="B211">
-        <v>7.019</v>
-      </c>
-      <c r="C211">
-        <v>0.326</v>
-      </c>
-      <c r="D211">
-        <v>25</v>
-      </c>
-      <c r="E211">
-        <v>0</v>
-      </c>
-      <c r="F211">
-        <v>18</v>
-      </c>
-      <c r="G211" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="212" spans="1:7">
-      <c r="A212" s="2">
-        <v>46298.1875</v>
-      </c>
-      <c r="B212">
-        <v>2.4</v>
-      </c>
-      <c r="C212">
-        <v>0.434</v>
-      </c>
-      <c r="D212">
-        <v>25</v>
-      </c>
-      <c r="E212">
-        <v>0</v>
-      </c>
-      <c r="F212">
-        <v>19</v>
-      </c>
-      <c r="G212" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="213" spans="1:7">
-      <c r="A213" s="2">
-        <v>46298.19791666666</v>
-      </c>
-      <c r="B213">
-        <v>13.151</v>
-      </c>
-      <c r="C213">
-        <v>0</v>
-      </c>
-      <c r="D213">
-        <v>25</v>
-      </c>
-      <c r="E213">
-        <v>0</v>
-      </c>
-      <c r="F213">
-        <v>20</v>
-      </c>
-      <c r="G213" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="214" spans="1:7">
-      <c r="A214" s="2">
-        <v>46298.20833333334</v>
-      </c>
-      <c r="B214">
-        <v>8.101000000000001</v>
-      </c>
-      <c r="C214">
-        <v>0</v>
-      </c>
-      <c r="D214">
-        <v>21.75</v>
-      </c>
-      <c r="E214">
-        <v>0</v>
-      </c>
-      <c r="F214">
-        <v>21</v>
-      </c>
-      <c r="G214" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="215" spans="1:7">
-      <c r="A215" s="2">
-        <v>46298.21875</v>
-      </c>
-      <c r="B215">
-        <v>2.207</v>
-      </c>
-      <c r="C215">
-        <v>0.008</v>
-      </c>
-      <c r="D215">
-        <v>21.75</v>
-      </c>
-      <c r="E215">
-        <v>0</v>
-      </c>
-      <c r="F215">
-        <v>22</v>
-      </c>
-      <c r="G215" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="216" spans="1:7">
-      <c r="A216" s="2">
-        <v>46298.22916666666</v>
-      </c>
-      <c r="B216">
-        <v>0.089</v>
-      </c>
-      <c r="C216">
-        <v>1.051</v>
-      </c>
-      <c r="D216">
-        <v>25</v>
-      </c>
-      <c r="E216">
-        <v>0</v>
-      </c>
-      <c r="F216">
-        <v>23</v>
-      </c>
-      <c r="G216" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="217" spans="1:7">
-      <c r="A217" s="2">
-        <v>46298.23958333334</v>
-      </c>
-      <c r="B217">
-        <v>0.062</v>
-      </c>
-      <c r="C217">
-        <v>2.089</v>
-      </c>
-      <c r="D217">
-        <v>25</v>
-      </c>
-      <c r="E217">
-        <v>0</v>
-      </c>
-      <c r="F217">
-        <v>24</v>
-      </c>
-      <c r="G217" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7">
-      <c r="A218" s="2">
-        <v>46298.25</v>
-      </c>
-      <c r="B218">
-        <v>13.046</v>
-      </c>
-      <c r="C218">
-        <v>0.105</v>
-      </c>
-      <c r="D218">
-        <v>0</v>
-      </c>
-      <c r="E218">
-        <v>0</v>
-      </c>
-      <c r="F218">
-        <v>25</v>
-      </c>
-      <c r="G218" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7">
-      <c r="A219" s="2">
-        <v>46298.26041666666</v>
-      </c>
-      <c r="B219">
-        <v>8.926</v>
-      </c>
-      <c r="C219">
-        <v>0</v>
-      </c>
-      <c r="D219">
-        <v>0</v>
-      </c>
-      <c r="E219">
-        <v>0</v>
-      </c>
-      <c r="F219">
-        <v>26</v>
-      </c>
-      <c r="G219" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7">
-      <c r="A220" s="2">
-        <v>46298.27083333334</v>
-      </c>
-      <c r="B220">
-        <v>13.632</v>
-      </c>
-      <c r="C220">
-        <v>0</v>
-      </c>
-      <c r="D220">
-        <v>0</v>
-      </c>
-      <c r="E220">
-        <v>0</v>
-      </c>
-      <c r="F220">
-        <v>27</v>
-      </c>
-      <c r="G220" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7">
-      <c r="A221" s="2">
-        <v>46298.28125</v>
-      </c>
-      <c r="B221">
-        <v>9.483000000000001</v>
-      </c>
-      <c r="C221">
-        <v>0</v>
-      </c>
-      <c r="D221">
-        <v>0</v>
-      </c>
-      <c r="E221">
-        <v>0</v>
-      </c>
-      <c r="F221">
-        <v>28</v>
-      </c>
-      <c r="G221" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7">
-      <c r="A222" s="2">
-        <v>46298.29166666666</v>
-      </c>
-      <c r="B222">
-        <v>0.85</v>
-      </c>
-      <c r="C222">
-        <v>0.059</v>
-      </c>
-      <c r="D222">
-        <v>0</v>
-      </c>
-      <c r="E222">
-        <v>0</v>
-      </c>
-      <c r="F222">
-        <v>29</v>
-      </c>
-      <c r="G222" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="223" spans="1:7">
-      <c r="A223" s="2">
-        <v>46298.30208333334</v>
-      </c>
-      <c r="B223">
-        <v>0.274</v>
-      </c>
-      <c r="C223">
-        <v>2.538</v>
-      </c>
-      <c r="D223">
-        <v>0</v>
-      </c>
-      <c r="E223">
-        <v>0</v>
-      </c>
-      <c r="F223">
-        <v>30</v>
-      </c>
-      <c r="G223" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7">
-      <c r="A224" s="2">
-        <v>46298.3125</v>
-      </c>
-      <c r="B224">
-        <v>0</v>
-      </c>
-      <c r="C224">
-        <v>20.359</v>
-      </c>
-      <c r="D224">
-        <v>0</v>
-      </c>
-      <c r="E224">
-        <v>0</v>
-      </c>
-      <c r="F224">
-        <v>31</v>
-      </c>
-      <c r="G224" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7">
-      <c r="A225" s="2">
-        <v>46298.32291666666</v>
-      </c>
-      <c r="B225">
-        <v>0</v>
-      </c>
-      <c r="C225">
-        <v>27.733</v>
-      </c>
-      <c r="D225">
-        <v>0</v>
-      </c>
-      <c r="E225">
-        <v>0</v>
-      </c>
-      <c r="F225">
-        <v>32</v>
-      </c>
-      <c r="G225" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7">
-      <c r="A226" s="2">
-        <v>46298.33333333334</v>
-      </c>
-      <c r="B226">
-        <v>0.054</v>
-      </c>
-      <c r="C226">
-        <v>3.19</v>
-      </c>
-      <c r="D226">
-        <v>0</v>
-      </c>
-      <c r="E226">
-        <v>0</v>
-      </c>
-      <c r="F226">
-        <v>33</v>
-      </c>
-      <c r="G226" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7">
-      <c r="A227" s="2">
-        <v>46298.34375</v>
-      </c>
-      <c r="B227">
-        <v>0</v>
-      </c>
-      <c r="C227">
-        <v>0</v>
-      </c>
-      <c r="D227">
-        <v>0</v>
-      </c>
-      <c r="E227">
-        <v>0</v>
-      </c>
-      <c r="F227">
-        <v>34</v>
-      </c>
-      <c r="G227" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7">
-      <c r="A228" s="2">
-        <v>46298.35416666666</v>
-      </c>
-      <c r="B228">
-        <v>0</v>
-      </c>
-      <c r="C228">
-        <v>0</v>
-      </c>
-      <c r="D228">
-        <v>0</v>
-      </c>
-      <c r="E228">
-        <v>0</v>
-      </c>
-      <c r="F228">
-        <v>35</v>
-      </c>
-      <c r="G228" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7">
-      <c r="A229" s="2">
-        <v>46298.36458333334</v>
-      </c>
-      <c r="B229">
-        <v>0</v>
-      </c>
-      <c r="C229">
-        <v>0</v>
-      </c>
-      <c r="D229">
-        <v>0</v>
-      </c>
-      <c r="E229">
-        <v>0</v>
-      </c>
-      <c r="F229">
-        <v>36</v>
-      </c>
-      <c r="G229" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7">
-      <c r="A230" s="2">
-        <v>46298.375</v>
-      </c>
-      <c r="B230">
-        <v>0</v>
-      </c>
-      <c r="C230">
-        <v>0</v>
-      </c>
-      <c r="D230">
-        <v>0</v>
-      </c>
-      <c r="E230">
-        <v>0</v>
-      </c>
-      <c r="F230">
-        <v>37</v>
-      </c>
-      <c r="G230" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7">
-      <c r="A231" s="2">
-        <v>46298.38541666666</v>
-      </c>
-      <c r="B231">
-        <v>0</v>
-      </c>
-      <c r="C231">
-        <v>0</v>
-      </c>
-      <c r="D231">
-        <v>0</v>
-      </c>
-      <c r="E231">
-        <v>0</v>
-      </c>
-      <c r="F231">
-        <v>38</v>
-      </c>
-      <c r="G231" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7">
-      <c r="A232" s="2">
-        <v>46298.39583333334</v>
-      </c>
-      <c r="B232">
-        <v>0</v>
-      </c>
-      <c r="C232">
-        <v>0</v>
-      </c>
-      <c r="D232">
-        <v>0</v>
-      </c>
-      <c r="E232">
-        <v>0</v>
-      </c>
-      <c r="F232">
-        <v>39</v>
-      </c>
-      <c r="G232" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7">
-      <c r="A233" s="2">
-        <v>46298.40625</v>
-      </c>
-      <c r="B233">
-        <v>0</v>
-      </c>
-      <c r="C233">
-        <v>0</v>
-      </c>
-      <c r="D233">
-        <v>0</v>
-      </c>
-      <c r="E233">
-        <v>0</v>
-      </c>
-      <c r="F233">
-        <v>40</v>
-      </c>
-      <c r="G233" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7">
-      <c r="A234" s="2">
-        <v>46298.41666666666</v>
-      </c>
-      <c r="B234">
-        <v>0</v>
-      </c>
-      <c r="C234">
-        <v>0</v>
-      </c>
-      <c r="D234">
-        <v>0</v>
-      </c>
-      <c r="E234">
-        <v>0</v>
-      </c>
-      <c r="F234">
-        <v>41</v>
-      </c>
-      <c r="G234" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7">
-      <c r="A235" s="2">
-        <v>46298.42708333334</v>
-      </c>
-      <c r="B235">
-        <v>0</v>
-      </c>
-      <c r="C235">
-        <v>0</v>
-      </c>
-      <c r="D235">
-        <v>0</v>
-      </c>
-      <c r="E235">
-        <v>0</v>
-      </c>
-      <c r="F235">
-        <v>42</v>
-      </c>
-      <c r="G235" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7">
-      <c r="A236" s="2">
-        <v>46298.4375</v>
-      </c>
-      <c r="B236">
-        <v>0</v>
-      </c>
-      <c r="C236">
-        <v>0</v>
-      </c>
-      <c r="D236">
-        <v>0</v>
-      </c>
-      <c r="E236">
-        <v>0</v>
-      </c>
-      <c r="F236">
-        <v>43</v>
-      </c>
-      <c r="G236" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7">
-      <c r="A237" s="2">
-        <v>46298.44791666666</v>
-      </c>
-      <c r="B237">
-        <v>0</v>
-      </c>
-      <c r="C237">
-        <v>0</v>
-      </c>
-      <c r="D237">
-        <v>0</v>
-      </c>
-      <c r="E237">
-        <v>0</v>
-      </c>
-      <c r="F237">
-        <v>44</v>
-      </c>
-      <c r="G237" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7">
-      <c r="A238" s="2">
-        <v>46298.45833333334</v>
-      </c>
-      <c r="B238">
-        <v>0</v>
-      </c>
-      <c r="C238">
-        <v>0</v>
-      </c>
-      <c r="D238">
-        <v>0</v>
-      </c>
-      <c r="E238">
-        <v>0</v>
-      </c>
-      <c r="F238">
-        <v>45</v>
-      </c>
-      <c r="G238" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7">
-      <c r="A239" s="2">
-        <v>46298.46875</v>
-      </c>
-      <c r="B239">
-        <v>0</v>
-      </c>
-      <c r="C239">
-        <v>0</v>
-      </c>
-      <c r="D239">
-        <v>0</v>
-      </c>
-      <c r="E239">
-        <v>0</v>
-      </c>
-      <c r="F239">
-        <v>46</v>
-      </c>
-      <c r="G239" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7">
-      <c r="A240" s="2">
-        <v>46298.47916666666</v>
-      </c>
-      <c r="B240">
-        <v>0</v>
-      </c>
-      <c r="C240">
-        <v>0</v>
-      </c>
-      <c r="D240">
-        <v>0</v>
-      </c>
-      <c r="E240">
-        <v>0</v>
-      </c>
-      <c r="F240">
-        <v>47</v>
-      </c>
-      <c r="G240" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="241" spans="1:7">
-      <c r="A241" s="2">
-        <v>46298.48958333334</v>
-      </c>
-      <c r="B241">
-        <v>0</v>
-      </c>
-      <c r="C241">
-        <v>0</v>
-      </c>
-      <c r="D241">
-        <v>0</v>
-      </c>
-      <c r="E241">
-        <v>0</v>
-      </c>
-      <c r="F241">
-        <v>48</v>
-      </c>
-      <c r="G241" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="242" spans="1:7">
-      <c r="A242" s="2">
-        <v>46298.5</v>
-      </c>
-      <c r="B242">
-        <v>0</v>
-      </c>
-      <c r="C242">
-        <v>0</v>
-      </c>
-      <c r="D242">
-        <v>0</v>
-      </c>
-      <c r="E242">
-        <v>0</v>
-      </c>
-      <c r="F242">
-        <v>49</v>
-      </c>
-      <c r="G242" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="243" spans="1:7">
-      <c r="A243" s="2">
-        <v>46298.51041666666</v>
-      </c>
-      <c r="B243">
-        <v>0</v>
-      </c>
-      <c r="C243">
-        <v>0</v>
-      </c>
-      <c r="D243">
-        <v>0</v>
-      </c>
-      <c r="E243">
-        <v>0</v>
-      </c>
-      <c r="F243">
-        <v>50</v>
-      </c>
-      <c r="G243" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="244" spans="1:7">
-      <c r="A244" s="2">
-        <v>46298.52083333334</v>
-      </c>
-      <c r="B244">
-        <v>0</v>
-      </c>
-      <c r="C244">
-        <v>0</v>
-      </c>
-      <c r="D244">
-        <v>0</v>
-      </c>
-      <c r="E244">
-        <v>0</v>
-      </c>
-      <c r="F244">
-        <v>51</v>
-      </c>
-      <c r="G244" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="245" spans="1:7">
-      <c r="A245" s="2">
-        <v>46298.53125</v>
-      </c>
-      <c r="B245">
-        <v>0</v>
-      </c>
-      <c r="C245">
-        <v>0</v>
-      </c>
-      <c r="D245">
-        <v>0</v>
-      </c>
-      <c r="E245">
-        <v>0</v>
-      </c>
-      <c r="F245">
-        <v>52</v>
-      </c>
-      <c r="G245" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="246" spans="1:7">
-      <c r="A246" s="2">
-        <v>46298.54166666666</v>
-      </c>
-      <c r="B246">
-        <v>0</v>
-      </c>
-      <c r="C246">
-        <v>0</v>
-      </c>
-      <c r="D246">
-        <v>0</v>
-      </c>
-      <c r="E246">
-        <v>0</v>
-      </c>
-      <c r="F246">
-        <v>53</v>
-      </c>
-      <c r="G246" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7">
-      <c r="A247" s="2">
-        <v>46298.55208333334</v>
-      </c>
-      <c r="B247">
-        <v>0</v>
-      </c>
-      <c r="C247">
-        <v>0</v>
-      </c>
-      <c r="D247">
-        <v>0</v>
-      </c>
-      <c r="E247">
-        <v>0</v>
-      </c>
-      <c r="F247">
-        <v>54</v>
-      </c>
-      <c r="G247" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7">
-      <c r="A248" s="2">
-        <v>46298.5625</v>
-      </c>
-      <c r="B248">
-        <v>0</v>
-      </c>
-      <c r="C248">
-        <v>0</v>
-      </c>
-      <c r="D248">
-        <v>0</v>
-      </c>
-      <c r="E248">
-        <v>0</v>
-      </c>
-      <c r="F248">
-        <v>55</v>
-      </c>
-      <c r="G248" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="249" spans="1:7">
-      <c r="A249" s="2">
-        <v>46298.57291666666</v>
-      </c>
-      <c r="B249">
-        <v>0</v>
-      </c>
-      <c r="C249">
-        <v>0</v>
-      </c>
-      <c r="D249">
-        <v>0</v>
-      </c>
-      <c r="E249">
-        <v>0</v>
-      </c>
-      <c r="F249">
-        <v>56</v>
-      </c>
-      <c r="G249" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7">
-      <c r="A250" s="2">
-        <v>46298.58333333334</v>
-      </c>
-      <c r="B250">
-        <v>0</v>
-      </c>
-      <c r="C250">
-        <v>0</v>
-      </c>
-      <c r="D250">
-        <v>0</v>
-      </c>
-      <c r="E250">
-        <v>0</v>
-      </c>
-      <c r="F250">
-        <v>57</v>
-      </c>
-      <c r="G250" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7">
-      <c r="A251" s="2">
-        <v>46298.59375</v>
-      </c>
-      <c r="B251">
-        <v>0</v>
-      </c>
-      <c r="C251">
-        <v>0</v>
-      </c>
-      <c r="D251">
-        <v>0</v>
-      </c>
-      <c r="E251">
-        <v>0</v>
-      </c>
-      <c r="F251">
-        <v>58</v>
-      </c>
-      <c r="G251" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="252" spans="1:7">
-      <c r="A252" s="2">
-        <v>46298.60416666666</v>
-      </c>
-      <c r="B252">
-        <v>0</v>
-      </c>
-      <c r="C252">
-        <v>0</v>
-      </c>
-      <c r="D252">
-        <v>0</v>
-      </c>
-      <c r="E252">
-        <v>0</v>
-      </c>
-      <c r="F252">
-        <v>59</v>
-      </c>
-      <c r="G252" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7">
-      <c r="A253" s="2">
-        <v>46298.61458333334</v>
-      </c>
-      <c r="B253">
-        <v>0</v>
-      </c>
-      <c r="C253">
-        <v>0</v>
-      </c>
-      <c r="D253">
-        <v>0</v>
-      </c>
-      <c r="E253">
-        <v>0</v>
-      </c>
-      <c r="F253">
-        <v>60</v>
-      </c>
-      <c r="G253" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7">
-      <c r="A254" s="2">
-        <v>46298.625</v>
-      </c>
-      <c r="B254">
-        <v>0</v>
-      </c>
-      <c r="C254">
-        <v>0</v>
-      </c>
-      <c r="D254">
-        <v>0</v>
-      </c>
-      <c r="E254">
-        <v>0</v>
-      </c>
-      <c r="F254">
-        <v>61</v>
-      </c>
-      <c r="G254" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7">
-      <c r="A255" s="2">
-        <v>46298.63541666666</v>
-      </c>
-      <c r="B255">
-        <v>0</v>
-      </c>
-      <c r="C255">
-        <v>0</v>
-      </c>
-      <c r="D255">
-        <v>0</v>
-      </c>
-      <c r="E255">
-        <v>0</v>
-      </c>
-      <c r="F255">
-        <v>62</v>
-      </c>
-      <c r="G255" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7">
-      <c r="A256" s="2">
-        <v>46298.64583333334</v>
-      </c>
-      <c r="B256">
-        <v>0</v>
-      </c>
-      <c r="C256">
-        <v>0</v>
-      </c>
-      <c r="D256">
-        <v>0</v>
-      </c>
-      <c r="E256">
-        <v>0</v>
-      </c>
-      <c r="F256">
-        <v>63</v>
-      </c>
-      <c r="G256" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7">
-      <c r="A257" s="2">
-        <v>46298.65625</v>
-      </c>
-      <c r="B257">
-        <v>0</v>
-      </c>
-      <c r="C257">
-        <v>0</v>
-      </c>
-      <c r="D257">
-        <v>0</v>
-      </c>
-      <c r="E257">
-        <v>0</v>
-      </c>
-      <c r="F257">
-        <v>64</v>
-      </c>
-      <c r="G257" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7">
-      <c r="A258" s="2">
-        <v>46298.66666666666</v>
-      </c>
-      <c r="B258">
-        <v>0</v>
-      </c>
-      <c r="C258">
-        <v>0</v>
-      </c>
-      <c r="D258">
-        <v>0</v>
-      </c>
-      <c r="E258">
-        <v>0</v>
-      </c>
-      <c r="F258">
-        <v>65</v>
-      </c>
-      <c r="G258" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7">
-      <c r="A259" s="2">
-        <v>46298.67708333334</v>
-      </c>
-      <c r="B259">
-        <v>0</v>
-      </c>
-      <c r="C259">
-        <v>0</v>
-      </c>
-      <c r="D259">
-        <v>0</v>
-      </c>
-      <c r="E259">
-        <v>0</v>
-      </c>
-      <c r="F259">
-        <v>66</v>
-      </c>
-      <c r="G259" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7">
-      <c r="A260" s="2">
-        <v>46298.6875</v>
-      </c>
-      <c r="B260">
-        <v>0</v>
-      </c>
-      <c r="C260">
-        <v>0</v>
-      </c>
-      <c r="D260">
-        <v>0</v>
-      </c>
-      <c r="E260">
-        <v>0</v>
-      </c>
-      <c r="F260">
-        <v>67</v>
-      </c>
-      <c r="G260" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7">
-      <c r="A261" s="2">
-        <v>46298.69791666666</v>
-      </c>
-      <c r="B261">
-        <v>0</v>
-      </c>
-      <c r="C261">
-        <v>0</v>
-      </c>
-      <c r="D261">
-        <v>0</v>
-      </c>
-      <c r="E261">
-        <v>0</v>
-      </c>
-      <c r="F261">
-        <v>68</v>
-      </c>
-      <c r="G261" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7">
-      <c r="A262" s="2">
-        <v>46298.70833333334</v>
-      </c>
-      <c r="B262">
-        <v>0</v>
-      </c>
-      <c r="C262">
-        <v>0</v>
-      </c>
-      <c r="D262">
-        <v>0</v>
-      </c>
-      <c r="E262">
-        <v>0</v>
-      </c>
-      <c r="F262">
-        <v>69</v>
-      </c>
-      <c r="G262" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7">
-      <c r="A263" s="2">
-        <v>46298.71875</v>
-      </c>
-      <c r="B263">
-        <v>0</v>
-      </c>
-      <c r="C263">
-        <v>0</v>
-      </c>
-      <c r="D263">
-        <v>0</v>
-      </c>
-      <c r="E263">
-        <v>0</v>
-      </c>
-      <c r="F263">
-        <v>70</v>
-      </c>
-      <c r="G263" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7">
-      <c r="A264" s="2">
-        <v>46298.72916666666</v>
-      </c>
-      <c r="B264">
-        <v>0</v>
-      </c>
-      <c r="C264">
-        <v>0</v>
-      </c>
-      <c r="D264">
-        <v>0</v>
-      </c>
-      <c r="E264">
-        <v>0</v>
-      </c>
-      <c r="F264">
-        <v>71</v>
-      </c>
-      <c r="G264" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7">
-      <c r="A265" s="2">
-        <v>46298.73958333334</v>
-      </c>
-      <c r="B265">
-        <v>0</v>
-      </c>
-      <c r="C265">
-        <v>0</v>
-      </c>
-      <c r="D265">
-        <v>0</v>
-      </c>
-      <c r="E265">
-        <v>0</v>
-      </c>
-      <c r="F265">
-        <v>72</v>
-      </c>
-      <c r="G265" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7">
-      <c r="A266" s="2">
-        <v>46298.75</v>
-      </c>
-      <c r="B266">
-        <v>0</v>
-      </c>
-      <c r="C266">
-        <v>0</v>
-      </c>
-      <c r="D266">
-        <v>0</v>
-      </c>
-      <c r="E266">
-        <v>0</v>
-      </c>
-      <c r="F266">
-        <v>73</v>
-      </c>
-      <c r="G266" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7">
-      <c r="A267" s="2">
-        <v>46298.76041666666</v>
-      </c>
-      <c r="B267">
-        <v>0</v>
-      </c>
-      <c r="C267">
-        <v>0</v>
-      </c>
-      <c r="D267">
-        <v>0</v>
-      </c>
-      <c r="E267">
-        <v>0</v>
-      </c>
-      <c r="F267">
-        <v>74</v>
-      </c>
-      <c r="G267" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7">
-      <c r="A268" s="2">
-        <v>46298.77083333334</v>
-      </c>
-      <c r="B268">
-        <v>0</v>
-      </c>
-      <c r="C268">
-        <v>0</v>
-      </c>
-      <c r="D268">
-        <v>0</v>
-      </c>
-      <c r="E268">
-        <v>0</v>
-      </c>
-      <c r="F268">
-        <v>75</v>
-      </c>
-      <c r="G268" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7">
-      <c r="A269" s="2">
-        <v>46298.78125</v>
-      </c>
-      <c r="B269">
-        <v>0</v>
-      </c>
-      <c r="C269">
-        <v>0</v>
-      </c>
-      <c r="D269">
-        <v>0</v>
-      </c>
-      <c r="E269">
-        <v>0</v>
-      </c>
-      <c r="F269">
-        <v>76</v>
-      </c>
-      <c r="G269" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7">
-      <c r="A270" s="2">
-        <v>46298.79166666666</v>
-      </c>
-      <c r="B270">
-        <v>0</v>
-      </c>
-      <c r="C270">
-        <v>0</v>
-      </c>
-      <c r="D270">
-        <v>0</v>
-      </c>
-      <c r="E270">
-        <v>0</v>
-      </c>
-      <c r="F270">
-        <v>77</v>
-      </c>
-      <c r="G270" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7">
-      <c r="A271" s="2">
-        <v>46298.80208333334</v>
-      </c>
-      <c r="B271">
-        <v>0</v>
-      </c>
-      <c r="C271">
-        <v>0</v>
-      </c>
-      <c r="D271">
-        <v>0</v>
-      </c>
-      <c r="E271">
-        <v>0</v>
-      </c>
-      <c r="F271">
-        <v>78</v>
-      </c>
-      <c r="G271" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7">
-      <c r="A272" s="2">
-        <v>46298.8125</v>
-      </c>
-      <c r="B272">
-        <v>0</v>
-      </c>
-      <c r="C272">
-        <v>0</v>
-      </c>
-      <c r="D272">
-        <v>0</v>
-      </c>
-      <c r="E272">
-        <v>0</v>
-      </c>
-      <c r="F272">
-        <v>79</v>
-      </c>
-      <c r="G272" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="273" spans="1:7">
-      <c r="A273" s="2">
-        <v>46298.82291666666</v>
-      </c>
-      <c r="B273">
-        <v>0</v>
-      </c>
-      <c r="C273">
-        <v>0</v>
-      </c>
-      <c r="D273">
-        <v>0</v>
-      </c>
-      <c r="E273">
-        <v>0</v>
-      </c>
-      <c r="F273">
-        <v>80</v>
-      </c>
-      <c r="G273" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7">
-      <c r="A274" s="2">
-        <v>46298.83333333334</v>
-      </c>
-      <c r="B274">
-        <v>0</v>
-      </c>
-      <c r="C274">
-        <v>0</v>
-      </c>
-      <c r="D274">
-        <v>0</v>
-      </c>
-      <c r="E274">
-        <v>0</v>
-      </c>
-      <c r="F274">
-        <v>81</v>
-      </c>
-      <c r="G274" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7">
-      <c r="A275" s="2">
-        <v>46298.84375</v>
-      </c>
-      <c r="B275">
-        <v>0</v>
-      </c>
-      <c r="C275">
-        <v>0</v>
-      </c>
-      <c r="D275">
-        <v>0</v>
-      </c>
-      <c r="E275">
-        <v>0</v>
-      </c>
-      <c r="F275">
-        <v>82</v>
-      </c>
-      <c r="G275" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7">
-      <c r="A276" s="2">
-        <v>46298.85416666666</v>
-      </c>
-      <c r="B276">
-        <v>0</v>
-      </c>
-      <c r="C276">
-        <v>0</v>
-      </c>
-      <c r="D276">
-        <v>0</v>
-      </c>
-      <c r="E276">
-        <v>0</v>
-      </c>
-      <c r="F276">
-        <v>83</v>
-      </c>
-      <c r="G276" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7">
-      <c r="A277" s="2">
-        <v>46298.86458333334</v>
-      </c>
-      <c r="B277">
-        <v>0</v>
-      </c>
-      <c r="C277">
-        <v>0</v>
-      </c>
-      <c r="D277">
-        <v>0</v>
-      </c>
-      <c r="E277">
-        <v>0</v>
-      </c>
-      <c r="F277">
-        <v>84</v>
-      </c>
-      <c r="G277" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7">
-      <c r="A278" s="2">
-        <v>46298.875</v>
-      </c>
-      <c r="B278">
-        <v>0</v>
-      </c>
-      <c r="C278">
-        <v>0</v>
-      </c>
-      <c r="D278">
-        <v>0</v>
-      </c>
-      <c r="E278">
-        <v>0</v>
-      </c>
-      <c r="F278">
-        <v>85</v>
-      </c>
-      <c r="G278" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7">
-      <c r="A279" s="2">
-        <v>46298.88541666666</v>
-      </c>
-      <c r="B279">
-        <v>0</v>
-      </c>
-      <c r="C279">
-        <v>0</v>
-      </c>
-      <c r="D279">
-        <v>0</v>
-      </c>
-      <c r="E279">
-        <v>0</v>
-      </c>
-      <c r="F279">
-        <v>86</v>
-      </c>
-      <c r="G279" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7">
-      <c r="A280" s="2">
-        <v>46298.89583333334</v>
-      </c>
-      <c r="B280">
-        <v>0</v>
-      </c>
-      <c r="C280">
-        <v>0</v>
-      </c>
-      <c r="D280">
-        <v>0</v>
-      </c>
-      <c r="E280">
-        <v>0</v>
-      </c>
-      <c r="F280">
-        <v>87</v>
-      </c>
-      <c r="G280" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7">
-      <c r="A281" s="2">
-        <v>46298.90625</v>
-      </c>
-      <c r="B281">
-        <v>0</v>
-      </c>
-      <c r="C281">
-        <v>0</v>
-      </c>
-      <c r="D281">
-        <v>0</v>
-      </c>
-      <c r="E281">
-        <v>0</v>
-      </c>
-      <c r="F281">
-        <v>88</v>
-      </c>
-      <c r="G281" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7">
-      <c r="A282" s="2">
-        <v>46298.91666666666</v>
-      </c>
-      <c r="B282">
-        <v>0</v>
-      </c>
-      <c r="C282">
-        <v>0</v>
-      </c>
-      <c r="D282">
-        <v>0</v>
-      </c>
-      <c r="E282">
-        <v>0</v>
-      </c>
-      <c r="F282">
-        <v>89</v>
-      </c>
-      <c r="G282" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7">
-      <c r="A283" s="2">
-        <v>46298.92708333334</v>
-      </c>
-      <c r="B283">
-        <v>0</v>
-      </c>
-      <c r="C283">
-        <v>0</v>
-      </c>
-      <c r="D283">
-        <v>0</v>
-      </c>
-      <c r="E283">
-        <v>0</v>
-      </c>
-      <c r="F283">
-        <v>90</v>
-      </c>
-      <c r="G283" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7">
-      <c r="A284" s="2">
-        <v>46298.9375</v>
-      </c>
-      <c r="B284">
-        <v>0</v>
-      </c>
-      <c r="C284">
-        <v>0</v>
-      </c>
-      <c r="D284">
-        <v>0</v>
-      </c>
-      <c r="E284">
-        <v>0</v>
-      </c>
-      <c r="F284">
-        <v>91</v>
-      </c>
-      <c r="G284" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="285" spans="1:7">
-      <c r="A285" s="2">
-        <v>46298.94791666666</v>
-      </c>
-      <c r="B285">
-        <v>0</v>
-      </c>
-      <c r="C285">
-        <v>0</v>
-      </c>
-      <c r="D285">
-        <v>0</v>
-      </c>
-      <c r="E285">
-        <v>0</v>
-      </c>
-      <c r="F285">
-        <v>92</v>
-      </c>
-      <c r="G285" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7">
-      <c r="A286" s="2">
-        <v>46298.95833333334</v>
-      </c>
-      <c r="B286">
-        <v>0</v>
-      </c>
-      <c r="C286">
-        <v>0</v>
-      </c>
-      <c r="D286">
-        <v>0</v>
-      </c>
-      <c r="E286">
-        <v>0</v>
-      </c>
-      <c r="F286">
-        <v>93</v>
-      </c>
-      <c r="G286" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7">
-      <c r="A287" s="2">
-        <v>46298.96875</v>
-      </c>
-      <c r="B287">
-        <v>0</v>
-      </c>
-      <c r="C287">
-        <v>0</v>
-      </c>
-      <c r="D287">
-        <v>0</v>
-      </c>
-      <c r="E287">
-        <v>0</v>
-      </c>
-      <c r="F287">
-        <v>94</v>
-      </c>
-      <c r="G287" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="288" spans="1:7">
-      <c r="A288" s="2">
-        <v>46298.97916666666</v>
-      </c>
-      <c r="B288">
-        <v>0</v>
-      </c>
-      <c r="C288">
-        <v>0</v>
-      </c>
-      <c r="D288">
-        <v>0</v>
-      </c>
-      <c r="E288">
-        <v>0</v>
-      </c>
-      <c r="F288">
-        <v>95</v>
-      </c>
-      <c r="G288" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7">
-      <c r="A289" s="2">
-        <v>46298.98958333334</v>
-      </c>
-      <c r="B289">
-        <v>0</v>
-      </c>
-      <c r="C289">
-        <v>0</v>
-      </c>
-      <c r="D289">
-        <v>0</v>
-      </c>
-      <c r="E289">
-        <v>0</v>
-      </c>
-      <c r="F289">
-        <v>96</v>
-      </c>
-      <c r="G289" t="s">
-        <v>294</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="487">
   <si>
     <t>Timestamp (CET)</t>
   </si>
@@ -611,6 +611,870 @@
   </si>
   <si>
     <t>04.10.202696</t>
+  </si>
+  <si>
+    <t>05.10.20261</t>
+  </si>
+  <si>
+    <t>05.10.20262</t>
+  </si>
+  <si>
+    <t>05.10.20263</t>
+  </si>
+  <si>
+    <t>05.10.20264</t>
+  </si>
+  <si>
+    <t>05.10.20265</t>
+  </si>
+  <si>
+    <t>05.10.20266</t>
+  </si>
+  <si>
+    <t>05.10.20267</t>
+  </si>
+  <si>
+    <t>05.10.20268</t>
+  </si>
+  <si>
+    <t>05.10.20269</t>
+  </si>
+  <si>
+    <t>05.10.202610</t>
+  </si>
+  <si>
+    <t>05.10.202611</t>
+  </si>
+  <si>
+    <t>05.10.202612</t>
+  </si>
+  <si>
+    <t>05.10.202613</t>
+  </si>
+  <si>
+    <t>05.10.202614</t>
+  </si>
+  <si>
+    <t>05.10.202615</t>
+  </si>
+  <si>
+    <t>05.10.202616</t>
+  </si>
+  <si>
+    <t>05.10.202617</t>
+  </si>
+  <si>
+    <t>05.10.202618</t>
+  </si>
+  <si>
+    <t>05.10.202619</t>
+  </si>
+  <si>
+    <t>05.10.202620</t>
+  </si>
+  <si>
+    <t>05.10.202621</t>
+  </si>
+  <si>
+    <t>05.10.202622</t>
+  </si>
+  <si>
+    <t>05.10.202623</t>
+  </si>
+  <si>
+    <t>05.10.202624</t>
+  </si>
+  <si>
+    <t>05.10.202625</t>
+  </si>
+  <si>
+    <t>05.10.202626</t>
+  </si>
+  <si>
+    <t>05.10.202627</t>
+  </si>
+  <si>
+    <t>05.10.202628</t>
+  </si>
+  <si>
+    <t>05.10.202629</t>
+  </si>
+  <si>
+    <t>05.10.202630</t>
+  </si>
+  <si>
+    <t>05.10.202631</t>
+  </si>
+  <si>
+    <t>05.10.202632</t>
+  </si>
+  <si>
+    <t>05.10.202633</t>
+  </si>
+  <si>
+    <t>05.10.202634</t>
+  </si>
+  <si>
+    <t>05.10.202635</t>
+  </si>
+  <si>
+    <t>05.10.202636</t>
+  </si>
+  <si>
+    <t>05.10.202637</t>
+  </si>
+  <si>
+    <t>05.10.202638</t>
+  </si>
+  <si>
+    <t>05.10.202639</t>
+  </si>
+  <si>
+    <t>05.10.202640</t>
+  </si>
+  <si>
+    <t>05.10.202641</t>
+  </si>
+  <si>
+    <t>05.10.202642</t>
+  </si>
+  <si>
+    <t>05.10.202643</t>
+  </si>
+  <si>
+    <t>05.10.202644</t>
+  </si>
+  <si>
+    <t>05.10.202645</t>
+  </si>
+  <si>
+    <t>05.10.202646</t>
+  </si>
+  <si>
+    <t>05.10.202647</t>
+  </si>
+  <si>
+    <t>05.10.202648</t>
+  </si>
+  <si>
+    <t>05.10.202649</t>
+  </si>
+  <si>
+    <t>05.10.202650</t>
+  </si>
+  <si>
+    <t>05.10.202651</t>
+  </si>
+  <si>
+    <t>05.10.202652</t>
+  </si>
+  <si>
+    <t>05.10.202653</t>
+  </si>
+  <si>
+    <t>05.10.202654</t>
+  </si>
+  <si>
+    <t>05.10.202655</t>
+  </si>
+  <si>
+    <t>05.10.202656</t>
+  </si>
+  <si>
+    <t>05.10.202657</t>
+  </si>
+  <si>
+    <t>05.10.202658</t>
+  </si>
+  <si>
+    <t>05.10.202659</t>
+  </si>
+  <si>
+    <t>05.10.202660</t>
+  </si>
+  <si>
+    <t>05.10.202661</t>
+  </si>
+  <si>
+    <t>05.10.202662</t>
+  </si>
+  <si>
+    <t>05.10.202663</t>
+  </si>
+  <si>
+    <t>05.10.202664</t>
+  </si>
+  <si>
+    <t>05.10.202665</t>
+  </si>
+  <si>
+    <t>05.10.202666</t>
+  </si>
+  <si>
+    <t>05.10.202667</t>
+  </si>
+  <si>
+    <t>05.10.202668</t>
+  </si>
+  <si>
+    <t>05.10.202669</t>
+  </si>
+  <si>
+    <t>05.10.202670</t>
+  </si>
+  <si>
+    <t>05.10.202671</t>
+  </si>
+  <si>
+    <t>05.10.202672</t>
+  </si>
+  <si>
+    <t>05.10.202673</t>
+  </si>
+  <si>
+    <t>05.10.202674</t>
+  </si>
+  <si>
+    <t>05.10.202675</t>
+  </si>
+  <si>
+    <t>05.10.202676</t>
+  </si>
+  <si>
+    <t>05.10.202677</t>
+  </si>
+  <si>
+    <t>05.10.202678</t>
+  </si>
+  <si>
+    <t>05.10.202679</t>
+  </si>
+  <si>
+    <t>05.10.202680</t>
+  </si>
+  <si>
+    <t>05.10.202681</t>
+  </si>
+  <si>
+    <t>05.10.202682</t>
+  </si>
+  <si>
+    <t>05.10.202683</t>
+  </si>
+  <si>
+    <t>05.10.202684</t>
+  </si>
+  <si>
+    <t>05.10.202685</t>
+  </si>
+  <si>
+    <t>05.10.202686</t>
+  </si>
+  <si>
+    <t>05.10.202687</t>
+  </si>
+  <si>
+    <t>05.10.202688</t>
+  </si>
+  <si>
+    <t>05.10.202689</t>
+  </si>
+  <si>
+    <t>05.10.202690</t>
+  </si>
+  <si>
+    <t>05.10.202691</t>
+  </si>
+  <si>
+    <t>05.10.202692</t>
+  </si>
+  <si>
+    <t>05.10.202693</t>
+  </si>
+  <si>
+    <t>05.10.202694</t>
+  </si>
+  <si>
+    <t>05.10.202695</t>
+  </si>
+  <si>
+    <t>05.10.202696</t>
+  </si>
+  <si>
+    <t>06.10.20261</t>
+  </si>
+  <si>
+    <t>06.10.20262</t>
+  </si>
+  <si>
+    <t>06.10.20263</t>
+  </si>
+  <si>
+    <t>06.10.20264</t>
+  </si>
+  <si>
+    <t>06.10.20265</t>
+  </si>
+  <si>
+    <t>06.10.20266</t>
+  </si>
+  <si>
+    <t>06.10.20267</t>
+  </si>
+  <si>
+    <t>06.10.20268</t>
+  </si>
+  <si>
+    <t>06.10.20269</t>
+  </si>
+  <si>
+    <t>06.10.202610</t>
+  </si>
+  <si>
+    <t>06.10.202611</t>
+  </si>
+  <si>
+    <t>06.10.202612</t>
+  </si>
+  <si>
+    <t>06.10.202613</t>
+  </si>
+  <si>
+    <t>06.10.202614</t>
+  </si>
+  <si>
+    <t>06.10.202615</t>
+  </si>
+  <si>
+    <t>06.10.202616</t>
+  </si>
+  <si>
+    <t>06.10.202617</t>
+  </si>
+  <si>
+    <t>06.10.202618</t>
+  </si>
+  <si>
+    <t>06.10.202619</t>
+  </si>
+  <si>
+    <t>06.10.202620</t>
+  </si>
+  <si>
+    <t>06.10.202621</t>
+  </si>
+  <si>
+    <t>06.10.202622</t>
+  </si>
+  <si>
+    <t>06.10.202623</t>
+  </si>
+  <si>
+    <t>06.10.202624</t>
+  </si>
+  <si>
+    <t>06.10.202625</t>
+  </si>
+  <si>
+    <t>06.10.202626</t>
+  </si>
+  <si>
+    <t>06.10.202627</t>
+  </si>
+  <si>
+    <t>06.10.202628</t>
+  </si>
+  <si>
+    <t>06.10.202629</t>
+  </si>
+  <si>
+    <t>06.10.202630</t>
+  </si>
+  <si>
+    <t>06.10.202631</t>
+  </si>
+  <si>
+    <t>06.10.202632</t>
+  </si>
+  <si>
+    <t>06.10.202633</t>
+  </si>
+  <si>
+    <t>06.10.202634</t>
+  </si>
+  <si>
+    <t>06.10.202635</t>
+  </si>
+  <si>
+    <t>06.10.202636</t>
+  </si>
+  <si>
+    <t>06.10.202637</t>
+  </si>
+  <si>
+    <t>06.10.202638</t>
+  </si>
+  <si>
+    <t>06.10.202639</t>
+  </si>
+  <si>
+    <t>06.10.202640</t>
+  </si>
+  <si>
+    <t>06.10.202641</t>
+  </si>
+  <si>
+    <t>06.10.202642</t>
+  </si>
+  <si>
+    <t>06.10.202643</t>
+  </si>
+  <si>
+    <t>06.10.202644</t>
+  </si>
+  <si>
+    <t>06.10.202645</t>
+  </si>
+  <si>
+    <t>06.10.202646</t>
+  </si>
+  <si>
+    <t>06.10.202647</t>
+  </si>
+  <si>
+    <t>06.10.202648</t>
+  </si>
+  <si>
+    <t>06.10.202649</t>
+  </si>
+  <si>
+    <t>06.10.202650</t>
+  </si>
+  <si>
+    <t>06.10.202651</t>
+  </si>
+  <si>
+    <t>06.10.202652</t>
+  </si>
+  <si>
+    <t>06.10.202653</t>
+  </si>
+  <si>
+    <t>06.10.202654</t>
+  </si>
+  <si>
+    <t>06.10.202655</t>
+  </si>
+  <si>
+    <t>06.10.202656</t>
+  </si>
+  <si>
+    <t>06.10.202657</t>
+  </si>
+  <si>
+    <t>06.10.202658</t>
+  </si>
+  <si>
+    <t>06.10.202659</t>
+  </si>
+  <si>
+    <t>06.10.202660</t>
+  </si>
+  <si>
+    <t>06.10.202661</t>
+  </si>
+  <si>
+    <t>06.10.202662</t>
+  </si>
+  <si>
+    <t>06.10.202663</t>
+  </si>
+  <si>
+    <t>06.10.202664</t>
+  </si>
+  <si>
+    <t>06.10.202665</t>
+  </si>
+  <si>
+    <t>06.10.202666</t>
+  </si>
+  <si>
+    <t>06.10.202667</t>
+  </si>
+  <si>
+    <t>06.10.202668</t>
+  </si>
+  <si>
+    <t>06.10.202669</t>
+  </si>
+  <si>
+    <t>06.10.202670</t>
+  </si>
+  <si>
+    <t>06.10.202671</t>
+  </si>
+  <si>
+    <t>06.10.202672</t>
+  </si>
+  <si>
+    <t>06.10.202673</t>
+  </si>
+  <si>
+    <t>06.10.202674</t>
+  </si>
+  <si>
+    <t>06.10.202675</t>
+  </si>
+  <si>
+    <t>06.10.202676</t>
+  </si>
+  <si>
+    <t>06.10.202677</t>
+  </si>
+  <si>
+    <t>06.10.202678</t>
+  </si>
+  <si>
+    <t>06.10.202679</t>
+  </si>
+  <si>
+    <t>06.10.202680</t>
+  </si>
+  <si>
+    <t>06.10.202681</t>
+  </si>
+  <si>
+    <t>06.10.202682</t>
+  </si>
+  <si>
+    <t>06.10.202683</t>
+  </si>
+  <si>
+    <t>06.10.202684</t>
+  </si>
+  <si>
+    <t>06.10.202685</t>
+  </si>
+  <si>
+    <t>06.10.202686</t>
+  </si>
+  <si>
+    <t>06.10.202687</t>
+  </si>
+  <si>
+    <t>06.10.202688</t>
+  </si>
+  <si>
+    <t>06.10.202689</t>
+  </si>
+  <si>
+    <t>06.10.202690</t>
+  </si>
+  <si>
+    <t>06.10.202691</t>
+  </si>
+  <si>
+    <t>06.10.202692</t>
+  </si>
+  <si>
+    <t>06.10.202693</t>
+  </si>
+  <si>
+    <t>06.10.202694</t>
+  </si>
+  <si>
+    <t>06.10.202695</t>
+  </si>
+  <si>
+    <t>06.10.202696</t>
+  </si>
+  <si>
+    <t>07.10.20261</t>
+  </si>
+  <si>
+    <t>07.10.20262</t>
+  </si>
+  <si>
+    <t>07.10.20263</t>
+  </si>
+  <si>
+    <t>07.10.20264</t>
+  </si>
+  <si>
+    <t>07.10.20265</t>
+  </si>
+  <si>
+    <t>07.10.20266</t>
+  </si>
+  <si>
+    <t>07.10.20267</t>
+  </si>
+  <si>
+    <t>07.10.20268</t>
+  </si>
+  <si>
+    <t>07.10.20269</t>
+  </si>
+  <si>
+    <t>07.10.202610</t>
+  </si>
+  <si>
+    <t>07.10.202611</t>
+  </si>
+  <si>
+    <t>07.10.202612</t>
+  </si>
+  <si>
+    <t>07.10.202613</t>
+  </si>
+  <si>
+    <t>07.10.202614</t>
+  </si>
+  <si>
+    <t>07.10.202615</t>
+  </si>
+  <si>
+    <t>07.10.202616</t>
+  </si>
+  <si>
+    <t>07.10.202617</t>
+  </si>
+  <si>
+    <t>07.10.202618</t>
+  </si>
+  <si>
+    <t>07.10.202619</t>
+  </si>
+  <si>
+    <t>07.10.202620</t>
+  </si>
+  <si>
+    <t>07.10.202621</t>
+  </si>
+  <si>
+    <t>07.10.202622</t>
+  </si>
+  <si>
+    <t>07.10.202623</t>
+  </si>
+  <si>
+    <t>07.10.202624</t>
+  </si>
+  <si>
+    <t>07.10.202625</t>
+  </si>
+  <si>
+    <t>07.10.202626</t>
+  </si>
+  <si>
+    <t>07.10.202627</t>
+  </si>
+  <si>
+    <t>07.10.202628</t>
+  </si>
+  <si>
+    <t>07.10.202629</t>
+  </si>
+  <si>
+    <t>07.10.202630</t>
+  </si>
+  <si>
+    <t>07.10.202631</t>
+  </si>
+  <si>
+    <t>07.10.202632</t>
+  </si>
+  <si>
+    <t>07.10.202633</t>
+  </si>
+  <si>
+    <t>07.10.202634</t>
+  </si>
+  <si>
+    <t>07.10.202635</t>
+  </si>
+  <si>
+    <t>07.10.202636</t>
+  </si>
+  <si>
+    <t>07.10.202637</t>
+  </si>
+  <si>
+    <t>07.10.202638</t>
+  </si>
+  <si>
+    <t>07.10.202639</t>
+  </si>
+  <si>
+    <t>07.10.202640</t>
+  </si>
+  <si>
+    <t>07.10.202641</t>
+  </si>
+  <si>
+    <t>07.10.202642</t>
+  </si>
+  <si>
+    <t>07.10.202643</t>
+  </si>
+  <si>
+    <t>07.10.202644</t>
+  </si>
+  <si>
+    <t>07.10.202645</t>
+  </si>
+  <si>
+    <t>07.10.202646</t>
+  </si>
+  <si>
+    <t>07.10.202647</t>
+  </si>
+  <si>
+    <t>07.10.202648</t>
+  </si>
+  <si>
+    <t>07.10.202649</t>
+  </si>
+  <si>
+    <t>07.10.202650</t>
+  </si>
+  <si>
+    <t>07.10.202651</t>
+  </si>
+  <si>
+    <t>07.10.202652</t>
+  </si>
+  <si>
+    <t>07.10.202653</t>
+  </si>
+  <si>
+    <t>07.10.202654</t>
+  </si>
+  <si>
+    <t>07.10.202655</t>
+  </si>
+  <si>
+    <t>07.10.202656</t>
+  </si>
+  <si>
+    <t>07.10.202657</t>
+  </si>
+  <si>
+    <t>07.10.202658</t>
+  </si>
+  <si>
+    <t>07.10.202659</t>
+  </si>
+  <si>
+    <t>07.10.202660</t>
+  </si>
+  <si>
+    <t>07.10.202661</t>
+  </si>
+  <si>
+    <t>07.10.202662</t>
+  </si>
+  <si>
+    <t>07.10.202663</t>
+  </si>
+  <si>
+    <t>07.10.202664</t>
+  </si>
+  <si>
+    <t>07.10.202665</t>
+  </si>
+  <si>
+    <t>07.10.202666</t>
+  </si>
+  <si>
+    <t>07.10.202667</t>
+  </si>
+  <si>
+    <t>07.10.202668</t>
+  </si>
+  <si>
+    <t>07.10.202669</t>
+  </si>
+  <si>
+    <t>07.10.202670</t>
+  </si>
+  <si>
+    <t>07.10.202671</t>
+  </si>
+  <si>
+    <t>07.10.202672</t>
+  </si>
+  <si>
+    <t>07.10.202673</t>
+  </si>
+  <si>
+    <t>07.10.202674</t>
+  </si>
+  <si>
+    <t>07.10.202675</t>
+  </si>
+  <si>
+    <t>07.10.202676</t>
+  </si>
+  <si>
+    <t>07.10.202677</t>
+  </si>
+  <si>
+    <t>07.10.202678</t>
+  </si>
+  <si>
+    <t>07.10.202679</t>
+  </si>
+  <si>
+    <t>07.10.202680</t>
+  </si>
+  <si>
+    <t>07.10.202681</t>
+  </si>
+  <si>
+    <t>07.10.202682</t>
+  </si>
+  <si>
+    <t>07.10.202683</t>
+  </si>
+  <si>
+    <t>07.10.202684</t>
+  </si>
+  <si>
+    <t>07.10.202685</t>
+  </si>
+  <si>
+    <t>07.10.202686</t>
+  </si>
+  <si>
+    <t>07.10.202687</t>
+  </si>
+  <si>
+    <t>07.10.202688</t>
+  </si>
+  <si>
+    <t>07.10.202689</t>
+  </si>
+  <si>
+    <t>07.10.202690</t>
+  </si>
+  <si>
+    <t>07.10.202691</t>
+  </si>
+  <si>
+    <t>07.10.202692</t>
+  </si>
+  <si>
+    <t>07.10.202693</t>
+  </si>
+  <si>
+    <t>07.10.202694</t>
+  </si>
+  <si>
+    <t>07.10.202695</t>
+  </si>
+  <si>
+    <t>07.10.202696</t>
   </si>
 </sst>
 </file>
@@ -972,7 +1836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G193"/>
+  <dimension ref="A1:G481"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1877,7 +2741,7 @@
         <v>46298.39583333334</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>28.886</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -3260,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>3.637</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -4016,10 +4880,10 @@
         <v>46299.36458333334</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>1.927</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="D133">
         <v>0</v>
@@ -4039,10 +4903,10 @@
         <v>46299.375</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>3.809</v>
       </c>
       <c r="D134">
         <v>0</v>
@@ -4062,7 +4926,7 @@
         <v>46299.38541666666</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>2.091</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -4085,10 +4949,10 @@
         <v>46299.39583333334</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>3.391</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>0.089</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -4108,10 +4972,10 @@
         <v>46299.40625</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>0.162</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>0.149</v>
       </c>
       <c r="D137">
         <v>0</v>
@@ -4131,7 +4995,7 @@
         <v>46299.41666666666</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>13.662</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -4154,10 +5018,10 @@
         <v>46299.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="D139">
         <v>0</v>
@@ -4177,10 +5041,10 @@
         <v>46299.4375</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>0.114</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>0.512</v>
       </c>
       <c r="D140">
         <v>0</v>
@@ -4200,10 +5064,10 @@
         <v>46299.44791666666</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>5.505</v>
       </c>
       <c r="D141">
         <v>0</v>
@@ -4226,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>7.142</v>
       </c>
       <c r="D142">
         <v>0</v>
@@ -4246,10 +5110,10 @@
         <v>46299.46875</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>5.246</v>
       </c>
       <c r="D143">
         <v>0</v>
@@ -4272,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>22.447</v>
       </c>
       <c r="D144">
         <v>0</v>
@@ -4295,7 +5159,7 @@
         <v>0</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="D145">
         <v>0</v>
@@ -4315,10 +5179,10 @@
         <v>46299.5</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="D146">
         <v>0</v>
@@ -4341,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>11.021</v>
       </c>
       <c r="D147">
         <v>0</v>
@@ -4361,10 +5225,10 @@
         <v>46299.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>0.313</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>10.568</v>
       </c>
       <c r="D148">
         <v>0</v>
@@ -4387,7 +5251,7 @@
         <v>0</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>17.619</v>
       </c>
       <c r="D149">
         <v>0</v>
@@ -4410,7 +5274,7 @@
         <v>0</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>10.777</v>
       </c>
       <c r="D150">
         <v>0</v>
@@ -4433,7 +5297,7 @@
         <v>0</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>9.865</v>
       </c>
       <c r="D151">
         <v>0</v>
@@ -4456,7 +5320,7 @@
         <v>0</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>9.487</v>
       </c>
       <c r="D152">
         <v>0</v>
@@ -4479,7 +5343,7 @@
         <v>0</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>19.711</v>
       </c>
       <c r="D153">
         <v>0</v>
@@ -4502,7 +5366,7 @@
         <v>0</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>13.662</v>
       </c>
       <c r="D154">
         <v>0</v>
@@ -4525,7 +5389,7 @@
         <v>0</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>18.098</v>
       </c>
       <c r="D155">
         <v>0</v>
@@ -4548,7 +5412,7 @@
         <v>0</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>10.15</v>
       </c>
       <c r="D156">
         <v>0</v>
@@ -4571,7 +5435,7 @@
         <v>0</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>11.392</v>
       </c>
       <c r="D157">
         <v>0</v>
@@ -4594,7 +5458,7 @@
         <v>0</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>36.616</v>
       </c>
       <c r="D158">
         <v>0</v>
@@ -4614,10 +5478,10 @@
         <v>46299.63541666666</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>13.491</v>
       </c>
       <c r="D159">
         <v>0</v>
@@ -4637,10 +5501,10 @@
         <v>46299.64583333334</v>
       </c>
       <c r="B160">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>0.473</v>
       </c>
       <c r="D160">
         <v>0</v>
@@ -4660,10 +5524,10 @@
         <v>46299.65625</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="D161">
         <v>0</v>
@@ -4686,7 +5550,7 @@
         <v>0</v>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>22.353</v>
       </c>
       <c r="D162">
         <v>0</v>
@@ -4706,10 +5570,10 @@
         <v>46299.67708333334</v>
       </c>
       <c r="B163">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>9.648</v>
       </c>
       <c r="D163">
         <v>0</v>
@@ -4729,10 +5593,10 @@
         <v>46299.6875</v>
       </c>
       <c r="B164">
-        <v>0</v>
+        <v>8.773</v>
       </c>
       <c r="C164">
-        <v>0</v>
+        <v>0.966</v>
       </c>
       <c r="D164">
         <v>0</v>
@@ -4752,7 +5616,7 @@
         <v>46299.69791666666</v>
       </c>
       <c r="B165">
-        <v>0</v>
+        <v>16.128</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -4775,10 +5639,10 @@
         <v>46299.70833333334</v>
       </c>
       <c r="B166">
-        <v>0</v>
+        <v>2.474</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>0.278</v>
       </c>
       <c r="D166">
         <v>0</v>
@@ -4798,10 +5662,10 @@
         <v>46299.71875</v>
       </c>
       <c r="B167">
-        <v>0</v>
+        <v>8.659000000000001</v>
       </c>
       <c r="C167">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="D167">
         <v>0</v>
@@ -4821,7 +5685,7 @@
         <v>46299.72916666666</v>
       </c>
       <c r="B168">
-        <v>0</v>
+        <v>6.569</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -4844,10 +5708,10 @@
         <v>46299.73958333334</v>
       </c>
       <c r="B169">
-        <v>0</v>
+        <v>0.482</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="D169">
         <v>0</v>
@@ -4867,10 +5731,10 @@
         <v>46299.75</v>
       </c>
       <c r="B170">
-        <v>0</v>
+        <v>0.623</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>0.891</v>
       </c>
       <c r="D170">
         <v>0</v>
@@ -4890,10 +5754,10 @@
         <v>46299.76041666666</v>
       </c>
       <c r="B171">
-        <v>0</v>
+        <v>0.324</v>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="D171">
         <v>0</v>
@@ -4913,10 +5777,10 @@
         <v>46299.77083333334</v>
       </c>
       <c r="B172">
-        <v>0</v>
+        <v>3.691</v>
       </c>
       <c r="C172">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="D172">
         <v>0</v>
@@ -4936,7 +5800,7 @@
         <v>46299.78125</v>
       </c>
       <c r="B173">
-        <v>0</v>
+        <v>5.015</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -4959,10 +5823,10 @@
         <v>46299.79166666666</v>
       </c>
       <c r="B174">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="C174">
-        <v>0</v>
+        <v>3.092</v>
       </c>
       <c r="D174">
         <v>0</v>
@@ -4982,10 +5846,10 @@
         <v>46299.80208333334</v>
       </c>
       <c r="B175">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="C175">
-        <v>0</v>
+        <v>9.018000000000001</v>
       </c>
       <c r="D175">
         <v>0</v>
@@ -5005,10 +5869,10 @@
         <v>46299.8125</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="C176">
-        <v>0</v>
+        <v>6.287</v>
       </c>
       <c r="D176">
         <v>0</v>
@@ -5028,10 +5892,10 @@
         <v>46299.82291666666</v>
       </c>
       <c r="B177">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="C177">
-        <v>0</v>
+        <v>5.636</v>
       </c>
       <c r="D177">
         <v>0</v>
@@ -5051,10 +5915,10 @@
         <v>46299.83333333334</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="C178">
-        <v>0</v>
+        <v>2.539</v>
       </c>
       <c r="D178">
         <v>0</v>
@@ -5077,7 +5941,7 @@
         <v>0</v>
       </c>
       <c r="C179">
-        <v>0</v>
+        <v>3.101</v>
       </c>
       <c r="D179">
         <v>0</v>
@@ -5100,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="C180">
-        <v>0</v>
+        <v>5.182</v>
       </c>
       <c r="D180">
         <v>0</v>
@@ -5123,7 +5987,7 @@
         <v>0</v>
       </c>
       <c r="C181">
-        <v>0</v>
+        <v>12.163</v>
       </c>
       <c r="D181">
         <v>0</v>
@@ -5146,7 +6010,7 @@
         <v>0</v>
       </c>
       <c r="C182">
-        <v>0</v>
+        <v>10.592</v>
       </c>
       <c r="D182">
         <v>0</v>
@@ -5169,7 +6033,7 @@
         <v>0</v>
       </c>
       <c r="C183">
-        <v>0</v>
+        <v>8.355</v>
       </c>
       <c r="D183">
         <v>0</v>
@@ -5192,7 +6056,7 @@
         <v>0</v>
       </c>
       <c r="C184">
-        <v>0</v>
+        <v>9.891999999999999</v>
       </c>
       <c r="D184">
         <v>0</v>
@@ -5215,7 +6079,7 @@
         <v>0</v>
       </c>
       <c r="C185">
-        <v>0</v>
+        <v>19.115</v>
       </c>
       <c r="D185">
         <v>0</v>
@@ -5238,7 +6102,7 @@
         <v>0</v>
       </c>
       <c r="C186">
-        <v>0</v>
+        <v>9.035</v>
       </c>
       <c r="D186">
         <v>0</v>
@@ -5258,10 +6122,10 @@
         <v>46299.92708333334</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="C187">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="D187">
         <v>0</v>
@@ -5284,7 +6148,7 @@
         <v>0</v>
       </c>
       <c r="C188">
-        <v>0</v>
+        <v>3.707</v>
       </c>
       <c r="D188">
         <v>0</v>
@@ -5307,7 +6171,7 @@
         <v>0</v>
       </c>
       <c r="C189">
-        <v>0</v>
+        <v>8.685</v>
       </c>
       <c r="D189">
         <v>0</v>
@@ -5330,7 +6194,7 @@
         <v>0</v>
       </c>
       <c r="C190">
-        <v>0</v>
+        <v>7.485</v>
       </c>
       <c r="D190">
         <v>0</v>
@@ -5353,13 +6217,13 @@
         <v>0</v>
       </c>
       <c r="C191">
-        <v>0</v>
+        <v>8.903</v>
       </c>
       <c r="D191">
         <v>0</v>
       </c>
       <c r="E191">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F191">
         <v>94</v>
@@ -5376,13 +6240,13 @@
         <v>0</v>
       </c>
       <c r="C192">
-        <v>0</v>
+        <v>9.878</v>
       </c>
       <c r="D192">
         <v>0</v>
       </c>
       <c r="E192">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F192">
         <v>95</v>
@@ -5399,19 +6263,6643 @@
         <v>0</v>
       </c>
       <c r="C193">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="D193">
         <v>0</v>
       </c>
       <c r="E193">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F193">
         <v>96</v>
       </c>
       <c r="G193" t="s">
         <v>198</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7">
+      <c r="A194" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B194">
+        <v>4.695</v>
+      </c>
+      <c r="C194">
+        <v>0.11</v>
+      </c>
+      <c r="D194">
+        <v>0</v>
+      </c>
+      <c r="E194">
+        <v>37.5</v>
+      </c>
+      <c r="F194">
+        <v>1</v>
+      </c>
+      <c r="G194" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7">
+      <c r="A195" s="2">
+        <v>46300.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>0.496</v>
+      </c>
+      <c r="C195">
+        <v>0.019</v>
+      </c>
+      <c r="D195">
+        <v>0</v>
+      </c>
+      <c r="E195">
+        <v>37.5</v>
+      </c>
+      <c r="F195">
+        <v>2</v>
+      </c>
+      <c r="G195" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7">
+      <c r="A196" s="2">
+        <v>46300.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>0.534</v>
+      </c>
+      <c r="C196">
+        <v>0.015</v>
+      </c>
+      <c r="D196">
+        <v>0</v>
+      </c>
+      <c r="E196">
+        <v>37.5</v>
+      </c>
+      <c r="F196">
+        <v>3</v>
+      </c>
+      <c r="G196" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7">
+      <c r="A197" s="2">
+        <v>46300.03125</v>
+      </c>
+      <c r="B197">
+        <v>1.606</v>
+      </c>
+      <c r="C197">
+        <v>0.866</v>
+      </c>
+      <c r="D197">
+        <v>0</v>
+      </c>
+      <c r="E197">
+        <v>0</v>
+      </c>
+      <c r="F197">
+        <v>4</v>
+      </c>
+      <c r="G197" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7">
+      <c r="A198" s="2">
+        <v>46300.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>0.046</v>
+      </c>
+      <c r="C198">
+        <v>0.697</v>
+      </c>
+      <c r="D198">
+        <v>0</v>
+      </c>
+      <c r="E198">
+        <v>0</v>
+      </c>
+      <c r="F198">
+        <v>5</v>
+      </c>
+      <c r="G198" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7">
+      <c r="A199" s="2">
+        <v>46300.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>0</v>
+      </c>
+      <c r="C199">
+        <v>0.475</v>
+      </c>
+      <c r="D199">
+        <v>0</v>
+      </c>
+      <c r="E199">
+        <v>0</v>
+      </c>
+      <c r="F199">
+        <v>6</v>
+      </c>
+      <c r="G199" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7">
+      <c r="A200" s="2">
+        <v>46300.0625</v>
+      </c>
+      <c r="B200">
+        <v>0.107</v>
+      </c>
+      <c r="C200">
+        <v>0.144</v>
+      </c>
+      <c r="D200">
+        <v>0</v>
+      </c>
+      <c r="E200">
+        <v>0</v>
+      </c>
+      <c r="F200">
+        <v>7</v>
+      </c>
+      <c r="G200" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7">
+      <c r="A201" s="2">
+        <v>46300.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="C201">
+        <v>1.801</v>
+      </c>
+      <c r="D201">
+        <v>0</v>
+      </c>
+      <c r="E201">
+        <v>0</v>
+      </c>
+      <c r="F201">
+        <v>8</v>
+      </c>
+      <c r="G201" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7">
+      <c r="A202" s="2">
+        <v>46300.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>1.068</v>
+      </c>
+      <c r="C202">
+        <v>3.978</v>
+      </c>
+      <c r="D202">
+        <v>0</v>
+      </c>
+      <c r="E202">
+        <v>0</v>
+      </c>
+      <c r="F202">
+        <v>9</v>
+      </c>
+      <c r="G202" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7">
+      <c r="A203" s="2">
+        <v>46300.09375</v>
+      </c>
+      <c r="B203">
+        <v>0.71</v>
+      </c>
+      <c r="C203">
+        <v>0.163</v>
+      </c>
+      <c r="D203">
+        <v>0</v>
+      </c>
+      <c r="E203">
+        <v>0</v>
+      </c>
+      <c r="F203">
+        <v>10</v>
+      </c>
+      <c r="G203" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7">
+      <c r="A204" s="2">
+        <v>46300.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>0</v>
+      </c>
+      <c r="C204">
+        <v>0.476</v>
+      </c>
+      <c r="D204">
+        <v>0</v>
+      </c>
+      <c r="E204">
+        <v>0</v>
+      </c>
+      <c r="F204">
+        <v>11</v>
+      </c>
+      <c r="G204" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7">
+      <c r="A205" s="2">
+        <v>46300.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>0.138</v>
+      </c>
+      <c r="C205">
+        <v>0.036</v>
+      </c>
+      <c r="D205">
+        <v>0</v>
+      </c>
+      <c r="E205">
+        <v>0</v>
+      </c>
+      <c r="F205">
+        <v>12</v>
+      </c>
+      <c r="G205" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7">
+      <c r="A206" s="2">
+        <v>46300.125</v>
+      </c>
+      <c r="B206">
+        <v>7.28</v>
+      </c>
+      <c r="C206">
+        <v>0.012</v>
+      </c>
+      <c r="D206">
+        <v>0</v>
+      </c>
+      <c r="E206">
+        <v>0</v>
+      </c>
+      <c r="F206">
+        <v>13</v>
+      </c>
+      <c r="G206" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7">
+      <c r="A207" s="2">
+        <v>46300.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>6.014</v>
+      </c>
+      <c r="C207">
+        <v>0.001</v>
+      </c>
+      <c r="D207">
+        <v>0</v>
+      </c>
+      <c r="E207">
+        <v>0</v>
+      </c>
+      <c r="F207">
+        <v>14</v>
+      </c>
+      <c r="G207" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7">
+      <c r="A208" s="2">
+        <v>46300.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>9.663</v>
+      </c>
+      <c r="C208">
+        <v>0</v>
+      </c>
+      <c r="D208">
+        <v>0</v>
+      </c>
+      <c r="E208">
+        <v>0</v>
+      </c>
+      <c r="F208">
+        <v>15</v>
+      </c>
+      <c r="G208" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7">
+      <c r="A209" s="2">
+        <v>46300.15625</v>
+      </c>
+      <c r="B209">
+        <v>8.005000000000001</v>
+      </c>
+      <c r="C209">
+        <v>0.01</v>
+      </c>
+      <c r="D209">
+        <v>0</v>
+      </c>
+      <c r="E209">
+        <v>0</v>
+      </c>
+      <c r="F209">
+        <v>16</v>
+      </c>
+      <c r="G209" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7">
+      <c r="A210" s="2">
+        <v>46300.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>2.094</v>
+      </c>
+      <c r="C210">
+        <v>1.423</v>
+      </c>
+      <c r="D210">
+        <v>0</v>
+      </c>
+      <c r="E210">
+        <v>0</v>
+      </c>
+      <c r="F210">
+        <v>17</v>
+      </c>
+      <c r="G210" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7">
+      <c r="A211" s="2">
+        <v>46300.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>5.891</v>
+      </c>
+      <c r="C211">
+        <v>0</v>
+      </c>
+      <c r="D211">
+        <v>0</v>
+      </c>
+      <c r="E211">
+        <v>0</v>
+      </c>
+      <c r="F211">
+        <v>18</v>
+      </c>
+      <c r="G211" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7">
+      <c r="A212" s="2">
+        <v>46300.1875</v>
+      </c>
+      <c r="B212">
+        <v>1.54</v>
+      </c>
+      <c r="C212">
+        <v>0.028</v>
+      </c>
+      <c r="D212">
+        <v>0</v>
+      </c>
+      <c r="E212">
+        <v>0</v>
+      </c>
+      <c r="F212">
+        <v>19</v>
+      </c>
+      <c r="G212" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7">
+      <c r="A213" s="2">
+        <v>46300.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>9.647</v>
+      </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
+      <c r="D213">
+        <v>0</v>
+      </c>
+      <c r="E213">
+        <v>0</v>
+      </c>
+      <c r="F213">
+        <v>20</v>
+      </c>
+      <c r="G213" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7">
+      <c r="A214" s="2">
+        <v>46300.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>0.447</v>
+      </c>
+      <c r="C214">
+        <v>4.162</v>
+      </c>
+      <c r="D214">
+        <v>0</v>
+      </c>
+      <c r="E214">
+        <v>0</v>
+      </c>
+      <c r="F214">
+        <v>21</v>
+      </c>
+      <c r="G214" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7">
+      <c r="A215" s="2">
+        <v>46300.21875</v>
+      </c>
+      <c r="B215">
+        <v>0.134</v>
+      </c>
+      <c r="C215">
+        <v>0.574</v>
+      </c>
+      <c r="D215">
+        <v>0</v>
+      </c>
+      <c r="E215">
+        <v>0</v>
+      </c>
+      <c r="F215">
+        <v>22</v>
+      </c>
+      <c r="G215" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7">
+      <c r="A216" s="2">
+        <v>46300.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>1.955</v>
+      </c>
+      <c r="C216">
+        <v>2.245</v>
+      </c>
+      <c r="D216">
+        <v>0</v>
+      </c>
+      <c r="E216">
+        <v>0</v>
+      </c>
+      <c r="F216">
+        <v>23</v>
+      </c>
+      <c r="G216" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7">
+      <c r="A217" s="2">
+        <v>46300.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>5.337</v>
+      </c>
+      <c r="C217">
+        <v>0</v>
+      </c>
+      <c r="D217">
+        <v>0</v>
+      </c>
+      <c r="E217">
+        <v>0</v>
+      </c>
+      <c r="F217">
+        <v>24</v>
+      </c>
+      <c r="G217" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7">
+      <c r="A218" s="2">
+        <v>46300.25</v>
+      </c>
+      <c r="B218">
+        <v>0.015</v>
+      </c>
+      <c r="C218">
+        <v>8.204000000000001</v>
+      </c>
+      <c r="D218">
+        <v>0</v>
+      </c>
+      <c r="E218">
+        <v>0</v>
+      </c>
+      <c r="F218">
+        <v>25</v>
+      </c>
+      <c r="G218" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7">
+      <c r="A219" s="2">
+        <v>46300.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>0.207</v>
+      </c>
+      <c r="C219">
+        <v>0.7</v>
+      </c>
+      <c r="D219">
+        <v>0</v>
+      </c>
+      <c r="E219">
+        <v>0</v>
+      </c>
+      <c r="F219">
+        <v>26</v>
+      </c>
+      <c r="G219" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7">
+      <c r="A220" s="2">
+        <v>46300.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>0.025</v>
+      </c>
+      <c r="C220">
+        <v>0.638</v>
+      </c>
+      <c r="D220">
+        <v>0</v>
+      </c>
+      <c r="E220">
+        <v>0</v>
+      </c>
+      <c r="F220">
+        <v>27</v>
+      </c>
+      <c r="G220" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7">
+      <c r="A221" s="2">
+        <v>46300.28125</v>
+      </c>
+      <c r="B221">
+        <v>1.921</v>
+      </c>
+      <c r="C221">
+        <v>0.029</v>
+      </c>
+      <c r="D221">
+        <v>0</v>
+      </c>
+      <c r="E221">
+        <v>0</v>
+      </c>
+      <c r="F221">
+        <v>28</v>
+      </c>
+      <c r="G221" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7">
+      <c r="A222" s="2">
+        <v>46300.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>7.919</v>
+      </c>
+      <c r="C222">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="D222">
+        <v>0</v>
+      </c>
+      <c r="E222">
+        <v>0</v>
+      </c>
+      <c r="F222">
+        <v>29</v>
+      </c>
+      <c r="G222" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7">
+      <c r="A223" s="2">
+        <v>46300.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>4.251</v>
+      </c>
+      <c r="C223">
+        <v>0</v>
+      </c>
+      <c r="D223">
+        <v>0</v>
+      </c>
+      <c r="E223">
+        <v>0</v>
+      </c>
+      <c r="F223">
+        <v>30</v>
+      </c>
+      <c r="G223" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7">
+      <c r="A224" s="2">
+        <v>46300.3125</v>
+      </c>
+      <c r="B224">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="C224">
+        <v>3.13</v>
+      </c>
+      <c r="D224">
+        <v>0</v>
+      </c>
+      <c r="E224">
+        <v>0</v>
+      </c>
+      <c r="F224">
+        <v>31</v>
+      </c>
+      <c r="G224" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7">
+      <c r="A225" s="2">
+        <v>46300.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>0</v>
+      </c>
+      <c r="C225">
+        <v>13.276</v>
+      </c>
+      <c r="D225">
+        <v>0</v>
+      </c>
+      <c r="E225">
+        <v>0</v>
+      </c>
+      <c r="F225">
+        <v>32</v>
+      </c>
+      <c r="G225" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7">
+      <c r="A226" s="2">
+        <v>46300.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>0</v>
+      </c>
+      <c r="C226">
+        <v>6.799</v>
+      </c>
+      <c r="D226">
+        <v>0</v>
+      </c>
+      <c r="E226">
+        <v>0</v>
+      </c>
+      <c r="F226">
+        <v>33</v>
+      </c>
+      <c r="G226" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7">
+      <c r="A227" s="2">
+        <v>46300.34375</v>
+      </c>
+      <c r="B227">
+        <v>0</v>
+      </c>
+      <c r="C227">
+        <v>12.552</v>
+      </c>
+      <c r="D227">
+        <v>0</v>
+      </c>
+      <c r="E227">
+        <v>0</v>
+      </c>
+      <c r="F227">
+        <v>34</v>
+      </c>
+      <c r="G227" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7">
+      <c r="A228" s="2">
+        <v>46300.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>0</v>
+      </c>
+      <c r="C228">
+        <v>22.568</v>
+      </c>
+      <c r="D228">
+        <v>0</v>
+      </c>
+      <c r="E228">
+        <v>0</v>
+      </c>
+      <c r="F228">
+        <v>35</v>
+      </c>
+      <c r="G228" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7">
+      <c r="A229" s="2">
+        <v>46300.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>0</v>
+      </c>
+      <c r="C229">
+        <v>46.419</v>
+      </c>
+      <c r="D229">
+        <v>0</v>
+      </c>
+      <c r="E229">
+        <v>0</v>
+      </c>
+      <c r="F229">
+        <v>36</v>
+      </c>
+      <c r="G229" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7">
+      <c r="A230" s="2">
+        <v>46300.375</v>
+      </c>
+      <c r="B230">
+        <v>14.742</v>
+      </c>
+      <c r="C230">
+        <v>2.468</v>
+      </c>
+      <c r="D230">
+        <v>0</v>
+      </c>
+      <c r="E230">
+        <v>0</v>
+      </c>
+      <c r="F230">
+        <v>37</v>
+      </c>
+      <c r="G230" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7">
+      <c r="A231" s="2">
+        <v>46300.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>12.756</v>
+      </c>
+      <c r="C231">
+        <v>0.255</v>
+      </c>
+      <c r="D231">
+        <v>0</v>
+      </c>
+      <c r="E231">
+        <v>0</v>
+      </c>
+      <c r="F231">
+        <v>38</v>
+      </c>
+      <c r="G231" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7">
+      <c r="A232" s="2">
+        <v>46300.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>0</v>
+      </c>
+      <c r="C232">
+        <v>4.319</v>
+      </c>
+      <c r="D232">
+        <v>0</v>
+      </c>
+      <c r="E232">
+        <v>0</v>
+      </c>
+      <c r="F232">
+        <v>39</v>
+      </c>
+      <c r="G232" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7">
+      <c r="A233" s="2">
+        <v>46300.40625</v>
+      </c>
+      <c r="B233">
+        <v>0.012</v>
+      </c>
+      <c r="C233">
+        <v>2.637</v>
+      </c>
+      <c r="D233">
+        <v>0</v>
+      </c>
+      <c r="E233">
+        <v>0</v>
+      </c>
+      <c r="F233">
+        <v>40</v>
+      </c>
+      <c r="G233" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7">
+      <c r="A234" s="2">
+        <v>46300.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>5.825</v>
+      </c>
+      <c r="C234">
+        <v>0.309</v>
+      </c>
+      <c r="D234">
+        <v>0</v>
+      </c>
+      <c r="E234">
+        <v>0</v>
+      </c>
+      <c r="F234">
+        <v>41</v>
+      </c>
+      <c r="G234" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7">
+      <c r="A235" s="2">
+        <v>46300.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>12.829</v>
+      </c>
+      <c r="C235">
+        <v>0</v>
+      </c>
+      <c r="D235">
+        <v>0</v>
+      </c>
+      <c r="E235">
+        <v>0</v>
+      </c>
+      <c r="F235">
+        <v>42</v>
+      </c>
+      <c r="G235" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7">
+      <c r="A236" s="2">
+        <v>46300.4375</v>
+      </c>
+      <c r="B236">
+        <v>2.103</v>
+      </c>
+      <c r="C236">
+        <v>0.005</v>
+      </c>
+      <c r="D236">
+        <v>0</v>
+      </c>
+      <c r="E236">
+        <v>0</v>
+      </c>
+      <c r="F236">
+        <v>43</v>
+      </c>
+      <c r="G236" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7">
+      <c r="A237" s="2">
+        <v>46300.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>0.569</v>
+      </c>
+      <c r="C237">
+        <v>0.336</v>
+      </c>
+      <c r="D237">
+        <v>0</v>
+      </c>
+      <c r="E237">
+        <v>0</v>
+      </c>
+      <c r="F237">
+        <v>44</v>
+      </c>
+      <c r="G237" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7">
+      <c r="A238" s="2">
+        <v>46300.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>0.002</v>
+      </c>
+      <c r="C238">
+        <v>6.57</v>
+      </c>
+      <c r="D238">
+        <v>0</v>
+      </c>
+      <c r="E238">
+        <v>0</v>
+      </c>
+      <c r="F238">
+        <v>45</v>
+      </c>
+      <c r="G238" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7">
+      <c r="A239" s="2">
+        <v>46300.46875</v>
+      </c>
+      <c r="B239">
+        <v>0.005</v>
+      </c>
+      <c r="C239">
+        <v>4.455</v>
+      </c>
+      <c r="D239">
+        <v>0</v>
+      </c>
+      <c r="E239">
+        <v>0</v>
+      </c>
+      <c r="F239">
+        <v>46</v>
+      </c>
+      <c r="G239" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7">
+      <c r="A240" s="2">
+        <v>46300.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>0.003</v>
+      </c>
+      <c r="C240">
+        <v>4.364</v>
+      </c>
+      <c r="D240">
+        <v>0</v>
+      </c>
+      <c r="E240">
+        <v>0</v>
+      </c>
+      <c r="F240">
+        <v>47</v>
+      </c>
+      <c r="G240" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7">
+      <c r="A241" s="2">
+        <v>46300.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>0</v>
+      </c>
+      <c r="C241">
+        <v>7.858</v>
+      </c>
+      <c r="D241">
+        <v>0</v>
+      </c>
+      <c r="E241">
+        <v>0</v>
+      </c>
+      <c r="F241">
+        <v>48</v>
+      </c>
+      <c r="G241" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7">
+      <c r="A242" s="2">
+        <v>46300.5</v>
+      </c>
+      <c r="B242">
+        <v>0</v>
+      </c>
+      <c r="C242">
+        <v>31.324</v>
+      </c>
+      <c r="D242">
+        <v>0</v>
+      </c>
+      <c r="E242">
+        <v>0</v>
+      </c>
+      <c r="F242">
+        <v>49</v>
+      </c>
+      <c r="G242" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7">
+      <c r="A243" s="2">
+        <v>46300.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>0</v>
+      </c>
+      <c r="C243">
+        <v>14.403</v>
+      </c>
+      <c r="D243">
+        <v>0</v>
+      </c>
+      <c r="E243">
+        <v>0</v>
+      </c>
+      <c r="F243">
+        <v>50</v>
+      </c>
+      <c r="G243" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7">
+      <c r="A244" s="2">
+        <v>46300.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>0</v>
+      </c>
+      <c r="C244">
+        <v>17.379</v>
+      </c>
+      <c r="D244">
+        <v>0</v>
+      </c>
+      <c r="E244">
+        <v>0</v>
+      </c>
+      <c r="F244">
+        <v>51</v>
+      </c>
+      <c r="G244" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7">
+      <c r="A245" s="2">
+        <v>46300.53125</v>
+      </c>
+      <c r="B245">
+        <v>0.073</v>
+      </c>
+      <c r="C245">
+        <v>7.841</v>
+      </c>
+      <c r="D245">
+        <v>0</v>
+      </c>
+      <c r="E245">
+        <v>0</v>
+      </c>
+      <c r="F245">
+        <v>52</v>
+      </c>
+      <c r="G245" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7">
+      <c r="A246" s="2">
+        <v>46300.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>0.255</v>
+      </c>
+      <c r="C246">
+        <v>1.269</v>
+      </c>
+      <c r="D246">
+        <v>0</v>
+      </c>
+      <c r="E246">
+        <v>0</v>
+      </c>
+      <c r="F246">
+        <v>53</v>
+      </c>
+      <c r="G246" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7">
+      <c r="A247" s="2">
+        <v>46300.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>0.006</v>
+      </c>
+      <c r="C247">
+        <v>4.32</v>
+      </c>
+      <c r="D247">
+        <v>0</v>
+      </c>
+      <c r="E247">
+        <v>0</v>
+      </c>
+      <c r="F247">
+        <v>54</v>
+      </c>
+      <c r="G247" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7">
+      <c r="A248" s="2">
+        <v>46300.5625</v>
+      </c>
+      <c r="B248">
+        <v>0</v>
+      </c>
+      <c r="C248">
+        <v>12.314</v>
+      </c>
+      <c r="D248">
+        <v>0</v>
+      </c>
+      <c r="E248">
+        <v>0</v>
+      </c>
+      <c r="F248">
+        <v>55</v>
+      </c>
+      <c r="G248" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7">
+      <c r="A249" s="2">
+        <v>46300.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>0</v>
+      </c>
+      <c r="C249">
+        <v>9.058</v>
+      </c>
+      <c r="D249">
+        <v>0</v>
+      </c>
+      <c r="E249">
+        <v>0</v>
+      </c>
+      <c r="F249">
+        <v>56</v>
+      </c>
+      <c r="G249" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7">
+      <c r="A250" s="2">
+        <v>46300.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>0</v>
+      </c>
+      <c r="C250">
+        <v>19.643</v>
+      </c>
+      <c r="D250">
+        <v>0</v>
+      </c>
+      <c r="E250">
+        <v>0</v>
+      </c>
+      <c r="F250">
+        <v>57</v>
+      </c>
+      <c r="G250" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7">
+      <c r="A251" s="2">
+        <v>46300.59375</v>
+      </c>
+      <c r="B251">
+        <v>0</v>
+      </c>
+      <c r="C251">
+        <v>16.458</v>
+      </c>
+      <c r="D251">
+        <v>0</v>
+      </c>
+      <c r="E251">
+        <v>0</v>
+      </c>
+      <c r="F251">
+        <v>58</v>
+      </c>
+      <c r="G251" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7">
+      <c r="A252" s="2">
+        <v>46300.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>0.005</v>
+      </c>
+      <c r="C252">
+        <v>8.58</v>
+      </c>
+      <c r="D252">
+        <v>0</v>
+      </c>
+      <c r="E252">
+        <v>0</v>
+      </c>
+      <c r="F252">
+        <v>59</v>
+      </c>
+      <c r="G252" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7">
+      <c r="A253" s="2">
+        <v>46300.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>0.056</v>
+      </c>
+      <c r="C253">
+        <v>14.705</v>
+      </c>
+      <c r="D253">
+        <v>0</v>
+      </c>
+      <c r="E253">
+        <v>0</v>
+      </c>
+      <c r="F253">
+        <v>60</v>
+      </c>
+      <c r="G253" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7">
+      <c r="A254" s="2">
+        <v>46300.625</v>
+      </c>
+      <c r="B254">
+        <v>0</v>
+      </c>
+      <c r="C254">
+        <v>2.405</v>
+      </c>
+      <c r="D254">
+        <v>0</v>
+      </c>
+      <c r="E254">
+        <v>0</v>
+      </c>
+      <c r="F254">
+        <v>61</v>
+      </c>
+      <c r="G254" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7">
+      <c r="A255" s="2">
+        <v>46300.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>0.154</v>
+      </c>
+      <c r="C255">
+        <v>0.395</v>
+      </c>
+      <c r="D255">
+        <v>0</v>
+      </c>
+      <c r="E255">
+        <v>0</v>
+      </c>
+      <c r="F255">
+        <v>62</v>
+      </c>
+      <c r="G255" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7">
+      <c r="A256" s="2">
+        <v>46300.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>0.109</v>
+      </c>
+      <c r="C256">
+        <v>0.454</v>
+      </c>
+      <c r="D256">
+        <v>0</v>
+      </c>
+      <c r="E256">
+        <v>0</v>
+      </c>
+      <c r="F256">
+        <v>63</v>
+      </c>
+      <c r="G256" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7">
+      <c r="A257" s="2">
+        <v>46300.65625</v>
+      </c>
+      <c r="B257">
+        <v>0.361</v>
+      </c>
+      <c r="C257">
+        <v>3.557</v>
+      </c>
+      <c r="D257">
+        <v>0</v>
+      </c>
+      <c r="E257">
+        <v>0</v>
+      </c>
+      <c r="F257">
+        <v>64</v>
+      </c>
+      <c r="G257" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7">
+      <c r="A258" s="2">
+        <v>46300.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>3.788</v>
+      </c>
+      <c r="C258">
+        <v>0.747</v>
+      </c>
+      <c r="D258">
+        <v>0</v>
+      </c>
+      <c r="E258">
+        <v>0</v>
+      </c>
+      <c r="F258">
+        <v>65</v>
+      </c>
+      <c r="G258" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7">
+      <c r="A259" s="2">
+        <v>46300.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>4.042</v>
+      </c>
+      <c r="C259">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="D259">
+        <v>0</v>
+      </c>
+      <c r="E259">
+        <v>0</v>
+      </c>
+      <c r="F259">
+        <v>66</v>
+      </c>
+      <c r="G259" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7">
+      <c r="A260" s="2">
+        <v>46300.6875</v>
+      </c>
+      <c r="B260">
+        <v>28.646</v>
+      </c>
+      <c r="C260">
+        <v>0</v>
+      </c>
+      <c r="D260">
+        <v>0</v>
+      </c>
+      <c r="E260">
+        <v>0</v>
+      </c>
+      <c r="F260">
+        <v>67</v>
+      </c>
+      <c r="G260" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7">
+      <c r="A261" s="2">
+        <v>46300.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>44.32</v>
+      </c>
+      <c r="C261">
+        <v>0</v>
+      </c>
+      <c r="D261">
+        <v>0</v>
+      </c>
+      <c r="E261">
+        <v>0</v>
+      </c>
+      <c r="F261">
+        <v>68</v>
+      </c>
+      <c r="G261" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7">
+      <c r="A262" s="2">
+        <v>46300.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>23.85</v>
+      </c>
+      <c r="C262">
+        <v>0</v>
+      </c>
+      <c r="D262">
+        <v>0</v>
+      </c>
+      <c r="E262">
+        <v>0</v>
+      </c>
+      <c r="F262">
+        <v>69</v>
+      </c>
+      <c r="G262" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7">
+      <c r="A263" s="2">
+        <v>46300.71875</v>
+      </c>
+      <c r="B263">
+        <v>43.729</v>
+      </c>
+      <c r="C263">
+        <v>0</v>
+      </c>
+      <c r="D263">
+        <v>0</v>
+      </c>
+      <c r="E263">
+        <v>0</v>
+      </c>
+      <c r="F263">
+        <v>70</v>
+      </c>
+      <c r="G263" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7">
+      <c r="A264" s="2">
+        <v>46300.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>24.523</v>
+      </c>
+      <c r="C264">
+        <v>0</v>
+      </c>
+      <c r="D264">
+        <v>0</v>
+      </c>
+      <c r="E264">
+        <v>0</v>
+      </c>
+      <c r="F264">
+        <v>71</v>
+      </c>
+      <c r="G264" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7">
+      <c r="A265" s="2">
+        <v>46300.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>21.901</v>
+      </c>
+      <c r="C265">
+        <v>0</v>
+      </c>
+      <c r="D265">
+        <v>0</v>
+      </c>
+      <c r="E265">
+        <v>0</v>
+      </c>
+      <c r="F265">
+        <v>72</v>
+      </c>
+      <c r="G265" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7">
+      <c r="A266" s="2">
+        <v>46300.75</v>
+      </c>
+      <c r="B266">
+        <v>1.535</v>
+      </c>
+      <c r="C266">
+        <v>0</v>
+      </c>
+      <c r="D266">
+        <v>0</v>
+      </c>
+      <c r="E266">
+        <v>0</v>
+      </c>
+      <c r="F266">
+        <v>73</v>
+      </c>
+      <c r="G266" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7">
+      <c r="A267" s="2">
+        <v>46300.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>3.576</v>
+      </c>
+      <c r="C267">
+        <v>0.007</v>
+      </c>
+      <c r="D267">
+        <v>0</v>
+      </c>
+      <c r="E267">
+        <v>0</v>
+      </c>
+      <c r="F267">
+        <v>74</v>
+      </c>
+      <c r="G267" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7">
+      <c r="A268" s="2">
+        <v>46300.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>15.813</v>
+      </c>
+      <c r="C268">
+        <v>0</v>
+      </c>
+      <c r="D268">
+        <v>0</v>
+      </c>
+      <c r="E268">
+        <v>0</v>
+      </c>
+      <c r="F268">
+        <v>75</v>
+      </c>
+      <c r="G268" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7">
+      <c r="A269" s="2">
+        <v>46300.78125</v>
+      </c>
+      <c r="B269">
+        <v>14.285</v>
+      </c>
+      <c r="C269">
+        <v>0</v>
+      </c>
+      <c r="D269">
+        <v>0</v>
+      </c>
+      <c r="E269">
+        <v>0</v>
+      </c>
+      <c r="F269">
+        <v>76</v>
+      </c>
+      <c r="G269" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7">
+      <c r="A270" s="2">
+        <v>46300.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>40.756</v>
+      </c>
+      <c r="C270">
+        <v>0</v>
+      </c>
+      <c r="D270">
+        <v>0</v>
+      </c>
+      <c r="E270">
+        <v>0</v>
+      </c>
+      <c r="F270">
+        <v>77</v>
+      </c>
+      <c r="G270" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7">
+      <c r="A271" s="2">
+        <v>46300.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>51.881</v>
+      </c>
+      <c r="C271">
+        <v>0</v>
+      </c>
+      <c r="D271">
+        <v>0</v>
+      </c>
+      <c r="E271">
+        <v>0</v>
+      </c>
+      <c r="F271">
+        <v>78</v>
+      </c>
+      <c r="G271" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7">
+      <c r="A272" s="2">
+        <v>46300.8125</v>
+      </c>
+      <c r="B272">
+        <v>20.656</v>
+      </c>
+      <c r="C272">
+        <v>0</v>
+      </c>
+      <c r="D272">
+        <v>37.5</v>
+      </c>
+      <c r="E272">
+        <v>0</v>
+      </c>
+      <c r="F272">
+        <v>79</v>
+      </c>
+      <c r="G272" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7">
+      <c r="A273" s="2">
+        <v>46300.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>27.56</v>
+      </c>
+      <c r="C273">
+        <v>0</v>
+      </c>
+      <c r="D273">
+        <v>37.5</v>
+      </c>
+      <c r="E273">
+        <v>0</v>
+      </c>
+      <c r="F273">
+        <v>80</v>
+      </c>
+      <c r="G273" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7">
+      <c r="A274" s="2">
+        <v>46300.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>70.744</v>
+      </c>
+      <c r="C274">
+        <v>0</v>
+      </c>
+      <c r="D274">
+        <v>37.5</v>
+      </c>
+      <c r="E274">
+        <v>0</v>
+      </c>
+      <c r="F274">
+        <v>81</v>
+      </c>
+      <c r="G274" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7">
+      <c r="A275" s="2">
+        <v>46300.84375</v>
+      </c>
+      <c r="B275">
+        <v>59.331</v>
+      </c>
+      <c r="C275">
+        <v>0</v>
+      </c>
+      <c r="D275">
+        <v>37.5</v>
+      </c>
+      <c r="E275">
+        <v>0</v>
+      </c>
+      <c r="F275">
+        <v>82</v>
+      </c>
+      <c r="G275" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7">
+      <c r="A276" s="2">
+        <v>46300.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>4.718</v>
+      </c>
+      <c r="C276">
+        <v>0.039</v>
+      </c>
+      <c r="D276">
+        <v>37.5</v>
+      </c>
+      <c r="E276">
+        <v>0</v>
+      </c>
+      <c r="F276">
+        <v>83</v>
+      </c>
+      <c r="G276" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7">
+      <c r="A277" s="2">
+        <v>46300.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>0.099</v>
+      </c>
+      <c r="C277">
+        <v>0.57</v>
+      </c>
+      <c r="D277">
+        <v>37.5</v>
+      </c>
+      <c r="E277">
+        <v>0</v>
+      </c>
+      <c r="F277">
+        <v>84</v>
+      </c>
+      <c r="G277" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7">
+      <c r="A278" s="2">
+        <v>46300.875</v>
+      </c>
+      <c r="B278">
+        <v>3.983</v>
+      </c>
+      <c r="C278">
+        <v>0.007</v>
+      </c>
+      <c r="D278">
+        <v>37.5</v>
+      </c>
+      <c r="E278">
+        <v>0</v>
+      </c>
+      <c r="F278">
+        <v>85</v>
+      </c>
+      <c r="G278" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7">
+      <c r="A279" s="2">
+        <v>46300.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>33.759</v>
+      </c>
+      <c r="C279">
+        <v>0</v>
+      </c>
+      <c r="D279">
+        <v>0</v>
+      </c>
+      <c r="E279">
+        <v>0</v>
+      </c>
+      <c r="F279">
+        <v>86</v>
+      </c>
+      <c r="G279" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
+      <c r="A280" s="2">
+        <v>46300.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>12.683</v>
+      </c>
+      <c r="C280">
+        <v>0.665</v>
+      </c>
+      <c r="D280">
+        <v>0</v>
+      </c>
+      <c r="E280">
+        <v>0</v>
+      </c>
+      <c r="F280">
+        <v>87</v>
+      </c>
+      <c r="G280" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7">
+      <c r="A281" s="2">
+        <v>46300.90625</v>
+      </c>
+      <c r="B281">
+        <v>0.153</v>
+      </c>
+      <c r="C281">
+        <v>3.876</v>
+      </c>
+      <c r="D281">
+        <v>0</v>
+      </c>
+      <c r="E281">
+        <v>0</v>
+      </c>
+      <c r="F281">
+        <v>88</v>
+      </c>
+      <c r="G281" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7">
+      <c r="A282" s="2">
+        <v>46300.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>16.433</v>
+      </c>
+      <c r="C282">
+        <v>0.958</v>
+      </c>
+      <c r="D282">
+        <v>0</v>
+      </c>
+      <c r="E282">
+        <v>0</v>
+      </c>
+      <c r="F282">
+        <v>89</v>
+      </c>
+      <c r="G282" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7">
+      <c r="A283" s="2">
+        <v>46300.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>15.41</v>
+      </c>
+      <c r="C283">
+        <v>0.163</v>
+      </c>
+      <c r="D283">
+        <v>0</v>
+      </c>
+      <c r="E283">
+        <v>0</v>
+      </c>
+      <c r="F283">
+        <v>90</v>
+      </c>
+      <c r="G283" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
+      <c r="A284" s="2">
+        <v>46300.9375</v>
+      </c>
+      <c r="B284">
+        <v>8.398</v>
+      </c>
+      <c r="C284">
+        <v>0</v>
+      </c>
+      <c r="D284">
+        <v>0</v>
+      </c>
+      <c r="E284">
+        <v>0</v>
+      </c>
+      <c r="F284">
+        <v>91</v>
+      </c>
+      <c r="G284" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7">
+      <c r="A285" s="2">
+        <v>46300.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>0.927</v>
+      </c>
+      <c r="C285">
+        <v>0.569</v>
+      </c>
+      <c r="D285">
+        <v>0</v>
+      </c>
+      <c r="E285">
+        <v>0</v>
+      </c>
+      <c r="F285">
+        <v>92</v>
+      </c>
+      <c r="G285" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7">
+      <c r="A286" s="2">
+        <v>46300.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>0.26</v>
+      </c>
+      <c r="C286">
+        <v>1.144</v>
+      </c>
+      <c r="D286">
+        <v>0</v>
+      </c>
+      <c r="E286">
+        <v>0</v>
+      </c>
+      <c r="F286">
+        <v>93</v>
+      </c>
+      <c r="G286" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7">
+      <c r="A287" s="2">
+        <v>46300.96875</v>
+      </c>
+      <c r="B287">
+        <v>0.33</v>
+      </c>
+      <c r="C287">
+        <v>0.569</v>
+      </c>
+      <c r="D287">
+        <v>0</v>
+      </c>
+      <c r="E287">
+        <v>0</v>
+      </c>
+      <c r="F287">
+        <v>94</v>
+      </c>
+      <c r="G287" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7">
+      <c r="A288" s="2">
+        <v>46300.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>4.252</v>
+      </c>
+      <c r="C288">
+        <v>0.37</v>
+      </c>
+      <c r="D288">
+        <v>0</v>
+      </c>
+      <c r="E288">
+        <v>0</v>
+      </c>
+      <c r="F288">
+        <v>95</v>
+      </c>
+      <c r="G288" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7">
+      <c r="A289" s="2">
+        <v>46300.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>7.253</v>
+      </c>
+      <c r="C289">
+        <v>0.204</v>
+      </c>
+      <c r="D289">
+        <v>0</v>
+      </c>
+      <c r="E289">
+        <v>0</v>
+      </c>
+      <c r="F289">
+        <v>96</v>
+      </c>
+      <c r="G289" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7">
+      <c r="A290" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B290">
+        <v>1.029</v>
+      </c>
+      <c r="C290">
+        <v>0.184</v>
+      </c>
+      <c r="D290">
+        <v>0</v>
+      </c>
+      <c r="E290">
+        <v>0</v>
+      </c>
+      <c r="F290">
+        <v>1</v>
+      </c>
+      <c r="G290" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7">
+      <c r="A291" s="2">
+        <v>46301.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>0.083</v>
+      </c>
+      <c r="C291">
+        <v>0.274</v>
+      </c>
+      <c r="D291">
+        <v>0</v>
+      </c>
+      <c r="E291">
+        <v>0</v>
+      </c>
+      <c r="F291">
+        <v>2</v>
+      </c>
+      <c r="G291" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7">
+      <c r="A292" s="2">
+        <v>46301.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>0.15</v>
+      </c>
+      <c r="C292">
+        <v>1.134</v>
+      </c>
+      <c r="D292">
+        <v>0</v>
+      </c>
+      <c r="E292">
+        <v>0</v>
+      </c>
+      <c r="F292">
+        <v>3</v>
+      </c>
+      <c r="G292" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7">
+      <c r="A293" s="2">
+        <v>46301.03125</v>
+      </c>
+      <c r="B293">
+        <v>0</v>
+      </c>
+      <c r="C293">
+        <v>4.267</v>
+      </c>
+      <c r="D293">
+        <v>0</v>
+      </c>
+      <c r="E293">
+        <v>0</v>
+      </c>
+      <c r="F293">
+        <v>4</v>
+      </c>
+      <c r="G293" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7">
+      <c r="A294" s="2">
+        <v>46301.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>0</v>
+      </c>
+      <c r="C294">
+        <v>3.227</v>
+      </c>
+      <c r="D294">
+        <v>0</v>
+      </c>
+      <c r="E294">
+        <v>0</v>
+      </c>
+      <c r="F294">
+        <v>5</v>
+      </c>
+      <c r="G294" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7">
+      <c r="A295" s="2">
+        <v>46301.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>0</v>
+      </c>
+      <c r="C295">
+        <v>3.087</v>
+      </c>
+      <c r="D295">
+        <v>0</v>
+      </c>
+      <c r="E295">
+        <v>0</v>
+      </c>
+      <c r="F295">
+        <v>6</v>
+      </c>
+      <c r="G295" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7">
+      <c r="A296" s="2">
+        <v>46301.0625</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+      <c r="C296">
+        <v>3.538</v>
+      </c>
+      <c r="D296">
+        <v>0</v>
+      </c>
+      <c r="E296">
+        <v>0</v>
+      </c>
+      <c r="F296">
+        <v>7</v>
+      </c>
+      <c r="G296" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7">
+      <c r="A297" s="2">
+        <v>46301.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>0.888</v>
+      </c>
+      <c r="C297">
+        <v>0.057</v>
+      </c>
+      <c r="D297">
+        <v>0</v>
+      </c>
+      <c r="E297">
+        <v>0</v>
+      </c>
+      <c r="F297">
+        <v>8</v>
+      </c>
+      <c r="G297" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7">
+      <c r="A298" s="2">
+        <v>46301.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>1.804</v>
+      </c>
+      <c r="C298">
+        <v>1.385</v>
+      </c>
+      <c r="D298">
+        <v>0</v>
+      </c>
+      <c r="E298">
+        <v>0</v>
+      </c>
+      <c r="F298">
+        <v>9</v>
+      </c>
+      <c r="G298" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7">
+      <c r="A299" s="2">
+        <v>46301.09375</v>
+      </c>
+      <c r="B299">
+        <v>2.548</v>
+      </c>
+      <c r="C299">
+        <v>0.236</v>
+      </c>
+      <c r="D299">
+        <v>0</v>
+      </c>
+      <c r="E299">
+        <v>0</v>
+      </c>
+      <c r="F299">
+        <v>10</v>
+      </c>
+      <c r="G299" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7">
+      <c r="A300" s="2">
+        <v>46301.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>13.694</v>
+      </c>
+      <c r="C300">
+        <v>0</v>
+      </c>
+      <c r="D300">
+        <v>0</v>
+      </c>
+      <c r="E300">
+        <v>0</v>
+      </c>
+      <c r="F300">
+        <v>11</v>
+      </c>
+      <c r="G300" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7">
+      <c r="A301" s="2">
+        <v>46301.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>0.399</v>
+      </c>
+      <c r="C301">
+        <v>0.231</v>
+      </c>
+      <c r="D301">
+        <v>0</v>
+      </c>
+      <c r="E301">
+        <v>0</v>
+      </c>
+      <c r="F301">
+        <v>12</v>
+      </c>
+      <c r="G301" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7">
+      <c r="A302" s="2">
+        <v>46301.125</v>
+      </c>
+      <c r="B302">
+        <v>1.026</v>
+      </c>
+      <c r="C302">
+        <v>0.775</v>
+      </c>
+      <c r="D302">
+        <v>0</v>
+      </c>
+      <c r="E302">
+        <v>0</v>
+      </c>
+      <c r="F302">
+        <v>13</v>
+      </c>
+      <c r="G302" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7">
+      <c r="A303" s="2">
+        <v>46301.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>0.146</v>
+      </c>
+      <c r="C303">
+        <v>0.401</v>
+      </c>
+      <c r="D303">
+        <v>0</v>
+      </c>
+      <c r="E303">
+        <v>0</v>
+      </c>
+      <c r="F303">
+        <v>14</v>
+      </c>
+      <c r="G303" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7">
+      <c r="A304" s="2">
+        <v>46301.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>3.279</v>
+      </c>
+      <c r="C304">
+        <v>0.314</v>
+      </c>
+      <c r="D304">
+        <v>0</v>
+      </c>
+      <c r="E304">
+        <v>0</v>
+      </c>
+      <c r="F304">
+        <v>15</v>
+      </c>
+      <c r="G304" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7">
+      <c r="A305" s="2">
+        <v>46301.15625</v>
+      </c>
+      <c r="B305">
+        <v>0</v>
+      </c>
+      <c r="C305">
+        <v>3.258</v>
+      </c>
+      <c r="D305">
+        <v>0</v>
+      </c>
+      <c r="E305">
+        <v>0</v>
+      </c>
+      <c r="F305">
+        <v>16</v>
+      </c>
+      <c r="G305" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7">
+      <c r="A306" s="2">
+        <v>46301.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>0.143</v>
+      </c>
+      <c r="C306">
+        <v>0.466</v>
+      </c>
+      <c r="D306">
+        <v>0</v>
+      </c>
+      <c r="E306">
+        <v>0</v>
+      </c>
+      <c r="F306">
+        <v>17</v>
+      </c>
+      <c r="G306" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7">
+      <c r="A307" s="2">
+        <v>46301.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>0.896</v>
+      </c>
+      <c r="C307">
+        <v>0.033</v>
+      </c>
+      <c r="D307">
+        <v>0</v>
+      </c>
+      <c r="E307">
+        <v>0</v>
+      </c>
+      <c r="F307">
+        <v>18</v>
+      </c>
+      <c r="G307" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7">
+      <c r="A308" s="2">
+        <v>46301.1875</v>
+      </c>
+      <c r="B308">
+        <v>9.968</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308">
+        <v>0</v>
+      </c>
+      <c r="E308">
+        <v>0</v>
+      </c>
+      <c r="F308">
+        <v>19</v>
+      </c>
+      <c r="G308" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7">
+      <c r="A309" s="2">
+        <v>46301.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>9.326000000000001</v>
+      </c>
+      <c r="C309">
+        <v>0</v>
+      </c>
+      <c r="D309">
+        <v>0</v>
+      </c>
+      <c r="E309">
+        <v>0</v>
+      </c>
+      <c r="F309">
+        <v>20</v>
+      </c>
+      <c r="G309" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7">
+      <c r="A310" s="2">
+        <v>46301.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>1.192</v>
+      </c>
+      <c r="C310">
+        <v>0.849</v>
+      </c>
+      <c r="D310">
+        <v>0</v>
+      </c>
+      <c r="E310">
+        <v>0</v>
+      </c>
+      <c r="F310">
+        <v>21</v>
+      </c>
+      <c r="G310" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7">
+      <c r="A311" s="2">
+        <v>46301.21875</v>
+      </c>
+      <c r="B311">
+        <v>15.081</v>
+      </c>
+      <c r="C311">
+        <v>0</v>
+      </c>
+      <c r="D311">
+        <v>0</v>
+      </c>
+      <c r="E311">
+        <v>0</v>
+      </c>
+      <c r="F311">
+        <v>22</v>
+      </c>
+      <c r="G311" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7">
+      <c r="A312" s="2">
+        <v>46301.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>30.314</v>
+      </c>
+      <c r="C312">
+        <v>0</v>
+      </c>
+      <c r="D312">
+        <v>0</v>
+      </c>
+      <c r="E312">
+        <v>0</v>
+      </c>
+      <c r="F312">
+        <v>23</v>
+      </c>
+      <c r="G312" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7">
+      <c r="A313" s="2">
+        <v>46301.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>40.806</v>
+      </c>
+      <c r="C313">
+        <v>0</v>
+      </c>
+      <c r="D313">
+        <v>0</v>
+      </c>
+      <c r="E313">
+        <v>0</v>
+      </c>
+      <c r="F313">
+        <v>24</v>
+      </c>
+      <c r="G313" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7">
+      <c r="A314" s="2">
+        <v>46301.25</v>
+      </c>
+      <c r="B314">
+        <v>19.729</v>
+      </c>
+      <c r="C314">
+        <v>0</v>
+      </c>
+      <c r="D314">
+        <v>0</v>
+      </c>
+      <c r="E314">
+        <v>0</v>
+      </c>
+      <c r="F314">
+        <v>25</v>
+      </c>
+      <c r="G314" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7">
+      <c r="A315" s="2">
+        <v>46301.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>23.944</v>
+      </c>
+      <c r="C315">
+        <v>0</v>
+      </c>
+      <c r="D315">
+        <v>0</v>
+      </c>
+      <c r="E315">
+        <v>0</v>
+      </c>
+      <c r="F315">
+        <v>26</v>
+      </c>
+      <c r="G315" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7">
+      <c r="A316" s="2">
+        <v>46301.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>30.409</v>
+      </c>
+      <c r="C316">
+        <v>0</v>
+      </c>
+      <c r="D316">
+        <v>0</v>
+      </c>
+      <c r="E316">
+        <v>0</v>
+      </c>
+      <c r="F316">
+        <v>27</v>
+      </c>
+      <c r="G316" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7">
+      <c r="A317" s="2">
+        <v>46301.28125</v>
+      </c>
+      <c r="B317">
+        <v>22.34</v>
+      </c>
+      <c r="C317">
+        <v>0</v>
+      </c>
+      <c r="D317">
+        <v>0</v>
+      </c>
+      <c r="E317">
+        <v>0</v>
+      </c>
+      <c r="F317">
+        <v>28</v>
+      </c>
+      <c r="G317" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7">
+      <c r="A318" s="2">
+        <v>46301.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>16.041</v>
+      </c>
+      <c r="C318">
+        <v>0</v>
+      </c>
+      <c r="D318">
+        <v>0</v>
+      </c>
+      <c r="E318">
+        <v>0</v>
+      </c>
+      <c r="F318">
+        <v>29</v>
+      </c>
+      <c r="G318" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7">
+      <c r="A319" s="2">
+        <v>46301.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>0.878</v>
+      </c>
+      <c r="C319">
+        <v>0.003</v>
+      </c>
+      <c r="D319">
+        <v>0</v>
+      </c>
+      <c r="E319">
+        <v>0</v>
+      </c>
+      <c r="F319">
+        <v>30</v>
+      </c>
+      <c r="G319" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7">
+      <c r="A320" s="2">
+        <v>46301.3125</v>
+      </c>
+      <c r="B320">
+        <v>0.076</v>
+      </c>
+      <c r="C320">
+        <v>0.202</v>
+      </c>
+      <c r="D320">
+        <v>0</v>
+      </c>
+      <c r="E320">
+        <v>0</v>
+      </c>
+      <c r="F320">
+        <v>31</v>
+      </c>
+      <c r="G320" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7">
+      <c r="A321" s="2">
+        <v>46301.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>0.028</v>
+      </c>
+      <c r="C321">
+        <v>0.574</v>
+      </c>
+      <c r="D321">
+        <v>0</v>
+      </c>
+      <c r="E321">
+        <v>0</v>
+      </c>
+      <c r="F321">
+        <v>32</v>
+      </c>
+      <c r="G321" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7">
+      <c r="A322" s="2">
+        <v>46301.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>0.529</v>
+      </c>
+      <c r="C322">
+        <v>0.068</v>
+      </c>
+      <c r="D322">
+        <v>0</v>
+      </c>
+      <c r="E322">
+        <v>0</v>
+      </c>
+      <c r="F322">
+        <v>33</v>
+      </c>
+      <c r="G322" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7">
+      <c r="A323" s="2">
+        <v>46301.34375</v>
+      </c>
+      <c r="B323">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="C323">
+        <v>0.704</v>
+      </c>
+      <c r="D323">
+        <v>0</v>
+      </c>
+      <c r="E323">
+        <v>0</v>
+      </c>
+      <c r="F323">
+        <v>34</v>
+      </c>
+      <c r="G323" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7">
+      <c r="A324" s="2">
+        <v>46301.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>0</v>
+      </c>
+      <c r="C324">
+        <v>15.214</v>
+      </c>
+      <c r="D324">
+        <v>0</v>
+      </c>
+      <c r="E324">
+        <v>0</v>
+      </c>
+      <c r="F324">
+        <v>35</v>
+      </c>
+      <c r="G324" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7">
+      <c r="A325" s="2">
+        <v>46301.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>0</v>
+      </c>
+      <c r="C325">
+        <v>28.467</v>
+      </c>
+      <c r="D325">
+        <v>0</v>
+      </c>
+      <c r="E325">
+        <v>0</v>
+      </c>
+      <c r="F325">
+        <v>36</v>
+      </c>
+      <c r="G325" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7">
+      <c r="A326" s="2">
+        <v>46301.375</v>
+      </c>
+      <c r="B326">
+        <v>1.017</v>
+      </c>
+      <c r="C326">
+        <v>4.76</v>
+      </c>
+      <c r="D326">
+        <v>0</v>
+      </c>
+      <c r="E326">
+        <v>0</v>
+      </c>
+      <c r="F326">
+        <v>37</v>
+      </c>
+      <c r="G326" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7">
+      <c r="A327" s="2">
+        <v>46301.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>0.148</v>
+      </c>
+      <c r="C327">
+        <v>2.177</v>
+      </c>
+      <c r="D327">
+        <v>0</v>
+      </c>
+      <c r="E327">
+        <v>0</v>
+      </c>
+      <c r="F327">
+        <v>38</v>
+      </c>
+      <c r="G327" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7">
+      <c r="A328" s="2">
+        <v>46301.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>6.181</v>
+      </c>
+      <c r="C328">
+        <v>0.026</v>
+      </c>
+      <c r="D328">
+        <v>0</v>
+      </c>
+      <c r="E328">
+        <v>0</v>
+      </c>
+      <c r="F328">
+        <v>39</v>
+      </c>
+      <c r="G328" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7">
+      <c r="A329" s="2">
+        <v>46301.40625</v>
+      </c>
+      <c r="B329">
+        <v>0.348</v>
+      </c>
+      <c r="C329">
+        <v>2.552</v>
+      </c>
+      <c r="D329">
+        <v>0</v>
+      </c>
+      <c r="E329">
+        <v>0</v>
+      </c>
+      <c r="F329">
+        <v>40</v>
+      </c>
+      <c r="G329" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7">
+      <c r="A330" s="2">
+        <v>46301.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>13.677</v>
+      </c>
+      <c r="C330">
+        <v>0.102</v>
+      </c>
+      <c r="D330">
+        <v>0</v>
+      </c>
+      <c r="E330">
+        <v>0</v>
+      </c>
+      <c r="F330">
+        <v>41</v>
+      </c>
+      <c r="G330" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7">
+      <c r="A331" s="2">
+        <v>46301.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>6.867</v>
+      </c>
+      <c r="C331">
+        <v>0.006</v>
+      </c>
+      <c r="D331">
+        <v>0</v>
+      </c>
+      <c r="E331">
+        <v>0</v>
+      </c>
+      <c r="F331">
+        <v>42</v>
+      </c>
+      <c r="G331" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7">
+      <c r="A332" s="2">
+        <v>46301.4375</v>
+      </c>
+      <c r="B332">
+        <v>0.165</v>
+      </c>
+      <c r="C332">
+        <v>3.578</v>
+      </c>
+      <c r="D332">
+        <v>0</v>
+      </c>
+      <c r="E332">
+        <v>0</v>
+      </c>
+      <c r="F332">
+        <v>43</v>
+      </c>
+      <c r="G332" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7">
+      <c r="A333" s="2">
+        <v>46301.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>0.01</v>
+      </c>
+      <c r="C333">
+        <v>4.844</v>
+      </c>
+      <c r="D333">
+        <v>0</v>
+      </c>
+      <c r="E333">
+        <v>0</v>
+      </c>
+      <c r="F333">
+        <v>44</v>
+      </c>
+      <c r="G333" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7">
+      <c r="A334" s="2">
+        <v>46301.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>0.078</v>
+      </c>
+      <c r="C334">
+        <v>5.362</v>
+      </c>
+      <c r="D334">
+        <v>0</v>
+      </c>
+      <c r="E334">
+        <v>0</v>
+      </c>
+      <c r="F334">
+        <v>45</v>
+      </c>
+      <c r="G334" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7">
+      <c r="A335" s="2">
+        <v>46301.46875</v>
+      </c>
+      <c r="B335">
+        <v>0.055</v>
+      </c>
+      <c r="C335">
+        <v>0.697</v>
+      </c>
+      <c r="D335">
+        <v>0</v>
+      </c>
+      <c r="E335">
+        <v>0</v>
+      </c>
+      <c r="F335">
+        <v>46</v>
+      </c>
+      <c r="G335" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7">
+      <c r="A336" s="2">
+        <v>46301.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>2.717</v>
+      </c>
+      <c r="C336">
+        <v>0.097</v>
+      </c>
+      <c r="D336">
+        <v>0</v>
+      </c>
+      <c r="E336">
+        <v>0</v>
+      </c>
+      <c r="F336">
+        <v>47</v>
+      </c>
+      <c r="G336" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7">
+      <c r="A337" s="2">
+        <v>46301.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>0.278</v>
+      </c>
+      <c r="C337">
+        <v>2.965</v>
+      </c>
+      <c r="D337">
+        <v>0</v>
+      </c>
+      <c r="E337">
+        <v>0</v>
+      </c>
+      <c r="F337">
+        <v>48</v>
+      </c>
+      <c r="G337" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7">
+      <c r="A338" s="2">
+        <v>46301.5</v>
+      </c>
+      <c r="B338">
+        <v>0</v>
+      </c>
+      <c r="C338">
+        <v>16.59</v>
+      </c>
+      <c r="D338">
+        <v>0</v>
+      </c>
+      <c r="E338">
+        <v>0</v>
+      </c>
+      <c r="F338">
+        <v>49</v>
+      </c>
+      <c r="G338" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7">
+      <c r="A339" s="2">
+        <v>46301.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>0</v>
+      </c>
+      <c r="C339">
+        <v>10.631</v>
+      </c>
+      <c r="D339">
+        <v>0</v>
+      </c>
+      <c r="E339">
+        <v>0</v>
+      </c>
+      <c r="F339">
+        <v>50</v>
+      </c>
+      <c r="G339" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7">
+      <c r="A340" s="2">
+        <v>46301.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>0.784</v>
+      </c>
+      <c r="C340">
+        <v>0.465</v>
+      </c>
+      <c r="D340">
+        <v>0</v>
+      </c>
+      <c r="E340">
+        <v>0</v>
+      </c>
+      <c r="F340">
+        <v>51</v>
+      </c>
+      <c r="G340" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7">
+      <c r="A341" s="2">
+        <v>46301.53125</v>
+      </c>
+      <c r="B341">
+        <v>0</v>
+      </c>
+      <c r="C341">
+        <v>0</v>
+      </c>
+      <c r="D341">
+        <v>0</v>
+      </c>
+      <c r="E341">
+        <v>0</v>
+      </c>
+      <c r="F341">
+        <v>52</v>
+      </c>
+      <c r="G341" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7">
+      <c r="A342" s="2">
+        <v>46301.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>0</v>
+      </c>
+      <c r="C342">
+        <v>5.985</v>
+      </c>
+      <c r="D342">
+        <v>0</v>
+      </c>
+      <c r="E342">
+        <v>0</v>
+      </c>
+      <c r="F342">
+        <v>53</v>
+      </c>
+      <c r="G342" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7">
+      <c r="A343" s="2">
+        <v>46301.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>0</v>
+      </c>
+      <c r="C343">
+        <v>4.097</v>
+      </c>
+      <c r="D343">
+        <v>0</v>
+      </c>
+      <c r="E343">
+        <v>0</v>
+      </c>
+      <c r="F343">
+        <v>54</v>
+      </c>
+      <c r="G343" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="344" spans="1:7">
+      <c r="A344" s="2">
+        <v>46301.5625</v>
+      </c>
+      <c r="B344">
+        <v>0.611</v>
+      </c>
+      <c r="C344">
+        <v>4.126</v>
+      </c>
+      <c r="D344">
+        <v>0</v>
+      </c>
+      <c r="E344">
+        <v>0</v>
+      </c>
+      <c r="F344">
+        <v>55</v>
+      </c>
+      <c r="G344" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7">
+      <c r="A345" s="2">
+        <v>46301.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>1.308</v>
+      </c>
+      <c r="C345">
+        <v>0.758</v>
+      </c>
+      <c r="D345">
+        <v>0</v>
+      </c>
+      <c r="E345">
+        <v>0</v>
+      </c>
+      <c r="F345">
+        <v>56</v>
+      </c>
+      <c r="G345" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7">
+      <c r="A346" s="2">
+        <v>46301.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>0</v>
+      </c>
+      <c r="C346">
+        <v>13.668</v>
+      </c>
+      <c r="D346">
+        <v>0</v>
+      </c>
+      <c r="E346">
+        <v>0</v>
+      </c>
+      <c r="F346">
+        <v>57</v>
+      </c>
+      <c r="G346" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="347" spans="1:7">
+      <c r="A347" s="2">
+        <v>46301.59375</v>
+      </c>
+      <c r="B347">
+        <v>0</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+      <c r="D347">
+        <v>0</v>
+      </c>
+      <c r="E347">
+        <v>0</v>
+      </c>
+      <c r="F347">
+        <v>58</v>
+      </c>
+      <c r="G347" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="348" spans="1:7">
+      <c r="A348" s="2">
+        <v>46301.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>0.449</v>
+      </c>
+      <c r="C348">
+        <v>0.477</v>
+      </c>
+      <c r="D348">
+        <v>0</v>
+      </c>
+      <c r="E348">
+        <v>0</v>
+      </c>
+      <c r="F348">
+        <v>59</v>
+      </c>
+      <c r="G348" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7">
+      <c r="A349" s="2">
+        <v>46301.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>0.012</v>
+      </c>
+      <c r="C349">
+        <v>6.087</v>
+      </c>
+      <c r="D349">
+        <v>0</v>
+      </c>
+      <c r="E349">
+        <v>0</v>
+      </c>
+      <c r="F349">
+        <v>60</v>
+      </c>
+      <c r="G349" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7">
+      <c r="A350" s="2">
+        <v>46301.625</v>
+      </c>
+      <c r="B350">
+        <v>0</v>
+      </c>
+      <c r="C350">
+        <v>64.404</v>
+      </c>
+      <c r="D350">
+        <v>0</v>
+      </c>
+      <c r="E350">
+        <v>0</v>
+      </c>
+      <c r="F350">
+        <v>61</v>
+      </c>
+      <c r="G350" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7">
+      <c r="A351" s="2">
+        <v>46301.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+      <c r="C351">
+        <v>47.486</v>
+      </c>
+      <c r="D351">
+        <v>0</v>
+      </c>
+      <c r="E351">
+        <v>0</v>
+      </c>
+      <c r="F351">
+        <v>62</v>
+      </c>
+      <c r="G351" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7">
+      <c r="A352" s="2">
+        <v>46301.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>0</v>
+      </c>
+      <c r="C352">
+        <v>20.263</v>
+      </c>
+      <c r="D352">
+        <v>0</v>
+      </c>
+      <c r="E352">
+        <v>37.5</v>
+      </c>
+      <c r="F352">
+        <v>63</v>
+      </c>
+      <c r="G352" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7">
+      <c r="A353" s="2">
+        <v>46301.65625</v>
+      </c>
+      <c r="B353">
+        <v>0.191</v>
+      </c>
+      <c r="C353">
+        <v>0.227</v>
+      </c>
+      <c r="D353">
+        <v>0</v>
+      </c>
+      <c r="E353">
+        <v>37.5</v>
+      </c>
+      <c r="F353">
+        <v>64</v>
+      </c>
+      <c r="G353" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7">
+      <c r="A354" s="2">
+        <v>46301.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+      <c r="C354">
+        <v>25.744</v>
+      </c>
+      <c r="D354">
+        <v>0</v>
+      </c>
+      <c r="E354">
+        <v>37.5</v>
+      </c>
+      <c r="F354">
+        <v>65</v>
+      </c>
+      <c r="G354" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7">
+      <c r="A355" s="2">
+        <v>46301.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>0.057</v>
+      </c>
+      <c r="C355">
+        <v>14.68</v>
+      </c>
+      <c r="D355">
+        <v>0</v>
+      </c>
+      <c r="E355">
+        <v>37.5</v>
+      </c>
+      <c r="F355">
+        <v>66</v>
+      </c>
+      <c r="G355" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7">
+      <c r="A356" s="2">
+        <v>46301.6875</v>
+      </c>
+      <c r="B356">
+        <v>0.219</v>
+      </c>
+      <c r="C356">
+        <v>0.212</v>
+      </c>
+      <c r="D356">
+        <v>0</v>
+      </c>
+      <c r="E356">
+        <v>37.5</v>
+      </c>
+      <c r="F356">
+        <v>67</v>
+      </c>
+      <c r="G356" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7">
+      <c r="A357" s="2">
+        <v>46301.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>26.402</v>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+      <c r="D357">
+        <v>0</v>
+      </c>
+      <c r="E357">
+        <v>37.5</v>
+      </c>
+      <c r="F357">
+        <v>68</v>
+      </c>
+      <c r="G357" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7">
+      <c r="A358" s="2">
+        <v>46301.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>11.445</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+      <c r="D358">
+        <v>0</v>
+      </c>
+      <c r="E358">
+        <v>37.5</v>
+      </c>
+      <c r="F358">
+        <v>69</v>
+      </c>
+      <c r="G358" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7">
+      <c r="A359" s="2">
+        <v>46301.71875</v>
+      </c>
+      <c r="B359">
+        <v>30.706</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+      <c r="D359">
+        <v>0</v>
+      </c>
+      <c r="E359">
+        <v>37.5</v>
+      </c>
+      <c r="F359">
+        <v>70</v>
+      </c>
+      <c r="G359" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7">
+      <c r="A360" s="2">
+        <v>46301.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>3.047</v>
+      </c>
+      <c r="C360">
+        <v>0.015</v>
+      </c>
+      <c r="D360">
+        <v>0</v>
+      </c>
+      <c r="E360">
+        <v>0</v>
+      </c>
+      <c r="F360">
+        <v>71</v>
+      </c>
+      <c r="G360" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7">
+      <c r="A361" s="2">
+        <v>46301.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>0.141</v>
+      </c>
+      <c r="C361">
+        <v>0.279</v>
+      </c>
+      <c r="D361">
+        <v>0</v>
+      </c>
+      <c r="E361">
+        <v>0</v>
+      </c>
+      <c r="F361">
+        <v>72</v>
+      </c>
+      <c r="G361" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7">
+      <c r="A362" s="2">
+        <v>46301.75</v>
+      </c>
+      <c r="B362">
+        <v>6.507</v>
+      </c>
+      <c r="C362">
+        <v>0.014</v>
+      </c>
+      <c r="D362">
+        <v>0</v>
+      </c>
+      <c r="E362">
+        <v>0</v>
+      </c>
+      <c r="F362">
+        <v>73</v>
+      </c>
+      <c r="G362" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7">
+      <c r="A363" s="2">
+        <v>46301.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>19.49</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+      <c r="D363">
+        <v>0</v>
+      </c>
+      <c r="E363">
+        <v>0</v>
+      </c>
+      <c r="F363">
+        <v>74</v>
+      </c>
+      <c r="G363" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7">
+      <c r="A364" s="2">
+        <v>46301.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>33.484</v>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+      <c r="D364">
+        <v>0</v>
+      </c>
+      <c r="E364">
+        <v>0</v>
+      </c>
+      <c r="F364">
+        <v>75</v>
+      </c>
+      <c r="G364" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7">
+      <c r="A365" s="2">
+        <v>46301.78125</v>
+      </c>
+      <c r="B365">
+        <v>37.934</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+      <c r="D365">
+        <v>0</v>
+      </c>
+      <c r="E365">
+        <v>0</v>
+      </c>
+      <c r="F365">
+        <v>76</v>
+      </c>
+      <c r="G365" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7">
+      <c r="A366" s="2">
+        <v>46301.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>23.509</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366">
+        <v>19.75</v>
+      </c>
+      <c r="E366">
+        <v>0</v>
+      </c>
+      <c r="F366">
+        <v>77</v>
+      </c>
+      <c r="G366" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7">
+      <c r="A367" s="2">
+        <v>46301.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>1.289</v>
+      </c>
+      <c r="C367">
+        <v>0.05</v>
+      </c>
+      <c r="D367">
+        <v>40</v>
+      </c>
+      <c r="E367">
+        <v>0</v>
+      </c>
+      <c r="F367">
+        <v>78</v>
+      </c>
+      <c r="G367" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7">
+      <c r="A368" s="2">
+        <v>46301.8125</v>
+      </c>
+      <c r="B368">
+        <v>0.057</v>
+      </c>
+      <c r="C368">
+        <v>0.227</v>
+      </c>
+      <c r="D368">
+        <v>40</v>
+      </c>
+      <c r="E368">
+        <v>0</v>
+      </c>
+      <c r="F368">
+        <v>79</v>
+      </c>
+      <c r="G368" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7">
+      <c r="A369" s="2">
+        <v>46301.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>0.238</v>
+      </c>
+      <c r="C369">
+        <v>1.822</v>
+      </c>
+      <c r="D369">
+        <v>29.75</v>
+      </c>
+      <c r="E369">
+        <v>0</v>
+      </c>
+      <c r="F369">
+        <v>80</v>
+      </c>
+      <c r="G369" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7">
+      <c r="A370" s="2">
+        <v>46301.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>0.015</v>
+      </c>
+      <c r="C370">
+        <v>1.422</v>
+      </c>
+      <c r="D370">
+        <v>25</v>
+      </c>
+      <c r="E370">
+        <v>0</v>
+      </c>
+      <c r="F370">
+        <v>81</v>
+      </c>
+      <c r="G370" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7">
+      <c r="A371" s="2">
+        <v>46301.84375</v>
+      </c>
+      <c r="B371">
+        <v>0.002</v>
+      </c>
+      <c r="C371">
+        <v>1.716</v>
+      </c>
+      <c r="D371">
+        <v>12.5</v>
+      </c>
+      <c r="E371">
+        <v>0</v>
+      </c>
+      <c r="F371">
+        <v>82</v>
+      </c>
+      <c r="G371" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7">
+      <c r="A372" s="2">
+        <v>46301.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>0.051</v>
+      </c>
+      <c r="C372">
+        <v>0.445</v>
+      </c>
+      <c r="D372">
+        <v>0</v>
+      </c>
+      <c r="E372">
+        <v>0</v>
+      </c>
+      <c r="F372">
+        <v>83</v>
+      </c>
+      <c r="G372" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7">
+      <c r="A373" s="2">
+        <v>46301.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+      <c r="C373">
+        <v>4.665</v>
+      </c>
+      <c r="D373">
+        <v>0</v>
+      </c>
+      <c r="E373">
+        <v>0</v>
+      </c>
+      <c r="F373">
+        <v>84</v>
+      </c>
+      <c r="G373" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7">
+      <c r="A374" s="2">
+        <v>46301.875</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+      <c r="C374">
+        <v>8.153</v>
+      </c>
+      <c r="D374">
+        <v>0</v>
+      </c>
+      <c r="E374">
+        <v>0</v>
+      </c>
+      <c r="F374">
+        <v>85</v>
+      </c>
+      <c r="G374" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="375" spans="1:7">
+      <c r="A375" s="2">
+        <v>46301.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>0.242</v>
+      </c>
+      <c r="C375">
+        <v>2.336</v>
+      </c>
+      <c r="D375">
+        <v>0</v>
+      </c>
+      <c r="E375">
+        <v>0</v>
+      </c>
+      <c r="F375">
+        <v>86</v>
+      </c>
+      <c r="G375" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="376" spans="1:7">
+      <c r="A376" s="2">
+        <v>46301.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+      <c r="C376">
+        <v>3.199</v>
+      </c>
+      <c r="D376">
+        <v>0</v>
+      </c>
+      <c r="E376">
+        <v>0</v>
+      </c>
+      <c r="F376">
+        <v>87</v>
+      </c>
+      <c r="G376" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="377" spans="1:7">
+      <c r="A377" s="2">
+        <v>46301.90625</v>
+      </c>
+      <c r="B377">
+        <v>0.146</v>
+      </c>
+      <c r="C377">
+        <v>3.29</v>
+      </c>
+      <c r="D377">
+        <v>0</v>
+      </c>
+      <c r="E377">
+        <v>0</v>
+      </c>
+      <c r="F377">
+        <v>88</v>
+      </c>
+      <c r="G377" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7">
+      <c r="A378" s="2">
+        <v>46301.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>6.353</v>
+      </c>
+      <c r="C378">
+        <v>0.904</v>
+      </c>
+      <c r="D378">
+        <v>0</v>
+      </c>
+      <c r="E378">
+        <v>0</v>
+      </c>
+      <c r="F378">
+        <v>89</v>
+      </c>
+      <c r="G378" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7">
+      <c r="A379" s="2">
+        <v>46301.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>12.175</v>
+      </c>
+      <c r="C379">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="D379">
+        <v>0</v>
+      </c>
+      <c r="E379">
+        <v>0</v>
+      </c>
+      <c r="F379">
+        <v>90</v>
+      </c>
+      <c r="G379" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7">
+      <c r="A380" s="2">
+        <v>46301.9375</v>
+      </c>
+      <c r="B380">
+        <v>5.481</v>
+      </c>
+      <c r="C380">
+        <v>0.619</v>
+      </c>
+      <c r="D380">
+        <v>0</v>
+      </c>
+      <c r="E380">
+        <v>0</v>
+      </c>
+      <c r="F380">
+        <v>91</v>
+      </c>
+      <c r="G380" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="381" spans="1:7">
+      <c r="A381" s="2">
+        <v>46301.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>0.256</v>
+      </c>
+      <c r="C381">
+        <v>6.321</v>
+      </c>
+      <c r="D381">
+        <v>0</v>
+      </c>
+      <c r="E381">
+        <v>0</v>
+      </c>
+      <c r="F381">
+        <v>92</v>
+      </c>
+      <c r="G381" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="382" spans="1:7">
+      <c r="A382" s="2">
+        <v>46301.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>16.86</v>
+      </c>
+      <c r="C382">
+        <v>1.462</v>
+      </c>
+      <c r="D382">
+        <v>0</v>
+      </c>
+      <c r="E382">
+        <v>0</v>
+      </c>
+      <c r="F382">
+        <v>93</v>
+      </c>
+      <c r="G382" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7">
+      <c r="A383" s="2">
+        <v>46301.96875</v>
+      </c>
+      <c r="B383">
+        <v>7.827</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383">
+        <v>0</v>
+      </c>
+      <c r="E383">
+        <v>0</v>
+      </c>
+      <c r="F383">
+        <v>94</v>
+      </c>
+      <c r="G383" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="384" spans="1:7">
+      <c r="A384" s="2">
+        <v>46301.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>2.986</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>0</v>
+      </c>
+      <c r="E384">
+        <v>0</v>
+      </c>
+      <c r="F384">
+        <v>95</v>
+      </c>
+      <c r="G384" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="385" spans="1:7">
+      <c r="A385" s="2">
+        <v>46301.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>1.099</v>
+      </c>
+      <c r="C385">
+        <v>1.066</v>
+      </c>
+      <c r="D385">
+        <v>0</v>
+      </c>
+      <c r="E385">
+        <v>0</v>
+      </c>
+      <c r="F385">
+        <v>96</v>
+      </c>
+      <c r="G385" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="386" spans="1:7">
+      <c r="A386" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B386">
+        <v>21.433</v>
+      </c>
+      <c r="C386">
+        <v>0.096</v>
+      </c>
+      <c r="D386">
+        <v>0</v>
+      </c>
+      <c r="E386">
+        <v>0</v>
+      </c>
+      <c r="F386">
+        <v>1</v>
+      </c>
+      <c r="G386" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="387" spans="1:7">
+      <c r="A387" s="2">
+        <v>46302.01041666666</v>
+      </c>
+      <c r="B387">
+        <v>27.354</v>
+      </c>
+      <c r="C387">
+        <v>0</v>
+      </c>
+      <c r="D387">
+        <v>0</v>
+      </c>
+      <c r="E387">
+        <v>0</v>
+      </c>
+      <c r="F387">
+        <v>2</v>
+      </c>
+      <c r="G387" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="388" spans="1:7">
+      <c r="A388" s="2">
+        <v>46302.02083333334</v>
+      </c>
+      <c r="B388">
+        <v>19.511</v>
+      </c>
+      <c r="C388">
+        <v>0</v>
+      </c>
+      <c r="D388">
+        <v>0</v>
+      </c>
+      <c r="E388">
+        <v>0</v>
+      </c>
+      <c r="F388">
+        <v>3</v>
+      </c>
+      <c r="G388" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="389" spans="1:7">
+      <c r="A389" s="2">
+        <v>46302.03125</v>
+      </c>
+      <c r="B389">
+        <v>24.424</v>
+      </c>
+      <c r="C389">
+        <v>0</v>
+      </c>
+      <c r="D389">
+        <v>0</v>
+      </c>
+      <c r="E389">
+        <v>0</v>
+      </c>
+      <c r="F389">
+        <v>4</v>
+      </c>
+      <c r="G389" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="390" spans="1:7">
+      <c r="A390" s="2">
+        <v>46302.04166666666</v>
+      </c>
+      <c r="B390">
+        <v>26.152</v>
+      </c>
+      <c r="C390">
+        <v>0</v>
+      </c>
+      <c r="D390">
+        <v>0</v>
+      </c>
+      <c r="E390">
+        <v>0</v>
+      </c>
+      <c r="F390">
+        <v>5</v>
+      </c>
+      <c r="G390" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="391" spans="1:7">
+      <c r="A391" s="2">
+        <v>46302.05208333334</v>
+      </c>
+      <c r="B391">
+        <v>0.554</v>
+      </c>
+      <c r="C391">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="D391">
+        <v>25</v>
+      </c>
+      <c r="E391">
+        <v>0</v>
+      </c>
+      <c r="F391">
+        <v>6</v>
+      </c>
+      <c r="G391" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="392" spans="1:7">
+      <c r="A392" s="2">
+        <v>46302.0625</v>
+      </c>
+      <c r="B392">
+        <v>5.632</v>
+      </c>
+      <c r="C392">
+        <v>0</v>
+      </c>
+      <c r="D392">
+        <v>25</v>
+      </c>
+      <c r="E392">
+        <v>0</v>
+      </c>
+      <c r="F392">
+        <v>7</v>
+      </c>
+      <c r="G392" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="393" spans="1:7">
+      <c r="A393" s="2">
+        <v>46302.07291666666</v>
+      </c>
+      <c r="B393">
+        <v>3.281</v>
+      </c>
+      <c r="C393">
+        <v>0.47</v>
+      </c>
+      <c r="D393">
+        <v>25</v>
+      </c>
+      <c r="E393">
+        <v>0</v>
+      </c>
+      <c r="F393">
+        <v>8</v>
+      </c>
+      <c r="G393" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="394" spans="1:7">
+      <c r="A394" s="2">
+        <v>46302.08333333334</v>
+      </c>
+      <c r="B394">
+        <v>6.403</v>
+      </c>
+      <c r="C394">
+        <v>0</v>
+      </c>
+      <c r="D394">
+        <v>25</v>
+      </c>
+      <c r="E394">
+        <v>0</v>
+      </c>
+      <c r="F394">
+        <v>9</v>
+      </c>
+      <c r="G394" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="395" spans="1:7">
+      <c r="A395" s="2">
+        <v>46302.09375</v>
+      </c>
+      <c r="B395">
+        <v>22.644</v>
+      </c>
+      <c r="C395">
+        <v>0</v>
+      </c>
+      <c r="D395">
+        <v>0</v>
+      </c>
+      <c r="E395">
+        <v>0</v>
+      </c>
+      <c r="F395">
+        <v>10</v>
+      </c>
+      <c r="G395" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="396" spans="1:7">
+      <c r="A396" s="2">
+        <v>46302.10416666666</v>
+      </c>
+      <c r="B396">
+        <v>10.201</v>
+      </c>
+      <c r="C396">
+        <v>0</v>
+      </c>
+      <c r="D396">
+        <v>0</v>
+      </c>
+      <c r="E396">
+        <v>0</v>
+      </c>
+      <c r="F396">
+        <v>11</v>
+      </c>
+      <c r="G396" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="397" spans="1:7">
+      <c r="A397" s="2">
+        <v>46302.11458333334</v>
+      </c>
+      <c r="B397">
+        <v>5.872</v>
+      </c>
+      <c r="C397">
+        <v>0</v>
+      </c>
+      <c r="D397">
+        <v>0</v>
+      </c>
+      <c r="E397">
+        <v>0</v>
+      </c>
+      <c r="F397">
+        <v>12</v>
+      </c>
+      <c r="G397" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="398" spans="1:7">
+      <c r="A398" s="2">
+        <v>46302.125</v>
+      </c>
+      <c r="B398">
+        <v>5.815</v>
+      </c>
+      <c r="C398">
+        <v>0</v>
+      </c>
+      <c r="D398">
+        <v>0</v>
+      </c>
+      <c r="E398">
+        <v>0</v>
+      </c>
+      <c r="F398">
+        <v>13</v>
+      </c>
+      <c r="G398" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="399" spans="1:7">
+      <c r="A399" s="2">
+        <v>46302.13541666666</v>
+      </c>
+      <c r="B399">
+        <v>9.999000000000001</v>
+      </c>
+      <c r="C399">
+        <v>0</v>
+      </c>
+      <c r="D399">
+        <v>0</v>
+      </c>
+      <c r="E399">
+        <v>0</v>
+      </c>
+      <c r="F399">
+        <v>14</v>
+      </c>
+      <c r="G399" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="400" spans="1:7">
+      <c r="A400" s="2">
+        <v>46302.14583333334</v>
+      </c>
+      <c r="B400">
+        <v>3.975</v>
+      </c>
+      <c r="C400">
+        <v>0</v>
+      </c>
+      <c r="D400">
+        <v>0</v>
+      </c>
+      <c r="E400">
+        <v>0</v>
+      </c>
+      <c r="F400">
+        <v>15</v>
+      </c>
+      <c r="G400" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="401" spans="1:7">
+      <c r="A401" s="2">
+        <v>46302.15625</v>
+      </c>
+      <c r="B401">
+        <v>15.934</v>
+      </c>
+      <c r="C401">
+        <v>0</v>
+      </c>
+      <c r="D401">
+        <v>0</v>
+      </c>
+      <c r="E401">
+        <v>0</v>
+      </c>
+      <c r="F401">
+        <v>16</v>
+      </c>
+      <c r="G401" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="402" spans="1:7">
+      <c r="A402" s="2">
+        <v>46302.16666666666</v>
+      </c>
+      <c r="B402">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="C402">
+        <v>0</v>
+      </c>
+      <c r="D402">
+        <v>0</v>
+      </c>
+      <c r="E402">
+        <v>0</v>
+      </c>
+      <c r="F402">
+        <v>17</v>
+      </c>
+      <c r="G402" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="403" spans="1:7">
+      <c r="A403" s="2">
+        <v>46302.17708333334</v>
+      </c>
+      <c r="B403">
+        <v>26.013</v>
+      </c>
+      <c r="C403">
+        <v>0</v>
+      </c>
+      <c r="D403">
+        <v>0</v>
+      </c>
+      <c r="E403">
+        <v>0</v>
+      </c>
+      <c r="F403">
+        <v>18</v>
+      </c>
+      <c r="G403" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="404" spans="1:7">
+      <c r="A404" s="2">
+        <v>46302.1875</v>
+      </c>
+      <c r="B404">
+        <v>19.229</v>
+      </c>
+      <c r="C404">
+        <v>0</v>
+      </c>
+      <c r="D404">
+        <v>0</v>
+      </c>
+      <c r="E404">
+        <v>0</v>
+      </c>
+      <c r="F404">
+        <v>19</v>
+      </c>
+      <c r="G404" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="405" spans="1:7">
+      <c r="A405" s="2">
+        <v>46302.19791666666</v>
+      </c>
+      <c r="B405">
+        <v>32.808</v>
+      </c>
+      <c r="C405">
+        <v>0</v>
+      </c>
+      <c r="D405">
+        <v>0</v>
+      </c>
+      <c r="E405">
+        <v>0</v>
+      </c>
+      <c r="F405">
+        <v>20</v>
+      </c>
+      <c r="G405" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="406" spans="1:7">
+      <c r="A406" s="2">
+        <v>46302.20833333334</v>
+      </c>
+      <c r="B406">
+        <v>19.984</v>
+      </c>
+      <c r="C406">
+        <v>0</v>
+      </c>
+      <c r="D406">
+        <v>0</v>
+      </c>
+      <c r="E406">
+        <v>0</v>
+      </c>
+      <c r="F406">
+        <v>21</v>
+      </c>
+      <c r="G406" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="407" spans="1:7">
+      <c r="A407" s="2">
+        <v>46302.21875</v>
+      </c>
+      <c r="B407">
+        <v>10.558</v>
+      </c>
+      <c r="C407">
+        <v>0</v>
+      </c>
+      <c r="D407">
+        <v>0</v>
+      </c>
+      <c r="E407">
+        <v>0</v>
+      </c>
+      <c r="F407">
+        <v>22</v>
+      </c>
+      <c r="G407" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="408" spans="1:7">
+      <c r="A408" s="2">
+        <v>46302.22916666666</v>
+      </c>
+      <c r="B408">
+        <v>23.457</v>
+      </c>
+      <c r="C408">
+        <v>0</v>
+      </c>
+      <c r="D408">
+        <v>0</v>
+      </c>
+      <c r="E408">
+        <v>0</v>
+      </c>
+      <c r="F408">
+        <v>23</v>
+      </c>
+      <c r="G408" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="409" spans="1:7">
+      <c r="A409" s="2">
+        <v>46302.23958333334</v>
+      </c>
+      <c r="B409">
+        <v>27.364</v>
+      </c>
+      <c r="C409">
+        <v>0</v>
+      </c>
+      <c r="D409">
+        <v>0</v>
+      </c>
+      <c r="E409">
+        <v>0</v>
+      </c>
+      <c r="F409">
+        <v>24</v>
+      </c>
+      <c r="G409" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="410" spans="1:7">
+      <c r="A410" s="2">
+        <v>46302.25</v>
+      </c>
+      <c r="B410">
+        <v>26.218</v>
+      </c>
+      <c r="C410">
+        <v>0</v>
+      </c>
+      <c r="D410">
+        <v>0</v>
+      </c>
+      <c r="E410">
+        <v>0</v>
+      </c>
+      <c r="F410">
+        <v>25</v>
+      </c>
+      <c r="G410" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="411" spans="1:7">
+      <c r="A411" s="2">
+        <v>46302.26041666666</v>
+      </c>
+      <c r="B411">
+        <v>52.106</v>
+      </c>
+      <c r="C411">
+        <v>0</v>
+      </c>
+      <c r="D411">
+        <v>0</v>
+      </c>
+      <c r="E411">
+        <v>0</v>
+      </c>
+      <c r="F411">
+        <v>26</v>
+      </c>
+      <c r="G411" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="412" spans="1:7">
+      <c r="A412" s="2">
+        <v>46302.27083333334</v>
+      </c>
+      <c r="B412">
+        <v>41.627</v>
+      </c>
+      <c r="C412">
+        <v>0</v>
+      </c>
+      <c r="D412">
+        <v>0</v>
+      </c>
+      <c r="E412">
+        <v>0</v>
+      </c>
+      <c r="F412">
+        <v>27</v>
+      </c>
+      <c r="G412" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="413" spans="1:7">
+      <c r="A413" s="2">
+        <v>46302.28125</v>
+      </c>
+      <c r="B413">
+        <v>20.222</v>
+      </c>
+      <c r="C413">
+        <v>0</v>
+      </c>
+      <c r="D413">
+        <v>0</v>
+      </c>
+      <c r="E413">
+        <v>0</v>
+      </c>
+      <c r="F413">
+        <v>28</v>
+      </c>
+      <c r="G413" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="414" spans="1:7">
+      <c r="A414" s="2">
+        <v>46302.29166666666</v>
+      </c>
+      <c r="B414">
+        <v>57.112</v>
+      </c>
+      <c r="C414">
+        <v>0</v>
+      </c>
+      <c r="D414">
+        <v>0</v>
+      </c>
+      <c r="E414">
+        <v>0</v>
+      </c>
+      <c r="F414">
+        <v>29</v>
+      </c>
+      <c r="G414" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="415" spans="1:7">
+      <c r="A415" s="2">
+        <v>46302.30208333334</v>
+      </c>
+      <c r="B415">
+        <v>31.186</v>
+      </c>
+      <c r="C415">
+        <v>0</v>
+      </c>
+      <c r="D415">
+        <v>0</v>
+      </c>
+      <c r="E415">
+        <v>0</v>
+      </c>
+      <c r="F415">
+        <v>30</v>
+      </c>
+      <c r="G415" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="416" spans="1:7">
+      <c r="A416" s="2">
+        <v>46302.3125</v>
+      </c>
+      <c r="B416">
+        <v>3.519</v>
+      </c>
+      <c r="C416">
+        <v>2.713</v>
+      </c>
+      <c r="D416">
+        <v>0</v>
+      </c>
+      <c r="E416">
+        <v>0</v>
+      </c>
+      <c r="F416">
+        <v>31</v>
+      </c>
+      <c r="G416" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="417" spans="1:7">
+      <c r="A417" s="2">
+        <v>46302.32291666666</v>
+      </c>
+      <c r="B417">
+        <v>0</v>
+      </c>
+      <c r="C417">
+        <v>30.757</v>
+      </c>
+      <c r="D417">
+        <v>0</v>
+      </c>
+      <c r="E417">
+        <v>0</v>
+      </c>
+      <c r="F417">
+        <v>32</v>
+      </c>
+      <c r="G417" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="418" spans="1:7">
+      <c r="A418" s="2">
+        <v>46302.33333333334</v>
+      </c>
+      <c r="B418">
+        <v>1.121</v>
+      </c>
+      <c r="C418">
+        <v>6.763</v>
+      </c>
+      <c r="D418">
+        <v>0</v>
+      </c>
+      <c r="E418">
+        <v>0</v>
+      </c>
+      <c r="F418">
+        <v>33</v>
+      </c>
+      <c r="G418" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="419" spans="1:7">
+      <c r="A419" s="2">
+        <v>46302.34375</v>
+      </c>
+      <c r="B419">
+        <v>0</v>
+      </c>
+      <c r="C419">
+        <v>17.334</v>
+      </c>
+      <c r="D419">
+        <v>0</v>
+      </c>
+      <c r="E419">
+        <v>0</v>
+      </c>
+      <c r="F419">
+        <v>34</v>
+      </c>
+      <c r="G419" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="420" spans="1:7">
+      <c r="A420" s="2">
+        <v>46302.35416666666</v>
+      </c>
+      <c r="B420">
+        <v>0</v>
+      </c>
+      <c r="C420">
+        <v>22.156</v>
+      </c>
+      <c r="D420">
+        <v>0</v>
+      </c>
+      <c r="E420">
+        <v>0</v>
+      </c>
+      <c r="F420">
+        <v>35</v>
+      </c>
+      <c r="G420" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="421" spans="1:7">
+      <c r="A421" s="2">
+        <v>46302.36458333334</v>
+      </c>
+      <c r="B421">
+        <v>0</v>
+      </c>
+      <c r="C421">
+        <v>10.188</v>
+      </c>
+      <c r="D421">
+        <v>0</v>
+      </c>
+      <c r="E421">
+        <v>20</v>
+      </c>
+      <c r="F421">
+        <v>36</v>
+      </c>
+      <c r="G421" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="422" spans="1:7">
+      <c r="A422" s="2">
+        <v>46302.375</v>
+      </c>
+      <c r="B422">
+        <v>7.204</v>
+      </c>
+      <c r="C422">
+        <v>2.059</v>
+      </c>
+      <c r="D422">
+        <v>0</v>
+      </c>
+      <c r="E422">
+        <v>20</v>
+      </c>
+      <c r="F422">
+        <v>37</v>
+      </c>
+      <c r="G422" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="423" spans="1:7">
+      <c r="A423" s="2">
+        <v>46302.38541666666</v>
+      </c>
+      <c r="B423">
+        <v>0</v>
+      </c>
+      <c r="C423">
+        <v>2.808</v>
+      </c>
+      <c r="D423">
+        <v>0</v>
+      </c>
+      <c r="E423">
+        <v>0</v>
+      </c>
+      <c r="F423">
+        <v>38</v>
+      </c>
+      <c r="G423" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="424" spans="1:7">
+      <c r="A424" s="2">
+        <v>46302.39583333334</v>
+      </c>
+      <c r="B424">
+        <v>1.541</v>
+      </c>
+      <c r="C424">
+        <v>0.276</v>
+      </c>
+      <c r="D424">
+        <v>0</v>
+      </c>
+      <c r="E424">
+        <v>0</v>
+      </c>
+      <c r="F424">
+        <v>39</v>
+      </c>
+      <c r="G424" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="425" spans="1:7">
+      <c r="A425" s="2">
+        <v>46302.40625</v>
+      </c>
+      <c r="B425">
+        <v>0</v>
+      </c>
+      <c r="C425">
+        <v>3.523</v>
+      </c>
+      <c r="D425">
+        <v>0</v>
+      </c>
+      <c r="E425">
+        <v>0</v>
+      </c>
+      <c r="F425">
+        <v>40</v>
+      </c>
+      <c r="G425" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="426" spans="1:7">
+      <c r="A426" s="2">
+        <v>46302.41666666666</v>
+      </c>
+      <c r="B426">
+        <v>4.299</v>
+      </c>
+      <c r="C426">
+        <v>0.269</v>
+      </c>
+      <c r="D426">
+        <v>0</v>
+      </c>
+      <c r="E426">
+        <v>0</v>
+      </c>
+      <c r="F426">
+        <v>41</v>
+      </c>
+      <c r="G426" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="427" spans="1:7">
+      <c r="A427" s="2">
+        <v>46302.42708333334</v>
+      </c>
+      <c r="B427">
+        <v>0</v>
+      </c>
+      <c r="C427">
+        <v>0</v>
+      </c>
+      <c r="D427">
+        <v>0</v>
+      </c>
+      <c r="E427">
+        <v>0</v>
+      </c>
+      <c r="F427">
+        <v>42</v>
+      </c>
+      <c r="G427" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="428" spans="1:7">
+      <c r="A428" s="2">
+        <v>46302.4375</v>
+      </c>
+      <c r="B428">
+        <v>0</v>
+      </c>
+      <c r="C428">
+        <v>0</v>
+      </c>
+      <c r="D428">
+        <v>0</v>
+      </c>
+      <c r="E428">
+        <v>0</v>
+      </c>
+      <c r="F428">
+        <v>43</v>
+      </c>
+      <c r="G428" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="429" spans="1:7">
+      <c r="A429" s="2">
+        <v>46302.44791666666</v>
+      </c>
+      <c r="B429">
+        <v>0</v>
+      </c>
+      <c r="C429">
+        <v>0</v>
+      </c>
+      <c r="D429">
+        <v>0</v>
+      </c>
+      <c r="E429">
+        <v>0</v>
+      </c>
+      <c r="F429">
+        <v>44</v>
+      </c>
+      <c r="G429" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="430" spans="1:7">
+      <c r="A430" s="2">
+        <v>46302.45833333334</v>
+      </c>
+      <c r="B430">
+        <v>0</v>
+      </c>
+      <c r="C430">
+        <v>0</v>
+      </c>
+      <c r="D430">
+        <v>0</v>
+      </c>
+      <c r="E430">
+        <v>0</v>
+      </c>
+      <c r="F430">
+        <v>45</v>
+      </c>
+      <c r="G430" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="431" spans="1:7">
+      <c r="A431" s="2">
+        <v>46302.46875</v>
+      </c>
+      <c r="B431">
+        <v>0</v>
+      </c>
+      <c r="C431">
+        <v>0</v>
+      </c>
+      <c r="D431">
+        <v>0</v>
+      </c>
+      <c r="E431">
+        <v>0</v>
+      </c>
+      <c r="F431">
+        <v>46</v>
+      </c>
+      <c r="G431" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="432" spans="1:7">
+      <c r="A432" s="2">
+        <v>46302.47916666666</v>
+      </c>
+      <c r="B432">
+        <v>0</v>
+      </c>
+      <c r="C432">
+        <v>0</v>
+      </c>
+      <c r="D432">
+        <v>0</v>
+      </c>
+      <c r="E432">
+        <v>0</v>
+      </c>
+      <c r="F432">
+        <v>47</v>
+      </c>
+      <c r="G432" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="433" spans="1:7">
+      <c r="A433" s="2">
+        <v>46302.48958333334</v>
+      </c>
+      <c r="B433">
+        <v>0</v>
+      </c>
+      <c r="C433">
+        <v>0</v>
+      </c>
+      <c r="D433">
+        <v>0</v>
+      </c>
+      <c r="E433">
+        <v>0</v>
+      </c>
+      <c r="F433">
+        <v>48</v>
+      </c>
+      <c r="G433" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="434" spans="1:7">
+      <c r="A434" s="2">
+        <v>46302.5</v>
+      </c>
+      <c r="B434">
+        <v>0</v>
+      </c>
+      <c r="C434">
+        <v>0</v>
+      </c>
+      <c r="D434">
+        <v>0</v>
+      </c>
+      <c r="E434">
+        <v>0</v>
+      </c>
+      <c r="F434">
+        <v>49</v>
+      </c>
+      <c r="G434" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="435" spans="1:7">
+      <c r="A435" s="2">
+        <v>46302.51041666666</v>
+      </c>
+      <c r="B435">
+        <v>0</v>
+      </c>
+      <c r="C435">
+        <v>0</v>
+      </c>
+      <c r="D435">
+        <v>0</v>
+      </c>
+      <c r="E435">
+        <v>0</v>
+      </c>
+      <c r="F435">
+        <v>50</v>
+      </c>
+      <c r="G435" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="436" spans="1:7">
+      <c r="A436" s="2">
+        <v>46302.52083333334</v>
+      </c>
+      <c r="B436">
+        <v>0</v>
+      </c>
+      <c r="C436">
+        <v>0</v>
+      </c>
+      <c r="D436">
+        <v>0</v>
+      </c>
+      <c r="E436">
+        <v>0</v>
+      </c>
+      <c r="F436">
+        <v>51</v>
+      </c>
+      <c r="G436" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="437" spans="1:7">
+      <c r="A437" s="2">
+        <v>46302.53125</v>
+      </c>
+      <c r="B437">
+        <v>0</v>
+      </c>
+      <c r="C437">
+        <v>0</v>
+      </c>
+      <c r="D437">
+        <v>0</v>
+      </c>
+      <c r="E437">
+        <v>0</v>
+      </c>
+      <c r="F437">
+        <v>52</v>
+      </c>
+      <c r="G437" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="438" spans="1:7">
+      <c r="A438" s="2">
+        <v>46302.54166666666</v>
+      </c>
+      <c r="B438">
+        <v>0</v>
+      </c>
+      <c r="C438">
+        <v>0</v>
+      </c>
+      <c r="D438">
+        <v>0</v>
+      </c>
+      <c r="E438">
+        <v>0</v>
+      </c>
+      <c r="F438">
+        <v>53</v>
+      </c>
+      <c r="G438" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="439" spans="1:7">
+      <c r="A439" s="2">
+        <v>46302.55208333334</v>
+      </c>
+      <c r="B439">
+        <v>0</v>
+      </c>
+      <c r="C439">
+        <v>0</v>
+      </c>
+      <c r="D439">
+        <v>0</v>
+      </c>
+      <c r="E439">
+        <v>0</v>
+      </c>
+      <c r="F439">
+        <v>54</v>
+      </c>
+      <c r="G439" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="440" spans="1:7">
+      <c r="A440" s="2">
+        <v>46302.5625</v>
+      </c>
+      <c r="B440">
+        <v>0</v>
+      </c>
+      <c r="C440">
+        <v>0</v>
+      </c>
+      <c r="D440">
+        <v>0</v>
+      </c>
+      <c r="E440">
+        <v>0</v>
+      </c>
+      <c r="F440">
+        <v>55</v>
+      </c>
+      <c r="G440" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="441" spans="1:7">
+      <c r="A441" s="2">
+        <v>46302.57291666666</v>
+      </c>
+      <c r="B441">
+        <v>0</v>
+      </c>
+      <c r="C441">
+        <v>0</v>
+      </c>
+      <c r="D441">
+        <v>0</v>
+      </c>
+      <c r="E441">
+        <v>0</v>
+      </c>
+      <c r="F441">
+        <v>56</v>
+      </c>
+      <c r="G441" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="442" spans="1:7">
+      <c r="A442" s="2">
+        <v>46302.58333333334</v>
+      </c>
+      <c r="B442">
+        <v>0</v>
+      </c>
+      <c r="C442">
+        <v>0</v>
+      </c>
+      <c r="D442">
+        <v>0</v>
+      </c>
+      <c r="E442">
+        <v>0</v>
+      </c>
+      <c r="F442">
+        <v>57</v>
+      </c>
+      <c r="G442" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="443" spans="1:7">
+      <c r="A443" s="2">
+        <v>46302.59375</v>
+      </c>
+      <c r="B443">
+        <v>0</v>
+      </c>
+      <c r="C443">
+        <v>0</v>
+      </c>
+      <c r="D443">
+        <v>0</v>
+      </c>
+      <c r="E443">
+        <v>0</v>
+      </c>
+      <c r="F443">
+        <v>58</v>
+      </c>
+      <c r="G443" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="444" spans="1:7">
+      <c r="A444" s="2">
+        <v>46302.60416666666</v>
+      </c>
+      <c r="B444">
+        <v>0</v>
+      </c>
+      <c r="C444">
+        <v>0</v>
+      </c>
+      <c r="D444">
+        <v>0</v>
+      </c>
+      <c r="E444">
+        <v>0</v>
+      </c>
+      <c r="F444">
+        <v>59</v>
+      </c>
+      <c r="G444" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="445" spans="1:7">
+      <c r="A445" s="2">
+        <v>46302.61458333334</v>
+      </c>
+      <c r="B445">
+        <v>0</v>
+      </c>
+      <c r="C445">
+        <v>0</v>
+      </c>
+      <c r="D445">
+        <v>0</v>
+      </c>
+      <c r="E445">
+        <v>0</v>
+      </c>
+      <c r="F445">
+        <v>60</v>
+      </c>
+      <c r="G445" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="446" spans="1:7">
+      <c r="A446" s="2">
+        <v>46302.625</v>
+      </c>
+      <c r="B446">
+        <v>0</v>
+      </c>
+      <c r="C446">
+        <v>0</v>
+      </c>
+      <c r="D446">
+        <v>0</v>
+      </c>
+      <c r="E446">
+        <v>0</v>
+      </c>
+      <c r="F446">
+        <v>61</v>
+      </c>
+      <c r="G446" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="447" spans="1:7">
+      <c r="A447" s="2">
+        <v>46302.63541666666</v>
+      </c>
+      <c r="B447">
+        <v>0</v>
+      </c>
+      <c r="C447">
+        <v>0</v>
+      </c>
+      <c r="D447">
+        <v>0</v>
+      </c>
+      <c r="E447">
+        <v>0</v>
+      </c>
+      <c r="F447">
+        <v>62</v>
+      </c>
+      <c r="G447" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="448" spans="1:7">
+      <c r="A448" s="2">
+        <v>46302.64583333334</v>
+      </c>
+      <c r="B448">
+        <v>0</v>
+      </c>
+      <c r="C448">
+        <v>0</v>
+      </c>
+      <c r="D448">
+        <v>0</v>
+      </c>
+      <c r="E448">
+        <v>0</v>
+      </c>
+      <c r="F448">
+        <v>63</v>
+      </c>
+      <c r="G448" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="449" spans="1:7">
+      <c r="A449" s="2">
+        <v>46302.65625</v>
+      </c>
+      <c r="B449">
+        <v>0</v>
+      </c>
+      <c r="C449">
+        <v>0</v>
+      </c>
+      <c r="D449">
+        <v>0</v>
+      </c>
+      <c r="E449">
+        <v>0</v>
+      </c>
+      <c r="F449">
+        <v>64</v>
+      </c>
+      <c r="G449" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="450" spans="1:7">
+      <c r="A450" s="2">
+        <v>46302.66666666666</v>
+      </c>
+      <c r="B450">
+        <v>0</v>
+      </c>
+      <c r="C450">
+        <v>0</v>
+      </c>
+      <c r="D450">
+        <v>0</v>
+      </c>
+      <c r="E450">
+        <v>0</v>
+      </c>
+      <c r="F450">
+        <v>65</v>
+      </c>
+      <c r="G450" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="451" spans="1:7">
+      <c r="A451" s="2">
+        <v>46302.67708333334</v>
+      </c>
+      <c r="B451">
+        <v>0</v>
+      </c>
+      <c r="C451">
+        <v>0</v>
+      </c>
+      <c r="D451">
+        <v>0</v>
+      </c>
+      <c r="E451">
+        <v>0</v>
+      </c>
+      <c r="F451">
+        <v>66</v>
+      </c>
+      <c r="G451" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="452" spans="1:7">
+      <c r="A452" s="2">
+        <v>46302.6875</v>
+      </c>
+      <c r="B452">
+        <v>0</v>
+      </c>
+      <c r="C452">
+        <v>0</v>
+      </c>
+      <c r="D452">
+        <v>0</v>
+      </c>
+      <c r="E452">
+        <v>0</v>
+      </c>
+      <c r="F452">
+        <v>67</v>
+      </c>
+      <c r="G452" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="453" spans="1:7">
+      <c r="A453" s="2">
+        <v>46302.69791666666</v>
+      </c>
+      <c r="B453">
+        <v>0</v>
+      </c>
+      <c r="C453">
+        <v>0</v>
+      </c>
+      <c r="D453">
+        <v>0</v>
+      </c>
+      <c r="E453">
+        <v>0</v>
+      </c>
+      <c r="F453">
+        <v>68</v>
+      </c>
+      <c r="G453" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="454" spans="1:7">
+      <c r="A454" s="2">
+        <v>46302.70833333334</v>
+      </c>
+      <c r="B454">
+        <v>0</v>
+      </c>
+      <c r="C454">
+        <v>0</v>
+      </c>
+      <c r="D454">
+        <v>0</v>
+      </c>
+      <c r="E454">
+        <v>0</v>
+      </c>
+      <c r="F454">
+        <v>69</v>
+      </c>
+      <c r="G454" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="455" spans="1:7">
+      <c r="A455" s="2">
+        <v>46302.71875</v>
+      </c>
+      <c r="B455">
+        <v>0</v>
+      </c>
+      <c r="C455">
+        <v>0</v>
+      </c>
+      <c r="D455">
+        <v>0</v>
+      </c>
+      <c r="E455">
+        <v>0</v>
+      </c>
+      <c r="F455">
+        <v>70</v>
+      </c>
+      <c r="G455" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="456" spans="1:7">
+      <c r="A456" s="2">
+        <v>46302.72916666666</v>
+      </c>
+      <c r="B456">
+        <v>0</v>
+      </c>
+      <c r="C456">
+        <v>0</v>
+      </c>
+      <c r="D456">
+        <v>0</v>
+      </c>
+      <c r="E456">
+        <v>0</v>
+      </c>
+      <c r="F456">
+        <v>71</v>
+      </c>
+      <c r="G456" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="457" spans="1:7">
+      <c r="A457" s="2">
+        <v>46302.73958333334</v>
+      </c>
+      <c r="B457">
+        <v>0</v>
+      </c>
+      <c r="C457">
+        <v>0</v>
+      </c>
+      <c r="D457">
+        <v>0</v>
+      </c>
+      <c r="E457">
+        <v>0</v>
+      </c>
+      <c r="F457">
+        <v>72</v>
+      </c>
+      <c r="G457" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="458" spans="1:7">
+      <c r="A458" s="2">
+        <v>46302.75</v>
+      </c>
+      <c r="B458">
+        <v>0</v>
+      </c>
+      <c r="C458">
+        <v>0</v>
+      </c>
+      <c r="D458">
+        <v>0</v>
+      </c>
+      <c r="E458">
+        <v>0</v>
+      </c>
+      <c r="F458">
+        <v>73</v>
+      </c>
+      <c r="G458" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="459" spans="1:7">
+      <c r="A459" s="2">
+        <v>46302.76041666666</v>
+      </c>
+      <c r="B459">
+        <v>0</v>
+      </c>
+      <c r="C459">
+        <v>0</v>
+      </c>
+      <c r="D459">
+        <v>0</v>
+      </c>
+      <c r="E459">
+        <v>0</v>
+      </c>
+      <c r="F459">
+        <v>74</v>
+      </c>
+      <c r="G459" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="460" spans="1:7">
+      <c r="A460" s="2">
+        <v>46302.77083333334</v>
+      </c>
+      <c r="B460">
+        <v>0</v>
+      </c>
+      <c r="C460">
+        <v>0</v>
+      </c>
+      <c r="D460">
+        <v>0</v>
+      </c>
+      <c r="E460">
+        <v>0</v>
+      </c>
+      <c r="F460">
+        <v>75</v>
+      </c>
+      <c r="G460" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="461" spans="1:7">
+      <c r="A461" s="2">
+        <v>46302.78125</v>
+      </c>
+      <c r="B461">
+        <v>0</v>
+      </c>
+      <c r="C461">
+        <v>0</v>
+      </c>
+      <c r="D461">
+        <v>0</v>
+      </c>
+      <c r="E461">
+        <v>0</v>
+      </c>
+      <c r="F461">
+        <v>76</v>
+      </c>
+      <c r="G461" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="462" spans="1:7">
+      <c r="A462" s="2">
+        <v>46302.79166666666</v>
+      </c>
+      <c r="B462">
+        <v>0</v>
+      </c>
+      <c r="C462">
+        <v>0</v>
+      </c>
+      <c r="D462">
+        <v>0</v>
+      </c>
+      <c r="E462">
+        <v>0</v>
+      </c>
+      <c r="F462">
+        <v>77</v>
+      </c>
+      <c r="G462" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="463" spans="1:7">
+      <c r="A463" s="2">
+        <v>46302.80208333334</v>
+      </c>
+      <c r="B463">
+        <v>0</v>
+      </c>
+      <c r="C463">
+        <v>0</v>
+      </c>
+      <c r="D463">
+        <v>0</v>
+      </c>
+      <c r="E463">
+        <v>0</v>
+      </c>
+      <c r="F463">
+        <v>78</v>
+      </c>
+      <c r="G463" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="464" spans="1:7">
+      <c r="A464" s="2">
+        <v>46302.8125</v>
+      </c>
+      <c r="B464">
+        <v>0</v>
+      </c>
+      <c r="C464">
+        <v>0</v>
+      </c>
+      <c r="D464">
+        <v>0</v>
+      </c>
+      <c r="E464">
+        <v>0</v>
+      </c>
+      <c r="F464">
+        <v>79</v>
+      </c>
+      <c r="G464" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="465" spans="1:7">
+      <c r="A465" s="2">
+        <v>46302.82291666666</v>
+      </c>
+      <c r="B465">
+        <v>0</v>
+      </c>
+      <c r="C465">
+        <v>0</v>
+      </c>
+      <c r="D465">
+        <v>0</v>
+      </c>
+      <c r="E465">
+        <v>0</v>
+      </c>
+      <c r="F465">
+        <v>80</v>
+      </c>
+      <c r="G465" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="466" spans="1:7">
+      <c r="A466" s="2">
+        <v>46302.83333333334</v>
+      </c>
+      <c r="B466">
+        <v>0</v>
+      </c>
+      <c r="C466">
+        <v>0</v>
+      </c>
+      <c r="D466">
+        <v>0</v>
+      </c>
+      <c r="E466">
+        <v>0</v>
+      </c>
+      <c r="F466">
+        <v>81</v>
+      </c>
+      <c r="G466" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="467" spans="1:7">
+      <c r="A467" s="2">
+        <v>46302.84375</v>
+      </c>
+      <c r="B467">
+        <v>0</v>
+      </c>
+      <c r="C467">
+        <v>0</v>
+      </c>
+      <c r="D467">
+        <v>0</v>
+      </c>
+      <c r="E467">
+        <v>0</v>
+      </c>
+      <c r="F467">
+        <v>82</v>
+      </c>
+      <c r="G467" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="468" spans="1:7">
+      <c r="A468" s="2">
+        <v>46302.85416666666</v>
+      </c>
+      <c r="B468">
+        <v>0</v>
+      </c>
+      <c r="C468">
+        <v>0</v>
+      </c>
+      <c r="D468">
+        <v>0</v>
+      </c>
+      <c r="E468">
+        <v>0</v>
+      </c>
+      <c r="F468">
+        <v>83</v>
+      </c>
+      <c r="G468" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="469" spans="1:7">
+      <c r="A469" s="2">
+        <v>46302.86458333334</v>
+      </c>
+      <c r="B469">
+        <v>0</v>
+      </c>
+      <c r="C469">
+        <v>0</v>
+      </c>
+      <c r="D469">
+        <v>0</v>
+      </c>
+      <c r="E469">
+        <v>0</v>
+      </c>
+      <c r="F469">
+        <v>84</v>
+      </c>
+      <c r="G469" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="470" spans="1:7">
+      <c r="A470" s="2">
+        <v>46302.875</v>
+      </c>
+      <c r="B470">
+        <v>0</v>
+      </c>
+      <c r="C470">
+        <v>0</v>
+      </c>
+      <c r="D470">
+        <v>0</v>
+      </c>
+      <c r="E470">
+        <v>0</v>
+      </c>
+      <c r="F470">
+        <v>85</v>
+      </c>
+      <c r="G470" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="471" spans="1:7">
+      <c r="A471" s="2">
+        <v>46302.88541666666</v>
+      </c>
+      <c r="B471">
+        <v>0</v>
+      </c>
+      <c r="C471">
+        <v>0</v>
+      </c>
+      <c r="D471">
+        <v>0</v>
+      </c>
+      <c r="E471">
+        <v>0</v>
+      </c>
+      <c r="F471">
+        <v>86</v>
+      </c>
+      <c r="G471" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="472" spans="1:7">
+      <c r="A472" s="2">
+        <v>46302.89583333334</v>
+      </c>
+      <c r="B472">
+        <v>0</v>
+      </c>
+      <c r="C472">
+        <v>0</v>
+      </c>
+      <c r="D472">
+        <v>0</v>
+      </c>
+      <c r="E472">
+        <v>0</v>
+      </c>
+      <c r="F472">
+        <v>87</v>
+      </c>
+      <c r="G472" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="473" spans="1:7">
+      <c r="A473" s="2">
+        <v>46302.90625</v>
+      </c>
+      <c r="B473">
+        <v>0</v>
+      </c>
+      <c r="C473">
+        <v>0</v>
+      </c>
+      <c r="D473">
+        <v>0</v>
+      </c>
+      <c r="E473">
+        <v>0</v>
+      </c>
+      <c r="F473">
+        <v>88</v>
+      </c>
+      <c r="G473" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="474" spans="1:7">
+      <c r="A474" s="2">
+        <v>46302.91666666666</v>
+      </c>
+      <c r="B474">
+        <v>0</v>
+      </c>
+      <c r="C474">
+        <v>0</v>
+      </c>
+      <c r="D474">
+        <v>0</v>
+      </c>
+      <c r="E474">
+        <v>0</v>
+      </c>
+      <c r="F474">
+        <v>89</v>
+      </c>
+      <c r="G474" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="475" spans="1:7">
+      <c r="A475" s="2">
+        <v>46302.92708333334</v>
+      </c>
+      <c r="B475">
+        <v>0</v>
+      </c>
+      <c r="C475">
+        <v>0</v>
+      </c>
+      <c r="D475">
+        <v>0</v>
+      </c>
+      <c r="E475">
+        <v>0</v>
+      </c>
+      <c r="F475">
+        <v>90</v>
+      </c>
+      <c r="G475" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="476" spans="1:7">
+      <c r="A476" s="2">
+        <v>46302.9375</v>
+      </c>
+      <c r="B476">
+        <v>0</v>
+      </c>
+      <c r="C476">
+        <v>0</v>
+      </c>
+      <c r="D476">
+        <v>0</v>
+      </c>
+      <c r="E476">
+        <v>0</v>
+      </c>
+      <c r="F476">
+        <v>91</v>
+      </c>
+      <c r="G476" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="477" spans="1:7">
+      <c r="A477" s="2">
+        <v>46302.94791666666</v>
+      </c>
+      <c r="B477">
+        <v>0</v>
+      </c>
+      <c r="C477">
+        <v>0</v>
+      </c>
+      <c r="D477">
+        <v>0</v>
+      </c>
+      <c r="E477">
+        <v>0</v>
+      </c>
+      <c r="F477">
+        <v>92</v>
+      </c>
+      <c r="G477" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="478" spans="1:7">
+      <c r="A478" s="2">
+        <v>46302.95833333334</v>
+      </c>
+      <c r="B478">
+        <v>0</v>
+      </c>
+      <c r="C478">
+        <v>0</v>
+      </c>
+      <c r="D478">
+        <v>0</v>
+      </c>
+      <c r="E478">
+        <v>0</v>
+      </c>
+      <c r="F478">
+        <v>93</v>
+      </c>
+      <c r="G478" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="479" spans="1:7">
+      <c r="A479" s="2">
+        <v>46302.96875</v>
+      </c>
+      <c r="B479">
+        <v>0</v>
+      </c>
+      <c r="C479">
+        <v>0</v>
+      </c>
+      <c r="D479">
+        <v>0</v>
+      </c>
+      <c r="E479">
+        <v>0</v>
+      </c>
+      <c r="F479">
+        <v>94</v>
+      </c>
+      <c r="G479" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="480" spans="1:7">
+      <c r="A480" s="2">
+        <v>46302.97916666666</v>
+      </c>
+      <c r="B480">
+        <v>0</v>
+      </c>
+      <c r="C480">
+        <v>0</v>
+      </c>
+      <c r="D480">
+        <v>0</v>
+      </c>
+      <c r="E480">
+        <v>0</v>
+      </c>
+      <c r="F480">
+        <v>95</v>
+      </c>
+      <c r="G480" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="481" spans="1:7">
+      <c r="A481" s="2">
+        <v>46302.98958333334</v>
+      </c>
+      <c r="B481">
+        <v>0</v>
+      </c>
+      <c r="C481">
+        <v>0</v>
+      </c>
+      <c r="D481">
+        <v>0</v>
+      </c>
+      <c r="E481">
+        <v>0</v>
+      </c>
+      <c r="F481">
+        <v>96</v>
+      </c>
+      <c r="G481" t="s">
+        <v>486</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -37,294 +37,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>07.10.20261</t>
-  </si>
-  <si>
-    <t>07.10.20262</t>
-  </si>
-  <si>
-    <t>07.10.20263</t>
-  </si>
-  <si>
-    <t>07.10.20264</t>
-  </si>
-  <si>
-    <t>07.10.20265</t>
-  </si>
-  <si>
-    <t>07.10.20266</t>
-  </si>
-  <si>
-    <t>07.10.20267</t>
-  </si>
-  <si>
-    <t>07.10.20268</t>
-  </si>
-  <si>
-    <t>07.10.20269</t>
-  </si>
-  <si>
-    <t>07.10.202610</t>
-  </si>
-  <si>
-    <t>07.10.202611</t>
-  </si>
-  <si>
-    <t>07.10.202612</t>
-  </si>
-  <si>
-    <t>07.10.202613</t>
-  </si>
-  <si>
-    <t>07.10.202614</t>
-  </si>
-  <si>
-    <t>07.10.202615</t>
-  </si>
-  <si>
-    <t>07.10.202616</t>
-  </si>
-  <si>
-    <t>07.10.202617</t>
-  </si>
-  <si>
-    <t>07.10.202618</t>
-  </si>
-  <si>
-    <t>07.10.202619</t>
-  </si>
-  <si>
-    <t>07.10.202620</t>
-  </si>
-  <si>
-    <t>07.10.202621</t>
-  </si>
-  <si>
-    <t>07.10.202622</t>
-  </si>
-  <si>
-    <t>07.10.202623</t>
-  </si>
-  <si>
-    <t>07.10.202624</t>
-  </si>
-  <si>
-    <t>07.10.202625</t>
-  </si>
-  <si>
-    <t>07.10.202626</t>
-  </si>
-  <si>
-    <t>07.10.202627</t>
-  </si>
-  <si>
-    <t>07.10.202628</t>
-  </si>
-  <si>
-    <t>07.10.202629</t>
-  </si>
-  <si>
-    <t>07.10.202630</t>
-  </si>
-  <si>
-    <t>07.10.202631</t>
-  </si>
-  <si>
-    <t>07.10.202632</t>
-  </si>
-  <si>
-    <t>07.10.202633</t>
-  </si>
-  <si>
-    <t>07.10.202634</t>
-  </si>
-  <si>
-    <t>07.10.202635</t>
-  </si>
-  <si>
-    <t>07.10.202636</t>
-  </si>
-  <si>
-    <t>07.10.202637</t>
-  </si>
-  <si>
-    <t>07.10.202638</t>
-  </si>
-  <si>
-    <t>07.10.202639</t>
-  </si>
-  <si>
-    <t>07.10.202640</t>
-  </si>
-  <si>
-    <t>07.10.202641</t>
-  </si>
-  <si>
-    <t>07.10.202642</t>
-  </si>
-  <si>
-    <t>07.10.202643</t>
-  </si>
-  <si>
-    <t>07.10.202644</t>
-  </si>
-  <si>
-    <t>07.10.202645</t>
-  </si>
-  <si>
-    <t>07.10.202646</t>
-  </si>
-  <si>
-    <t>07.10.202647</t>
-  </si>
-  <si>
-    <t>07.10.202648</t>
-  </si>
-  <si>
-    <t>07.10.202649</t>
-  </si>
-  <si>
-    <t>07.10.202650</t>
-  </si>
-  <si>
-    <t>07.10.202651</t>
-  </si>
-  <si>
-    <t>07.10.202652</t>
-  </si>
-  <si>
-    <t>07.10.202653</t>
-  </si>
-  <si>
-    <t>07.10.202654</t>
-  </si>
-  <si>
-    <t>07.10.202655</t>
-  </si>
-  <si>
-    <t>07.10.202656</t>
-  </si>
-  <si>
-    <t>07.10.202657</t>
-  </si>
-  <si>
-    <t>07.10.202658</t>
-  </si>
-  <si>
-    <t>07.10.202659</t>
-  </si>
-  <si>
-    <t>07.10.202660</t>
-  </si>
-  <si>
-    <t>07.10.202661</t>
-  </si>
-  <si>
-    <t>07.10.202662</t>
-  </si>
-  <si>
-    <t>07.10.202663</t>
-  </si>
-  <si>
-    <t>07.10.202664</t>
-  </si>
-  <si>
-    <t>07.10.202665</t>
-  </si>
-  <si>
-    <t>07.10.202666</t>
-  </si>
-  <si>
-    <t>07.10.202667</t>
-  </si>
-  <si>
-    <t>07.10.202668</t>
-  </si>
-  <si>
-    <t>07.10.202669</t>
-  </si>
-  <si>
-    <t>07.10.202670</t>
-  </si>
-  <si>
-    <t>07.10.202671</t>
-  </si>
-  <si>
-    <t>07.10.202672</t>
-  </si>
-  <si>
-    <t>07.10.202673</t>
-  </si>
-  <si>
-    <t>07.10.202674</t>
-  </si>
-  <si>
-    <t>07.10.202675</t>
-  </si>
-  <si>
-    <t>07.10.202676</t>
-  </si>
-  <si>
-    <t>07.10.202677</t>
-  </si>
-  <si>
-    <t>07.10.202678</t>
-  </si>
-  <si>
-    <t>07.10.202679</t>
-  </si>
-  <si>
-    <t>07.10.202680</t>
-  </si>
-  <si>
-    <t>07.10.202681</t>
-  </si>
-  <si>
-    <t>07.10.202682</t>
-  </si>
-  <si>
-    <t>07.10.202683</t>
-  </si>
-  <si>
-    <t>07.10.202684</t>
-  </si>
-  <si>
-    <t>07.10.202685</t>
-  </si>
-  <si>
-    <t>07.10.202686</t>
-  </si>
-  <si>
-    <t>07.10.202687</t>
-  </si>
-  <si>
-    <t>07.10.202688</t>
-  </si>
-  <si>
-    <t>07.10.202689</t>
-  </si>
-  <si>
-    <t>07.10.202690</t>
-  </si>
-  <si>
-    <t>07.10.202691</t>
-  </si>
-  <si>
-    <t>07.10.202692</t>
-  </si>
-  <si>
-    <t>07.10.202693</t>
-  </si>
-  <si>
-    <t>07.10.202694</t>
-  </si>
-  <si>
-    <t>07.10.202695</t>
-  </si>
-  <si>
-    <t>07.10.202696</t>
-  </si>
-  <si>
     <t>08.10.20261</t>
   </si>
   <si>
@@ -611,6 +323,294 @@
   </si>
   <si>
     <t>08.10.202696</t>
+  </si>
+  <si>
+    <t>09.10.20261</t>
+  </si>
+  <si>
+    <t>09.10.20262</t>
+  </si>
+  <si>
+    <t>09.10.20263</t>
+  </si>
+  <si>
+    <t>09.10.20264</t>
+  </si>
+  <si>
+    <t>09.10.20265</t>
+  </si>
+  <si>
+    <t>09.10.20266</t>
+  </si>
+  <si>
+    <t>09.10.20267</t>
+  </si>
+  <si>
+    <t>09.10.20268</t>
+  </si>
+  <si>
+    <t>09.10.20269</t>
+  </si>
+  <si>
+    <t>09.10.202610</t>
+  </si>
+  <si>
+    <t>09.10.202611</t>
+  </si>
+  <si>
+    <t>09.10.202612</t>
+  </si>
+  <si>
+    <t>09.10.202613</t>
+  </si>
+  <si>
+    <t>09.10.202614</t>
+  </si>
+  <si>
+    <t>09.10.202615</t>
+  </si>
+  <si>
+    <t>09.10.202616</t>
+  </si>
+  <si>
+    <t>09.10.202617</t>
+  </si>
+  <si>
+    <t>09.10.202618</t>
+  </si>
+  <si>
+    <t>09.10.202619</t>
+  </si>
+  <si>
+    <t>09.10.202620</t>
+  </si>
+  <si>
+    <t>09.10.202621</t>
+  </si>
+  <si>
+    <t>09.10.202622</t>
+  </si>
+  <si>
+    <t>09.10.202623</t>
+  </si>
+  <si>
+    <t>09.10.202624</t>
+  </si>
+  <si>
+    <t>09.10.202625</t>
+  </si>
+  <si>
+    <t>09.10.202626</t>
+  </si>
+  <si>
+    <t>09.10.202627</t>
+  </si>
+  <si>
+    <t>09.10.202628</t>
+  </si>
+  <si>
+    <t>09.10.202629</t>
+  </si>
+  <si>
+    <t>09.10.202630</t>
+  </si>
+  <si>
+    <t>09.10.202631</t>
+  </si>
+  <si>
+    <t>09.10.202632</t>
+  </si>
+  <si>
+    <t>09.10.202633</t>
+  </si>
+  <si>
+    <t>09.10.202634</t>
+  </si>
+  <si>
+    <t>09.10.202635</t>
+  </si>
+  <si>
+    <t>09.10.202636</t>
+  </si>
+  <si>
+    <t>09.10.202637</t>
+  </si>
+  <si>
+    <t>09.10.202638</t>
+  </si>
+  <si>
+    <t>09.10.202639</t>
+  </si>
+  <si>
+    <t>09.10.202640</t>
+  </si>
+  <si>
+    <t>09.10.202641</t>
+  </si>
+  <si>
+    <t>09.10.202642</t>
+  </si>
+  <si>
+    <t>09.10.202643</t>
+  </si>
+  <si>
+    <t>09.10.202644</t>
+  </si>
+  <si>
+    <t>09.10.202645</t>
+  </si>
+  <si>
+    <t>09.10.202646</t>
+  </si>
+  <si>
+    <t>09.10.202647</t>
+  </si>
+  <si>
+    <t>09.10.202648</t>
+  </si>
+  <si>
+    <t>09.10.202649</t>
+  </si>
+  <si>
+    <t>09.10.202650</t>
+  </si>
+  <si>
+    <t>09.10.202651</t>
+  </si>
+  <si>
+    <t>09.10.202652</t>
+  </si>
+  <si>
+    <t>09.10.202653</t>
+  </si>
+  <si>
+    <t>09.10.202654</t>
+  </si>
+  <si>
+    <t>09.10.202655</t>
+  </si>
+  <si>
+    <t>09.10.202656</t>
+  </si>
+  <si>
+    <t>09.10.202657</t>
+  </si>
+  <si>
+    <t>09.10.202658</t>
+  </si>
+  <si>
+    <t>09.10.202659</t>
+  </si>
+  <si>
+    <t>09.10.202660</t>
+  </si>
+  <si>
+    <t>09.10.202661</t>
+  </si>
+  <si>
+    <t>09.10.202662</t>
+  </si>
+  <si>
+    <t>09.10.202663</t>
+  </si>
+  <si>
+    <t>09.10.202664</t>
+  </si>
+  <si>
+    <t>09.10.202665</t>
+  </si>
+  <si>
+    <t>09.10.202666</t>
+  </si>
+  <si>
+    <t>09.10.202667</t>
+  </si>
+  <si>
+    <t>09.10.202668</t>
+  </si>
+  <si>
+    <t>09.10.202669</t>
+  </si>
+  <si>
+    <t>09.10.202670</t>
+  </si>
+  <si>
+    <t>09.10.202671</t>
+  </si>
+  <si>
+    <t>09.10.202672</t>
+  </si>
+  <si>
+    <t>09.10.202673</t>
+  </si>
+  <si>
+    <t>09.10.202674</t>
+  </si>
+  <si>
+    <t>09.10.202675</t>
+  </si>
+  <si>
+    <t>09.10.202676</t>
+  </si>
+  <si>
+    <t>09.10.202677</t>
+  </si>
+  <si>
+    <t>09.10.202678</t>
+  </si>
+  <si>
+    <t>09.10.202679</t>
+  </si>
+  <si>
+    <t>09.10.202680</t>
+  </si>
+  <si>
+    <t>09.10.202681</t>
+  </si>
+  <si>
+    <t>09.10.202682</t>
+  </si>
+  <si>
+    <t>09.10.202683</t>
+  </si>
+  <si>
+    <t>09.10.202684</t>
+  </si>
+  <si>
+    <t>09.10.202685</t>
+  </si>
+  <si>
+    <t>09.10.202686</t>
+  </si>
+  <si>
+    <t>09.10.202687</t>
+  </si>
+  <si>
+    <t>09.10.202688</t>
+  </si>
+  <si>
+    <t>09.10.202689</t>
+  </si>
+  <si>
+    <t>09.10.202690</t>
+  </si>
+  <si>
+    <t>09.10.202691</t>
+  </si>
+  <si>
+    <t>09.10.202692</t>
+  </si>
+  <si>
+    <t>09.10.202693</t>
+  </si>
+  <si>
+    <t>09.10.202694</t>
+  </si>
+  <si>
+    <t>09.10.202695</t>
+  </si>
+  <si>
+    <t>09.10.202696</t>
   </si>
 </sst>
 </file>
@@ -1000,13 +1000,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B2">
-        <v>21.433</v>
+        <v>0.075</v>
       </c>
       <c r="C2">
-        <v>0.096</v>
+        <v>2.495</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1023,13 +1023,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46302.01041666666</v>
+        <v>46303.01041666666</v>
       </c>
       <c r="B3">
-        <v>27.354</v>
+        <v>0.005</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1046,13 +1046,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46302.02083333334</v>
+        <v>46303.02083333334</v>
       </c>
       <c r="B4">
-        <v>19.511</v>
+        <v>0.362</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1069,13 +1069,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46302.03125</v>
+        <v>46303.03125</v>
       </c>
       <c r="B5">
-        <v>24.424</v>
+        <v>4.543</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1092,13 +1092,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46302.04166666666</v>
+        <v>46303.04166666666</v>
       </c>
       <c r="B6">
-        <v>26.152</v>
+        <v>1.94</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1115,16 +1115,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46302.05208333334</v>
+        <v>46303.05208333334</v>
       </c>
       <c r="B7">
-        <v>0.554</v>
+        <v>0.143</v>
       </c>
       <c r="C7">
-        <v>0.008999999999999999</v>
+        <v>0.121</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1138,16 +1138,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46302.0625</v>
+        <v>46303.0625</v>
       </c>
       <c r="B8">
-        <v>5.632</v>
+        <v>1.483</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1161,16 +1161,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46302.07291666666</v>
+        <v>46303.07291666666</v>
       </c>
       <c r="B9">
-        <v>3.281</v>
+        <v>4.954</v>
       </c>
       <c r="C9">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1184,16 +1184,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46302.08333333334</v>
+        <v>46303.08333333334</v>
       </c>
       <c r="B10">
-        <v>6.403</v>
+        <v>11.522</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1207,10 +1207,10 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46302.09375</v>
+        <v>46303.09375</v>
       </c>
       <c r="B11">
-        <v>22.644</v>
+        <v>31.022</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46302.10416666666</v>
+        <v>46303.10416666666</v>
       </c>
       <c r="B12">
-        <v>10.201</v>
+        <v>27.57</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1253,10 +1253,10 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46302.11458333334</v>
+        <v>46303.11458333334</v>
       </c>
       <c r="B13">
-        <v>5.872</v>
+        <v>22.975</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46302.125</v>
+        <v>46303.125</v>
       </c>
       <c r="B14">
-        <v>5.815</v>
+        <v>14.987</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1299,10 +1299,10 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46302.13541666666</v>
+        <v>46303.13541666666</v>
       </c>
       <c r="B15">
-        <v>9.999000000000001</v>
+        <v>18.079</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1322,10 +1322,10 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46302.14583333334</v>
+        <v>46303.14583333334</v>
       </c>
       <c r="B16">
-        <v>3.975</v>
+        <v>19.113</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1345,10 +1345,10 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46302.15625</v>
+        <v>46303.15625</v>
       </c>
       <c r="B17">
-        <v>15.934</v>
+        <v>27.942</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46302.16666666666</v>
+        <v>46303.16666666666</v>
       </c>
       <c r="B18">
-        <v>9.529999999999999</v>
+        <v>7.336</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1391,10 +1391,10 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46302.17708333334</v>
+        <v>46303.17708333334</v>
       </c>
       <c r="B19">
-        <v>26.013</v>
+        <v>10.539</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1414,13 +1414,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46302.1875</v>
+        <v>46303.1875</v>
       </c>
       <c r="B20">
-        <v>19.229</v>
+        <v>3.006</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1437,13 +1437,13 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46302.19791666666</v>
+        <v>46303.19791666666</v>
       </c>
       <c r="B21">
-        <v>32.808</v>
+        <v>3.439</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46302.20833333334</v>
+        <v>46303.20833333334</v>
       </c>
       <c r="B22">
-        <v>19.984</v>
+        <v>5.481</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1483,10 +1483,10 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46302.21875</v>
+        <v>46303.21875</v>
       </c>
       <c r="B23">
-        <v>10.558</v>
+        <v>5.679</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1506,10 +1506,10 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46302.22916666666</v>
+        <v>46303.22916666666</v>
       </c>
       <c r="B24">
-        <v>23.457</v>
+        <v>19.721</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1529,10 +1529,10 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46302.23958333334</v>
+        <v>46303.23958333334</v>
       </c>
       <c r="B25">
-        <v>27.364</v>
+        <v>10.141</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1552,16 +1552,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46302.25</v>
+        <v>46303.25</v>
       </c>
       <c r="B26">
-        <v>26.218</v>
+        <v>3.623</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>1.089</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1575,16 +1575,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46302.26041666666</v>
+        <v>46303.26041666666</v>
       </c>
       <c r="B27">
-        <v>52.106</v>
+        <v>2.02</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1598,16 +1598,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46302.27083333334</v>
+        <v>46303.27083333334</v>
       </c>
       <c r="B28">
-        <v>41.627</v>
+        <v>0.217</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>0.282</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1621,16 +1621,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46302.28125</v>
+        <v>46303.28125</v>
       </c>
       <c r="B29">
-        <v>20.222</v>
+        <v>0.437</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>0.194</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1644,16 +1644,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46302.29166666666</v>
+        <v>46303.29166666666</v>
       </c>
       <c r="B30">
-        <v>57.112</v>
+        <v>6.655</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1667,16 +1667,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46302.30208333334</v>
+        <v>46303.30208333334</v>
       </c>
       <c r="B31">
-        <v>31.186</v>
+        <v>16.324</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1690,16 +1690,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46302.3125</v>
+        <v>46303.3125</v>
       </c>
       <c r="B32">
-        <v>3.519</v>
+        <v>2.646</v>
       </c>
       <c r="C32">
-        <v>2.713</v>
+        <v>4.702</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1713,16 +1713,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46302.32291666666</v>
+        <v>46303.32291666666</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>0.931</v>
       </c>
       <c r="C33">
-        <v>30.757</v>
+        <v>5.277</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1736,16 +1736,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46302.33333333334</v>
+        <v>46303.33333333334</v>
       </c>
       <c r="B34">
-        <v>1.121</v>
+        <v>0.913</v>
       </c>
       <c r="C34">
-        <v>6.763</v>
+        <v>0.43</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>19.75</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1759,16 +1759,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46302.34375</v>
+        <v>46303.34375</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>6.363</v>
       </c>
       <c r="C35">
-        <v>17.334</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -1782,16 +1782,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46302.35416666666</v>
+        <v>46303.35416666666</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>21.744</v>
       </c>
       <c r="C36">
-        <v>22.156</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -1805,19 +1805,19 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46302.36458333334</v>
+        <v>46303.36458333334</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>1.881</v>
       </c>
       <c r="C37">
-        <v>10.188</v>
+        <v>5.052</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="E37">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F37">
         <v>36</v>
@@ -1828,19 +1828,19 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46302.375</v>
+        <v>46303.375</v>
       </c>
       <c r="B38">
-        <v>7.204</v>
+        <v>0.407</v>
       </c>
       <c r="C38">
-        <v>2.059</v>
+        <v>2.318</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E38">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F38">
         <v>37</v>
@@ -1851,16 +1851,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46302.38541666666</v>
+        <v>46303.38541666666</v>
       </c>
       <c r="B39">
         <v>0</v>
       </c>
       <c r="C39">
-        <v>2.808</v>
+        <v>8.952999999999999</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>53.5</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46302.39583333334</v>
+        <v>46303.39583333334</v>
       </c>
       <c r="B40">
-        <v>1.541</v>
+        <v>3.561</v>
       </c>
       <c r="C40">
-        <v>0.276</v>
+        <v>1.556</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -1897,16 +1897,16 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46302.40625</v>
+        <v>46303.40625</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>0.106</v>
       </c>
       <c r="C41">
-        <v>3.523</v>
+        <v>5.156</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -1920,13 +1920,13 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46302.41666666666</v>
+        <v>46303.41666666666</v>
       </c>
       <c r="B42">
-        <v>4.299</v>
+        <v>1.452</v>
       </c>
       <c r="C42">
-        <v>0.269</v>
+        <v>3.963</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -1943,13 +1943,13 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46302.42708333334</v>
+        <v>46303.42708333334</v>
       </c>
       <c r="B43">
-        <v>0.066</v>
+        <v>0.185</v>
       </c>
       <c r="C43">
-        <v>5.785</v>
+        <v>1.174</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -1966,13 +1966,13 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46302.4375</v>
+        <v>46303.4375</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="C44">
-        <v>4.98</v>
+        <v>6.079</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -1989,13 +1989,13 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46302.44791666666</v>
+        <v>46303.44791666666</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="C45">
-        <v>14.694</v>
+        <v>2.395</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2012,13 +2012,13 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46302.45833333334</v>
+        <v>46303.45833333334</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="C46">
-        <v>16.108</v>
+        <v>3.746</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2035,13 +2035,13 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46302.46875</v>
+        <v>46303.46875</v>
       </c>
       <c r="B47">
         <v>0</v>
       </c>
       <c r="C47">
-        <v>7.933</v>
+        <v>9.829000000000001</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2058,13 +2058,13 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46302.47916666666</v>
+        <v>46303.47916666666</v>
       </c>
       <c r="B48">
         <v>0</v>
       </c>
       <c r="C48">
-        <v>6.412</v>
+        <v>15.701</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2081,13 +2081,13 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46302.48958333334</v>
+        <v>46303.48958333334</v>
       </c>
       <c r="B49">
         <v>0</v>
       </c>
       <c r="C49">
-        <v>4.434</v>
+        <v>3.611</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2104,13 +2104,13 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46302.5</v>
+        <v>46303.5</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="C50">
-        <v>18.108</v>
+        <v>4.665</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46302.51041666666</v>
+        <v>46303.51041666666</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C51">
-        <v>7.706</v>
+        <v>3.638</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2150,13 +2150,13 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46302.52083333334</v>
+        <v>46303.52083333334</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="C52">
-        <v>3.095</v>
+        <v>0.706</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2173,13 +2173,13 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46302.53125</v>
+        <v>46303.53125</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="C53">
-        <v>5.916</v>
+        <v>2.087</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2196,13 +2196,13 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46302.54166666666</v>
+        <v>46303.54166666666</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>3.923</v>
       </c>
       <c r="C54">
-        <v>6.731</v>
+        <v>0</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2219,13 +2219,13 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46302.55208333334</v>
+        <v>46303.55208333334</v>
       </c>
       <c r="B55">
-        <v>4.389</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C55">
-        <v>0.026</v>
+        <v>2.748</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2242,13 +2242,13 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46302.5625</v>
+        <v>46303.5625</v>
       </c>
       <c r="B56">
-        <v>4.944</v>
+        <v>0.344</v>
       </c>
       <c r="C56">
-        <v>0.039</v>
+        <v>0.773</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2265,13 +2265,13 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46302.57291666666</v>
+        <v>46303.57291666666</v>
       </c>
       <c r="B57">
-        <v>11.558</v>
+        <v>0.399</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>1.482</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2288,13 +2288,13 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46302.58333333334</v>
+        <v>46303.58333333334</v>
       </c>
       <c r="B58">
-        <v>5.184</v>
+        <v>0.649</v>
       </c>
       <c r="C58">
-        <v>0.01</v>
+        <v>9.260999999999999</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2311,13 +2311,13 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46302.59375</v>
+        <v>46303.59375</v>
       </c>
       <c r="B59">
-        <v>0.224</v>
+        <v>0.059</v>
       </c>
       <c r="C59">
-        <v>0.514</v>
+        <v>2.544</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2334,13 +2334,13 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46302.60416666666</v>
+        <v>46303.60416666666</v>
       </c>
       <c r="B60">
-        <v>3.926</v>
+        <v>0.114</v>
       </c>
       <c r="C60">
-        <v>0.5639999999999999</v>
+        <v>1.163</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2357,13 +2357,13 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46302.61458333334</v>
+        <v>46303.61458333334</v>
       </c>
       <c r="B61">
-        <v>1.844</v>
+        <v>1.838</v>
       </c>
       <c r="C61">
-        <v>2.093</v>
+        <v>0.08</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2380,13 +2380,13 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46302.625</v>
+        <v>46303.625</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="C62">
-        <v>16.179</v>
+        <v>0.442</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2403,13 +2403,13 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46302.63541666666</v>
+        <v>46303.63541666666</v>
       </c>
       <c r="B63">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="C63">
-        <v>4.686</v>
+        <v>14.716</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2426,19 +2426,19 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46302.64583333334</v>
+        <v>46303.64583333334</v>
       </c>
       <c r="B64">
-        <v>0.702</v>
+        <v>7.106</v>
       </c>
       <c r="C64">
-        <v>5.589</v>
+        <v>0.042</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F64">
         <v>63</v>
@@ -2449,19 +2449,19 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46302.65625</v>
+        <v>46303.65625</v>
       </c>
       <c r="B65">
-        <v>0.094</v>
+        <v>25.116</v>
       </c>
       <c r="C65">
-        <v>5.011</v>
+        <v>0</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F65">
         <v>64</v>
@@ -2472,13 +2472,13 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46302.66666666666</v>
+        <v>46303.66666666666</v>
       </c>
       <c r="B66">
-        <v>4.274</v>
+        <v>10.975</v>
       </c>
       <c r="C66">
-        <v>9.93</v>
+        <v>0</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -2495,13 +2495,13 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46302.67708333334</v>
+        <v>46303.67708333334</v>
       </c>
       <c r="B67">
-        <v>9.863</v>
+        <v>13.703</v>
       </c>
       <c r="C67">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46302.6875</v>
+        <v>46303.6875</v>
       </c>
       <c r="B68">
-        <v>11.769</v>
+        <v>27.461</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -2541,16 +2541,16 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46302.69791666666</v>
+        <v>46303.69791666666</v>
       </c>
       <c r="B69">
-        <v>25.72</v>
+        <v>20.131</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46302.70833333334</v>
+        <v>46303.70833333334</v>
       </c>
       <c r="B70">
-        <v>17.332</v>
+        <v>15.444</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -2587,10 +2587,10 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46302.71875</v>
+        <v>46303.71875</v>
       </c>
       <c r="B71">
-        <v>22.973</v>
+        <v>26.206</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -2610,16 +2610,16 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46302.72916666666</v>
+        <v>46303.72916666666</v>
       </c>
       <c r="B72">
-        <v>5.706</v>
+        <v>9.15</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>12.5</v>
+        <v>37.5</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -2633,16 +2633,16 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46302.73958333334</v>
+        <v>46303.73958333334</v>
       </c>
       <c r="B73">
-        <v>0.424</v>
+        <v>14.355</v>
       </c>
       <c r="C73">
-        <v>0.178</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -2656,16 +2656,16 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46302.75</v>
+        <v>46303.75</v>
       </c>
       <c r="B74">
-        <v>0.147</v>
+        <v>2.207</v>
       </c>
       <c r="C74">
-        <v>0.635</v>
+        <v>0.177</v>
       </c>
       <c r="D74">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -2679,16 +2679,16 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46302.76041666666</v>
+        <v>46303.76041666666</v>
       </c>
       <c r="B75">
-        <v>0.008</v>
+        <v>1.323</v>
       </c>
       <c r="C75">
-        <v>6.91</v>
+        <v>1.393</v>
       </c>
       <c r="D75">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -2702,16 +2702,16 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46302.77083333334</v>
+        <v>46303.77083333334</v>
       </c>
       <c r="B76">
-        <v>0.983</v>
+        <v>0.418</v>
       </c>
       <c r="C76">
-        <v>0.021</v>
+        <v>0.208</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -2725,16 +2725,16 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46302.78125</v>
+        <v>46303.78125</v>
       </c>
       <c r="B77">
-        <v>2.623</v>
+        <v>0.146</v>
       </c>
       <c r="C77">
-        <v>0.049</v>
+        <v>0.448</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -2748,13 +2748,13 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46302.79166666666</v>
+        <v>46303.79166666666</v>
       </c>
       <c r="B78">
-        <v>0.302</v>
+        <v>0.488</v>
       </c>
       <c r="C78">
-        <v>0.035</v>
+        <v>0.229</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -2771,13 +2771,13 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46302.80208333334</v>
+        <v>46303.80208333334</v>
       </c>
       <c r="B79">
-        <v>0.03</v>
+        <v>0.202</v>
       </c>
       <c r="C79">
-        <v>0.913</v>
+        <v>0.105</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -2794,19 +2794,19 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46302.8125</v>
+        <v>46303.8125</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>0.165</v>
       </c>
       <c r="C80">
-        <v>2.332</v>
+        <v>0.123</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F80">
         <v>79</v>
@@ -2817,19 +2817,19 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46302.82291666666</v>
+        <v>46303.82291666666</v>
       </c>
       <c r="B81">
-        <v>1.721</v>
+        <v>0.099</v>
       </c>
       <c r="C81">
-        <v>0.039</v>
+        <v>0.31</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F81">
         <v>80</v>
@@ -2840,10 +2840,10 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46302.83333333334</v>
+        <v>46303.83333333334</v>
       </c>
       <c r="B82">
-        <v>15.841</v>
+        <v>14.843</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2852,7 +2852,7 @@
         <v>0</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F82">
         <v>81</v>
@@ -2863,13 +2863,13 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46302.84375</v>
+        <v>46303.84375</v>
       </c>
       <c r="B83">
-        <v>16.632</v>
+        <v>12.947</v>
       </c>
       <c r="C83">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -2886,13 +2886,13 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46302.85416666666</v>
+        <v>46303.85416666666</v>
       </c>
       <c r="B84">
-        <v>8.701000000000001</v>
+        <v>5.909</v>
       </c>
       <c r="C84">
-        <v>0.004</v>
+        <v>0.097</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46302.86458333334</v>
+        <v>46303.86458333334</v>
       </c>
       <c r="B85">
-        <v>2.522</v>
+        <v>4.379</v>
       </c>
       <c r="C85">
-        <v>0.018</v>
+        <v>1.299</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -2932,13 +2932,13 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46302.875</v>
+        <v>46303.875</v>
       </c>
       <c r="B86">
-        <v>12.945</v>
+        <v>8.374000000000001</v>
       </c>
       <c r="C86">
-        <v>0.27</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -2955,13 +2955,13 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46302.88541666666</v>
+        <v>46303.88541666666</v>
       </c>
       <c r="B87">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="C87">
-        <v>6.404</v>
+        <v>1.49</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -2978,13 +2978,13 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46302.89583333334</v>
+        <v>46303.89583333334</v>
       </c>
       <c r="B88">
-        <v>0.004</v>
+        <v>0.015</v>
       </c>
       <c r="C88">
-        <v>4.68</v>
+        <v>0.944</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3001,13 +3001,13 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46302.90625</v>
+        <v>46303.90625</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="C89">
-        <v>5.228</v>
+        <v>3.665</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3024,13 +3024,13 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46302.91666666666</v>
+        <v>46303.91666666666</v>
       </c>
       <c r="B90">
-        <v>0.018</v>
+        <v>7.41</v>
       </c>
       <c r="C90">
-        <v>3.545</v>
+        <v>0.993</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3047,13 +3047,13 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46302.92708333334</v>
+        <v>46303.92708333334</v>
       </c>
       <c r="B91">
-        <v>0.016</v>
+        <v>9.519</v>
       </c>
       <c r="C91">
-        <v>1.122</v>
+        <v>0</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3070,13 +3070,13 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46302.9375</v>
+        <v>46303.9375</v>
       </c>
       <c r="B92">
-        <v>3.408</v>
+        <v>13.437</v>
       </c>
       <c r="C92">
-        <v>1.092</v>
+        <v>0</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3093,13 +3093,13 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46302.94791666666</v>
+        <v>46303.94791666666</v>
       </c>
       <c r="B93">
-        <v>3.653</v>
+        <v>12.028</v>
       </c>
       <c r="C93">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3116,13 +3116,13 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46302.95833333334</v>
+        <v>46303.95833333334</v>
       </c>
       <c r="B94">
-        <v>4.794</v>
+        <v>14.696</v>
       </c>
       <c r="C94">
-        <v>0.591</v>
+        <v>0</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3139,13 +3139,13 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46302.96875</v>
+        <v>46303.96875</v>
       </c>
       <c r="B95">
-        <v>0.193</v>
+        <v>5.957</v>
       </c>
       <c r="C95">
-        <v>0.07199999999999999</v>
+        <v>0.026</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3162,13 +3162,13 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46302.97916666666</v>
+        <v>46303.97916666666</v>
       </c>
       <c r="B96">
-        <v>7.525</v>
+        <v>0.018</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3185,13 +3185,13 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46302.98958333334</v>
+        <v>46303.98958333334</v>
       </c>
       <c r="B97">
-        <v>5.745</v>
+        <v>1.126</v>
       </c>
       <c r="C97">
-        <v>1.444</v>
+        <v>0.411</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3208,13 +3208,13 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B98">
-        <v>0.075</v>
+        <v>4.293</v>
       </c>
       <c r="C98">
-        <v>2.495</v>
+        <v>0</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3231,13 +3231,13 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46303.01041666666</v>
+        <v>46304.01041666666</v>
       </c>
       <c r="B99">
-        <v>0.005</v>
+        <v>4.642</v>
       </c>
       <c r="C99">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -3254,13 +3254,13 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46303.02083333334</v>
+        <v>46304.02083333334</v>
       </c>
       <c r="B100">
-        <v>0.362</v>
+        <v>5.413</v>
       </c>
       <c r="C100">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -3277,13 +3277,13 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46303.03125</v>
+        <v>46304.03125</v>
       </c>
       <c r="B101">
-        <v>4.543</v>
+        <v>0.698</v>
       </c>
       <c r="C101">
-        <v>0.006</v>
+        <v>1.788</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46303.04166666666</v>
+        <v>46304.04166666666</v>
       </c>
       <c r="B102">
-        <v>1.94</v>
+        <v>11.905</v>
       </c>
       <c r="C102">
-        <v>0.05</v>
+        <v>0.507</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3323,13 +3323,13 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46303.05208333334</v>
+        <v>46304.05208333334</v>
       </c>
       <c r="B103">
-        <v>0.143</v>
+        <v>4.742</v>
       </c>
       <c r="C103">
-        <v>0.121</v>
+        <v>0</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -3346,10 +3346,10 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46303.0625</v>
+        <v>46304.0625</v>
       </c>
       <c r="B104">
-        <v>1.483</v>
+        <v>25.578</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46303.07291666666</v>
+        <v>46304.07291666666</v>
       </c>
       <c r="B105">
-        <v>4.954</v>
+        <v>20.903</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -3392,10 +3392,10 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46303.08333333334</v>
+        <v>46304.08333333334</v>
       </c>
       <c r="B106">
-        <v>11.522</v>
+        <v>11.54</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -3415,10 +3415,10 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46303.09375</v>
+        <v>46304.09375</v>
       </c>
       <c r="B107">
-        <v>31.022</v>
+        <v>18.361</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46303.10416666666</v>
+        <v>46304.10416666666</v>
       </c>
       <c r="B108">
-        <v>27.57</v>
+        <v>23.123</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -3461,10 +3461,10 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46303.11458333334</v>
+        <v>46304.11458333334</v>
       </c>
       <c r="B109">
-        <v>22.975</v>
+        <v>36.561</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -3484,10 +3484,10 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46303.125</v>
+        <v>46304.125</v>
       </c>
       <c r="B110">
-        <v>14.987</v>
+        <v>49.765</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -3507,16 +3507,16 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46303.13541666666</v>
+        <v>46304.13541666666</v>
       </c>
       <c r="B111">
-        <v>18.079</v>
+        <v>35.578</v>
       </c>
       <c r="C111">
         <v>0</v>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -3530,16 +3530,16 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46303.14583333334</v>
+        <v>46304.14583333334</v>
       </c>
       <c r="B112">
-        <v>19.113</v>
+        <v>23.305</v>
       </c>
       <c r="C112">
         <v>0</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -3553,16 +3553,16 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46303.15625</v>
+        <v>46304.15625</v>
       </c>
       <c r="B113">
-        <v>27.942</v>
+        <v>43.251</v>
       </c>
       <c r="C113">
         <v>0</v>
       </c>
       <c r="D113">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -3576,16 +3576,16 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46303.16666666666</v>
+        <v>46304.16666666666</v>
       </c>
       <c r="B114">
-        <v>7.336</v>
+        <v>7.688</v>
       </c>
       <c r="C114">
         <v>0</v>
       </c>
       <c r="D114">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -3599,16 +3599,16 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46303.17708333334</v>
+        <v>46304.17708333334</v>
       </c>
       <c r="B115">
-        <v>10.539</v>
+        <v>1.659</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -3622,16 +3622,16 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46303.1875</v>
+        <v>46304.1875</v>
       </c>
       <c r="B116">
-        <v>3.006</v>
+        <v>0.205</v>
       </c>
       <c r="C116">
-        <v>0.02</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="D116">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -3645,16 +3645,16 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46303.19791666666</v>
+        <v>46304.19791666666</v>
       </c>
       <c r="B117">
-        <v>3.439</v>
+        <v>1.806</v>
       </c>
       <c r="C117">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -3668,16 +3668,16 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46303.20833333334</v>
+        <v>46304.20833333334</v>
       </c>
       <c r="B118">
-        <v>5.481</v>
+        <v>14.024</v>
       </c>
       <c r="C118">
         <v>0</v>
       </c>
       <c r="D118">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -3691,16 +3691,16 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46303.21875</v>
+        <v>46304.21875</v>
       </c>
       <c r="B119">
-        <v>5.679</v>
+        <v>31.426</v>
       </c>
       <c r="C119">
         <v>0</v>
       </c>
       <c r="D119">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46303.22916666666</v>
+        <v>46304.22916666666</v>
       </c>
       <c r="B120">
-        <v>19.721</v>
+        <v>10.545</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -3737,16 +3737,16 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46303.23958333334</v>
+        <v>46304.23958333334</v>
       </c>
       <c r="B121">
-        <v>10.141</v>
+        <v>8.079000000000001</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -3760,16 +3760,16 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="B122">
-        <v>3.623</v>
+        <v>4.402</v>
       </c>
       <c r="C122">
-        <v>1.089</v>
+        <v>1.59</v>
       </c>
       <c r="D122">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -3783,16 +3783,16 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46303.26041666666</v>
+        <v>46304.26041666666</v>
       </c>
       <c r="B123">
-        <v>2.02</v>
+        <v>0.131</v>
       </c>
       <c r="C123">
-        <v>0.018</v>
+        <v>0.119</v>
       </c>
       <c r="D123">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -3806,16 +3806,16 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46303.27083333334</v>
+        <v>46304.27083333334</v>
       </c>
       <c r="B124">
-        <v>0.217</v>
+        <v>0.215</v>
       </c>
       <c r="C124">
-        <v>0.282</v>
+        <v>0.147</v>
       </c>
       <c r="D124">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -3829,16 +3829,16 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46303.28125</v>
+        <v>46304.28125</v>
       </c>
       <c r="B125">
-        <v>0.437</v>
+        <v>3.824</v>
       </c>
       <c r="C125">
-        <v>0.194</v>
+        <v>0.013</v>
       </c>
       <c r="D125">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -3852,16 +3852,16 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46303.29166666666</v>
+        <v>46304.29166666666</v>
       </c>
       <c r="B126">
-        <v>6.655</v>
+        <v>1.694</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="D126">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -3875,16 +3875,16 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46303.30208333334</v>
+        <v>46304.30208333334</v>
       </c>
       <c r="B127">
-        <v>16.324</v>
+        <v>5.396</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D127">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -3898,16 +3898,16 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46303.3125</v>
+        <v>46304.3125</v>
       </c>
       <c r="B128">
-        <v>2.646</v>
+        <v>0.585</v>
       </c>
       <c r="C128">
-        <v>4.702</v>
+        <v>0.233</v>
       </c>
       <c r="D128">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -3921,16 +3921,16 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46303.32291666666</v>
+        <v>46304.32291666666</v>
       </c>
       <c r="B129">
-        <v>0.931</v>
+        <v>3.763</v>
       </c>
       <c r="C129">
-        <v>5.277</v>
+        <v>0.036</v>
       </c>
       <c r="D129">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -3944,19 +3944,19 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46303.33333333334</v>
+        <v>46304.33333333334</v>
       </c>
       <c r="B130">
-        <v>0.913</v>
+        <v>26.973</v>
       </c>
       <c r="C130">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="D130">
-        <v>19.75</v>
+        <v>0</v>
       </c>
       <c r="E130">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F130">
         <v>33</v>
@@ -3967,19 +3967,19 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46303.34375</v>
+        <v>46304.34375</v>
       </c>
       <c r="B131">
-        <v>6.363</v>
+        <v>26.055</v>
       </c>
       <c r="C131">
         <v>0</v>
       </c>
       <c r="D131">
-        <v>67.5</v>
+        <v>0</v>
       </c>
       <c r="E131">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F131">
         <v>34</v>
@@ -3990,16 +3990,16 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46303.35416666666</v>
+        <v>46304.35416666666</v>
       </c>
       <c r="B132">
-        <v>21.744</v>
+        <v>4.45</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>1.089</v>
       </c>
       <c r="D132">
-        <v>67.5</v>
+        <v>0</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -4013,16 +4013,16 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46303.36458333334</v>
+        <v>46304.36458333334</v>
       </c>
       <c r="B133">
-        <v>1.881</v>
+        <v>0.414</v>
       </c>
       <c r="C133">
-        <v>5.052</v>
+        <v>7.102</v>
       </c>
       <c r="D133">
-        <v>67.5</v>
+        <v>0</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -4036,16 +4036,16 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46303.375</v>
+        <v>46304.375</v>
       </c>
       <c r="B134">
-        <v>0.407</v>
+        <v>0</v>
       </c>
       <c r="C134">
-        <v>2.318</v>
+        <v>0</v>
       </c>
       <c r="D134">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -4059,16 +4059,16 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46303.38541666666</v>
+        <v>46304.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
       </c>
       <c r="C135">
-        <v>8.952999999999999</v>
+        <v>0</v>
       </c>
       <c r="D135">
-        <v>53.5</v>
+        <v>0</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -4082,16 +4082,16 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46303.39583333334</v>
+        <v>46304.39583333334</v>
       </c>
       <c r="B136">
-        <v>3.561</v>
+        <v>0</v>
       </c>
       <c r="C136">
-        <v>1.556</v>
+        <v>0</v>
       </c>
       <c r="D136">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -4105,16 +4105,16 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46303.40625</v>
+        <v>46304.40625</v>
       </c>
       <c r="B137">
-        <v>0.106</v>
+        <v>0</v>
       </c>
       <c r="C137">
-        <v>5.156</v>
+        <v>0</v>
       </c>
       <c r="D137">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -4128,13 +4128,13 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46303.41666666666</v>
+        <v>46304.41666666666</v>
       </c>
       <c r="B138">
-        <v>1.452</v>
+        <v>0</v>
       </c>
       <c r="C138">
-        <v>3.963</v>
+        <v>0</v>
       </c>
       <c r="D138">
         <v>0</v>
@@ -4151,7 +4151,7 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46303.42708333334</v>
+        <v>46304.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46303.4375</v>
+        <v>46304.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -4197,7 +4197,7 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46303.44791666666</v>
+        <v>46304.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -4220,7 +4220,7 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46303.45833333334</v>
+        <v>46304.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -4243,7 +4243,7 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46303.46875</v>
+        <v>46304.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46303.47916666666</v>
+        <v>46304.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -4289,7 +4289,7 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46303.48958333334</v>
+        <v>46304.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -4312,7 +4312,7 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46303.5</v>
+        <v>46304.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -4335,7 +4335,7 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46303.51041666666</v>
+        <v>46304.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -4358,7 +4358,7 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46303.52083333334</v>
+        <v>46304.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -4381,7 +4381,7 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46303.53125</v>
+        <v>46304.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46303.54166666666</v>
+        <v>46304.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46303.55208333334</v>
+        <v>46304.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -4450,7 +4450,7 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46303.5625</v>
+        <v>46304.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4473,7 +4473,7 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46303.57291666666</v>
+        <v>46304.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4496,7 +4496,7 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46303.58333333334</v>
+        <v>46304.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46303.59375</v>
+        <v>46304.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4542,7 +4542,7 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46303.60416666666</v>
+        <v>46304.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46303.61458333334</v>
+        <v>46304.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46303.625</v>
+        <v>46304.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4611,7 +4611,7 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46303.63541666666</v>
+        <v>46304.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46303.64583333334</v>
+        <v>46304.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46303.65625</v>
+        <v>46304.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46303.66666666666</v>
+        <v>46304.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46303.67708333334</v>
+        <v>46304.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46303.6875</v>
+        <v>46304.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46303.69791666666</v>
+        <v>46304.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4772,7 +4772,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46303.70833333334</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46303.71875</v>
+        <v>46304.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46303.72916666666</v>
+        <v>46304.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46303.73958333334</v>
+        <v>46304.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46303.75</v>
+        <v>46304.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46303.76041666666</v>
+        <v>46304.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46303.77083333334</v>
+        <v>46304.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46303.78125</v>
+        <v>46304.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46303.79166666666</v>
+        <v>46304.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46303.80208333334</v>
+        <v>46304.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46303.8125</v>
+        <v>46304.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -5025,7 +5025,7 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46303.82291666666</v>
+        <v>46304.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46303.83333333334</v>
+        <v>46304.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -5071,7 +5071,7 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46303.84375</v>
+        <v>46304.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -5094,7 +5094,7 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46303.85416666666</v>
+        <v>46304.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46303.86458333334</v>
+        <v>46304.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46303.875</v>
+        <v>46304.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46303.88541666666</v>
+        <v>46304.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46303.89583333334</v>
+        <v>46304.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46303.90625</v>
+        <v>46304.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46303.91666666666</v>
+        <v>46304.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46303.92708333334</v>
+        <v>46304.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46303.9375</v>
+        <v>46304.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46303.94791666666</v>
+        <v>46304.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46303.95833333334</v>
+        <v>46304.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -5347,7 +5347,7 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46303.96875</v>
+        <v>46304.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46303.97916666666</v>
+        <v>46304.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46303.98958333334</v>
+        <v>46304.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="391">
   <si>
     <t>Timestamp (CET)</t>
   </si>
@@ -37,294 +37,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>08.10.20261</t>
-  </si>
-  <si>
-    <t>08.10.20262</t>
-  </si>
-  <si>
-    <t>08.10.20263</t>
-  </si>
-  <si>
-    <t>08.10.20264</t>
-  </si>
-  <si>
-    <t>08.10.20265</t>
-  </si>
-  <si>
-    <t>08.10.20266</t>
-  </si>
-  <si>
-    <t>08.10.20267</t>
-  </si>
-  <si>
-    <t>08.10.20268</t>
-  </si>
-  <si>
-    <t>08.10.20269</t>
-  </si>
-  <si>
-    <t>08.10.202610</t>
-  </si>
-  <si>
-    <t>08.10.202611</t>
-  </si>
-  <si>
-    <t>08.10.202612</t>
-  </si>
-  <si>
-    <t>08.10.202613</t>
-  </si>
-  <si>
-    <t>08.10.202614</t>
-  </si>
-  <si>
-    <t>08.10.202615</t>
-  </si>
-  <si>
-    <t>08.10.202616</t>
-  </si>
-  <si>
-    <t>08.10.202617</t>
-  </si>
-  <si>
-    <t>08.10.202618</t>
-  </si>
-  <si>
-    <t>08.10.202619</t>
-  </si>
-  <si>
-    <t>08.10.202620</t>
-  </si>
-  <si>
-    <t>08.10.202621</t>
-  </si>
-  <si>
-    <t>08.10.202622</t>
-  </si>
-  <si>
-    <t>08.10.202623</t>
-  </si>
-  <si>
-    <t>08.10.202624</t>
-  </si>
-  <si>
-    <t>08.10.202625</t>
-  </si>
-  <si>
-    <t>08.10.202626</t>
-  </si>
-  <si>
-    <t>08.10.202627</t>
-  </si>
-  <si>
-    <t>08.10.202628</t>
-  </si>
-  <si>
-    <t>08.10.202629</t>
-  </si>
-  <si>
-    <t>08.10.202630</t>
-  </si>
-  <si>
-    <t>08.10.202631</t>
-  </si>
-  <si>
-    <t>08.10.202632</t>
-  </si>
-  <si>
-    <t>08.10.202633</t>
-  </si>
-  <si>
-    <t>08.10.202634</t>
-  </si>
-  <si>
-    <t>08.10.202635</t>
-  </si>
-  <si>
-    <t>08.10.202636</t>
-  </si>
-  <si>
-    <t>08.10.202637</t>
-  </si>
-  <si>
-    <t>08.10.202638</t>
-  </si>
-  <si>
-    <t>08.10.202639</t>
-  </si>
-  <si>
-    <t>08.10.202640</t>
-  </si>
-  <si>
-    <t>08.10.202641</t>
-  </si>
-  <si>
-    <t>08.10.202642</t>
-  </si>
-  <si>
-    <t>08.10.202643</t>
-  </si>
-  <si>
-    <t>08.10.202644</t>
-  </si>
-  <si>
-    <t>08.10.202645</t>
-  </si>
-  <si>
-    <t>08.10.202646</t>
-  </si>
-  <si>
-    <t>08.10.202647</t>
-  </si>
-  <si>
-    <t>08.10.202648</t>
-  </si>
-  <si>
-    <t>08.10.202649</t>
-  </si>
-  <si>
-    <t>08.10.202650</t>
-  </si>
-  <si>
-    <t>08.10.202651</t>
-  </si>
-  <si>
-    <t>08.10.202652</t>
-  </si>
-  <si>
-    <t>08.10.202653</t>
-  </si>
-  <si>
-    <t>08.10.202654</t>
-  </si>
-  <si>
-    <t>08.10.202655</t>
-  </si>
-  <si>
-    <t>08.10.202656</t>
-  </si>
-  <si>
-    <t>08.10.202657</t>
-  </si>
-  <si>
-    <t>08.10.202658</t>
-  </si>
-  <si>
-    <t>08.10.202659</t>
-  </si>
-  <si>
-    <t>08.10.202660</t>
-  </si>
-  <si>
-    <t>08.10.202661</t>
-  </si>
-  <si>
-    <t>08.10.202662</t>
-  </si>
-  <si>
-    <t>08.10.202663</t>
-  </si>
-  <si>
-    <t>08.10.202664</t>
-  </si>
-  <si>
-    <t>08.10.202665</t>
-  </si>
-  <si>
-    <t>08.10.202666</t>
-  </si>
-  <si>
-    <t>08.10.202667</t>
-  </si>
-  <si>
-    <t>08.10.202668</t>
-  </si>
-  <si>
-    <t>08.10.202669</t>
-  </si>
-  <si>
-    <t>08.10.202670</t>
-  </si>
-  <si>
-    <t>08.10.202671</t>
-  </si>
-  <si>
-    <t>08.10.202672</t>
-  </si>
-  <si>
-    <t>08.10.202673</t>
-  </si>
-  <si>
-    <t>08.10.202674</t>
-  </si>
-  <si>
-    <t>08.10.202675</t>
-  </si>
-  <si>
-    <t>08.10.202676</t>
-  </si>
-  <si>
-    <t>08.10.202677</t>
-  </si>
-  <si>
-    <t>08.10.202678</t>
-  </si>
-  <si>
-    <t>08.10.202679</t>
-  </si>
-  <si>
-    <t>08.10.202680</t>
-  </si>
-  <si>
-    <t>08.10.202681</t>
-  </si>
-  <si>
-    <t>08.10.202682</t>
-  </si>
-  <si>
-    <t>08.10.202683</t>
-  </si>
-  <si>
-    <t>08.10.202684</t>
-  </si>
-  <si>
-    <t>08.10.202685</t>
-  </si>
-  <si>
-    <t>08.10.202686</t>
-  </si>
-  <si>
-    <t>08.10.202687</t>
-  </si>
-  <si>
-    <t>08.10.202688</t>
-  </si>
-  <si>
-    <t>08.10.202689</t>
-  </si>
-  <si>
-    <t>08.10.202690</t>
-  </si>
-  <si>
-    <t>08.10.202691</t>
-  </si>
-  <si>
-    <t>08.10.202692</t>
-  </si>
-  <si>
-    <t>08.10.202693</t>
-  </si>
-  <si>
-    <t>08.10.202694</t>
-  </si>
-  <si>
-    <t>08.10.202695</t>
-  </si>
-  <si>
-    <t>08.10.202696</t>
-  </si>
-  <si>
     <t>09.10.20261</t>
   </si>
   <si>
@@ -611,6 +323,870 @@
   </si>
   <si>
     <t>09.10.202696</t>
+  </si>
+  <si>
+    <t>10.10.20261</t>
+  </si>
+  <si>
+    <t>10.10.20262</t>
+  </si>
+  <si>
+    <t>10.10.20263</t>
+  </si>
+  <si>
+    <t>10.10.20264</t>
+  </si>
+  <si>
+    <t>10.10.20265</t>
+  </si>
+  <si>
+    <t>10.10.20266</t>
+  </si>
+  <si>
+    <t>10.10.20267</t>
+  </si>
+  <si>
+    <t>10.10.20268</t>
+  </si>
+  <si>
+    <t>10.10.20269</t>
+  </si>
+  <si>
+    <t>10.10.202610</t>
+  </si>
+  <si>
+    <t>10.10.202611</t>
+  </si>
+  <si>
+    <t>10.10.202612</t>
+  </si>
+  <si>
+    <t>10.10.202613</t>
+  </si>
+  <si>
+    <t>10.10.202614</t>
+  </si>
+  <si>
+    <t>10.10.202615</t>
+  </si>
+  <si>
+    <t>10.10.202616</t>
+  </si>
+  <si>
+    <t>10.10.202617</t>
+  </si>
+  <si>
+    <t>10.10.202618</t>
+  </si>
+  <si>
+    <t>10.10.202619</t>
+  </si>
+  <si>
+    <t>10.10.202620</t>
+  </si>
+  <si>
+    <t>10.10.202621</t>
+  </si>
+  <si>
+    <t>10.10.202622</t>
+  </si>
+  <si>
+    <t>10.10.202623</t>
+  </si>
+  <si>
+    <t>10.10.202624</t>
+  </si>
+  <si>
+    <t>10.10.202625</t>
+  </si>
+  <si>
+    <t>10.10.202626</t>
+  </si>
+  <si>
+    <t>10.10.202627</t>
+  </si>
+  <si>
+    <t>10.10.202628</t>
+  </si>
+  <si>
+    <t>10.10.202629</t>
+  </si>
+  <si>
+    <t>10.10.202630</t>
+  </si>
+  <si>
+    <t>10.10.202631</t>
+  </si>
+  <si>
+    <t>10.10.202632</t>
+  </si>
+  <si>
+    <t>10.10.202633</t>
+  </si>
+  <si>
+    <t>10.10.202634</t>
+  </si>
+  <si>
+    <t>10.10.202635</t>
+  </si>
+  <si>
+    <t>10.10.202636</t>
+  </si>
+  <si>
+    <t>10.10.202637</t>
+  </si>
+  <si>
+    <t>10.10.202638</t>
+  </si>
+  <si>
+    <t>10.10.202639</t>
+  </si>
+  <si>
+    <t>10.10.202640</t>
+  </si>
+  <si>
+    <t>10.10.202641</t>
+  </si>
+  <si>
+    <t>10.10.202642</t>
+  </si>
+  <si>
+    <t>10.10.202643</t>
+  </si>
+  <si>
+    <t>10.10.202644</t>
+  </si>
+  <si>
+    <t>10.10.202645</t>
+  </si>
+  <si>
+    <t>10.10.202646</t>
+  </si>
+  <si>
+    <t>10.10.202647</t>
+  </si>
+  <si>
+    <t>10.10.202648</t>
+  </si>
+  <si>
+    <t>10.10.202649</t>
+  </si>
+  <si>
+    <t>10.10.202650</t>
+  </si>
+  <si>
+    <t>10.10.202651</t>
+  </si>
+  <si>
+    <t>10.10.202652</t>
+  </si>
+  <si>
+    <t>10.10.202653</t>
+  </si>
+  <si>
+    <t>10.10.202654</t>
+  </si>
+  <si>
+    <t>10.10.202655</t>
+  </si>
+  <si>
+    <t>10.10.202656</t>
+  </si>
+  <si>
+    <t>10.10.202657</t>
+  </si>
+  <si>
+    <t>10.10.202658</t>
+  </si>
+  <si>
+    <t>10.10.202659</t>
+  </si>
+  <si>
+    <t>10.10.202660</t>
+  </si>
+  <si>
+    <t>10.10.202661</t>
+  </si>
+  <si>
+    <t>10.10.202662</t>
+  </si>
+  <si>
+    <t>10.10.202663</t>
+  </si>
+  <si>
+    <t>10.10.202664</t>
+  </si>
+  <si>
+    <t>10.10.202665</t>
+  </si>
+  <si>
+    <t>10.10.202666</t>
+  </si>
+  <si>
+    <t>10.10.202667</t>
+  </si>
+  <si>
+    <t>10.10.202668</t>
+  </si>
+  <si>
+    <t>10.10.202669</t>
+  </si>
+  <si>
+    <t>10.10.202670</t>
+  </si>
+  <si>
+    <t>10.10.202671</t>
+  </si>
+  <si>
+    <t>10.10.202672</t>
+  </si>
+  <si>
+    <t>10.10.202673</t>
+  </si>
+  <si>
+    <t>10.10.202674</t>
+  </si>
+  <si>
+    <t>10.10.202675</t>
+  </si>
+  <si>
+    <t>10.10.202676</t>
+  </si>
+  <si>
+    <t>10.10.202677</t>
+  </si>
+  <si>
+    <t>10.10.202678</t>
+  </si>
+  <si>
+    <t>10.10.202679</t>
+  </si>
+  <si>
+    <t>10.10.202680</t>
+  </si>
+  <si>
+    <t>10.10.202681</t>
+  </si>
+  <si>
+    <t>10.10.202682</t>
+  </si>
+  <si>
+    <t>10.10.202683</t>
+  </si>
+  <si>
+    <t>10.10.202684</t>
+  </si>
+  <si>
+    <t>10.10.202685</t>
+  </si>
+  <si>
+    <t>10.10.202686</t>
+  </si>
+  <si>
+    <t>10.10.202687</t>
+  </si>
+  <si>
+    <t>10.10.202688</t>
+  </si>
+  <si>
+    <t>10.10.202689</t>
+  </si>
+  <si>
+    <t>10.10.202690</t>
+  </si>
+  <si>
+    <t>10.10.202691</t>
+  </si>
+  <si>
+    <t>10.10.202692</t>
+  </si>
+  <si>
+    <t>10.10.202693</t>
+  </si>
+  <si>
+    <t>10.10.202694</t>
+  </si>
+  <si>
+    <t>10.10.202695</t>
+  </si>
+  <si>
+    <t>10.10.202696</t>
+  </si>
+  <si>
+    <t>11.10.20261</t>
+  </si>
+  <si>
+    <t>11.10.20262</t>
+  </si>
+  <si>
+    <t>11.10.20263</t>
+  </si>
+  <si>
+    <t>11.10.20264</t>
+  </si>
+  <si>
+    <t>11.10.20265</t>
+  </si>
+  <si>
+    <t>11.10.20266</t>
+  </si>
+  <si>
+    <t>11.10.20267</t>
+  </si>
+  <si>
+    <t>11.10.20268</t>
+  </si>
+  <si>
+    <t>11.10.20269</t>
+  </si>
+  <si>
+    <t>11.10.202610</t>
+  </si>
+  <si>
+    <t>11.10.202611</t>
+  </si>
+  <si>
+    <t>11.10.202612</t>
+  </si>
+  <si>
+    <t>11.10.202613</t>
+  </si>
+  <si>
+    <t>11.10.202614</t>
+  </si>
+  <si>
+    <t>11.10.202615</t>
+  </si>
+  <si>
+    <t>11.10.202616</t>
+  </si>
+  <si>
+    <t>11.10.202617</t>
+  </si>
+  <si>
+    <t>11.10.202618</t>
+  </si>
+  <si>
+    <t>11.10.202619</t>
+  </si>
+  <si>
+    <t>11.10.202620</t>
+  </si>
+  <si>
+    <t>11.10.202621</t>
+  </si>
+  <si>
+    <t>11.10.202622</t>
+  </si>
+  <si>
+    <t>11.10.202623</t>
+  </si>
+  <si>
+    <t>11.10.202624</t>
+  </si>
+  <si>
+    <t>11.10.202625</t>
+  </si>
+  <si>
+    <t>11.10.202626</t>
+  </si>
+  <si>
+    <t>11.10.202627</t>
+  </si>
+  <si>
+    <t>11.10.202628</t>
+  </si>
+  <si>
+    <t>11.10.202629</t>
+  </si>
+  <si>
+    <t>11.10.202630</t>
+  </si>
+  <si>
+    <t>11.10.202631</t>
+  </si>
+  <si>
+    <t>11.10.202632</t>
+  </si>
+  <si>
+    <t>11.10.202633</t>
+  </si>
+  <si>
+    <t>11.10.202634</t>
+  </si>
+  <si>
+    <t>11.10.202635</t>
+  </si>
+  <si>
+    <t>11.10.202636</t>
+  </si>
+  <si>
+    <t>11.10.202637</t>
+  </si>
+  <si>
+    <t>11.10.202638</t>
+  </si>
+  <si>
+    <t>11.10.202639</t>
+  </si>
+  <si>
+    <t>11.10.202640</t>
+  </si>
+  <si>
+    <t>11.10.202641</t>
+  </si>
+  <si>
+    <t>11.10.202642</t>
+  </si>
+  <si>
+    <t>11.10.202643</t>
+  </si>
+  <si>
+    <t>11.10.202644</t>
+  </si>
+  <si>
+    <t>11.10.202645</t>
+  </si>
+  <si>
+    <t>11.10.202646</t>
+  </si>
+  <si>
+    <t>11.10.202647</t>
+  </si>
+  <si>
+    <t>11.10.202648</t>
+  </si>
+  <si>
+    <t>11.10.202649</t>
+  </si>
+  <si>
+    <t>11.10.202650</t>
+  </si>
+  <si>
+    <t>11.10.202651</t>
+  </si>
+  <si>
+    <t>11.10.202652</t>
+  </si>
+  <si>
+    <t>11.10.202653</t>
+  </si>
+  <si>
+    <t>11.10.202654</t>
+  </si>
+  <si>
+    <t>11.10.202655</t>
+  </si>
+  <si>
+    <t>11.10.202656</t>
+  </si>
+  <si>
+    <t>11.10.202657</t>
+  </si>
+  <si>
+    <t>11.10.202658</t>
+  </si>
+  <si>
+    <t>11.10.202659</t>
+  </si>
+  <si>
+    <t>11.10.202660</t>
+  </si>
+  <si>
+    <t>11.10.202661</t>
+  </si>
+  <si>
+    <t>11.10.202662</t>
+  </si>
+  <si>
+    <t>11.10.202663</t>
+  </si>
+  <si>
+    <t>11.10.202664</t>
+  </si>
+  <si>
+    <t>11.10.202665</t>
+  </si>
+  <si>
+    <t>11.10.202666</t>
+  </si>
+  <si>
+    <t>11.10.202667</t>
+  </si>
+  <si>
+    <t>11.10.202668</t>
+  </si>
+  <si>
+    <t>11.10.202669</t>
+  </si>
+  <si>
+    <t>11.10.202670</t>
+  </si>
+  <si>
+    <t>11.10.202671</t>
+  </si>
+  <si>
+    <t>11.10.202672</t>
+  </si>
+  <si>
+    <t>11.10.202673</t>
+  </si>
+  <si>
+    <t>11.10.202674</t>
+  </si>
+  <si>
+    <t>11.10.202675</t>
+  </si>
+  <si>
+    <t>11.10.202676</t>
+  </si>
+  <si>
+    <t>11.10.202677</t>
+  </si>
+  <si>
+    <t>11.10.202678</t>
+  </si>
+  <si>
+    <t>11.10.202679</t>
+  </si>
+  <si>
+    <t>11.10.202680</t>
+  </si>
+  <si>
+    <t>11.10.202681</t>
+  </si>
+  <si>
+    <t>11.10.202682</t>
+  </si>
+  <si>
+    <t>11.10.202683</t>
+  </si>
+  <si>
+    <t>11.10.202684</t>
+  </si>
+  <si>
+    <t>11.10.202685</t>
+  </si>
+  <si>
+    <t>11.10.202686</t>
+  </si>
+  <si>
+    <t>11.10.202687</t>
+  </si>
+  <si>
+    <t>11.10.202688</t>
+  </si>
+  <si>
+    <t>11.10.202689</t>
+  </si>
+  <si>
+    <t>11.10.202690</t>
+  </si>
+  <si>
+    <t>11.10.202691</t>
+  </si>
+  <si>
+    <t>11.10.202692</t>
+  </si>
+  <si>
+    <t>11.10.202693</t>
+  </si>
+  <si>
+    <t>11.10.202694</t>
+  </si>
+  <si>
+    <t>11.10.202695</t>
+  </si>
+  <si>
+    <t>11.10.202696</t>
+  </si>
+  <si>
+    <t>12.10.20261</t>
+  </si>
+  <si>
+    <t>12.10.20262</t>
+  </si>
+  <si>
+    <t>12.10.20263</t>
+  </si>
+  <si>
+    <t>12.10.20264</t>
+  </si>
+  <si>
+    <t>12.10.20265</t>
+  </si>
+  <si>
+    <t>12.10.20266</t>
+  </si>
+  <si>
+    <t>12.10.20267</t>
+  </si>
+  <si>
+    <t>12.10.20268</t>
+  </si>
+  <si>
+    <t>12.10.20269</t>
+  </si>
+  <si>
+    <t>12.10.202610</t>
+  </si>
+  <si>
+    <t>12.10.202611</t>
+  </si>
+  <si>
+    <t>12.10.202612</t>
+  </si>
+  <si>
+    <t>12.10.202613</t>
+  </si>
+  <si>
+    <t>12.10.202614</t>
+  </si>
+  <si>
+    <t>12.10.202615</t>
+  </si>
+  <si>
+    <t>12.10.202616</t>
+  </si>
+  <si>
+    <t>12.10.202617</t>
+  </si>
+  <si>
+    <t>12.10.202618</t>
+  </si>
+  <si>
+    <t>12.10.202619</t>
+  </si>
+  <si>
+    <t>12.10.202620</t>
+  </si>
+  <si>
+    <t>12.10.202621</t>
+  </si>
+  <si>
+    <t>12.10.202622</t>
+  </si>
+  <si>
+    <t>12.10.202623</t>
+  </si>
+  <si>
+    <t>12.10.202624</t>
+  </si>
+  <si>
+    <t>12.10.202625</t>
+  </si>
+  <si>
+    <t>12.10.202626</t>
+  </si>
+  <si>
+    <t>12.10.202627</t>
+  </si>
+  <si>
+    <t>12.10.202628</t>
+  </si>
+  <si>
+    <t>12.10.202629</t>
+  </si>
+  <si>
+    <t>12.10.202630</t>
+  </si>
+  <si>
+    <t>12.10.202631</t>
+  </si>
+  <si>
+    <t>12.10.202632</t>
+  </si>
+  <si>
+    <t>12.10.202633</t>
+  </si>
+  <si>
+    <t>12.10.202634</t>
+  </si>
+  <si>
+    <t>12.10.202635</t>
+  </si>
+  <si>
+    <t>12.10.202636</t>
+  </si>
+  <si>
+    <t>12.10.202637</t>
+  </si>
+  <si>
+    <t>12.10.202638</t>
+  </si>
+  <si>
+    <t>12.10.202639</t>
+  </si>
+  <si>
+    <t>12.10.202640</t>
+  </si>
+  <si>
+    <t>12.10.202641</t>
+  </si>
+  <si>
+    <t>12.10.202642</t>
+  </si>
+  <si>
+    <t>12.10.202643</t>
+  </si>
+  <si>
+    <t>12.10.202644</t>
+  </si>
+  <si>
+    <t>12.10.202645</t>
+  </si>
+  <si>
+    <t>12.10.202646</t>
+  </si>
+  <si>
+    <t>12.10.202647</t>
+  </si>
+  <si>
+    <t>12.10.202648</t>
+  </si>
+  <si>
+    <t>12.10.202649</t>
+  </si>
+  <si>
+    <t>12.10.202650</t>
+  </si>
+  <si>
+    <t>12.10.202651</t>
+  </si>
+  <si>
+    <t>12.10.202652</t>
+  </si>
+  <si>
+    <t>12.10.202653</t>
+  </si>
+  <si>
+    <t>12.10.202654</t>
+  </si>
+  <si>
+    <t>12.10.202655</t>
+  </si>
+  <si>
+    <t>12.10.202656</t>
+  </si>
+  <si>
+    <t>12.10.202657</t>
+  </si>
+  <si>
+    <t>12.10.202658</t>
+  </si>
+  <si>
+    <t>12.10.202659</t>
+  </si>
+  <si>
+    <t>12.10.202660</t>
+  </si>
+  <si>
+    <t>12.10.202661</t>
+  </si>
+  <si>
+    <t>12.10.202662</t>
+  </si>
+  <si>
+    <t>12.10.202663</t>
+  </si>
+  <si>
+    <t>12.10.202664</t>
+  </si>
+  <si>
+    <t>12.10.202665</t>
+  </si>
+  <si>
+    <t>12.10.202666</t>
+  </si>
+  <si>
+    <t>12.10.202667</t>
+  </si>
+  <si>
+    <t>12.10.202668</t>
+  </si>
+  <si>
+    <t>12.10.202669</t>
+  </si>
+  <si>
+    <t>12.10.202670</t>
+  </si>
+  <si>
+    <t>12.10.202671</t>
+  </si>
+  <si>
+    <t>12.10.202672</t>
+  </si>
+  <si>
+    <t>12.10.202673</t>
+  </si>
+  <si>
+    <t>12.10.202674</t>
+  </si>
+  <si>
+    <t>12.10.202675</t>
+  </si>
+  <si>
+    <t>12.10.202676</t>
+  </si>
+  <si>
+    <t>12.10.202677</t>
+  </si>
+  <si>
+    <t>12.10.202678</t>
+  </si>
+  <si>
+    <t>12.10.202679</t>
+  </si>
+  <si>
+    <t>12.10.202680</t>
+  </si>
+  <si>
+    <t>12.10.202681</t>
+  </si>
+  <si>
+    <t>12.10.202682</t>
+  </si>
+  <si>
+    <t>12.10.202683</t>
+  </si>
+  <si>
+    <t>12.10.202684</t>
+  </si>
+  <si>
+    <t>12.10.202685</t>
+  </si>
+  <si>
+    <t>12.10.202686</t>
+  </si>
+  <si>
+    <t>12.10.202687</t>
+  </si>
+  <si>
+    <t>12.10.202688</t>
+  </si>
+  <si>
+    <t>12.10.202689</t>
+  </si>
+  <si>
+    <t>12.10.202690</t>
+  </si>
+  <si>
+    <t>12.10.202691</t>
+  </si>
+  <si>
+    <t>12.10.202692</t>
+  </si>
+  <si>
+    <t>12.10.202693</t>
+  </si>
+  <si>
+    <t>12.10.202694</t>
+  </si>
+  <si>
+    <t>12.10.202695</t>
+  </si>
+  <si>
+    <t>12.10.202696</t>
   </si>
 </sst>
 </file>
@@ -972,7 +1548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G193"/>
+  <dimension ref="A1:G385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1000,13 +1576,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B2">
-        <v>0.075</v>
+        <v>4.293</v>
       </c>
       <c r="C2">
-        <v>2.495</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1023,13 +1599,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46303.01041666666</v>
+        <v>46304.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.005</v>
+        <v>4.642</v>
       </c>
       <c r="C3">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1046,13 +1622,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46303.02083333334</v>
+        <v>46304.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.362</v>
+        <v>5.413</v>
       </c>
       <c r="C4">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1069,13 +1645,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46303.03125</v>
+        <v>46304.03125</v>
       </c>
       <c r="B5">
-        <v>4.543</v>
+        <v>0.698</v>
       </c>
       <c r="C5">
-        <v>0.006</v>
+        <v>1.788</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1092,13 +1668,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46303.04166666666</v>
+        <v>46304.04166666666</v>
       </c>
       <c r="B6">
-        <v>1.94</v>
+        <v>11.905</v>
       </c>
       <c r="C6">
-        <v>0.05</v>
+        <v>0.507</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1115,13 +1691,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46303.05208333334</v>
+        <v>46304.05208333334</v>
       </c>
       <c r="B7">
-        <v>0.143</v>
+        <v>4.742</v>
       </c>
       <c r="C7">
-        <v>0.121</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1138,10 +1714,10 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46303.0625</v>
+        <v>46304.0625</v>
       </c>
       <c r="B8">
-        <v>1.483</v>
+        <v>25.578</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1161,10 +1737,10 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46303.07291666666</v>
+        <v>46304.07291666666</v>
       </c>
       <c r="B9">
-        <v>4.954</v>
+        <v>20.903</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1184,10 +1760,10 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46303.08333333334</v>
+        <v>46304.08333333334</v>
       </c>
       <c r="B10">
-        <v>11.522</v>
+        <v>11.54</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1207,10 +1783,10 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46303.09375</v>
+        <v>46304.09375</v>
       </c>
       <c r="B11">
-        <v>31.022</v>
+        <v>18.361</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1230,10 +1806,10 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46303.10416666666</v>
+        <v>46304.10416666666</v>
       </c>
       <c r="B12">
-        <v>27.57</v>
+        <v>23.123</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1253,10 +1829,10 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46303.11458333334</v>
+        <v>46304.11458333334</v>
       </c>
       <c r="B13">
-        <v>22.975</v>
+        <v>36.561</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1276,10 +1852,10 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46303.125</v>
+        <v>46304.125</v>
       </c>
       <c r="B14">
-        <v>14.987</v>
+        <v>49.765</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1299,16 +1875,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46303.13541666666</v>
+        <v>46304.13541666666</v>
       </c>
       <c r="B15">
-        <v>18.079</v>
+        <v>35.578</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1322,16 +1898,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46303.14583333334</v>
+        <v>46304.14583333334</v>
       </c>
       <c r="B16">
-        <v>19.113</v>
+        <v>23.305</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1345,16 +1921,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46303.15625</v>
+        <v>46304.15625</v>
       </c>
       <c r="B17">
-        <v>27.942</v>
+        <v>43.251</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1368,16 +1944,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46303.16666666666</v>
+        <v>46304.16666666666</v>
       </c>
       <c r="B18">
-        <v>7.336</v>
+        <v>7.688</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1391,16 +1967,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46303.17708333334</v>
+        <v>46304.17708333334</v>
       </c>
       <c r="B19">
-        <v>10.539</v>
+        <v>1.659</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1414,16 +1990,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46303.1875</v>
+        <v>46304.1875</v>
       </c>
       <c r="B20">
-        <v>3.006</v>
+        <v>0.205</v>
       </c>
       <c r="C20">
-        <v>0.02</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1437,16 +2013,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46303.19791666666</v>
+        <v>46304.19791666666</v>
       </c>
       <c r="B21">
-        <v>3.439</v>
+        <v>1.806</v>
       </c>
       <c r="C21">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1460,16 +2036,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46303.20833333334</v>
+        <v>46304.20833333334</v>
       </c>
       <c r="B22">
-        <v>5.481</v>
+        <v>14.024</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1483,16 +2059,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46303.21875</v>
+        <v>46304.21875</v>
       </c>
       <c r="B23">
-        <v>5.679</v>
+        <v>31.426</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1506,16 +2082,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46303.22916666666</v>
+        <v>46304.22916666666</v>
       </c>
       <c r="B24">
-        <v>19.721</v>
+        <v>10.545</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1529,16 +2105,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46303.23958333334</v>
+        <v>46304.23958333334</v>
       </c>
       <c r="B25">
-        <v>10.141</v>
+        <v>8.079000000000001</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1552,16 +2128,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="B26">
-        <v>3.623</v>
+        <v>4.402</v>
       </c>
       <c r="C26">
-        <v>1.089</v>
+        <v>1.59</v>
       </c>
       <c r="D26">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1575,16 +2151,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46303.26041666666</v>
+        <v>46304.26041666666</v>
       </c>
       <c r="B27">
-        <v>2.02</v>
+        <v>0.131</v>
       </c>
       <c r="C27">
-        <v>0.018</v>
+        <v>0.119</v>
       </c>
       <c r="D27">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1598,16 +2174,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46303.27083333334</v>
+        <v>46304.27083333334</v>
       </c>
       <c r="B28">
-        <v>0.217</v>
+        <v>0.215</v>
       </c>
       <c r="C28">
-        <v>0.282</v>
+        <v>0.147</v>
       </c>
       <c r="D28">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1621,16 +2197,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46303.28125</v>
+        <v>46304.28125</v>
       </c>
       <c r="B29">
-        <v>0.437</v>
+        <v>3.824</v>
       </c>
       <c r="C29">
-        <v>0.194</v>
+        <v>0.013</v>
       </c>
       <c r="D29">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1644,16 +2220,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46303.29166666666</v>
+        <v>46304.29166666666</v>
       </c>
       <c r="B30">
-        <v>6.655</v>
+        <v>1.694</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="D30">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1667,16 +2243,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46303.30208333334</v>
+        <v>46304.30208333334</v>
       </c>
       <c r="B31">
-        <v>16.324</v>
+        <v>5.396</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D31">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1690,16 +2266,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46303.3125</v>
+        <v>46304.3125</v>
       </c>
       <c r="B32">
-        <v>2.646</v>
+        <v>0.585</v>
       </c>
       <c r="C32">
-        <v>4.702</v>
+        <v>0.233</v>
       </c>
       <c r="D32">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1713,16 +2289,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46303.32291666666</v>
+        <v>46304.32291666666</v>
       </c>
       <c r="B33">
-        <v>0.931</v>
+        <v>3.763</v>
       </c>
       <c r="C33">
-        <v>5.277</v>
+        <v>0.036</v>
       </c>
       <c r="D33">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1736,19 +2312,19 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46303.33333333334</v>
+        <v>46304.33333333334</v>
       </c>
       <c r="B34">
-        <v>0.913</v>
+        <v>26.973</v>
       </c>
       <c r="C34">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>19.75</v>
+        <v>0</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F34">
         <v>33</v>
@@ -1759,19 +2335,19 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46303.34375</v>
+        <v>46304.34375</v>
       </c>
       <c r="B35">
-        <v>6.363</v>
+        <v>26.055</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35">
-        <v>67.5</v>
+        <v>0</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F35">
         <v>34</v>
@@ -1782,16 +2358,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46303.35416666666</v>
+        <v>46304.35416666666</v>
       </c>
       <c r="B36">
-        <v>21.744</v>
+        <v>4.45</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>1.089</v>
       </c>
       <c r="D36">
-        <v>67.5</v>
+        <v>0</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -1805,16 +2381,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46303.36458333334</v>
+        <v>46304.36458333334</v>
       </c>
       <c r="B37">
-        <v>1.881</v>
+        <v>0.414</v>
       </c>
       <c r="C37">
-        <v>5.052</v>
+        <v>7.102</v>
       </c>
       <c r="D37">
-        <v>67.5</v>
+        <v>0</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -1828,16 +2404,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46303.375</v>
+        <v>46304.375</v>
       </c>
       <c r="B38">
-        <v>0.407</v>
+        <v>18.914</v>
       </c>
       <c r="C38">
-        <v>2.318</v>
+        <v>0.372</v>
       </c>
       <c r="D38">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -1851,16 +2427,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46303.38541666666</v>
+        <v>46304.38541666666</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>16.928</v>
       </c>
       <c r="C39">
-        <v>8.952999999999999</v>
+        <v>0.546</v>
       </c>
       <c r="D39">
-        <v>53.5</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -1874,16 +2450,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46303.39583333334</v>
+        <v>46304.39583333334</v>
       </c>
       <c r="B40">
-        <v>3.561</v>
+        <v>3.829</v>
       </c>
       <c r="C40">
-        <v>1.556</v>
+        <v>0.022</v>
       </c>
       <c r="D40">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -1897,16 +2473,16 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46303.40625</v>
+        <v>46304.40625</v>
       </c>
       <c r="B41">
-        <v>0.106</v>
+        <v>9.65</v>
       </c>
       <c r="C41">
-        <v>5.156</v>
+        <v>0.723</v>
       </c>
       <c r="D41">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -1920,13 +2496,13 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46303.41666666666</v>
+        <v>46304.41666666666</v>
       </c>
       <c r="B42">
-        <v>1.452</v>
+        <v>1.802</v>
       </c>
       <c r="C42">
-        <v>3.963</v>
+        <v>0.17</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -1943,13 +2519,13 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46303.42708333334</v>
+        <v>46304.42708333334</v>
       </c>
       <c r="B43">
-        <v>0.185</v>
+        <v>1.568</v>
       </c>
       <c r="C43">
-        <v>1.174</v>
+        <v>0.018</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -1966,13 +2542,13 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46303.4375</v>
+        <v>46304.4375</v>
       </c>
       <c r="B44">
-        <v>0.08</v>
+        <v>0.759</v>
       </c>
       <c r="C44">
-        <v>6.079</v>
+        <v>0.292</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -1989,13 +2565,13 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46303.44791666666</v>
+        <v>46304.44791666666</v>
       </c>
       <c r="B45">
-        <v>0.06</v>
+        <v>3.865</v>
       </c>
       <c r="C45">
-        <v>2.395</v>
+        <v>0.015</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2012,13 +2588,13 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46303.45833333334</v>
+        <v>46304.45833333334</v>
       </c>
       <c r="B46">
-        <v>0.161</v>
+        <v>0.783</v>
       </c>
       <c r="C46">
-        <v>3.746</v>
+        <v>0.092</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2035,13 +2611,13 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46303.46875</v>
+        <v>46304.46875</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>0.181</v>
       </c>
       <c r="C47">
-        <v>9.829000000000001</v>
+        <v>2.68</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2058,13 +2634,13 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46303.47916666666</v>
+        <v>46304.47916666666</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>1.719</v>
       </c>
       <c r="C48">
-        <v>15.701</v>
+        <v>3.037</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2081,13 +2657,13 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46303.48958333334</v>
+        <v>46304.48958333334</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="C49">
-        <v>3.611</v>
+        <v>2.935</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2104,13 +2680,13 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46303.5</v>
+        <v>46304.5</v>
       </c>
       <c r="B50">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>4.665</v>
+        <v>1.98</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2127,13 +2703,13 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46303.51041666666</v>
+        <v>46304.51041666666</v>
       </c>
       <c r="B51">
-        <v>0.005</v>
+        <v>0.031</v>
       </c>
       <c r="C51">
-        <v>3.638</v>
+        <v>11.426</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2150,13 +2726,13 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46303.52083333334</v>
+        <v>46304.52083333334</v>
       </c>
       <c r="B52">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <v>0.706</v>
+        <v>12.324</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2173,13 +2749,13 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46303.53125</v>
+        <v>46304.53125</v>
       </c>
       <c r="B53">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>2.087</v>
+        <v>22.133</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2196,13 +2772,13 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46303.54166666666</v>
+        <v>46304.54166666666</v>
       </c>
       <c r="B54">
-        <v>3.923</v>
+        <v>0.028</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>4.767</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2219,13 +2795,13 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46303.55208333334</v>
+        <v>46304.55208333334</v>
       </c>
       <c r="B55">
-        <v>0.08500000000000001</v>
+        <v>0</v>
       </c>
       <c r="C55">
-        <v>2.748</v>
+        <v>13.704</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2242,13 +2818,13 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46303.5625</v>
+        <v>46304.5625</v>
       </c>
       <c r="B56">
-        <v>0.344</v>
+        <v>0.214</v>
       </c>
       <c r="C56">
-        <v>0.773</v>
+        <v>3.054</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2265,13 +2841,13 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46303.57291666666</v>
+        <v>46304.57291666666</v>
       </c>
       <c r="B57">
-        <v>0.399</v>
+        <v>0.872</v>
       </c>
       <c r="C57">
-        <v>1.482</v>
+        <v>0.28</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2288,13 +2864,13 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46303.58333333334</v>
+        <v>46304.58333333334</v>
       </c>
       <c r="B58">
-        <v>0.649</v>
+        <v>1.614</v>
       </c>
       <c r="C58">
-        <v>9.260999999999999</v>
+        <v>1.151</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2311,13 +2887,13 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46303.59375</v>
+        <v>46304.59375</v>
       </c>
       <c r="B59">
-        <v>0.059</v>
+        <v>1.96</v>
       </c>
       <c r="C59">
-        <v>2.544</v>
+        <v>0.153</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2334,13 +2910,13 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46303.60416666666</v>
+        <v>46304.60416666666</v>
       </c>
       <c r="B60">
-        <v>0.114</v>
+        <v>3.055</v>
       </c>
       <c r="C60">
-        <v>1.163</v>
+        <v>0.017</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2357,13 +2933,13 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46303.61458333334</v>
+        <v>46304.61458333334</v>
       </c>
       <c r="B61">
-        <v>1.838</v>
+        <v>40.237</v>
       </c>
       <c r="C61">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2380,16 +2956,16 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46303.625</v>
+        <v>46304.625</v>
       </c>
       <c r="B62">
-        <v>0.188</v>
+        <v>10.88</v>
       </c>
       <c r="C62">
-        <v>0.442</v>
+        <v>0.242</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -2403,16 +2979,16 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46303.63541666666</v>
+        <v>46304.63541666666</v>
       </c>
       <c r="B63">
-        <v>0.002</v>
+        <v>0.219</v>
       </c>
       <c r="C63">
-        <v>14.716</v>
+        <v>0.401</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -2426,19 +3002,19 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46303.64583333334</v>
+        <v>46304.64583333334</v>
       </c>
       <c r="B64">
-        <v>7.106</v>
+        <v>1.975</v>
       </c>
       <c r="C64">
-        <v>0.042</v>
+        <v>1.601</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="E64">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F64">
         <v>63</v>
@@ -2449,19 +3025,19 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46303.65625</v>
+        <v>46304.65625</v>
       </c>
       <c r="B65">
-        <v>25.116</v>
+        <v>8.484</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>51.75</v>
       </c>
       <c r="E65">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F65">
         <v>64</v>
@@ -2472,16 +3048,16 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46303.66666666666</v>
+        <v>46304.66666666666</v>
       </c>
       <c r="B66">
-        <v>10.975</v>
+        <v>0.828</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>17.466</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -2495,16 +3071,16 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46303.67708333334</v>
+        <v>46304.67708333334</v>
       </c>
       <c r="B67">
-        <v>13.703</v>
+        <v>0.221</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>1.838</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -2518,16 +3094,16 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46303.6875</v>
+        <v>46304.6875</v>
       </c>
       <c r="B68">
-        <v>27.461</v>
+        <v>2.285</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -2541,16 +3117,16 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46303.69791666666</v>
+        <v>46304.69791666666</v>
       </c>
       <c r="B69">
-        <v>20.131</v>
+        <v>2.004</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>0.104</v>
       </c>
       <c r="D69">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -2564,16 +3140,16 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46303.70833333334</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="B70">
-        <v>15.444</v>
+        <v>0.027</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>3.123</v>
       </c>
       <c r="D70">
-        <v>12.5</v>
+        <v>37.5</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -2587,16 +3163,16 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46303.71875</v>
+        <v>46304.71875</v>
       </c>
       <c r="B71">
-        <v>26.206</v>
+        <v>0.094</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>1.741</v>
       </c>
       <c r="D71">
-        <v>12.5</v>
+        <v>37.5</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -2610,16 +3186,16 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46303.72916666666</v>
+        <v>46304.72916666666</v>
       </c>
       <c r="B72">
-        <v>9.15</v>
+        <v>0.281</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="D72">
-        <v>37.5</v>
+        <v>16.5</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -2633,16 +3209,16 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46303.73958333334</v>
+        <v>46304.73958333334</v>
       </c>
       <c r="B73">
-        <v>14.355</v>
+        <v>5.504</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="D73">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -2656,16 +3232,16 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46303.75</v>
+        <v>46304.75</v>
       </c>
       <c r="B74">
-        <v>2.207</v>
+        <v>5.816</v>
       </c>
       <c r="C74">
-        <v>0.177</v>
+        <v>0</v>
       </c>
       <c r="D74">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -2679,16 +3255,16 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46303.76041666666</v>
+        <v>46304.76041666666</v>
       </c>
       <c r="B75">
-        <v>1.323</v>
+        <v>4.458</v>
       </c>
       <c r="C75">
-        <v>1.393</v>
+        <v>0.067</v>
       </c>
       <c r="D75">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -2702,16 +3278,16 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46303.77083333334</v>
+        <v>46304.77083333334</v>
       </c>
       <c r="B76">
-        <v>0.418</v>
+        <v>4.022</v>
       </c>
       <c r="C76">
-        <v>0.208</v>
+        <v>0</v>
       </c>
       <c r="D76">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -2725,16 +3301,16 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46303.78125</v>
+        <v>46304.78125</v>
       </c>
       <c r="B77">
-        <v>0.146</v>
+        <v>4.366</v>
       </c>
       <c r="C77">
-        <v>0.448</v>
+        <v>0.03</v>
       </c>
       <c r="D77">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -2748,13 +3324,13 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46303.79166666666</v>
+        <v>46304.79166666666</v>
       </c>
       <c r="B78">
-        <v>0.488</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C78">
-        <v>0.229</v>
+        <v>0.428</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -2771,13 +3347,13 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46303.80208333334</v>
+        <v>46304.80208333334</v>
       </c>
       <c r="B79">
-        <v>0.202</v>
+        <v>0.153</v>
       </c>
       <c r="C79">
-        <v>0.105</v>
+        <v>0.221</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -2794,19 +3370,19 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46303.8125</v>
+        <v>46304.8125</v>
       </c>
       <c r="B80">
-        <v>0.165</v>
+        <v>0.132</v>
       </c>
       <c r="C80">
-        <v>0.123</v>
+        <v>0.267</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
       <c r="E80">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F80">
         <v>79</v>
@@ -2817,19 +3393,19 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46303.82291666666</v>
+        <v>46304.82291666666</v>
       </c>
       <c r="B81">
-        <v>0.099</v>
+        <v>0.484</v>
       </c>
       <c r="C81">
-        <v>0.31</v>
+        <v>0.285</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
       <c r="E81">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F81">
         <v>80</v>
@@ -2840,19 +3416,19 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46303.83333333334</v>
+        <v>46304.83333333334</v>
       </c>
       <c r="B82">
-        <v>14.843</v>
+        <v>8.365</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="D82">
         <v>0</v>
       </c>
       <c r="E82">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F82">
         <v>81</v>
@@ -2863,13 +3439,13 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46303.84375</v>
+        <v>46304.84375</v>
       </c>
       <c r="B83">
-        <v>12.947</v>
+        <v>1.033</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -2886,13 +3462,13 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46303.85416666666</v>
+        <v>46304.85416666666</v>
       </c>
       <c r="B84">
-        <v>5.909</v>
+        <v>4.525</v>
       </c>
       <c r="C84">
-        <v>0.097</v>
+        <v>0.006</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -2909,13 +3485,13 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46303.86458333334</v>
+        <v>46304.86458333334</v>
       </c>
       <c r="B85">
-        <v>4.379</v>
+        <v>9.015000000000001</v>
       </c>
       <c r="C85">
-        <v>1.299</v>
+        <v>0.439</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -2932,13 +3508,13 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46303.875</v>
+        <v>46304.875</v>
       </c>
       <c r="B86">
-        <v>8.374000000000001</v>
+        <v>43.068</v>
       </c>
       <c r="C86">
-        <v>0.07199999999999999</v>
+        <v>0</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -2955,13 +3531,13 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46303.88541666666</v>
+        <v>46304.88541666666</v>
       </c>
       <c r="B87">
-        <v>0.34</v>
+        <v>27.499</v>
       </c>
       <c r="C87">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -2978,13 +3554,13 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46303.89583333334</v>
+        <v>46304.89583333334</v>
       </c>
       <c r="B88">
-        <v>0.015</v>
+        <v>4.573</v>
       </c>
       <c r="C88">
-        <v>0.944</v>
+        <v>0.101</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3001,13 +3577,13 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46303.90625</v>
+        <v>46304.90625</v>
       </c>
       <c r="B89">
-        <v>0.018</v>
+        <v>2.102</v>
       </c>
       <c r="C89">
-        <v>3.665</v>
+        <v>1.193</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3024,13 +3600,13 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46303.91666666666</v>
+        <v>46304.91666666666</v>
       </c>
       <c r="B90">
-        <v>7.41</v>
+        <v>22.461</v>
       </c>
       <c r="C90">
-        <v>0.993</v>
+        <v>0.49</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3047,10 +3623,10 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46303.92708333334</v>
+        <v>46304.92708333334</v>
       </c>
       <c r="B91">
-        <v>9.519</v>
+        <v>21.287</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -3070,10 +3646,10 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46303.9375</v>
+        <v>46304.9375</v>
       </c>
       <c r="B92">
-        <v>13.437</v>
+        <v>10.753</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -3093,10 +3669,10 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46303.94791666666</v>
+        <v>46304.94791666666</v>
       </c>
       <c r="B93">
-        <v>12.028</v>
+        <v>20.334</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -3116,10 +3692,10 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46303.95833333334</v>
+        <v>46304.95833333334</v>
       </c>
       <c r="B94">
-        <v>14.696</v>
+        <v>48.244</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -3139,16 +3715,16 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46303.96875</v>
+        <v>46304.96875</v>
       </c>
       <c r="B95">
-        <v>5.957</v>
+        <v>50.257</v>
       </c>
       <c r="C95">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -3162,16 +3738,16 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46303.97916666666</v>
+        <v>46304.97916666666</v>
       </c>
       <c r="B96">
-        <v>0.018</v>
+        <v>8.965</v>
       </c>
       <c r="C96">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>52.25</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -3185,16 +3761,16 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46303.98958333334</v>
+        <v>46304.98958333334</v>
       </c>
       <c r="B97">
-        <v>1.126</v>
+        <v>14.323</v>
       </c>
       <c r="C97">
-        <v>0.411</v>
+        <v>0</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>48.25</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -3208,16 +3784,16 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B98">
-        <v>4.293</v>
+        <v>0.43</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>0.543</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -3231,16 +3807,16 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46304.01041666666</v>
+        <v>46305.01041666666</v>
       </c>
       <c r="B99">
-        <v>4.642</v>
+        <v>14.988</v>
       </c>
       <c r="C99">
         <v>0</v>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -3254,16 +3830,16 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46304.02083333334</v>
+        <v>46305.02083333334</v>
       </c>
       <c r="B100">
-        <v>5.413</v>
+        <v>2.684</v>
       </c>
       <c r="C100">
         <v>0</v>
       </c>
       <c r="D100">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -3277,16 +3853,16 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46304.03125</v>
+        <v>46305.03125</v>
       </c>
       <c r="B101">
-        <v>0.698</v>
+        <v>4.356</v>
       </c>
       <c r="C101">
-        <v>1.788</v>
+        <v>0.079</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -3300,16 +3876,16 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46304.04166666666</v>
+        <v>46305.04166666666</v>
       </c>
       <c r="B102">
-        <v>11.905</v>
+        <v>5.82</v>
       </c>
       <c r="C102">
-        <v>0.507</v>
+        <v>0</v>
       </c>
       <c r="D102">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -3323,16 +3899,16 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46304.05208333334</v>
+        <v>46305.05208333334</v>
       </c>
       <c r="B103">
-        <v>4.742</v>
+        <v>0.615</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>0.145</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -3346,13 +3922,13 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46304.0625</v>
+        <v>46305.0625</v>
       </c>
       <c r="B104">
-        <v>25.578</v>
+        <v>5.334</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>0.542</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -3369,13 +3945,13 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46304.07291666666</v>
+        <v>46305.07291666666</v>
       </c>
       <c r="B105">
-        <v>20.903</v>
+        <v>0</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>5.93</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -3392,13 +3968,13 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46304.08333333334</v>
+        <v>46305.08333333334</v>
       </c>
       <c r="B106">
-        <v>11.54</v>
+        <v>0</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>4.553</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -3415,13 +3991,13 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46304.09375</v>
+        <v>46305.09375</v>
       </c>
       <c r="B107">
-        <v>18.361</v>
+        <v>0.011</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>1.126</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -3438,13 +4014,13 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46304.10416666666</v>
+        <v>46305.10416666666</v>
       </c>
       <c r="B108">
-        <v>23.123</v>
+        <v>0.015</v>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>0.679</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -3461,13 +4037,13 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46304.11458333334</v>
+        <v>46305.11458333334</v>
       </c>
       <c r="B109">
-        <v>36.561</v>
+        <v>0.02</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>0.428</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -3484,13 +4060,13 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46304.125</v>
+        <v>46305.125</v>
       </c>
       <c r="B110">
-        <v>49.765</v>
+        <v>1.004</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>0.248</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -3507,16 +4083,16 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46304.13541666666</v>
+        <v>46305.13541666666</v>
       </c>
       <c r="B111">
-        <v>35.578</v>
+        <v>0.784</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>0.307</v>
       </c>
       <c r="D111">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -3530,16 +4106,16 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46304.14583333334</v>
+        <v>46305.14583333334</v>
       </c>
       <c r="B112">
-        <v>23.305</v>
+        <v>5.79</v>
       </c>
       <c r="C112">
         <v>0</v>
       </c>
       <c r="D112">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -3553,16 +4129,16 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46304.15625</v>
+        <v>46305.15625</v>
       </c>
       <c r="B113">
-        <v>43.251</v>
+        <v>13.814</v>
       </c>
       <c r="C113">
         <v>0</v>
       </c>
       <c r="D113">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -3576,16 +4152,16 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46304.16666666666</v>
+        <v>46305.16666666666</v>
       </c>
       <c r="B114">
-        <v>7.688</v>
+        <v>26.69</v>
       </c>
       <c r="C114">
         <v>0</v>
       </c>
       <c r="D114">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -3599,16 +4175,16 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46304.17708333334</v>
+        <v>46305.17708333334</v>
       </c>
       <c r="B115">
-        <v>1.659</v>
+        <v>10.214</v>
       </c>
       <c r="C115">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="D115">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -3622,16 +4198,16 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46304.1875</v>
+        <v>46305.1875</v>
       </c>
       <c r="B116">
-        <v>0.205</v>
+        <v>15.922</v>
       </c>
       <c r="C116">
-        <v>0.06900000000000001</v>
+        <v>0</v>
       </c>
       <c r="D116">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -3645,16 +4221,16 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46304.19791666666</v>
+        <v>46305.19791666666</v>
       </c>
       <c r="B117">
-        <v>1.806</v>
+        <v>1.908</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="D117">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -3668,16 +4244,16 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46304.20833333334</v>
+        <v>46305.20833333334</v>
       </c>
       <c r="B118">
-        <v>14.024</v>
+        <v>0.114</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>0.198</v>
       </c>
       <c r="D118">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -3691,16 +4267,16 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46304.21875</v>
+        <v>46305.21875</v>
       </c>
       <c r="B119">
-        <v>31.426</v>
+        <v>0.142</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>0.225</v>
       </c>
       <c r="D119">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -3714,16 +4290,16 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46304.22916666666</v>
+        <v>46305.22916666666</v>
       </c>
       <c r="B120">
-        <v>10.545</v>
+        <v>0.167</v>
       </c>
       <c r="C120">
-        <v>0.021</v>
+        <v>0.241</v>
       </c>
       <c r="D120">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -3737,16 +4313,16 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46304.23958333334</v>
+        <v>46305.23958333334</v>
       </c>
       <c r="B121">
-        <v>8.079000000000001</v>
+        <v>0.314</v>
       </c>
       <c r="C121">
-        <v>0.027</v>
+        <v>0.173</v>
       </c>
       <c r="D121">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -3760,16 +4336,16 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46304.25</v>
+        <v>46305.25</v>
       </c>
       <c r="B122">
-        <v>4.402</v>
+        <v>0</v>
       </c>
       <c r="C122">
-        <v>1.59</v>
+        <v>7.509</v>
       </c>
       <c r="D122">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -3783,16 +4359,16 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46304.26041666666</v>
+        <v>46305.26041666666</v>
       </c>
       <c r="B123">
-        <v>0.131</v>
+        <v>0</v>
       </c>
       <c r="C123">
-        <v>0.119</v>
+        <v>6.718</v>
       </c>
       <c r="D123">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -3806,19 +4382,19 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46304.27083333334</v>
+        <v>46305.27083333334</v>
       </c>
       <c r="B124">
-        <v>0.215</v>
+        <v>0.073</v>
       </c>
       <c r="C124">
-        <v>0.147</v>
+        <v>1.901</v>
       </c>
       <c r="D124">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E124">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F124">
         <v>27</v>
@@ -3829,19 +4405,19 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46304.28125</v>
+        <v>46305.28125</v>
       </c>
       <c r="B125">
-        <v>3.824</v>
+        <v>0.041</v>
       </c>
       <c r="C125">
-        <v>0.013</v>
+        <v>0.223</v>
       </c>
       <c r="D125">
         <v>0</v>
       </c>
       <c r="E125">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F125">
         <v>28</v>
@@ -3852,19 +4428,19 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46304.29166666666</v>
+        <v>46305.29166666666</v>
       </c>
       <c r="B126">
-        <v>1.694</v>
+        <v>0.772</v>
       </c>
       <c r="C126">
-        <v>0.048</v>
+        <v>0.156</v>
       </c>
       <c r="D126">
         <v>0</v>
       </c>
       <c r="E126">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F126">
         <v>29</v>
@@ -3875,19 +4451,19 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46304.30208333334</v>
+        <v>46305.30208333334</v>
       </c>
       <c r="B127">
-        <v>5.396</v>
+        <v>0.067</v>
       </c>
       <c r="C127">
-        <v>0.01</v>
+        <v>2.942</v>
       </c>
       <c r="D127">
         <v>0</v>
       </c>
       <c r="E127">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F127">
         <v>30</v>
@@ -3898,19 +4474,19 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46304.3125</v>
+        <v>46305.3125</v>
       </c>
       <c r="B128">
-        <v>0.585</v>
+        <v>0.206</v>
       </c>
       <c r="C128">
-        <v>0.233</v>
+        <v>0.502</v>
       </c>
       <c r="D128">
         <v>0</v>
       </c>
       <c r="E128">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F128">
         <v>31</v>
@@ -3921,13 +4497,13 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46304.32291666666</v>
+        <v>46305.32291666666</v>
       </c>
       <c r="B129">
-        <v>3.763</v>
+        <v>0</v>
       </c>
       <c r="C129">
-        <v>0.036</v>
+        <v>15.505</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -3944,19 +4520,19 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46304.33333333334</v>
+        <v>46305.33333333334</v>
       </c>
       <c r="B130">
-        <v>26.973</v>
+        <v>19.998</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="D130">
         <v>0</v>
       </c>
       <c r="E130">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F130">
         <v>33</v>
@@ -3967,10 +4543,10 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46304.34375</v>
+        <v>46305.34375</v>
       </c>
       <c r="B131">
-        <v>26.055</v>
+        <v>33.086</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -3979,7 +4555,7 @@
         <v>0</v>
       </c>
       <c r="E131">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F131">
         <v>34</v>
@@ -3990,16 +4566,16 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46304.35416666666</v>
+        <v>46305.35416666666</v>
       </c>
       <c r="B132">
-        <v>4.45</v>
+        <v>8.103</v>
       </c>
       <c r="C132">
-        <v>1.089</v>
+        <v>0.031</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -4013,16 +4589,16 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46304.36458333334</v>
+        <v>46305.36458333334</v>
       </c>
       <c r="B133">
-        <v>0.414</v>
+        <v>9.221</v>
       </c>
       <c r="C133">
-        <v>7.102</v>
+        <v>0.617</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -4036,16 +4612,16 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46304.375</v>
+        <v>46305.375</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>14.783</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -4059,16 +4635,16 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46304.38541666666</v>
+        <v>46305.38541666666</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>0.103</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -4082,16 +4658,16 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46304.39583333334</v>
+        <v>46305.39583333334</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>7.497</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="D136">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -4105,16 +4681,16 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46304.40625</v>
+        <v>46305.40625</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>2.225</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>3.413</v>
       </c>
       <c r="D137">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -4128,16 +4704,16 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46304.41666666666</v>
+        <v>46305.41666666666</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>2.833</v>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -4151,16 +4727,16 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46304.42708333334</v>
+        <v>46305.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>6.131</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -4174,16 +4750,16 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46304.4375</v>
+        <v>46305.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>17.623</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -4197,16 +4773,16 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46304.44791666666</v>
+        <v>46305.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>38.518</v>
       </c>
       <c r="D141">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -4220,19 +4796,19 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46304.45833333334</v>
+        <v>46305.45833333334</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>7.257</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>8.733000000000001</v>
       </c>
       <c r="D142">
         <v>0</v>
       </c>
       <c r="E142">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F142">
         <v>45</v>
@@ -4243,10 +4819,10 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46304.46875</v>
+        <v>46305.46875</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>15.232</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -4255,7 +4831,7 @@
         <v>0</v>
       </c>
       <c r="E143">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F143">
         <v>46</v>
@@ -4266,10 +4842,10 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46304.47916666666</v>
+        <v>46305.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>10.247</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -4278,7 +4854,7 @@
         <v>0</v>
       </c>
       <c r="E144">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F144">
         <v>47</v>
@@ -4289,16 +4865,16 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46304.48958333334</v>
+        <v>46305.48958333334</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>4.483</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>7.243</v>
       </c>
       <c r="D145">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -4312,16 +4888,16 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46304.5</v>
+        <v>46305.5</v>
       </c>
       <c r="B146">
         <v>0</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>10.027</v>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>27.5</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -4335,13 +4911,13 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46304.51041666666</v>
+        <v>46305.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>14.201</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>0.417</v>
       </c>
       <c r="D147">
         <v>0</v>
@@ -4358,10 +4934,10 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46304.52083333334</v>
+        <v>46305.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>31.926</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -4381,10 +4957,10 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46304.53125</v>
+        <v>46305.53125</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>27.131</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -4404,10 +4980,10 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46304.54166666666</v>
+        <v>46305.54166666666</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>25.335</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -4427,13 +5003,13 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46304.55208333334</v>
+        <v>46305.55208333334</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>4.331</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="D151">
         <v>0</v>
@@ -4450,13 +5026,13 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46304.5625</v>
+        <v>46305.5625</v>
       </c>
       <c r="B152">
-        <v>0</v>
+        <v>0.577</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>0.104</v>
       </c>
       <c r="D152">
         <v>0</v>
@@ -4473,13 +5049,13 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46304.57291666666</v>
+        <v>46305.57291666666</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>0.311</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="D153">
         <v>0</v>
@@ -4496,13 +5072,13 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46304.58333333334</v>
+        <v>46305.58333333334</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>1.774</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="D154">
         <v>0</v>
@@ -4519,13 +5095,13 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46304.59375</v>
+        <v>46305.59375</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>0.627</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>0.319</v>
       </c>
       <c r="D155">
         <v>0</v>
@@ -4542,13 +5118,13 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46304.60416666666</v>
+        <v>46305.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>3.678</v>
       </c>
       <c r="D156">
         <v>0</v>
@@ -4565,13 +5141,13 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46304.61458333334</v>
+        <v>46305.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>8.147</v>
       </c>
       <c r="D157">
         <v>0</v>
@@ -4588,13 +5164,13 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46304.625</v>
+        <v>46305.625</v>
       </c>
       <c r="B158">
         <v>0</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>17.151</v>
       </c>
       <c r="D158">
         <v>0</v>
@@ -4611,13 +5187,13 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46304.63541666666</v>
+        <v>46305.63541666666</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>2.099</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>0.971</v>
       </c>
       <c r="D159">
         <v>0</v>
@@ -4634,10 +5210,10 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46304.64583333334</v>
+        <v>46305.64583333334</v>
       </c>
       <c r="B160">
-        <v>0</v>
+        <v>15.697</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -4657,10 +5233,10 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46304.65625</v>
+        <v>46305.65625</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>31.247</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -4680,10 +5256,10 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46304.66666666666</v>
+        <v>46305.66666666666</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>23.579</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -4703,10 +5279,10 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46304.67708333334</v>
+        <v>46305.67708333334</v>
       </c>
       <c r="B163">
-        <v>0</v>
+        <v>26.333</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -4726,10 +5302,10 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46304.6875</v>
+        <v>46305.6875</v>
       </c>
       <c r="B164">
-        <v>0</v>
+        <v>38.045</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -4749,10 +5325,10 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46304.69791666666</v>
+        <v>46305.69791666666</v>
       </c>
       <c r="B165">
-        <v>0</v>
+        <v>47.656</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -4772,10 +5348,10 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46304.70833333334</v>
+        <v>46305.70833333334</v>
       </c>
       <c r="B166">
-        <v>0</v>
+        <v>44.631</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -4795,10 +5371,10 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46304.71875</v>
+        <v>46305.71875</v>
       </c>
       <c r="B167">
-        <v>0</v>
+        <v>45.292</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -4818,16 +5394,16 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46304.72916666666</v>
+        <v>46305.72916666666</v>
       </c>
       <c r="B168">
-        <v>0</v>
+        <v>10.443</v>
       </c>
       <c r="C168">
         <v>0</v>
       </c>
       <c r="D168">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -4841,16 +5417,16 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46304.73958333334</v>
+        <v>46305.73958333334</v>
       </c>
       <c r="B169">
-        <v>0</v>
+        <v>5.699</v>
       </c>
       <c r="C169">
         <v>0</v>
       </c>
       <c r="D169">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -4864,16 +5440,16 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46304.75</v>
+        <v>46305.75</v>
       </c>
       <c r="B170">
-        <v>0</v>
+        <v>20.904</v>
       </c>
       <c r="C170">
         <v>0</v>
       </c>
       <c r="D170">
-        <v>0</v>
+        <v>47.75</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -4887,16 +5463,16 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46304.76041666666</v>
+        <v>46305.76041666666</v>
       </c>
       <c r="B171">
-        <v>0</v>
+        <v>9.409000000000001</v>
       </c>
       <c r="C171">
         <v>0</v>
       </c>
       <c r="D171">
-        <v>0</v>
+        <v>47.75</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -4910,16 +5486,16 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46304.77083333334</v>
+        <v>46305.77083333334</v>
       </c>
       <c r="B172">
-        <v>0</v>
+        <v>5.454</v>
       </c>
       <c r="C172">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="D172">
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -4933,16 +5509,16 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46304.78125</v>
+        <v>46305.78125</v>
       </c>
       <c r="B173">
-        <v>0</v>
+        <v>4.365</v>
       </c>
       <c r="C173">
         <v>0</v>
       </c>
       <c r="D173">
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -4956,16 +5532,16 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46304.79166666666</v>
+        <v>46305.79166666666</v>
       </c>
       <c r="B174">
-        <v>0</v>
+        <v>2.353</v>
       </c>
       <c r="C174">
-        <v>0</v>
+        <v>4.432</v>
       </c>
       <c r="D174">
-        <v>0</v>
+        <v>46.5</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -4979,16 +5555,16 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46304.80208333334</v>
+        <v>46305.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
       </c>
       <c r="C175">
-        <v>0</v>
+        <v>2.255</v>
       </c>
       <c r="D175">
-        <v>0</v>
+        <v>46.5</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -5002,16 +5578,16 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46304.8125</v>
+        <v>46305.8125</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="C176">
-        <v>0</v>
+        <v>1.312</v>
       </c>
       <c r="D176">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -5025,16 +5601,16 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46304.82291666666</v>
+        <v>46305.82291666666</v>
       </c>
       <c r="B177">
-        <v>0</v>
+        <v>1.321</v>
       </c>
       <c r="C177">
-        <v>0</v>
+        <v>4.364</v>
       </c>
       <c r="D177">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E177">
         <v>0</v>
@@ -5048,13 +5624,13 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46304.83333333334</v>
+        <v>46305.83333333334</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>10.287</v>
       </c>
       <c r="C178">
-        <v>0</v>
+        <v>0.495</v>
       </c>
       <c r="D178">
         <v>0</v>
@@ -5071,10 +5647,10 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46304.84375</v>
+        <v>46305.84375</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>10.953</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -5094,10 +5670,10 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46304.85416666666</v>
+        <v>46305.85416666666</v>
       </c>
       <c r="B180">
-        <v>0</v>
+        <v>11.469</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -5117,10 +5693,10 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46304.86458333334</v>
+        <v>46305.86458333334</v>
       </c>
       <c r="B181">
-        <v>0</v>
+        <v>6.002</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -5140,10 +5716,10 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46304.875</v>
+        <v>46305.875</v>
       </c>
       <c r="B182">
-        <v>0</v>
+        <v>20.007</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -5163,10 +5739,10 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46304.88541666666</v>
+        <v>46305.88541666666</v>
       </c>
       <c r="B183">
-        <v>0</v>
+        <v>13.67</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -5186,10 +5762,10 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46304.89583333334</v>
+        <v>46305.89583333334</v>
       </c>
       <c r="B184">
-        <v>0</v>
+        <v>11.767</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -5209,10 +5785,10 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46304.90625</v>
+        <v>46305.90625</v>
       </c>
       <c r="B185">
-        <v>0</v>
+        <v>7.904</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -5232,10 +5808,10 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46304.91666666666</v>
+        <v>46305.91666666666</v>
       </c>
       <c r="B186">
-        <v>0</v>
+        <v>25.129</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -5255,10 +5831,10 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46304.92708333334</v>
+        <v>46305.92708333334</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>19.956</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -5278,16 +5854,16 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46304.9375</v>
+        <v>46305.9375</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>0.132</v>
       </c>
       <c r="C188">
-        <v>0</v>
+        <v>0.364</v>
       </c>
       <c r="D188">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -5301,16 +5877,16 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46304.94791666666</v>
+        <v>46305.94791666666</v>
       </c>
       <c r="B189">
-        <v>0</v>
+        <v>2.163</v>
       </c>
       <c r="C189">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="D189">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -5324,13 +5900,13 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46304.95833333334</v>
+        <v>46305.95833333334</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>19.203</v>
       </c>
       <c r="C190">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="D190">
         <v>0</v>
@@ -5347,13 +5923,13 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46304.96875</v>
+        <v>46305.96875</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>7.076</v>
       </c>
       <c r="C191">
-        <v>0</v>
+        <v>0.211</v>
       </c>
       <c r="D191">
         <v>0</v>
@@ -5370,10 +5946,10 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46304.97916666666</v>
+        <v>46305.97916666666</v>
       </c>
       <c r="B192">
-        <v>0</v>
+        <v>8.901</v>
       </c>
       <c r="C192">
         <v>0</v>
@@ -5393,13 +5969,13 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46304.98958333334</v>
+        <v>46305.98958333334</v>
       </c>
       <c r="B193">
-        <v>0</v>
+        <v>1.439</v>
       </c>
       <c r="C193">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="D193">
         <v>0</v>
@@ -5412,6 +5988,4422 @@
       </c>
       <c r="G193" t="s">
         <v>198</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7">
+      <c r="A194" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B194">
+        <v>9.718</v>
+      </c>
+      <c r="C194">
+        <v>0</v>
+      </c>
+      <c r="D194">
+        <v>0</v>
+      </c>
+      <c r="E194">
+        <v>0</v>
+      </c>
+      <c r="F194">
+        <v>1</v>
+      </c>
+      <c r="G194" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7">
+      <c r="A195" s="2">
+        <v>46306.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>17.462</v>
+      </c>
+      <c r="C195">
+        <v>0</v>
+      </c>
+      <c r="D195">
+        <v>0</v>
+      </c>
+      <c r="E195">
+        <v>0</v>
+      </c>
+      <c r="F195">
+        <v>2</v>
+      </c>
+      <c r="G195" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7">
+      <c r="A196" s="2">
+        <v>46306.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="C196">
+        <v>0.834</v>
+      </c>
+      <c r="D196">
+        <v>0</v>
+      </c>
+      <c r="E196">
+        <v>0</v>
+      </c>
+      <c r="F196">
+        <v>3</v>
+      </c>
+      <c r="G196" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7">
+      <c r="A197" s="2">
+        <v>46306.03125</v>
+      </c>
+      <c r="B197">
+        <v>6.196</v>
+      </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+      <c r="D197">
+        <v>0</v>
+      </c>
+      <c r="E197">
+        <v>0</v>
+      </c>
+      <c r="F197">
+        <v>4</v>
+      </c>
+      <c r="G197" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7">
+      <c r="A198" s="2">
+        <v>46306.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>6.139</v>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+      <c r="D198">
+        <v>0</v>
+      </c>
+      <c r="E198">
+        <v>0</v>
+      </c>
+      <c r="F198">
+        <v>5</v>
+      </c>
+      <c r="G198" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7">
+      <c r="A199" s="2">
+        <v>46306.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>15.255</v>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+      <c r="D199">
+        <v>0</v>
+      </c>
+      <c r="E199">
+        <v>0</v>
+      </c>
+      <c r="F199">
+        <v>6</v>
+      </c>
+      <c r="G199" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7">
+      <c r="A200" s="2">
+        <v>46306.0625</v>
+      </c>
+      <c r="B200">
+        <v>24.497</v>
+      </c>
+      <c r="C200">
+        <v>0</v>
+      </c>
+      <c r="D200">
+        <v>0</v>
+      </c>
+      <c r="E200">
+        <v>0</v>
+      </c>
+      <c r="F200">
+        <v>7</v>
+      </c>
+      <c r="G200" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7">
+      <c r="A201" s="2">
+        <v>46306.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>0.891</v>
+      </c>
+      <c r="C201">
+        <v>0.262</v>
+      </c>
+      <c r="D201">
+        <v>0</v>
+      </c>
+      <c r="E201">
+        <v>0</v>
+      </c>
+      <c r="F201">
+        <v>8</v>
+      </c>
+      <c r="G201" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7">
+      <c r="A202" s="2">
+        <v>46306.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>2.021</v>
+      </c>
+      <c r="C202">
+        <v>0.002</v>
+      </c>
+      <c r="D202">
+        <v>0</v>
+      </c>
+      <c r="E202">
+        <v>0</v>
+      </c>
+      <c r="F202">
+        <v>9</v>
+      </c>
+      <c r="G202" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7">
+      <c r="A203" s="2">
+        <v>46306.09375</v>
+      </c>
+      <c r="B203">
+        <v>0.345</v>
+      </c>
+      <c r="C203">
+        <v>0.133</v>
+      </c>
+      <c r="D203">
+        <v>0</v>
+      </c>
+      <c r="E203">
+        <v>0</v>
+      </c>
+      <c r="F203">
+        <v>10</v>
+      </c>
+      <c r="G203" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7">
+      <c r="A204" s="2">
+        <v>46306.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>6.18</v>
+      </c>
+      <c r="C204">
+        <v>0</v>
+      </c>
+      <c r="D204">
+        <v>0</v>
+      </c>
+      <c r="E204">
+        <v>0</v>
+      </c>
+      <c r="F204">
+        <v>11</v>
+      </c>
+      <c r="G204" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7">
+      <c r="A205" s="2">
+        <v>46306.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>2.306</v>
+      </c>
+      <c r="C205">
+        <v>0.622</v>
+      </c>
+      <c r="D205">
+        <v>0</v>
+      </c>
+      <c r="E205">
+        <v>0</v>
+      </c>
+      <c r="F205">
+        <v>12</v>
+      </c>
+      <c r="G205" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7">
+      <c r="A206" s="2">
+        <v>46306.125</v>
+      </c>
+      <c r="B206">
+        <v>9.314</v>
+      </c>
+      <c r="C206">
+        <v>0</v>
+      </c>
+      <c r="D206">
+        <v>0</v>
+      </c>
+      <c r="E206">
+        <v>0</v>
+      </c>
+      <c r="F206">
+        <v>13</v>
+      </c>
+      <c r="G206" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7">
+      <c r="A207" s="2">
+        <v>46306.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>3.975</v>
+      </c>
+      <c r="C207">
+        <v>0.078</v>
+      </c>
+      <c r="D207">
+        <v>0</v>
+      </c>
+      <c r="E207">
+        <v>0</v>
+      </c>
+      <c r="F207">
+        <v>14</v>
+      </c>
+      <c r="G207" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7">
+      <c r="A208" s="2">
+        <v>46306.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>0.928</v>
+      </c>
+      <c r="C208">
+        <v>0.201</v>
+      </c>
+      <c r="D208">
+        <v>0</v>
+      </c>
+      <c r="E208">
+        <v>0</v>
+      </c>
+      <c r="F208">
+        <v>15</v>
+      </c>
+      <c r="G208" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7">
+      <c r="A209" s="2">
+        <v>46306.15625</v>
+      </c>
+      <c r="B209">
+        <v>12.163</v>
+      </c>
+      <c r="C209">
+        <v>0.001</v>
+      </c>
+      <c r="D209">
+        <v>0</v>
+      </c>
+      <c r="E209">
+        <v>0</v>
+      </c>
+      <c r="F209">
+        <v>16</v>
+      </c>
+      <c r="G209" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7">
+      <c r="A210" s="2">
+        <v>46306.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>0.033</v>
+      </c>
+      <c r="C210">
+        <v>0.291</v>
+      </c>
+      <c r="D210">
+        <v>25</v>
+      </c>
+      <c r="E210">
+        <v>0</v>
+      </c>
+      <c r="F210">
+        <v>17</v>
+      </c>
+      <c r="G210" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7">
+      <c r="A211" s="2">
+        <v>46306.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>0.15</v>
+      </c>
+      <c r="C211">
+        <v>0.168</v>
+      </c>
+      <c r="D211">
+        <v>25</v>
+      </c>
+      <c r="E211">
+        <v>0</v>
+      </c>
+      <c r="F211">
+        <v>18</v>
+      </c>
+      <c r="G211" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7">
+      <c r="A212" s="2">
+        <v>46306.1875</v>
+      </c>
+      <c r="B212">
+        <v>23.812</v>
+      </c>
+      <c r="C212">
+        <v>0</v>
+      </c>
+      <c r="D212">
+        <v>25</v>
+      </c>
+      <c r="E212">
+        <v>0</v>
+      </c>
+      <c r="F212">
+        <v>19</v>
+      </c>
+      <c r="G212" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7">
+      <c r="A213" s="2">
+        <v>46306.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>13.449</v>
+      </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
+      <c r="D213">
+        <v>25</v>
+      </c>
+      <c r="E213">
+        <v>0</v>
+      </c>
+      <c r="F213">
+        <v>20</v>
+      </c>
+      <c r="G213" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7">
+      <c r="A214" s="2">
+        <v>46306.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>7.691</v>
+      </c>
+      <c r="C214">
+        <v>0</v>
+      </c>
+      <c r="D214">
+        <v>25</v>
+      </c>
+      <c r="E214">
+        <v>0</v>
+      </c>
+      <c r="F214">
+        <v>21</v>
+      </c>
+      <c r="G214" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7">
+      <c r="A215" s="2">
+        <v>46306.21875</v>
+      </c>
+      <c r="B215">
+        <v>0.794</v>
+      </c>
+      <c r="C215">
+        <v>0</v>
+      </c>
+      <c r="D215">
+        <v>25</v>
+      </c>
+      <c r="E215">
+        <v>0</v>
+      </c>
+      <c r="F215">
+        <v>22</v>
+      </c>
+      <c r="G215" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7">
+      <c r="A216" s="2">
+        <v>46306.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>0.841</v>
+      </c>
+      <c r="C216">
+        <v>0.01</v>
+      </c>
+      <c r="D216">
+        <v>25</v>
+      </c>
+      <c r="E216">
+        <v>0</v>
+      </c>
+      <c r="F216">
+        <v>23</v>
+      </c>
+      <c r="G216" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7">
+      <c r="A217" s="2">
+        <v>46306.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>0.413</v>
+      </c>
+      <c r="C217">
+        <v>0.105</v>
+      </c>
+      <c r="D217">
+        <v>25</v>
+      </c>
+      <c r="E217">
+        <v>0</v>
+      </c>
+      <c r="F217">
+        <v>24</v>
+      </c>
+      <c r="G217" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7">
+      <c r="A218" s="2">
+        <v>46306.25</v>
+      </c>
+      <c r="B218">
+        <v>3.636</v>
+      </c>
+      <c r="C218">
+        <v>0</v>
+      </c>
+      <c r="D218">
+        <v>16</v>
+      </c>
+      <c r="E218">
+        <v>0</v>
+      </c>
+      <c r="F218">
+        <v>25</v>
+      </c>
+      <c r="G218" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7">
+      <c r="A219" s="2">
+        <v>46306.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>1.406</v>
+      </c>
+      <c r="C219">
+        <v>0.1</v>
+      </c>
+      <c r="D219">
+        <v>37.5</v>
+      </c>
+      <c r="E219">
+        <v>0</v>
+      </c>
+      <c r="F219">
+        <v>26</v>
+      </c>
+      <c r="G219" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7">
+      <c r="A220" s="2">
+        <v>46306.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>0.128</v>
+      </c>
+      <c r="C220">
+        <v>0.84</v>
+      </c>
+      <c r="D220">
+        <v>62.5</v>
+      </c>
+      <c r="E220">
+        <v>0</v>
+      </c>
+      <c r="F220">
+        <v>27</v>
+      </c>
+      <c r="G220" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7">
+      <c r="A221" s="2">
+        <v>46306.28125</v>
+      </c>
+      <c r="B221">
+        <v>0.233</v>
+      </c>
+      <c r="C221">
+        <v>0.1</v>
+      </c>
+      <c r="D221">
+        <v>62.5</v>
+      </c>
+      <c r="E221">
+        <v>0</v>
+      </c>
+      <c r="F221">
+        <v>28</v>
+      </c>
+      <c r="G221" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7">
+      <c r="A222" s="2">
+        <v>46306.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>0.38</v>
+      </c>
+      <c r="C222">
+        <v>0.147</v>
+      </c>
+      <c r="D222">
+        <v>62.5</v>
+      </c>
+      <c r="E222">
+        <v>0</v>
+      </c>
+      <c r="F222">
+        <v>29</v>
+      </c>
+      <c r="G222" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7">
+      <c r="A223" s="2">
+        <v>46306.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>6.219</v>
+      </c>
+      <c r="C223">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="D223">
+        <v>70.75</v>
+      </c>
+      <c r="E223">
+        <v>0</v>
+      </c>
+      <c r="F223">
+        <v>30</v>
+      </c>
+      <c r="G223" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7">
+      <c r="A224" s="2">
+        <v>46306.3125</v>
+      </c>
+      <c r="B224">
+        <v>0.285</v>
+      </c>
+      <c r="C224">
+        <v>3.989</v>
+      </c>
+      <c r="D224">
+        <v>70.75</v>
+      </c>
+      <c r="E224">
+        <v>0</v>
+      </c>
+      <c r="F224">
+        <v>31</v>
+      </c>
+      <c r="G224" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7">
+      <c r="A225" s="2">
+        <v>46306.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>0.045</v>
+      </c>
+      <c r="C225">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D225">
+        <v>70.75</v>
+      </c>
+      <c r="E225">
+        <v>0</v>
+      </c>
+      <c r="F225">
+        <v>32</v>
+      </c>
+      <c r="G225" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7">
+      <c r="A226" s="2">
+        <v>46306.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>1.426</v>
+      </c>
+      <c r="C226">
+        <v>1.164</v>
+      </c>
+      <c r="D226">
+        <v>75</v>
+      </c>
+      <c r="E226">
+        <v>0</v>
+      </c>
+      <c r="F226">
+        <v>33</v>
+      </c>
+      <c r="G226" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7">
+      <c r="A227" s="2">
+        <v>46306.34375</v>
+      </c>
+      <c r="B227">
+        <v>0</v>
+      </c>
+      <c r="C227">
+        <v>22.256</v>
+      </c>
+      <c r="D227">
+        <v>75</v>
+      </c>
+      <c r="E227">
+        <v>0</v>
+      </c>
+      <c r="F227">
+        <v>34</v>
+      </c>
+      <c r="G227" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7">
+      <c r="A228" s="2">
+        <v>46306.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>0.078</v>
+      </c>
+      <c r="C228">
+        <v>5.825</v>
+      </c>
+      <c r="D228">
+        <v>0</v>
+      </c>
+      <c r="E228">
+        <v>0</v>
+      </c>
+      <c r="F228">
+        <v>35</v>
+      </c>
+      <c r="G228" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7">
+      <c r="A229" s="2">
+        <v>46306.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>5.302</v>
+      </c>
+      <c r="C229">
+        <v>1.022</v>
+      </c>
+      <c r="D229">
+        <v>0</v>
+      </c>
+      <c r="E229">
+        <v>0</v>
+      </c>
+      <c r="F229">
+        <v>36</v>
+      </c>
+      <c r="G229" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7">
+      <c r="A230" s="2">
+        <v>46306.375</v>
+      </c>
+      <c r="B230">
+        <v>10.778</v>
+      </c>
+      <c r="C230">
+        <v>0</v>
+      </c>
+      <c r="D230">
+        <v>0</v>
+      </c>
+      <c r="E230">
+        <v>0</v>
+      </c>
+      <c r="F230">
+        <v>37</v>
+      </c>
+      <c r="G230" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7">
+      <c r="A231" s="2">
+        <v>46306.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>11.03</v>
+      </c>
+      <c r="C231">
+        <v>0.57</v>
+      </c>
+      <c r="D231">
+        <v>0</v>
+      </c>
+      <c r="E231">
+        <v>0</v>
+      </c>
+      <c r="F231">
+        <v>38</v>
+      </c>
+      <c r="G231" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7">
+      <c r="A232" s="2">
+        <v>46306.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>0</v>
+      </c>
+      <c r="C232">
+        <v>5.62</v>
+      </c>
+      <c r="D232">
+        <v>0</v>
+      </c>
+      <c r="E232">
+        <v>0</v>
+      </c>
+      <c r="F232">
+        <v>39</v>
+      </c>
+      <c r="G232" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7">
+      <c r="A233" s="2">
+        <v>46306.40625</v>
+      </c>
+      <c r="B233">
+        <v>0</v>
+      </c>
+      <c r="C233">
+        <v>10.73</v>
+      </c>
+      <c r="D233">
+        <v>0</v>
+      </c>
+      <c r="E233">
+        <v>0</v>
+      </c>
+      <c r="F233">
+        <v>40</v>
+      </c>
+      <c r="G233" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7">
+      <c r="A234" s="2">
+        <v>46306.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>0</v>
+      </c>
+      <c r="C234">
+        <v>20.219</v>
+      </c>
+      <c r="D234">
+        <v>0</v>
+      </c>
+      <c r="E234">
+        <v>0</v>
+      </c>
+      <c r="F234">
+        <v>41</v>
+      </c>
+      <c r="G234" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7">
+      <c r="A235" s="2">
+        <v>46306.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>0</v>
+      </c>
+      <c r="C235">
+        <v>31.925</v>
+      </c>
+      <c r="D235">
+        <v>0</v>
+      </c>
+      <c r="E235">
+        <v>0</v>
+      </c>
+      <c r="F235">
+        <v>42</v>
+      </c>
+      <c r="G235" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7">
+      <c r="A236" s="2">
+        <v>46306.4375</v>
+      </c>
+      <c r="B236">
+        <v>0</v>
+      </c>
+      <c r="C236">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="D236">
+        <v>0</v>
+      </c>
+      <c r="E236">
+        <v>50</v>
+      </c>
+      <c r="F236">
+        <v>43</v>
+      </c>
+      <c r="G236" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7">
+      <c r="A237" s="2">
+        <v>46306.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>0</v>
+      </c>
+      <c r="C237">
+        <v>7.461</v>
+      </c>
+      <c r="D237">
+        <v>0</v>
+      </c>
+      <c r="E237">
+        <v>50</v>
+      </c>
+      <c r="F237">
+        <v>44</v>
+      </c>
+      <c r="G237" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7">
+      <c r="A238" s="2">
+        <v>46306.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>0.023</v>
+      </c>
+      <c r="C238">
+        <v>1.307</v>
+      </c>
+      <c r="D238">
+        <v>0</v>
+      </c>
+      <c r="E238">
+        <v>50</v>
+      </c>
+      <c r="F238">
+        <v>45</v>
+      </c>
+      <c r="G238" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7">
+      <c r="A239" s="2">
+        <v>46306.46875</v>
+      </c>
+      <c r="B239">
+        <v>0.22</v>
+      </c>
+      <c r="C239">
+        <v>0.33</v>
+      </c>
+      <c r="D239">
+        <v>0</v>
+      </c>
+      <c r="E239">
+        <v>50</v>
+      </c>
+      <c r="F239">
+        <v>46</v>
+      </c>
+      <c r="G239" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7">
+      <c r="A240" s="2">
+        <v>46306.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>0.093</v>
+      </c>
+      <c r="C240">
+        <v>1.294</v>
+      </c>
+      <c r="D240">
+        <v>0</v>
+      </c>
+      <c r="E240">
+        <v>37.5</v>
+      </c>
+      <c r="F240">
+        <v>47</v>
+      </c>
+      <c r="G240" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7">
+      <c r="A241" s="2">
+        <v>46306.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>0.166</v>
+      </c>
+      <c r="C241">
+        <v>0.164</v>
+      </c>
+      <c r="D241">
+        <v>0</v>
+      </c>
+      <c r="E241">
+        <v>37.5</v>
+      </c>
+      <c r="F241">
+        <v>48</v>
+      </c>
+      <c r="G241" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7">
+      <c r="A242" s="2">
+        <v>46306.5</v>
+      </c>
+      <c r="B242">
+        <v>4.672</v>
+      </c>
+      <c r="C242">
+        <v>0.031</v>
+      </c>
+      <c r="D242">
+        <v>0</v>
+      </c>
+      <c r="E242">
+        <v>37.5</v>
+      </c>
+      <c r="F242">
+        <v>49</v>
+      </c>
+      <c r="G242" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7">
+      <c r="A243" s="2">
+        <v>46306.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>0.789</v>
+      </c>
+      <c r="C243">
+        <v>0.016</v>
+      </c>
+      <c r="D243">
+        <v>0</v>
+      </c>
+      <c r="E243">
+        <v>25</v>
+      </c>
+      <c r="F243">
+        <v>50</v>
+      </c>
+      <c r="G243" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7">
+      <c r="A244" s="2">
+        <v>46306.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>5.288</v>
+      </c>
+      <c r="C244">
+        <v>0.008</v>
+      </c>
+      <c r="D244">
+        <v>0</v>
+      </c>
+      <c r="E244">
+        <v>12.5</v>
+      </c>
+      <c r="F244">
+        <v>51</v>
+      </c>
+      <c r="G244" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7">
+      <c r="A245" s="2">
+        <v>46306.53125</v>
+      </c>
+      <c r="B245">
+        <v>0.493</v>
+      </c>
+      <c r="C245">
+        <v>0.128</v>
+      </c>
+      <c r="D245">
+        <v>0</v>
+      </c>
+      <c r="E245">
+        <v>12.5</v>
+      </c>
+      <c r="F245">
+        <v>52</v>
+      </c>
+      <c r="G245" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7">
+      <c r="A246" s="2">
+        <v>46306.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>0.532</v>
+      </c>
+      <c r="C246">
+        <v>0.152</v>
+      </c>
+      <c r="D246">
+        <v>0</v>
+      </c>
+      <c r="E246">
+        <v>12.5</v>
+      </c>
+      <c r="F246">
+        <v>53</v>
+      </c>
+      <c r="G246" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7">
+      <c r="A247" s="2">
+        <v>46306.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="C247">
+        <v>2.378</v>
+      </c>
+      <c r="D247">
+        <v>0</v>
+      </c>
+      <c r="E247">
+        <v>12.5</v>
+      </c>
+      <c r="F247">
+        <v>54</v>
+      </c>
+      <c r="G247" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7">
+      <c r="A248" s="2">
+        <v>46306.5625</v>
+      </c>
+      <c r="B248">
+        <v>0.004</v>
+      </c>
+      <c r="C248">
+        <v>1.333</v>
+      </c>
+      <c r="D248">
+        <v>0</v>
+      </c>
+      <c r="E248">
+        <v>12.5</v>
+      </c>
+      <c r="F248">
+        <v>55</v>
+      </c>
+      <c r="G248" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7">
+      <c r="A249" s="2">
+        <v>46306.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>0.185</v>
+      </c>
+      <c r="C249">
+        <v>0.606</v>
+      </c>
+      <c r="D249">
+        <v>0</v>
+      </c>
+      <c r="E249">
+        <v>12.5</v>
+      </c>
+      <c r="F249">
+        <v>56</v>
+      </c>
+      <c r="G249" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7">
+      <c r="A250" s="2">
+        <v>46306.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>6.977</v>
+      </c>
+      <c r="C250">
+        <v>0.054</v>
+      </c>
+      <c r="D250">
+        <v>0</v>
+      </c>
+      <c r="E250">
+        <v>12.5</v>
+      </c>
+      <c r="F250">
+        <v>57</v>
+      </c>
+      <c r="G250" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7">
+      <c r="A251" s="2">
+        <v>46306.59375</v>
+      </c>
+      <c r="B251">
+        <v>29.519</v>
+      </c>
+      <c r="C251">
+        <v>0</v>
+      </c>
+      <c r="D251">
+        <v>0</v>
+      </c>
+      <c r="E251">
+        <v>12.5</v>
+      </c>
+      <c r="F251">
+        <v>58</v>
+      </c>
+      <c r="G251" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7">
+      <c r="A252" s="2">
+        <v>46306.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>46.415</v>
+      </c>
+      <c r="C252">
+        <v>0</v>
+      </c>
+      <c r="D252">
+        <v>0</v>
+      </c>
+      <c r="E252">
+        <v>0</v>
+      </c>
+      <c r="F252">
+        <v>59</v>
+      </c>
+      <c r="G252" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7">
+      <c r="A253" s="2">
+        <v>46306.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>55.427</v>
+      </c>
+      <c r="C253">
+        <v>0</v>
+      </c>
+      <c r="D253">
+        <v>0</v>
+      </c>
+      <c r="E253">
+        <v>0</v>
+      </c>
+      <c r="F253">
+        <v>60</v>
+      </c>
+      <c r="G253" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7">
+      <c r="A254" s="2">
+        <v>46306.625</v>
+      </c>
+      <c r="B254">
+        <v>20.039</v>
+      </c>
+      <c r="C254">
+        <v>0</v>
+      </c>
+      <c r="D254">
+        <v>25</v>
+      </c>
+      <c r="E254">
+        <v>0</v>
+      </c>
+      <c r="F254">
+        <v>61</v>
+      </c>
+      <c r="G254" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7">
+      <c r="A255" s="2">
+        <v>46306.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>32.474</v>
+      </c>
+      <c r="C255">
+        <v>0</v>
+      </c>
+      <c r="D255">
+        <v>37.5</v>
+      </c>
+      <c r="E255">
+        <v>0</v>
+      </c>
+      <c r="F255">
+        <v>62</v>
+      </c>
+      <c r="G255" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7">
+      <c r="A256" s="2">
+        <v>46306.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>37.547</v>
+      </c>
+      <c r="C256">
+        <v>0</v>
+      </c>
+      <c r="D256">
+        <v>50</v>
+      </c>
+      <c r="E256">
+        <v>0</v>
+      </c>
+      <c r="F256">
+        <v>63</v>
+      </c>
+      <c r="G256" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7">
+      <c r="A257" s="2">
+        <v>46306.65625</v>
+      </c>
+      <c r="B257">
+        <v>35.366</v>
+      </c>
+      <c r="C257">
+        <v>0</v>
+      </c>
+      <c r="D257">
+        <v>50</v>
+      </c>
+      <c r="E257">
+        <v>0</v>
+      </c>
+      <c r="F257">
+        <v>64</v>
+      </c>
+      <c r="G257" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7">
+      <c r="A258" s="2">
+        <v>46306.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>1.946</v>
+      </c>
+      <c r="C258">
+        <v>3.72</v>
+      </c>
+      <c r="D258">
+        <v>50</v>
+      </c>
+      <c r="E258">
+        <v>0</v>
+      </c>
+      <c r="F258">
+        <v>65</v>
+      </c>
+      <c r="G258" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7">
+      <c r="A259" s="2">
+        <v>46306.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>0.056</v>
+      </c>
+      <c r="C259">
+        <v>0.727</v>
+      </c>
+      <c r="D259">
+        <v>50</v>
+      </c>
+      <c r="E259">
+        <v>0</v>
+      </c>
+      <c r="F259">
+        <v>66</v>
+      </c>
+      <c r="G259" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7">
+      <c r="A260" s="2">
+        <v>46306.6875</v>
+      </c>
+      <c r="B260">
+        <v>8.686</v>
+      </c>
+      <c r="C260">
+        <v>0.002</v>
+      </c>
+      <c r="D260">
+        <v>27.5</v>
+      </c>
+      <c r="E260">
+        <v>0</v>
+      </c>
+      <c r="F260">
+        <v>67</v>
+      </c>
+      <c r="G260" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7">
+      <c r="A261" s="2">
+        <v>46306.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>1.3</v>
+      </c>
+      <c r="C261">
+        <v>0.166</v>
+      </c>
+      <c r="D261">
+        <v>37.5</v>
+      </c>
+      <c r="E261">
+        <v>0</v>
+      </c>
+      <c r="F261">
+        <v>68</v>
+      </c>
+      <c r="G261" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7">
+      <c r="A262" s="2">
+        <v>46306.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>0</v>
+      </c>
+      <c r="C262">
+        <v>8.041</v>
+      </c>
+      <c r="D262">
+        <v>25</v>
+      </c>
+      <c r="E262">
+        <v>0</v>
+      </c>
+      <c r="F262">
+        <v>69</v>
+      </c>
+      <c r="G262" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7">
+      <c r="A263" s="2">
+        <v>46306.71875</v>
+      </c>
+      <c r="B263">
+        <v>0.065</v>
+      </c>
+      <c r="C263">
+        <v>1.177</v>
+      </c>
+      <c r="D263">
+        <v>25</v>
+      </c>
+      <c r="E263">
+        <v>0</v>
+      </c>
+      <c r="F263">
+        <v>70</v>
+      </c>
+      <c r="G263" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7">
+      <c r="A264" s="2">
+        <v>46306.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>4.354</v>
+      </c>
+      <c r="C264">
+        <v>0.366</v>
+      </c>
+      <c r="D264">
+        <v>0</v>
+      </c>
+      <c r="E264">
+        <v>0</v>
+      </c>
+      <c r="F264">
+        <v>71</v>
+      </c>
+      <c r="G264" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7">
+      <c r="A265" s="2">
+        <v>46306.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>9.888999999999999</v>
+      </c>
+      <c r="C265">
+        <v>0</v>
+      </c>
+      <c r="D265">
+        <v>0</v>
+      </c>
+      <c r="E265">
+        <v>0</v>
+      </c>
+      <c r="F265">
+        <v>72</v>
+      </c>
+      <c r="G265" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7">
+      <c r="A266" s="2">
+        <v>46306.75</v>
+      </c>
+      <c r="B266">
+        <v>5.842</v>
+      </c>
+      <c r="C266">
+        <v>0</v>
+      </c>
+      <c r="D266">
+        <v>0</v>
+      </c>
+      <c r="E266">
+        <v>0</v>
+      </c>
+      <c r="F266">
+        <v>73</v>
+      </c>
+      <c r="G266" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7">
+      <c r="A267" s="2">
+        <v>46306.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>13.057</v>
+      </c>
+      <c r="C267">
+        <v>0</v>
+      </c>
+      <c r="D267">
+        <v>0</v>
+      </c>
+      <c r="E267">
+        <v>0</v>
+      </c>
+      <c r="F267">
+        <v>74</v>
+      </c>
+      <c r="G267" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7">
+      <c r="A268" s="2">
+        <v>46306.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>4.5</v>
+      </c>
+      <c r="C268">
+        <v>0.003</v>
+      </c>
+      <c r="D268">
+        <v>0</v>
+      </c>
+      <c r="E268">
+        <v>0</v>
+      </c>
+      <c r="F268">
+        <v>75</v>
+      </c>
+      <c r="G268" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7">
+      <c r="A269" s="2">
+        <v>46306.78125</v>
+      </c>
+      <c r="B269">
+        <v>0.918</v>
+      </c>
+      <c r="C269">
+        <v>1.875</v>
+      </c>
+      <c r="D269">
+        <v>0</v>
+      </c>
+      <c r="E269">
+        <v>0</v>
+      </c>
+      <c r="F269">
+        <v>76</v>
+      </c>
+      <c r="G269" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7">
+      <c r="A270" s="2">
+        <v>46306.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>23.276</v>
+      </c>
+      <c r="C270">
+        <v>0</v>
+      </c>
+      <c r="D270">
+        <v>0</v>
+      </c>
+      <c r="E270">
+        <v>0</v>
+      </c>
+      <c r="F270">
+        <v>77</v>
+      </c>
+      <c r="G270" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7">
+      <c r="A271" s="2">
+        <v>46306.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>0.315</v>
+      </c>
+      <c r="C271">
+        <v>0.222</v>
+      </c>
+      <c r="D271">
+        <v>0</v>
+      </c>
+      <c r="E271">
+        <v>0</v>
+      </c>
+      <c r="F271">
+        <v>78</v>
+      </c>
+      <c r="G271" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7">
+      <c r="A272" s="2">
+        <v>46306.8125</v>
+      </c>
+      <c r="B272">
+        <v>0.154</v>
+      </c>
+      <c r="C272">
+        <v>0.061</v>
+      </c>
+      <c r="D272">
+        <v>0</v>
+      </c>
+      <c r="E272">
+        <v>0</v>
+      </c>
+      <c r="F272">
+        <v>79</v>
+      </c>
+      <c r="G272" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7">
+      <c r="A273" s="2">
+        <v>46306.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>0.135</v>
+      </c>
+      <c r="C273">
+        <v>4.489</v>
+      </c>
+      <c r="D273">
+        <v>0</v>
+      </c>
+      <c r="E273">
+        <v>0</v>
+      </c>
+      <c r="F273">
+        <v>80</v>
+      </c>
+      <c r="G273" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7">
+      <c r="A274" s="2">
+        <v>46306.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>0</v>
+      </c>
+      <c r="C274">
+        <v>9.701000000000001</v>
+      </c>
+      <c r="D274">
+        <v>0</v>
+      </c>
+      <c r="E274">
+        <v>0</v>
+      </c>
+      <c r="F274">
+        <v>81</v>
+      </c>
+      <c r="G274" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7">
+      <c r="A275" s="2">
+        <v>46306.84375</v>
+      </c>
+      <c r="B275">
+        <v>0</v>
+      </c>
+      <c r="C275">
+        <v>16.453</v>
+      </c>
+      <c r="D275">
+        <v>0</v>
+      </c>
+      <c r="E275">
+        <v>0</v>
+      </c>
+      <c r="F275">
+        <v>82</v>
+      </c>
+      <c r="G275" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7">
+      <c r="A276" s="2">
+        <v>46306.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>0</v>
+      </c>
+      <c r="C276">
+        <v>15.019</v>
+      </c>
+      <c r="D276">
+        <v>0</v>
+      </c>
+      <c r="E276">
+        <v>0</v>
+      </c>
+      <c r="F276">
+        <v>83</v>
+      </c>
+      <c r="G276" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7">
+      <c r="A277" s="2">
+        <v>46306.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>0</v>
+      </c>
+      <c r="C277">
+        <v>6.263</v>
+      </c>
+      <c r="D277">
+        <v>0</v>
+      </c>
+      <c r="E277">
+        <v>0</v>
+      </c>
+      <c r="F277">
+        <v>84</v>
+      </c>
+      <c r="G277" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7">
+      <c r="A278" s="2">
+        <v>46306.875</v>
+      </c>
+      <c r="B278">
+        <v>0</v>
+      </c>
+      <c r="C278">
+        <v>4.234</v>
+      </c>
+      <c r="D278">
+        <v>0</v>
+      </c>
+      <c r="E278">
+        <v>0</v>
+      </c>
+      <c r="F278">
+        <v>85</v>
+      </c>
+      <c r="G278" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7">
+      <c r="A279" s="2">
+        <v>46306.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>0</v>
+      </c>
+      <c r="C279">
+        <v>3.444</v>
+      </c>
+      <c r="D279">
+        <v>0</v>
+      </c>
+      <c r="E279">
+        <v>0</v>
+      </c>
+      <c r="F279">
+        <v>86</v>
+      </c>
+      <c r="G279" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
+      <c r="A280" s="2">
+        <v>46306.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>0</v>
+      </c>
+      <c r="C280">
+        <v>7.719</v>
+      </c>
+      <c r="D280">
+        <v>0</v>
+      </c>
+      <c r="E280">
+        <v>0</v>
+      </c>
+      <c r="F280">
+        <v>87</v>
+      </c>
+      <c r="G280" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7">
+      <c r="A281" s="2">
+        <v>46306.90625</v>
+      </c>
+      <c r="B281">
+        <v>0</v>
+      </c>
+      <c r="C281">
+        <v>11.453</v>
+      </c>
+      <c r="D281">
+        <v>0</v>
+      </c>
+      <c r="E281">
+        <v>0</v>
+      </c>
+      <c r="F281">
+        <v>88</v>
+      </c>
+      <c r="G281" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7">
+      <c r="A282" s="2">
+        <v>46306.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>0.006</v>
+      </c>
+      <c r="C282">
+        <v>6.982</v>
+      </c>
+      <c r="D282">
+        <v>0</v>
+      </c>
+      <c r="E282">
+        <v>0</v>
+      </c>
+      <c r="F282">
+        <v>89</v>
+      </c>
+      <c r="G282" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7">
+      <c r="A283" s="2">
+        <v>46306.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>0</v>
+      </c>
+      <c r="C283">
+        <v>6.294</v>
+      </c>
+      <c r="D283">
+        <v>0</v>
+      </c>
+      <c r="E283">
+        <v>0</v>
+      </c>
+      <c r="F283">
+        <v>90</v>
+      </c>
+      <c r="G283" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
+      <c r="A284" s="2">
+        <v>46306.9375</v>
+      </c>
+      <c r="B284">
+        <v>0</v>
+      </c>
+      <c r="C284">
+        <v>5.267</v>
+      </c>
+      <c r="D284">
+        <v>0</v>
+      </c>
+      <c r="E284">
+        <v>0</v>
+      </c>
+      <c r="F284">
+        <v>91</v>
+      </c>
+      <c r="G284" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7">
+      <c r="A285" s="2">
+        <v>46306.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>0.002</v>
+      </c>
+      <c r="C285">
+        <v>3.479</v>
+      </c>
+      <c r="D285">
+        <v>0</v>
+      </c>
+      <c r="E285">
+        <v>0</v>
+      </c>
+      <c r="F285">
+        <v>92</v>
+      </c>
+      <c r="G285" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7">
+      <c r="A286" s="2">
+        <v>46306.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>8.505000000000001</v>
+      </c>
+      <c r="C286">
+        <v>1.614</v>
+      </c>
+      <c r="D286">
+        <v>0</v>
+      </c>
+      <c r="E286">
+        <v>0</v>
+      </c>
+      <c r="F286">
+        <v>93</v>
+      </c>
+      <c r="G286" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7">
+      <c r="A287" s="2">
+        <v>46306.96875</v>
+      </c>
+      <c r="B287">
+        <v>2.033</v>
+      </c>
+      <c r="C287">
+        <v>0</v>
+      </c>
+      <c r="D287">
+        <v>0</v>
+      </c>
+      <c r="E287">
+        <v>0</v>
+      </c>
+      <c r="F287">
+        <v>94</v>
+      </c>
+      <c r="G287" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7">
+      <c r="A288" s="2">
+        <v>46306.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>18.403</v>
+      </c>
+      <c r="C288">
+        <v>0</v>
+      </c>
+      <c r="D288">
+        <v>0</v>
+      </c>
+      <c r="E288">
+        <v>0</v>
+      </c>
+      <c r="F288">
+        <v>95</v>
+      </c>
+      <c r="G288" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7">
+      <c r="A289" s="2">
+        <v>46306.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>24.5</v>
+      </c>
+      <c r="C289">
+        <v>0</v>
+      </c>
+      <c r="D289">
+        <v>0</v>
+      </c>
+      <c r="E289">
+        <v>0</v>
+      </c>
+      <c r="F289">
+        <v>96</v>
+      </c>
+      <c r="G289" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7">
+      <c r="A290" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B290">
+        <v>7.62</v>
+      </c>
+      <c r="C290">
+        <v>0</v>
+      </c>
+      <c r="D290">
+        <v>0</v>
+      </c>
+      <c r="E290">
+        <v>0</v>
+      </c>
+      <c r="F290">
+        <v>1</v>
+      </c>
+      <c r="G290" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7">
+      <c r="A291" s="2">
+        <v>46307.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>9.08</v>
+      </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
+      <c r="D291">
+        <v>0</v>
+      </c>
+      <c r="E291">
+        <v>0</v>
+      </c>
+      <c r="F291">
+        <v>2</v>
+      </c>
+      <c r="G291" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7">
+      <c r="A292" s="2">
+        <v>46307.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>2.372</v>
+      </c>
+      <c r="C292">
+        <v>0.04</v>
+      </c>
+      <c r="D292">
+        <v>18</v>
+      </c>
+      <c r="E292">
+        <v>0</v>
+      </c>
+      <c r="F292">
+        <v>3</v>
+      </c>
+      <c r="G292" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7">
+      <c r="A293" s="2">
+        <v>46307.03125</v>
+      </c>
+      <c r="B293">
+        <v>1.259</v>
+      </c>
+      <c r="C293">
+        <v>0.378</v>
+      </c>
+      <c r="D293">
+        <v>18</v>
+      </c>
+      <c r="E293">
+        <v>0</v>
+      </c>
+      <c r="F293">
+        <v>4</v>
+      </c>
+      <c r="G293" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7">
+      <c r="A294" s="2">
+        <v>46307.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>0.059</v>
+      </c>
+      <c r="C294">
+        <v>0.165</v>
+      </c>
+      <c r="D294">
+        <v>24</v>
+      </c>
+      <c r="E294">
+        <v>0</v>
+      </c>
+      <c r="F294">
+        <v>5</v>
+      </c>
+      <c r="G294" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7">
+      <c r="A295" s="2">
+        <v>46307.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>0.237</v>
+      </c>
+      <c r="C295">
+        <v>0.224</v>
+      </c>
+      <c r="D295">
+        <v>0</v>
+      </c>
+      <c r="E295">
+        <v>0</v>
+      </c>
+      <c r="F295">
+        <v>6</v>
+      </c>
+      <c r="G295" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7">
+      <c r="A296" s="2">
+        <v>46307.0625</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+      <c r="C296">
+        <v>1.174</v>
+      </c>
+      <c r="D296">
+        <v>25</v>
+      </c>
+      <c r="E296">
+        <v>0</v>
+      </c>
+      <c r="F296">
+        <v>7</v>
+      </c>
+      <c r="G296" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7">
+      <c r="A297" s="2">
+        <v>46307.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>0.019</v>
+      </c>
+      <c r="C297">
+        <v>2.007</v>
+      </c>
+      <c r="D297">
+        <v>0</v>
+      </c>
+      <c r="E297">
+        <v>0</v>
+      </c>
+      <c r="F297">
+        <v>8</v>
+      </c>
+      <c r="G297" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7">
+      <c r="A298" s="2">
+        <v>46307.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>0</v>
+      </c>
+      <c r="C298">
+        <v>8.609</v>
+      </c>
+      <c r="D298">
+        <v>0</v>
+      </c>
+      <c r="E298">
+        <v>0</v>
+      </c>
+      <c r="F298">
+        <v>9</v>
+      </c>
+      <c r="G298" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7">
+      <c r="A299" s="2">
+        <v>46307.09375</v>
+      </c>
+      <c r="B299">
+        <v>0</v>
+      </c>
+      <c r="C299">
+        <v>28.727</v>
+      </c>
+      <c r="D299">
+        <v>0</v>
+      </c>
+      <c r="E299">
+        <v>0</v>
+      </c>
+      <c r="F299">
+        <v>10</v>
+      </c>
+      <c r="G299" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7">
+      <c r="A300" s="2">
+        <v>46307.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>0</v>
+      </c>
+      <c r="C300">
+        <v>21.553</v>
+      </c>
+      <c r="D300">
+        <v>0</v>
+      </c>
+      <c r="E300">
+        <v>0</v>
+      </c>
+      <c r="F300">
+        <v>11</v>
+      </c>
+      <c r="G300" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7">
+      <c r="A301" s="2">
+        <v>46307.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>0</v>
+      </c>
+      <c r="C301">
+        <v>10.111</v>
+      </c>
+      <c r="D301">
+        <v>0</v>
+      </c>
+      <c r="E301">
+        <v>37.5</v>
+      </c>
+      <c r="F301">
+        <v>12</v>
+      </c>
+      <c r="G301" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7">
+      <c r="A302" s="2">
+        <v>46307.125</v>
+      </c>
+      <c r="B302">
+        <v>0</v>
+      </c>
+      <c r="C302">
+        <v>6.978</v>
+      </c>
+      <c r="D302">
+        <v>0</v>
+      </c>
+      <c r="E302">
+        <v>37.5</v>
+      </c>
+      <c r="F302">
+        <v>13</v>
+      </c>
+      <c r="G302" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7">
+      <c r="A303" s="2">
+        <v>46307.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>0</v>
+      </c>
+      <c r="C303">
+        <v>31.267</v>
+      </c>
+      <c r="D303">
+        <v>0</v>
+      </c>
+      <c r="E303">
+        <v>37.5</v>
+      </c>
+      <c r="F303">
+        <v>14</v>
+      </c>
+      <c r="G303" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7">
+      <c r="A304" s="2">
+        <v>46307.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>0</v>
+      </c>
+      <c r="C304">
+        <v>70.099</v>
+      </c>
+      <c r="D304">
+        <v>0</v>
+      </c>
+      <c r="E304">
+        <v>37.5</v>
+      </c>
+      <c r="F304">
+        <v>15</v>
+      </c>
+      <c r="G304" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7">
+      <c r="A305" s="2">
+        <v>46307.15625</v>
+      </c>
+      <c r="B305">
+        <v>0</v>
+      </c>
+      <c r="C305">
+        <v>68.53700000000001</v>
+      </c>
+      <c r="D305">
+        <v>0</v>
+      </c>
+      <c r="E305">
+        <v>57</v>
+      </c>
+      <c r="F305">
+        <v>16</v>
+      </c>
+      <c r="G305" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7">
+      <c r="A306" s="2">
+        <v>46307.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>0</v>
+      </c>
+      <c r="C306">
+        <v>56.24</v>
+      </c>
+      <c r="D306">
+        <v>0</v>
+      </c>
+      <c r="E306">
+        <v>87.5</v>
+      </c>
+      <c r="F306">
+        <v>17</v>
+      </c>
+      <c r="G306" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7">
+      <c r="A307" s="2">
+        <v>46307.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>0</v>
+      </c>
+      <c r="C307">
+        <v>19.813</v>
+      </c>
+      <c r="D307">
+        <v>0</v>
+      </c>
+      <c r="E307">
+        <v>137.5</v>
+      </c>
+      <c r="F307">
+        <v>18</v>
+      </c>
+      <c r="G307" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7">
+      <c r="A308" s="2">
+        <v>46307.1875</v>
+      </c>
+      <c r="B308">
+        <v>3.067</v>
+      </c>
+      <c r="C308">
+        <v>0.041</v>
+      </c>
+      <c r="D308">
+        <v>0</v>
+      </c>
+      <c r="E308">
+        <v>125</v>
+      </c>
+      <c r="F308">
+        <v>19</v>
+      </c>
+      <c r="G308" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7">
+      <c r="A309" s="2">
+        <v>46307.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>22.407</v>
+      </c>
+      <c r="C309">
+        <v>0</v>
+      </c>
+      <c r="D309">
+        <v>0</v>
+      </c>
+      <c r="E309">
+        <v>137.5</v>
+      </c>
+      <c r="F309">
+        <v>20</v>
+      </c>
+      <c r="G309" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7">
+      <c r="A310" s="2">
+        <v>46307.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>3.716</v>
+      </c>
+      <c r="C310">
+        <v>3.599</v>
+      </c>
+      <c r="D310">
+        <v>0</v>
+      </c>
+      <c r="E310">
+        <v>125</v>
+      </c>
+      <c r="F310">
+        <v>21</v>
+      </c>
+      <c r="G310" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7">
+      <c r="A311" s="2">
+        <v>46307.21875</v>
+      </c>
+      <c r="B311">
+        <v>0.004</v>
+      </c>
+      <c r="C311">
+        <v>2.206</v>
+      </c>
+      <c r="D311">
+        <v>0</v>
+      </c>
+      <c r="E311">
+        <v>137.5</v>
+      </c>
+      <c r="F311">
+        <v>22</v>
+      </c>
+      <c r="G311" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7">
+      <c r="A312" s="2">
+        <v>46307.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>4.736</v>
+      </c>
+      <c r="C312">
+        <v>0</v>
+      </c>
+      <c r="D312">
+        <v>0</v>
+      </c>
+      <c r="E312">
+        <v>137.5</v>
+      </c>
+      <c r="F312">
+        <v>23</v>
+      </c>
+      <c r="G312" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7">
+      <c r="A313" s="2">
+        <v>46307.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>33.556</v>
+      </c>
+      <c r="C313">
+        <v>0</v>
+      </c>
+      <c r="D313">
+        <v>0</v>
+      </c>
+      <c r="E313">
+        <v>137.5</v>
+      </c>
+      <c r="F313">
+        <v>24</v>
+      </c>
+      <c r="G313" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7">
+      <c r="A314" s="2">
+        <v>46307.25</v>
+      </c>
+      <c r="B314">
+        <v>48.253</v>
+      </c>
+      <c r="C314">
+        <v>0</v>
+      </c>
+      <c r="D314">
+        <v>0</v>
+      </c>
+      <c r="E314">
+        <v>125</v>
+      </c>
+      <c r="F314">
+        <v>25</v>
+      </c>
+      <c r="G314" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7">
+      <c r="A315" s="2">
+        <v>46307.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>69.78700000000001</v>
+      </c>
+      <c r="C315">
+        <v>0</v>
+      </c>
+      <c r="D315">
+        <v>0</v>
+      </c>
+      <c r="E315">
+        <v>75</v>
+      </c>
+      <c r="F315">
+        <v>26</v>
+      </c>
+      <c r="G315" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7">
+      <c r="A316" s="2">
+        <v>46307.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>61.25</v>
+      </c>
+      <c r="C316">
+        <v>0</v>
+      </c>
+      <c r="D316">
+        <v>0</v>
+      </c>
+      <c r="E316">
+        <v>25</v>
+      </c>
+      <c r="F316">
+        <v>27</v>
+      </c>
+      <c r="G316" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7">
+      <c r="A317" s="2">
+        <v>46307.28125</v>
+      </c>
+      <c r="B317">
+        <v>59.678</v>
+      </c>
+      <c r="C317">
+        <v>0</v>
+      </c>
+      <c r="D317">
+        <v>0</v>
+      </c>
+      <c r="E317">
+        <v>0</v>
+      </c>
+      <c r="F317">
+        <v>28</v>
+      </c>
+      <c r="G317" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7">
+      <c r="A318" s="2">
+        <v>46307.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>52.252</v>
+      </c>
+      <c r="C318">
+        <v>0</v>
+      </c>
+      <c r="D318">
+        <v>25</v>
+      </c>
+      <c r="E318">
+        <v>0</v>
+      </c>
+      <c r="F318">
+        <v>29</v>
+      </c>
+      <c r="G318" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7">
+      <c r="A319" s="2">
+        <v>46307.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>87.75</v>
+      </c>
+      <c r="C319">
+        <v>0</v>
+      </c>
+      <c r="D319">
+        <v>39.25</v>
+      </c>
+      <c r="E319">
+        <v>0</v>
+      </c>
+      <c r="F319">
+        <v>30</v>
+      </c>
+      <c r="G319" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7">
+      <c r="A320" s="2">
+        <v>46307.3125</v>
+      </c>
+      <c r="B320">
+        <v>22.198</v>
+      </c>
+      <c r="C320">
+        <v>0</v>
+      </c>
+      <c r="D320">
+        <v>120.25</v>
+      </c>
+      <c r="E320">
+        <v>0</v>
+      </c>
+      <c r="F320">
+        <v>31</v>
+      </c>
+      <c r="G320" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7">
+      <c r="A321" s="2">
+        <v>46307.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>8.118</v>
+      </c>
+      <c r="C321">
+        <v>0.193</v>
+      </c>
+      <c r="D321">
+        <v>120.25</v>
+      </c>
+      <c r="E321">
+        <v>0</v>
+      </c>
+      <c r="F321">
+        <v>32</v>
+      </c>
+      <c r="G321" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7">
+      <c r="A322" s="2">
+        <v>46307.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>0.397</v>
+      </c>
+      <c r="C322">
+        <v>0.392</v>
+      </c>
+      <c r="D322">
+        <v>127.75</v>
+      </c>
+      <c r="E322">
+        <v>0</v>
+      </c>
+      <c r="F322">
+        <v>33</v>
+      </c>
+      <c r="G322" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7">
+      <c r="A323" s="2">
+        <v>46307.34375</v>
+      </c>
+      <c r="B323">
+        <v>0.432</v>
+      </c>
+      <c r="C323">
+        <v>0.225</v>
+      </c>
+      <c r="D323">
+        <v>112.75</v>
+      </c>
+      <c r="E323">
+        <v>0</v>
+      </c>
+      <c r="F323">
+        <v>34</v>
+      </c>
+      <c r="G323" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7">
+      <c r="A324" s="2">
+        <v>46307.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>1.178</v>
+      </c>
+      <c r="C324">
+        <v>0.03</v>
+      </c>
+      <c r="D324">
+        <v>87.5</v>
+      </c>
+      <c r="E324">
+        <v>0</v>
+      </c>
+      <c r="F324">
+        <v>35</v>
+      </c>
+      <c r="G324" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7">
+      <c r="A325" s="2">
+        <v>46307.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>0.113</v>
+      </c>
+      <c r="C325">
+        <v>0.231</v>
+      </c>
+      <c r="D325">
+        <v>87.5</v>
+      </c>
+      <c r="E325">
+        <v>0</v>
+      </c>
+      <c r="F325">
+        <v>36</v>
+      </c>
+      <c r="G325" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7">
+      <c r="A326" s="2">
+        <v>46307.375</v>
+      </c>
+      <c r="B326">
+        <v>1.014</v>
+      </c>
+      <c r="C326">
+        <v>0</v>
+      </c>
+      <c r="D326">
+        <v>49</v>
+      </c>
+      <c r="E326">
+        <v>0</v>
+      </c>
+      <c r="F326">
+        <v>37</v>
+      </c>
+      <c r="G326" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7">
+      <c r="A327" s="2">
+        <v>46307.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>6.084</v>
+      </c>
+      <c r="C327">
+        <v>0</v>
+      </c>
+      <c r="D327">
+        <v>25</v>
+      </c>
+      <c r="E327">
+        <v>0</v>
+      </c>
+      <c r="F327">
+        <v>38</v>
+      </c>
+      <c r="G327" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7">
+      <c r="A328" s="2">
+        <v>46307.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>0</v>
+      </c>
+      <c r="C328">
+        <v>0</v>
+      </c>
+      <c r="D328">
+        <v>25</v>
+      </c>
+      <c r="E328">
+        <v>0</v>
+      </c>
+      <c r="F328">
+        <v>39</v>
+      </c>
+      <c r="G328" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7">
+      <c r="A329" s="2">
+        <v>46307.40625</v>
+      </c>
+      <c r="B329">
+        <v>0</v>
+      </c>
+      <c r="C329">
+        <v>0</v>
+      </c>
+      <c r="D329">
+        <v>25</v>
+      </c>
+      <c r="E329">
+        <v>0</v>
+      </c>
+      <c r="F329">
+        <v>40</v>
+      </c>
+      <c r="G329" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7">
+      <c r="A330" s="2">
+        <v>46307.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>0</v>
+      </c>
+      <c r="C330">
+        <v>0</v>
+      </c>
+      <c r="D330">
+        <v>0</v>
+      </c>
+      <c r="E330">
+        <v>0</v>
+      </c>
+      <c r="F330">
+        <v>41</v>
+      </c>
+      <c r="G330" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7">
+      <c r="A331" s="2">
+        <v>46307.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>0</v>
+      </c>
+      <c r="C331">
+        <v>0</v>
+      </c>
+      <c r="D331">
+        <v>0</v>
+      </c>
+      <c r="E331">
+        <v>0</v>
+      </c>
+      <c r="F331">
+        <v>42</v>
+      </c>
+      <c r="G331" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7">
+      <c r="A332" s="2">
+        <v>46307.4375</v>
+      </c>
+      <c r="B332">
+        <v>0</v>
+      </c>
+      <c r="C332">
+        <v>0</v>
+      </c>
+      <c r="D332">
+        <v>0</v>
+      </c>
+      <c r="E332">
+        <v>0</v>
+      </c>
+      <c r="F332">
+        <v>43</v>
+      </c>
+      <c r="G332" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7">
+      <c r="A333" s="2">
+        <v>46307.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>0</v>
+      </c>
+      <c r="C333">
+        <v>0</v>
+      </c>
+      <c r="D333">
+        <v>0</v>
+      </c>
+      <c r="E333">
+        <v>0</v>
+      </c>
+      <c r="F333">
+        <v>44</v>
+      </c>
+      <c r="G333" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7">
+      <c r="A334" s="2">
+        <v>46307.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>0</v>
+      </c>
+      <c r="C334">
+        <v>0</v>
+      </c>
+      <c r="D334">
+        <v>0</v>
+      </c>
+      <c r="E334">
+        <v>0</v>
+      </c>
+      <c r="F334">
+        <v>45</v>
+      </c>
+      <c r="G334" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7">
+      <c r="A335" s="2">
+        <v>46307.46875</v>
+      </c>
+      <c r="B335">
+        <v>0</v>
+      </c>
+      <c r="C335">
+        <v>0</v>
+      </c>
+      <c r="D335">
+        <v>0</v>
+      </c>
+      <c r="E335">
+        <v>0</v>
+      </c>
+      <c r="F335">
+        <v>46</v>
+      </c>
+      <c r="G335" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7">
+      <c r="A336" s="2">
+        <v>46307.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>0</v>
+      </c>
+      <c r="C336">
+        <v>0</v>
+      </c>
+      <c r="D336">
+        <v>0</v>
+      </c>
+      <c r="E336">
+        <v>0</v>
+      </c>
+      <c r="F336">
+        <v>47</v>
+      </c>
+      <c r="G336" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7">
+      <c r="A337" s="2">
+        <v>46307.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>0</v>
+      </c>
+      <c r="C337">
+        <v>0</v>
+      </c>
+      <c r="D337">
+        <v>0</v>
+      </c>
+      <c r="E337">
+        <v>0</v>
+      </c>
+      <c r="F337">
+        <v>48</v>
+      </c>
+      <c r="G337" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7">
+      <c r="A338" s="2">
+        <v>46307.5</v>
+      </c>
+      <c r="B338">
+        <v>0</v>
+      </c>
+      <c r="C338">
+        <v>0</v>
+      </c>
+      <c r="D338">
+        <v>0</v>
+      </c>
+      <c r="E338">
+        <v>0</v>
+      </c>
+      <c r="F338">
+        <v>49</v>
+      </c>
+      <c r="G338" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7">
+      <c r="A339" s="2">
+        <v>46307.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>0</v>
+      </c>
+      <c r="C339">
+        <v>0</v>
+      </c>
+      <c r="D339">
+        <v>0</v>
+      </c>
+      <c r="E339">
+        <v>0</v>
+      </c>
+      <c r="F339">
+        <v>50</v>
+      </c>
+      <c r="G339" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7">
+      <c r="A340" s="2">
+        <v>46307.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>0</v>
+      </c>
+      <c r="C340">
+        <v>0</v>
+      </c>
+      <c r="D340">
+        <v>0</v>
+      </c>
+      <c r="E340">
+        <v>0</v>
+      </c>
+      <c r="F340">
+        <v>51</v>
+      </c>
+      <c r="G340" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7">
+      <c r="A341" s="2">
+        <v>46307.53125</v>
+      </c>
+      <c r="B341">
+        <v>0</v>
+      </c>
+      <c r="C341">
+        <v>0</v>
+      </c>
+      <c r="D341">
+        <v>0</v>
+      </c>
+      <c r="E341">
+        <v>0</v>
+      </c>
+      <c r="F341">
+        <v>52</v>
+      </c>
+      <c r="G341" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7">
+      <c r="A342" s="2">
+        <v>46307.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>0</v>
+      </c>
+      <c r="C342">
+        <v>0</v>
+      </c>
+      <c r="D342">
+        <v>0</v>
+      </c>
+      <c r="E342">
+        <v>0</v>
+      </c>
+      <c r="F342">
+        <v>53</v>
+      </c>
+      <c r="G342" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7">
+      <c r="A343" s="2">
+        <v>46307.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>0</v>
+      </c>
+      <c r="C343">
+        <v>0</v>
+      </c>
+      <c r="D343">
+        <v>0</v>
+      </c>
+      <c r="E343">
+        <v>0</v>
+      </c>
+      <c r="F343">
+        <v>54</v>
+      </c>
+      <c r="G343" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="344" spans="1:7">
+      <c r="A344" s="2">
+        <v>46307.5625</v>
+      </c>
+      <c r="B344">
+        <v>0</v>
+      </c>
+      <c r="C344">
+        <v>0</v>
+      </c>
+      <c r="D344">
+        <v>0</v>
+      </c>
+      <c r="E344">
+        <v>0</v>
+      </c>
+      <c r="F344">
+        <v>55</v>
+      </c>
+      <c r="G344" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7">
+      <c r="A345" s="2">
+        <v>46307.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>0</v>
+      </c>
+      <c r="C345">
+        <v>0</v>
+      </c>
+      <c r="D345">
+        <v>0</v>
+      </c>
+      <c r="E345">
+        <v>0</v>
+      </c>
+      <c r="F345">
+        <v>56</v>
+      </c>
+      <c r="G345" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7">
+      <c r="A346" s="2">
+        <v>46307.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>0</v>
+      </c>
+      <c r="C346">
+        <v>0</v>
+      </c>
+      <c r="D346">
+        <v>0</v>
+      </c>
+      <c r="E346">
+        <v>0</v>
+      </c>
+      <c r="F346">
+        <v>57</v>
+      </c>
+      <c r="G346" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="347" spans="1:7">
+      <c r="A347" s="2">
+        <v>46307.59375</v>
+      </c>
+      <c r="B347">
+        <v>0</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+      <c r="D347">
+        <v>0</v>
+      </c>
+      <c r="E347">
+        <v>0</v>
+      </c>
+      <c r="F347">
+        <v>58</v>
+      </c>
+      <c r="G347" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="348" spans="1:7">
+      <c r="A348" s="2">
+        <v>46307.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>0</v>
+      </c>
+      <c r="C348">
+        <v>0</v>
+      </c>
+      <c r="D348">
+        <v>0</v>
+      </c>
+      <c r="E348">
+        <v>0</v>
+      </c>
+      <c r="F348">
+        <v>59</v>
+      </c>
+      <c r="G348" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7">
+      <c r="A349" s="2">
+        <v>46307.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>0</v>
+      </c>
+      <c r="C349">
+        <v>0</v>
+      </c>
+      <c r="D349">
+        <v>0</v>
+      </c>
+      <c r="E349">
+        <v>0</v>
+      </c>
+      <c r="F349">
+        <v>60</v>
+      </c>
+      <c r="G349" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7">
+      <c r="A350" s="2">
+        <v>46307.625</v>
+      </c>
+      <c r="B350">
+        <v>0</v>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+      <c r="D350">
+        <v>0</v>
+      </c>
+      <c r="E350">
+        <v>0</v>
+      </c>
+      <c r="F350">
+        <v>61</v>
+      </c>
+      <c r="G350" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7">
+      <c r="A351" s="2">
+        <v>46307.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+      <c r="C351">
+        <v>0</v>
+      </c>
+      <c r="D351">
+        <v>0</v>
+      </c>
+      <c r="E351">
+        <v>0</v>
+      </c>
+      <c r="F351">
+        <v>62</v>
+      </c>
+      <c r="G351" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7">
+      <c r="A352" s="2">
+        <v>46307.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>0</v>
+      </c>
+      <c r="C352">
+        <v>0</v>
+      </c>
+      <c r="D352">
+        <v>0</v>
+      </c>
+      <c r="E352">
+        <v>0</v>
+      </c>
+      <c r="F352">
+        <v>63</v>
+      </c>
+      <c r="G352" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7">
+      <c r="A353" s="2">
+        <v>46307.65625</v>
+      </c>
+      <c r="B353">
+        <v>0</v>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+      <c r="D353">
+        <v>0</v>
+      </c>
+      <c r="E353">
+        <v>0</v>
+      </c>
+      <c r="F353">
+        <v>64</v>
+      </c>
+      <c r="G353" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7">
+      <c r="A354" s="2">
+        <v>46307.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+      <c r="C354">
+        <v>0</v>
+      </c>
+      <c r="D354">
+        <v>0</v>
+      </c>
+      <c r="E354">
+        <v>0</v>
+      </c>
+      <c r="F354">
+        <v>65</v>
+      </c>
+      <c r="G354" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7">
+      <c r="A355" s="2">
+        <v>46307.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>0</v>
+      </c>
+      <c r="C355">
+        <v>0</v>
+      </c>
+      <c r="D355">
+        <v>0</v>
+      </c>
+      <c r="E355">
+        <v>0</v>
+      </c>
+      <c r="F355">
+        <v>66</v>
+      </c>
+      <c r="G355" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7">
+      <c r="A356" s="2">
+        <v>46307.6875</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+      <c r="D356">
+        <v>0</v>
+      </c>
+      <c r="E356">
+        <v>0</v>
+      </c>
+      <c r="F356">
+        <v>67</v>
+      </c>
+      <c r="G356" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7">
+      <c r="A357" s="2">
+        <v>46307.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>0</v>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+      <c r="D357">
+        <v>0</v>
+      </c>
+      <c r="E357">
+        <v>0</v>
+      </c>
+      <c r="F357">
+        <v>68</v>
+      </c>
+      <c r="G357" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7">
+      <c r="A358" s="2">
+        <v>46307.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>0</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+      <c r="D358">
+        <v>0</v>
+      </c>
+      <c r="E358">
+        <v>0</v>
+      </c>
+      <c r="F358">
+        <v>69</v>
+      </c>
+      <c r="G358" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7">
+      <c r="A359" s="2">
+        <v>46307.71875</v>
+      </c>
+      <c r="B359">
+        <v>0</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+      <c r="D359">
+        <v>0</v>
+      </c>
+      <c r="E359">
+        <v>0</v>
+      </c>
+      <c r="F359">
+        <v>70</v>
+      </c>
+      <c r="G359" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7">
+      <c r="A360" s="2">
+        <v>46307.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>0</v>
+      </c>
+      <c r="C360">
+        <v>0</v>
+      </c>
+      <c r="D360">
+        <v>0</v>
+      </c>
+      <c r="E360">
+        <v>0</v>
+      </c>
+      <c r="F360">
+        <v>71</v>
+      </c>
+      <c r="G360" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7">
+      <c r="A361" s="2">
+        <v>46307.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>0</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+      <c r="D361">
+        <v>0</v>
+      </c>
+      <c r="E361">
+        <v>0</v>
+      </c>
+      <c r="F361">
+        <v>72</v>
+      </c>
+      <c r="G361" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7">
+      <c r="A362" s="2">
+        <v>46307.75</v>
+      </c>
+      <c r="B362">
+        <v>0</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+      <c r="D362">
+        <v>0</v>
+      </c>
+      <c r="E362">
+        <v>0</v>
+      </c>
+      <c r="F362">
+        <v>73</v>
+      </c>
+      <c r="G362" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7">
+      <c r="A363" s="2">
+        <v>46307.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>0</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+      <c r="D363">
+        <v>0</v>
+      </c>
+      <c r="E363">
+        <v>0</v>
+      </c>
+      <c r="F363">
+        <v>74</v>
+      </c>
+      <c r="G363" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7">
+      <c r="A364" s="2">
+        <v>46307.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+      <c r="D364">
+        <v>0</v>
+      </c>
+      <c r="E364">
+        <v>0</v>
+      </c>
+      <c r="F364">
+        <v>75</v>
+      </c>
+      <c r="G364" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7">
+      <c r="A365" s="2">
+        <v>46307.78125</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+      <c r="D365">
+        <v>0</v>
+      </c>
+      <c r="E365">
+        <v>0</v>
+      </c>
+      <c r="F365">
+        <v>76</v>
+      </c>
+      <c r="G365" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7">
+      <c r="A366" s="2">
+        <v>46307.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>0</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366">
+        <v>0</v>
+      </c>
+      <c r="E366">
+        <v>0</v>
+      </c>
+      <c r="F366">
+        <v>77</v>
+      </c>
+      <c r="G366" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7">
+      <c r="A367" s="2">
+        <v>46307.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+      <c r="D367">
+        <v>0</v>
+      </c>
+      <c r="E367">
+        <v>0</v>
+      </c>
+      <c r="F367">
+        <v>78</v>
+      </c>
+      <c r="G367" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7">
+      <c r="A368" s="2">
+        <v>46307.8125</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368">
+        <v>0</v>
+      </c>
+      <c r="E368">
+        <v>0</v>
+      </c>
+      <c r="F368">
+        <v>79</v>
+      </c>
+      <c r="G368" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7">
+      <c r="A369" s="2">
+        <v>46307.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+      <c r="D369">
+        <v>0</v>
+      </c>
+      <c r="E369">
+        <v>0</v>
+      </c>
+      <c r="F369">
+        <v>80</v>
+      </c>
+      <c r="G369" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7">
+      <c r="A370" s="2">
+        <v>46307.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370">
+        <v>0</v>
+      </c>
+      <c r="E370">
+        <v>0</v>
+      </c>
+      <c r="F370">
+        <v>81</v>
+      </c>
+      <c r="G370" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7">
+      <c r="A371" s="2">
+        <v>46307.84375</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371">
+        <v>0</v>
+      </c>
+      <c r="E371">
+        <v>0</v>
+      </c>
+      <c r="F371">
+        <v>82</v>
+      </c>
+      <c r="G371" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7">
+      <c r="A372" s="2">
+        <v>46307.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372">
+        <v>0</v>
+      </c>
+      <c r="E372">
+        <v>0</v>
+      </c>
+      <c r="F372">
+        <v>83</v>
+      </c>
+      <c r="G372" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7">
+      <c r="A373" s="2">
+        <v>46307.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>0</v>
+      </c>
+      <c r="E373">
+        <v>0</v>
+      </c>
+      <c r="F373">
+        <v>84</v>
+      </c>
+      <c r="G373" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7">
+      <c r="A374" s="2">
+        <v>46307.875</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>0</v>
+      </c>
+      <c r="E374">
+        <v>0</v>
+      </c>
+      <c r="F374">
+        <v>85</v>
+      </c>
+      <c r="G374" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="375" spans="1:7">
+      <c r="A375" s="2">
+        <v>46307.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375">
+        <v>0</v>
+      </c>
+      <c r="E375">
+        <v>0</v>
+      </c>
+      <c r="F375">
+        <v>86</v>
+      </c>
+      <c r="G375" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="376" spans="1:7">
+      <c r="A376" s="2">
+        <v>46307.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376">
+        <v>0</v>
+      </c>
+      <c r="E376">
+        <v>0</v>
+      </c>
+      <c r="F376">
+        <v>87</v>
+      </c>
+      <c r="G376" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="377" spans="1:7">
+      <c r="A377" s="2">
+        <v>46307.90625</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+      <c r="D377">
+        <v>0</v>
+      </c>
+      <c r="E377">
+        <v>0</v>
+      </c>
+      <c r="F377">
+        <v>88</v>
+      </c>
+      <c r="G377" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7">
+      <c r="A378" s="2">
+        <v>46307.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>0</v>
+      </c>
+      <c r="E378">
+        <v>0</v>
+      </c>
+      <c r="F378">
+        <v>89</v>
+      </c>
+      <c r="G378" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7">
+      <c r="A379" s="2">
+        <v>46307.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379">
+        <v>0</v>
+      </c>
+      <c r="E379">
+        <v>0</v>
+      </c>
+      <c r="F379">
+        <v>90</v>
+      </c>
+      <c r="G379" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7">
+      <c r="A380" s="2">
+        <v>46307.9375</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+      <c r="D380">
+        <v>0</v>
+      </c>
+      <c r="E380">
+        <v>0</v>
+      </c>
+      <c r="F380">
+        <v>91</v>
+      </c>
+      <c r="G380" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="381" spans="1:7">
+      <c r="A381" s="2">
+        <v>46307.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381">
+        <v>0</v>
+      </c>
+      <c r="E381">
+        <v>0</v>
+      </c>
+      <c r="F381">
+        <v>92</v>
+      </c>
+      <c r="G381" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="382" spans="1:7">
+      <c r="A382" s="2">
+        <v>46307.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382">
+        <v>0</v>
+      </c>
+      <c r="E382">
+        <v>0</v>
+      </c>
+      <c r="F382">
+        <v>93</v>
+      </c>
+      <c r="G382" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7">
+      <c r="A383" s="2">
+        <v>46307.96875</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383">
+        <v>0</v>
+      </c>
+      <c r="E383">
+        <v>0</v>
+      </c>
+      <c r="F383">
+        <v>94</v>
+      </c>
+      <c r="G383" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="384" spans="1:7">
+      <c r="A384" s="2">
+        <v>46307.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>0</v>
+      </c>
+      <c r="E384">
+        <v>0</v>
+      </c>
+      <c r="F384">
+        <v>95</v>
+      </c>
+      <c r="G384" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="385" spans="1:7">
+      <c r="A385" s="2">
+        <v>46307.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>0</v>
+      </c>
+      <c r="E385">
+        <v>0</v>
+      </c>
+      <c r="F385">
+        <v>96</v>
+      </c>
+      <c r="G385" t="s">
+        <v>390</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -37,294 +37,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>12.10.20261</t>
-  </si>
-  <si>
-    <t>12.10.20262</t>
-  </si>
-  <si>
-    <t>12.10.20263</t>
-  </si>
-  <si>
-    <t>12.10.20264</t>
-  </si>
-  <si>
-    <t>12.10.20265</t>
-  </si>
-  <si>
-    <t>12.10.20266</t>
-  </si>
-  <si>
-    <t>12.10.20267</t>
-  </si>
-  <si>
-    <t>12.10.20268</t>
-  </si>
-  <si>
-    <t>12.10.20269</t>
-  </si>
-  <si>
-    <t>12.10.202610</t>
-  </si>
-  <si>
-    <t>12.10.202611</t>
-  </si>
-  <si>
-    <t>12.10.202612</t>
-  </si>
-  <si>
-    <t>12.10.202613</t>
-  </si>
-  <si>
-    <t>12.10.202614</t>
-  </si>
-  <si>
-    <t>12.10.202615</t>
-  </si>
-  <si>
-    <t>12.10.202616</t>
-  </si>
-  <si>
-    <t>12.10.202617</t>
-  </si>
-  <si>
-    <t>12.10.202618</t>
-  </si>
-  <si>
-    <t>12.10.202619</t>
-  </si>
-  <si>
-    <t>12.10.202620</t>
-  </si>
-  <si>
-    <t>12.10.202621</t>
-  </si>
-  <si>
-    <t>12.10.202622</t>
-  </si>
-  <si>
-    <t>12.10.202623</t>
-  </si>
-  <si>
-    <t>12.10.202624</t>
-  </si>
-  <si>
-    <t>12.10.202625</t>
-  </si>
-  <si>
-    <t>12.10.202626</t>
-  </si>
-  <si>
-    <t>12.10.202627</t>
-  </si>
-  <si>
-    <t>12.10.202628</t>
-  </si>
-  <si>
-    <t>12.10.202629</t>
-  </si>
-  <si>
-    <t>12.10.202630</t>
-  </si>
-  <si>
-    <t>12.10.202631</t>
-  </si>
-  <si>
-    <t>12.10.202632</t>
-  </si>
-  <si>
-    <t>12.10.202633</t>
-  </si>
-  <si>
-    <t>12.10.202634</t>
-  </si>
-  <si>
-    <t>12.10.202635</t>
-  </si>
-  <si>
-    <t>12.10.202636</t>
-  </si>
-  <si>
-    <t>12.10.202637</t>
-  </si>
-  <si>
-    <t>12.10.202638</t>
-  </si>
-  <si>
-    <t>12.10.202639</t>
-  </si>
-  <si>
-    <t>12.10.202640</t>
-  </si>
-  <si>
-    <t>12.10.202641</t>
-  </si>
-  <si>
-    <t>12.10.202642</t>
-  </si>
-  <si>
-    <t>12.10.202643</t>
-  </si>
-  <si>
-    <t>12.10.202644</t>
-  </si>
-  <si>
-    <t>12.10.202645</t>
-  </si>
-  <si>
-    <t>12.10.202646</t>
-  </si>
-  <si>
-    <t>12.10.202647</t>
-  </si>
-  <si>
-    <t>12.10.202648</t>
-  </si>
-  <si>
-    <t>12.10.202649</t>
-  </si>
-  <si>
-    <t>12.10.202650</t>
-  </si>
-  <si>
-    <t>12.10.202651</t>
-  </si>
-  <si>
-    <t>12.10.202652</t>
-  </si>
-  <si>
-    <t>12.10.202653</t>
-  </si>
-  <si>
-    <t>12.10.202654</t>
-  </si>
-  <si>
-    <t>12.10.202655</t>
-  </si>
-  <si>
-    <t>12.10.202656</t>
-  </si>
-  <si>
-    <t>12.10.202657</t>
-  </si>
-  <si>
-    <t>12.10.202658</t>
-  </si>
-  <si>
-    <t>12.10.202659</t>
-  </si>
-  <si>
-    <t>12.10.202660</t>
-  </si>
-  <si>
-    <t>12.10.202661</t>
-  </si>
-  <si>
-    <t>12.10.202662</t>
-  </si>
-  <si>
-    <t>12.10.202663</t>
-  </si>
-  <si>
-    <t>12.10.202664</t>
-  </si>
-  <si>
-    <t>12.10.202665</t>
-  </si>
-  <si>
-    <t>12.10.202666</t>
-  </si>
-  <si>
-    <t>12.10.202667</t>
-  </si>
-  <si>
-    <t>12.10.202668</t>
-  </si>
-  <si>
-    <t>12.10.202669</t>
-  </si>
-  <si>
-    <t>12.10.202670</t>
-  </si>
-  <si>
-    <t>12.10.202671</t>
-  </si>
-  <si>
-    <t>12.10.202672</t>
-  </si>
-  <si>
-    <t>12.10.202673</t>
-  </si>
-  <si>
-    <t>12.10.202674</t>
-  </si>
-  <si>
-    <t>12.10.202675</t>
-  </si>
-  <si>
-    <t>12.10.202676</t>
-  </si>
-  <si>
-    <t>12.10.202677</t>
-  </si>
-  <si>
-    <t>12.10.202678</t>
-  </si>
-  <si>
-    <t>12.10.202679</t>
-  </si>
-  <si>
-    <t>12.10.202680</t>
-  </si>
-  <si>
-    <t>12.10.202681</t>
-  </si>
-  <si>
-    <t>12.10.202682</t>
-  </si>
-  <si>
-    <t>12.10.202683</t>
-  </si>
-  <si>
-    <t>12.10.202684</t>
-  </si>
-  <si>
-    <t>12.10.202685</t>
-  </si>
-  <si>
-    <t>12.10.202686</t>
-  </si>
-  <si>
-    <t>12.10.202687</t>
-  </si>
-  <si>
-    <t>12.10.202688</t>
-  </si>
-  <si>
-    <t>12.10.202689</t>
-  </si>
-  <si>
-    <t>12.10.202690</t>
-  </si>
-  <si>
-    <t>12.10.202691</t>
-  </si>
-  <si>
-    <t>12.10.202692</t>
-  </si>
-  <si>
-    <t>12.10.202693</t>
-  </si>
-  <si>
-    <t>12.10.202694</t>
-  </si>
-  <si>
-    <t>12.10.202695</t>
-  </si>
-  <si>
-    <t>12.10.202696</t>
-  </si>
-  <si>
     <t>13.10.20261</t>
   </si>
   <si>
@@ -611,6 +323,294 @@
   </si>
   <si>
     <t>13.10.202696</t>
+  </si>
+  <si>
+    <t>14.10.20261</t>
+  </si>
+  <si>
+    <t>14.10.20262</t>
+  </si>
+  <si>
+    <t>14.10.20263</t>
+  </si>
+  <si>
+    <t>14.10.20264</t>
+  </si>
+  <si>
+    <t>14.10.20265</t>
+  </si>
+  <si>
+    <t>14.10.20266</t>
+  </si>
+  <si>
+    <t>14.10.20267</t>
+  </si>
+  <si>
+    <t>14.10.20268</t>
+  </si>
+  <si>
+    <t>14.10.20269</t>
+  </si>
+  <si>
+    <t>14.10.202610</t>
+  </si>
+  <si>
+    <t>14.10.202611</t>
+  </si>
+  <si>
+    <t>14.10.202612</t>
+  </si>
+  <si>
+    <t>14.10.202613</t>
+  </si>
+  <si>
+    <t>14.10.202614</t>
+  </si>
+  <si>
+    <t>14.10.202615</t>
+  </si>
+  <si>
+    <t>14.10.202616</t>
+  </si>
+  <si>
+    <t>14.10.202617</t>
+  </si>
+  <si>
+    <t>14.10.202618</t>
+  </si>
+  <si>
+    <t>14.10.202619</t>
+  </si>
+  <si>
+    <t>14.10.202620</t>
+  </si>
+  <si>
+    <t>14.10.202621</t>
+  </si>
+  <si>
+    <t>14.10.202622</t>
+  </si>
+  <si>
+    <t>14.10.202623</t>
+  </si>
+  <si>
+    <t>14.10.202624</t>
+  </si>
+  <si>
+    <t>14.10.202625</t>
+  </si>
+  <si>
+    <t>14.10.202626</t>
+  </si>
+  <si>
+    <t>14.10.202627</t>
+  </si>
+  <si>
+    <t>14.10.202628</t>
+  </si>
+  <si>
+    <t>14.10.202629</t>
+  </si>
+  <si>
+    <t>14.10.202630</t>
+  </si>
+  <si>
+    <t>14.10.202631</t>
+  </si>
+  <si>
+    <t>14.10.202632</t>
+  </si>
+  <si>
+    <t>14.10.202633</t>
+  </si>
+  <si>
+    <t>14.10.202634</t>
+  </si>
+  <si>
+    <t>14.10.202635</t>
+  </si>
+  <si>
+    <t>14.10.202636</t>
+  </si>
+  <si>
+    <t>14.10.202637</t>
+  </si>
+  <si>
+    <t>14.10.202638</t>
+  </si>
+  <si>
+    <t>14.10.202639</t>
+  </si>
+  <si>
+    <t>14.10.202640</t>
+  </si>
+  <si>
+    <t>14.10.202641</t>
+  </si>
+  <si>
+    <t>14.10.202642</t>
+  </si>
+  <si>
+    <t>14.10.202643</t>
+  </si>
+  <si>
+    <t>14.10.202644</t>
+  </si>
+  <si>
+    <t>14.10.202645</t>
+  </si>
+  <si>
+    <t>14.10.202646</t>
+  </si>
+  <si>
+    <t>14.10.202647</t>
+  </si>
+  <si>
+    <t>14.10.202648</t>
+  </si>
+  <si>
+    <t>14.10.202649</t>
+  </si>
+  <si>
+    <t>14.10.202650</t>
+  </si>
+  <si>
+    <t>14.10.202651</t>
+  </si>
+  <si>
+    <t>14.10.202652</t>
+  </si>
+  <si>
+    <t>14.10.202653</t>
+  </si>
+  <si>
+    <t>14.10.202654</t>
+  </si>
+  <si>
+    <t>14.10.202655</t>
+  </si>
+  <si>
+    <t>14.10.202656</t>
+  </si>
+  <si>
+    <t>14.10.202657</t>
+  </si>
+  <si>
+    <t>14.10.202658</t>
+  </si>
+  <si>
+    <t>14.10.202659</t>
+  </si>
+  <si>
+    <t>14.10.202660</t>
+  </si>
+  <si>
+    <t>14.10.202661</t>
+  </si>
+  <si>
+    <t>14.10.202662</t>
+  </si>
+  <si>
+    <t>14.10.202663</t>
+  </si>
+  <si>
+    <t>14.10.202664</t>
+  </si>
+  <si>
+    <t>14.10.202665</t>
+  </si>
+  <si>
+    <t>14.10.202666</t>
+  </si>
+  <si>
+    <t>14.10.202667</t>
+  </si>
+  <si>
+    <t>14.10.202668</t>
+  </si>
+  <si>
+    <t>14.10.202669</t>
+  </si>
+  <si>
+    <t>14.10.202670</t>
+  </si>
+  <si>
+    <t>14.10.202671</t>
+  </si>
+  <si>
+    <t>14.10.202672</t>
+  </si>
+  <si>
+    <t>14.10.202673</t>
+  </si>
+  <si>
+    <t>14.10.202674</t>
+  </si>
+  <si>
+    <t>14.10.202675</t>
+  </si>
+  <si>
+    <t>14.10.202676</t>
+  </si>
+  <si>
+    <t>14.10.202677</t>
+  </si>
+  <si>
+    <t>14.10.202678</t>
+  </si>
+  <si>
+    <t>14.10.202679</t>
+  </si>
+  <si>
+    <t>14.10.202680</t>
+  </si>
+  <si>
+    <t>14.10.202681</t>
+  </si>
+  <si>
+    <t>14.10.202682</t>
+  </si>
+  <si>
+    <t>14.10.202683</t>
+  </si>
+  <si>
+    <t>14.10.202684</t>
+  </si>
+  <si>
+    <t>14.10.202685</t>
+  </si>
+  <si>
+    <t>14.10.202686</t>
+  </si>
+  <si>
+    <t>14.10.202687</t>
+  </si>
+  <si>
+    <t>14.10.202688</t>
+  </si>
+  <si>
+    <t>14.10.202689</t>
+  </si>
+  <si>
+    <t>14.10.202690</t>
+  </si>
+  <si>
+    <t>14.10.202691</t>
+  </si>
+  <si>
+    <t>14.10.202692</t>
+  </si>
+  <si>
+    <t>14.10.202693</t>
+  </si>
+  <si>
+    <t>14.10.202694</t>
+  </si>
+  <si>
+    <t>14.10.202695</t>
+  </si>
+  <si>
+    <t>14.10.202696</t>
   </si>
 </sst>
 </file>
@@ -1000,13 +1000,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B2">
-        <v>7.62</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>4.041</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1023,13 +1023,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46307.01041666666</v>
+        <v>46308.01041666666</v>
       </c>
       <c r="B3">
-        <v>9.08</v>
+        <v>0.04</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>0.985</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1046,19 +1046,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46307.02083333334</v>
+        <v>46308.02083333334</v>
       </c>
       <c r="B4">
-        <v>2.372</v>
+        <v>0.045</v>
       </c>
       <c r="C4">
-        <v>0.04</v>
+        <v>1.859</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -1069,19 +1069,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46307.03125</v>
+        <v>46308.03125</v>
       </c>
       <c r="B5">
-        <v>1.259</v>
+        <v>10.617</v>
       </c>
       <c r="C5">
-        <v>0.378</v>
+        <v>0.268</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -1092,19 +1092,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46307.04166666666</v>
+        <v>46308.04166666666</v>
       </c>
       <c r="B6">
-        <v>0.059</v>
+        <v>32.138</v>
       </c>
       <c r="C6">
-        <v>0.165</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -1115,19 +1115,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46307.05208333334</v>
+        <v>46308.05208333334</v>
       </c>
       <c r="B7">
-        <v>0.237</v>
+        <v>15.785</v>
       </c>
       <c r="C7">
-        <v>0.224</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -1138,19 +1138,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46307.0625</v>
+        <v>46308.0625</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>17.488</v>
       </c>
       <c r="C8">
-        <v>1.174</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -1161,13 +1161,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46307.07291666666</v>
+        <v>46308.07291666666</v>
       </c>
       <c r="B9">
-        <v>0.019</v>
+        <v>17.612</v>
       </c>
       <c r="C9">
-        <v>2.007</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1184,13 +1184,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46307.08333333334</v>
+        <v>46308.08333333334</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>1.712</v>
       </c>
       <c r="C10">
-        <v>8.609</v>
+        <v>0.01</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1207,13 +1207,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46307.09375</v>
+        <v>46308.09375</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>11.01</v>
       </c>
       <c r="C11">
-        <v>28.727</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1230,13 +1230,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46307.10416666666</v>
+        <v>46308.10416666666</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>6.306</v>
       </c>
       <c r="C12">
-        <v>21.553</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1253,19 +1253,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46307.11458333334</v>
+        <v>46308.11458333334</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>3.038</v>
       </c>
       <c r="C13">
-        <v>10.111</v>
+        <v>0.704</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>12</v>
@@ -1276,19 +1276,19 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46307.125</v>
+        <v>46308.125</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>6.785</v>
       </c>
       <c r="C14">
-        <v>6.978</v>
+        <v>0.363</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F14">
         <v>13</v>
@@ -1299,19 +1299,19 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46307.13541666666</v>
+        <v>46308.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>3.505</v>
       </c>
       <c r="C15">
-        <v>31.267</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <v>14</v>
@@ -1322,19 +1322,19 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46307.14583333334</v>
+        <v>46308.14583333334</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="C16">
-        <v>70.099</v>
+        <v>2.537</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>15</v>
@@ -1345,19 +1345,19 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46307.15625</v>
+        <v>46308.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="C17">
-        <v>68.53700000000001</v>
+        <v>1.066</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>16</v>
@@ -1368,19 +1368,19 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46307.16666666666</v>
+        <v>46308.16666666666</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>0.358</v>
       </c>
       <c r="C18">
-        <v>56.24</v>
+        <v>1.293</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="F18">
         <v>17</v>
@@ -1391,19 +1391,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46307.17708333334</v>
+        <v>46308.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>0.043</v>
       </c>
       <c r="C19">
-        <v>19.813</v>
+        <v>0.528</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>137.5</v>
+        <v>0</v>
       </c>
       <c r="F19">
         <v>18</v>
@@ -1414,19 +1414,19 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46307.1875</v>
+        <v>46308.1875</v>
       </c>
       <c r="B20">
-        <v>3.067</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="C20">
-        <v>0.041</v>
+        <v>0.116</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F20">
         <v>19</v>
@@ -1437,19 +1437,19 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46307.19791666666</v>
+        <v>46308.19791666666</v>
       </c>
       <c r="B21">
-        <v>22.407</v>
+        <v>4.255</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>137.5</v>
+        <v>0</v>
       </c>
       <c r="F21">
         <v>20</v>
@@ -1460,19 +1460,19 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46307.20833333334</v>
+        <v>46308.20833333334</v>
       </c>
       <c r="B22">
-        <v>3.716</v>
+        <v>3.1</v>
       </c>
       <c r="C22">
-        <v>3.599</v>
+        <v>1.412</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <v>21</v>
@@ -1483,19 +1483,19 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46307.21875</v>
+        <v>46308.21875</v>
       </c>
       <c r="B23">
-        <v>0.004</v>
+        <v>0.093</v>
       </c>
       <c r="C23">
-        <v>2.206</v>
+        <v>5.055</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>137.5</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <v>22</v>
@@ -1506,19 +1506,19 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46307.22916666666</v>
+        <v>46308.22916666666</v>
       </c>
       <c r="B24">
-        <v>4.736</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>6.974</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>137.5</v>
+        <v>0</v>
       </c>
       <c r="F24">
         <v>23</v>
@@ -1529,19 +1529,19 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46307.23958333334</v>
+        <v>46308.23958333334</v>
       </c>
       <c r="B25">
-        <v>33.556</v>
+        <v>0.537</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>137.5</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>24</v>
@@ -1552,19 +1552,19 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="B26">
-        <v>48.253</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>35.376</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F26">
         <v>25</v>
@@ -1575,19 +1575,19 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46307.26041666666</v>
+        <v>46308.26041666666</v>
       </c>
       <c r="B27">
-        <v>69.78700000000001</v>
+        <v>1.289</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>4.477</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F27">
         <v>26</v>
@@ -1598,19 +1598,19 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46307.27083333334</v>
+        <v>46308.27083333334</v>
       </c>
       <c r="B28">
-        <v>61.25</v>
+        <v>1.875</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
       <c r="E28">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F28">
         <v>27</v>
@@ -1621,13 +1621,13 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46307.28125</v>
+        <v>46308.28125</v>
       </c>
       <c r="B29">
-        <v>59.678</v>
+        <v>0.128</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>0.211</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1644,16 +1644,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46307.29166666666</v>
+        <v>46308.29166666666</v>
       </c>
       <c r="B30">
-        <v>52.252</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>3.163</v>
       </c>
       <c r="D30">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1667,16 +1667,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46307.30208333334</v>
+        <v>46308.30208333334</v>
       </c>
       <c r="B31">
-        <v>87.75</v>
+        <v>0.151</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>0.239</v>
       </c>
       <c r="D31">
-        <v>39.25</v>
+        <v>0</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1690,16 +1690,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46307.3125</v>
+        <v>46308.3125</v>
       </c>
       <c r="B32">
-        <v>22.198</v>
+        <v>0.099</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>0.128</v>
       </c>
       <c r="D32">
-        <v>120.25</v>
+        <v>0</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1713,16 +1713,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46307.32291666666</v>
+        <v>46308.32291666666</v>
       </c>
       <c r="B33">
-        <v>8.118</v>
+        <v>0.06</v>
       </c>
       <c r="C33">
-        <v>0.193</v>
+        <v>0.351</v>
       </c>
       <c r="D33">
-        <v>120.25</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1736,19 +1736,19 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46307.33333333334</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="B34">
-        <v>0.397</v>
+        <v>0.241</v>
       </c>
       <c r="C34">
-        <v>0.392</v>
+        <v>0.136</v>
       </c>
       <c r="D34">
-        <v>127.75</v>
+        <v>0</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F34">
         <v>33</v>
@@ -1759,19 +1759,19 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46307.34375</v>
+        <v>46308.34375</v>
       </c>
       <c r="B35">
-        <v>0.432</v>
+        <v>0.581</v>
       </c>
       <c r="C35">
-        <v>0.225</v>
+        <v>0.2</v>
       </c>
       <c r="D35">
-        <v>112.75</v>
+        <v>0</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F35">
         <v>34</v>
@@ -1782,19 +1782,19 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46307.35416666666</v>
+        <v>46308.35416666666</v>
       </c>
       <c r="B36">
-        <v>1.178</v>
+        <v>0.09</v>
       </c>
       <c r="C36">
-        <v>0.03</v>
+        <v>0.275</v>
       </c>
       <c r="D36">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F36">
         <v>35</v>
@@ -1805,19 +1805,19 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46307.36458333334</v>
+        <v>46308.36458333334</v>
       </c>
       <c r="B37">
-        <v>0.113</v>
+        <v>0.129</v>
       </c>
       <c r="C37">
-        <v>0.231</v>
+        <v>0.122</v>
       </c>
       <c r="D37">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F37">
         <v>36</v>
@@ -1828,19 +1828,19 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46307.375</v>
+        <v>46308.375</v>
       </c>
       <c r="B38">
-        <v>1.014</v>
+        <v>0.341</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>1.473</v>
       </c>
       <c r="D38">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F38">
         <v>37</v>
@@ -1851,19 +1851,19 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46307.38541666666</v>
+        <v>46308.38541666666</v>
       </c>
       <c r="B39">
-        <v>6.084</v>
+        <v>0.957</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>1.864</v>
       </c>
       <c r="D39">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F39">
         <v>38</v>
@@ -1874,19 +1874,19 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46307.39583333334</v>
+        <v>46308.39583333334</v>
       </c>
       <c r="B40">
-        <v>0.323</v>
+        <v>0.919</v>
       </c>
       <c r="C40">
-        <v>0.182</v>
+        <v>0.621</v>
       </c>
       <c r="D40">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F40">
         <v>39</v>
@@ -1897,19 +1897,19 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46307.40625</v>
+        <v>46308.40625</v>
       </c>
       <c r="B41">
-        <v>0.288</v>
+        <v>1.853</v>
       </c>
       <c r="C41">
-        <v>2.68</v>
+        <v>4.535</v>
       </c>
       <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
         <v>25</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
       </c>
       <c r="F41">
         <v>40</v>
@@ -1920,19 +1920,19 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46307.41666666666</v>
+        <v>46308.41666666666</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>0.855</v>
       </c>
       <c r="C42">
-        <v>2.662</v>
+        <v>1.9</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F42">
         <v>41</v>
@@ -1943,19 +1943,19 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46307.42708333334</v>
+        <v>46308.42708333334</v>
       </c>
       <c r="B43">
-        <v>6.332</v>
+        <v>9.939</v>
       </c>
       <c r="C43">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F43">
         <v>42</v>
@@ -1966,16 +1966,16 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46307.4375</v>
+        <v>46308.4375</v>
       </c>
       <c r="B44">
-        <v>4.044</v>
+        <v>2.028</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>0.486</v>
       </c>
       <c r="D44">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -1989,16 +1989,16 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46307.44791666666</v>
+        <v>46308.44791666666</v>
       </c>
       <c r="B45">
-        <v>5.265</v>
+        <v>0.079</v>
       </c>
       <c r="C45">
-        <v>0.149</v>
+        <v>3.181</v>
       </c>
       <c r="D45">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -2012,16 +2012,16 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46307.45833333334</v>
+        <v>46308.45833333334</v>
       </c>
       <c r="B46">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>2.133</v>
+        <v>9.438000000000001</v>
       </c>
       <c r="D46">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2035,16 +2035,16 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46307.46875</v>
+        <v>46308.46875</v>
       </c>
       <c r="B47">
-        <v>0.015</v>
+        <v>0.003</v>
       </c>
       <c r="C47">
-        <v>1.654</v>
+        <v>8.981</v>
       </c>
       <c r="D47">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -2058,16 +2058,16 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46307.47916666666</v>
+        <v>46308.47916666666</v>
       </c>
       <c r="B48">
         <v>0</v>
       </c>
       <c r="C48">
-        <v>6.651</v>
+        <v>7.342</v>
       </c>
       <c r="D48">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -2081,19 +2081,19 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46307.48958333334</v>
+        <v>46308.48958333334</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C49">
-        <v>19.758</v>
+        <v>1.318</v>
       </c>
       <c r="D49">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F49">
         <v>48</v>
@@ -2104,19 +2104,19 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46307.5</v>
+        <v>46308.5</v>
       </c>
       <c r="B50">
         <v>0</v>
       </c>
       <c r="C50">
-        <v>20.783</v>
+        <v>14.256</v>
       </c>
       <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
         <v>50</v>
-      </c>
-      <c r="E50">
-        <v>0</v>
       </c>
       <c r="F50">
         <v>49</v>
@@ -2127,19 +2127,19 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46307.51041666666</v>
+        <v>46308.51041666666</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="C51">
-        <v>16.391</v>
+        <v>13.297</v>
       </c>
       <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
         <v>50</v>
-      </c>
-      <c r="E51">
-        <v>0</v>
       </c>
       <c r="F51">
         <v>50</v>
@@ -2150,19 +2150,19 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46307.52083333334</v>
+        <v>46308.52083333334</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>10.184</v>
       </c>
       <c r="C52">
-        <v>36.484</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F52">
         <v>51</v>
@@ -2173,19 +2173,19 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46307.53125</v>
+        <v>46308.53125</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>32.523</v>
       </c>
       <c r="C53">
-        <v>25.144</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F53">
         <v>52</v>
@@ -2196,19 +2196,19 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46307.54166666666</v>
+        <v>46308.54166666666</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>25.538</v>
       </c>
       <c r="C54">
-        <v>41.923</v>
+        <v>0</v>
       </c>
       <c r="D54">
-        <v>47.5</v>
+        <v>0</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F54">
         <v>53</v>
@@ -2219,19 +2219,19 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46307.55208333334</v>
+        <v>46308.55208333334</v>
       </c>
       <c r="B55">
-        <v>0.007</v>
+        <v>33.614</v>
       </c>
       <c r="C55">
-        <v>18.484</v>
+        <v>0</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F55">
         <v>54</v>
@@ -2242,13 +2242,13 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46307.5625</v>
+        <v>46308.5625</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>24.849</v>
       </c>
       <c r="C56">
-        <v>14.01</v>
+        <v>0</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2265,13 +2265,13 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46307.57291666666</v>
+        <v>46308.57291666666</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>8.375999999999999</v>
       </c>
       <c r="C57">
-        <v>35.816</v>
+        <v>0</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2288,13 +2288,13 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46307.58333333334</v>
+        <v>46308.58333333334</v>
       </c>
       <c r="B58">
-        <v>0.05</v>
+        <v>24.693</v>
       </c>
       <c r="C58">
-        <v>2.225</v>
+        <v>0</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2311,13 +2311,13 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46307.59375</v>
+        <v>46308.59375</v>
       </c>
       <c r="B59">
-        <v>0.066</v>
+        <v>29.671</v>
       </c>
       <c r="C59">
-        <v>0.315</v>
+        <v>0</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2334,13 +2334,13 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46307.60416666666</v>
+        <v>46308.60416666666</v>
       </c>
       <c r="B60">
-        <v>0.383</v>
+        <v>12.678</v>
       </c>
       <c r="C60">
-        <v>1.282</v>
+        <v>0</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2357,13 +2357,13 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46307.61458333334</v>
+        <v>46308.61458333334</v>
       </c>
       <c r="B61">
-        <v>0.08400000000000001</v>
+        <v>23.595</v>
       </c>
       <c r="C61">
-        <v>0.784</v>
+        <v>0</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2380,13 +2380,13 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46307.625</v>
+        <v>46308.625</v>
       </c>
       <c r="B62">
-        <v>2.492</v>
+        <v>0.031</v>
       </c>
       <c r="C62">
-        <v>1.073</v>
+        <v>11.064</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2403,13 +2403,13 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46307.63541666666</v>
+        <v>46308.63541666666</v>
       </c>
       <c r="B63">
-        <v>4.951</v>
+        <v>0.039</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>4.499</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2426,13 +2426,13 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46307.64583333334</v>
+        <v>46308.64583333334</v>
       </c>
       <c r="B64">
-        <v>4.264</v>
+        <v>0.805</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>0.068</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -2449,13 +2449,13 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46307.65625</v>
+        <v>46308.65625</v>
       </c>
       <c r="B65">
-        <v>4.204</v>
+        <v>15.287</v>
       </c>
       <c r="C65">
-        <v>0.209</v>
+        <v>0.006</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -2472,13 +2472,13 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46307.66666666666</v>
+        <v>46308.66666666666</v>
       </c>
       <c r="B66">
-        <v>0.008999999999999999</v>
+        <v>5.077</v>
       </c>
       <c r="C66">
-        <v>3.221</v>
+        <v>0.026</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -2495,13 +2495,13 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46307.67708333334</v>
+        <v>46308.67708333334</v>
       </c>
       <c r="B67">
-        <v>6.626</v>
+        <v>2.336</v>
       </c>
       <c r="C67">
-        <v>0.149</v>
+        <v>0.228</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -2518,13 +2518,13 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46307.6875</v>
+        <v>46308.6875</v>
       </c>
       <c r="B68">
-        <v>8.551</v>
+        <v>7.345</v>
       </c>
       <c r="C68">
-        <v>0.202</v>
+        <v>3.055</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -2541,10 +2541,10 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46307.69791666666</v>
+        <v>46308.69791666666</v>
       </c>
       <c r="B69">
-        <v>9.993</v>
+        <v>29.22</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46307.70833333334</v>
+        <v>46308.70833333334</v>
       </c>
       <c r="B70">
-        <v>21.216</v>
+        <v>45.926</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -2587,16 +2587,16 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46307.71875</v>
+        <v>46308.71875</v>
       </c>
       <c r="B71">
-        <v>27.372</v>
+        <v>33.501</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -2610,16 +2610,16 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46307.72916666666</v>
+        <v>46308.72916666666</v>
       </c>
       <c r="B72">
-        <v>30.942</v>
+        <v>20.465</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -2633,16 +2633,16 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46307.73958333334</v>
+        <v>46308.73958333334</v>
       </c>
       <c r="B73">
-        <v>42.228</v>
+        <v>33.458</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -2656,16 +2656,16 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46307.75</v>
+        <v>46308.75</v>
       </c>
       <c r="B74">
-        <v>23.597</v>
+        <v>33.998</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>25</v>
+        <v>62.5</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -2679,16 +2679,16 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46307.76041666666</v>
+        <v>46308.76041666666</v>
       </c>
       <c r="B75">
-        <v>39.344</v>
+        <v>5.812</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="D75">
-        <v>25</v>
+        <v>62.5</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -2702,16 +2702,16 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46307.77083333334</v>
+        <v>46308.77083333334</v>
       </c>
       <c r="B76">
-        <v>38.367</v>
+        <v>1.216</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="D76">
-        <v>25</v>
+        <v>62.5</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -2725,16 +2725,16 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46307.78125</v>
+        <v>46308.78125</v>
       </c>
       <c r="B77">
-        <v>13.747</v>
+        <v>10.626</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
       <c r="D77">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -2748,16 +2748,16 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46307.79166666666</v>
+        <v>46308.79166666666</v>
       </c>
       <c r="B78">
-        <v>0.358</v>
+        <v>19.292</v>
       </c>
       <c r="C78">
-        <v>0.182</v>
+        <v>0</v>
       </c>
       <c r="D78">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -2771,16 +2771,16 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46307.80208333334</v>
+        <v>46308.80208333334</v>
       </c>
       <c r="B79">
-        <v>0.07099999999999999</v>
+        <v>11.652</v>
       </c>
       <c r="C79">
-        <v>0.757</v>
+        <v>0</v>
       </c>
       <c r="D79">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46307.8125</v>
+        <v>46308.8125</v>
       </c>
       <c r="B80">
-        <v>0.052</v>
+        <v>0.078</v>
       </c>
       <c r="C80">
-        <v>6.41</v>
+        <v>4.721</v>
       </c>
       <c r="D80">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -2817,16 +2817,16 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46307.82291666666</v>
+        <v>46308.82291666666</v>
       </c>
       <c r="B81">
-        <v>0</v>
+        <v>0.674</v>
       </c>
       <c r="C81">
-        <v>14.232</v>
+        <v>2.922</v>
       </c>
       <c r="D81">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -2840,16 +2840,16 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46307.83333333334</v>
+        <v>46308.83333333334</v>
       </c>
       <c r="B82">
-        <v>0</v>
+        <v>2.605</v>
       </c>
       <c r="C82">
-        <v>9.557</v>
+        <v>0.274</v>
       </c>
       <c r="D82">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -2863,13 +2863,13 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46307.84375</v>
+        <v>46308.84375</v>
       </c>
       <c r="B83">
-        <v>0</v>
+        <v>8.93</v>
       </c>
       <c r="C83">
-        <v>12.023</v>
+        <v>0.125</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -2886,13 +2886,13 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46307.85416666666</v>
+        <v>46308.85416666666</v>
       </c>
       <c r="B84">
-        <v>0</v>
+        <v>2.812</v>
       </c>
       <c r="C84">
-        <v>8.84</v>
+        <v>1.225</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46307.86458333334</v>
+        <v>46308.86458333334</v>
       </c>
       <c r="B85">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="C85">
-        <v>11.671</v>
+        <v>3.494</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -2932,13 +2932,13 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46307.875</v>
+        <v>46308.875</v>
       </c>
       <c r="B86">
-        <v>0</v>
+        <v>6.143</v>
       </c>
       <c r="C86">
-        <v>6.681</v>
+        <v>0.528</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -2955,19 +2955,19 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46307.88541666666</v>
+        <v>46308.88541666666</v>
       </c>
       <c r="B87">
-        <v>0.021</v>
+        <v>12.648</v>
       </c>
       <c r="C87">
-        <v>3.771</v>
+        <v>0</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
       <c r="E87">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F87">
         <v>86</v>
@@ -2978,19 +2978,19 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46307.89583333334</v>
+        <v>46308.89583333334</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>7.303</v>
       </c>
       <c r="C88">
-        <v>3.07</v>
+        <v>2.496</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
       <c r="E88">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F88">
         <v>87</v>
@@ -3001,19 +3001,19 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46307.90625</v>
+        <v>46308.90625</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>1.099</v>
       </c>
       <c r="C89">
-        <v>9.669</v>
+        <v>1.153</v>
       </c>
       <c r="D89">
         <v>0</v>
       </c>
       <c r="E89">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F89">
         <v>88</v>
@@ -3024,19 +3024,19 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46307.91666666666</v>
+        <v>46308.91666666666</v>
       </c>
       <c r="B90">
-        <v>1.436</v>
+        <v>2.376</v>
       </c>
       <c r="C90">
-        <v>2.812</v>
+        <v>0</v>
       </c>
       <c r="D90">
         <v>0</v>
       </c>
       <c r="E90">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F90">
         <v>89</v>
@@ -3047,19 +3047,19 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46307.92708333334</v>
+        <v>46308.92708333334</v>
       </c>
       <c r="B91">
-        <v>11.18</v>
+        <v>29.442</v>
       </c>
       <c r="C91">
-        <v>1.169</v>
+        <v>0</v>
       </c>
       <c r="D91">
         <v>0</v>
       </c>
       <c r="E91">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F91">
         <v>90</v>
@@ -3070,19 +3070,19 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46307.9375</v>
+        <v>46308.9375</v>
       </c>
       <c r="B92">
-        <v>16.052</v>
+        <v>32.11</v>
       </c>
       <c r="C92">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="D92">
         <v>0</v>
       </c>
       <c r="E92">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F92">
         <v>91</v>
@@ -3093,19 +3093,19 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46307.94791666666</v>
+        <v>46308.94791666666</v>
       </c>
       <c r="B93">
-        <v>1.951</v>
+        <v>14.469</v>
       </c>
       <c r="C93">
-        <v>0.819</v>
+        <v>0.355</v>
       </c>
       <c r="D93">
         <v>0</v>
       </c>
       <c r="E93">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F93">
         <v>92</v>
@@ -3116,16 +3116,16 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46307.95833333334</v>
+        <v>46308.95833333334</v>
       </c>
       <c r="B94">
-        <v>2.929</v>
+        <v>22.199</v>
       </c>
       <c r="C94">
-        <v>0.317</v>
+        <v>0.021</v>
       </c>
       <c r="D94">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3139,16 +3139,16 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46307.96875</v>
+        <v>46308.96875</v>
       </c>
       <c r="B95">
-        <v>5.821</v>
+        <v>27.025</v>
       </c>
       <c r="C95">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -3162,16 +3162,16 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46307.97916666666</v>
+        <v>46308.97916666666</v>
       </c>
       <c r="B96">
-        <v>1.639</v>
+        <v>20.255</v>
       </c>
       <c r="C96">
-        <v>0.291</v>
+        <v>0</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -3185,16 +3185,16 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46307.98958333334</v>
+        <v>46308.98958333334</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>7.41</v>
       </c>
       <c r="C97">
-        <v>5.769</v>
+        <v>0</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -3208,16 +3208,16 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>30.169</v>
       </c>
       <c r="C98">
-        <v>4.041</v>
+        <v>0</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>35.5</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -3231,16 +3231,16 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46308.01041666666</v>
+        <v>46309.01041666666</v>
       </c>
       <c r="B99">
-        <v>0.04</v>
+        <v>8.423999999999999</v>
       </c>
       <c r="C99">
-        <v>0.985</v>
+        <v>0.015</v>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>52.5</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -3254,19 +3254,19 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46308.02083333334</v>
+        <v>46309.02083333334</v>
       </c>
       <c r="B100">
-        <v>0.045</v>
+        <v>8.657999999999999</v>
       </c>
       <c r="C100">
-        <v>1.859</v>
+        <v>0</v>
       </c>
       <c r="D100">
-        <v>0</v>
+        <v>52.5</v>
       </c>
       <c r="E100">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F100">
         <v>3</v>
@@ -3277,19 +3277,19 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46308.03125</v>
+        <v>46309.03125</v>
       </c>
       <c r="B101">
-        <v>10.617</v>
+        <v>11.691</v>
       </c>
       <c r="C101">
-        <v>0.268</v>
+        <v>0.219</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="E101">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F101">
         <v>4</v>
@@ -3300,19 +3300,19 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46308.04166666666</v>
+        <v>46309.04166666666</v>
       </c>
       <c r="B102">
-        <v>32.138</v>
+        <v>0.064</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>0.258</v>
       </c>
       <c r="D102">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E102">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F102">
         <v>5</v>
@@ -3323,19 +3323,19 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46308.05208333334</v>
+        <v>46309.05208333334</v>
       </c>
       <c r="B103">
-        <v>15.785</v>
+        <v>24.238</v>
       </c>
       <c r="C103">
         <v>0</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E103">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F103">
         <v>6</v>
@@ -3346,19 +3346,19 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46308.0625</v>
+        <v>46309.0625</v>
       </c>
       <c r="B104">
-        <v>17.488</v>
+        <v>30.263</v>
       </c>
       <c r="C104">
         <v>0</v>
       </c>
       <c r="D104">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E104">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F104">
         <v>7</v>
@@ -3369,16 +3369,16 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46308.07291666666</v>
+        <v>46309.07291666666</v>
       </c>
       <c r="B105">
-        <v>17.612</v>
+        <v>9.971</v>
       </c>
       <c r="C105">
         <v>0</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -3392,16 +3392,16 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46308.08333333334</v>
+        <v>46309.08333333334</v>
       </c>
       <c r="B106">
-        <v>1.712</v>
+        <v>19.339</v>
       </c>
       <c r="C106">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>20.25</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -3415,16 +3415,16 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46308.09375</v>
+        <v>46309.09375</v>
       </c>
       <c r="B107">
-        <v>11.01</v>
+        <v>1.022</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>0.163</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>20.25</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -3438,16 +3438,16 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46308.10416666666</v>
+        <v>46309.10416666666</v>
       </c>
       <c r="B108">
-        <v>6.306</v>
+        <v>0.7</v>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>2.485</v>
       </c>
       <c r="D108">
-        <v>0</v>
+        <v>20.25</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -3461,16 +3461,16 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46308.11458333334</v>
+        <v>46309.11458333334</v>
       </c>
       <c r="B109">
-        <v>3.038</v>
+        <v>0</v>
       </c>
       <c r="C109">
-        <v>0.704</v>
+        <v>9.531000000000001</v>
       </c>
       <c r="D109">
-        <v>0</v>
+        <v>20.25</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -3484,13 +3484,13 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46308.125</v>
+        <v>46309.125</v>
       </c>
       <c r="B110">
-        <v>6.785</v>
+        <v>0.9</v>
       </c>
       <c r="C110">
-        <v>0.363</v>
+        <v>0.539</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -3507,13 +3507,13 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46308.13541666666</v>
+        <v>46309.13541666666</v>
       </c>
       <c r="B111">
-        <v>3.505</v>
+        <v>0.115</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>2.663</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -3530,13 +3530,13 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46308.14583333334</v>
+        <v>46309.14583333334</v>
       </c>
       <c r="B112">
-        <v>0.42</v>
+        <v>8.617000000000001</v>
       </c>
       <c r="C112">
-        <v>2.537</v>
+        <v>0.515</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -3553,13 +3553,13 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46308.15625</v>
+        <v>46309.15625</v>
       </c>
       <c r="B113">
-        <v>0.023</v>
+        <v>2.309</v>
       </c>
       <c r="C113">
-        <v>1.066</v>
+        <v>0.021</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -3576,13 +3576,13 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46308.16666666666</v>
+        <v>46309.16666666666</v>
       </c>
       <c r="B114">
-        <v>0.358</v>
+        <v>14.866</v>
       </c>
       <c r="C114">
-        <v>1.293</v>
+        <v>0</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -3599,13 +3599,13 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46308.17708333334</v>
+        <v>46309.17708333334</v>
       </c>
       <c r="B115">
-        <v>0.043</v>
+        <v>13.077</v>
       </c>
       <c r="C115">
-        <v>0.528</v>
+        <v>0</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -3622,13 +3622,13 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46308.1875</v>
+        <v>46309.1875</v>
       </c>
       <c r="B116">
-        <v>0.6820000000000001</v>
+        <v>26.329</v>
       </c>
       <c r="C116">
-        <v>0.116</v>
+        <v>0</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -3645,13 +3645,13 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46308.19791666666</v>
+        <v>46309.19791666666</v>
       </c>
       <c r="B117">
-        <v>4.255</v>
+        <v>9.478</v>
       </c>
       <c r="C117">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -3668,13 +3668,13 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46308.20833333334</v>
+        <v>46309.20833333334</v>
       </c>
       <c r="B118">
-        <v>3.1</v>
+        <v>27.383</v>
       </c>
       <c r="C118">
-        <v>1.412</v>
+        <v>0</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -3691,13 +3691,13 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46308.21875</v>
+        <v>46309.21875</v>
       </c>
       <c r="B119">
-        <v>0.093</v>
+        <v>33.037</v>
       </c>
       <c r="C119">
-        <v>5.055</v>
+        <v>0</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46308.22916666666</v>
+        <v>46309.22916666666</v>
       </c>
       <c r="B120">
-        <v>0</v>
+        <v>12.231</v>
       </c>
       <c r="C120">
-        <v>6.974</v>
+        <v>0</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -3737,16 +3737,16 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46308.23958333334</v>
+        <v>46309.23958333334</v>
       </c>
       <c r="B121">
-        <v>0.537</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="C121">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -3760,16 +3760,16 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46308.25</v>
+        <v>46309.25</v>
       </c>
       <c r="B122">
-        <v>0</v>
+        <v>36.304</v>
       </c>
       <c r="C122">
-        <v>35.376</v>
+        <v>0</v>
       </c>
       <c r="D122">
-        <v>0</v>
+        <v>33.5</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -3783,16 +3783,16 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46308.26041666666</v>
+        <v>46309.26041666666</v>
       </c>
       <c r="B123">
-        <v>1.289</v>
+        <v>34.876</v>
       </c>
       <c r="C123">
-        <v>4.477</v>
+        <v>0</v>
       </c>
       <c r="D123">
-        <v>0</v>
+        <v>33.5</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -3806,16 +3806,16 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46308.27083333334</v>
+        <v>46309.27083333334</v>
       </c>
       <c r="B124">
-        <v>1.875</v>
+        <v>17.406</v>
       </c>
       <c r="C124">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>33.5</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -3829,16 +3829,16 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46308.28125</v>
+        <v>46309.28125</v>
       </c>
       <c r="B125">
-        <v>0.128</v>
+        <v>11.475</v>
       </c>
       <c r="C125">
-        <v>0.211</v>
+        <v>0</v>
       </c>
       <c r="D125">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -3852,16 +3852,16 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46308.29166666666</v>
+        <v>46309.29166666666</v>
       </c>
       <c r="B126">
-        <v>0</v>
+        <v>1.719</v>
       </c>
       <c r="C126">
-        <v>3.163</v>
+        <v>0</v>
       </c>
       <c r="D126">
-        <v>0</v>
+        <v>36.5</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -3875,16 +3875,16 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46308.30208333334</v>
+        <v>46309.30208333334</v>
       </c>
       <c r="B127">
-        <v>0.151</v>
+        <v>0.534</v>
       </c>
       <c r="C127">
-        <v>0.239</v>
+        <v>0.196</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>36.5</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -3898,16 +3898,16 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46308.3125</v>
+        <v>46309.3125</v>
       </c>
       <c r="B128">
-        <v>0.099</v>
+        <v>0.056</v>
       </c>
       <c r="C128">
-        <v>0.128</v>
+        <v>0.707</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>36.5</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -3921,13 +3921,13 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46308.32291666666</v>
+        <v>46309.32291666666</v>
       </c>
       <c r="B129">
-        <v>0.06</v>
+        <v>0.231</v>
       </c>
       <c r="C129">
-        <v>0.351</v>
+        <v>0.206</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -3944,19 +3944,19 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46308.33333333334</v>
+        <v>46309.33333333334</v>
       </c>
       <c r="B130">
-        <v>0.241</v>
+        <v>0.175</v>
       </c>
       <c r="C130">
-        <v>0.136</v>
+        <v>0.582</v>
       </c>
       <c r="D130">
         <v>0</v>
       </c>
       <c r="E130">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F130">
         <v>33</v>
@@ -3967,13 +3967,13 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46308.34375</v>
+        <v>46309.34375</v>
       </c>
       <c r="B131">
-        <v>0.581</v>
+        <v>0.598</v>
       </c>
       <c r="C131">
-        <v>0.2</v>
+        <v>0.194</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -3990,19 +3990,19 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46308.35416666666</v>
+        <v>46309.35416666666</v>
       </c>
       <c r="B132">
-        <v>0.09</v>
+        <v>0.319</v>
       </c>
       <c r="C132">
-        <v>0.275</v>
+        <v>12.862</v>
       </c>
       <c r="D132">
         <v>0</v>
       </c>
       <c r="E132">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="F132">
         <v>35</v>
@@ -4013,19 +4013,19 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46308.36458333334</v>
+        <v>46309.36458333334</v>
       </c>
       <c r="B133">
-        <v>0.129</v>
+        <v>0</v>
       </c>
       <c r="C133">
-        <v>0.122</v>
+        <v>14.059</v>
       </c>
       <c r="D133">
         <v>0</v>
       </c>
       <c r="E133">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="F133">
         <v>36</v>
@@ -4036,19 +4036,19 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46308.375</v>
+        <v>46309.375</v>
       </c>
       <c r="B134">
-        <v>0.341</v>
+        <v>0</v>
       </c>
       <c r="C134">
-        <v>1.473</v>
+        <v>7.86</v>
       </c>
       <c r="D134">
         <v>0</v>
       </c>
       <c r="E134">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F134">
         <v>37</v>
@@ -4059,13 +4059,13 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46308.38541666666</v>
+        <v>46309.38541666666</v>
       </c>
       <c r="B135">
-        <v>0.957</v>
+        <v>0.044</v>
       </c>
       <c r="C135">
-        <v>1.864</v>
+        <v>2.811</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -4082,19 +4082,19 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46308.39583333334</v>
+        <v>46309.39583333334</v>
       </c>
       <c r="B136">
-        <v>0.919</v>
+        <v>0.006</v>
       </c>
       <c r="C136">
-        <v>0.621</v>
+        <v>21.127</v>
       </c>
       <c r="D136">
         <v>0</v>
       </c>
       <c r="E136">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F136">
         <v>39</v>
@@ -4105,19 +4105,19 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46308.40625</v>
+        <v>46309.40625</v>
       </c>
       <c r="B137">
-        <v>1.853</v>
+        <v>0</v>
       </c>
       <c r="C137">
-        <v>4.535</v>
+        <v>17.576</v>
       </c>
       <c r="D137">
         <v>0</v>
       </c>
       <c r="E137">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F137">
         <v>40</v>
@@ -4128,19 +4128,19 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46308.41666666666</v>
+        <v>46309.41666666666</v>
       </c>
       <c r="B138">
-        <v>0.855</v>
+        <v>0.005</v>
       </c>
       <c r="C138">
-        <v>1.9</v>
+        <v>2.657</v>
       </c>
       <c r="D138">
         <v>0</v>
       </c>
       <c r="E138">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F138">
         <v>41</v>
@@ -4151,19 +4151,19 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46308.42708333334</v>
+        <v>46309.42708333334</v>
       </c>
       <c r="B139">
-        <v>9.939</v>
+        <v>0.011</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>9.708</v>
       </c>
       <c r="D139">
         <v>0</v>
       </c>
       <c r="E139">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F139">
         <v>42</v>
@@ -4174,13 +4174,13 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46308.4375</v>
+        <v>46309.4375</v>
       </c>
       <c r="B140">
-        <v>2.028</v>
+        <v>0</v>
       </c>
       <c r="C140">
-        <v>0.486</v>
+        <v>15.128</v>
       </c>
       <c r="D140">
         <v>0</v>
@@ -4197,13 +4197,13 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46308.44791666666</v>
+        <v>46309.44791666666</v>
       </c>
       <c r="B141">
-        <v>0.079</v>
+        <v>0</v>
       </c>
       <c r="C141">
-        <v>3.181</v>
+        <v>31.762</v>
       </c>
       <c r="D141">
         <v>0</v>
@@ -4220,13 +4220,13 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46308.45833333334</v>
+        <v>46309.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
       </c>
       <c r="C142">
-        <v>9.438000000000001</v>
+        <v>13.167</v>
       </c>
       <c r="D142">
         <v>0</v>
@@ -4243,19 +4243,19 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46308.46875</v>
+        <v>46309.46875</v>
       </c>
       <c r="B143">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="C143">
-        <v>8.981</v>
+        <v>8.395</v>
       </c>
       <c r="D143">
         <v>0</v>
       </c>
       <c r="E143">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F143">
         <v>46</v>
@@ -4266,13 +4266,13 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46308.47916666666</v>
+        <v>46309.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
       </c>
       <c r="C144">
-        <v>7.342</v>
+        <v>31.499</v>
       </c>
       <c r="D144">
         <v>0</v>
@@ -4289,19 +4289,19 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46308.48958333334</v>
+        <v>46309.48958333334</v>
       </c>
       <c r="B145">
-        <v>0.08400000000000001</v>
+        <v>0</v>
       </c>
       <c r="C145">
-        <v>1.318</v>
+        <v>68.86199999999999</v>
       </c>
       <c r="D145">
         <v>0</v>
       </c>
       <c r="E145">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F145">
         <v>48</v>
@@ -4312,19 +4312,19 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="B146">
         <v>0</v>
       </c>
       <c r="C146">
-        <v>14.256</v>
+        <v>51.701</v>
       </c>
       <c r="D146">
         <v>0</v>
       </c>
       <c r="E146">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F146">
         <v>49</v>
@@ -4335,19 +4335,19 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46308.51041666666</v>
+        <v>46309.51041666666</v>
       </c>
       <c r="B147">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="C147">
-        <v>13.297</v>
+        <v>88.294</v>
       </c>
       <c r="D147">
         <v>0</v>
       </c>
       <c r="E147">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F147">
         <v>50</v>
@@ -4358,19 +4358,19 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46308.52083333334</v>
+        <v>46309.52083333334</v>
       </c>
       <c r="B148">
-        <v>10.184</v>
+        <v>0</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>120.919</v>
       </c>
       <c r="D148">
         <v>0</v>
       </c>
       <c r="E148">
-        <v>62.5</v>
+        <v>37.5</v>
       </c>
       <c r="F148">
         <v>51</v>
@@ -4381,19 +4381,19 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46308.53125</v>
+        <v>46309.53125</v>
       </c>
       <c r="B149">
-        <v>32.523</v>
+        <v>0</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>64.994</v>
       </c>
       <c r="D149">
         <v>0</v>
       </c>
       <c r="E149">
-        <v>62.5</v>
+        <v>112.5</v>
       </c>
       <c r="F149">
         <v>52</v>
@@ -4404,19 +4404,19 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46308.54166666666</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="B150">
-        <v>25.538</v>
+        <v>0</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>29.621</v>
       </c>
       <c r="D150">
         <v>0</v>
       </c>
       <c r="E150">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="F150">
         <v>53</v>
@@ -4427,19 +4427,19 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46308.55208333334</v>
+        <v>46309.55208333334</v>
       </c>
       <c r="B151">
-        <v>33.614</v>
+        <v>0</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>5.159</v>
       </c>
       <c r="D151">
         <v>0</v>
       </c>
       <c r="E151">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="F151">
         <v>54</v>
@@ -4450,19 +4450,19 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46308.5625</v>
+        <v>46309.5625</v>
       </c>
       <c r="B152">
-        <v>24.849</v>
+        <v>0</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>33.385</v>
       </c>
       <c r="D152">
         <v>0</v>
       </c>
       <c r="E152">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F152">
         <v>55</v>
@@ -4473,19 +4473,19 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46308.57291666666</v>
+        <v>46309.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>68.017</v>
       </c>
       <c r="D153">
         <v>0</v>
       </c>
       <c r="E153">
-        <v>0</v>
+        <v>162.5</v>
       </c>
       <c r="F153">
         <v>56</v>
@@ -4496,19 +4496,19 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46308.58333333334</v>
+        <v>46309.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>65.83499999999999</v>
       </c>
       <c r="D154">
         <v>0</v>
       </c>
       <c r="E154">
-        <v>0</v>
+        <v>162.5</v>
       </c>
       <c r="F154">
         <v>57</v>
@@ -4519,19 +4519,19 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46308.59375</v>
+        <v>46309.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>28.542</v>
       </c>
       <c r="D155">
         <v>0</v>
       </c>
       <c r="E155">
-        <v>0</v>
+        <v>187.5</v>
       </c>
       <c r="F155">
         <v>58</v>
@@ -4542,19 +4542,19 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46308.60416666666</v>
+        <v>46309.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>50.258</v>
       </c>
       <c r="D156">
         <v>0</v>
       </c>
       <c r="E156">
-        <v>0</v>
+        <v>187.5</v>
       </c>
       <c r="F156">
         <v>59</v>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46308.61458333334</v>
+        <v>46309.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4577,7 +4577,7 @@
         <v>0</v>
       </c>
       <c r="E157">
-        <v>0</v>
+        <v>187.5</v>
       </c>
       <c r="F157">
         <v>60</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46308.625</v>
+        <v>46309.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4611,7 +4611,7 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46308.63541666666</v>
+        <v>46309.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46308.64583333334</v>
+        <v>46309.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46308.65625</v>
+        <v>46309.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46308.66666666666</v>
+        <v>46309.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46308.67708333334</v>
+        <v>46309.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46308.6875</v>
+        <v>46309.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46308.69791666666</v>
+        <v>46309.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4772,7 +4772,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46308.70833333334</v>
+        <v>46309.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46308.71875</v>
+        <v>46309.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46308.72916666666</v>
+        <v>46309.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46308.73958333334</v>
+        <v>46309.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46308.75</v>
+        <v>46309.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46308.76041666666</v>
+        <v>46309.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46308.77083333334</v>
+        <v>46309.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46308.78125</v>
+        <v>46309.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46308.79166666666</v>
+        <v>46309.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46308.80208333334</v>
+        <v>46309.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46308.8125</v>
+        <v>46309.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -5025,7 +5025,7 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46308.82291666666</v>
+        <v>46309.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46308.83333333334</v>
+        <v>46309.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -5071,7 +5071,7 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46308.84375</v>
+        <v>46309.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -5094,7 +5094,7 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46308.85416666666</v>
+        <v>46309.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46308.86458333334</v>
+        <v>46309.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46308.875</v>
+        <v>46309.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46308.88541666666</v>
+        <v>46309.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46308.89583333334</v>
+        <v>46309.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46308.90625</v>
+        <v>46309.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46308.91666666666</v>
+        <v>46309.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46308.92708333334</v>
+        <v>46309.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46308.9375</v>
+        <v>46309.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46308.94791666666</v>
+        <v>46309.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46308.95833333334</v>
+        <v>46309.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -5347,7 +5347,7 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46308.96875</v>
+        <v>46309.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46308.97916666666</v>
+        <v>46309.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46308.98958333334</v>
+        <v>46309.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -37,580 +37,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>13.10.20261</t>
-  </si>
-  <si>
-    <t>13.10.20262</t>
-  </si>
-  <si>
-    <t>13.10.20263</t>
-  </si>
-  <si>
-    <t>13.10.20264</t>
-  </si>
-  <si>
-    <t>13.10.20265</t>
-  </si>
-  <si>
-    <t>13.10.20266</t>
-  </si>
-  <si>
-    <t>13.10.20267</t>
-  </si>
-  <si>
-    <t>13.10.20268</t>
-  </si>
-  <si>
-    <t>13.10.20269</t>
-  </si>
-  <si>
-    <t>13.10.202610</t>
-  </si>
-  <si>
-    <t>13.10.202611</t>
-  </si>
-  <si>
-    <t>13.10.202612</t>
-  </si>
-  <si>
-    <t>13.10.202613</t>
-  </si>
-  <si>
-    <t>13.10.202614</t>
-  </si>
-  <si>
-    <t>13.10.202615</t>
-  </si>
-  <si>
-    <t>13.10.202616</t>
-  </si>
-  <si>
-    <t>13.10.202617</t>
-  </si>
-  <si>
-    <t>13.10.202618</t>
-  </si>
-  <si>
-    <t>13.10.202619</t>
-  </si>
-  <si>
-    <t>13.10.202620</t>
-  </si>
-  <si>
-    <t>13.10.202621</t>
-  </si>
-  <si>
-    <t>13.10.202622</t>
-  </si>
-  <si>
-    <t>13.10.202623</t>
-  </si>
-  <si>
-    <t>13.10.202624</t>
-  </si>
-  <si>
-    <t>13.10.202625</t>
-  </si>
-  <si>
-    <t>13.10.202626</t>
-  </si>
-  <si>
-    <t>13.10.202627</t>
-  </si>
-  <si>
-    <t>13.10.202628</t>
-  </si>
-  <si>
-    <t>13.10.202629</t>
-  </si>
-  <si>
-    <t>13.10.202630</t>
-  </si>
-  <si>
-    <t>13.10.202631</t>
-  </si>
-  <si>
-    <t>13.10.202632</t>
-  </si>
-  <si>
-    <t>13.10.202633</t>
-  </si>
-  <si>
-    <t>13.10.202634</t>
-  </si>
-  <si>
-    <t>13.10.202635</t>
-  </si>
-  <si>
-    <t>13.10.202636</t>
-  </si>
-  <si>
-    <t>13.10.202637</t>
-  </si>
-  <si>
-    <t>13.10.202638</t>
-  </si>
-  <si>
-    <t>13.10.202639</t>
-  </si>
-  <si>
-    <t>13.10.202640</t>
-  </si>
-  <si>
-    <t>13.10.202641</t>
-  </si>
-  <si>
-    <t>13.10.202642</t>
-  </si>
-  <si>
-    <t>13.10.202643</t>
-  </si>
-  <si>
-    <t>13.10.202644</t>
-  </si>
-  <si>
-    <t>13.10.202645</t>
-  </si>
-  <si>
-    <t>13.10.202646</t>
-  </si>
-  <si>
-    <t>13.10.202647</t>
-  </si>
-  <si>
-    <t>13.10.202648</t>
-  </si>
-  <si>
-    <t>13.10.202649</t>
-  </si>
-  <si>
-    <t>13.10.202650</t>
-  </si>
-  <si>
-    <t>13.10.202651</t>
-  </si>
-  <si>
-    <t>13.10.202652</t>
-  </si>
-  <si>
-    <t>13.10.202653</t>
-  </si>
-  <si>
-    <t>13.10.202654</t>
-  </si>
-  <si>
-    <t>13.10.202655</t>
-  </si>
-  <si>
-    <t>13.10.202656</t>
-  </si>
-  <si>
-    <t>13.10.202657</t>
-  </si>
-  <si>
-    <t>13.10.202658</t>
-  </si>
-  <si>
-    <t>13.10.202659</t>
-  </si>
-  <si>
-    <t>13.10.202660</t>
-  </si>
-  <si>
-    <t>13.10.202661</t>
-  </si>
-  <si>
-    <t>13.10.202662</t>
-  </si>
-  <si>
-    <t>13.10.202663</t>
-  </si>
-  <si>
-    <t>13.10.202664</t>
-  </si>
-  <si>
-    <t>13.10.202665</t>
-  </si>
-  <si>
-    <t>13.10.202666</t>
-  </si>
-  <si>
-    <t>13.10.202667</t>
-  </si>
-  <si>
-    <t>13.10.202668</t>
-  </si>
-  <si>
-    <t>13.10.202669</t>
-  </si>
-  <si>
-    <t>13.10.202670</t>
-  </si>
-  <si>
-    <t>13.10.202671</t>
-  </si>
-  <si>
-    <t>13.10.202672</t>
-  </si>
-  <si>
-    <t>13.10.202673</t>
-  </si>
-  <si>
-    <t>13.10.202674</t>
-  </si>
-  <si>
-    <t>13.10.202675</t>
-  </si>
-  <si>
-    <t>13.10.202676</t>
-  </si>
-  <si>
-    <t>13.10.202677</t>
-  </si>
-  <si>
-    <t>13.10.202678</t>
-  </si>
-  <si>
-    <t>13.10.202679</t>
-  </si>
-  <si>
-    <t>13.10.202680</t>
-  </si>
-  <si>
-    <t>13.10.202681</t>
-  </si>
-  <si>
-    <t>13.10.202682</t>
-  </si>
-  <si>
-    <t>13.10.202683</t>
-  </si>
-  <si>
-    <t>13.10.202684</t>
-  </si>
-  <si>
-    <t>13.10.202685</t>
-  </si>
-  <si>
-    <t>13.10.202686</t>
-  </si>
-  <si>
-    <t>13.10.202687</t>
-  </si>
-  <si>
-    <t>13.10.202688</t>
-  </si>
-  <si>
-    <t>13.10.202689</t>
-  </si>
-  <si>
-    <t>13.10.202690</t>
-  </si>
-  <si>
-    <t>13.10.202691</t>
-  </si>
-  <si>
-    <t>13.10.202692</t>
-  </si>
-  <si>
-    <t>13.10.202693</t>
-  </si>
-  <si>
-    <t>13.10.202694</t>
-  </si>
-  <si>
-    <t>13.10.202695</t>
-  </si>
-  <si>
-    <t>13.10.202696</t>
-  </si>
-  <si>
-    <t>14.10.20261</t>
-  </si>
-  <si>
-    <t>14.10.20262</t>
-  </si>
-  <si>
-    <t>14.10.20263</t>
-  </si>
-  <si>
-    <t>14.10.20264</t>
-  </si>
-  <si>
-    <t>14.10.20265</t>
-  </si>
-  <si>
-    <t>14.10.20266</t>
-  </si>
-  <si>
-    <t>14.10.20267</t>
-  </si>
-  <si>
-    <t>14.10.20268</t>
-  </si>
-  <si>
-    <t>14.10.20269</t>
-  </si>
-  <si>
-    <t>14.10.202610</t>
-  </si>
-  <si>
-    <t>14.10.202611</t>
-  </si>
-  <si>
-    <t>14.10.202612</t>
-  </si>
-  <si>
-    <t>14.10.202613</t>
-  </si>
-  <si>
-    <t>14.10.202614</t>
-  </si>
-  <si>
-    <t>14.10.202615</t>
-  </si>
-  <si>
-    <t>14.10.202616</t>
-  </si>
-  <si>
-    <t>14.10.202617</t>
-  </si>
-  <si>
-    <t>14.10.202618</t>
-  </si>
-  <si>
-    <t>14.10.202619</t>
-  </si>
-  <si>
-    <t>14.10.202620</t>
-  </si>
-  <si>
-    <t>14.10.202621</t>
-  </si>
-  <si>
-    <t>14.10.202622</t>
-  </si>
-  <si>
-    <t>14.10.202623</t>
-  </si>
-  <si>
-    <t>14.10.202624</t>
-  </si>
-  <si>
-    <t>14.10.202625</t>
-  </si>
-  <si>
-    <t>14.10.202626</t>
-  </si>
-  <si>
-    <t>14.10.202627</t>
-  </si>
-  <si>
-    <t>14.10.202628</t>
-  </si>
-  <si>
-    <t>14.10.202629</t>
-  </si>
-  <si>
-    <t>14.10.202630</t>
-  </si>
-  <si>
-    <t>14.10.202631</t>
-  </si>
-  <si>
-    <t>14.10.202632</t>
-  </si>
-  <si>
-    <t>14.10.202633</t>
-  </si>
-  <si>
-    <t>14.10.202634</t>
-  </si>
-  <si>
-    <t>14.10.202635</t>
-  </si>
-  <si>
-    <t>14.10.202636</t>
-  </si>
-  <si>
-    <t>14.10.202637</t>
-  </si>
-  <si>
-    <t>14.10.202638</t>
-  </si>
-  <si>
-    <t>14.10.202639</t>
-  </si>
-  <si>
-    <t>14.10.202640</t>
-  </si>
-  <si>
-    <t>14.10.202641</t>
-  </si>
-  <si>
-    <t>14.10.202642</t>
-  </si>
-  <si>
-    <t>14.10.202643</t>
-  </si>
-  <si>
-    <t>14.10.202644</t>
-  </si>
-  <si>
-    <t>14.10.202645</t>
-  </si>
-  <si>
-    <t>14.10.202646</t>
-  </si>
-  <si>
-    <t>14.10.202647</t>
-  </si>
-  <si>
-    <t>14.10.202648</t>
-  </si>
-  <si>
-    <t>14.10.202649</t>
-  </si>
-  <si>
-    <t>14.10.202650</t>
-  </si>
-  <si>
-    <t>14.10.202651</t>
-  </si>
-  <si>
-    <t>14.10.202652</t>
-  </si>
-  <si>
-    <t>14.10.202653</t>
-  </si>
-  <si>
-    <t>14.10.202654</t>
-  </si>
-  <si>
-    <t>14.10.202655</t>
-  </si>
-  <si>
-    <t>14.10.202656</t>
-  </si>
-  <si>
-    <t>14.10.202657</t>
-  </si>
-  <si>
-    <t>14.10.202658</t>
-  </si>
-  <si>
-    <t>14.10.202659</t>
-  </si>
-  <si>
-    <t>14.10.202660</t>
-  </si>
-  <si>
-    <t>14.10.202661</t>
-  </si>
-  <si>
-    <t>14.10.202662</t>
-  </si>
-  <si>
-    <t>14.10.202663</t>
-  </si>
-  <si>
-    <t>14.10.202664</t>
-  </si>
-  <si>
-    <t>14.10.202665</t>
-  </si>
-  <si>
-    <t>14.10.202666</t>
-  </si>
-  <si>
-    <t>14.10.202667</t>
-  </si>
-  <si>
-    <t>14.10.202668</t>
-  </si>
-  <si>
-    <t>14.10.202669</t>
-  </si>
-  <si>
-    <t>14.10.202670</t>
-  </si>
-  <si>
-    <t>14.10.202671</t>
-  </si>
-  <si>
-    <t>14.10.202672</t>
-  </si>
-  <si>
-    <t>14.10.202673</t>
-  </si>
-  <si>
-    <t>14.10.202674</t>
-  </si>
-  <si>
-    <t>14.10.202675</t>
-  </si>
-  <si>
-    <t>14.10.202676</t>
-  </si>
-  <si>
-    <t>14.10.202677</t>
-  </si>
-  <si>
-    <t>14.10.202678</t>
-  </si>
-  <si>
-    <t>14.10.202679</t>
-  </si>
-  <si>
-    <t>14.10.202680</t>
-  </si>
-  <si>
-    <t>14.10.202681</t>
-  </si>
-  <si>
-    <t>14.10.202682</t>
-  </si>
-  <si>
-    <t>14.10.202683</t>
-  </si>
-  <si>
-    <t>14.10.202684</t>
-  </si>
-  <si>
-    <t>14.10.202685</t>
-  </si>
-  <si>
-    <t>14.10.202686</t>
-  </si>
-  <si>
-    <t>14.10.202687</t>
-  </si>
-  <si>
-    <t>14.10.202688</t>
-  </si>
-  <si>
-    <t>14.10.202689</t>
-  </si>
-  <si>
-    <t>14.10.202690</t>
-  </si>
-  <si>
-    <t>14.10.202691</t>
-  </si>
-  <si>
-    <t>14.10.202692</t>
-  </si>
-  <si>
-    <t>14.10.202693</t>
-  </si>
-  <si>
-    <t>14.10.202694</t>
-  </si>
-  <si>
-    <t>14.10.202695</t>
-  </si>
-  <si>
-    <t>14.10.202696</t>
+    <t>15.10.20261</t>
+  </si>
+  <si>
+    <t>15.10.20262</t>
+  </si>
+  <si>
+    <t>15.10.20263</t>
+  </si>
+  <si>
+    <t>15.10.20264</t>
+  </si>
+  <si>
+    <t>15.10.20265</t>
+  </si>
+  <si>
+    <t>15.10.20266</t>
+  </si>
+  <si>
+    <t>15.10.20267</t>
+  </si>
+  <si>
+    <t>15.10.20268</t>
+  </si>
+  <si>
+    <t>15.10.20269</t>
+  </si>
+  <si>
+    <t>15.10.202610</t>
+  </si>
+  <si>
+    <t>15.10.202611</t>
+  </si>
+  <si>
+    <t>15.10.202612</t>
+  </si>
+  <si>
+    <t>15.10.202613</t>
+  </si>
+  <si>
+    <t>15.10.202614</t>
+  </si>
+  <si>
+    <t>15.10.202615</t>
+  </si>
+  <si>
+    <t>15.10.202616</t>
+  </si>
+  <si>
+    <t>15.10.202617</t>
+  </si>
+  <si>
+    <t>15.10.202618</t>
+  </si>
+  <si>
+    <t>15.10.202619</t>
+  </si>
+  <si>
+    <t>15.10.202620</t>
+  </si>
+  <si>
+    <t>15.10.202621</t>
+  </si>
+  <si>
+    <t>15.10.202622</t>
+  </si>
+  <si>
+    <t>15.10.202623</t>
+  </si>
+  <si>
+    <t>15.10.202624</t>
+  </si>
+  <si>
+    <t>15.10.202625</t>
+  </si>
+  <si>
+    <t>15.10.202626</t>
+  </si>
+  <si>
+    <t>15.10.202627</t>
+  </si>
+  <si>
+    <t>15.10.202628</t>
+  </si>
+  <si>
+    <t>15.10.202629</t>
+  </si>
+  <si>
+    <t>15.10.202630</t>
+  </si>
+  <si>
+    <t>15.10.202631</t>
+  </si>
+  <si>
+    <t>15.10.202632</t>
+  </si>
+  <si>
+    <t>15.10.202633</t>
+  </si>
+  <si>
+    <t>15.10.202634</t>
+  </si>
+  <si>
+    <t>15.10.202635</t>
+  </si>
+  <si>
+    <t>15.10.202636</t>
+  </si>
+  <si>
+    <t>15.10.202637</t>
+  </si>
+  <si>
+    <t>15.10.202638</t>
+  </si>
+  <si>
+    <t>15.10.202639</t>
+  </si>
+  <si>
+    <t>15.10.202640</t>
+  </si>
+  <si>
+    <t>15.10.202641</t>
+  </si>
+  <si>
+    <t>15.10.202642</t>
+  </si>
+  <si>
+    <t>15.10.202643</t>
+  </si>
+  <si>
+    <t>15.10.202644</t>
+  </si>
+  <si>
+    <t>15.10.202645</t>
+  </si>
+  <si>
+    <t>15.10.202646</t>
+  </si>
+  <si>
+    <t>15.10.202647</t>
+  </si>
+  <si>
+    <t>15.10.202648</t>
+  </si>
+  <si>
+    <t>15.10.202649</t>
+  </si>
+  <si>
+    <t>15.10.202650</t>
+  </si>
+  <si>
+    <t>15.10.202651</t>
+  </si>
+  <si>
+    <t>15.10.202652</t>
+  </si>
+  <si>
+    <t>15.10.202653</t>
+  </si>
+  <si>
+    <t>15.10.202654</t>
+  </si>
+  <si>
+    <t>15.10.202655</t>
+  </si>
+  <si>
+    <t>15.10.202656</t>
+  </si>
+  <si>
+    <t>15.10.202657</t>
+  </si>
+  <si>
+    <t>15.10.202658</t>
+  </si>
+  <si>
+    <t>15.10.202659</t>
+  </si>
+  <si>
+    <t>15.10.202660</t>
+  </si>
+  <si>
+    <t>15.10.202661</t>
+  </si>
+  <si>
+    <t>15.10.202662</t>
+  </si>
+  <si>
+    <t>15.10.202663</t>
+  </si>
+  <si>
+    <t>15.10.202664</t>
+  </si>
+  <si>
+    <t>15.10.202665</t>
+  </si>
+  <si>
+    <t>15.10.202666</t>
+  </si>
+  <si>
+    <t>15.10.202667</t>
+  </si>
+  <si>
+    <t>15.10.202668</t>
+  </si>
+  <si>
+    <t>15.10.202669</t>
+  </si>
+  <si>
+    <t>15.10.202670</t>
+  </si>
+  <si>
+    <t>15.10.202671</t>
+  </si>
+  <si>
+    <t>15.10.202672</t>
+  </si>
+  <si>
+    <t>15.10.202673</t>
+  </si>
+  <si>
+    <t>15.10.202674</t>
+  </si>
+  <si>
+    <t>15.10.202675</t>
+  </si>
+  <si>
+    <t>15.10.202676</t>
+  </si>
+  <si>
+    <t>15.10.202677</t>
+  </si>
+  <si>
+    <t>15.10.202678</t>
+  </si>
+  <si>
+    <t>15.10.202679</t>
+  </si>
+  <si>
+    <t>15.10.202680</t>
+  </si>
+  <si>
+    <t>15.10.202681</t>
+  </si>
+  <si>
+    <t>15.10.202682</t>
+  </si>
+  <si>
+    <t>15.10.202683</t>
+  </si>
+  <si>
+    <t>15.10.202684</t>
+  </si>
+  <si>
+    <t>15.10.202685</t>
+  </si>
+  <si>
+    <t>15.10.202686</t>
+  </si>
+  <si>
+    <t>15.10.202687</t>
+  </si>
+  <si>
+    <t>15.10.202688</t>
+  </si>
+  <si>
+    <t>15.10.202689</t>
+  </si>
+  <si>
+    <t>15.10.202690</t>
+  </si>
+  <si>
+    <t>15.10.202691</t>
+  </si>
+  <si>
+    <t>15.10.202692</t>
+  </si>
+  <si>
+    <t>15.10.202693</t>
+  </si>
+  <si>
+    <t>15.10.202694</t>
+  </si>
+  <si>
+    <t>15.10.202695</t>
+  </si>
+  <si>
+    <t>15.10.202696</t>
+  </si>
+  <si>
+    <t>16.10.20261</t>
+  </si>
+  <si>
+    <t>16.10.20262</t>
+  </si>
+  <si>
+    <t>16.10.20263</t>
+  </si>
+  <si>
+    <t>16.10.20264</t>
+  </si>
+  <si>
+    <t>16.10.20265</t>
+  </si>
+  <si>
+    <t>16.10.20266</t>
+  </si>
+  <si>
+    <t>16.10.20267</t>
+  </si>
+  <si>
+    <t>16.10.20268</t>
+  </si>
+  <si>
+    <t>16.10.20269</t>
+  </si>
+  <si>
+    <t>16.10.202610</t>
+  </si>
+  <si>
+    <t>16.10.202611</t>
+  </si>
+  <si>
+    <t>16.10.202612</t>
+  </si>
+  <si>
+    <t>16.10.202613</t>
+  </si>
+  <si>
+    <t>16.10.202614</t>
+  </si>
+  <si>
+    <t>16.10.202615</t>
+  </si>
+  <si>
+    <t>16.10.202616</t>
+  </si>
+  <si>
+    <t>16.10.202617</t>
+  </si>
+  <si>
+    <t>16.10.202618</t>
+  </si>
+  <si>
+    <t>16.10.202619</t>
+  </si>
+  <si>
+    <t>16.10.202620</t>
+  </si>
+  <si>
+    <t>16.10.202621</t>
+  </si>
+  <si>
+    <t>16.10.202622</t>
+  </si>
+  <si>
+    <t>16.10.202623</t>
+  </si>
+  <si>
+    <t>16.10.202624</t>
+  </si>
+  <si>
+    <t>16.10.202625</t>
+  </si>
+  <si>
+    <t>16.10.202626</t>
+  </si>
+  <si>
+    <t>16.10.202627</t>
+  </si>
+  <si>
+    <t>16.10.202628</t>
+  </si>
+  <si>
+    <t>16.10.202629</t>
+  </si>
+  <si>
+    <t>16.10.202630</t>
+  </si>
+  <si>
+    <t>16.10.202631</t>
+  </si>
+  <si>
+    <t>16.10.202632</t>
+  </si>
+  <si>
+    <t>16.10.202633</t>
+  </si>
+  <si>
+    <t>16.10.202634</t>
+  </si>
+  <si>
+    <t>16.10.202635</t>
+  </si>
+  <si>
+    <t>16.10.202636</t>
+  </si>
+  <si>
+    <t>16.10.202637</t>
+  </si>
+  <si>
+    <t>16.10.202638</t>
+  </si>
+  <si>
+    <t>16.10.202639</t>
+  </si>
+  <si>
+    <t>16.10.202640</t>
+  </si>
+  <si>
+    <t>16.10.202641</t>
+  </si>
+  <si>
+    <t>16.10.202642</t>
+  </si>
+  <si>
+    <t>16.10.202643</t>
+  </si>
+  <si>
+    <t>16.10.202644</t>
+  </si>
+  <si>
+    <t>16.10.202645</t>
+  </si>
+  <si>
+    <t>16.10.202646</t>
+  </si>
+  <si>
+    <t>16.10.202647</t>
+  </si>
+  <si>
+    <t>16.10.202648</t>
+  </si>
+  <si>
+    <t>16.10.202649</t>
+  </si>
+  <si>
+    <t>16.10.202650</t>
+  </si>
+  <si>
+    <t>16.10.202651</t>
+  </si>
+  <si>
+    <t>16.10.202652</t>
+  </si>
+  <si>
+    <t>16.10.202653</t>
+  </si>
+  <si>
+    <t>16.10.202654</t>
+  </si>
+  <si>
+    <t>16.10.202655</t>
+  </si>
+  <si>
+    <t>16.10.202656</t>
+  </si>
+  <si>
+    <t>16.10.202657</t>
+  </si>
+  <si>
+    <t>16.10.202658</t>
+  </si>
+  <si>
+    <t>16.10.202659</t>
+  </si>
+  <si>
+    <t>16.10.202660</t>
+  </si>
+  <si>
+    <t>16.10.202661</t>
+  </si>
+  <si>
+    <t>16.10.202662</t>
+  </si>
+  <si>
+    <t>16.10.202663</t>
+  </si>
+  <si>
+    <t>16.10.202664</t>
+  </si>
+  <si>
+    <t>16.10.202665</t>
+  </si>
+  <si>
+    <t>16.10.202666</t>
+  </si>
+  <si>
+    <t>16.10.202667</t>
+  </si>
+  <si>
+    <t>16.10.202668</t>
+  </si>
+  <si>
+    <t>16.10.202669</t>
+  </si>
+  <si>
+    <t>16.10.202670</t>
+  </si>
+  <si>
+    <t>16.10.202671</t>
+  </si>
+  <si>
+    <t>16.10.202672</t>
+  </si>
+  <si>
+    <t>16.10.202673</t>
+  </si>
+  <si>
+    <t>16.10.202674</t>
+  </si>
+  <si>
+    <t>16.10.202675</t>
+  </si>
+  <si>
+    <t>16.10.202676</t>
+  </si>
+  <si>
+    <t>16.10.202677</t>
+  </si>
+  <si>
+    <t>16.10.202678</t>
+  </si>
+  <si>
+    <t>16.10.202679</t>
+  </si>
+  <si>
+    <t>16.10.202680</t>
+  </si>
+  <si>
+    <t>16.10.202681</t>
+  </si>
+  <si>
+    <t>16.10.202682</t>
+  </si>
+  <si>
+    <t>16.10.202683</t>
+  </si>
+  <si>
+    <t>16.10.202684</t>
+  </si>
+  <si>
+    <t>16.10.202685</t>
+  </si>
+  <si>
+    <t>16.10.202686</t>
+  </si>
+  <si>
+    <t>16.10.202687</t>
+  </si>
+  <si>
+    <t>16.10.202688</t>
+  </si>
+  <si>
+    <t>16.10.202689</t>
+  </si>
+  <si>
+    <t>16.10.202690</t>
+  </si>
+  <si>
+    <t>16.10.202691</t>
+  </si>
+  <si>
+    <t>16.10.202692</t>
+  </si>
+  <si>
+    <t>16.10.202693</t>
+  </si>
+  <si>
+    <t>16.10.202694</t>
+  </si>
+  <si>
+    <t>16.10.202695</t>
+  </si>
+  <si>
+    <t>16.10.202696</t>
   </si>
 </sst>
 </file>
@@ -1000,16 +1000,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>21.768</v>
       </c>
       <c r="C2">
-        <v>4.041</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>20.25</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1023,16 +1023,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46308.01041666666</v>
+        <v>46310.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.04</v>
+        <v>6.192</v>
       </c>
       <c r="C3">
-        <v>0.985</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1046,19 +1046,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46308.02083333334</v>
+        <v>46310.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.045</v>
+        <v>4.244</v>
       </c>
       <c r="C4">
-        <v>1.859</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>15.25</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -1069,19 +1069,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46308.03125</v>
+        <v>46310.03125</v>
       </c>
       <c r="B5">
-        <v>10.617</v>
+        <v>16.19</v>
       </c>
       <c r="C5">
-        <v>0.268</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -1092,19 +1092,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46308.04166666666</v>
+        <v>46310.04166666666</v>
       </c>
       <c r="B6">
-        <v>32.138</v>
+        <v>2.898</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>11.25</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46308.05208333334</v>
+        <v>46310.05208333334</v>
       </c>
       <c r="B7">
-        <v>15.785</v>
+        <v>12.534</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -1138,19 +1138,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46308.0625</v>
+        <v>46310.0625</v>
       </c>
       <c r="B8">
-        <v>17.488</v>
+        <v>0.412</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>4.522</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -1161,13 +1161,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46308.07291666666</v>
+        <v>46310.07291666666</v>
       </c>
       <c r="B9">
-        <v>17.612</v>
+        <v>0.042</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1.649</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1184,13 +1184,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46308.08333333334</v>
+        <v>46310.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.712</v>
+        <v>0.008</v>
       </c>
       <c r="C10">
-        <v>0.01</v>
+        <v>3.463</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1207,13 +1207,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46308.09375</v>
+        <v>46310.09375</v>
       </c>
       <c r="B11">
-        <v>11.01</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>4.799</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1230,13 +1230,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46308.10416666666</v>
+        <v>46310.10416666666</v>
       </c>
       <c r="B12">
-        <v>6.306</v>
+        <v>0.77</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1253,13 +1253,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46308.11458333334</v>
+        <v>46310.11458333334</v>
       </c>
       <c r="B13">
-        <v>3.038</v>
+        <v>15.815</v>
       </c>
       <c r="C13">
-        <v>0.704</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1276,13 +1276,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46308.125</v>
+        <v>46310.125</v>
       </c>
       <c r="B14">
-        <v>6.785</v>
+        <v>10.129</v>
       </c>
       <c r="C14">
-        <v>0.363</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1299,13 +1299,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46308.13541666666</v>
+        <v>46310.13541666666</v>
       </c>
       <c r="B15">
-        <v>3.505</v>
+        <v>5.931</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>0.382</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1322,13 +1322,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46308.14583333334</v>
+        <v>46310.14583333334</v>
       </c>
       <c r="B16">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>2.537</v>
+        <v>2.627</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46308.15625</v>
+        <v>46310.15625</v>
       </c>
       <c r="B17">
-        <v>0.023</v>
+        <v>0.043</v>
       </c>
       <c r="C17">
-        <v>1.066</v>
+        <v>0.491</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1368,13 +1368,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46308.16666666666</v>
+        <v>46310.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.358</v>
+        <v>0.007</v>
       </c>
       <c r="C18">
-        <v>1.293</v>
+        <v>4.836</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1391,13 +1391,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46308.17708333334</v>
+        <v>46310.17708333334</v>
       </c>
       <c r="B19">
-        <v>0.043</v>
+        <v>0.001</v>
       </c>
       <c r="C19">
-        <v>0.528</v>
+        <v>8.992000000000001</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1414,13 +1414,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46308.1875</v>
+        <v>46310.1875</v>
       </c>
       <c r="B20">
-        <v>0.6820000000000001</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>0.116</v>
+        <v>9.448</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1437,13 +1437,13 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46308.19791666666</v>
+        <v>46310.19791666666</v>
       </c>
       <c r="B21">
-        <v>4.255</v>
+        <v>4.112</v>
       </c>
       <c r="C21">
-        <v>0.09</v>
+        <v>1.818</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1460,13 +1460,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46308.20833333334</v>
+        <v>46310.20833333334</v>
       </c>
       <c r="B22">
-        <v>3.1</v>
+        <v>20.627</v>
       </c>
       <c r="C22">
-        <v>1.412</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1483,13 +1483,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46308.21875</v>
+        <v>46310.21875</v>
       </c>
       <c r="B23">
-        <v>0.093</v>
+        <v>19.445</v>
       </c>
       <c r="C23">
-        <v>5.055</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1506,13 +1506,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46308.22916666666</v>
+        <v>46310.22916666666</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>18.638</v>
       </c>
       <c r="C24">
-        <v>6.974</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1529,13 +1529,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46308.23958333334</v>
+        <v>46310.23958333334</v>
       </c>
       <c r="B25">
-        <v>0.537</v>
+        <v>38.082</v>
       </c>
       <c r="C25">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1552,13 +1552,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46308.25</v>
+        <v>46310.25</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>18.861</v>
       </c>
       <c r="C26">
-        <v>35.376</v>
+        <v>0</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1575,13 +1575,13 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46308.26041666666</v>
+        <v>46310.26041666666</v>
       </c>
       <c r="B27">
-        <v>1.289</v>
+        <v>39.825</v>
       </c>
       <c r="C27">
-        <v>4.477</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1598,16 +1598,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46308.27083333334</v>
+        <v>46310.27083333334</v>
       </c>
       <c r="B28">
-        <v>1.875</v>
+        <v>26.214</v>
       </c>
       <c r="C28">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1621,16 +1621,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46308.28125</v>
+        <v>46310.28125</v>
       </c>
       <c r="B29">
-        <v>0.128</v>
+        <v>5.274</v>
       </c>
       <c r="C29">
-        <v>0.211</v>
+        <v>0.001</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1644,16 +1644,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46308.29166666666</v>
+        <v>46310.29166666666</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>17.573</v>
       </c>
       <c r="C30">
-        <v>3.163</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1667,16 +1667,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46308.30208333334</v>
+        <v>46310.30208333334</v>
       </c>
       <c r="B31">
-        <v>0.151</v>
+        <v>25.642</v>
       </c>
       <c r="C31">
-        <v>0.239</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1690,16 +1690,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46308.3125</v>
+        <v>46310.3125</v>
       </c>
       <c r="B32">
-        <v>0.099</v>
+        <v>21.438</v>
       </c>
       <c r="C32">
-        <v>0.128</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1713,16 +1713,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46308.32291666666</v>
+        <v>46310.32291666666</v>
       </c>
       <c r="B33">
-        <v>0.06</v>
+        <v>5.886</v>
       </c>
       <c r="C33">
-        <v>0.351</v>
+        <v>0.14</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1736,19 +1736,19 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46308.33333333334</v>
+        <v>46310.33333333334</v>
       </c>
       <c r="B34">
-        <v>0.241</v>
+        <v>82.312</v>
       </c>
       <c r="C34">
-        <v>0.136</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E34">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F34">
         <v>33</v>
@@ -1759,19 +1759,19 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46308.34375</v>
+        <v>46310.34375</v>
       </c>
       <c r="B35">
-        <v>0.581</v>
+        <v>87.51900000000001</v>
       </c>
       <c r="C35">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="E35">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F35">
         <v>34</v>
@@ -1782,19 +1782,19 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46308.35416666666</v>
+        <v>46310.35416666666</v>
       </c>
       <c r="B36">
-        <v>0.09</v>
+        <v>58.285</v>
       </c>
       <c r="C36">
-        <v>0.275</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="E36">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F36">
         <v>35</v>
@@ -1805,19 +1805,19 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46308.36458333334</v>
+        <v>46310.36458333334</v>
       </c>
       <c r="B37">
-        <v>0.129</v>
+        <v>0.751</v>
       </c>
       <c r="C37">
-        <v>0.122</v>
+        <v>0.317</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>186.75</v>
       </c>
       <c r="E37">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F37">
         <v>36</v>
@@ -1828,19 +1828,19 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46308.375</v>
+        <v>46310.375</v>
       </c>
       <c r="B38">
-        <v>0.341</v>
+        <v>0.852</v>
       </c>
       <c r="C38">
-        <v>1.473</v>
+        <v>0.196</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>164.25</v>
       </c>
       <c r="E38">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F38">
         <v>37</v>
@@ -1851,19 +1851,19 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46308.38541666666</v>
+        <v>46310.38541666666</v>
       </c>
       <c r="B39">
-        <v>0.957</v>
+        <v>0.116</v>
       </c>
       <c r="C39">
-        <v>1.864</v>
+        <v>0.588</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>164.25</v>
       </c>
       <c r="E39">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F39">
         <v>38</v>
@@ -1874,19 +1874,19 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46308.39583333334</v>
+        <v>46310.39583333334</v>
       </c>
       <c r="B40">
-        <v>0.919</v>
+        <v>0.228</v>
       </c>
       <c r="C40">
-        <v>0.621</v>
+        <v>0.429</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>146.25</v>
       </c>
       <c r="E40">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F40">
         <v>39</v>
@@ -1897,19 +1897,19 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46308.40625</v>
+        <v>46310.40625</v>
       </c>
       <c r="B41">
-        <v>1.853</v>
+        <v>0.424</v>
       </c>
       <c r="C41">
-        <v>4.535</v>
+        <v>0.506</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>110.25</v>
       </c>
       <c r="E41">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F41">
         <v>40</v>
@@ -1920,19 +1920,19 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46308.41666666666</v>
+        <v>46310.41666666666</v>
       </c>
       <c r="B42">
-        <v>0.855</v>
+        <v>63.171</v>
       </c>
       <c r="C42">
-        <v>1.9</v>
+        <v>0.002</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="E42">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F42">
         <v>41</v>
@@ -1943,19 +1943,19 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46308.42708333334</v>
+        <v>46310.42708333334</v>
       </c>
       <c r="B43">
-        <v>9.939</v>
+        <v>86.241</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="E43">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F43">
         <v>42</v>
@@ -1966,16 +1966,16 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46308.4375</v>
+        <v>46310.4375</v>
       </c>
       <c r="B44">
-        <v>2.028</v>
+        <v>58.439</v>
       </c>
       <c r="C44">
-        <v>0.486</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>161.75</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -1989,16 +1989,16 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46308.44791666666</v>
+        <v>46310.44791666666</v>
       </c>
       <c r="B45">
-        <v>0.079</v>
+        <v>30.894</v>
       </c>
       <c r="C45">
-        <v>3.181</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>153.75</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -2012,16 +2012,16 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46308.45833333334</v>
+        <v>46310.45833333334</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="C46">
-        <v>9.438000000000001</v>
+        <v>5.924</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>187.5</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2035,16 +2035,16 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46308.46875</v>
+        <v>46310.46875</v>
       </c>
       <c r="B47">
-        <v>0.003</v>
+        <v>0.061</v>
       </c>
       <c r="C47">
-        <v>8.981</v>
+        <v>1.179</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>187.5</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -2058,16 +2058,16 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46308.47916666666</v>
+        <v>46310.47916666666</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>0.314</v>
       </c>
       <c r="C48">
-        <v>7.342</v>
+        <v>0.221</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>149.25</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -2081,19 +2081,19 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46308.48958333334</v>
+        <v>46310.48958333334</v>
       </c>
       <c r="B49">
-        <v>0.08400000000000001</v>
+        <v>0.319</v>
       </c>
       <c r="C49">
-        <v>1.318</v>
+        <v>2.085</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="E49">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F49">
         <v>48</v>
@@ -2104,19 +2104,19 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46308.5</v>
+        <v>46310.5</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>0.049</v>
       </c>
       <c r="C50">
-        <v>14.256</v>
+        <v>2.785</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="E50">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F50">
         <v>49</v>
@@ -2127,19 +2127,19 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46308.51041666666</v>
+        <v>46310.51041666666</v>
       </c>
       <c r="B51">
-        <v>0.008</v>
+        <v>0.705</v>
       </c>
       <c r="C51">
-        <v>13.297</v>
+        <v>0.602</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E51">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F51">
         <v>50</v>
@@ -2150,19 +2150,19 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46308.52083333334</v>
+        <v>46310.52083333334</v>
       </c>
       <c r="B52">
-        <v>10.184</v>
+        <v>0.507</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F52">
         <v>51</v>
@@ -2173,10 +2173,10 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46308.53125</v>
+        <v>46310.53125</v>
       </c>
       <c r="B53">
-        <v>32.523</v>
+        <v>23.02</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="E53">
-        <v>62.5</v>
+        <v>70</v>
       </c>
       <c r="F53">
         <v>52</v>
@@ -2196,19 +2196,19 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46308.54166666666</v>
+        <v>46310.54166666666</v>
       </c>
       <c r="B54">
-        <v>25.538</v>
+        <v>10.75</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>0.123</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F54">
         <v>53</v>
@@ -2219,13 +2219,13 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46308.55208333334</v>
+        <v>46310.55208333334</v>
       </c>
       <c r="B55">
-        <v>33.614</v>
+        <v>3.865</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46308.5625</v>
+        <v>46310.5625</v>
       </c>
       <c r="B56">
-        <v>24.849</v>
+        <v>12.704</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -2254,7 +2254,7 @@
         <v>0</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F56">
         <v>55</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46308.57291666666</v>
+        <v>46310.57291666666</v>
       </c>
       <c r="B57">
-        <v>8.375999999999999</v>
+        <v>21.64</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F57">
         <v>56</v>
@@ -2288,19 +2288,19 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46308.58333333334</v>
+        <v>46310.58333333334</v>
       </c>
       <c r="B58">
-        <v>24.693</v>
+        <v>7.003</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F58">
         <v>57</v>
@@ -2311,19 +2311,19 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46308.59375</v>
+        <v>46310.59375</v>
       </c>
       <c r="B59">
-        <v>29.671</v>
+        <v>14.806</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F59">
         <v>58</v>
@@ -2334,10 +2334,10 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46308.60416666666</v>
+        <v>46310.60416666666</v>
       </c>
       <c r="B60">
-        <v>12.678</v>
+        <v>10.982</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -2357,13 +2357,13 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46308.61458333334</v>
+        <v>46310.61458333334</v>
       </c>
       <c r="B61">
-        <v>23.595</v>
+        <v>12.629</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2380,13 +2380,13 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46308.625</v>
+        <v>46310.625</v>
       </c>
       <c r="B62">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="C62">
-        <v>11.064</v>
+        <v>14.564</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2403,13 +2403,13 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46308.63541666666</v>
+        <v>46310.63541666666</v>
       </c>
       <c r="B63">
-        <v>0.039</v>
+        <v>0.325</v>
       </c>
       <c r="C63">
-        <v>4.499</v>
+        <v>0.281</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2426,19 +2426,19 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46308.64583333334</v>
+        <v>46310.64583333334</v>
       </c>
       <c r="B64">
-        <v>0.805</v>
+        <v>19.298</v>
       </c>
       <c r="C64">
-        <v>0.068</v>
+        <v>0.229</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F64">
         <v>63</v>
@@ -2449,19 +2449,19 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46308.65625</v>
+        <v>46310.65625</v>
       </c>
       <c r="B65">
-        <v>15.287</v>
+        <v>26.31</v>
       </c>
       <c r="C65">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F65">
         <v>64</v>
@@ -2472,19 +2472,19 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46308.66666666666</v>
+        <v>46310.66666666666</v>
       </c>
       <c r="B66">
-        <v>5.077</v>
+        <v>7.127</v>
       </c>
       <c r="C66">
-        <v>0.026</v>
+        <v>0.014</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>44.25</v>
       </c>
       <c r="F66">
         <v>65</v>
@@ -2495,19 +2495,19 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46308.67708333334</v>
+        <v>46310.67708333334</v>
       </c>
       <c r="B67">
-        <v>2.336</v>
+        <v>1.659</v>
       </c>
       <c r="C67">
-        <v>0.228</v>
+        <v>0.031</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>44.25</v>
       </c>
       <c r="F67">
         <v>66</v>
@@ -2518,19 +2518,19 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46308.6875</v>
+        <v>46310.6875</v>
       </c>
       <c r="B68">
-        <v>7.345</v>
+        <v>28.739</v>
       </c>
       <c r="C68">
-        <v>3.055</v>
+        <v>0</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F68">
         <v>67</v>
@@ -2541,10 +2541,10 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46308.69791666666</v>
+        <v>46310.69791666666</v>
       </c>
       <c r="B69">
-        <v>29.22</v>
+        <v>42.218</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F69">
         <v>68</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46308.70833333334</v>
+        <v>46310.70833333334</v>
       </c>
       <c r="B70">
-        <v>45.926</v>
+        <v>29.738</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F70">
         <v>69</v>
@@ -2587,16 +2587,16 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46308.71875</v>
+        <v>46310.71875</v>
       </c>
       <c r="B71">
-        <v>33.501</v>
+        <v>29.792</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -2610,16 +2610,16 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46308.72916666666</v>
+        <v>46310.72916666666</v>
       </c>
       <c r="B72">
-        <v>20.465</v>
+        <v>41.983</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -2633,16 +2633,16 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46308.73958333334</v>
+        <v>46310.73958333334</v>
       </c>
       <c r="B73">
-        <v>33.458</v>
+        <v>9.535</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>1.584</v>
       </c>
       <c r="D73">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -2656,16 +2656,16 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46308.75</v>
+        <v>46310.75</v>
       </c>
       <c r="B74">
-        <v>33.998</v>
+        <v>0.328</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>4.812</v>
       </c>
       <c r="D74">
-        <v>62.5</v>
+        <v>37.5</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -2679,16 +2679,16 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46308.76041666666</v>
+        <v>46310.76041666666</v>
       </c>
       <c r="B75">
-        <v>5.812</v>
+        <v>0.176</v>
       </c>
       <c r="C75">
-        <v>0.026</v>
+        <v>1.203</v>
       </c>
       <c r="D75">
-        <v>62.5</v>
+        <v>37.5</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -2702,16 +2702,16 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46308.77083333334</v>
+        <v>46310.77083333334</v>
       </c>
       <c r="B76">
-        <v>1.216</v>
+        <v>0.211</v>
       </c>
       <c r="C76">
-        <v>0.021</v>
+        <v>0.169</v>
       </c>
       <c r="D76">
-        <v>62.5</v>
+        <v>35.75</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -2725,16 +2725,16 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46308.78125</v>
+        <v>46310.78125</v>
       </c>
       <c r="B77">
-        <v>10.626</v>
+        <v>0.09</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>0.134</v>
       </c>
       <c r="D77">
-        <v>50</v>
+        <v>36.75</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -2748,16 +2748,16 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46308.79166666666</v>
+        <v>46310.79166666666</v>
       </c>
       <c r="B78">
-        <v>19.292</v>
+        <v>11.373</v>
       </c>
       <c r="C78">
         <v>0</v>
       </c>
       <c r="D78">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -2771,16 +2771,16 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46308.80208333334</v>
+        <v>46310.80208333334</v>
       </c>
       <c r="B79">
-        <v>11.652</v>
+        <v>4.43</v>
       </c>
       <c r="C79">
         <v>0</v>
       </c>
       <c r="D79">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46308.8125</v>
+        <v>46310.8125</v>
       </c>
       <c r="B80">
-        <v>0.078</v>
+        <v>11.111</v>
       </c>
       <c r="C80">
-        <v>4.721</v>
+        <v>1.517</v>
       </c>
       <c r="D80">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -2817,16 +2817,16 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46308.82291666666</v>
+        <v>46310.82291666666</v>
       </c>
       <c r="B81">
-        <v>0.674</v>
+        <v>4.463</v>
       </c>
       <c r="C81">
-        <v>2.922</v>
+        <v>0.102</v>
       </c>
       <c r="D81">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -2840,13 +2840,13 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46308.83333333334</v>
+        <v>46310.83333333334</v>
       </c>
       <c r="B82">
-        <v>2.605</v>
+        <v>4.287</v>
       </c>
       <c r="C82">
-        <v>0.274</v>
+        <v>1.718</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -2863,13 +2863,13 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46308.84375</v>
+        <v>46310.84375</v>
       </c>
       <c r="B83">
-        <v>8.93</v>
+        <v>0.026</v>
       </c>
       <c r="C83">
-        <v>0.125</v>
+        <v>2.192</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -2886,13 +2886,13 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46308.85416666666</v>
+        <v>46310.85416666666</v>
       </c>
       <c r="B84">
-        <v>2.812</v>
+        <v>0.011</v>
       </c>
       <c r="C84">
-        <v>1.225</v>
+        <v>8.183</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46308.86458333334</v>
+        <v>46310.86458333334</v>
       </c>
       <c r="B85">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="C85">
-        <v>3.494</v>
+        <v>5.933</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -2932,13 +2932,13 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46308.875</v>
+        <v>46310.875</v>
       </c>
       <c r="B86">
-        <v>6.143</v>
+        <v>2.714</v>
       </c>
       <c r="C86">
-        <v>0.528</v>
+        <v>1.46</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -2955,13 +2955,13 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46308.88541666666</v>
+        <v>46310.88541666666</v>
       </c>
       <c r="B87">
-        <v>12.648</v>
+        <v>0.857</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>0.412</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -2978,13 +2978,13 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46308.89583333334</v>
+        <v>46310.89583333334</v>
       </c>
       <c r="B88">
-        <v>7.303</v>
+        <v>0.336</v>
       </c>
       <c r="C88">
-        <v>2.496</v>
+        <v>0.842</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3001,13 +3001,13 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46308.90625</v>
+        <v>46310.90625</v>
       </c>
       <c r="B89">
-        <v>1.099</v>
+        <v>0.015</v>
       </c>
       <c r="C89">
-        <v>1.153</v>
+        <v>2.563</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3024,13 +3024,13 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46308.91666666666</v>
+        <v>46310.91666666666</v>
       </c>
       <c r="B90">
-        <v>2.376</v>
+        <v>2.497</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>0.832</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3047,13 +3047,13 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46308.92708333334</v>
+        <v>46310.92708333334</v>
       </c>
       <c r="B91">
-        <v>29.442</v>
+        <v>1.598</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3070,13 +3070,13 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46308.9375</v>
+        <v>46310.9375</v>
       </c>
       <c r="B92">
-        <v>32.11</v>
+        <v>0.304</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>0.156</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3093,13 +3093,13 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46308.94791666666</v>
+        <v>46310.94791666666</v>
       </c>
       <c r="B93">
-        <v>14.469</v>
+        <v>0.034</v>
       </c>
       <c r="C93">
-        <v>0.355</v>
+        <v>4.118</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3116,16 +3116,16 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46308.95833333334</v>
+        <v>46310.95833333334</v>
       </c>
       <c r="B94">
-        <v>22.199</v>
+        <v>0.002</v>
       </c>
       <c r="C94">
-        <v>0.021</v>
+        <v>3.909</v>
       </c>
       <c r="D94">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3139,16 +3139,16 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46308.96875</v>
+        <v>46310.96875</v>
       </c>
       <c r="B95">
-        <v>27.025</v>
+        <v>0</v>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>4.158</v>
       </c>
       <c r="D95">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -3162,16 +3162,16 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46308.97916666666</v>
+        <v>46310.97916666666</v>
       </c>
       <c r="B96">
-        <v>20.255</v>
+        <v>0.019</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>0.961</v>
       </c>
       <c r="D96">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -3185,16 +3185,16 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46308.98958333334</v>
+        <v>46310.98958333334</v>
       </c>
       <c r="B97">
-        <v>7.41</v>
+        <v>0.132</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="D97">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -3208,16 +3208,16 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="B98">
-        <v>30.169</v>
+        <v>1.663</v>
       </c>
       <c r="C98">
         <v>0</v>
       </c>
       <c r="D98">
-        <v>35.5</v>
+        <v>0</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -3231,16 +3231,16 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46309.01041666666</v>
+        <v>46311.01041666666</v>
       </c>
       <c r="B99">
-        <v>8.423999999999999</v>
+        <v>5.058</v>
       </c>
       <c r="C99">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="D99">
-        <v>52.5</v>
+        <v>0</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46309.02083333334</v>
+        <v>46311.02083333334</v>
       </c>
       <c r="B100">
-        <v>8.657999999999999</v>
+        <v>22.692</v>
       </c>
       <c r="C100">
         <v>0</v>
       </c>
       <c r="D100">
-        <v>52.5</v>
+        <v>0</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -3277,16 +3277,16 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46309.03125</v>
+        <v>46311.03125</v>
       </c>
       <c r="B101">
-        <v>11.691</v>
+        <v>1.309</v>
       </c>
       <c r="C101">
-        <v>0.219</v>
+        <v>0.167</v>
       </c>
       <c r="D101">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -3300,16 +3300,16 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46309.04166666666</v>
+        <v>46311.04166666666</v>
       </c>
       <c r="B102">
-        <v>0.064</v>
+        <v>3.23</v>
       </c>
       <c r="C102">
-        <v>0.258</v>
+        <v>0.054</v>
       </c>
       <c r="D102">
-        <v>37.5</v>
+        <v>22.75</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -3323,16 +3323,16 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46309.05208333334</v>
+        <v>46311.05208333334</v>
       </c>
       <c r="B103">
-        <v>24.238</v>
+        <v>0.141</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>1.417</v>
       </c>
       <c r="D103">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -3346,16 +3346,16 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46309.0625</v>
+        <v>46311.0625</v>
       </c>
       <c r="B104">
-        <v>30.263</v>
+        <v>0.013</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>4.628</v>
       </c>
       <c r="D104">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -3369,16 +3369,16 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46309.07291666666</v>
+        <v>46311.07291666666</v>
       </c>
       <c r="B105">
-        <v>9.971</v>
+        <v>0</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>12.88</v>
       </c>
       <c r="D105">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -3392,16 +3392,16 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46309.08333333334</v>
+        <v>46311.08333333334</v>
       </c>
       <c r="B106">
-        <v>19.339</v>
+        <v>0.011</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>2.678</v>
       </c>
       <c r="D106">
-        <v>20.25</v>
+        <v>0</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -3415,16 +3415,16 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46309.09375</v>
+        <v>46311.09375</v>
       </c>
       <c r="B107">
-        <v>1.022</v>
+        <v>0.008</v>
       </c>
       <c r="C107">
-        <v>0.163</v>
+        <v>5.862</v>
       </c>
       <c r="D107">
-        <v>20.25</v>
+        <v>0</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -3438,16 +3438,16 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46309.10416666666</v>
+        <v>46311.10416666666</v>
       </c>
       <c r="B108">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="C108">
-        <v>2.485</v>
+        <v>8.457000000000001</v>
       </c>
       <c r="D108">
-        <v>20.25</v>
+        <v>0</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -3461,16 +3461,16 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46309.11458333334</v>
+        <v>46311.11458333334</v>
       </c>
       <c r="B109">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="C109">
-        <v>9.531000000000001</v>
+        <v>1.464</v>
       </c>
       <c r="D109">
-        <v>20.25</v>
+        <v>0</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -3484,13 +3484,13 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46309.125</v>
+        <v>46311.125</v>
       </c>
       <c r="B110">
-        <v>0.9</v>
+        <v>3.072</v>
       </c>
       <c r="C110">
-        <v>0.539</v>
+        <v>0.015</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -3507,13 +3507,13 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46309.13541666666</v>
+        <v>46311.13541666666</v>
       </c>
       <c r="B111">
-        <v>0.115</v>
+        <v>14.189</v>
       </c>
       <c r="C111">
-        <v>2.663</v>
+        <v>0</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -3530,13 +3530,13 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46309.14583333334</v>
+        <v>46311.14583333334</v>
       </c>
       <c r="B112">
-        <v>8.617000000000001</v>
+        <v>3.087</v>
       </c>
       <c r="C112">
-        <v>0.515</v>
+        <v>0.016</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -3553,13 +3553,13 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46309.15625</v>
+        <v>46311.15625</v>
       </c>
       <c r="B113">
-        <v>2.309</v>
+        <v>6.626</v>
       </c>
       <c r="C113">
-        <v>0.021</v>
+        <v>0.024</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -3576,13 +3576,13 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46309.16666666666</v>
+        <v>46311.16666666666</v>
       </c>
       <c r="B114">
-        <v>14.866</v>
+        <v>0.274</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -3599,13 +3599,13 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46309.17708333334</v>
+        <v>46311.17708333334</v>
       </c>
       <c r="B115">
-        <v>13.077</v>
+        <v>0.188</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>0.041</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -3622,13 +3622,13 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46309.1875</v>
+        <v>46311.1875</v>
       </c>
       <c r="B116">
-        <v>26.329</v>
+        <v>0.143</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>0.235</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -3645,13 +3645,13 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46309.19791666666</v>
+        <v>46311.19791666666</v>
       </c>
       <c r="B117">
-        <v>9.478</v>
+        <v>0.002</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>3.088</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -3668,13 +3668,13 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46309.20833333334</v>
+        <v>46311.20833333334</v>
       </c>
       <c r="B118">
-        <v>27.383</v>
+        <v>0</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>6.463</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -3691,13 +3691,13 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46309.21875</v>
+        <v>46311.21875</v>
       </c>
       <c r="B119">
-        <v>33.037</v>
+        <v>0.075</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>0.388</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46309.22916666666</v>
+        <v>46311.22916666666</v>
       </c>
       <c r="B120">
-        <v>12.231</v>
+        <v>0.03</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>0.199</v>
       </c>
       <c r="D120">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -3737,16 +3737,16 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46309.23958333334</v>
+        <v>46311.23958333334</v>
       </c>
       <c r="B121">
-        <v>9.390000000000001</v>
+        <v>0.217</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>0.236</v>
       </c>
       <c r="D121">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -3760,16 +3760,16 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46309.25</v>
+        <v>46311.25</v>
       </c>
       <c r="B122">
-        <v>36.304</v>
+        <v>0</v>
       </c>
       <c r="C122">
-        <v>0</v>
+        <v>8.736000000000001</v>
       </c>
       <c r="D122">
-        <v>33.5</v>
+        <v>0</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -3783,16 +3783,16 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46309.26041666666</v>
+        <v>46311.26041666666</v>
       </c>
       <c r="B123">
-        <v>34.876</v>
+        <v>0.172</v>
       </c>
       <c r="C123">
-        <v>0</v>
+        <v>0.321</v>
       </c>
       <c r="D123">
-        <v>33.5</v>
+        <v>0</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -3806,16 +3806,16 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46309.27083333334</v>
+        <v>46311.27083333334</v>
       </c>
       <c r="B124">
-        <v>17.406</v>
+        <v>0.017</v>
       </c>
       <c r="C124">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="D124">
-        <v>33.5</v>
+        <v>0</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -3829,16 +3829,16 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46309.28125</v>
+        <v>46311.28125</v>
       </c>
       <c r="B125">
-        <v>11.475</v>
+        <v>0.004</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>1.893</v>
       </c>
       <c r="D125">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -3852,16 +3852,16 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46309.29166666666</v>
+        <v>46311.29166666666</v>
       </c>
       <c r="B126">
-        <v>1.719</v>
+        <v>0.35</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>0.176</v>
       </c>
       <c r="D126">
-        <v>36.5</v>
+        <v>0</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -3875,16 +3875,16 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46309.30208333334</v>
+        <v>46311.30208333334</v>
       </c>
       <c r="B127">
-        <v>0.534</v>
+        <v>0.394</v>
       </c>
       <c r="C127">
-        <v>0.196</v>
+        <v>0.099</v>
       </c>
       <c r="D127">
-        <v>36.5</v>
+        <v>0</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -3898,16 +3898,16 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46309.3125</v>
+        <v>46311.3125</v>
       </c>
       <c r="B128">
-        <v>0.056</v>
+        <v>1.924</v>
       </c>
       <c r="C128">
-        <v>0.707</v>
+        <v>0.114</v>
       </c>
       <c r="D128">
-        <v>36.5</v>
+        <v>0</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -3921,13 +3921,13 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46309.32291666666</v>
+        <v>46311.32291666666</v>
       </c>
       <c r="B129">
-        <v>0.231</v>
+        <v>0.389</v>
       </c>
       <c r="C129">
-        <v>0.206</v>
+        <v>0.108</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -3944,13 +3944,13 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46309.33333333334</v>
+        <v>46311.33333333334</v>
       </c>
       <c r="B130">
-        <v>0.175</v>
+        <v>22.835</v>
       </c>
       <c r="C130">
-        <v>0.582</v>
+        <v>0</v>
       </c>
       <c r="D130">
         <v>0</v>
@@ -3967,19 +3967,19 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46309.34375</v>
+        <v>46311.34375</v>
       </c>
       <c r="B131">
-        <v>0.598</v>
+        <v>6.489</v>
       </c>
       <c r="C131">
-        <v>0.194</v>
+        <v>0.83</v>
       </c>
       <c r="D131">
         <v>0</v>
       </c>
       <c r="E131">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F131">
         <v>34</v>
@@ -3990,19 +3990,19 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46309.35416666666</v>
+        <v>46311.35416666666</v>
       </c>
       <c r="B132">
-        <v>0.319</v>
+        <v>2.285</v>
       </c>
       <c r="C132">
-        <v>12.862</v>
+        <v>3.821</v>
       </c>
       <c r="D132">
         <v>0</v>
       </c>
       <c r="E132">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F132">
         <v>35</v>
@@ -4013,19 +4013,19 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46309.36458333334</v>
+        <v>46311.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
       </c>
       <c r="C133">
-        <v>14.059</v>
+        <v>14.676</v>
       </c>
       <c r="D133">
         <v>0</v>
       </c>
       <c r="E133">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F133">
         <v>36</v>
@@ -4036,13 +4036,13 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46309.375</v>
+        <v>46311.375</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="C134">
-        <v>7.86</v>
+        <v>9.237</v>
       </c>
       <c r="D134">
         <v>0</v>
@@ -4059,19 +4059,19 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46309.38541666666</v>
+        <v>46311.38541666666</v>
       </c>
       <c r="B135">
-        <v>0.044</v>
+        <v>0.011</v>
       </c>
       <c r="C135">
-        <v>2.811</v>
+        <v>3.766</v>
       </c>
       <c r="D135">
         <v>0</v>
       </c>
       <c r="E135">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F135">
         <v>38</v>
@@ -4082,13 +4082,13 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46309.39583333334</v>
+        <v>46311.39583333334</v>
       </c>
       <c r="B136">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="C136">
-        <v>21.127</v>
+        <v>14.128</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -4105,19 +4105,19 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46309.40625</v>
+        <v>46311.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
       </c>
       <c r="C137">
-        <v>17.576</v>
+        <v>23.793</v>
       </c>
       <c r="D137">
         <v>0</v>
       </c>
       <c r="E137">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F137">
         <v>40</v>
@@ -4128,19 +4128,19 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46309.41666666666</v>
+        <v>46311.41666666666</v>
       </c>
       <c r="B138">
-        <v>0.005</v>
+        <v>2.164</v>
       </c>
       <c r="C138">
-        <v>2.657</v>
+        <v>6.274</v>
       </c>
       <c r="D138">
         <v>0</v>
       </c>
       <c r="E138">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F138">
         <v>41</v>
@@ -4151,13 +4151,13 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46309.42708333334</v>
+        <v>46311.42708333334</v>
       </c>
       <c r="B139">
-        <v>0.011</v>
+        <v>0.067</v>
       </c>
       <c r="C139">
-        <v>9.708</v>
+        <v>0.723</v>
       </c>
       <c r="D139">
         <v>0</v>
@@ -4174,13 +4174,13 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46309.4375</v>
+        <v>46311.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
       </c>
       <c r="C140">
-        <v>15.128</v>
+        <v>6.158</v>
       </c>
       <c r="D140">
         <v>0</v>
@@ -4197,13 +4197,13 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46309.44791666666</v>
+        <v>46311.44791666666</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>11.561</v>
       </c>
       <c r="C141">
-        <v>31.762</v>
+        <v>0.677</v>
       </c>
       <c r="D141">
         <v>0</v>
@@ -4220,13 +4220,13 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46309.45833333334</v>
+        <v>46311.45833333334</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>0.447</v>
       </c>
       <c r="C142">
-        <v>13.167</v>
+        <v>1.006</v>
       </c>
       <c r="D142">
         <v>0</v>
@@ -4243,19 +4243,19 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46309.46875</v>
+        <v>46311.46875</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="C143">
-        <v>8.395</v>
+        <v>4.021</v>
       </c>
       <c r="D143">
         <v>0</v>
       </c>
       <c r="E143">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F143">
         <v>46</v>
@@ -4266,13 +4266,13 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46309.47916666666</v>
+        <v>46311.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>2.433</v>
       </c>
       <c r="C144">
-        <v>31.499</v>
+        <v>0.322</v>
       </c>
       <c r="D144">
         <v>0</v>
@@ -4289,13 +4289,13 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46309.48958333334</v>
+        <v>46311.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
       </c>
       <c r="C145">
-        <v>68.86199999999999</v>
+        <v>15.561</v>
       </c>
       <c r="D145">
         <v>0</v>
@@ -4312,13 +4312,13 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="B146">
         <v>0</v>
       </c>
       <c r="C146">
-        <v>51.701</v>
+        <v>27.087</v>
       </c>
       <c r="D146">
         <v>0</v>
@@ -4335,13 +4335,13 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46309.51041666666</v>
+        <v>46311.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>0.458</v>
       </c>
       <c r="C147">
-        <v>88.294</v>
+        <v>4.928</v>
       </c>
       <c r="D147">
         <v>0</v>
@@ -4358,19 +4358,19 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46309.52083333334</v>
+        <v>46311.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>0.292</v>
       </c>
       <c r="C148">
-        <v>120.919</v>
+        <v>1.712</v>
       </c>
       <c r="D148">
         <v>0</v>
       </c>
       <c r="E148">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F148">
         <v>51</v>
@@ -4381,19 +4381,19 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46309.53125</v>
+        <v>46311.53125</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>1.888</v>
       </c>
       <c r="C149">
-        <v>64.994</v>
+        <v>21.668</v>
       </c>
       <c r="D149">
         <v>0</v>
       </c>
       <c r="E149">
-        <v>112.5</v>
+        <v>0</v>
       </c>
       <c r="F149">
         <v>52</v>
@@ -4404,19 +4404,19 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46309.54166666666</v>
+        <v>46311.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
       </c>
       <c r="C150">
-        <v>29.621</v>
+        <v>0</v>
       </c>
       <c r="D150">
         <v>0</v>
       </c>
       <c r="E150">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F150">
         <v>53</v>
@@ -4427,19 +4427,19 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46309.55208333334</v>
+        <v>46311.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
       </c>
       <c r="C151">
-        <v>5.159</v>
+        <v>0</v>
       </c>
       <c r="D151">
         <v>0</v>
       </c>
       <c r="E151">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F151">
         <v>54</v>
@@ -4450,19 +4450,19 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46309.5625</v>
+        <v>46311.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
       </c>
       <c r="C152">
-        <v>33.385</v>
+        <v>0</v>
       </c>
       <c r="D152">
         <v>0</v>
       </c>
       <c r="E152">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F152">
         <v>55</v>
@@ -4473,19 +4473,19 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46309.57291666666</v>
+        <v>46311.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
       </c>
       <c r="C153">
-        <v>68.017</v>
+        <v>0</v>
       </c>
       <c r="D153">
         <v>0</v>
       </c>
       <c r="E153">
-        <v>162.5</v>
+        <v>0</v>
       </c>
       <c r="F153">
         <v>56</v>
@@ -4496,19 +4496,19 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46309.58333333334</v>
+        <v>46311.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
       </c>
       <c r="C154">
-        <v>65.83499999999999</v>
+        <v>0</v>
       </c>
       <c r="D154">
         <v>0</v>
       </c>
       <c r="E154">
-        <v>162.5</v>
+        <v>0</v>
       </c>
       <c r="F154">
         <v>57</v>
@@ -4519,19 +4519,19 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46309.59375</v>
+        <v>46311.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
       </c>
       <c r="C155">
-        <v>28.542</v>
+        <v>0</v>
       </c>
       <c r="D155">
         <v>0</v>
       </c>
       <c r="E155">
-        <v>187.5</v>
+        <v>0</v>
       </c>
       <c r="F155">
         <v>58</v>
@@ -4542,19 +4542,19 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46309.60416666666</v>
+        <v>46311.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
       </c>
       <c r="C156">
-        <v>50.258</v>
+        <v>0</v>
       </c>
       <c r="D156">
         <v>0</v>
       </c>
       <c r="E156">
-        <v>187.5</v>
+        <v>0</v>
       </c>
       <c r="F156">
         <v>59</v>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46309.61458333334</v>
+        <v>46311.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4577,7 +4577,7 @@
         <v>0</v>
       </c>
       <c r="E157">
-        <v>187.5</v>
+        <v>0</v>
       </c>
       <c r="F157">
         <v>60</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46309.625</v>
+        <v>46311.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4611,7 +4611,7 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46309.63541666666</v>
+        <v>46311.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46309.64583333334</v>
+        <v>46311.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46309.65625</v>
+        <v>46311.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46309.66666666666</v>
+        <v>46311.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46309.67708333334</v>
+        <v>46311.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46309.6875</v>
+        <v>46311.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46309.69791666666</v>
+        <v>46311.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4772,7 +4772,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46309.70833333334</v>
+        <v>46311.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46309.71875</v>
+        <v>46311.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46309.72916666666</v>
+        <v>46311.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46309.73958333334</v>
+        <v>46311.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46309.75</v>
+        <v>46311.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46309.76041666666</v>
+        <v>46311.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46309.77083333334</v>
+        <v>46311.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46309.78125</v>
+        <v>46311.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46309.79166666666</v>
+        <v>46311.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46309.80208333334</v>
+        <v>46311.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46309.8125</v>
+        <v>46311.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -5025,7 +5025,7 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46309.82291666666</v>
+        <v>46311.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46309.83333333334</v>
+        <v>46311.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -5071,7 +5071,7 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46309.84375</v>
+        <v>46311.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -5094,7 +5094,7 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46309.85416666666</v>
+        <v>46311.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46309.86458333334</v>
+        <v>46311.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46309.875</v>
+        <v>46311.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46309.88541666666</v>
+        <v>46311.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46309.89583333334</v>
+        <v>46311.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46309.90625</v>
+        <v>46311.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46309.91666666666</v>
+        <v>46311.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46309.92708333334</v>
+        <v>46311.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46309.9375</v>
+        <v>46311.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46309.94791666666</v>
+        <v>46311.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46309.95833333334</v>
+        <v>46311.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -5347,7 +5347,7 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46309.96875</v>
+        <v>46311.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46309.97916666666</v>
+        <v>46311.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46309.98958333334</v>
+        <v>46311.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -37,580 +37,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>15.10.20261</t>
-  </si>
-  <si>
-    <t>15.10.20262</t>
-  </si>
-  <si>
-    <t>15.10.20263</t>
-  </si>
-  <si>
-    <t>15.10.20264</t>
-  </si>
-  <si>
-    <t>15.10.20265</t>
-  </si>
-  <si>
-    <t>15.10.20266</t>
-  </si>
-  <si>
-    <t>15.10.20267</t>
-  </si>
-  <si>
-    <t>15.10.20268</t>
-  </si>
-  <si>
-    <t>15.10.20269</t>
-  </si>
-  <si>
-    <t>15.10.202610</t>
-  </si>
-  <si>
-    <t>15.10.202611</t>
-  </si>
-  <si>
-    <t>15.10.202612</t>
-  </si>
-  <si>
-    <t>15.10.202613</t>
-  </si>
-  <si>
-    <t>15.10.202614</t>
-  </si>
-  <si>
-    <t>15.10.202615</t>
-  </si>
-  <si>
-    <t>15.10.202616</t>
-  </si>
-  <si>
-    <t>15.10.202617</t>
-  </si>
-  <si>
-    <t>15.10.202618</t>
-  </si>
-  <si>
-    <t>15.10.202619</t>
-  </si>
-  <si>
-    <t>15.10.202620</t>
-  </si>
-  <si>
-    <t>15.10.202621</t>
-  </si>
-  <si>
-    <t>15.10.202622</t>
-  </si>
-  <si>
-    <t>15.10.202623</t>
-  </si>
-  <si>
-    <t>15.10.202624</t>
-  </si>
-  <si>
-    <t>15.10.202625</t>
-  </si>
-  <si>
-    <t>15.10.202626</t>
-  </si>
-  <si>
-    <t>15.10.202627</t>
-  </si>
-  <si>
-    <t>15.10.202628</t>
-  </si>
-  <si>
-    <t>15.10.202629</t>
-  </si>
-  <si>
-    <t>15.10.202630</t>
-  </si>
-  <si>
-    <t>15.10.202631</t>
-  </si>
-  <si>
-    <t>15.10.202632</t>
-  </si>
-  <si>
-    <t>15.10.202633</t>
-  </si>
-  <si>
-    <t>15.10.202634</t>
-  </si>
-  <si>
-    <t>15.10.202635</t>
-  </si>
-  <si>
-    <t>15.10.202636</t>
-  </si>
-  <si>
-    <t>15.10.202637</t>
-  </si>
-  <si>
-    <t>15.10.202638</t>
-  </si>
-  <si>
-    <t>15.10.202639</t>
-  </si>
-  <si>
-    <t>15.10.202640</t>
-  </si>
-  <si>
-    <t>15.10.202641</t>
-  </si>
-  <si>
-    <t>15.10.202642</t>
-  </si>
-  <si>
-    <t>15.10.202643</t>
-  </si>
-  <si>
-    <t>15.10.202644</t>
-  </si>
-  <si>
-    <t>15.10.202645</t>
-  </si>
-  <si>
-    <t>15.10.202646</t>
-  </si>
-  <si>
-    <t>15.10.202647</t>
-  </si>
-  <si>
-    <t>15.10.202648</t>
-  </si>
-  <si>
-    <t>15.10.202649</t>
-  </si>
-  <si>
-    <t>15.10.202650</t>
-  </si>
-  <si>
-    <t>15.10.202651</t>
-  </si>
-  <si>
-    <t>15.10.202652</t>
-  </si>
-  <si>
-    <t>15.10.202653</t>
-  </si>
-  <si>
-    <t>15.10.202654</t>
-  </si>
-  <si>
-    <t>15.10.202655</t>
-  </si>
-  <si>
-    <t>15.10.202656</t>
-  </si>
-  <si>
-    <t>15.10.202657</t>
-  </si>
-  <si>
-    <t>15.10.202658</t>
-  </si>
-  <si>
-    <t>15.10.202659</t>
-  </si>
-  <si>
-    <t>15.10.202660</t>
-  </si>
-  <si>
-    <t>15.10.202661</t>
-  </si>
-  <si>
-    <t>15.10.202662</t>
-  </si>
-  <si>
-    <t>15.10.202663</t>
-  </si>
-  <si>
-    <t>15.10.202664</t>
-  </si>
-  <si>
-    <t>15.10.202665</t>
-  </si>
-  <si>
-    <t>15.10.202666</t>
-  </si>
-  <si>
-    <t>15.10.202667</t>
-  </si>
-  <si>
-    <t>15.10.202668</t>
-  </si>
-  <si>
-    <t>15.10.202669</t>
-  </si>
-  <si>
-    <t>15.10.202670</t>
-  </si>
-  <si>
-    <t>15.10.202671</t>
-  </si>
-  <si>
-    <t>15.10.202672</t>
-  </si>
-  <si>
-    <t>15.10.202673</t>
-  </si>
-  <si>
-    <t>15.10.202674</t>
-  </si>
-  <si>
-    <t>15.10.202675</t>
-  </si>
-  <si>
-    <t>15.10.202676</t>
-  </si>
-  <si>
-    <t>15.10.202677</t>
-  </si>
-  <si>
-    <t>15.10.202678</t>
-  </si>
-  <si>
-    <t>15.10.202679</t>
-  </si>
-  <si>
-    <t>15.10.202680</t>
-  </si>
-  <si>
-    <t>15.10.202681</t>
-  </si>
-  <si>
-    <t>15.10.202682</t>
-  </si>
-  <si>
-    <t>15.10.202683</t>
-  </si>
-  <si>
-    <t>15.10.202684</t>
-  </si>
-  <si>
-    <t>15.10.202685</t>
-  </si>
-  <si>
-    <t>15.10.202686</t>
-  </si>
-  <si>
-    <t>15.10.202687</t>
-  </si>
-  <si>
-    <t>15.10.202688</t>
-  </si>
-  <si>
-    <t>15.10.202689</t>
-  </si>
-  <si>
-    <t>15.10.202690</t>
-  </si>
-  <si>
-    <t>15.10.202691</t>
-  </si>
-  <si>
-    <t>15.10.202692</t>
-  </si>
-  <si>
-    <t>15.10.202693</t>
-  </si>
-  <si>
-    <t>15.10.202694</t>
-  </si>
-  <si>
-    <t>15.10.202695</t>
-  </si>
-  <si>
-    <t>15.10.202696</t>
-  </si>
-  <si>
-    <t>16.10.20261</t>
-  </si>
-  <si>
-    <t>16.10.20262</t>
-  </si>
-  <si>
-    <t>16.10.20263</t>
-  </si>
-  <si>
-    <t>16.10.20264</t>
-  </si>
-  <si>
-    <t>16.10.20265</t>
-  </si>
-  <si>
-    <t>16.10.20266</t>
-  </si>
-  <si>
-    <t>16.10.20267</t>
-  </si>
-  <si>
-    <t>16.10.20268</t>
-  </si>
-  <si>
-    <t>16.10.20269</t>
-  </si>
-  <si>
-    <t>16.10.202610</t>
-  </si>
-  <si>
-    <t>16.10.202611</t>
-  </si>
-  <si>
-    <t>16.10.202612</t>
-  </si>
-  <si>
-    <t>16.10.202613</t>
-  </si>
-  <si>
-    <t>16.10.202614</t>
-  </si>
-  <si>
-    <t>16.10.202615</t>
-  </si>
-  <si>
-    <t>16.10.202616</t>
-  </si>
-  <si>
-    <t>16.10.202617</t>
-  </si>
-  <si>
-    <t>16.10.202618</t>
-  </si>
-  <si>
-    <t>16.10.202619</t>
-  </si>
-  <si>
-    <t>16.10.202620</t>
-  </si>
-  <si>
-    <t>16.10.202621</t>
-  </si>
-  <si>
-    <t>16.10.202622</t>
-  </si>
-  <si>
-    <t>16.10.202623</t>
-  </si>
-  <si>
-    <t>16.10.202624</t>
-  </si>
-  <si>
-    <t>16.10.202625</t>
-  </si>
-  <si>
-    <t>16.10.202626</t>
-  </si>
-  <si>
-    <t>16.10.202627</t>
-  </si>
-  <si>
-    <t>16.10.202628</t>
-  </si>
-  <si>
-    <t>16.10.202629</t>
-  </si>
-  <si>
-    <t>16.10.202630</t>
-  </si>
-  <si>
-    <t>16.10.202631</t>
-  </si>
-  <si>
-    <t>16.10.202632</t>
-  </si>
-  <si>
-    <t>16.10.202633</t>
-  </si>
-  <si>
-    <t>16.10.202634</t>
-  </si>
-  <si>
-    <t>16.10.202635</t>
-  </si>
-  <si>
-    <t>16.10.202636</t>
-  </si>
-  <si>
-    <t>16.10.202637</t>
-  </si>
-  <si>
-    <t>16.10.202638</t>
-  </si>
-  <si>
-    <t>16.10.202639</t>
-  </si>
-  <si>
-    <t>16.10.202640</t>
-  </si>
-  <si>
-    <t>16.10.202641</t>
-  </si>
-  <si>
-    <t>16.10.202642</t>
-  </si>
-  <si>
-    <t>16.10.202643</t>
-  </si>
-  <si>
-    <t>16.10.202644</t>
-  </si>
-  <si>
-    <t>16.10.202645</t>
-  </si>
-  <si>
-    <t>16.10.202646</t>
-  </si>
-  <si>
-    <t>16.10.202647</t>
-  </si>
-  <si>
-    <t>16.10.202648</t>
-  </si>
-  <si>
-    <t>16.10.202649</t>
-  </si>
-  <si>
-    <t>16.10.202650</t>
-  </si>
-  <si>
-    <t>16.10.202651</t>
-  </si>
-  <si>
-    <t>16.10.202652</t>
-  </si>
-  <si>
-    <t>16.10.202653</t>
-  </si>
-  <si>
-    <t>16.10.202654</t>
-  </si>
-  <si>
-    <t>16.10.202655</t>
-  </si>
-  <si>
-    <t>16.10.202656</t>
-  </si>
-  <si>
-    <t>16.10.202657</t>
-  </si>
-  <si>
-    <t>16.10.202658</t>
-  </si>
-  <si>
-    <t>16.10.202659</t>
-  </si>
-  <si>
-    <t>16.10.202660</t>
-  </si>
-  <si>
-    <t>16.10.202661</t>
-  </si>
-  <si>
-    <t>16.10.202662</t>
-  </si>
-  <si>
-    <t>16.10.202663</t>
-  </si>
-  <si>
-    <t>16.10.202664</t>
-  </si>
-  <si>
-    <t>16.10.202665</t>
-  </si>
-  <si>
-    <t>16.10.202666</t>
-  </si>
-  <si>
-    <t>16.10.202667</t>
-  </si>
-  <si>
-    <t>16.10.202668</t>
-  </si>
-  <si>
-    <t>16.10.202669</t>
-  </si>
-  <si>
-    <t>16.10.202670</t>
-  </si>
-  <si>
-    <t>16.10.202671</t>
-  </si>
-  <si>
-    <t>16.10.202672</t>
-  </si>
-  <si>
-    <t>16.10.202673</t>
-  </si>
-  <si>
-    <t>16.10.202674</t>
-  </si>
-  <si>
-    <t>16.10.202675</t>
-  </si>
-  <si>
-    <t>16.10.202676</t>
-  </si>
-  <si>
-    <t>16.10.202677</t>
-  </si>
-  <si>
-    <t>16.10.202678</t>
-  </si>
-  <si>
-    <t>16.10.202679</t>
-  </si>
-  <si>
-    <t>16.10.202680</t>
-  </si>
-  <si>
-    <t>16.10.202681</t>
-  </si>
-  <si>
-    <t>16.10.202682</t>
-  </si>
-  <si>
-    <t>16.10.202683</t>
-  </si>
-  <si>
-    <t>16.10.202684</t>
-  </si>
-  <si>
-    <t>16.10.202685</t>
-  </si>
-  <si>
-    <t>16.10.202686</t>
-  </si>
-  <si>
-    <t>16.10.202687</t>
-  </si>
-  <si>
-    <t>16.10.202688</t>
-  </si>
-  <si>
-    <t>16.10.202689</t>
-  </si>
-  <si>
-    <t>16.10.202690</t>
-  </si>
-  <si>
-    <t>16.10.202691</t>
-  </si>
-  <si>
-    <t>16.10.202692</t>
-  </si>
-  <si>
-    <t>16.10.202693</t>
-  </si>
-  <si>
-    <t>16.10.202694</t>
-  </si>
-  <si>
-    <t>16.10.202695</t>
-  </si>
-  <si>
-    <t>16.10.202696</t>
+    <t>20.10.20261</t>
+  </si>
+  <si>
+    <t>20.10.20262</t>
+  </si>
+  <si>
+    <t>20.10.20263</t>
+  </si>
+  <si>
+    <t>20.10.20264</t>
+  </si>
+  <si>
+    <t>20.10.20265</t>
+  </si>
+  <si>
+    <t>20.10.20266</t>
+  </si>
+  <si>
+    <t>20.10.20267</t>
+  </si>
+  <si>
+    <t>20.10.20268</t>
+  </si>
+  <si>
+    <t>20.10.20269</t>
+  </si>
+  <si>
+    <t>20.10.202610</t>
+  </si>
+  <si>
+    <t>20.10.202611</t>
+  </si>
+  <si>
+    <t>20.10.202612</t>
+  </si>
+  <si>
+    <t>20.10.202613</t>
+  </si>
+  <si>
+    <t>20.10.202614</t>
+  </si>
+  <si>
+    <t>20.10.202615</t>
+  </si>
+  <si>
+    <t>20.10.202616</t>
+  </si>
+  <si>
+    <t>20.10.202617</t>
+  </si>
+  <si>
+    <t>20.10.202618</t>
+  </si>
+  <si>
+    <t>20.10.202619</t>
+  </si>
+  <si>
+    <t>20.10.202620</t>
+  </si>
+  <si>
+    <t>20.10.202621</t>
+  </si>
+  <si>
+    <t>20.10.202622</t>
+  </si>
+  <si>
+    <t>20.10.202623</t>
+  </si>
+  <si>
+    <t>20.10.202624</t>
+  </si>
+  <si>
+    <t>20.10.202625</t>
+  </si>
+  <si>
+    <t>20.10.202626</t>
+  </si>
+  <si>
+    <t>20.10.202627</t>
+  </si>
+  <si>
+    <t>20.10.202628</t>
+  </si>
+  <si>
+    <t>20.10.202629</t>
+  </si>
+  <si>
+    <t>20.10.202630</t>
+  </si>
+  <si>
+    <t>20.10.202631</t>
+  </si>
+  <si>
+    <t>20.10.202632</t>
+  </si>
+  <si>
+    <t>20.10.202633</t>
+  </si>
+  <si>
+    <t>20.10.202634</t>
+  </si>
+  <si>
+    <t>20.10.202635</t>
+  </si>
+  <si>
+    <t>20.10.202636</t>
+  </si>
+  <si>
+    <t>20.10.202637</t>
+  </si>
+  <si>
+    <t>20.10.202638</t>
+  </si>
+  <si>
+    <t>20.10.202639</t>
+  </si>
+  <si>
+    <t>20.10.202640</t>
+  </si>
+  <si>
+    <t>20.10.202641</t>
+  </si>
+  <si>
+    <t>20.10.202642</t>
+  </si>
+  <si>
+    <t>20.10.202643</t>
+  </si>
+  <si>
+    <t>20.10.202644</t>
+  </si>
+  <si>
+    <t>20.10.202645</t>
+  </si>
+  <si>
+    <t>20.10.202646</t>
+  </si>
+  <si>
+    <t>20.10.202647</t>
+  </si>
+  <si>
+    <t>20.10.202648</t>
+  </si>
+  <si>
+    <t>20.10.202649</t>
+  </si>
+  <si>
+    <t>20.10.202650</t>
+  </si>
+  <si>
+    <t>20.10.202651</t>
+  </si>
+  <si>
+    <t>20.10.202652</t>
+  </si>
+  <si>
+    <t>20.10.202653</t>
+  </si>
+  <si>
+    <t>20.10.202654</t>
+  </si>
+  <si>
+    <t>20.10.202655</t>
+  </si>
+  <si>
+    <t>20.10.202656</t>
+  </si>
+  <si>
+    <t>20.10.202657</t>
+  </si>
+  <si>
+    <t>20.10.202658</t>
+  </si>
+  <si>
+    <t>20.10.202659</t>
+  </si>
+  <si>
+    <t>20.10.202660</t>
+  </si>
+  <si>
+    <t>20.10.202661</t>
+  </si>
+  <si>
+    <t>20.10.202662</t>
+  </si>
+  <si>
+    <t>20.10.202663</t>
+  </si>
+  <si>
+    <t>20.10.202664</t>
+  </si>
+  <si>
+    <t>20.10.202665</t>
+  </si>
+  <si>
+    <t>20.10.202666</t>
+  </si>
+  <si>
+    <t>20.10.202667</t>
+  </si>
+  <si>
+    <t>20.10.202668</t>
+  </si>
+  <si>
+    <t>20.10.202669</t>
+  </si>
+  <si>
+    <t>20.10.202670</t>
+  </si>
+  <si>
+    <t>20.10.202671</t>
+  </si>
+  <si>
+    <t>20.10.202672</t>
+  </si>
+  <si>
+    <t>20.10.202673</t>
+  </si>
+  <si>
+    <t>20.10.202674</t>
+  </si>
+  <si>
+    <t>20.10.202675</t>
+  </si>
+  <si>
+    <t>20.10.202676</t>
+  </si>
+  <si>
+    <t>20.10.202677</t>
+  </si>
+  <si>
+    <t>20.10.202678</t>
+  </si>
+  <si>
+    <t>20.10.202679</t>
+  </si>
+  <si>
+    <t>20.10.202680</t>
+  </si>
+  <si>
+    <t>20.10.202681</t>
+  </si>
+  <si>
+    <t>20.10.202682</t>
+  </si>
+  <si>
+    <t>20.10.202683</t>
+  </si>
+  <si>
+    <t>20.10.202684</t>
+  </si>
+  <si>
+    <t>20.10.202685</t>
+  </si>
+  <si>
+    <t>20.10.202686</t>
+  </si>
+  <si>
+    <t>20.10.202687</t>
+  </si>
+  <si>
+    <t>20.10.202688</t>
+  </si>
+  <si>
+    <t>20.10.202689</t>
+  </si>
+  <si>
+    <t>20.10.202690</t>
+  </si>
+  <si>
+    <t>20.10.202691</t>
+  </si>
+  <si>
+    <t>20.10.202692</t>
+  </si>
+  <si>
+    <t>20.10.202693</t>
+  </si>
+  <si>
+    <t>20.10.202694</t>
+  </si>
+  <si>
+    <t>20.10.202695</t>
+  </si>
+  <si>
+    <t>20.10.202696</t>
+  </si>
+  <si>
+    <t>21.10.20261</t>
+  </si>
+  <si>
+    <t>21.10.20262</t>
+  </si>
+  <si>
+    <t>21.10.20263</t>
+  </si>
+  <si>
+    <t>21.10.20264</t>
+  </si>
+  <si>
+    <t>21.10.20265</t>
+  </si>
+  <si>
+    <t>21.10.20266</t>
+  </si>
+  <si>
+    <t>21.10.20267</t>
+  </si>
+  <si>
+    <t>21.10.20268</t>
+  </si>
+  <si>
+    <t>21.10.20269</t>
+  </si>
+  <si>
+    <t>21.10.202610</t>
+  </si>
+  <si>
+    <t>21.10.202611</t>
+  </si>
+  <si>
+    <t>21.10.202612</t>
+  </si>
+  <si>
+    <t>21.10.202613</t>
+  </si>
+  <si>
+    <t>21.10.202614</t>
+  </si>
+  <si>
+    <t>21.10.202615</t>
+  </si>
+  <si>
+    <t>21.10.202616</t>
+  </si>
+  <si>
+    <t>21.10.202617</t>
+  </si>
+  <si>
+    <t>21.10.202618</t>
+  </si>
+  <si>
+    <t>21.10.202619</t>
+  </si>
+  <si>
+    <t>21.10.202620</t>
+  </si>
+  <si>
+    <t>21.10.202621</t>
+  </si>
+  <si>
+    <t>21.10.202622</t>
+  </si>
+  <si>
+    <t>21.10.202623</t>
+  </si>
+  <si>
+    <t>21.10.202624</t>
+  </si>
+  <si>
+    <t>21.10.202625</t>
+  </si>
+  <si>
+    <t>21.10.202626</t>
+  </si>
+  <si>
+    <t>21.10.202627</t>
+  </si>
+  <si>
+    <t>21.10.202628</t>
+  </si>
+  <si>
+    <t>21.10.202629</t>
+  </si>
+  <si>
+    <t>21.10.202630</t>
+  </si>
+  <si>
+    <t>21.10.202631</t>
+  </si>
+  <si>
+    <t>21.10.202632</t>
+  </si>
+  <si>
+    <t>21.10.202633</t>
+  </si>
+  <si>
+    <t>21.10.202634</t>
+  </si>
+  <si>
+    <t>21.10.202635</t>
+  </si>
+  <si>
+    <t>21.10.202636</t>
+  </si>
+  <si>
+    <t>21.10.202637</t>
+  </si>
+  <si>
+    <t>21.10.202638</t>
+  </si>
+  <si>
+    <t>21.10.202639</t>
+  </si>
+  <si>
+    <t>21.10.202640</t>
+  </si>
+  <si>
+    <t>21.10.202641</t>
+  </si>
+  <si>
+    <t>21.10.202642</t>
+  </si>
+  <si>
+    <t>21.10.202643</t>
+  </si>
+  <si>
+    <t>21.10.202644</t>
+  </si>
+  <si>
+    <t>21.10.202645</t>
+  </si>
+  <si>
+    <t>21.10.202646</t>
+  </si>
+  <si>
+    <t>21.10.202647</t>
+  </si>
+  <si>
+    <t>21.10.202648</t>
+  </si>
+  <si>
+    <t>21.10.202649</t>
+  </si>
+  <si>
+    <t>21.10.202650</t>
+  </si>
+  <si>
+    <t>21.10.202651</t>
+  </si>
+  <si>
+    <t>21.10.202652</t>
+  </si>
+  <si>
+    <t>21.10.202653</t>
+  </si>
+  <si>
+    <t>21.10.202654</t>
+  </si>
+  <si>
+    <t>21.10.202655</t>
+  </si>
+  <si>
+    <t>21.10.202656</t>
+  </si>
+  <si>
+    <t>21.10.202657</t>
+  </si>
+  <si>
+    <t>21.10.202658</t>
+  </si>
+  <si>
+    <t>21.10.202659</t>
+  </si>
+  <si>
+    <t>21.10.202660</t>
+  </si>
+  <si>
+    <t>21.10.202661</t>
+  </si>
+  <si>
+    <t>21.10.202662</t>
+  </si>
+  <si>
+    <t>21.10.202663</t>
+  </si>
+  <si>
+    <t>21.10.202664</t>
+  </si>
+  <si>
+    <t>21.10.202665</t>
+  </si>
+  <si>
+    <t>21.10.202666</t>
+  </si>
+  <si>
+    <t>21.10.202667</t>
+  </si>
+  <si>
+    <t>21.10.202668</t>
+  </si>
+  <si>
+    <t>21.10.202669</t>
+  </si>
+  <si>
+    <t>21.10.202670</t>
+  </si>
+  <si>
+    <t>21.10.202671</t>
+  </si>
+  <si>
+    <t>21.10.202672</t>
+  </si>
+  <si>
+    <t>21.10.202673</t>
+  </si>
+  <si>
+    <t>21.10.202674</t>
+  </si>
+  <si>
+    <t>21.10.202675</t>
+  </si>
+  <si>
+    <t>21.10.202676</t>
+  </si>
+  <si>
+    <t>21.10.202677</t>
+  </si>
+  <si>
+    <t>21.10.202678</t>
+  </si>
+  <si>
+    <t>21.10.202679</t>
+  </si>
+  <si>
+    <t>21.10.202680</t>
+  </si>
+  <si>
+    <t>21.10.202681</t>
+  </si>
+  <si>
+    <t>21.10.202682</t>
+  </si>
+  <si>
+    <t>21.10.202683</t>
+  </si>
+  <si>
+    <t>21.10.202684</t>
+  </si>
+  <si>
+    <t>21.10.202685</t>
+  </si>
+  <si>
+    <t>21.10.202686</t>
+  </si>
+  <si>
+    <t>21.10.202687</t>
+  </si>
+  <si>
+    <t>21.10.202688</t>
+  </si>
+  <si>
+    <t>21.10.202689</t>
+  </si>
+  <si>
+    <t>21.10.202690</t>
+  </si>
+  <si>
+    <t>21.10.202691</t>
+  </si>
+  <si>
+    <t>21.10.202692</t>
+  </si>
+  <si>
+    <t>21.10.202693</t>
+  </si>
+  <si>
+    <t>21.10.202694</t>
+  </si>
+  <si>
+    <t>21.10.202695</t>
+  </si>
+  <si>
+    <t>21.10.202696</t>
   </si>
 </sst>
 </file>
@@ -1000,16 +1000,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46310</v>
+        <v>46315</v>
       </c>
       <c r="B2">
-        <v>21.768</v>
+        <v>0.053</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>7.99</v>
       </c>
       <c r="D2">
-        <v>20.25</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1023,16 +1023,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46310.01041666666</v>
+        <v>46315.01041666666</v>
       </c>
       <c r="B3">
-        <v>6.192</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>19.345</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1046,16 +1046,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46310.02083333334</v>
+        <v>46315.02083333334</v>
       </c>
       <c r="B4">
-        <v>4.244</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>13.189</v>
       </c>
       <c r="D4">
-        <v>15.25</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1069,16 +1069,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46310.03125</v>
+        <v>46315.03125</v>
       </c>
       <c r="B5">
-        <v>16.19</v>
+        <v>0.032</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>2.205</v>
       </c>
       <c r="D5">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1092,16 +1092,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46310.04166666666</v>
+        <v>46315.04166666666</v>
       </c>
       <c r="B6">
-        <v>2.898</v>
+        <v>23.606</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D6">
-        <v>11.25</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1115,16 +1115,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46310.05208333334</v>
+        <v>46315.05208333334</v>
       </c>
       <c r="B7">
-        <v>12.534</v>
+        <v>26.444</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1138,16 +1138,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46310.0625</v>
+        <v>46315.0625</v>
       </c>
       <c r="B8">
-        <v>0.412</v>
+        <v>15.138</v>
       </c>
       <c r="C8">
-        <v>4.522</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1161,16 +1161,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46310.07291666666</v>
+        <v>46315.07291666666</v>
       </c>
       <c r="B9">
-        <v>0.042</v>
+        <v>7.281</v>
       </c>
       <c r="C9">
-        <v>1.649</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1184,13 +1184,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46310.08333333334</v>
+        <v>46315.08333333334</v>
       </c>
       <c r="B10">
-        <v>0.008</v>
+        <v>2.356</v>
       </c>
       <c r="C10">
-        <v>3.463</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1207,13 +1207,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46310.09375</v>
+        <v>46315.09375</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="C11">
-        <v>4.799</v>
+        <v>4.064</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1230,13 +1230,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46310.10416666666</v>
+        <v>46315.10416666666</v>
       </c>
       <c r="B12">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>0.058</v>
+        <v>5.647</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1253,13 +1253,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46310.11458333334</v>
+        <v>46315.11458333334</v>
       </c>
       <c r="B13">
-        <v>15.815</v>
+        <v>0.011</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>3.107</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1276,13 +1276,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46310.125</v>
+        <v>46315.125</v>
       </c>
       <c r="B14">
-        <v>10.129</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>6.191</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1299,13 +1299,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46310.13541666666</v>
+        <v>46315.13541666666</v>
       </c>
       <c r="B15">
-        <v>5.931</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>0.382</v>
+        <v>8.704000000000001</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1322,13 +1322,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46310.14583333334</v>
+        <v>46315.14583333334</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>0.225</v>
       </c>
       <c r="C16">
-        <v>2.627</v>
+        <v>4.783</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46310.15625</v>
+        <v>46315.15625</v>
       </c>
       <c r="B17">
-        <v>0.043</v>
+        <v>8.170999999999999</v>
       </c>
       <c r="C17">
-        <v>0.491</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1368,13 +1368,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46310.16666666666</v>
+        <v>46315.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.007</v>
+        <v>2.744</v>
       </c>
       <c r="C18">
-        <v>4.836</v>
+        <v>0.2</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1391,13 +1391,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46310.17708333334</v>
+        <v>46315.17708333334</v>
       </c>
       <c r="B19">
-        <v>0.001</v>
+        <v>1.575</v>
       </c>
       <c r="C19">
-        <v>8.992000000000001</v>
+        <v>0.159</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1414,13 +1414,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46310.1875</v>
+        <v>46315.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>0.323</v>
       </c>
       <c r="C20">
-        <v>9.448</v>
+        <v>0.487</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1437,13 +1437,13 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46310.19791666666</v>
+        <v>46315.19791666666</v>
       </c>
       <c r="B21">
-        <v>4.112</v>
+        <v>0.532</v>
       </c>
       <c r="C21">
-        <v>1.818</v>
+        <v>0.341</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1460,13 +1460,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46310.20833333334</v>
+        <v>46315.20833333334</v>
       </c>
       <c r="B22">
-        <v>20.627</v>
+        <v>0.018</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>4.887</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1483,13 +1483,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46310.21875</v>
+        <v>46315.21875</v>
       </c>
       <c r="B23">
-        <v>19.445</v>
+        <v>0.052</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1506,13 +1506,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46310.22916666666</v>
+        <v>46315.22916666666</v>
       </c>
       <c r="B24">
-        <v>18.638</v>
+        <v>0.276</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>0.244</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1529,13 +1529,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46310.23958333334</v>
+        <v>46315.23958333334</v>
       </c>
       <c r="B25">
-        <v>38.082</v>
+        <v>2.878</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>0.313</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1552,13 +1552,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46310.25</v>
+        <v>46315.25</v>
       </c>
       <c r="B26">
-        <v>18.861</v>
+        <v>1.36</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>3.544</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1575,13 +1575,13 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46310.26041666666</v>
+        <v>46315.26041666666</v>
       </c>
       <c r="B27">
-        <v>39.825</v>
+        <v>0.273</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>0.321</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1598,16 +1598,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46310.27083333334</v>
+        <v>46315.27083333334</v>
       </c>
       <c r="B28">
-        <v>26.214</v>
+        <v>3.263</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="D28">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1621,16 +1621,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46310.28125</v>
+        <v>46315.28125</v>
       </c>
       <c r="B29">
-        <v>5.274</v>
+        <v>3.338</v>
       </c>
       <c r="C29">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="D29">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1644,16 +1644,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46310.29166666666</v>
+        <v>46315.29166666666</v>
       </c>
       <c r="B30">
-        <v>17.573</v>
+        <v>0.581</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="D30">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1667,16 +1667,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46310.30208333334</v>
+        <v>46315.30208333334</v>
       </c>
       <c r="B31">
-        <v>25.642</v>
+        <v>0.034</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>2.277</v>
       </c>
       <c r="D31">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1690,16 +1690,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46310.3125</v>
+        <v>46315.3125</v>
       </c>
       <c r="B32">
-        <v>21.438</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>5.164</v>
       </c>
       <c r="D32">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1713,16 +1713,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46310.32291666666</v>
+        <v>46315.32291666666</v>
       </c>
       <c r="B33">
-        <v>5.886</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>0.14</v>
+        <v>9.404</v>
       </c>
       <c r="D33">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1736,16 +1736,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46310.33333333334</v>
+        <v>46315.33333333334</v>
       </c>
       <c r="B34">
-        <v>82.312</v>
+        <v>0.054</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>2.271</v>
       </c>
       <c r="D34">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1759,16 +1759,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46310.34375</v>
+        <v>46315.34375</v>
       </c>
       <c r="B35">
-        <v>87.51900000000001</v>
+        <v>0.174</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>1.041</v>
       </c>
       <c r="D35">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -1782,16 +1782,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46310.35416666666</v>
+        <v>46315.35416666666</v>
       </c>
       <c r="B36">
-        <v>58.285</v>
+        <v>17.083</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="D36">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -1805,16 +1805,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46310.36458333334</v>
+        <v>46315.36458333334</v>
       </c>
       <c r="B37">
-        <v>0.751</v>
+        <v>2.969</v>
       </c>
       <c r="C37">
-        <v>0.317</v>
+        <v>2.596</v>
       </c>
       <c r="D37">
-        <v>186.75</v>
+        <v>0</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -1828,16 +1828,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46310.375</v>
+        <v>46315.375</v>
       </c>
       <c r="B38">
-        <v>0.852</v>
+        <v>5.988</v>
       </c>
       <c r="C38">
-        <v>0.196</v>
+        <v>0.454</v>
       </c>
       <c r="D38">
-        <v>164.25</v>
+        <v>0</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -1851,16 +1851,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46310.38541666666</v>
+        <v>46315.38541666666</v>
       </c>
       <c r="B39">
-        <v>0.116</v>
+        <v>6.509</v>
       </c>
       <c r="C39">
-        <v>0.588</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>164.25</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46310.39583333334</v>
+        <v>46315.39583333334</v>
       </c>
       <c r="B40">
-        <v>0.228</v>
+        <v>1.038</v>
       </c>
       <c r="C40">
-        <v>0.429</v>
+        <v>0.32</v>
       </c>
       <c r="D40">
-        <v>146.25</v>
+        <v>0</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -1897,16 +1897,16 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46310.40625</v>
+        <v>46315.40625</v>
       </c>
       <c r="B41">
-        <v>0.424</v>
+        <v>0.168</v>
       </c>
       <c r="C41">
-        <v>0.506</v>
+        <v>2.546</v>
       </c>
       <c r="D41">
-        <v>110.25</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -1920,16 +1920,16 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46310.41666666666</v>
+        <v>46315.41666666666</v>
       </c>
       <c r="B42">
-        <v>63.171</v>
+        <v>0.075</v>
       </c>
       <c r="C42">
-        <v>0.002</v>
+        <v>1.871</v>
       </c>
       <c r="D42">
-        <v>112.5</v>
+        <v>0</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -1943,16 +1943,16 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46310.42708333334</v>
+        <v>46315.42708333334</v>
       </c>
       <c r="B43">
-        <v>86.241</v>
+        <v>0.056</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>0.378</v>
       </c>
       <c r="D43">
-        <v>112.5</v>
+        <v>0</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -1966,19 +1966,19 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46310.4375</v>
+        <v>46315.4375</v>
       </c>
       <c r="B44">
-        <v>58.439</v>
+        <v>0.528</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="D44">
-        <v>161.75</v>
+        <v>0</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F44">
         <v>43</v>
@@ -1989,19 +1989,19 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46310.44791666666</v>
+        <v>46315.44791666666</v>
       </c>
       <c r="B45">
-        <v>30.894</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>1.453</v>
       </c>
       <c r="D45">
-        <v>153.75</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F45">
         <v>44</v>
@@ -2012,19 +2012,19 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46310.45833333334</v>
+        <v>46315.45833333334</v>
       </c>
       <c r="B46">
-        <v>0.008</v>
+        <v>0.745</v>
       </c>
       <c r="C46">
-        <v>5.924</v>
+        <v>0.122</v>
       </c>
       <c r="D46">
-        <v>187.5</v>
+        <v>0</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F46">
         <v>45</v>
@@ -2035,19 +2035,19 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46310.46875</v>
+        <v>46315.46875</v>
       </c>
       <c r="B47">
-        <v>0.061</v>
+        <v>0.036</v>
       </c>
       <c r="C47">
-        <v>1.179</v>
+        <v>1.279</v>
       </c>
       <c r="D47">
-        <v>187.5</v>
+        <v>0</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F47">
         <v>46</v>
@@ -2058,16 +2058,16 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46310.47916666666</v>
+        <v>46315.47916666666</v>
       </c>
       <c r="B48">
-        <v>0.314</v>
+        <v>0.091</v>
       </c>
       <c r="C48">
-        <v>0.221</v>
+        <v>1.807</v>
       </c>
       <c r="D48">
-        <v>149.25</v>
+        <v>0</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -2081,16 +2081,16 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46310.48958333334</v>
+        <v>46315.48958333334</v>
       </c>
       <c r="B49">
-        <v>0.319</v>
+        <v>0.344</v>
       </c>
       <c r="C49">
-        <v>2.085</v>
+        <v>0.979</v>
       </c>
       <c r="D49">
-        <v>112.5</v>
+        <v>0</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -2104,19 +2104,19 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46310.5</v>
+        <v>46315.5</v>
       </c>
       <c r="B50">
-        <v>0.049</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>2.785</v>
+        <v>6.625</v>
       </c>
       <c r="D50">
-        <v>112.5</v>
+        <v>0</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F50">
         <v>49</v>
@@ -2127,19 +2127,19 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46310.51041666666</v>
+        <v>46315.51041666666</v>
       </c>
       <c r="B51">
-        <v>0.705</v>
+        <v>0.71</v>
       </c>
       <c r="C51">
-        <v>0.602</v>
+        <v>0.344</v>
       </c>
       <c r="D51">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F51">
         <v>50</v>
@@ -2150,19 +2150,19 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46310.52083333334</v>
+        <v>46315.52083333334</v>
       </c>
       <c r="B52">
-        <v>0.507</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <v>0.08799999999999999</v>
+        <v>0.918</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F52">
         <v>51</v>
@@ -2173,19 +2173,19 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46310.53125</v>
+        <v>46315.53125</v>
       </c>
       <c r="B53">
-        <v>23.02</v>
+        <v>0.01</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>1.094</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F53">
         <v>52</v>
@@ -2196,19 +2196,19 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46310.54166666666</v>
+        <v>46315.54166666666</v>
       </c>
       <c r="B54">
-        <v>10.75</v>
+        <v>0.221</v>
       </c>
       <c r="C54">
-        <v>0.123</v>
+        <v>0.392</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F54">
         <v>53</v>
@@ -2219,19 +2219,19 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46310.55208333334</v>
+        <v>46315.55208333334</v>
       </c>
       <c r="B55">
-        <v>3.865</v>
+        <v>0.125</v>
       </c>
       <c r="C55">
-        <v>0.074</v>
+        <v>0.165</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="F55">
         <v>54</v>
@@ -2242,19 +2242,19 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46310.5625</v>
+        <v>46315.5625</v>
       </c>
       <c r="B56">
-        <v>12.704</v>
+        <v>0.475</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="F56">
         <v>55</v>
@@ -2265,19 +2265,19 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46310.57291666666</v>
+        <v>46315.57291666666</v>
       </c>
       <c r="B57">
-        <v>21.64</v>
+        <v>0.139</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="F57">
         <v>56</v>
@@ -2288,19 +2288,19 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46310.58333333334</v>
+        <v>46315.58333333334</v>
       </c>
       <c r="B58">
-        <v>7.003</v>
+        <v>0.16</v>
       </c>
       <c r="C58">
-        <v>0.064</v>
+        <v>0.871</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="F58">
         <v>57</v>
@@ -2311,19 +2311,19 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46310.59375</v>
+        <v>46315.59375</v>
       </c>
       <c r="B59">
-        <v>14.806</v>
+        <v>0.379</v>
       </c>
       <c r="C59">
-        <v>0.037</v>
+        <v>0.185</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="F59">
         <v>58</v>
@@ -2334,19 +2334,19 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46310.60416666666</v>
+        <v>46315.60416666666</v>
       </c>
       <c r="B60">
-        <v>10.982</v>
+        <v>2.275</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>2.991</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F60">
         <v>59</v>
@@ -2357,19 +2357,19 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46310.61458333334</v>
+        <v>46315.61458333334</v>
       </c>
       <c r="B61">
-        <v>12.629</v>
+        <v>6.249</v>
       </c>
       <c r="C61">
-        <v>0.065</v>
+        <v>2.439</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F61">
         <v>60</v>
@@ -2380,19 +2380,19 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46310.625</v>
+        <v>46315.625</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="C62">
-        <v>14.564</v>
+        <v>2.468</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F62">
         <v>61</v>
@@ -2403,19 +2403,19 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46310.63541666666</v>
+        <v>46315.63541666666</v>
       </c>
       <c r="B63">
-        <v>0.325</v>
+        <v>5.561</v>
       </c>
       <c r="C63">
-        <v>0.281</v>
+        <v>0.387</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F63">
         <v>62</v>
@@ -2426,19 +2426,19 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46310.64583333334</v>
+        <v>46315.64583333334</v>
       </c>
       <c r="B64">
-        <v>19.298</v>
+        <v>18.759</v>
       </c>
       <c r="C64">
-        <v>0.229</v>
+        <v>0</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>62.5</v>
+        <v>25</v>
       </c>
       <c r="F64">
         <v>63</v>
@@ -2449,10 +2449,10 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46310.65625</v>
+        <v>46315.65625</v>
       </c>
       <c r="B65">
-        <v>26.31</v>
+        <v>38.119</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="E65">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="F65">
         <v>64</v>
@@ -2472,19 +2472,19 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46310.66666666666</v>
+        <v>46315.66666666666</v>
       </c>
       <c r="B66">
-        <v>7.127</v>
+        <v>15.335</v>
       </c>
       <c r="C66">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>44.25</v>
+        <v>25</v>
       </c>
       <c r="F66">
         <v>65</v>
@@ -2495,19 +2495,19 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46310.67708333334</v>
+        <v>46315.67708333334</v>
       </c>
       <c r="B67">
-        <v>1.659</v>
+        <v>19.731</v>
       </c>
       <c r="C67">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>44.25</v>
+        <v>0</v>
       </c>
       <c r="F67">
         <v>66</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46310.6875</v>
+        <v>46315.6875</v>
       </c>
       <c r="B68">
-        <v>28.739</v>
+        <v>36.061</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -2530,7 +2530,7 @@
         <v>0</v>
       </c>
       <c r="E68">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F68">
         <v>67</v>
@@ -2541,10 +2541,10 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46310.69791666666</v>
+        <v>46315.69791666666</v>
       </c>
       <c r="B69">
-        <v>42.218</v>
+        <v>45.421</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="E69">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F69">
         <v>68</v>
@@ -2564,19 +2564,19 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46310.70833333334</v>
+        <v>46315.70833333334</v>
       </c>
       <c r="B70">
-        <v>29.738</v>
+        <v>7.143</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E70">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F70">
         <v>69</v>
@@ -2587,16 +2587,16 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46310.71875</v>
+        <v>46315.71875</v>
       </c>
       <c r="B71">
-        <v>29.792</v>
+        <v>0.176</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -2610,16 +2610,16 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46310.72916666666</v>
+        <v>46315.72916666666</v>
       </c>
       <c r="B72">
-        <v>41.983</v>
+        <v>0</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -2633,13 +2633,13 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46310.73958333334</v>
+        <v>46315.73958333334</v>
       </c>
       <c r="B73">
-        <v>9.535</v>
+        <v>0</v>
       </c>
       <c r="C73">
-        <v>1.584</v>
+        <v>0</v>
       </c>
       <c r="D73">
         <v>37.5</v>
@@ -2656,13 +2656,13 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46310.75</v>
+        <v>46315.75</v>
       </c>
       <c r="B74">
-        <v>0.328</v>
+        <v>0</v>
       </c>
       <c r="C74">
-        <v>4.812</v>
+        <v>0</v>
       </c>
       <c r="D74">
         <v>37.5</v>
@@ -2679,13 +2679,13 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46310.76041666666</v>
+        <v>46315.76041666666</v>
       </c>
       <c r="B75">
-        <v>0.176</v>
+        <v>0</v>
       </c>
       <c r="C75">
-        <v>1.203</v>
+        <v>0</v>
       </c>
       <c r="D75">
         <v>37.5</v>
@@ -2702,16 +2702,16 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46310.77083333334</v>
+        <v>46315.77083333334</v>
       </c>
       <c r="B76">
-        <v>0.211</v>
+        <v>0</v>
       </c>
       <c r="C76">
-        <v>0.169</v>
+        <v>0</v>
       </c>
       <c r="D76">
-        <v>35.75</v>
+        <v>12.25</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -2725,16 +2725,16 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46310.78125</v>
+        <v>46315.78125</v>
       </c>
       <c r="B77">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="C77">
-        <v>0.134</v>
+        <v>0</v>
       </c>
       <c r="D77">
-        <v>36.75</v>
+        <v>12.5</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -2748,16 +2748,16 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46310.79166666666</v>
+        <v>46315.79166666666</v>
       </c>
       <c r="B78">
-        <v>11.373</v>
+        <v>0</v>
       </c>
       <c r="C78">
         <v>0</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -2771,16 +2771,16 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46310.80208333334</v>
+        <v>46315.80208333334</v>
       </c>
       <c r="B79">
-        <v>4.43</v>
+        <v>21.729</v>
       </c>
       <c r="C79">
         <v>0</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46310.8125</v>
+        <v>46315.8125</v>
       </c>
       <c r="B80">
-        <v>11.111</v>
+        <v>12.454</v>
       </c>
       <c r="C80">
-        <v>1.517</v>
+        <v>0</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -2817,13 +2817,13 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46310.82291666666</v>
+        <v>46315.82291666666</v>
       </c>
       <c r="B81">
-        <v>4.463</v>
+        <v>54.277</v>
       </c>
       <c r="C81">
-        <v>0.102</v>
+        <v>0</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -2840,16 +2840,16 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46310.83333333334</v>
+        <v>46315.83333333334</v>
       </c>
       <c r="B82">
-        <v>4.287</v>
+        <v>67.018</v>
       </c>
       <c r="C82">
-        <v>1.718</v>
+        <v>0</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -2863,16 +2863,16 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46310.84375</v>
+        <v>46315.84375</v>
       </c>
       <c r="B83">
-        <v>0.026</v>
+        <v>27.225</v>
       </c>
       <c r="C83">
-        <v>2.192</v>
+        <v>0.08</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -2886,16 +2886,16 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46310.85416666666</v>
+        <v>46315.85416666666</v>
       </c>
       <c r="B84">
-        <v>0.011</v>
+        <v>0.073</v>
       </c>
       <c r="C84">
-        <v>8.183</v>
+        <v>0.268</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>86.5</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -2909,16 +2909,16 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46310.86458333334</v>
+        <v>46315.86458333334</v>
       </c>
       <c r="B85">
-        <v>0</v>
+        <v>9.989000000000001</v>
       </c>
       <c r="C85">
-        <v>5.933</v>
+        <v>0</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -2932,16 +2932,16 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46310.875</v>
+        <v>46315.875</v>
       </c>
       <c r="B86">
-        <v>2.714</v>
+        <v>23.845</v>
       </c>
       <c r="C86">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="D86">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -2955,16 +2955,16 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46310.88541666666</v>
+        <v>46315.88541666666</v>
       </c>
       <c r="B87">
-        <v>0.857</v>
+        <v>21.275</v>
       </c>
       <c r="C87">
-        <v>0.412</v>
+        <v>0</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -2978,13 +2978,13 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46310.89583333334</v>
+        <v>46315.89583333334</v>
       </c>
       <c r="B88">
-        <v>0.336</v>
+        <v>44.34</v>
       </c>
       <c r="C88">
-        <v>0.842</v>
+        <v>0</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3001,13 +3001,13 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46310.90625</v>
+        <v>46315.90625</v>
       </c>
       <c r="B89">
-        <v>0.015</v>
+        <v>35.886</v>
       </c>
       <c r="C89">
-        <v>2.563</v>
+        <v>0</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3024,16 +3024,16 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46310.91666666666</v>
+        <v>46315.91666666666</v>
       </c>
       <c r="B90">
-        <v>2.497</v>
+        <v>2.229</v>
       </c>
       <c r="C90">
-        <v>0.832</v>
+        <v>1.726</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>48.5</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -3047,16 +3047,16 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46310.92708333334</v>
+        <v>46315.92708333334</v>
       </c>
       <c r="B91">
-        <v>1.598</v>
+        <v>0</v>
       </c>
       <c r="C91">
-        <v>0.08699999999999999</v>
+        <v>5.475</v>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>48.5</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -3070,16 +3070,16 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46310.9375</v>
+        <v>46315.9375</v>
       </c>
       <c r="B92">
-        <v>0.304</v>
+        <v>0</v>
       </c>
       <c r="C92">
-        <v>0.156</v>
+        <v>18.968</v>
       </c>
       <c r="D92">
-        <v>0</v>
+        <v>48.5</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -3093,16 +3093,16 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46310.94791666666</v>
+        <v>46315.94791666666</v>
       </c>
       <c r="B93">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="C93">
-        <v>4.118</v>
+        <v>19.133</v>
       </c>
       <c r="D93">
-        <v>0</v>
+        <v>48.5</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -3116,16 +3116,16 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46310.95833333334</v>
+        <v>46315.95833333334</v>
       </c>
       <c r="B94">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="C94">
-        <v>3.909</v>
+        <v>14.45</v>
       </c>
       <c r="D94">
-        <v>0</v>
+        <v>43.25</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3139,13 +3139,13 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46310.96875</v>
+        <v>46315.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
       </c>
       <c r="C95">
-        <v>4.158</v>
+        <v>6.406</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3162,13 +3162,13 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46310.97916666666</v>
+        <v>46315.97916666666</v>
       </c>
       <c r="B96">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="C96">
-        <v>0.961</v>
+        <v>10.597</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3185,13 +3185,13 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46310.98958333334</v>
+        <v>46315.98958333334</v>
       </c>
       <c r="B97">
-        <v>0.132</v>
+        <v>0</v>
       </c>
       <c r="C97">
-        <v>0.26</v>
+        <v>16.641</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3208,13 +3208,13 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46311</v>
+        <v>46316</v>
       </c>
       <c r="B98">
-        <v>1.663</v>
+        <v>5.706</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>4.145</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3231,13 +3231,13 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46311.01041666666</v>
+        <v>46316.01041666666</v>
       </c>
       <c r="B99">
-        <v>5.058</v>
+        <v>0.062</v>
       </c>
       <c r="C99">
-        <v>0</v>
+        <v>1.966</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -3254,13 +3254,13 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46311.02083333334</v>
+        <v>46316.02083333334</v>
       </c>
       <c r="B100">
-        <v>22.692</v>
+        <v>0.446</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>0.979</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -3277,16 +3277,16 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46311.03125</v>
+        <v>46316.03125</v>
       </c>
       <c r="B101">
-        <v>1.309</v>
+        <v>7.897</v>
       </c>
       <c r="C101">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="D101">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -3300,16 +3300,16 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46311.04166666666</v>
+        <v>46316.04166666666</v>
       </c>
       <c r="B102">
-        <v>3.23</v>
+        <v>3.743</v>
       </c>
       <c r="C102">
-        <v>0.054</v>
+        <v>0.049</v>
       </c>
       <c r="D102">
-        <v>22.75</v>
+        <v>0</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -3323,13 +3323,13 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46311.05208333334</v>
+        <v>46316.05208333334</v>
       </c>
       <c r="B103">
-        <v>0.141</v>
+        <v>0.496</v>
       </c>
       <c r="C103">
-        <v>1.417</v>
+        <v>0.012</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -3346,13 +3346,13 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46311.0625</v>
+        <v>46316.0625</v>
       </c>
       <c r="B104">
-        <v>0.013</v>
+        <v>3.12</v>
       </c>
       <c r="C104">
-        <v>4.628</v>
+        <v>0</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -3369,13 +3369,13 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46311.07291666666</v>
+        <v>46316.07291666666</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>12.075</v>
       </c>
       <c r="C105">
-        <v>12.88</v>
+        <v>0</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -3392,13 +3392,13 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46311.08333333334</v>
+        <v>46316.08333333334</v>
       </c>
       <c r="B106">
-        <v>0.011</v>
+        <v>17.108</v>
       </c>
       <c r="C106">
-        <v>2.678</v>
+        <v>0</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -3415,16 +3415,16 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46311.09375</v>
+        <v>46316.09375</v>
       </c>
       <c r="B107">
-        <v>0.008</v>
+        <v>0.183</v>
       </c>
       <c r="C107">
-        <v>5.862</v>
+        <v>6.13</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>47.75</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -3438,16 +3438,16 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46311.10416666666</v>
+        <v>46316.10416666666</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>0.889</v>
       </c>
       <c r="C108">
-        <v>8.457000000000001</v>
+        <v>0.912</v>
       </c>
       <c r="D108">
-        <v>0</v>
+        <v>47.75</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -3461,16 +3461,16 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46311.11458333334</v>
+        <v>46316.11458333334</v>
       </c>
       <c r="B109">
-        <v>0.033</v>
+        <v>0.143</v>
       </c>
       <c r="C109">
-        <v>1.464</v>
+        <v>1.982</v>
       </c>
       <c r="D109">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -3484,16 +3484,16 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46311.125</v>
+        <v>46316.125</v>
       </c>
       <c r="B110">
-        <v>3.072</v>
+        <v>0.506</v>
       </c>
       <c r="C110">
-        <v>0.015</v>
+        <v>0.089</v>
       </c>
       <c r="D110">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -3507,16 +3507,16 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46311.13541666666</v>
+        <v>46316.13541666666</v>
       </c>
       <c r="B111">
-        <v>14.189</v>
+        <v>25.097</v>
       </c>
       <c r="C111">
         <v>0</v>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>30.5</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -3530,16 +3530,16 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46311.14583333334</v>
+        <v>46316.14583333334</v>
       </c>
       <c r="B112">
-        <v>3.087</v>
+        <v>7.911</v>
       </c>
       <c r="C112">
-        <v>0.016</v>
+        <v>0.003</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -3553,16 +3553,16 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46311.15625</v>
+        <v>46316.15625</v>
       </c>
       <c r="B113">
-        <v>6.626</v>
+        <v>0.051</v>
       </c>
       <c r="C113">
-        <v>0.024</v>
+        <v>0.472</v>
       </c>
       <c r="D113">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -3576,16 +3576,16 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46311.16666666666</v>
+        <v>46316.16666666666</v>
       </c>
       <c r="B114">
-        <v>0.274</v>
+        <v>10.817</v>
       </c>
       <c r="C114">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="D114">
-        <v>0</v>
+        <v>30.5</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -3599,16 +3599,16 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46311.17708333334</v>
+        <v>46316.17708333334</v>
       </c>
       <c r="B115">
-        <v>0.188</v>
+        <v>0.512</v>
       </c>
       <c r="C115">
-        <v>0.041</v>
+        <v>0.171</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -3622,16 +3622,16 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46311.1875</v>
+        <v>46316.1875</v>
       </c>
       <c r="B116">
-        <v>0.143</v>
+        <v>0.188</v>
       </c>
       <c r="C116">
-        <v>0.235</v>
+        <v>0.308</v>
       </c>
       <c r="D116">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -3645,16 +3645,16 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46311.19791666666</v>
+        <v>46316.19791666666</v>
       </c>
       <c r="B117">
-        <v>0.002</v>
+        <v>0.044</v>
       </c>
       <c r="C117">
-        <v>3.088</v>
+        <v>0.283</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -3668,16 +3668,16 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46311.20833333334</v>
+        <v>46316.20833333334</v>
       </c>
       <c r="B118">
-        <v>0</v>
+        <v>0.028</v>
       </c>
       <c r="C118">
-        <v>6.463</v>
+        <v>4.472</v>
       </c>
       <c r="D118">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -3691,16 +3691,16 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46311.21875</v>
+        <v>46316.21875</v>
       </c>
       <c r="B119">
-        <v>0.075</v>
+        <v>0.128</v>
       </c>
       <c r="C119">
-        <v>0.388</v>
+        <v>1.623</v>
       </c>
       <c r="D119">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -3714,13 +3714,13 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46311.22916666666</v>
+        <v>46316.22916666666</v>
       </c>
       <c r="B120">
-        <v>0.03</v>
+        <v>36.495</v>
       </c>
       <c r="C120">
-        <v>0.199</v>
+        <v>0</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -3737,13 +3737,13 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46311.23958333334</v>
+        <v>46316.23958333334</v>
       </c>
       <c r="B121">
-        <v>0.217</v>
+        <v>36.702</v>
       </c>
       <c r="C121">
-        <v>0.236</v>
+        <v>0</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -3760,13 +3760,13 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46311.25</v>
+        <v>46316.25</v>
       </c>
       <c r="B122">
-        <v>0</v>
+        <v>15.593</v>
       </c>
       <c r="C122">
-        <v>8.736000000000001</v>
+        <v>0</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -3783,13 +3783,13 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46311.26041666666</v>
+        <v>46316.26041666666</v>
       </c>
       <c r="B123">
-        <v>0.172</v>
+        <v>31.51</v>
       </c>
       <c r="C123">
-        <v>0.321</v>
+        <v>0</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -3806,13 +3806,13 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46311.27083333334</v>
+        <v>46316.27083333334</v>
       </c>
       <c r="B124">
-        <v>0.017</v>
+        <v>22.919</v>
       </c>
       <c r="C124">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -3829,13 +3829,13 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46311.28125</v>
+        <v>46316.28125</v>
       </c>
       <c r="B125">
-        <v>0.004</v>
+        <v>33.346</v>
       </c>
       <c r="C125">
-        <v>1.893</v>
+        <v>0</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -3852,13 +3852,13 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46311.29166666666</v>
+        <v>46316.29166666666</v>
       </c>
       <c r="B126">
-        <v>0.35</v>
+        <v>3.439</v>
       </c>
       <c r="C126">
-        <v>0.176</v>
+        <v>2.015</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -3875,13 +3875,13 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46311.30208333334</v>
+        <v>46316.30208333334</v>
       </c>
       <c r="B127">
-        <v>0.394</v>
+        <v>2.85</v>
       </c>
       <c r="C127">
-        <v>0.099</v>
+        <v>0.083</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -3898,13 +3898,13 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46311.3125</v>
+        <v>46316.3125</v>
       </c>
       <c r="B128">
-        <v>1.924</v>
+        <v>1.046</v>
       </c>
       <c r="C128">
-        <v>0.114</v>
+        <v>1.075</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -3921,13 +3921,13 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46311.32291666666</v>
+        <v>46316.32291666666</v>
       </c>
       <c r="B129">
-        <v>0.389</v>
+        <v>0.113</v>
       </c>
       <c r="C129">
-        <v>0.108</v>
+        <v>2.033</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46311.33333333334</v>
+        <v>46316.33333333334</v>
       </c>
       <c r="B130">
-        <v>22.835</v>
+        <v>16.105</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -3967,13 +3967,13 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46311.34375</v>
+        <v>46316.34375</v>
       </c>
       <c r="B131">
-        <v>6.489</v>
+        <v>26.328</v>
       </c>
       <c r="C131">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -3990,16 +3990,16 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46311.35416666666</v>
+        <v>46316.35416666666</v>
       </c>
       <c r="B132">
-        <v>2.285</v>
+        <v>23.555</v>
       </c>
       <c r="C132">
-        <v>3.821</v>
+        <v>0</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -4013,16 +4013,16 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46311.36458333334</v>
+        <v>46316.36458333334</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>27.931</v>
       </c>
       <c r="C133">
-        <v>14.676</v>
+        <v>0</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -4036,16 +4036,16 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46311.375</v>
+        <v>46316.375</v>
       </c>
       <c r="B134">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="C134">
-        <v>9.237</v>
+        <v>0</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -4059,16 +4059,16 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46311.38541666666</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="B135">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="C135">
-        <v>3.766</v>
+        <v>0</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -4082,13 +4082,13 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46311.39583333334</v>
+        <v>46316.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
       </c>
       <c r="C136">
-        <v>14.128</v>
+        <v>0</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -4105,19 +4105,19 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46311.40625</v>
+        <v>46316.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
       </c>
       <c r="C137">
-        <v>23.793</v>
+        <v>0</v>
       </c>
       <c r="D137">
         <v>0</v>
       </c>
       <c r="E137">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F137">
         <v>40</v>
@@ -4128,19 +4128,19 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46311.41666666666</v>
+        <v>46316.41666666666</v>
       </c>
       <c r="B138">
-        <v>2.164</v>
+        <v>0</v>
       </c>
       <c r="C138">
-        <v>6.274</v>
+        <v>0</v>
       </c>
       <c r="D138">
         <v>0</v>
       </c>
       <c r="E138">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="F138">
         <v>41</v>
@@ -4151,13 +4151,13 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46311.42708333334</v>
+        <v>46316.42708333334</v>
       </c>
       <c r="B139">
-        <v>0.067</v>
+        <v>0</v>
       </c>
       <c r="C139">
-        <v>0.723</v>
+        <v>0</v>
       </c>
       <c r="D139">
         <v>0</v>
@@ -4174,13 +4174,13 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46311.4375</v>
+        <v>46316.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
       </c>
       <c r="C140">
-        <v>6.158</v>
+        <v>0</v>
       </c>
       <c r="D140">
         <v>0</v>
@@ -4197,13 +4197,13 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46311.44791666666</v>
+        <v>46316.44791666666</v>
       </c>
       <c r="B141">
-        <v>11.561</v>
+        <v>0</v>
       </c>
       <c r="C141">
-        <v>0.677</v>
+        <v>0</v>
       </c>
       <c r="D141">
         <v>0</v>
@@ -4220,13 +4220,13 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46311.45833333334</v>
+        <v>46316.45833333334</v>
       </c>
       <c r="B142">
-        <v>0.447</v>
+        <v>0</v>
       </c>
       <c r="C142">
-        <v>1.006</v>
+        <v>0</v>
       </c>
       <c r="D142">
         <v>0</v>
@@ -4243,13 +4243,13 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46311.46875</v>
+        <v>46316.46875</v>
       </c>
       <c r="B143">
-        <v>0.067</v>
+        <v>0</v>
       </c>
       <c r="C143">
-        <v>4.021</v>
+        <v>0</v>
       </c>
       <c r="D143">
         <v>0</v>
@@ -4266,13 +4266,13 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46311.47916666666</v>
+        <v>46316.47916666666</v>
       </c>
       <c r="B144">
-        <v>2.433</v>
+        <v>0</v>
       </c>
       <c r="C144">
-        <v>0.322</v>
+        <v>0</v>
       </c>
       <c r="D144">
         <v>0</v>
@@ -4289,13 +4289,13 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46311.48958333334</v>
+        <v>46316.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
       </c>
       <c r="C145">
-        <v>15.561</v>
+        <v>0</v>
       </c>
       <c r="D145">
         <v>0</v>
@@ -4312,13 +4312,13 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46311.5</v>
+        <v>46316.5</v>
       </c>
       <c r="B146">
         <v>0</v>
       </c>
       <c r="C146">
-        <v>27.087</v>
+        <v>0</v>
       </c>
       <c r="D146">
         <v>0</v>
@@ -4335,13 +4335,13 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46311.51041666666</v>
+        <v>46316.51041666666</v>
       </c>
       <c r="B147">
-        <v>0.458</v>
+        <v>0</v>
       </c>
       <c r="C147">
-        <v>4.928</v>
+        <v>0</v>
       </c>
       <c r="D147">
         <v>0</v>
@@ -4358,13 +4358,13 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46311.52083333334</v>
+        <v>46316.52083333334</v>
       </c>
       <c r="B148">
-        <v>0.292</v>
+        <v>0</v>
       </c>
       <c r="C148">
-        <v>1.712</v>
+        <v>0</v>
       </c>
       <c r="D148">
         <v>0</v>
@@ -4381,13 +4381,13 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46311.53125</v>
+        <v>46316.53125</v>
       </c>
       <c r="B149">
-        <v>1.888</v>
+        <v>0</v>
       </c>
       <c r="C149">
-        <v>21.668</v>
+        <v>0</v>
       </c>
       <c r="D149">
         <v>0</v>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46311.54166666666</v>
+        <v>46316.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46311.55208333334</v>
+        <v>46316.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -4450,7 +4450,7 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46311.5625</v>
+        <v>46316.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4473,7 +4473,7 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46311.57291666666</v>
+        <v>46316.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4496,7 +4496,7 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46311.58333333334</v>
+        <v>46316.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46311.59375</v>
+        <v>46316.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4542,7 +4542,7 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46311.60416666666</v>
+        <v>46316.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46311.61458333334</v>
+        <v>46316.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46311.625</v>
+        <v>46316.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4611,7 +4611,7 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46311.63541666666</v>
+        <v>46316.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46311.64583333334</v>
+        <v>46316.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46311.65625</v>
+        <v>46316.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46311.66666666666</v>
+        <v>46316.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46311.67708333334</v>
+        <v>46316.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46311.6875</v>
+        <v>46316.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46311.69791666666</v>
+        <v>46316.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4772,7 +4772,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46311.70833333334</v>
+        <v>46316.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46311.71875</v>
+        <v>46316.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46311.72916666666</v>
+        <v>46316.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46311.73958333334</v>
+        <v>46316.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46311.75</v>
+        <v>46316.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46311.76041666666</v>
+        <v>46316.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46311.77083333334</v>
+        <v>46316.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46311.78125</v>
+        <v>46316.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46311.79166666666</v>
+        <v>46316.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46311.80208333334</v>
+        <v>46316.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46311.8125</v>
+        <v>46316.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -5025,7 +5025,7 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46311.82291666666</v>
+        <v>46316.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -5048,7 +5048,7 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46311.83333333334</v>
+        <v>46316.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -5071,7 +5071,7 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46311.84375</v>
+        <v>46316.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -5094,7 +5094,7 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46311.85416666666</v>
+        <v>46316.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46311.86458333334</v>
+        <v>46316.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46311.875</v>
+        <v>46316.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46311.88541666666</v>
+        <v>46316.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46311.89583333334</v>
+        <v>46316.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46311.90625</v>
+        <v>46316.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46311.91666666666</v>
+        <v>46316.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46311.92708333334</v>
+        <v>46316.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46311.9375</v>
+        <v>46316.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46311.94791666666</v>
+        <v>46316.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46311.95833333334</v>
+        <v>46316.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -5347,7 +5347,7 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46311.96875</v>
+        <v>46316.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46311.97916666666</v>
+        <v>46316.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46311.98958333334</v>
+        <v>46316.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
+++ b/data_fetching/Entsoe/Balancing_Energy_Activation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="195">
   <si>
     <t>Timestamp (CET)</t>
   </si>
@@ -37,580 +37,568 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>20.10.20261</t>
-  </si>
-  <si>
-    <t>20.10.20262</t>
-  </si>
-  <si>
-    <t>20.10.20263</t>
-  </si>
-  <si>
-    <t>20.10.20264</t>
-  </si>
-  <si>
-    <t>20.10.20265</t>
-  </si>
-  <si>
-    <t>20.10.20266</t>
-  </si>
-  <si>
-    <t>20.10.20267</t>
-  </si>
-  <si>
-    <t>20.10.20268</t>
-  </si>
-  <si>
-    <t>20.10.20269</t>
-  </si>
-  <si>
-    <t>20.10.202610</t>
-  </si>
-  <si>
-    <t>20.10.202611</t>
-  </si>
-  <si>
-    <t>20.10.202612</t>
-  </si>
-  <si>
-    <t>20.10.202613</t>
-  </si>
-  <si>
-    <t>20.10.202614</t>
-  </si>
-  <si>
-    <t>20.10.202615</t>
-  </si>
-  <si>
-    <t>20.10.202616</t>
-  </si>
-  <si>
-    <t>20.10.202617</t>
-  </si>
-  <si>
-    <t>20.10.202618</t>
-  </si>
-  <si>
-    <t>20.10.202619</t>
-  </si>
-  <si>
-    <t>20.10.202620</t>
-  </si>
-  <si>
-    <t>20.10.202621</t>
-  </si>
-  <si>
-    <t>20.10.202622</t>
-  </si>
-  <si>
-    <t>20.10.202623</t>
-  </si>
-  <si>
-    <t>20.10.202624</t>
-  </si>
-  <si>
-    <t>20.10.202625</t>
-  </si>
-  <si>
-    <t>20.10.202626</t>
-  </si>
-  <si>
-    <t>20.10.202627</t>
-  </si>
-  <si>
-    <t>20.10.202628</t>
-  </si>
-  <si>
-    <t>20.10.202629</t>
-  </si>
-  <si>
-    <t>20.10.202630</t>
-  </si>
-  <si>
-    <t>20.10.202631</t>
-  </si>
-  <si>
-    <t>20.10.202632</t>
-  </si>
-  <si>
-    <t>20.10.202633</t>
-  </si>
-  <si>
-    <t>20.10.202634</t>
-  </si>
-  <si>
-    <t>20.10.202635</t>
-  </si>
-  <si>
-    <t>20.10.202636</t>
-  </si>
-  <si>
-    <t>20.10.202637</t>
-  </si>
-  <si>
-    <t>20.10.202638</t>
-  </si>
-  <si>
-    <t>20.10.202639</t>
-  </si>
-  <si>
-    <t>20.10.202640</t>
-  </si>
-  <si>
-    <t>20.10.202641</t>
-  </si>
-  <si>
-    <t>20.10.202642</t>
-  </si>
-  <si>
-    <t>20.10.202643</t>
-  </si>
-  <si>
-    <t>20.10.202644</t>
-  </si>
-  <si>
-    <t>20.10.202645</t>
-  </si>
-  <si>
-    <t>20.10.202646</t>
-  </si>
-  <si>
-    <t>20.10.202647</t>
-  </si>
-  <si>
-    <t>20.10.202648</t>
-  </si>
-  <si>
-    <t>20.10.202649</t>
-  </si>
-  <si>
-    <t>20.10.202650</t>
-  </si>
-  <si>
-    <t>20.10.202651</t>
-  </si>
-  <si>
-    <t>20.10.202652</t>
-  </si>
-  <si>
-    <t>20.10.202653</t>
-  </si>
-  <si>
-    <t>20.10.202654</t>
-  </si>
-  <si>
-    <t>20.10.202655</t>
-  </si>
-  <si>
-    <t>20.10.202656</t>
-  </si>
-  <si>
-    <t>20.10.202657</t>
-  </si>
-  <si>
-    <t>20.10.202658</t>
-  </si>
-  <si>
-    <t>20.10.202659</t>
-  </si>
-  <si>
-    <t>20.10.202660</t>
-  </si>
-  <si>
-    <t>20.10.202661</t>
-  </si>
-  <si>
-    <t>20.10.202662</t>
-  </si>
-  <si>
-    <t>20.10.202663</t>
-  </si>
-  <si>
-    <t>20.10.202664</t>
-  </si>
-  <si>
-    <t>20.10.202665</t>
-  </si>
-  <si>
-    <t>20.10.202666</t>
-  </si>
-  <si>
-    <t>20.10.202667</t>
-  </si>
-  <si>
-    <t>20.10.202668</t>
-  </si>
-  <si>
-    <t>20.10.202669</t>
-  </si>
-  <si>
-    <t>20.10.202670</t>
-  </si>
-  <si>
-    <t>20.10.202671</t>
-  </si>
-  <si>
-    <t>20.10.202672</t>
-  </si>
-  <si>
-    <t>20.10.202673</t>
-  </si>
-  <si>
-    <t>20.10.202674</t>
-  </si>
-  <si>
-    <t>20.10.202675</t>
-  </si>
-  <si>
-    <t>20.10.202676</t>
-  </si>
-  <si>
-    <t>20.10.202677</t>
-  </si>
-  <si>
-    <t>20.10.202678</t>
-  </si>
-  <si>
-    <t>20.10.202679</t>
-  </si>
-  <si>
-    <t>20.10.202680</t>
-  </si>
-  <si>
-    <t>20.10.202681</t>
-  </si>
-  <si>
-    <t>20.10.202682</t>
-  </si>
-  <si>
-    <t>20.10.202683</t>
-  </si>
-  <si>
-    <t>20.10.202684</t>
-  </si>
-  <si>
-    <t>20.10.202685</t>
-  </si>
-  <si>
-    <t>20.10.202686</t>
-  </si>
-  <si>
-    <t>20.10.202687</t>
-  </si>
-  <si>
-    <t>20.10.202688</t>
-  </si>
-  <si>
-    <t>20.10.202689</t>
-  </si>
-  <si>
-    <t>20.10.202690</t>
-  </si>
-  <si>
-    <t>20.10.202691</t>
-  </si>
-  <si>
-    <t>20.10.202692</t>
-  </si>
-  <si>
-    <t>20.10.202693</t>
-  </si>
-  <si>
-    <t>20.10.202694</t>
-  </si>
-  <si>
-    <t>20.10.202695</t>
-  </si>
-  <si>
-    <t>20.10.202696</t>
-  </si>
-  <si>
-    <t>21.10.20261</t>
-  </si>
-  <si>
-    <t>21.10.20262</t>
-  </si>
-  <si>
-    <t>21.10.20263</t>
-  </si>
-  <si>
-    <t>21.10.20264</t>
-  </si>
-  <si>
-    <t>21.10.20265</t>
-  </si>
-  <si>
-    <t>21.10.20266</t>
-  </si>
-  <si>
-    <t>21.10.20267</t>
-  </si>
-  <si>
-    <t>21.10.20268</t>
-  </si>
-  <si>
-    <t>21.10.20269</t>
-  </si>
-  <si>
-    <t>21.10.202610</t>
-  </si>
-  <si>
-    <t>21.10.202611</t>
-  </si>
-  <si>
-    <t>21.10.202612</t>
-  </si>
-  <si>
-    <t>21.10.202613</t>
-  </si>
-  <si>
-    <t>21.10.202614</t>
-  </si>
-  <si>
-    <t>21.10.202615</t>
-  </si>
-  <si>
-    <t>21.10.202616</t>
-  </si>
-  <si>
-    <t>21.10.202617</t>
-  </si>
-  <si>
-    <t>21.10.202618</t>
-  </si>
-  <si>
-    <t>21.10.202619</t>
-  </si>
-  <si>
-    <t>21.10.202620</t>
-  </si>
-  <si>
-    <t>21.10.202621</t>
-  </si>
-  <si>
-    <t>21.10.202622</t>
-  </si>
-  <si>
-    <t>21.10.202623</t>
-  </si>
-  <si>
-    <t>21.10.202624</t>
-  </si>
-  <si>
-    <t>21.10.202625</t>
-  </si>
-  <si>
-    <t>21.10.202626</t>
-  </si>
-  <si>
-    <t>21.10.202627</t>
-  </si>
-  <si>
-    <t>21.10.202628</t>
-  </si>
-  <si>
-    <t>21.10.202629</t>
-  </si>
-  <si>
-    <t>21.10.202630</t>
-  </si>
-  <si>
-    <t>21.10.202631</t>
-  </si>
-  <si>
-    <t>21.10.202632</t>
-  </si>
-  <si>
-    <t>21.10.202633</t>
-  </si>
-  <si>
-    <t>21.10.202634</t>
-  </si>
-  <si>
-    <t>21.10.202635</t>
-  </si>
-  <si>
-    <t>21.10.202636</t>
-  </si>
-  <si>
-    <t>21.10.202637</t>
-  </si>
-  <si>
-    <t>21.10.202638</t>
-  </si>
-  <si>
-    <t>21.10.202639</t>
-  </si>
-  <si>
-    <t>21.10.202640</t>
-  </si>
-  <si>
-    <t>21.10.202641</t>
-  </si>
-  <si>
-    <t>21.10.202642</t>
-  </si>
-  <si>
-    <t>21.10.202643</t>
-  </si>
-  <si>
-    <t>21.10.202644</t>
-  </si>
-  <si>
-    <t>21.10.202645</t>
-  </si>
-  <si>
-    <t>21.10.202646</t>
-  </si>
-  <si>
-    <t>21.10.202647</t>
-  </si>
-  <si>
-    <t>21.10.202648</t>
-  </si>
-  <si>
-    <t>21.10.202649</t>
-  </si>
-  <si>
-    <t>21.10.202650</t>
-  </si>
-  <si>
-    <t>21.10.202651</t>
-  </si>
-  <si>
-    <t>21.10.202652</t>
-  </si>
-  <si>
-    <t>21.10.202653</t>
-  </si>
-  <si>
-    <t>21.10.202654</t>
-  </si>
-  <si>
-    <t>21.10.202655</t>
-  </si>
-  <si>
-    <t>21.10.202656</t>
-  </si>
-  <si>
-    <t>21.10.202657</t>
-  </si>
-  <si>
-    <t>21.10.202658</t>
-  </si>
-  <si>
-    <t>21.10.202659</t>
-  </si>
-  <si>
-    <t>21.10.202660</t>
-  </si>
-  <si>
-    <t>21.10.202661</t>
-  </si>
-  <si>
-    <t>21.10.202662</t>
-  </si>
-  <si>
-    <t>21.10.202663</t>
-  </si>
-  <si>
-    <t>21.10.202664</t>
-  </si>
-  <si>
-    <t>21.10.202665</t>
-  </si>
-  <si>
-    <t>21.10.202666</t>
-  </si>
-  <si>
-    <t>21.10.202667</t>
-  </si>
-  <si>
-    <t>21.10.202668</t>
-  </si>
-  <si>
-    <t>21.10.202669</t>
-  </si>
-  <si>
-    <t>21.10.202670</t>
-  </si>
-  <si>
-    <t>21.10.202671</t>
-  </si>
-  <si>
-    <t>21.10.202672</t>
-  </si>
-  <si>
-    <t>21.10.202673</t>
-  </si>
-  <si>
-    <t>21.10.202674</t>
-  </si>
-  <si>
-    <t>21.10.202675</t>
-  </si>
-  <si>
-    <t>21.10.202676</t>
-  </si>
-  <si>
-    <t>21.10.202677</t>
-  </si>
-  <si>
-    <t>21.10.202678</t>
-  </si>
-  <si>
-    <t>21.10.202679</t>
-  </si>
-  <si>
-    <t>21.10.202680</t>
-  </si>
-  <si>
-    <t>21.10.202681</t>
-  </si>
-  <si>
-    <t>21.10.202682</t>
-  </si>
-  <si>
-    <t>21.10.202683</t>
-  </si>
-  <si>
-    <t>21.10.202684</t>
-  </si>
-  <si>
-    <t>21.10.202685</t>
-  </si>
-  <si>
-    <t>21.10.202686</t>
-  </si>
-  <si>
-    <t>21.10.202687</t>
-  </si>
-  <si>
-    <t>21.10.202688</t>
-  </si>
-  <si>
-    <t>21.10.202689</t>
-  </si>
-  <si>
-    <t>21.10.202690</t>
-  </si>
-  <si>
-    <t>21.10.202691</t>
-  </si>
-  <si>
-    <t>21.10.202692</t>
-  </si>
-  <si>
-    <t>21.10.202693</t>
-  </si>
-  <si>
-    <t>21.10.202694</t>
-  </si>
-  <si>
-    <t>21.10.202695</t>
-  </si>
-  <si>
-    <t>21.10.202696</t>
+    <t>24.10.20261</t>
+  </si>
+  <si>
+    <t>24.10.20262</t>
+  </si>
+  <si>
+    <t>24.10.20263</t>
+  </si>
+  <si>
+    <t>24.10.20264</t>
+  </si>
+  <si>
+    <t>24.10.20265</t>
+  </si>
+  <si>
+    <t>24.10.20266</t>
+  </si>
+  <si>
+    <t>24.10.20267</t>
+  </si>
+  <si>
+    <t>24.10.20268</t>
+  </si>
+  <si>
+    <t>24.10.20269</t>
+  </si>
+  <si>
+    <t>24.10.202610</t>
+  </si>
+  <si>
+    <t>24.10.202611</t>
+  </si>
+  <si>
+    <t>24.10.202612</t>
+  </si>
+  <si>
+    <t>24.10.202613</t>
+  </si>
+  <si>
+    <t>24.10.202614</t>
+  </si>
+  <si>
+    <t>24.10.202615</t>
+  </si>
+  <si>
+    <t>24.10.202616</t>
+  </si>
+  <si>
+    <t>24.10.202617</t>
+  </si>
+  <si>
+    <t>24.10.202618</t>
+  </si>
+  <si>
+    <t>24.10.202619</t>
+  </si>
+  <si>
+    <t>24.10.202620</t>
+  </si>
+  <si>
+    <t>24.10.202621</t>
+  </si>
+  <si>
+    <t>24.10.202622</t>
+  </si>
+  <si>
+    <t>24.10.202623</t>
+  </si>
+  <si>
+    <t>24.10.202624</t>
+  </si>
+  <si>
+    <t>24.10.202625</t>
+  </si>
+  <si>
+    <t>24.10.202626</t>
+  </si>
+  <si>
+    <t>24.10.202627</t>
+  </si>
+  <si>
+    <t>24.10.202628</t>
+  </si>
+  <si>
+    <t>24.10.202629</t>
+  </si>
+  <si>
+    <t>24.10.202630</t>
+  </si>
+  <si>
+    <t>24.10.202631</t>
+  </si>
+  <si>
+    <t>24.10.202632</t>
+  </si>
+  <si>
+    <t>24.10.202633</t>
+  </si>
+  <si>
+    <t>24.10.202634</t>
+  </si>
+  <si>
+    <t>24.10.202635</t>
+  </si>
+  <si>
+    <t>24.10.202636</t>
+  </si>
+  <si>
+    <t>24.10.202637</t>
+  </si>
+  <si>
+    <t>24.10.202638</t>
+  </si>
+  <si>
+    <t>24.10.202639</t>
+  </si>
+  <si>
+    <t>24.10.202640</t>
+  </si>
+  <si>
+    <t>24.10.202641</t>
+  </si>
+  <si>
+    <t>24.10.202642</t>
+  </si>
+  <si>
+    <t>24.10.202643</t>
+  </si>
+  <si>
+    <t>24.10.202644</t>
+  </si>
+  <si>
+    <t>24.10.202645</t>
+  </si>
+  <si>
+    <t>24.10.202646</t>
+  </si>
+  <si>
+    <t>24.10.202647</t>
+  </si>
+  <si>
+    <t>24.10.202648</t>
+  </si>
+  <si>
+    <t>24.10.202649</t>
+  </si>
+  <si>
+    <t>24.10.202650</t>
+  </si>
+  <si>
+    <t>24.10.202651</t>
+  </si>
+  <si>
+    <t>24.10.202652</t>
+  </si>
+  <si>
+    <t>24.10.202653</t>
+  </si>
+  <si>
+    <t>24.10.202654</t>
+  </si>
+  <si>
+    <t>24.10.202655</t>
+  </si>
+  <si>
+    <t>24.10.202656</t>
+  </si>
+  <si>
+    <t>24.10.202657</t>
+  </si>
+  <si>
+    <t>24.10.202658</t>
+  </si>
+  <si>
+    <t>24.10.202659</t>
+  </si>
+  <si>
+    <t>24.10.202660</t>
+  </si>
+  <si>
+    <t>24.10.202661</t>
+  </si>
+  <si>
+    <t>24.10.202662</t>
+  </si>
+  <si>
+    <t>24.10.202663</t>
+  </si>
+  <si>
+    <t>24.10.202664</t>
+  </si>
+  <si>
+    <t>24.10.202665</t>
+  </si>
+  <si>
+    <t>24.10.202666</t>
+  </si>
+  <si>
+    <t>24.10.202667</t>
+  </si>
+  <si>
+    <t>24.10.202668</t>
+  </si>
+  <si>
+    <t>24.10.202669</t>
+  </si>
+  <si>
+    <t>24.10.202670</t>
+  </si>
+  <si>
+    <t>24.10.202671</t>
+  </si>
+  <si>
+    <t>24.10.202672</t>
+  </si>
+  <si>
+    <t>24.10.202673</t>
+  </si>
+  <si>
+    <t>24.10.202674</t>
+  </si>
+  <si>
+    <t>24.10.202675</t>
+  </si>
+  <si>
+    <t>24.10.202676</t>
+  </si>
+  <si>
+    <t>24.10.202677</t>
+  </si>
+  <si>
+    <t>24.10.202678</t>
+  </si>
+  <si>
+    <t>24.10.202679</t>
+  </si>
+  <si>
+    <t>24.10.202680</t>
+  </si>
+  <si>
+    <t>24.10.202681</t>
+  </si>
+  <si>
+    <t>24.10.202682</t>
+  </si>
+  <si>
+    <t>24.10.202683</t>
+  </si>
+  <si>
+    <t>24.10.202684</t>
+  </si>
+  <si>
+    <t>24.10.202685</t>
+  </si>
+  <si>
+    <t>24.10.202686</t>
+  </si>
+  <si>
+    <t>24.10.202687</t>
+  </si>
+  <si>
+    <t>24.10.202688</t>
+  </si>
+  <si>
+    <t>24.10.202689</t>
+  </si>
+  <si>
+    <t>24.10.202690</t>
+  </si>
+  <si>
+    <t>24.10.202691</t>
+  </si>
+  <si>
+    <t>24.10.202692</t>
+  </si>
+  <si>
+    <t>24.10.202693</t>
+  </si>
+  <si>
+    <t>24.10.202694</t>
+  </si>
+  <si>
+    <t>24.10.202695</t>
+  </si>
+  <si>
+    <t>24.10.202696</t>
+  </si>
+  <si>
+    <t>25.10.20261</t>
+  </si>
+  <si>
+    <t>25.10.20262</t>
+  </si>
+  <si>
+    <t>25.10.20263</t>
+  </si>
+  <si>
+    <t>25.10.20264</t>
+  </si>
+  <si>
+    <t>25.10.20265</t>
+  </si>
+  <si>
+    <t>25.10.20266</t>
+  </si>
+  <si>
+    <t>25.10.20267</t>
+  </si>
+  <si>
+    <t>25.10.20268</t>
+  </si>
+  <si>
+    <t>25.10.20269</t>
+  </si>
+  <si>
+    <t>25.10.202610</t>
+  </si>
+  <si>
+    <t>25.10.202611</t>
+  </si>
+  <si>
+    <t>25.10.202612</t>
+  </si>
+  <si>
+    <t>25.10.202613</t>
+  </si>
+  <si>
+    <t>25.10.202614</t>
+  </si>
+  <si>
+    <t>25.10.202615</t>
+  </si>
+  <si>
+    <t>25.10.202616</t>
+  </si>
+  <si>
+    <t>25.10.202617</t>
+  </si>
+  <si>
+    <t>25.10.202618</t>
+  </si>
+  <si>
+    <t>25.10.202619</t>
+  </si>
+  <si>
+    <t>25.10.202620</t>
+  </si>
+  <si>
+    <t>25.10.202621</t>
+  </si>
+  <si>
+    <t>25.10.202622</t>
+  </si>
+  <si>
+    <t>25.10.202623</t>
+  </si>
+  <si>
+    <t>25.10.202624</t>
+  </si>
+  <si>
+    <t>25.10.202625</t>
+  </si>
+  <si>
+    <t>25.10.202626</t>
+  </si>
+  <si>
+    <t>25.10.202627</t>
+  </si>
+  <si>
+    <t>25.10.202628</t>
+  </si>
+  <si>
+    <t>25.10.202629</t>
+  </si>
+  <si>
+    <t>25.10.202630</t>
+  </si>
+  <si>
+    <t>25.10.202631</t>
+  </si>
+  <si>
+    <t>25.10.202632</t>
+  </si>
+  <si>
+    <t>25.10.202633</t>
+  </si>
+  <si>
+    <t>25.10.202634</t>
+  </si>
+  <si>
+    <t>25.10.202635</t>
+  </si>
+  <si>
+    <t>25.10.202636</t>
+  </si>
+  <si>
+    <t>25.10.202637</t>
+  </si>
+  <si>
+    <t>25.10.202638</t>
+  </si>
+  <si>
+    <t>25.10.202639</t>
+  </si>
+  <si>
+    <t>25.10.202640</t>
+  </si>
+  <si>
+    <t>25.10.202641</t>
+  </si>
+  <si>
+    <t>25.10.202642</t>
+  </si>
+  <si>
+    <t>25.10.202643</t>
+  </si>
+  <si>
+    <t>25.10.202644</t>
+  </si>
+  <si>
+    <t>25.10.202645</t>
+  </si>
+  <si>
+    <t>25.10.202646</t>
+  </si>
+  <si>
+    <t>25.10.202647</t>
+  </si>
+  <si>
+    <t>25.10.202648</t>
+  </si>
+  <si>
+    <t>25.10.202649</t>
+  </si>
+  <si>
+    <t>25.10.202650</t>
+  </si>
+  <si>
+    <t>25.10.202651</t>
+  </si>
+  <si>
+    <t>25.10.202652</t>
+  </si>
+  <si>
+    <t>25.10.202653</t>
+  </si>
+  <si>
+    <t>25.10.202654</t>
+  </si>
+  <si>
+    <t>25.10.202655</t>
+  </si>
+  <si>
+    <t>25.10.202656</t>
+  </si>
+  <si>
+    <t>25.10.202657</t>
+  </si>
+  <si>
+    <t>25.10.202658</t>
+  </si>
+  <si>
+    <t>25.10.202659</t>
+  </si>
+  <si>
+    <t>25.10.202660</t>
+  </si>
+  <si>
+    <t>25.10.202661</t>
+  </si>
+  <si>
+    <t>25.10.202662</t>
+  </si>
+  <si>
+    <t>25.10.202663</t>
+  </si>
+  <si>
+    <t>25.10.202664</t>
+  </si>
+  <si>
+    <t>25.10.202665</t>
+  </si>
+  <si>
+    <t>25.10.202666</t>
+  </si>
+  <si>
+    <t>25.10.202667</t>
+  </si>
+  <si>
+    <t>25.10.202668</t>
+  </si>
+  <si>
+    <t>25.10.202669</t>
+  </si>
+  <si>
+    <t>25.10.202670</t>
+  </si>
+  <si>
+    <t>25.10.202671</t>
+  </si>
+  <si>
+    <t>25.10.202672</t>
+  </si>
+  <si>
+    <t>25.10.202673</t>
+  </si>
+  <si>
+    <t>25.10.202674</t>
+  </si>
+  <si>
+    <t>25.10.202675</t>
+  </si>
+  <si>
+    <t>25.10.202676</t>
+  </si>
+  <si>
+    <t>25.10.202677</t>
+  </si>
+  <si>
+    <t>25.10.202678</t>
+  </si>
+  <si>
+    <t>25.10.202679</t>
+  </si>
+  <si>
+    <t>25.10.202680</t>
+  </si>
+  <si>
+    <t>25.10.202681</t>
+  </si>
+  <si>
+    <t>25.10.202682</t>
+  </si>
+  <si>
+    <t>25.10.202683</t>
+  </si>
+  <si>
+    <t>25.10.202684</t>
+  </si>
+  <si>
+    <t>25.10.202685</t>
+  </si>
+  <si>
+    <t>25.10.202686</t>
+  </si>
+  <si>
+    <t>25.10.202687</t>
+  </si>
+  <si>
+    <t>25.10.202688</t>
+  </si>
+  <si>
+    <t>25.10.202689</t>
+  </si>
+  <si>
+    <t>25.10.202690</t>
+  </si>
+  <si>
+    <t>25.10.202691</t>
+  </si>
+  <si>
+    <t>25.10.202692</t>
   </si>
 </sst>
 </file>
@@ -1000,13 +988,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="B2">
-        <v>0.053</v>
+        <v>0.039</v>
       </c>
       <c r="C2">
-        <v>7.99</v>
+        <v>5.806</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1023,13 +1011,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>46315.01041666666</v>
+        <v>46319.01041666666</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="C3">
-        <v>19.345</v>
+        <v>0.52</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1046,19 +1034,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>46315.02083333334</v>
+        <v>46319.02083333334</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="C4">
-        <v>13.189</v>
+        <v>1.022</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -1069,19 +1057,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>46315.03125</v>
+        <v>46319.03125</v>
       </c>
       <c r="B5">
-        <v>0.032</v>
+        <v>0.046</v>
       </c>
       <c r="C5">
-        <v>2.205</v>
+        <v>1.166</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -1092,19 +1080,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>46315.04166666666</v>
+        <v>46319.04166666666</v>
       </c>
       <c r="B6">
-        <v>23.606</v>
+        <v>0.156</v>
       </c>
       <c r="C6">
-        <v>0.02</v>
+        <v>1.345</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -1115,19 +1103,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>46315.05208333334</v>
+        <v>46319.05208333334</v>
       </c>
       <c r="B7">
-        <v>26.444</v>
+        <v>0.002</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>2.662</v>
       </c>
       <c r="D7">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -1138,19 +1126,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>46315.0625</v>
+        <v>46319.0625</v>
       </c>
       <c r="B8">
-        <v>15.138</v>
+        <v>0.036</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>2.569</v>
       </c>
       <c r="D8">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>57.5</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -1161,19 +1149,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>46315.07291666666</v>
+        <v>46319.07291666666</v>
       </c>
       <c r="B9">
-        <v>7.281</v>
+        <v>0.106</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>0.163</v>
       </c>
       <c r="D9">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>57.5</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -1184,19 +1172,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>46315.08333333334</v>
+        <v>46319.08333333334</v>
       </c>
       <c r="B10">
-        <v>2.356</v>
+        <v>0.259</v>
       </c>
       <c r="C10">
-        <v>0.08699999999999999</v>
+        <v>1.491</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>57.5</v>
       </c>
       <c r="F10">
         <v>9</v>
@@ -1207,19 +1195,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>46315.09375</v>
+        <v>46319.09375</v>
       </c>
       <c r="B11">
-        <v>0.002</v>
+        <v>1.337</v>
       </c>
       <c r="C11">
-        <v>4.064</v>
+        <v>0.854</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -1230,19 +1218,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>46315.10416666666</v>
+        <v>46319.10416666666</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>8.24</v>
       </c>
       <c r="C12">
-        <v>5.647</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F12">
         <v>11</v>
@@ -1253,19 +1241,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>46315.11458333334</v>
+        <v>46319.11458333334</v>
       </c>
       <c r="B13">
-        <v>0.011</v>
+        <v>13.83</v>
       </c>
       <c r="C13">
-        <v>3.107</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F13">
         <v>12</v>
@@ -1276,19 +1264,19 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>46315.125</v>
+        <v>46319.125</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>0.732</v>
       </c>
       <c r="C14">
-        <v>6.191</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F14">
         <v>13</v>
@@ -1299,19 +1287,19 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>46315.13541666666</v>
+        <v>46319.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>16.695</v>
       </c>
       <c r="C15">
-        <v>8.704000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F15">
         <v>14</v>
@@ -1322,13 +1310,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>46315.14583333334</v>
+        <v>46319.14583333334</v>
       </c>
       <c r="B16">
-        <v>0.225</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>4.783</v>
+        <v>7.811</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1345,13 +1333,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>46315.15625</v>
+        <v>46319.15625</v>
       </c>
       <c r="B17">
-        <v>8.170999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>10.449</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1368,13 +1356,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>46315.16666666666</v>
+        <v>46319.16666666666</v>
       </c>
       <c r="B18">
-        <v>2.744</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>0.2</v>
+        <v>9.872999999999999</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1391,19 +1379,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>46315.17708333334</v>
+        <v>46319.17708333334</v>
       </c>
       <c r="B19">
-        <v>1.575</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>0.159</v>
+        <v>3.996</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F19">
         <v>18</v>
@@ -1414,19 +1402,19 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>46315.1875</v>
+        <v>46319.1875</v>
       </c>
       <c r="B20">
-        <v>0.323</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>0.487</v>
+        <v>8.614000000000001</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F20">
         <v>19</v>
@@ -1437,19 +1425,19 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>46315.19791666666</v>
+        <v>46319.19791666666</v>
       </c>
       <c r="B21">
-        <v>0.532</v>
+        <v>0.16</v>
       </c>
       <c r="C21">
-        <v>0.341</v>
+        <v>2.358</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F21">
         <v>20</v>
@@ -1460,19 +1448,19 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>46315.20833333334</v>
+        <v>46319.20833333334</v>
       </c>
       <c r="B22">
-        <v>0.018</v>
+        <v>0.09</v>
       </c>
       <c r="C22">
-        <v>4.887</v>
+        <v>0.187</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F22">
         <v>21</v>
@@ -1483,13 +1471,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2">
-        <v>46315.21875</v>
+        <v>46319.21875</v>
       </c>
       <c r="B23">
-        <v>0.052</v>
+        <v>0.063</v>
       </c>
       <c r="C23">
-        <v>0.58</v>
+        <v>0.289</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1506,13 +1494,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2">
-        <v>46315.22916666666</v>
+        <v>46319.22916666666</v>
       </c>
       <c r="B24">
-        <v>0.276</v>
+        <v>0.259</v>
       </c>
       <c r="C24">
-        <v>0.244</v>
+        <v>0.112</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1529,13 +1517,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2">
-        <v>46315.23958333334</v>
+        <v>46319.23958333334</v>
       </c>
       <c r="B25">
-        <v>2.878</v>
+        <v>0.098</v>
       </c>
       <c r="C25">
-        <v>0.313</v>
+        <v>0.633</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1552,13 +1540,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2">
-        <v>46315.25</v>
+        <v>46319.25</v>
       </c>
       <c r="B26">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>3.544</v>
+        <v>4.453</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1575,13 +1563,13 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2">
-        <v>46315.26041666666</v>
+        <v>46319.26041666666</v>
       </c>
       <c r="B27">
-        <v>0.273</v>
+        <v>0.002</v>
       </c>
       <c r="C27">
-        <v>0.321</v>
+        <v>2.555</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1598,13 +1586,13 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2">
-        <v>46315.27083333334</v>
+        <v>46319.27083333334</v>
       </c>
       <c r="B28">
-        <v>3.263</v>
+        <v>1.819</v>
       </c>
       <c r="C28">
-        <v>0.006</v>
+        <v>0.55</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1621,13 +1609,13 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2">
-        <v>46315.28125</v>
+        <v>46319.28125</v>
       </c>
       <c r="B29">
-        <v>3.338</v>
+        <v>3.206</v>
       </c>
       <c r="C29">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1644,13 +1632,13 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2">
-        <v>46315.29166666666</v>
+        <v>46319.29166666666</v>
       </c>
       <c r="B30">
-        <v>0.581</v>
+        <v>0.016</v>
       </c>
       <c r="C30">
-        <v>0.042</v>
+        <v>3.791</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1667,13 +1655,13 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2">
-        <v>46315.30208333334</v>
+        <v>46319.30208333334</v>
       </c>
       <c r="B31">
-        <v>0.034</v>
+        <v>0.178</v>
       </c>
       <c r="C31">
-        <v>2.277</v>
+        <v>0.104</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1690,13 +1678,13 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2">
-        <v>46315.3125</v>
+        <v>46319.3125</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="C32">
-        <v>5.164</v>
+        <v>0.74</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -1713,13 +1701,13 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2">
-        <v>46315.32291666666</v>
+        <v>46319.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>9.404</v>
+        <v>3.798</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -1736,13 +1724,13 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2">
-        <v>46315.33333333334</v>
+        <v>46319.33333333334</v>
       </c>
       <c r="B34">
-        <v>0.054</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>2.271</v>
+        <v>5.401</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -1759,13 +1747,13 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2">
-        <v>46315.34375</v>
+        <v>46319.34375</v>
       </c>
       <c r="B35">
-        <v>0.174</v>
+        <v>0.162</v>
       </c>
       <c r="C35">
-        <v>1.041</v>
+        <v>0.387</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -1782,19 +1770,19 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2">
-        <v>46315.35416666666</v>
+        <v>46319.35416666666</v>
       </c>
       <c r="B36">
-        <v>17.083</v>
+        <v>0.482</v>
       </c>
       <c r="C36">
-        <v>0.014</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>13.25</v>
       </c>
       <c r="F36">
         <v>35</v>
@@ -1805,19 +1793,19 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2">
-        <v>46315.36458333334</v>
+        <v>46319.36458333334</v>
       </c>
       <c r="B37">
-        <v>2.969</v>
+        <v>4.691</v>
       </c>
       <c r="C37">
-        <v>2.596</v>
+        <v>0.118</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>13.25</v>
       </c>
       <c r="F37">
         <v>36</v>
@@ -1828,19 +1816,19 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2">
-        <v>46315.375</v>
+        <v>46319.375</v>
       </c>
       <c r="B38">
-        <v>5.988</v>
+        <v>31.778</v>
       </c>
       <c r="C38">
-        <v>0.454</v>
+        <v>0</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F38">
         <v>37</v>
@@ -1851,10 +1839,10 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2">
-        <v>46315.38541666666</v>
+        <v>46319.38541666666</v>
       </c>
       <c r="B39">
-        <v>6.509</v>
+        <v>43.356</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -1863,7 +1851,7 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F39">
         <v>38</v>
@@ -1874,13 +1862,13 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2">
-        <v>46315.39583333334</v>
+        <v>46319.39583333334</v>
       </c>
       <c r="B40">
-        <v>1.038</v>
+        <v>72.48099999999999</v>
       </c>
       <c r="C40">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -1897,16 +1885,16 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2">
-        <v>46315.40625</v>
+        <v>46319.40625</v>
       </c>
       <c r="B41">
-        <v>0.168</v>
+        <v>31.37</v>
       </c>
       <c r="C41">
-        <v>2.546</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -1920,16 +1908,16 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2">
-        <v>46315.41666666666</v>
+        <v>46319.41666666666</v>
       </c>
       <c r="B42">
-        <v>0.075</v>
+        <v>38.266</v>
       </c>
       <c r="C42">
-        <v>1.871</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>48.25</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -1943,16 +1931,16 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <v>46315.42708333334</v>
+        <v>46319.42708333334</v>
       </c>
       <c r="B43">
-        <v>0.056</v>
+        <v>26.047</v>
       </c>
       <c r="C43">
-        <v>0.378</v>
+        <v>1.043</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -1966,19 +1954,19 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <v>46315.4375</v>
+        <v>46319.4375</v>
       </c>
       <c r="B44">
-        <v>0.528</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>0.6860000000000001</v>
+        <v>5.94</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>66.25</v>
       </c>
       <c r="E44">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F44">
         <v>43</v>
@@ -1989,19 +1977,19 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <v>46315.44791666666</v>
+        <v>46319.44791666666</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="C45">
-        <v>1.453</v>
+        <v>5.379</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>66.25</v>
       </c>
       <c r="E45">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F45">
         <v>44</v>
@@ -2012,19 +2000,19 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <v>46315.45833333334</v>
+        <v>46319.45833333334</v>
       </c>
       <c r="B46">
-        <v>0.745</v>
+        <v>0.273</v>
       </c>
       <c r="C46">
-        <v>0.122</v>
+        <v>1.744</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>48.5</v>
       </c>
       <c r="E46">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F46">
         <v>45</v>
@@ -2035,19 +2023,19 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <v>46315.46875</v>
+        <v>46319.46875</v>
       </c>
       <c r="B47">
-        <v>0.036</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <v>1.279</v>
+        <v>7.899</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>48.5</v>
       </c>
       <c r="E47">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F47">
         <v>46</v>
@@ -2058,16 +2046,16 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <v>46315.47916666666</v>
+        <v>46319.47916666666</v>
       </c>
       <c r="B48">
-        <v>0.091</v>
+        <v>0.014</v>
       </c>
       <c r="C48">
-        <v>1.807</v>
+        <v>3.77</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -2081,13 +2069,13 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <v>46315.48958333334</v>
+        <v>46319.48958333334</v>
       </c>
       <c r="B49">
-        <v>0.344</v>
+        <v>0.997</v>
       </c>
       <c r="C49">
-        <v>0.979</v>
+        <v>0.136</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2104,19 +2092,19 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <v>46315.5</v>
+        <v>46319.5</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>0.128</v>
       </c>
       <c r="C50">
-        <v>6.625</v>
+        <v>0.428</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F50">
         <v>49</v>
@@ -2127,19 +2115,19 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <v>46315.51041666666</v>
+        <v>46319.51041666666</v>
       </c>
       <c r="B51">
-        <v>0.71</v>
+        <v>0.007</v>
       </c>
       <c r="C51">
-        <v>0.344</v>
+        <v>4.14</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F51">
         <v>50</v>
@@ -2150,19 +2138,19 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <v>46315.52083333334</v>
+        <v>46319.52083333334</v>
       </c>
       <c r="B52">
         <v>0</v>
       </c>
       <c r="C52">
-        <v>0.918</v>
+        <v>4.199</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F52">
         <v>51</v>
@@ -2173,19 +2161,19 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <v>46315.53125</v>
+        <v>46319.53125</v>
       </c>
       <c r="B53">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>1.094</v>
+        <v>2.864</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F53">
         <v>52</v>
@@ -2196,19 +2184,19 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <v>46315.54166666666</v>
+        <v>46319.54166666666</v>
       </c>
       <c r="B54">
-        <v>0.221</v>
+        <v>0.192</v>
       </c>
       <c r="C54">
-        <v>0.392</v>
+        <v>0.131</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F54">
         <v>53</v>
@@ -2219,19 +2207,19 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <v>46315.55208333334</v>
+        <v>46319.55208333334</v>
       </c>
       <c r="B55">
-        <v>0.125</v>
+        <v>0.043</v>
       </c>
       <c r="C55">
-        <v>0.165</v>
+        <v>0.15</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F55">
         <v>54</v>
@@ -2242,19 +2230,19 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <v>46315.5625</v>
+        <v>46319.5625</v>
       </c>
       <c r="B56">
-        <v>0.475</v>
+        <v>0.153</v>
       </c>
       <c r="C56">
-        <v>0.13</v>
+        <v>0.108</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F56">
         <v>55</v>
@@ -2265,19 +2253,19 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <v>46315.57291666666</v>
+        <v>46319.57291666666</v>
       </c>
       <c r="B57">
-        <v>0.139</v>
+        <v>0</v>
       </c>
       <c r="C57">
-        <v>0.138</v>
+        <v>8.597</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F57">
         <v>56</v>
@@ -2288,19 +2276,19 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <v>46315.58333333334</v>
+        <v>46319.58333333334</v>
       </c>
       <c r="B58">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="C58">
-        <v>0.871</v>
+        <v>28.394</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F58">
         <v>57</v>
@@ -2311,19 +2299,19 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <v>46315.59375</v>
+        <v>46319.59375</v>
       </c>
       <c r="B59">
-        <v>0.379</v>
+        <v>0</v>
       </c>
       <c r="C59">
-        <v>0.185</v>
+        <v>24.865</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F59">
         <v>58</v>
@@ -2334,19 +2322,19 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <v>46315.60416666666</v>
+        <v>46319.60416666666</v>
       </c>
       <c r="B60">
-        <v>2.275</v>
+        <v>0</v>
       </c>
       <c r="C60">
-        <v>2.991</v>
+        <v>22.99</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F60">
         <v>59</v>
@@ -2357,19 +2345,19 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <v>46315.61458333334</v>
+        <v>46319.61458333334</v>
       </c>
       <c r="B61">
-        <v>6.249</v>
+        <v>0</v>
       </c>
       <c r="C61">
-        <v>2.439</v>
+        <v>24.184</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F61">
         <v>60</v>
@@ -2380,19 +2368,19 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <v>46315.625</v>
+        <v>46319.625</v>
       </c>
       <c r="B62">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="C62">
-        <v>2.468</v>
+        <v>9.772</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F62">
         <v>61</v>
@@ -2403,19 +2391,19 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <v>46315.63541666666</v>
+        <v>46319.63541666666</v>
       </c>
       <c r="B63">
-        <v>5.561</v>
+        <v>0</v>
       </c>
       <c r="C63">
-        <v>0.387</v>
+        <v>19.765</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F63">
         <v>62</v>
@@ -2426,19 +2414,19 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <v>46315.64583333334</v>
+        <v>46319.64583333334</v>
       </c>
       <c r="B64">
-        <v>18.759</v>
+        <v>6.333</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>6.786</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F64">
         <v>63</v>
@@ -2449,10 +2437,10 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <v>46315.65625</v>
+        <v>46319.65625</v>
       </c>
       <c r="B65">
-        <v>38.119</v>
+        <v>27.455</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -2461,7 +2449,7 @@
         <v>0</v>
       </c>
       <c r="E65">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F65">
         <v>64</v>
@@ -2472,10 +2460,10 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <v>46315.66666666666</v>
+        <v>46319.66666666666</v>
       </c>
       <c r="B66">
-        <v>15.335</v>
+        <v>18.886</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -2484,7 +2472,7 @@
         <v>0</v>
       </c>
       <c r="E66">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F66">
         <v>65</v>
@@ -2495,10 +2483,10 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2">
-        <v>46315.67708333334</v>
+        <v>46319.67708333334</v>
       </c>
       <c r="B67">
-        <v>19.731</v>
+        <v>37.682</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -2518,16 +2506,16 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <v>46315.6875</v>
+        <v>46319.6875</v>
       </c>
       <c r="B68">
-        <v>36.061</v>
+        <v>24.867</v>
       </c>
       <c r="C68">
         <v>0</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>41.25</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -2541,16 +2529,16 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <v>46315.69791666666</v>
+        <v>46319.69791666666</v>
       </c>
       <c r="B69">
-        <v>45.421</v>
+        <v>35.677</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>41.25</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -2564,16 +2552,16 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <v>46315.70833333334</v>
+        <v>46319.70833333334</v>
       </c>
       <c r="B70">
-        <v>7.143</v>
+        <v>3.667</v>
       </c>
       <c r="C70">
-        <v>0.012</v>
+        <v>0.018</v>
       </c>
       <c r="D70">
-        <v>37.5</v>
+        <v>47.5</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -2587,16 +2575,16 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <v>46315.71875</v>
+        <v>46319.71875</v>
       </c>
       <c r="B71">
-        <v>0.176</v>
+        <v>14.298</v>
       </c>
       <c r="C71">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="D71">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -2610,16 +2598,16 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <v>46315.72916666666</v>
+        <v>46319.72916666666</v>
       </c>
       <c r="B72">
-        <v>0</v>
+        <v>15.608</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -2633,16 +2621,16 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <v>46315.73958333334</v>
+        <v>46319.73958333334</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>22.852</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -2656,16 +2644,16 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <v>46315.75</v>
+        <v>46319.75</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>15.223</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>37.5</v>
+        <v>44.25</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -2679,16 +2667,16 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <v>46315.76041666666</v>
+        <v>46319.76041666666</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>16.797</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75">
-        <v>37.5</v>
+        <v>44.25</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -2702,16 +2690,16 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <v>46315.77083333334</v>
+        <v>46319.77083333334</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>12.956</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>12.25</v>
+        <v>46.25</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -2725,16 +2713,16 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <v>46315.78125</v>
+        <v>46319.78125</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>15.624</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>0.142</v>
       </c>
       <c r="D77">
-        <v>12.5</v>
+        <v>46.25</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -2748,16 +2736,16 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <v>46315.79166666666</v>
+        <v>46319.79166666666</v>
       </c>
       <c r="B78">
-        <v>0</v>
+        <v>20.753</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D78">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -2771,16 +2759,16 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <v>46315.80208333334</v>
+        <v>46319.80208333334</v>
       </c>
       <c r="B79">
-        <v>21.729</v>
+        <v>17.31</v>
       </c>
       <c r="C79">
         <v>0</v>
       </c>
       <c r="D79">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -2794,16 +2782,16 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <v>46315.8125</v>
+        <v>46319.8125</v>
       </c>
       <c r="B80">
-        <v>12.454</v>
+        <v>20.007</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>0.415</v>
       </c>
       <c r="D80">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -2817,13 +2805,13 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2">
-        <v>46315.82291666666</v>
+        <v>46319.82291666666</v>
       </c>
       <c r="B81">
-        <v>54.277</v>
+        <v>5.909</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>0.321</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -2840,16 +2828,16 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2">
-        <v>46315.83333333334</v>
+        <v>46319.83333333334</v>
       </c>
       <c r="B82">
-        <v>67.018</v>
+        <v>22.146</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -2863,16 +2851,16 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2">
-        <v>46315.84375</v>
+        <v>46319.84375</v>
       </c>
       <c r="B83">
-        <v>27.225</v>
+        <v>32.25</v>
       </c>
       <c r="C83">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="D83">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -2886,16 +2874,16 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2">
-        <v>46315.85416666666</v>
+        <v>46319.85416666666</v>
       </c>
       <c r="B84">
-        <v>0.073</v>
+        <v>21.751</v>
       </c>
       <c r="C84">
-        <v>0.268</v>
+        <v>0</v>
       </c>
       <c r="D84">
-        <v>86.5</v>
+        <v>0</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -2909,16 +2897,16 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2">
-        <v>46315.86458333334</v>
+        <v>46319.86458333334</v>
       </c>
       <c r="B85">
-        <v>9.989000000000001</v>
+        <v>12.966</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>0.352</v>
       </c>
       <c r="D85">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -2932,16 +2920,16 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2">
-        <v>46315.875</v>
+        <v>46319.875</v>
       </c>
       <c r="B86">
-        <v>23.845</v>
+        <v>15.533</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>0.097</v>
       </c>
       <c r="D86">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -2955,16 +2943,16 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2">
-        <v>46315.88541666666</v>
+        <v>46319.88541666666</v>
       </c>
       <c r="B87">
-        <v>21.275</v>
+        <v>16.923</v>
       </c>
       <c r="C87">
         <v>0</v>
       </c>
       <c r="D87">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -2978,13 +2966,13 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2">
-        <v>46315.89583333334</v>
+        <v>46319.89583333334</v>
       </c>
       <c r="B88">
-        <v>44.34</v>
+        <v>7.525</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>0.591</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3001,13 +2989,13 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2">
-        <v>46315.90625</v>
+        <v>46319.90625</v>
       </c>
       <c r="B89">
-        <v>35.886</v>
+        <v>3.808</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>0.142</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3024,16 +3012,16 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2">
-        <v>46315.91666666666</v>
+        <v>46319.91666666666</v>
       </c>
       <c r="B90">
-        <v>2.229</v>
+        <v>21.232</v>
       </c>
       <c r="C90">
-        <v>1.726</v>
+        <v>0</v>
       </c>
       <c r="D90">
-        <v>48.5</v>
+        <v>0</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -3047,16 +3035,16 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2">
-        <v>46315.92708333334</v>
+        <v>46319.92708333334</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>31.447</v>
       </c>
       <c r="C91">
-        <v>5.475</v>
+        <v>0</v>
       </c>
       <c r="D91">
-        <v>48.5</v>
+        <v>0</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -3070,16 +3058,16 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2">
-        <v>46315.9375</v>
+        <v>46319.9375</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>25.622</v>
       </c>
       <c r="C92">
-        <v>18.968</v>
+        <v>0</v>
       </c>
       <c r="D92">
-        <v>48.5</v>
+        <v>0</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -3093,16 +3081,16 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2">
-        <v>46315.94791666666</v>
+        <v>46319.94791666666</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>25.178</v>
       </c>
       <c r="C93">
-        <v>19.133</v>
+        <v>0</v>
       </c>
       <c r="D93">
-        <v>48.5</v>
+        <v>0</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -3116,16 +3104,16 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2">
-        <v>46315.95833333334</v>
+        <v>46319.95833333334</v>
       </c>
       <c r="B94">
-        <v>0</v>
+        <v>37.551</v>
       </c>
       <c r="C94">
-        <v>14.45</v>
+        <v>0</v>
       </c>
       <c r="D94">
-        <v>43.25</v>
+        <v>0</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3139,13 +3127,13 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2">
-        <v>46315.96875</v>
+        <v>46319.96875</v>
       </c>
       <c r="B95">
-        <v>0</v>
+        <v>45.497</v>
       </c>
       <c r="C95">
-        <v>6.406</v>
+        <v>0</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3162,13 +3150,13 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2">
-        <v>46315.97916666666</v>
+        <v>46319.97916666666</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>30.351</v>
       </c>
       <c r="C96">
-        <v>10.597</v>
+        <v>0</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3185,13 +3173,13 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2">
-        <v>46315.98958333334</v>
+        <v>46319.98958333334</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>16.042</v>
       </c>
       <c r="C97">
-        <v>16.641</v>
+        <v>0</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3208,13 +3196,13 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="B98">
-        <v>5.706</v>
+        <v>13.665</v>
       </c>
       <c r="C98">
-        <v>4.145</v>
+        <v>0</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3231,13 +3219,13 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2">
-        <v>46316.01041666666</v>
+        <v>46320.01041666666</v>
       </c>
       <c r="B99">
-        <v>0.062</v>
+        <v>24.286</v>
       </c>
       <c r="C99">
-        <v>1.966</v>
+        <v>0</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -3254,13 +3242,13 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2">
-        <v>46316.02083333334</v>
+        <v>46320.02083333334</v>
       </c>
       <c r="B100">
-        <v>0.446</v>
+        <v>4.557</v>
       </c>
       <c r="C100">
-        <v>0.979</v>
+        <v>0</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -3277,13 +3265,13 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2">
-        <v>46316.03125</v>
+        <v>46320.03125</v>
       </c>
       <c r="B101">
-        <v>7.897</v>
+        <v>1.759</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>1.675</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -3300,13 +3288,13 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2">
-        <v>46316.04166666666</v>
+        <v>46320.04166666666</v>
       </c>
       <c r="B102">
-        <v>3.743</v>
+        <v>20.419</v>
       </c>
       <c r="C102">
-        <v>0.049</v>
+        <v>0.146</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3323,13 +3311,13 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2">
-        <v>46316.05208333334</v>
+        <v>46320.05208333334</v>
       </c>
       <c r="B103">
-        <v>0.496</v>
+        <v>12.89</v>
       </c>
       <c r="C103">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -3346,10 +3334,10 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2">
-        <v>46316.0625</v>
+        <v>46320.0625</v>
       </c>
       <c r="B104">
-        <v>3.12</v>
+        <v>9.837999999999999</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -3369,10 +3357,10 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2">
-        <v>46316.07291666666</v>
+        <v>46320.07291666666</v>
       </c>
       <c r="B105">
-        <v>12.075</v>
+        <v>0</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -3392,10 +3380,10 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2">
-        <v>46316.08333333334</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B106">
-        <v>17.108</v>
+        <v>0</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -3415,309 +3403,309 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2">
-        <v>46316.09375</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B107">
-        <v>0.183</v>
+        <v>21.206</v>
       </c>
       <c r="C107">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="D107">
-        <v>47.75</v>
+        <v>0</v>
       </c>
       <c r="E107">
         <v>0</v>
       </c>
       <c r="F107">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G107" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2">
-        <v>46316.10416666666</v>
+        <v>46320.09375</v>
       </c>
       <c r="B108">
-        <v>0.889</v>
+        <v>0</v>
       </c>
       <c r="C108">
-        <v>0.912</v>
+        <v>0</v>
       </c>
       <c r="D108">
-        <v>47.75</v>
+        <v>0</v>
       </c>
       <c r="E108">
         <v>0</v>
       </c>
       <c r="F108">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G108" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2">
-        <v>46316.11458333334</v>
+        <v>46320.09375</v>
       </c>
       <c r="B109">
-        <v>0.143</v>
+        <v>19.311</v>
       </c>
       <c r="C109">
-        <v>1.982</v>
+        <v>0</v>
       </c>
       <c r="D109">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E109">
         <v>0</v>
       </c>
       <c r="F109">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G109" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2">
-        <v>46316.125</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B110">
-        <v>0.506</v>
+        <v>0</v>
       </c>
       <c r="C110">
-        <v>0.089</v>
+        <v>0</v>
       </c>
       <c r="D110">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E110">
         <v>0</v>
       </c>
       <c r="F110">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G110" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2">
-        <v>46316.13541666666</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B111">
-        <v>25.097</v>
+        <v>19.468</v>
       </c>
       <c r="C111">
         <v>0</v>
       </c>
       <c r="D111">
-        <v>30.5</v>
+        <v>0</v>
       </c>
       <c r="E111">
         <v>0</v>
       </c>
       <c r="F111">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G111" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <v>46316.14583333334</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B112">
-        <v>7.911</v>
+        <v>6.306</v>
       </c>
       <c r="C112">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E112">
         <v>0</v>
       </c>
       <c r="F112">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G112" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2">
-        <v>46316.15625</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B113">
-        <v>0.051</v>
+        <v>0</v>
       </c>
       <c r="C113">
-        <v>0.472</v>
+        <v>0</v>
       </c>
       <c r="D113">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E113">
         <v>0</v>
       </c>
       <c r="F113">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G113" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2">
-        <v>46316.16666666666</v>
+        <v>46320.125</v>
       </c>
       <c r="B114">
-        <v>10.817</v>
+        <v>17.171</v>
       </c>
       <c r="C114">
         <v>0</v>
       </c>
       <c r="D114">
-        <v>30.5</v>
+        <v>0</v>
       </c>
       <c r="E114">
         <v>0</v>
       </c>
       <c r="F114">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G114" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2">
-        <v>46316.17708333334</v>
+        <v>46320.13541666666</v>
       </c>
       <c r="B115">
-        <v>0.512</v>
+        <v>24.171</v>
       </c>
       <c r="C115">
-        <v>0.171</v>
+        <v>0</v>
       </c>
       <c r="D115">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E115">
         <v>0</v>
       </c>
       <c r="F115">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G115" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <v>46316.1875</v>
+        <v>46320.14583333334</v>
       </c>
       <c r="B116">
-        <v>0.188</v>
+        <v>28.253</v>
       </c>
       <c r="C116">
-        <v>0.308</v>
+        <v>0</v>
       </c>
       <c r="D116">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E116">
         <v>0</v>
       </c>
       <c r="F116">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G116" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <v>46316.19791666666</v>
+        <v>46320.15625</v>
       </c>
       <c r="B117">
-        <v>0.044</v>
+        <v>9.832000000000001</v>
       </c>
       <c r="C117">
-        <v>0.283</v>
+        <v>0</v>
       </c>
       <c r="D117">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E117">
         <v>0</v>
       </c>
       <c r="F117">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G117" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <v>46316.20833333334</v>
+        <v>46320.16666666666</v>
       </c>
       <c r="B118">
-        <v>0.028</v>
+        <v>16.359</v>
       </c>
       <c r="C118">
-        <v>4.472</v>
+        <v>0</v>
       </c>
       <c r="D118">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E118">
         <v>0</v>
       </c>
       <c r="F118">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G118" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <v>46316.21875</v>
+        <v>46320.17708333334</v>
       </c>
       <c r="B119">
-        <v>0.128</v>
+        <v>12.708</v>
       </c>
       <c r="C119">
-        <v>1.623</v>
+        <v>0</v>
       </c>
       <c r="D119">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E119">
         <v>0</v>
       </c>
       <c r="F119">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G119" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <v>46316.22916666666</v>
+        <v>46320.1875</v>
       </c>
       <c r="B120">
-        <v>36.495</v>
+        <v>9.157</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -3729,18 +3717,18 @@
         <v>0</v>
       </c>
       <c r="F120">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G120" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <v>46316.23958333334</v>
+        <v>46320.19791666666</v>
       </c>
       <c r="B121">
-        <v>36.702</v>
+        <v>13.527</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -3752,18 +3740,18 @@
         <v>0</v>
       </c>
       <c r="F121">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G121" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <v>46316.25</v>
+        <v>46320.20833333334</v>
       </c>
       <c r="B122">
-        <v>15.593</v>
+        <v>23.192</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -3775,18 +3763,18 @@
         <v>0</v>
       </c>
       <c r="F122">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G122" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <v>46316.26041666666</v>
+        <v>46320.21875</v>
       </c>
       <c r="B123">
-        <v>31.51</v>
+        <v>15.83</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -3798,18 +3786,18 @@
         <v>0</v>
       </c>
       <c r="F123">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G123" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <v>46316.27083333334</v>
+        <v>46320.22916666666</v>
       </c>
       <c r="B124">
-        <v>22.919</v>
+        <v>15.987</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -3821,21 +3809,21 @@
         <v>0</v>
       </c>
       <c r="F124">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G124" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <v>46316.28125</v>
+        <v>46320.23958333334</v>
       </c>
       <c r="B125">
-        <v>33.346</v>
+        <v>3.415</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -3844,21 +3832,21 @@
         <v>0</v>
       </c>
       <c r="F125">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G125" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <v>46316.29166666666</v>
+        <v>46320.25</v>
       </c>
       <c r="B126">
-        <v>3.439</v>
+        <v>25.992</v>
       </c>
       <c r="C126">
-        <v>2.015</v>
+        <v>0</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -3867,21 +3855,21 @@
         <v>0</v>
       </c>
       <c r="F126">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G126" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <v>46316.30208333334</v>
+        <v>46320.26041666666</v>
       </c>
       <c r="B127">
-        <v>2.85</v>
+        <v>5.68</v>
       </c>
       <c r="C127">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -3890,67 +3878,67 @@
         <v>0</v>
       </c>
       <c r="F127">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G127" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <v>46316.3125</v>
+        <v>46320.27083333334</v>
       </c>
       <c r="B128">
-        <v>1.046</v>
+        <v>0.168</v>
       </c>
       <c r="C128">
-        <v>1.075</v>
+        <v>1.567</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E128">
         <v>0</v>
       </c>
       <c r="F128">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G128" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <v>46316.32291666666</v>
+        <v>46320.28125</v>
       </c>
       <c r="B129">
-        <v>0.113</v>
+        <v>0.016</v>
       </c>
       <c r="C129">
-        <v>2.033</v>
+        <v>4.729</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E129">
         <v>0</v>
       </c>
       <c r="F129">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G129" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <v>46316.33333333334</v>
+        <v>46320.29166666666</v>
       </c>
       <c r="B130">
-        <v>16.105</v>
+        <v>0.503</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>0.237</v>
       </c>
       <c r="D130">
         <v>0</v>
@@ -3959,21 +3947,21 @@
         <v>0</v>
       </c>
       <c r="F130">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G130" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <v>46316.34375</v>
+        <v>46320.30208333334</v>
       </c>
       <c r="B131">
-        <v>26.328</v>
+        <v>0</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>6.168</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -3982,107 +3970,107 @@
         <v>0</v>
       </c>
       <c r="F131">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G131" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <v>46316.35416666666</v>
+        <v>46320.3125</v>
       </c>
       <c r="B132">
-        <v>23.555</v>
+        <v>0.027</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>0.597</v>
       </c>
       <c r="D132">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E132">
         <v>0</v>
       </c>
       <c r="F132">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G132" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <v>46316.36458333334</v>
+        <v>46320.32291666666</v>
       </c>
       <c r="B133">
-        <v>27.931</v>
+        <v>0.398</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>0.122</v>
       </c>
       <c r="D133">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E133">
         <v>0</v>
       </c>
       <c r="F133">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G133" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <v>46316.375</v>
+        <v>46320.33333333334</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>0.524</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="D134">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="E134">
         <v>0</v>
       </c>
       <c r="F134">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G134" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <v>46316.38541666666</v>
+        <v>46320.34375</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>9.474</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>0.256</v>
       </c>
       <c r="D135">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E135">
         <v>0</v>
       </c>
       <c r="F135">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G135" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <v>46316.39583333334</v>
+        <v>46320.35416666666</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -4097,15 +4085,15 @@
         <v>0</v>
       </c>
       <c r="F136">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G136" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <v>46316.40625</v>
+        <v>46320.36458333334</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -4120,15 +4108,15 @@
         <v>0</v>
       </c>
       <c r="F137">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G137" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <v>46316.41666666666</v>
+        <v>46320.375</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -4143,15 +4131,15 @@
         <v>0</v>
       </c>
       <c r="F138">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G138" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <v>46316.42708333334</v>
+        <v>46320.38541666666</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -4166,15 +4154,15 @@
         <v>0</v>
       </c>
       <c r="F139">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G139" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <v>46316.4375</v>
+        <v>46320.39583333334</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -4189,15 +4177,15 @@
         <v>0</v>
       </c>
       <c r="F140">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G140" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <v>46316.44791666666</v>
+        <v>46320.40625</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -4212,15 +4200,15 @@
         <v>0</v>
       </c>
       <c r="F141">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G141" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <v>46316.45833333334</v>
+        <v>46320.41666666666</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -4235,15 +4223,15 @@
         <v>0</v>
       </c>
       <c r="F142">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G142" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <v>46316.46875</v>
+        <v>46320.42708333334</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -4258,15 +4246,15 @@
         <v>0</v>
       </c>
       <c r="F143">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G143" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <v>46316.47916666666</v>
+        <v>46320.4375</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -4281,15 +4269,15 @@
         <v>0</v>
       </c>
       <c r="F144">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G144" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <v>46316.48958333334</v>
+        <v>46320.44791666666</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -4304,15 +4292,15 @@
         <v>0</v>
       </c>
       <c r="F145">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G145" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <v>46316.5</v>
+        <v>46320.45833333334</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -4327,15 +4315,15 @@
         <v>0</v>
       </c>
       <c r="F146">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G146" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <v>46316.51041666666</v>
+        <v>46320.46875</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -4350,15 +4338,15 @@
         <v>0</v>
       </c>
       <c r="F147">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G147" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2">
-        <v>46316.52083333334</v>
+        <v>46320.47916666666</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -4373,15 +4361,15 @@
         <v>0</v>
       </c>
       <c r="F148">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G148" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2">
-        <v>46316.53125</v>
+        <v>46320.48958333334</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -4396,15 +4384,15 @@
         <v>0</v>
       </c>
       <c r="F149">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G149" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2">
-        <v>46316.54166666666</v>
+        <v>46320.5</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -4419,15 +4407,15 @@
         <v>0</v>
       </c>
       <c r="F150">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G150" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2">
-        <v>46316.55208333334</v>
+        <v>46320.51041666666</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -4442,15 +4430,15 @@
         <v>0</v>
       </c>
       <c r="F151">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G151" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2">
-        <v>46316.5625</v>
+        <v>46320.52083333334</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4465,15 +4453,15 @@
         <v>0</v>
       </c>
       <c r="F152">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G152" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2">
-        <v>46316.57291666666</v>
+        <v>46320.53125</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4488,15 +4476,15 @@
         <v>0</v>
       </c>
       <c r="F153">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G153" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2">
-        <v>46316.58333333334</v>
+        <v>46320.54166666666</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4511,15 +4499,15 @@
         <v>0</v>
       </c>
       <c r="F154">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G154" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2">
-        <v>46316.59375</v>
+        <v>46320.55208333334</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4534,15 +4522,15 @@
         <v>0</v>
       </c>
       <c r="F155">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G155" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2">
-        <v>46316.60416666666</v>
+        <v>46320.5625</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4557,15 +4545,15 @@
         <v>0</v>
       </c>
       <c r="F156">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G156" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2">
-        <v>46316.61458333334</v>
+        <v>46320.57291666666</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4580,15 +4568,15 @@
         <v>0</v>
       </c>
       <c r="F157">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G157" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2">
-        <v>46316.625</v>
+        <v>46320.58333333334</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4603,15 +4591,15 @@
         <v>0</v>
       </c>
       <c r="F158">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G158" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2">
-        <v>46316.63541666666</v>
+        <v>46320.59375</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4626,15 +4614,15 @@
         <v>0</v>
       </c>
       <c r="F159">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G159" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2">
-        <v>46316.64583333334</v>
+        <v>46320.60416666666</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4649,15 +4637,15 @@
         <v>0</v>
       </c>
       <c r="F160">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G160" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2">
-        <v>46316.65625</v>
+        <v>46320.61458333334</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4672,15 +4660,15 @@
         <v>0</v>
       </c>
       <c r="F161">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G161" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2">
-        <v>46316.66666666666</v>
+        <v>46320.625</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4695,15 +4683,15 @@
         <v>0</v>
       </c>
       <c r="F162">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G162" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2">
-        <v>46316.67708333334</v>
+        <v>46320.63541666666</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4718,15 +4706,15 @@
         <v>0</v>
       </c>
       <c r="F163">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G163" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2">
-        <v>46316.6875</v>
+        <v>46320.64583333334</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4741,15 +4729,15 @@
         <v>0</v>
       </c>
       <c r="F164">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G164" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2">
-        <v>46316.69791666666</v>
+        <v>46320.65625</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4764,15 +4752,15 @@
         <v>0</v>
       </c>
       <c r="F165">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G165" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2">
-        <v>46316.70833333334</v>
+        <v>46320.66666666666</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4787,15 +4775,15 @@
         <v>0</v>
       </c>
       <c r="F166">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G166" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2">
-        <v>46316.71875</v>
+        <v>46320.67708333334</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4810,15 +4798,15 @@
         <v>0</v>
       </c>
       <c r="F167">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G167" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2">
-        <v>46316.72916666666</v>
+        <v>46320.6875</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4833,15 +4821,15 @@
         <v>0</v>
       </c>
       <c r="F168">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G168" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2">
-        <v>46316.73958333334</v>
+        <v>46320.69791666666</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4856,15 +4844,15 @@
         <v>0</v>
       </c>
       <c r="F169">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G169" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2">
-        <v>46316.75</v>
+        <v>46320.70833333334</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4879,15 +4867,15 @@
         <v>0</v>
       </c>
       <c r="F170">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G170" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
-        <v>46316.76041666666</v>
+        <v>46320.71875</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4902,15 +4890,15 @@
         <v>0</v>
       </c>
       <c r="F171">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G171" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
-        <v>46316.77083333334</v>
+        <v>46320.72916666666</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4925,15 +4913,15 @@
         <v>0</v>
       </c>
       <c r="F172">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G172" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
-        <v>46316.78125</v>
+        <v>46320.73958333334</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4948,15 +4936,15 @@
         <v>0</v>
       </c>
       <c r="F173">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G173" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
-        <v>46316.79166666666</v>
+        <v>46320.75</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4971,15 +4959,15 @@
         <v>0</v>
       </c>
       <c r="F174">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G174" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
-        <v>46316.80208333334</v>
+        <v>46320.76041666666</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4994,15 +4982,15 @@
         <v>0</v>
       </c>
       <c r="F175">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G175" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
-        <v>46316.8125</v>
+        <v>46320.77083333334</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -5017,15 +5005,15 @@
         <v>0</v>
       </c>
       <c r="F176">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G176" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2">
-        <v>46316.82291666666</v>
+        <v>46320.78125</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -5040,15 +5028,15 @@
         <v>0</v>
       </c>
       <c r="F177">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G177" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2">
-        <v>46316.83333333334</v>
+        <v>46320.79166666666</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -5063,15 +5051,15 @@
         <v>0</v>
       </c>
       <c r="F178">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G178" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2">
-        <v>46316.84375</v>
+        <v>46320.80208333334</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -5086,15 +5074,15 @@
         <v>0</v>
       </c>
       <c r="F179">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G179" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2">
-        <v>46316.85416666666</v>
+        <v>46320.8125</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -5109,15 +5097,15 @@
         <v>0</v>
       </c>
       <c r="F180">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G180" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="2">
-        <v>46316.86458333334</v>
+        <v>46320.82291666666</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -5132,15 +5120,15 @@
         <v>0</v>
       </c>
       <c r="F181">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G181" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <v>46316.875</v>
+        <v>46320.83333333334</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -5155,15 +5143,15 @@
         <v>0</v>
       </c>
       <c r="F182">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G182" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <v>46316.88541666666</v>
+        <v>46320.84375</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -5178,15 +5166,15 @@
         <v>0</v>
       </c>
       <c r="F183">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G183" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <v>46316.89583333334</v>
+        <v>46320.85416666666</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -5201,15 +5189,15 @@
         <v>0</v>
       </c>
       <c r="F184">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G184" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <v>46316.90625</v>
+        <v>46320.86458333334</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -5224,15 +5212,15 @@
         <v>0</v>
       </c>
       <c r="F185">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G185" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <v>46316.91666666666</v>
+        <v>46320.875</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -5247,15 +5235,15 @@
         <v>0</v>
       </c>
       <c r="F186">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G186" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <v>46316.92708333334</v>
+        <v>46320.88541666666</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -5270,15 +5258,15 @@
         <v>0</v>
       </c>
       <c r="F187">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G187" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <v>46316.9375</v>
+        <v>46320.89583333334</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -5293,15 +5281,15 @@
         <v>0</v>
       </c>
       <c r="F188">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G188" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <v>46316.94791666666</v>
+        <v>46320.90625</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -5316,15 +5304,15 @@
         <v>0</v>
       </c>
       <c r="F189">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G189" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <v>46316.95833333334</v>
+        <v>46320.91666666666</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -5339,15 +5327,15 @@
         <v>0</v>
       </c>
       <c r="F190">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G190" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <v>46316.96875</v>
+        <v>46320.92708333334</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -5362,15 +5350,15 @@
         <v>0</v>
       </c>
       <c r="F191">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G191" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <v>46316.97916666666</v>
+        <v>46320.9375</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -5385,15 +5373,15 @@
         <v>0</v>
       </c>
       <c r="F192">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G192" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <v>46316.98958333334</v>
+        <v>46320.94791666666</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -5408,10 +5396,10 @@
         <v>0</v>
       </c>
       <c r="F193">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G193" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
